--- a/data/FF.MI.xlsx
+++ b/data/FF.MI.xlsx
@@ -58182,7 +58182,7 @@
         <v>7.1399998664856</v>
       </c>
       <c r="D2514" t="n">
-        <v>6.92000007629395</v>
+        <v>6.8600001335144</v>
       </c>
       <c r="E2514" t="n">
         <v>7.01999998092651</v>
@@ -58191,6 +58191,29 @@
         <v>6.8600001335144</v>
       </c>
       <c r="G2514" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2515">
+      <c r="A2515" s="1" t="n">
+        <v>46279.2916666667</v>
+      </c>
+      <c r="B2515" t="n">
+        <v>27618</v>
+      </c>
+      <c r="C2515" t="n">
+        <v>7.07999992370605</v>
+      </c>
+      <c r="D2515" t="n">
+        <v>6.94000005722046</v>
+      </c>
+      <c r="E2515" t="n">
+        <v>7</v>
+      </c>
+      <c r="F2515" t="n">
+        <v>6.98000001907349</v>
+      </c>
+      <c r="G2515" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/FF.MI.xlsx
+++ b/data/FF.MI.xlsx
@@ -58217,6 +58217,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="2516">
+      <c r="A2516" s="1" t="n">
+        <v>46280.2916666667</v>
+      </c>
+      <c r="B2516" t="n">
+        <v>26771</v>
+      </c>
+      <c r="C2516" t="n">
+        <v>7.05999994277954</v>
+      </c>
+      <c r="D2516" t="n">
+        <v>6.92000007629395</v>
+      </c>
+      <c r="E2516" t="n">
+        <v>6.98000001907349</v>
+      </c>
+      <c r="F2516" t="n">
+        <v>6.92000007629395</v>
+      </c>
+      <c r="G2516" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/FF.MI.xlsx
+++ b/data/FF.MI.xlsx
@@ -58240,6 +58240,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="2517">
+      <c r="A2517" s="1" t="n">
+        <v>46281.2916666667</v>
+      </c>
+      <c r="B2517" t="n">
+        <v>13334</v>
+      </c>
+      <c r="C2517" t="n">
+        <v>7.01999998092651</v>
+      </c>
+      <c r="D2517" t="n">
+        <v>6.88000011444092</v>
+      </c>
+      <c r="E2517" t="n">
+        <v>7</v>
+      </c>
+      <c r="F2517" t="n">
+        <v>6.94000005722046</v>
+      </c>
+      <c r="G2517" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/FF.MI.xlsx
+++ b/data/FF.MI.xlsx
@@ -58263,6 +58263,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="2518">
+      <c r="A2518" s="1" t="n">
+        <v>46282.2916666667</v>
+      </c>
+      <c r="B2518" t="n">
+        <v>35146</v>
+      </c>
+      <c r="C2518" t="n">
+        <v>7.17999982833862</v>
+      </c>
+      <c r="D2518" t="n">
+        <v>6.94000005722046</v>
+      </c>
+      <c r="E2518" t="n">
+        <v>6.94000005722046</v>
+      </c>
+      <c r="F2518" t="n">
+        <v>7.09999990463257</v>
+      </c>
+      <c r="G2518" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/FF.MI.xlsx
+++ b/data/FF.MI.xlsx
@@ -58104,22 +58104,22 @@
     </row>
     <row r="2511">
       <c r="A2511" s="1" t="n">
-        <v>46273.2916666667</v>
+        <v>46272.2916666667</v>
       </c>
       <c r="B2511" t="n">
-        <v>135841</v>
+        <v>40098</v>
       </c>
       <c r="C2511" t="n">
-        <v>8.34000015258789</v>
+        <v>8.31999969482422</v>
       </c>
       <c r="D2511" t="n">
-        <v>7.40000009536743</v>
+        <v>8.0600004196167</v>
       </c>
       <c r="E2511" t="n">
-        <v>8.15999984741211</v>
+        <v>8.30000019073486</v>
       </c>
       <c r="F2511" t="n">
-        <v>7.48000001907349</v>
+        <v>8.26000022888184</v>
       </c>
       <c r="G2511" t="s">
         <v>7</v>
@@ -58127,22 +58127,22 @@
     </row>
     <row r="2512">
       <c r="A2512" s="1" t="n">
-        <v>46274.2916666667</v>
+        <v>46273.2916666667</v>
       </c>
       <c r="B2512" t="n">
-        <v>171384</v>
+        <v>135841</v>
       </c>
       <c r="C2512" t="n">
-        <v>7.57999992370605</v>
+        <v>8.34000015258789</v>
       </c>
       <c r="D2512" t="n">
-        <v>7.1399998664856</v>
+        <v>7.40000009536743</v>
       </c>
       <c r="E2512" t="n">
+        <v>8.15999984741211</v>
+      </c>
+      <c r="F2512" t="n">
         <v>7.48000001907349</v>
-      </c>
-      <c r="F2512" t="n">
-        <v>7.32000017166138</v>
       </c>
       <c r="G2512" t="s">
         <v>7</v>
@@ -58150,22 +58150,22 @@
     </row>
     <row r="2513">
       <c r="A2513" s="1" t="n">
-        <v>46275.2916666667</v>
+        <v>46274.2916666667</v>
       </c>
       <c r="B2513" t="n">
-        <v>57697</v>
+        <v>171384</v>
       </c>
       <c r="C2513" t="n">
-        <v>7.34000015258789</v>
+        <v>7.57999992370605</v>
       </c>
       <c r="D2513" t="n">
-        <v>7.03999996185303</v>
+        <v>7.1399998664856</v>
       </c>
       <c r="E2513" t="n">
-        <v>7.26000022888184</v>
+        <v>7.48000001907349</v>
       </c>
       <c r="F2513" t="n">
-        <v>7.03999996185303</v>
+        <v>7.32000017166138</v>
       </c>
       <c r="G2513" t="s">
         <v>7</v>
@@ -58173,22 +58173,22 @@
     </row>
     <row r="2514">
       <c r="A2514" s="1" t="n">
-        <v>46276.2916666667</v>
+        <v>46275.2916666667</v>
       </c>
       <c r="B2514" t="n">
-        <v>43545</v>
+        <v>57697</v>
       </c>
       <c r="C2514" t="n">
-        <v>7.1399998664856</v>
+        <v>7.34000015258789</v>
       </c>
       <c r="D2514" t="n">
-        <v>6.8600001335144</v>
+        <v>7.03999996185303</v>
       </c>
       <c r="E2514" t="n">
-        <v>7.01999998092651</v>
+        <v>7.26000022888184</v>
       </c>
       <c r="F2514" t="n">
-        <v>6.8600001335144</v>
+        <v>7.03999996185303</v>
       </c>
       <c r="G2514" t="s">
         <v>7</v>
@@ -58196,22 +58196,22 @@
     </row>
     <row r="2515">
       <c r="A2515" s="1" t="n">
-        <v>46279.2916666667</v>
+        <v>46276.2916666667</v>
       </c>
       <c r="B2515" t="n">
-        <v>27618</v>
+        <v>43545</v>
       </c>
       <c r="C2515" t="n">
-        <v>7.07999992370605</v>
+        <v>7.1399998664856</v>
       </c>
       <c r="D2515" t="n">
-        <v>6.94000005722046</v>
+        <v>6.8600001335144</v>
       </c>
       <c r="E2515" t="n">
-        <v>7</v>
+        <v>7.01999998092651</v>
       </c>
       <c r="F2515" t="n">
-        <v>6.98000001907349</v>
+        <v>6.8600001335144</v>
       </c>
       <c r="G2515" t="s">
         <v>7</v>
@@ -58219,22 +58219,22 @@
     </row>
     <row r="2516">
       <c r="A2516" s="1" t="n">
-        <v>46280.2916666667</v>
+        <v>46279.2916666667</v>
       </c>
       <c r="B2516" t="n">
-        <v>26771</v>
+        <v>27618</v>
       </c>
       <c r="C2516" t="n">
-        <v>7.05999994277954</v>
+        <v>7.07999992370605</v>
       </c>
       <c r="D2516" t="n">
-        <v>6.92000007629395</v>
+        <v>6.94000005722046</v>
       </c>
       <c r="E2516" t="n">
+        <v>7</v>
+      </c>
+      <c r="F2516" t="n">
         <v>6.98000001907349</v>
-      </c>
-      <c r="F2516" t="n">
-        <v>6.92000007629395</v>
       </c>
       <c r="G2516" t="s">
         <v>7</v>
@@ -58242,22 +58242,22 @@
     </row>
     <row r="2517">
       <c r="A2517" s="1" t="n">
-        <v>46281.2916666667</v>
+        <v>46280.2916666667</v>
       </c>
       <c r="B2517" t="n">
-        <v>13334</v>
+        <v>26771</v>
       </c>
       <c r="C2517" t="n">
-        <v>7.01999998092651</v>
+        <v>7.05999994277954</v>
       </c>
       <c r="D2517" t="n">
-        <v>6.88000011444092</v>
+        <v>6.92000007629395</v>
       </c>
       <c r="E2517" t="n">
-        <v>7</v>
+        <v>6.98000001907349</v>
       </c>
       <c r="F2517" t="n">
-        <v>6.94000005722046</v>
+        <v>6.92000007629395</v>
       </c>
       <c r="G2517" t="s">
         <v>7</v>
@@ -58265,24 +58265,47 @@
     </row>
     <row r="2518">
       <c r="A2518" s="1" t="n">
-        <v>46282.2916666667</v>
+        <v>46281.2916666667</v>
       </c>
       <c r="B2518" t="n">
-        <v>35146</v>
+        <v>13334</v>
       </c>
       <c r="C2518" t="n">
+        <v>7.01999998092651</v>
+      </c>
+      <c r="D2518" t="n">
+        <v>6.88000011444092</v>
+      </c>
+      <c r="E2518" t="n">
+        <v>7</v>
+      </c>
+      <c r="F2518" t="n">
+        <v>6.94000005722046</v>
+      </c>
+      <c r="G2518" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2519">
+      <c r="A2519" s="1" t="n">
+        <v>46283.2916666667</v>
+      </c>
+      <c r="B2519" t="n">
+        <v>45232</v>
+      </c>
+      <c r="C2519" t="n">
         <v>7.17999982833862</v>
       </c>
-      <c r="D2518" t="n">
-        <v>6.94000005722046</v>
-      </c>
-      <c r="E2518" t="n">
-        <v>6.94000005722046</v>
-      </c>
-      <c r="F2518" t="n">
+      <c r="D2519" t="n">
+        <v>7.07999992370605</v>
+      </c>
+      <c r="E2519" t="n">
         <v>7.09999990463257</v>
       </c>
-      <c r="G2518" t="s">
+      <c r="F2519" t="n">
+        <v>7.01999998092651</v>
+      </c>
+      <c r="G2519" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/FF.MI.xlsx
+++ b/data/FF.MI.xlsx
@@ -421,7 +421,7 @@
         <v>10</v>
       </c>
       <c r="G2" t="n">
-        <v>8.92192840576172</v>
+        <v>8.92192935943604</v>
       </c>
       <c r="H2" t="s">
         <v>8</v>
@@ -473,7 +473,7 @@
         <v>10</v>
       </c>
       <c r="G4" t="n">
-        <v>8.92192840576172</v>
+        <v>8.92192935943604</v>
       </c>
       <c r="H4" t="s">
         <v>8</v>
@@ -499,7 +499,7 @@
         <v>10</v>
       </c>
       <c r="G5" t="n">
-        <v>8.92192840576172</v>
+        <v>8.92192935943604</v>
       </c>
       <c r="H5" t="s">
         <v>8</v>
@@ -525,7 +525,7 @@
         <v>10</v>
       </c>
       <c r="G6" t="n">
-        <v>8.92192840576172</v>
+        <v>8.92192935943604</v>
       </c>
       <c r="H6" t="s">
         <v>8</v>
@@ -551,7 +551,7 @@
         <v>10</v>
       </c>
       <c r="G7" t="n">
-        <v>8.92192840576172</v>
+        <v>8.92192935943604</v>
       </c>
       <c r="H7" t="s">
         <v>8</v>
@@ -629,7 +629,7 @@
         <v>10</v>
       </c>
       <c r="G10" t="n">
-        <v>8.92192840576172</v>
+        <v>8.92192935943604</v>
       </c>
       <c r="H10" t="s">
         <v>8</v>
@@ -655,7 +655,7 @@
         <v>10</v>
       </c>
       <c r="G11" t="n">
-        <v>8.92192840576172</v>
+        <v>8.92192935943604</v>
       </c>
       <c r="H11" t="s">
         <v>8</v>
@@ -681,7 +681,7 @@
         <v>10</v>
       </c>
       <c r="G12" t="n">
-        <v>8.92192840576172</v>
+        <v>8.92192935943604</v>
       </c>
       <c r="H12" t="s">
         <v>8</v>
@@ -707,7 +707,7 @@
         <v>10</v>
       </c>
       <c r="G13" t="n">
-        <v>8.92192840576172</v>
+        <v>8.92192935943604</v>
       </c>
       <c r="H13" t="s">
         <v>8</v>
@@ -733,7 +733,7 @@
         <v>10</v>
       </c>
       <c r="G14" t="n">
-        <v>8.92192840576172</v>
+        <v>8.92192935943604</v>
       </c>
       <c r="H14" t="s">
         <v>8</v>
@@ -811,7 +811,7 @@
         <v>10.0200004577637</v>
       </c>
       <c r="G17" t="n">
-        <v>8.93977355957031</v>
+        <v>8.93977451324463</v>
       </c>
       <c r="H17" t="s">
         <v>8</v>
@@ -967,7 +967,7 @@
         <v>9.86499977111816</v>
       </c>
       <c r="G23" t="n">
-        <v>8.80148220062256</v>
+        <v>8.80148410797119</v>
       </c>
       <c r="H23" t="s">
         <v>8</v>
@@ -993,7 +993,7 @@
         <v>9.86499977111816</v>
       </c>
       <c r="G24" t="n">
-        <v>8.80148220062256</v>
+        <v>8.80148410797119</v>
       </c>
       <c r="H24" t="s">
         <v>8</v>
@@ -1019,7 +1019,7 @@
         <v>9.86499977111816</v>
       </c>
       <c r="G25" t="n">
-        <v>8.80148220062256</v>
+        <v>8.80148410797119</v>
       </c>
       <c r="H25" t="s">
         <v>8</v>
@@ -1045,7 +1045,7 @@
         <v>10</v>
       </c>
       <c r="G26" t="n">
-        <v>8.92192840576172</v>
+        <v>8.92192935943604</v>
       </c>
       <c r="H26" t="s">
         <v>8</v>
@@ -1643,7 +1643,7 @@
         <v>10</v>
       </c>
       <c r="G49" t="n">
-        <v>8.92192840576172</v>
+        <v>8.92192935943604</v>
       </c>
       <c r="H49" t="s">
         <v>8</v>
@@ -1669,7 +1669,7 @@
         <v>10</v>
       </c>
       <c r="G50" t="n">
-        <v>8.92192840576172</v>
+        <v>8.92192935943604</v>
       </c>
       <c r="H50" t="s">
         <v>8</v>
@@ -2085,7 +2085,7 @@
         <v>9.76000022888184</v>
       </c>
       <c r="G66" t="n">
-        <v>8.70780467987061</v>
+        <v>8.70780277252197</v>
       </c>
       <c r="H66" t="s">
         <v>8</v>
@@ -2111,7 +2111,7 @@
         <v>9.76000022888184</v>
       </c>
       <c r="G67" t="n">
-        <v>8.70780467987061</v>
+        <v>8.70780277252197</v>
       </c>
       <c r="H67" t="s">
         <v>8</v>
@@ -2605,7 +2605,7 @@
         <v>9.97000026702881</v>
       </c>
       <c r="G86" t="n">
-        <v>8.89516258239746</v>
+        <v>8.89516448974609</v>
       </c>
       <c r="H86" t="s">
         <v>8</v>
@@ -2631,7 +2631,7 @@
         <v>9.97000026702881</v>
       </c>
       <c r="G87" t="n">
-        <v>8.89516258239746</v>
+        <v>8.89516448974609</v>
       </c>
       <c r="H87" t="s">
         <v>8</v>
@@ -2657,7 +2657,7 @@
         <v>9.97000026702881</v>
       </c>
       <c r="G88" t="n">
-        <v>8.89516258239746</v>
+        <v>8.89516448974609</v>
       </c>
       <c r="H88" t="s">
         <v>8</v>
@@ -2683,7 +2683,7 @@
         <v>9.97000026702881</v>
       </c>
       <c r="G89" t="n">
-        <v>8.89516258239746</v>
+        <v>8.89516448974609</v>
       </c>
       <c r="H89" t="s">
         <v>8</v>
@@ -2709,7 +2709,7 @@
         <v>9.97000026702881</v>
       </c>
       <c r="G90" t="n">
-        <v>8.89516258239746</v>
+        <v>8.89516448974609</v>
       </c>
       <c r="H90" t="s">
         <v>8</v>
@@ -2735,7 +2735,7 @@
         <v>9.97000026702881</v>
       </c>
       <c r="G91" t="n">
-        <v>8.89516258239746</v>
+        <v>8.89516448974609</v>
       </c>
       <c r="H91" t="s">
         <v>8</v>
@@ -2761,7 +2761,7 @@
         <v>9.97000026702881</v>
       </c>
       <c r="G92" t="n">
-        <v>8.89516258239746</v>
+        <v>8.89516448974609</v>
       </c>
       <c r="H92" t="s">
         <v>8</v>
@@ -2787,7 +2787,7 @@
         <v>10.1700000762939</v>
       </c>
       <c r="G93" t="n">
-        <v>9.07360172271729</v>
+        <v>9.07360363006592</v>
       </c>
       <c r="H93" t="s">
         <v>8</v>
@@ -2813,7 +2813,7 @@
         <v>10.1700000762939</v>
       </c>
       <c r="G94" t="n">
-        <v>9.07360172271729</v>
+        <v>9.07360363006592</v>
       </c>
       <c r="H94" t="s">
         <v>8</v>
@@ -2839,7 +2839,7 @@
         <v>10.1700000762939</v>
       </c>
       <c r="G95" t="n">
-        <v>9.07360172271729</v>
+        <v>9.07360363006592</v>
       </c>
       <c r="H95" t="s">
         <v>8</v>
@@ -2865,7 +2865,7 @@
         <v>10.1700000762939</v>
       </c>
       <c r="G96" t="n">
-        <v>9.07360172271729</v>
+        <v>9.07360363006592</v>
       </c>
       <c r="H96" t="s">
         <v>8</v>
@@ -2891,7 +2891,7 @@
         <v>10.1700000762939</v>
       </c>
       <c r="G97" t="n">
-        <v>9.07360172271729</v>
+        <v>9.07360363006592</v>
       </c>
       <c r="H97" t="s">
         <v>8</v>
@@ -2917,7 +2917,7 @@
         <v>10.1700000762939</v>
       </c>
       <c r="G98" t="n">
-        <v>9.07360172271729</v>
+        <v>9.07360363006592</v>
       </c>
       <c r="H98" t="s">
         <v>8</v>
@@ -2943,7 +2943,7 @@
         <v>10.1700000762939</v>
       </c>
       <c r="G99" t="n">
-        <v>9.07360172271729</v>
+        <v>9.07360363006592</v>
       </c>
       <c r="H99" t="s">
         <v>8</v>
@@ -2969,7 +2969,7 @@
         <v>10.1700000762939</v>
       </c>
       <c r="G100" t="n">
-        <v>9.07360172271729</v>
+        <v>9.07360363006592</v>
       </c>
       <c r="H100" t="s">
         <v>8</v>
@@ -2995,7 +2995,7 @@
         <v>10.1700000762939</v>
       </c>
       <c r="G101" t="n">
-        <v>9.07360172271729</v>
+        <v>9.07360363006592</v>
       </c>
       <c r="H101" t="s">
         <v>8</v>
@@ -3073,7 +3073,7 @@
         <v>10</v>
       </c>
       <c r="G104" t="n">
-        <v>8.92192840576172</v>
+        <v>8.92192935943604</v>
       </c>
       <c r="H104" t="s">
         <v>8</v>
@@ -3099,7 +3099,7 @@
         <v>10</v>
       </c>
       <c r="G105" t="n">
-        <v>8.92192840576172</v>
+        <v>8.92192935943604</v>
       </c>
       <c r="H105" t="s">
         <v>8</v>
@@ -3229,7 +3229,7 @@
         <v>10</v>
       </c>
       <c r="G110" t="n">
-        <v>8.92192840576172</v>
+        <v>8.92192935943604</v>
       </c>
       <c r="H110" t="s">
         <v>8</v>
@@ -3255,7 +3255,7 @@
         <v>10</v>
       </c>
       <c r="G111" t="n">
-        <v>8.92192840576172</v>
+        <v>8.92192935943604</v>
       </c>
       <c r="H111" t="s">
         <v>8</v>
@@ -3281,7 +3281,7 @@
         <v>10</v>
       </c>
       <c r="G112" t="n">
-        <v>8.92192840576172</v>
+        <v>8.92192935943604</v>
       </c>
       <c r="H112" t="s">
         <v>8</v>
@@ -3359,7 +3359,7 @@
         <v>9.88000011444092</v>
       </c>
       <c r="G115" t="n">
-        <v>8.81486797332764</v>
+        <v>8.81486415863037</v>
       </c>
       <c r="H115" t="s">
         <v>8</v>
@@ -3385,7 +3385,7 @@
         <v>9.88000011444092</v>
       </c>
       <c r="G116" t="n">
-        <v>8.81486797332764</v>
+        <v>8.81486415863037</v>
       </c>
       <c r="H116" t="s">
         <v>8</v>
@@ -3411,7 +3411,7 @@
         <v>9.81999969482422</v>
       </c>
       <c r="G117" t="n">
-        <v>8.76133346557617</v>
+        <v>8.7613353729248</v>
       </c>
       <c r="H117" t="s">
         <v>8</v>
@@ -3437,7 +3437,7 @@
         <v>10</v>
       </c>
       <c r="G118" t="n">
-        <v>8.92192840576172</v>
+        <v>8.92192935943604</v>
       </c>
       <c r="H118" t="s">
         <v>8</v>
@@ -3463,7 +3463,7 @@
         <v>9.88000011444092</v>
       </c>
       <c r="G119" t="n">
-        <v>8.81486797332764</v>
+        <v>8.81486415863037</v>
       </c>
       <c r="H119" t="s">
         <v>8</v>
@@ -3489,7 +3489,7 @@
         <v>9.88000011444092</v>
       </c>
       <c r="G120" t="n">
-        <v>8.81486797332764</v>
+        <v>8.81486415863037</v>
       </c>
       <c r="H120" t="s">
         <v>8</v>
@@ -3593,7 +3593,7 @@
         <v>9.81999969482422</v>
       </c>
       <c r="G124" t="n">
-        <v>8.76133346557617</v>
+        <v>8.7613353729248</v>
       </c>
       <c r="H124" t="s">
         <v>8</v>
@@ -3619,7 +3619,7 @@
         <v>10</v>
       </c>
       <c r="G125" t="n">
-        <v>8.92192840576172</v>
+        <v>8.92192935943604</v>
       </c>
       <c r="H125" t="s">
         <v>8</v>
@@ -3671,7 +3671,7 @@
         <v>10</v>
       </c>
       <c r="G127" t="n">
-        <v>8.92192840576172</v>
+        <v>8.92192935943604</v>
       </c>
       <c r="H127" t="s">
         <v>8</v>
@@ -3697,7 +3697,7 @@
         <v>9.97000026702881</v>
       </c>
       <c r="G128" t="n">
-        <v>8.89516258239746</v>
+        <v>8.89516448974609</v>
       </c>
       <c r="H128" t="s">
         <v>8</v>
@@ -3723,7 +3723,7 @@
         <v>9.92000007629395</v>
       </c>
       <c r="G129" t="n">
-        <v>8.85055446624756</v>
+        <v>8.85055255889893</v>
       </c>
       <c r="H129" t="s">
         <v>8</v>
@@ -3801,7 +3801,7 @@
         <v>10</v>
       </c>
       <c r="G132" t="n">
-        <v>8.92192840576172</v>
+        <v>8.92192935943604</v>
       </c>
       <c r="H132" t="s">
         <v>8</v>
@@ -3905,7 +3905,7 @@
         <v>10.3999996185303</v>
       </c>
       <c r="G136" t="n">
-        <v>9.27880668640137</v>
+        <v>9.27880573272705</v>
       </c>
       <c r="H136" t="s">
         <v>8</v>
@@ -3931,7 +3931,7 @@
         <v>10.5200004577637</v>
       </c>
       <c r="G137" t="n">
-        <v>9.38587093353271</v>
+        <v>9.3858699798584</v>
       </c>
       <c r="H137" t="s">
         <v>8</v>
@@ -3957,7 +3957,7 @@
         <v>10.6000003814697</v>
       </c>
       <c r="G138" t="n">
-        <v>9.45724678039551</v>
+        <v>9.45724487304688</v>
       </c>
       <c r="H138" t="s">
         <v>8</v>
@@ -3983,7 +3983,7 @@
         <v>10.6000003814697</v>
       </c>
       <c r="G139" t="n">
-        <v>9.45724678039551</v>
+        <v>9.45724487304688</v>
       </c>
       <c r="H139" t="s">
         <v>8</v>
@@ -4009,7 +4009,7 @@
         <v>10.6000003814697</v>
       </c>
       <c r="G140" t="n">
-        <v>9.45724678039551</v>
+        <v>9.45724487304688</v>
       </c>
       <c r="H140" t="s">
         <v>8</v>
@@ -4113,7 +4113,7 @@
         <v>10.539999961853</v>
       </c>
       <c r="G144" t="n">
-        <v>9.40371227264404</v>
+        <v>9.40371322631836</v>
       </c>
       <c r="H144" t="s">
         <v>8</v>
@@ -4165,7 +4165,7 @@
         <v>10.5500001907349</v>
       </c>
       <c r="G146" t="n">
-        <v>9.41263580322266</v>
+        <v>9.41263484954834</v>
       </c>
       <c r="H146" t="s">
         <v>8</v>
@@ -4191,7 +4191,7 @@
         <v>10.6000003814697</v>
       </c>
       <c r="G147" t="n">
-        <v>9.45724678039551</v>
+        <v>9.45724487304688</v>
       </c>
       <c r="H147" t="s">
         <v>8</v>
@@ -4321,7 +4321,7 @@
         <v>10.5799999237061</v>
       </c>
       <c r="G152" t="n">
-        <v>9.43940162658691</v>
+        <v>9.4394006729126</v>
       </c>
       <c r="H152" t="s">
         <v>8</v>
@@ -4347,7 +4347,7 @@
         <v>10.5500001907349</v>
       </c>
       <c r="G153" t="n">
-        <v>9.41263580322266</v>
+        <v>9.41263484954834</v>
       </c>
       <c r="H153" t="s">
         <v>8</v>
@@ -4373,7 +4373,7 @@
         <v>10.6199998855591</v>
       </c>
       <c r="G154" t="n">
-        <v>9.47509002685547</v>
+        <v>9.47508811950684</v>
       </c>
       <c r="H154" t="s">
         <v>8</v>
@@ -4425,7 +4425,7 @@
         <v>10.6000003814697</v>
       </c>
       <c r="G156" t="n">
-        <v>9.45724678039551</v>
+        <v>9.45724487304688</v>
       </c>
       <c r="H156" t="s">
         <v>8</v>
@@ -4451,7 +4451,7 @@
         <v>10.789999961853</v>
       </c>
       <c r="G157" t="n">
-        <v>9.62676239013672</v>
+        <v>9.6267614364624</v>
       </c>
       <c r="H157" t="s">
         <v>8</v>
@@ -4477,7 +4477,7 @@
         <v>10.9700002670288</v>
       </c>
       <c r="G158" t="n">
-        <v>9.78735637664795</v>
+        <v>9.78735733032227</v>
       </c>
       <c r="H158" t="s">
         <v>8</v>
@@ -4555,7 +4555,7 @@
         <v>10.9499998092651</v>
       </c>
       <c r="G161" t="n">
-        <v>9.76951217651367</v>
+        <v>9.76951313018799</v>
       </c>
       <c r="H161" t="s">
         <v>8</v>
@@ -4633,7 +4633,7 @@
         <v>10.7600002288818</v>
       </c>
       <c r="G164" t="n">
-        <v>9.59999561309814</v>
+        <v>9.59999656677246</v>
       </c>
       <c r="H164" t="s">
         <v>8</v>
@@ -4737,7 +4737,7 @@
         <v>10.789999961853</v>
       </c>
       <c r="G168" t="n">
-        <v>9.62676239013672</v>
+        <v>9.6267614364624</v>
       </c>
       <c r="H168" t="s">
         <v>8</v>
@@ -4763,7 +4763,7 @@
         <v>10.6300001144409</v>
       </c>
       <c r="G169" t="n">
-        <v>9.48401165008545</v>
+        <v>9.48401260375977</v>
       </c>
       <c r="H169" t="s">
         <v>8</v>
@@ -4841,7 +4841,7 @@
         <v>10.8199996948242</v>
       </c>
       <c r="G172" t="n">
-        <v>9.65352821350098</v>
+        <v>9.65352630615234</v>
       </c>
       <c r="H172" t="s">
         <v>8</v>
@@ -4867,7 +4867,7 @@
         <v>10.6899995803833</v>
       </c>
       <c r="G173" t="n">
-        <v>9.53754138946533</v>
+        <v>9.53754234313965</v>
       </c>
       <c r="H173" t="s">
         <v>8</v>
@@ -4893,7 +4893,7 @@
         <v>10.710000038147</v>
       </c>
       <c r="G174" t="n">
-        <v>9.55538558959961</v>
+        <v>9.55538654327393</v>
       </c>
       <c r="H174" t="s">
         <v>8</v>
@@ -4971,7 +4971,7 @@
         <v>10.6599998474121</v>
       </c>
       <c r="G177" t="n">
-        <v>9.51077556610107</v>
+        <v>9.51077651977539</v>
       </c>
       <c r="H177" t="s">
         <v>8</v>
@@ -5101,7 +5101,7 @@
         <v>10.6199998855591</v>
       </c>
       <c r="G182" t="n">
-        <v>9.47509002685547</v>
+        <v>9.47508811950684</v>
       </c>
       <c r="H182" t="s">
         <v>8</v>
@@ -5127,7 +5127,7 @@
         <v>10.6400003433228</v>
       </c>
       <c r="G183" t="n">
-        <v>9.49293231964111</v>
+        <v>9.49293327331543</v>
       </c>
       <c r="H183" t="s">
         <v>8</v>
@@ -5153,7 +5153,7 @@
         <v>10.6000003814697</v>
       </c>
       <c r="G184" t="n">
-        <v>9.45724678039551</v>
+        <v>9.45724487304688</v>
       </c>
       <c r="H184" t="s">
         <v>8</v>
@@ -5179,7 +5179,7 @@
         <v>10.5500001907349</v>
       </c>
       <c r="G185" t="n">
-        <v>9.41263580322266</v>
+        <v>9.41263484954834</v>
       </c>
       <c r="H185" t="s">
         <v>8</v>
@@ -5257,7 +5257,7 @@
         <v>10.789999961853</v>
       </c>
       <c r="G188" t="n">
-        <v>9.62676239013672</v>
+        <v>9.6267614364624</v>
       </c>
       <c r="H188" t="s">
         <v>8</v>
@@ -5283,7 +5283,7 @@
         <v>10.789999961853</v>
       </c>
       <c r="G189" t="n">
-        <v>9.62676239013672</v>
+        <v>9.6267614364624</v>
       </c>
       <c r="H189" t="s">
         <v>8</v>
@@ -5309,7 +5309,7 @@
         <v>10.6000003814697</v>
       </c>
       <c r="G190" t="n">
-        <v>9.45724678039551</v>
+        <v>9.45724487304688</v>
       </c>
       <c r="H190" t="s">
         <v>8</v>
@@ -5335,7 +5335,7 @@
         <v>10.6000003814697</v>
       </c>
       <c r="G191" t="n">
-        <v>9.45724678039551</v>
+        <v>9.45724487304688</v>
       </c>
       <c r="H191" t="s">
         <v>8</v>
@@ -5361,7 +5361,7 @@
         <v>10.6000003814697</v>
       </c>
       <c r="G192" t="n">
-        <v>9.45724678039551</v>
+        <v>9.45724487304688</v>
       </c>
       <c r="H192" t="s">
         <v>8</v>
@@ -5387,7 +5387,7 @@
         <v>10.6899995803833</v>
       </c>
       <c r="G193" t="n">
-        <v>9.53754138946533</v>
+        <v>9.53754234313965</v>
       </c>
       <c r="H193" t="s">
         <v>8</v>
@@ -5413,7 +5413,7 @@
         <v>10.6899995803833</v>
       </c>
       <c r="G194" t="n">
-        <v>9.53754138946533</v>
+        <v>9.53754234313965</v>
       </c>
       <c r="H194" t="s">
         <v>8</v>
@@ -5543,7 +5543,7 @@
         <v>10.5500001907349</v>
       </c>
       <c r="G199" t="n">
-        <v>9.41263580322266</v>
+        <v>9.41263484954834</v>
       </c>
       <c r="H199" t="s">
         <v>8</v>
@@ -5595,7 +5595,7 @@
         <v>10.539999961853</v>
       </c>
       <c r="G201" t="n">
-        <v>9.40371227264404</v>
+        <v>9.40371322631836</v>
       </c>
       <c r="H201" t="s">
         <v>8</v>
@@ -5621,7 +5621,7 @@
         <v>10.6400003433228</v>
       </c>
       <c r="G202" t="n">
-        <v>9.49293231964111</v>
+        <v>9.49293327331543</v>
       </c>
       <c r="H202" t="s">
         <v>8</v>
@@ -5647,7 +5647,7 @@
         <v>10.6899995803833</v>
       </c>
       <c r="G203" t="n">
-        <v>9.53754138946533</v>
+        <v>9.53754234313965</v>
       </c>
       <c r="H203" t="s">
         <v>8</v>
@@ -5673,7 +5673,7 @@
         <v>10.6599998474121</v>
       </c>
       <c r="G204" t="n">
-        <v>9.51077556610107</v>
+        <v>9.51077651977539</v>
       </c>
       <c r="H204" t="s">
         <v>8</v>
@@ -5699,7 +5699,7 @@
         <v>10.6199998855591</v>
       </c>
       <c r="G205" t="n">
-        <v>9.47509002685547</v>
+        <v>9.47508811950684</v>
       </c>
       <c r="H205" t="s">
         <v>8</v>
@@ -5725,7 +5725,7 @@
         <v>10.6700000762939</v>
       </c>
       <c r="G206" t="n">
-        <v>9.51969909667969</v>
+        <v>9.519700050354</v>
       </c>
       <c r="H206" t="s">
         <v>8</v>
@@ -5751,7 +5751,7 @@
         <v>10.6199998855591</v>
       </c>
       <c r="G207" t="n">
-        <v>9.47509002685547</v>
+        <v>9.47508811950684</v>
       </c>
       <c r="H207" t="s">
         <v>8</v>
@@ -5803,7 +5803,7 @@
         <v>10.6300001144409</v>
       </c>
       <c r="G209" t="n">
-        <v>9.48401165008545</v>
+        <v>9.48401260375977</v>
       </c>
       <c r="H209" t="s">
         <v>8</v>
@@ -5855,7 +5855,7 @@
         <v>10.789999961853</v>
       </c>
       <c r="G211" t="n">
-        <v>9.62676239013672</v>
+        <v>9.6267614364624</v>
       </c>
       <c r="H211" t="s">
         <v>8</v>
@@ -5933,7 +5933,7 @@
         <v>10.8299999237061</v>
       </c>
       <c r="G214" t="n">
-        <v>9.66244888305664</v>
+        <v>9.66245079040527</v>
       </c>
       <c r="H214" t="s">
         <v>8</v>
@@ -5959,7 +5959,7 @@
         <v>10.8500003814697</v>
       </c>
       <c r="G215" t="n">
-        <v>9.68029308319092</v>
+        <v>9.68029403686523</v>
       </c>
       <c r="H215" t="s">
         <v>8</v>
@@ -6011,7 +6011,7 @@
         <v>10.7600002288818</v>
       </c>
       <c r="G217" t="n">
-        <v>9.59999561309814</v>
+        <v>9.59999656677246</v>
       </c>
       <c r="H217" t="s">
         <v>8</v>
@@ -6115,7 +6115,7 @@
         <v>10.6199998855591</v>
       </c>
       <c r="G221" t="n">
-        <v>9.47509002685547</v>
+        <v>9.47508811950684</v>
       </c>
       <c r="H221" t="s">
         <v>8</v>
@@ -6167,7 +6167,7 @@
         <v>10.8199996948242</v>
       </c>
       <c r="G223" t="n">
-        <v>9.65352821350098</v>
+        <v>9.65352630615234</v>
       </c>
       <c r="H223" t="s">
         <v>8</v>
@@ -6271,7 +6271,7 @@
         <v>10.7600002288818</v>
       </c>
       <c r="G227" t="n">
-        <v>9.59999561309814</v>
+        <v>9.59999656677246</v>
       </c>
       <c r="H227" t="s">
         <v>8</v>
@@ -6323,7 +6323,7 @@
         <v>10.710000038147</v>
       </c>
       <c r="G229" t="n">
-        <v>9.55538558959961</v>
+        <v>9.55538654327393</v>
       </c>
       <c r="H229" t="s">
         <v>8</v>
@@ -6401,7 +6401,7 @@
         <v>10.710000038147</v>
       </c>
       <c r="G232" t="n">
-        <v>9.55538558959961</v>
+        <v>9.55538654327393</v>
       </c>
       <c r="H232" t="s">
         <v>8</v>
@@ -6479,7 +6479,7 @@
         <v>10.6400003433228</v>
       </c>
       <c r="G235" t="n">
-        <v>9.49293231964111</v>
+        <v>9.49293327331543</v>
       </c>
       <c r="H235" t="s">
         <v>8</v>
@@ -6505,7 +6505,7 @@
         <v>10.6000003814697</v>
       </c>
       <c r="G236" t="n">
-        <v>9.45724678039551</v>
+        <v>9.45724487304688</v>
       </c>
       <c r="H236" t="s">
         <v>8</v>
@@ -6583,7 +6583,7 @@
         <v>10.6000003814697</v>
       </c>
       <c r="G239" t="n">
-        <v>9.45724678039551</v>
+        <v>9.45724487304688</v>
       </c>
       <c r="H239" t="s">
         <v>8</v>
@@ -6609,7 +6609,7 @@
         <v>10.6000003814697</v>
       </c>
       <c r="G240" t="n">
-        <v>9.45724678039551</v>
+        <v>9.45724487304688</v>
       </c>
       <c r="H240" t="s">
         <v>8</v>
@@ -6635,7 +6635,7 @@
         <v>10.6000003814697</v>
       </c>
       <c r="G241" t="n">
-        <v>9.45724678039551</v>
+        <v>9.45724487304688</v>
       </c>
       <c r="H241" t="s">
         <v>8</v>
@@ -6661,7 +6661,7 @@
         <v>10.3999996185303</v>
       </c>
       <c r="G242" t="n">
-        <v>9.27880668640137</v>
+        <v>9.27880573272705</v>
       </c>
       <c r="H242" t="s">
         <v>8</v>
@@ -6687,7 +6687,7 @@
         <v>10.5299997329712</v>
       </c>
       <c r="G243" t="n">
-        <v>9.39479064941406</v>
+        <v>9.39479160308838</v>
       </c>
       <c r="H243" t="s">
         <v>8</v>
@@ -6739,7 +6739,7 @@
         <v>10.3999996185303</v>
       </c>
       <c r="G245" t="n">
-        <v>9.27880668640137</v>
+        <v>9.27880573272705</v>
       </c>
       <c r="H245" t="s">
         <v>8</v>
@@ -6765,7 +6765,7 @@
         <v>10.289999961853</v>
       </c>
       <c r="G246" t="n">
-        <v>9.18066501617432</v>
+        <v>9.1806640625</v>
       </c>
       <c r="H246" t="s">
         <v>8</v>
@@ -6791,7 +6791,7 @@
         <v>10.2200002670288</v>
       </c>
       <c r="G247" t="n">
-        <v>9.11821174621582</v>
+        <v>9.1182107925415</v>
       </c>
       <c r="H247" t="s">
         <v>8</v>
@@ -6817,7 +6817,7 @@
         <v>10.1999998092651</v>
       </c>
       <c r="G248" t="n">
-        <v>9.10036849975586</v>
+        <v>9.10036754608154</v>
       </c>
       <c r="H248" t="s">
         <v>8</v>
@@ -6843,7 +6843,7 @@
         <v>10.1999998092651</v>
       </c>
       <c r="G249" t="n">
-        <v>9.10036849975586</v>
+        <v>9.10036754608154</v>
       </c>
       <c r="H249" t="s">
         <v>8</v>
@@ -6869,7 +6869,7 @@
         <v>10.1999998092651</v>
       </c>
       <c r="G250" t="n">
-        <v>9.10036849975586</v>
+        <v>9.10036754608154</v>
       </c>
       <c r="H250" t="s">
         <v>8</v>
@@ -6895,7 +6895,7 @@
         <v>10.1300001144409</v>
       </c>
       <c r="G251" t="n">
-        <v>9.03791427612305</v>
+        <v>9.03791618347168</v>
       </c>
       <c r="H251" t="s">
         <v>8</v>
@@ -6947,7 +6947,7 @@
         <v>10.289999961853</v>
       </c>
       <c r="G253" t="n">
-        <v>9.18066501617432</v>
+        <v>9.1806640625</v>
       </c>
       <c r="H253" t="s">
         <v>8</v>
@@ -6973,7 +6973,7 @@
         <v>10.3699998855591</v>
       </c>
       <c r="G254" t="n">
-        <v>9.25203990936279</v>
+        <v>9.25204181671143</v>
       </c>
       <c r="H254" t="s">
         <v>8</v>
@@ -6999,7 +6999,7 @@
         <v>10.1599998474121</v>
       </c>
       <c r="G255" t="n">
-        <v>9.06468105316162</v>
+        <v>9.0646800994873</v>
       </c>
       <c r="H255" t="s">
         <v>8</v>
@@ -7025,7 +7025,7 @@
         <v>10.2600002288818</v>
       </c>
       <c r="G256" t="n">
-        <v>9.15390014648438</v>
+        <v>9.15389919281006</v>
       </c>
       <c r="H256" t="s">
         <v>8</v>
@@ -7051,7 +7051,7 @@
         <v>10.210000038147</v>
       </c>
       <c r="G257" t="n">
-        <v>9.10929012298584</v>
+        <v>9.10928916931152</v>
       </c>
       <c r="H257" t="s">
         <v>8</v>
@@ -7259,7 +7259,7 @@
         <v>10.3400001525879</v>
       </c>
       <c r="G265" t="n">
-        <v>9.22527408599854</v>
+        <v>9.22527503967285</v>
       </c>
       <c r="H265" t="s">
         <v>8</v>
@@ -7337,7 +7337,7 @@
         <v>10.3500003814697</v>
       </c>
       <c r="G268" t="n">
-        <v>9.23419761657715</v>
+        <v>9.23419857025146</v>
       </c>
       <c r="H268" t="s">
         <v>8</v>
@@ -7415,7 +7415,7 @@
         <v>10.460000038147</v>
       </c>
       <c r="G271" t="n">
-        <v>9.33233833312988</v>
+        <v>9.33233737945557</v>
       </c>
       <c r="H271" t="s">
         <v>8</v>
@@ -7467,7 +7467,7 @@
         <v>10.539999961853</v>
       </c>
       <c r="G273" t="n">
-        <v>9.40371227264404</v>
+        <v>9.40371322631836</v>
       </c>
       <c r="H273" t="s">
         <v>8</v>
@@ -7545,7 +7545,7 @@
         <v>10.1800003051758</v>
       </c>
       <c r="G276" t="n">
-        <v>9.0825252532959</v>
+        <v>9.08252429962158</v>
       </c>
       <c r="H276" t="s">
         <v>8</v>
@@ -7571,7 +7571,7 @@
         <v>10.0799999237061</v>
       </c>
       <c r="G277" t="n">
-        <v>8.99330520629883</v>
+        <v>8.99330425262451</v>
       </c>
       <c r="H277" t="s">
         <v>8</v>
@@ -7597,7 +7597,7 @@
         <v>10.1499996185303</v>
       </c>
       <c r="G278" t="n">
-        <v>9.05575847625732</v>
+        <v>9.05575942993164</v>
       </c>
       <c r="H278" t="s">
         <v>8</v>
@@ -7623,7 +7623,7 @@
         <v>10.1400003433228</v>
       </c>
       <c r="G279" t="n">
-        <v>9.04683589935303</v>
+        <v>9.04683685302734</v>
       </c>
       <c r="H279" t="s">
         <v>8</v>
@@ -7727,7 +7727,7 @@
         <v>10.1999998092651</v>
       </c>
       <c r="G283" t="n">
-        <v>9.10036849975586</v>
+        <v>9.10036754608154</v>
       </c>
       <c r="H283" t="s">
         <v>8</v>
@@ -7753,7 +7753,7 @@
         <v>10.1599998474121</v>
       </c>
       <c r="G284" t="n">
-        <v>9.06468105316162</v>
+        <v>9.0646800994873</v>
       </c>
       <c r="H284" t="s">
         <v>8</v>
@@ -7779,7 +7779,7 @@
         <v>10.1599998474121</v>
       </c>
       <c r="G285" t="n">
-        <v>9.06468105316162</v>
+        <v>9.0646800994873</v>
       </c>
       <c r="H285" t="s">
         <v>8</v>
@@ -7857,7 +7857,7 @@
         <v>10.1400003433228</v>
       </c>
       <c r="G288" t="n">
-        <v>9.04683589935303</v>
+        <v>9.04683685302734</v>
       </c>
       <c r="H288" t="s">
         <v>8</v>
@@ -7883,7 +7883,7 @@
         <v>10.1400003433228</v>
       </c>
       <c r="G289" t="n">
-        <v>9.04683589935303</v>
+        <v>9.04683685302734</v>
       </c>
       <c r="H289" t="s">
         <v>8</v>
@@ -7909,7 +7909,7 @@
         <v>10.1599998474121</v>
       </c>
       <c r="G290" t="n">
-        <v>9.06468105316162</v>
+        <v>9.0646800994873</v>
       </c>
       <c r="H290" t="s">
         <v>8</v>
@@ -7935,7 +7935,7 @@
         <v>10.1300001144409</v>
       </c>
       <c r="G291" t="n">
-        <v>9.03791427612305</v>
+        <v>9.03791618347168</v>
       </c>
       <c r="H291" t="s">
         <v>8</v>
@@ -8117,7 +8117,7 @@
         <v>10.0799999237061</v>
       </c>
       <c r="G298" t="n">
-        <v>8.99330520629883</v>
+        <v>8.99330425262451</v>
       </c>
       <c r="H298" t="s">
         <v>8</v>
@@ -8325,7 +8325,7 @@
         <v>10.0799999237061</v>
       </c>
       <c r="G306" t="n">
-        <v>8.99330520629883</v>
+        <v>8.99330425262451</v>
       </c>
       <c r="H306" t="s">
         <v>8</v>
@@ -8455,7 +8455,7 @@
         <v>10</v>
       </c>
       <c r="G311" t="n">
-        <v>8.92192840576172</v>
+        <v>8.92192935943604</v>
       </c>
       <c r="H311" t="s">
         <v>8</v>
@@ -8481,7 +8481,7 @@
         <v>10</v>
       </c>
       <c r="G312" t="n">
-        <v>8.92192840576172</v>
+        <v>8.92192935943604</v>
       </c>
       <c r="H312" t="s">
         <v>8</v>
@@ -8507,7 +8507,7 @@
         <v>10</v>
       </c>
       <c r="G313" t="n">
-        <v>8.92192840576172</v>
+        <v>8.92192935943604</v>
       </c>
       <c r="H313" t="s">
         <v>8</v>
@@ -8533,7 +8533,7 @@
         <v>10</v>
       </c>
       <c r="G314" t="n">
-        <v>8.92192840576172</v>
+        <v>8.92192935943604</v>
       </c>
       <c r="H314" t="s">
         <v>8</v>
@@ -8637,7 +8637,7 @@
         <v>10.1999998092651</v>
       </c>
       <c r="G318" t="n">
-        <v>9.10036849975586</v>
+        <v>9.10036754608154</v>
       </c>
       <c r="H318" t="s">
         <v>8</v>
@@ -8663,7 +8663,7 @@
         <v>10.1999998092651</v>
       </c>
       <c r="G319" t="n">
-        <v>9.10036849975586</v>
+        <v>9.10036754608154</v>
       </c>
       <c r="H319" t="s">
         <v>8</v>
@@ -8689,7 +8689,7 @@
         <v>10</v>
       </c>
       <c r="G320" t="n">
-        <v>8.92192840576172</v>
+        <v>8.92192935943604</v>
       </c>
       <c r="H320" t="s">
         <v>8</v>
@@ -8715,7 +8715,7 @@
         <v>10.1999998092651</v>
       </c>
       <c r="G321" t="n">
-        <v>9.10036849975586</v>
+        <v>9.10036754608154</v>
       </c>
       <c r="H321" t="s">
         <v>8</v>
@@ -8741,7 +8741,7 @@
         <v>10.1999998092651</v>
       </c>
       <c r="G322" t="n">
-        <v>9.10036849975586</v>
+        <v>9.10036754608154</v>
       </c>
       <c r="H322" t="s">
         <v>8</v>
@@ -8819,7 +8819,7 @@
         <v>10.1999998092651</v>
       </c>
       <c r="G325" t="n">
-        <v>9.10036849975586</v>
+        <v>9.10036754608154</v>
       </c>
       <c r="H325" t="s">
         <v>8</v>
@@ -8845,7 +8845,7 @@
         <v>10.1999998092651</v>
       </c>
       <c r="G326" t="n">
-        <v>9.10036849975586</v>
+        <v>9.10036754608154</v>
       </c>
       <c r="H326" t="s">
         <v>8</v>
@@ -8897,7 +8897,7 @@
         <v>10</v>
       </c>
       <c r="G328" t="n">
-        <v>8.92192840576172</v>
+        <v>8.92192935943604</v>
       </c>
       <c r="H328" t="s">
         <v>8</v>
@@ -9001,7 +9001,7 @@
         <v>10</v>
       </c>
       <c r="G332" t="n">
-        <v>8.92192840576172</v>
+        <v>8.92192935943604</v>
       </c>
       <c r="H332" t="s">
         <v>8</v>
@@ -9027,7 +9027,7 @@
         <v>10</v>
       </c>
       <c r="G333" t="n">
-        <v>8.92192840576172</v>
+        <v>8.92192935943604</v>
       </c>
       <c r="H333" t="s">
         <v>8</v>
@@ -9053,7 +9053,7 @@
         <v>10</v>
       </c>
       <c r="G334" t="n">
-        <v>8.92192840576172</v>
+        <v>8.92192935943604</v>
       </c>
       <c r="H334" t="s">
         <v>8</v>
@@ -9079,7 +9079,7 @@
         <v>10</v>
       </c>
       <c r="G335" t="n">
-        <v>8.92192840576172</v>
+        <v>8.92192935943604</v>
       </c>
       <c r="H335" t="s">
         <v>8</v>
@@ -9183,7 +9183,7 @@
         <v>10</v>
       </c>
       <c r="G339" t="n">
-        <v>8.92192840576172</v>
+        <v>8.92192935943604</v>
       </c>
       <c r="H339" t="s">
         <v>8</v>
@@ -9261,7 +9261,7 @@
         <v>10</v>
       </c>
       <c r="G342" t="n">
-        <v>8.92192840576172</v>
+        <v>8.92192935943604</v>
       </c>
       <c r="H342" t="s">
         <v>8</v>
@@ -9287,7 +9287,7 @@
         <v>10</v>
       </c>
       <c r="G343" t="n">
-        <v>8.92192840576172</v>
+        <v>8.92192935943604</v>
       </c>
       <c r="H343" t="s">
         <v>8</v>
@@ -9313,7 +9313,7 @@
         <v>10</v>
       </c>
       <c r="G344" t="n">
-        <v>8.92192840576172</v>
+        <v>8.92192935943604</v>
       </c>
       <c r="H344" t="s">
         <v>8</v>
@@ -9339,7 +9339,7 @@
         <v>10</v>
       </c>
       <c r="G345" t="n">
-        <v>8.92192840576172</v>
+        <v>8.92192935943604</v>
       </c>
       <c r="H345" t="s">
         <v>8</v>
@@ -9365,7 +9365,7 @@
         <v>10</v>
       </c>
       <c r="G346" t="n">
-        <v>8.92192840576172</v>
+        <v>8.92192935943604</v>
       </c>
       <c r="H346" t="s">
         <v>8</v>
@@ -9391,7 +9391,7 @@
         <v>10</v>
       </c>
       <c r="G347" t="n">
-        <v>8.92192840576172</v>
+        <v>8.92192935943604</v>
       </c>
       <c r="H347" t="s">
         <v>8</v>
@@ -9417,7 +9417,7 @@
         <v>10</v>
       </c>
       <c r="G348" t="n">
-        <v>8.92192840576172</v>
+        <v>8.92192935943604</v>
       </c>
       <c r="H348" t="s">
         <v>8</v>
@@ -9443,7 +9443,7 @@
         <v>10</v>
       </c>
       <c r="G349" t="n">
-        <v>8.92192840576172</v>
+        <v>8.92192935943604</v>
       </c>
       <c r="H349" t="s">
         <v>8</v>
@@ -9495,7 +9495,7 @@
         <v>10</v>
       </c>
       <c r="G351" t="n">
-        <v>8.92192840576172</v>
+        <v>8.92192935943604</v>
       </c>
       <c r="H351" t="s">
         <v>8</v>
@@ -9521,7 +9521,7 @@
         <v>10</v>
       </c>
       <c r="G352" t="n">
-        <v>8.92192840576172</v>
+        <v>8.92192935943604</v>
       </c>
       <c r="H352" t="s">
         <v>8</v>
@@ -9547,7 +9547,7 @@
         <v>10</v>
       </c>
       <c r="G353" t="n">
-        <v>8.92192840576172</v>
+        <v>8.92192935943604</v>
       </c>
       <c r="H353" t="s">
         <v>8</v>
@@ -9573,7 +9573,7 @@
         <v>10</v>
       </c>
       <c r="G354" t="n">
-        <v>8.92192840576172</v>
+        <v>8.92192935943604</v>
       </c>
       <c r="H354" t="s">
         <v>8</v>
@@ -9807,7 +9807,7 @@
         <v>10</v>
       </c>
       <c r="G363" t="n">
-        <v>8.92192840576172</v>
+        <v>8.92192935943604</v>
       </c>
       <c r="H363" t="s">
         <v>8</v>
@@ -9885,7 +9885,7 @@
         <v>9.85000038146973</v>
       </c>
       <c r="G366" t="n">
-        <v>8.78809928894043</v>
+        <v>8.78810119628906</v>
       </c>
       <c r="H366" t="s">
         <v>8</v>
@@ -10041,7 +10041,7 @@
         <v>9.85000038146973</v>
       </c>
       <c r="G372" t="n">
-        <v>8.78809928894043</v>
+        <v>8.78810119628906</v>
       </c>
       <c r="H372" t="s">
         <v>8</v>
@@ -10119,7 +10119,7 @@
         <v>10</v>
       </c>
       <c r="G375" t="n">
-        <v>8.92192840576172</v>
+        <v>8.92192935943604</v>
       </c>
       <c r="H375" t="s">
         <v>8</v>
@@ -10145,7 +10145,7 @@
         <v>10</v>
       </c>
       <c r="G376" t="n">
-        <v>8.92192840576172</v>
+        <v>8.92192935943604</v>
       </c>
       <c r="H376" t="s">
         <v>8</v>
@@ -10197,7 +10197,7 @@
         <v>10</v>
       </c>
       <c r="G378" t="n">
-        <v>8.92192840576172</v>
+        <v>8.92192935943604</v>
       </c>
       <c r="H378" t="s">
         <v>8</v>
@@ -10223,7 +10223,7 @@
         <v>10</v>
       </c>
       <c r="G379" t="n">
-        <v>8.92192840576172</v>
+        <v>8.92192935943604</v>
       </c>
       <c r="H379" t="s">
         <v>8</v>
@@ -10249,7 +10249,7 @@
         <v>10</v>
       </c>
       <c r="G380" t="n">
-        <v>8.92192840576172</v>
+        <v>8.92192935943604</v>
       </c>
       <c r="H380" t="s">
         <v>8</v>
@@ -10275,7 +10275,7 @@
         <v>10</v>
       </c>
       <c r="G381" t="n">
-        <v>8.92192840576172</v>
+        <v>8.92192935943604</v>
       </c>
       <c r="H381" t="s">
         <v>8</v>
@@ -10301,7 +10301,7 @@
         <v>10</v>
       </c>
       <c r="G382" t="n">
-        <v>8.92192840576172</v>
+        <v>8.92192935943604</v>
       </c>
       <c r="H382" t="s">
         <v>8</v>
@@ -10509,7 +10509,7 @@
         <v>9.85000038146973</v>
       </c>
       <c r="G390" t="n">
-        <v>8.78809928894043</v>
+        <v>8.78810119628906</v>
       </c>
       <c r="H390" t="s">
         <v>8</v>
@@ -10535,7 +10535,7 @@
         <v>9.85000038146973</v>
       </c>
       <c r="G391" t="n">
-        <v>8.78809928894043</v>
+        <v>8.78810119628906</v>
       </c>
       <c r="H391" t="s">
         <v>8</v>
@@ -10561,7 +10561,7 @@
         <v>9.85000038146973</v>
       </c>
       <c r="G392" t="n">
-        <v>8.78809928894043</v>
+        <v>8.78810119628906</v>
       </c>
       <c r="H392" t="s">
         <v>8</v>
@@ -10587,7 +10587,7 @@
         <v>9.85000038146973</v>
       </c>
       <c r="G393" t="n">
-        <v>8.78809928894043</v>
+        <v>8.78810119628906</v>
       </c>
       <c r="H393" t="s">
         <v>8</v>
@@ -10613,7 +10613,7 @@
         <v>9.85000038146973</v>
       </c>
       <c r="G394" t="n">
-        <v>8.78809928894043</v>
+        <v>8.78810119628906</v>
       </c>
       <c r="H394" t="s">
         <v>8</v>
@@ -10899,7 +10899,7 @@
         <v>9.85000038146973</v>
       </c>
       <c r="G405" t="n">
-        <v>8.78809928894043</v>
+        <v>8.78810119628906</v>
       </c>
       <c r="H405" t="s">
         <v>8</v>
@@ -10925,7 +10925,7 @@
         <v>9.85000038146973</v>
       </c>
       <c r="G406" t="n">
-        <v>8.78809928894043</v>
+        <v>8.78810119628906</v>
       </c>
       <c r="H406" t="s">
         <v>8</v>
@@ -11107,7 +11107,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G413" t="n">
-        <v>8.65427017211914</v>
+        <v>8.65427207946777</v>
       </c>
       <c r="H413" t="s">
         <v>8</v>
@@ -11133,7 +11133,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G414" t="n">
-        <v>8.65427017211914</v>
+        <v>8.65427207946777</v>
       </c>
       <c r="H414" t="s">
         <v>8</v>
@@ -11185,7 +11185,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G416" t="n">
-        <v>8.65427017211914</v>
+        <v>8.65427207946777</v>
       </c>
       <c r="H416" t="s">
         <v>8</v>
@@ -11211,7 +11211,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G417" t="n">
-        <v>8.65427017211914</v>
+        <v>8.65427207946777</v>
       </c>
       <c r="H417" t="s">
         <v>8</v>
@@ -11367,7 +11367,7 @@
         <v>9.85000038146973</v>
       </c>
       <c r="G423" t="n">
-        <v>8.78809928894043</v>
+        <v>8.78810119628906</v>
       </c>
       <c r="H423" t="s">
         <v>8</v>
@@ -11679,7 +11679,7 @@
         <v>10.1999998092651</v>
       </c>
       <c r="G435" t="n">
-        <v>9.10036849975586</v>
+        <v>9.10036754608154</v>
       </c>
       <c r="H435" t="s">
         <v>8</v>
@@ -11705,7 +11705,7 @@
         <v>10.1999998092651</v>
       </c>
       <c r="G436" t="n">
-        <v>9.10036849975586</v>
+        <v>9.10036754608154</v>
       </c>
       <c r="H436" t="s">
         <v>8</v>
@@ -11731,7 +11731,7 @@
         <v>10.1999998092651</v>
       </c>
       <c r="G437" t="n">
-        <v>9.10036849975586</v>
+        <v>9.10036754608154</v>
       </c>
       <c r="H437" t="s">
         <v>8</v>
@@ -11757,7 +11757,7 @@
         <v>10.1999998092651</v>
       </c>
       <c r="G438" t="n">
-        <v>9.10036849975586</v>
+        <v>9.10036754608154</v>
       </c>
       <c r="H438" t="s">
         <v>8</v>
@@ -11783,7 +11783,7 @@
         <v>10.1999998092651</v>
       </c>
       <c r="G439" t="n">
-        <v>9.10036849975586</v>
+        <v>9.10036754608154</v>
       </c>
       <c r="H439" t="s">
         <v>8</v>
@@ -11913,7 +11913,7 @@
         <v>10.3999996185303</v>
       </c>
       <c r="G444" t="n">
-        <v>9.27880668640137</v>
+        <v>9.27880573272705</v>
       </c>
       <c r="H444" t="s">
         <v>8</v>
@@ -11939,7 +11939,7 @@
         <v>10.3999996185303</v>
       </c>
       <c r="G445" t="n">
-        <v>9.27880668640137</v>
+        <v>9.27880573272705</v>
       </c>
       <c r="H445" t="s">
         <v>8</v>
@@ -11965,7 +11965,7 @@
         <v>10.3999996185303</v>
       </c>
       <c r="G446" t="n">
-        <v>9.27880668640137</v>
+        <v>9.27880573272705</v>
       </c>
       <c r="H446" t="s">
         <v>8</v>
@@ -11991,7 +11991,7 @@
         <v>10.3999996185303</v>
       </c>
       <c r="G447" t="n">
-        <v>9.27880668640137</v>
+        <v>9.27880573272705</v>
       </c>
       <c r="H447" t="s">
         <v>8</v>
@@ -12017,7 +12017,7 @@
         <v>10.3999996185303</v>
       </c>
       <c r="G448" t="n">
-        <v>9.27880668640137</v>
+        <v>9.27880573272705</v>
       </c>
       <c r="H448" t="s">
         <v>8</v>
@@ -12043,7 +12043,7 @@
         <v>10.1999998092651</v>
       </c>
       <c r="G449" t="n">
-        <v>9.10036849975586</v>
+        <v>9.10036754608154</v>
       </c>
       <c r="H449" t="s">
         <v>8</v>
@@ -12095,7 +12095,7 @@
         <v>10.3999996185303</v>
       </c>
       <c r="G451" t="n">
-        <v>9.27880668640137</v>
+        <v>9.27880573272705</v>
       </c>
       <c r="H451" t="s">
         <v>8</v>
@@ -12121,7 +12121,7 @@
         <v>10.3999996185303</v>
       </c>
       <c r="G452" t="n">
-        <v>9.27880668640137</v>
+        <v>9.27880573272705</v>
       </c>
       <c r="H452" t="s">
         <v>8</v>
@@ -12147,7 +12147,7 @@
         <v>10.3999996185303</v>
       </c>
       <c r="G453" t="n">
-        <v>9.27880668640137</v>
+        <v>9.27880573272705</v>
       </c>
       <c r="H453" t="s">
         <v>8</v>
@@ -12199,7 +12199,7 @@
         <v>10.3999996185303</v>
       </c>
       <c r="G455" t="n">
-        <v>9.27880668640137</v>
+        <v>9.27880573272705</v>
       </c>
       <c r="H455" t="s">
         <v>8</v>
@@ -12251,7 +12251,7 @@
         <v>10.3999996185303</v>
       </c>
       <c r="G457" t="n">
-        <v>9.27880668640137</v>
+        <v>9.27880573272705</v>
       </c>
       <c r="H457" t="s">
         <v>8</v>
@@ -12329,7 +12329,7 @@
         <v>10.3999996185303</v>
       </c>
       <c r="G460" t="n">
-        <v>9.27880668640137</v>
+        <v>9.27880573272705</v>
       </c>
       <c r="H460" t="s">
         <v>8</v>
@@ -12355,7 +12355,7 @@
         <v>10.3999996185303</v>
       </c>
       <c r="G461" t="n">
-        <v>9.27880668640137</v>
+        <v>9.27880573272705</v>
       </c>
       <c r="H461" t="s">
         <v>8</v>
@@ -12537,7 +12537,7 @@
         <v>10.1999998092651</v>
       </c>
       <c r="G468" t="n">
-        <v>9.10036849975586</v>
+        <v>9.10036754608154</v>
       </c>
       <c r="H468" t="s">
         <v>8</v>
@@ -12563,7 +12563,7 @@
         <v>10.1999998092651</v>
       </c>
       <c r="G469" t="n">
-        <v>9.10036849975586</v>
+        <v>9.10036754608154</v>
       </c>
       <c r="H469" t="s">
         <v>8</v>
@@ -12589,7 +12589,7 @@
         <v>10.1999998092651</v>
       </c>
       <c r="G470" t="n">
-        <v>9.10036849975586</v>
+        <v>9.10036754608154</v>
       </c>
       <c r="H470" t="s">
         <v>8</v>
@@ -12615,7 +12615,7 @@
         <v>10.1999998092651</v>
       </c>
       <c r="G471" t="n">
-        <v>9.10036849975586</v>
+        <v>9.10036754608154</v>
       </c>
       <c r="H471" t="s">
         <v>8</v>
@@ -12667,7 +12667,7 @@
         <v>10.1999998092651</v>
       </c>
       <c r="G473" t="n">
-        <v>9.10036849975586</v>
+        <v>9.10036754608154</v>
       </c>
       <c r="H473" t="s">
         <v>8</v>
@@ -12693,7 +12693,7 @@
         <v>10.1999998092651</v>
       </c>
       <c r="G474" t="n">
-        <v>9.10036849975586</v>
+        <v>9.10036754608154</v>
       </c>
       <c r="H474" t="s">
         <v>8</v>
@@ -12745,7 +12745,7 @@
         <v>10.1999998092651</v>
       </c>
       <c r="G476" t="n">
-        <v>9.10036849975586</v>
+        <v>9.10036754608154</v>
       </c>
       <c r="H476" t="s">
         <v>8</v>
@@ -12771,7 +12771,7 @@
         <v>10.1999998092651</v>
       </c>
       <c r="G477" t="n">
-        <v>9.10036849975586</v>
+        <v>9.10036754608154</v>
       </c>
       <c r="H477" t="s">
         <v>8</v>
@@ -12797,7 +12797,7 @@
         <v>10.1999998092651</v>
       </c>
       <c r="G478" t="n">
-        <v>9.10036849975586</v>
+        <v>9.10036754608154</v>
       </c>
       <c r="H478" t="s">
         <v>8</v>
@@ -12823,7 +12823,7 @@
         <v>10.1999998092651</v>
       </c>
       <c r="G479" t="n">
-        <v>9.10036849975586</v>
+        <v>9.10036754608154</v>
       </c>
       <c r="H479" t="s">
         <v>8</v>
@@ -12849,7 +12849,7 @@
         <v>10.1999998092651</v>
       </c>
       <c r="G480" t="n">
-        <v>9.10036849975586</v>
+        <v>9.10036754608154</v>
       </c>
       <c r="H480" t="s">
         <v>8</v>
@@ -12875,7 +12875,7 @@
         <v>10.1999998092651</v>
       </c>
       <c r="G481" t="n">
-        <v>9.10036849975586</v>
+        <v>9.10036754608154</v>
       </c>
       <c r="H481" t="s">
         <v>8</v>
@@ -12927,7 +12927,7 @@
         <v>10.1999998092651</v>
       </c>
       <c r="G483" t="n">
-        <v>9.10036849975586</v>
+        <v>9.10036754608154</v>
       </c>
       <c r="H483" t="s">
         <v>8</v>
@@ -12953,7 +12953,7 @@
         <v>10.1999998092651</v>
       </c>
       <c r="G484" t="n">
-        <v>9.10036849975586</v>
+        <v>9.10036754608154</v>
       </c>
       <c r="H484" t="s">
         <v>8</v>
@@ -13005,7 +13005,7 @@
         <v>10</v>
       </c>
       <c r="G486" t="n">
-        <v>8.92192840576172</v>
+        <v>8.92192935943604</v>
       </c>
       <c r="H486" t="s">
         <v>8</v>
@@ -13083,7 +13083,7 @@
         <v>10.1999998092651</v>
       </c>
       <c r="G489" t="n">
-        <v>9.10036849975586</v>
+        <v>9.10036754608154</v>
       </c>
       <c r="H489" t="s">
         <v>8</v>
@@ -13109,7 +13109,7 @@
         <v>10.1999998092651</v>
       </c>
       <c r="G490" t="n">
-        <v>9.10036849975586</v>
+        <v>9.10036754608154</v>
       </c>
       <c r="H490" t="s">
         <v>8</v>
@@ -13161,7 +13161,7 @@
         <v>10.1999998092651</v>
       </c>
       <c r="G492" t="n">
-        <v>9.10036849975586</v>
+        <v>9.10036754608154</v>
       </c>
       <c r="H492" t="s">
         <v>8</v>
@@ -13187,7 +13187,7 @@
         <v>10</v>
       </c>
       <c r="G493" t="n">
-        <v>8.92192840576172</v>
+        <v>8.92192935943604</v>
       </c>
       <c r="H493" t="s">
         <v>8</v>
@@ -13291,7 +13291,7 @@
         <v>10</v>
       </c>
       <c r="G497" t="n">
-        <v>8.92192840576172</v>
+        <v>8.92192935943604</v>
       </c>
       <c r="H497" t="s">
         <v>8</v>
@@ -13317,7 +13317,7 @@
         <v>9.64999961853027</v>
       </c>
       <c r="G498" t="n">
-        <v>8.60966110229492</v>
+        <v>8.60966205596924</v>
       </c>
       <c r="H498" t="s">
         <v>8</v>
@@ -13395,7 +13395,7 @@
         <v>9.85000038146973</v>
       </c>
       <c r="G501" t="n">
-        <v>8.78809928894043</v>
+        <v>8.78810119628906</v>
       </c>
       <c r="H501" t="s">
         <v>8</v>
@@ -13421,7 +13421,7 @@
         <v>9.85000038146973</v>
       </c>
       <c r="G502" t="n">
-        <v>8.78809928894043</v>
+        <v>8.78810119628906</v>
       </c>
       <c r="H502" t="s">
         <v>8</v>
@@ -13551,7 +13551,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G507" t="n">
-        <v>8.65427017211914</v>
+        <v>8.65427207946777</v>
       </c>
       <c r="H507" t="s">
         <v>8</v>
@@ -13629,7 +13629,7 @@
         <v>9.85000038146973</v>
       </c>
       <c r="G510" t="n">
-        <v>8.78809928894043</v>
+        <v>8.78810119628906</v>
       </c>
       <c r="H510" t="s">
         <v>8</v>
@@ -13707,7 +13707,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G513" t="n">
-        <v>8.65427017211914</v>
+        <v>8.65427207946777</v>
       </c>
       <c r="H513" t="s">
         <v>8</v>
@@ -13733,7 +13733,7 @@
         <v>9.64999961853027</v>
       </c>
       <c r="G514" t="n">
-        <v>8.60966110229492</v>
+        <v>8.60966205596924</v>
       </c>
       <c r="H514" t="s">
         <v>8</v>
@@ -13759,7 +13759,7 @@
         <v>9.64999961853027</v>
       </c>
       <c r="G515" t="n">
-        <v>8.60966110229492</v>
+        <v>8.60966205596924</v>
       </c>
       <c r="H515" t="s">
         <v>8</v>
@@ -13785,7 +13785,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G516" t="n">
-        <v>8.65427017211914</v>
+        <v>8.65427207946777</v>
       </c>
       <c r="H516" t="s">
         <v>8</v>
@@ -13811,7 +13811,7 @@
         <v>9.64999961853027</v>
       </c>
       <c r="G517" t="n">
-        <v>8.60966110229492</v>
+        <v>8.60966205596924</v>
       </c>
       <c r="H517" t="s">
         <v>8</v>
@@ -13837,7 +13837,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G518" t="n">
-        <v>8.65427017211914</v>
+        <v>8.65427207946777</v>
       </c>
       <c r="H518" t="s">
         <v>8</v>
@@ -13863,7 +13863,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G519" t="n">
-        <v>8.65427017211914</v>
+        <v>8.65427207946777</v>
       </c>
       <c r="H519" t="s">
         <v>8</v>
@@ -13967,7 +13967,7 @@
         <v>9.64999961853027</v>
       </c>
       <c r="G523" t="n">
-        <v>8.60966110229492</v>
+        <v>8.60966205596924</v>
       </c>
       <c r="H523" t="s">
         <v>8</v>
@@ -14045,7 +14045,7 @@
         <v>9.64999961853027</v>
       </c>
       <c r="G526" t="n">
-        <v>8.60966110229492</v>
+        <v>8.60966205596924</v>
       </c>
       <c r="H526" t="s">
         <v>8</v>
@@ -14071,7 +14071,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G527" t="n">
-        <v>8.65427017211914</v>
+        <v>8.65427207946777</v>
       </c>
       <c r="H527" t="s">
         <v>8</v>
@@ -14097,7 +14097,7 @@
         <v>9.55000019073486</v>
       </c>
       <c r="G528" t="n">
-        <v>8.52044200897217</v>
+        <v>8.5204439163208</v>
       </c>
       <c r="H528" t="s">
         <v>8</v>
@@ -14123,7 +14123,7 @@
         <v>9.5</v>
       </c>
       <c r="G529" t="n">
-        <v>8.47583293914795</v>
+        <v>8.47583389282227</v>
       </c>
       <c r="H529" t="s">
         <v>8</v>
@@ -14201,7 +14201,7 @@
         <v>9</v>
       </c>
       <c r="G532" t="n">
-        <v>8.02973747253418</v>
+        <v>8.02973651885986</v>
       </c>
       <c r="H532" t="s">
         <v>8</v>
@@ -14227,7 +14227,7 @@
         <v>9</v>
       </c>
       <c r="G533" t="n">
-        <v>8.02973747253418</v>
+        <v>8.02973651885986</v>
       </c>
       <c r="H533" t="s">
         <v>8</v>
@@ -14279,7 +14279,7 @@
         <v>8.85000038146973</v>
       </c>
       <c r="G535" t="n">
-        <v>7.89590692520142</v>
+        <v>7.89590740203857</v>
       </c>
       <c r="H535" t="s">
         <v>8</v>
@@ -14305,7 +14305,7 @@
         <v>8.85000038146973</v>
       </c>
       <c r="G536" t="n">
-        <v>7.89590692520142</v>
+        <v>7.89590740203857</v>
       </c>
       <c r="H536" t="s">
         <v>8</v>
@@ -14331,7 +14331,7 @@
         <v>8.94999980926514</v>
       </c>
       <c r="G537" t="n">
-        <v>7.98512649536133</v>
+        <v>7.98512840270996</v>
       </c>
       <c r="H537" t="s">
         <v>8</v>
@@ -14357,7 +14357,7 @@
         <v>9</v>
       </c>
       <c r="G538" t="n">
-        <v>8.02973747253418</v>
+        <v>8.02973651885986</v>
       </c>
       <c r="H538" t="s">
         <v>8</v>
@@ -14383,7 +14383,7 @@
         <v>9.10000038146973</v>
       </c>
       <c r="G539" t="n">
-        <v>8.1189546585083</v>
+        <v>8.11895656585693</v>
       </c>
       <c r="H539" t="s">
         <v>8</v>
@@ -14487,7 +14487,7 @@
         <v>9.10000038146973</v>
       </c>
       <c r="G543" t="n">
-        <v>8.1189546585083</v>
+        <v>8.11895656585693</v>
       </c>
       <c r="H543" t="s">
         <v>8</v>
@@ -14513,7 +14513,7 @@
         <v>9.10000038146973</v>
       </c>
       <c r="G544" t="n">
-        <v>8.1189546585083</v>
+        <v>8.11895656585693</v>
       </c>
       <c r="H544" t="s">
         <v>8</v>
@@ -14539,7 +14539,7 @@
         <v>9.10000038146973</v>
       </c>
       <c r="G545" t="n">
-        <v>8.1189546585083</v>
+        <v>8.11895656585693</v>
       </c>
       <c r="H545" t="s">
         <v>8</v>
@@ -14565,7 +14565,7 @@
         <v>9</v>
       </c>
       <c r="G546" t="n">
-        <v>8.02973747253418</v>
+        <v>8.02973651885986</v>
       </c>
       <c r="H546" t="s">
         <v>8</v>
@@ -14591,7 +14591,7 @@
         <v>8.85000038146973</v>
       </c>
       <c r="G547" t="n">
-        <v>7.89590692520142</v>
+        <v>7.89590740203857</v>
       </c>
       <c r="H547" t="s">
         <v>8</v>
@@ -14617,7 +14617,7 @@
         <v>8.85000038146973</v>
       </c>
       <c r="G548" t="n">
-        <v>7.89590692520142</v>
+        <v>7.89590740203857</v>
       </c>
       <c r="H548" t="s">
         <v>8</v>
@@ -14643,7 +14643,7 @@
         <v>8.85000038146973</v>
       </c>
       <c r="G549" t="n">
-        <v>7.89590692520142</v>
+        <v>7.89590740203857</v>
       </c>
       <c r="H549" t="s">
         <v>8</v>
@@ -14669,7 +14669,7 @@
         <v>8.85000038146973</v>
       </c>
       <c r="G550" t="n">
-        <v>7.89590692520142</v>
+        <v>7.89590740203857</v>
       </c>
       <c r="H550" t="s">
         <v>8</v>
@@ -14747,7 +14747,7 @@
         <v>8.75</v>
       </c>
       <c r="G553" t="n">
-        <v>7.80668878555298</v>
+        <v>7.80668830871582</v>
       </c>
       <c r="H553" t="s">
         <v>8</v>
@@ -14773,7 +14773,7 @@
         <v>8.75</v>
       </c>
       <c r="G554" t="n">
-        <v>7.80668878555298</v>
+        <v>7.80668830871582</v>
       </c>
       <c r="H554" t="s">
         <v>8</v>
@@ -14799,7 +14799,7 @@
         <v>8.75</v>
       </c>
       <c r="G555" t="n">
-        <v>7.80668878555298</v>
+        <v>7.80668830871582</v>
       </c>
       <c r="H555" t="s">
         <v>8</v>
@@ -14825,7 +14825,7 @@
         <v>9.14999961853027</v>
       </c>
       <c r="G556" t="n">
-        <v>8.16356563568115</v>
+        <v>8.16356658935547</v>
       </c>
       <c r="H556" t="s">
         <v>8</v>
@@ -14851,7 +14851,7 @@
         <v>9.05000019073486</v>
       </c>
       <c r="G557" t="n">
-        <v>8.0743465423584</v>
+        <v>8.07434558868408</v>
       </c>
       <c r="H557" t="s">
         <v>8</v>
@@ -14877,7 +14877,7 @@
         <v>9.25</v>
       </c>
       <c r="G558" t="n">
-        <v>8.25278377532959</v>
+        <v>8.25278472900391</v>
       </c>
       <c r="H558" t="s">
         <v>8</v>
@@ -14903,7 +14903,7 @@
         <v>9.25</v>
       </c>
       <c r="G559" t="n">
-        <v>8.25278377532959</v>
+        <v>8.25278472900391</v>
       </c>
       <c r="H559" t="s">
         <v>8</v>
@@ -14929,7 +14929,7 @@
         <v>9.25</v>
       </c>
       <c r="G560" t="n">
-        <v>8.25278377532959</v>
+        <v>8.25278472900391</v>
       </c>
       <c r="H560" t="s">
         <v>8</v>
@@ -14955,7 +14955,7 @@
         <v>9.25</v>
       </c>
       <c r="G561" t="n">
-        <v>8.25278377532959</v>
+        <v>8.25278472900391</v>
       </c>
       <c r="H561" t="s">
         <v>8</v>
@@ -15007,7 +15007,7 @@
         <v>9.64999961853027</v>
       </c>
       <c r="G563" t="n">
-        <v>8.60966110229492</v>
+        <v>8.60966205596924</v>
       </c>
       <c r="H563" t="s">
         <v>8</v>
@@ -15033,7 +15033,7 @@
         <v>9.55000019073486</v>
       </c>
       <c r="G564" t="n">
-        <v>8.52044200897217</v>
+        <v>8.5204439163208</v>
       </c>
       <c r="H564" t="s">
         <v>8</v>
@@ -15059,7 +15059,7 @@
         <v>9.60000038146973</v>
       </c>
       <c r="G565" t="n">
-        <v>8.56505298614502</v>
+        <v>8.5650520324707</v>
       </c>
       <c r="H565" t="s">
         <v>8</v>
@@ -15085,7 +15085,7 @@
         <v>9.60000038146973</v>
       </c>
       <c r="G566" t="n">
-        <v>8.56505298614502</v>
+        <v>8.5650520324707</v>
       </c>
       <c r="H566" t="s">
         <v>8</v>
@@ -15111,7 +15111,7 @@
         <v>9.60000038146973</v>
       </c>
       <c r="G567" t="n">
-        <v>8.56505298614502</v>
+        <v>8.5650520324707</v>
       </c>
       <c r="H567" t="s">
         <v>8</v>
@@ -15137,7 +15137,7 @@
         <v>9.64999961853027</v>
       </c>
       <c r="G568" t="n">
-        <v>8.60966110229492</v>
+        <v>8.60966205596924</v>
       </c>
       <c r="H568" t="s">
         <v>8</v>
@@ -15163,7 +15163,7 @@
         <v>9.55000019073486</v>
       </c>
       <c r="G569" t="n">
-        <v>8.52044200897217</v>
+        <v>8.5204439163208</v>
       </c>
       <c r="H569" t="s">
         <v>8</v>
@@ -15189,7 +15189,7 @@
         <v>9.60000038146973</v>
       </c>
       <c r="G570" t="n">
-        <v>8.56505298614502</v>
+        <v>8.5650520324707</v>
       </c>
       <c r="H570" t="s">
         <v>8</v>
@@ -15215,7 +15215,7 @@
         <v>9.60000038146973</v>
       </c>
       <c r="G571" t="n">
-        <v>8.56505298614502</v>
+        <v>8.5650520324707</v>
       </c>
       <c r="H571" t="s">
         <v>8</v>
@@ -15241,7 +15241,7 @@
         <v>9.60000038146973</v>
       </c>
       <c r="G572" t="n">
-        <v>8.56505298614502</v>
+        <v>8.5650520324707</v>
       </c>
       <c r="H572" t="s">
         <v>8</v>
@@ -15267,7 +15267,7 @@
         <v>9.64999961853027</v>
       </c>
       <c r="G573" t="n">
-        <v>8.60966110229492</v>
+        <v>8.60966205596924</v>
       </c>
       <c r="H573" t="s">
         <v>8</v>
@@ -15293,7 +15293,7 @@
         <v>9.64999961853027</v>
       </c>
       <c r="G574" t="n">
-        <v>8.60966110229492</v>
+        <v>8.60966205596924</v>
       </c>
       <c r="H574" t="s">
         <v>8</v>
@@ -15319,7 +15319,7 @@
         <v>9.64999961853027</v>
       </c>
       <c r="G575" t="n">
-        <v>8.60966110229492</v>
+        <v>8.60966205596924</v>
       </c>
       <c r="H575" t="s">
         <v>8</v>
@@ -15345,7 +15345,7 @@
         <v>9.64999961853027</v>
       </c>
       <c r="G576" t="n">
-        <v>8.60966110229492</v>
+        <v>8.60966205596924</v>
       </c>
       <c r="H576" t="s">
         <v>8</v>
@@ -15371,7 +15371,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G577" t="n">
-        <v>8.65427017211914</v>
+        <v>8.65427207946777</v>
       </c>
       <c r="H577" t="s">
         <v>8</v>
@@ -15423,7 +15423,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G579" t="n">
-        <v>8.65427017211914</v>
+        <v>8.65427207946777</v>
       </c>
       <c r="H579" t="s">
         <v>8</v>
@@ -15501,7 +15501,7 @@
         <v>9.85000038146973</v>
       </c>
       <c r="G582" t="n">
-        <v>8.78809928894043</v>
+        <v>8.78810119628906</v>
       </c>
       <c r="H582" t="s">
         <v>8</v>
@@ -15527,7 +15527,7 @@
         <v>9.85000038146973</v>
       </c>
       <c r="G583" t="n">
-        <v>8.78809928894043</v>
+        <v>8.78810119628906</v>
       </c>
       <c r="H583" t="s">
         <v>8</v>
@@ -15579,7 +15579,7 @@
         <v>9.85000038146973</v>
       </c>
       <c r="G585" t="n">
-        <v>8.78809928894043</v>
+        <v>8.78810119628906</v>
       </c>
       <c r="H585" t="s">
         <v>8</v>
@@ -15605,7 +15605,7 @@
         <v>9.85000038146973</v>
       </c>
       <c r="G586" t="n">
-        <v>8.78809928894043</v>
+        <v>8.78810119628906</v>
       </c>
       <c r="H586" t="s">
         <v>8</v>
@@ -15631,7 +15631,7 @@
         <v>9.85000038146973</v>
       </c>
       <c r="G587" t="n">
-        <v>8.78809928894043</v>
+        <v>8.78810119628906</v>
       </c>
       <c r="H587" t="s">
         <v>8</v>
@@ -15657,7 +15657,7 @@
         <v>9.85000038146973</v>
       </c>
       <c r="G588" t="n">
-        <v>8.78809928894043</v>
+        <v>8.78810119628906</v>
       </c>
       <c r="H588" t="s">
         <v>8</v>
@@ -15787,7 +15787,7 @@
         <v>10</v>
       </c>
       <c r="G593" t="n">
-        <v>8.92192840576172</v>
+        <v>8.92192935943604</v>
       </c>
       <c r="H593" t="s">
         <v>8</v>
@@ -15813,7 +15813,7 @@
         <v>10</v>
       </c>
       <c r="G594" t="n">
-        <v>8.92192840576172</v>
+        <v>8.92192935943604</v>
       </c>
       <c r="H594" t="s">
         <v>8</v>
@@ -15839,7 +15839,7 @@
         <v>10</v>
       </c>
       <c r="G595" t="n">
-        <v>8.92192840576172</v>
+        <v>8.92192935943604</v>
       </c>
       <c r="H595" t="s">
         <v>8</v>
@@ -15891,7 +15891,7 @@
         <v>10.1999998092651</v>
       </c>
       <c r="G597" t="n">
-        <v>9.10036849975586</v>
+        <v>9.10036754608154</v>
       </c>
       <c r="H597" t="s">
         <v>8</v>
@@ -15917,7 +15917,7 @@
         <v>10.1999998092651</v>
       </c>
       <c r="G598" t="n">
-        <v>9.10036849975586</v>
+        <v>9.10036754608154</v>
       </c>
       <c r="H598" t="s">
         <v>8</v>
@@ -15969,7 +15969,7 @@
         <v>10.1999998092651</v>
       </c>
       <c r="G600" t="n">
-        <v>9.10036849975586</v>
+        <v>9.10036754608154</v>
       </c>
       <c r="H600" t="s">
         <v>8</v>
@@ -16047,7 +16047,7 @@
         <v>10.1999998092651</v>
       </c>
       <c r="G603" t="n">
-        <v>9.10036849975586</v>
+        <v>9.10036754608154</v>
       </c>
       <c r="H603" t="s">
         <v>8</v>
@@ -16099,7 +16099,7 @@
         <v>10.1999998092651</v>
       </c>
       <c r="G605" t="n">
-        <v>9.10036849975586</v>
+        <v>9.10036754608154</v>
       </c>
       <c r="H605" t="s">
         <v>8</v>
@@ -16177,7 +16177,7 @@
         <v>10.1999998092651</v>
       </c>
       <c r="G608" t="n">
-        <v>9.10036849975586</v>
+        <v>9.10036754608154</v>
       </c>
       <c r="H608" t="s">
         <v>8</v>
@@ -16203,7 +16203,7 @@
         <v>10.1999998092651</v>
       </c>
       <c r="G609" t="n">
-        <v>9.10036849975586</v>
+        <v>9.10036754608154</v>
       </c>
       <c r="H609" t="s">
         <v>8</v>
@@ -16255,7 +16255,7 @@
         <v>10.1999998092651</v>
       </c>
       <c r="G611" t="n">
-        <v>9.10036849975586</v>
+        <v>9.10036754608154</v>
       </c>
       <c r="H611" t="s">
         <v>8</v>
@@ -16307,7 +16307,7 @@
         <v>10.1999998092651</v>
       </c>
       <c r="G613" t="n">
-        <v>9.10036849975586</v>
+        <v>9.10036754608154</v>
       </c>
       <c r="H613" t="s">
         <v>8</v>
@@ -16359,7 +16359,7 @@
         <v>10.3999996185303</v>
       </c>
       <c r="G615" t="n">
-        <v>9.27880668640137</v>
+        <v>9.27880573272705</v>
       </c>
       <c r="H615" t="s">
         <v>8</v>
@@ -16385,7 +16385,7 @@
         <v>10.3999996185303</v>
       </c>
       <c r="G616" t="n">
-        <v>9.27880668640137</v>
+        <v>9.27880573272705</v>
       </c>
       <c r="H616" t="s">
         <v>8</v>
@@ -16541,7 +16541,7 @@
         <v>10.6000003814697</v>
       </c>
       <c r="G622" t="n">
-        <v>9.45724678039551</v>
+        <v>9.45724487304688</v>
       </c>
       <c r="H622" t="s">
         <v>8</v>
@@ -16593,7 +16593,7 @@
         <v>10.3999996185303</v>
       </c>
       <c r="G624" t="n">
-        <v>9.27880668640137</v>
+        <v>9.27880573272705</v>
       </c>
       <c r="H624" t="s">
         <v>8</v>
@@ -16619,7 +16619,7 @@
         <v>10.3999996185303</v>
       </c>
       <c r="G625" t="n">
-        <v>9.27880668640137</v>
+        <v>9.27880573272705</v>
       </c>
       <c r="H625" t="s">
         <v>8</v>
@@ -16801,7 +16801,7 @@
         <v>10.3999996185303</v>
       </c>
       <c r="G632" t="n">
-        <v>9.27880668640137</v>
+        <v>9.27880573272705</v>
       </c>
       <c r="H632" t="s">
         <v>8</v>
@@ -16879,7 +16879,7 @@
         <v>10.3999996185303</v>
       </c>
       <c r="G635" t="n">
-        <v>9.27880668640137</v>
+        <v>9.27880573272705</v>
       </c>
       <c r="H635" t="s">
         <v>8</v>
@@ -16957,7 +16957,7 @@
         <v>10.3999996185303</v>
       </c>
       <c r="G638" t="n">
-        <v>9.27880668640137</v>
+        <v>9.27880573272705</v>
       </c>
       <c r="H638" t="s">
         <v>8</v>
@@ -17009,7 +17009,7 @@
         <v>10.3999996185303</v>
       </c>
       <c r="G640" t="n">
-        <v>9.27880668640137</v>
+        <v>9.27880573272705</v>
       </c>
       <c r="H640" t="s">
         <v>8</v>
@@ -17035,7 +17035,7 @@
         <v>10.3999996185303</v>
       </c>
       <c r="G641" t="n">
-        <v>9.27880668640137</v>
+        <v>9.27880573272705</v>
       </c>
       <c r="H641" t="s">
         <v>8</v>
@@ -17061,7 +17061,7 @@
         <v>10.3999996185303</v>
       </c>
       <c r="G642" t="n">
-        <v>9.27880668640137</v>
+        <v>9.27880573272705</v>
       </c>
       <c r="H642" t="s">
         <v>8</v>
@@ -17113,7 +17113,7 @@
         <v>10.3999996185303</v>
       </c>
       <c r="G644" t="n">
-        <v>9.36977577209473</v>
+        <v>9.36977481842041</v>
       </c>
       <c r="H644" t="s">
         <v>8</v>
@@ -17139,7 +17139,7 @@
         <v>10.1999998092651</v>
       </c>
       <c r="G645" t="n">
-        <v>9.18958759307861</v>
+        <v>9.1895866394043</v>
       </c>
       <c r="H645" t="s">
         <v>8</v>
@@ -17165,7 +17165,7 @@
         <v>10.1000003814697</v>
       </c>
       <c r="G646" t="n">
-        <v>9.09949398040771</v>
+        <v>9.0994930267334</v>
       </c>
       <c r="H646" t="s">
         <v>8</v>
@@ -17191,7 +17191,7 @@
         <v>10.3000001907349</v>
       </c>
       <c r="G647" t="n">
-        <v>9.27968215942383</v>
+        <v>9.27968120574951</v>
       </c>
       <c r="H647" t="s">
         <v>8</v>
@@ -17217,7 +17217,7 @@
         <v>10.1000003814697</v>
       </c>
       <c r="G648" t="n">
-        <v>9.09949398040771</v>
+        <v>9.0994930267334</v>
       </c>
       <c r="H648" t="s">
         <v>8</v>
@@ -17243,7 +17243,7 @@
         <v>10</v>
       </c>
       <c r="G649" t="n">
-        <v>9.00939846038818</v>
+        <v>9.0093994140625</v>
       </c>
       <c r="H649" t="s">
         <v>8</v>
@@ -17269,7 +17269,7 @@
         <v>10</v>
       </c>
       <c r="G650" t="n">
-        <v>9.00939846038818</v>
+        <v>9.0093994140625</v>
       </c>
       <c r="H650" t="s">
         <v>8</v>
@@ -17295,7 +17295,7 @@
         <v>10</v>
       </c>
       <c r="G651" t="n">
-        <v>9.00939846038818</v>
+        <v>9.0093994140625</v>
       </c>
       <c r="H651" t="s">
         <v>8</v>
@@ -17321,7 +17321,7 @@
         <v>10</v>
       </c>
       <c r="G652" t="n">
-        <v>9.00939846038818</v>
+        <v>9.0093994140625</v>
       </c>
       <c r="H652" t="s">
         <v>8</v>
@@ -17347,7 +17347,7 @@
         <v>10</v>
       </c>
       <c r="G653" t="n">
-        <v>9.00939846038818</v>
+        <v>9.0093994140625</v>
       </c>
       <c r="H653" t="s">
         <v>8</v>
@@ -17373,7 +17373,7 @@
         <v>10.1000003814697</v>
       </c>
       <c r="G654" t="n">
-        <v>9.09949398040771</v>
+        <v>9.0994930267334</v>
       </c>
       <c r="H654" t="s">
         <v>8</v>
@@ -17399,7 +17399,7 @@
         <v>10</v>
       </c>
       <c r="G655" t="n">
-        <v>9.00939846038818</v>
+        <v>9.0093994140625</v>
       </c>
       <c r="H655" t="s">
         <v>8</v>
@@ -17425,7 +17425,7 @@
         <v>10</v>
       </c>
       <c r="G656" t="n">
-        <v>9.00939846038818</v>
+        <v>9.0093994140625</v>
       </c>
       <c r="H656" t="s">
         <v>8</v>
@@ -17451,7 +17451,7 @@
         <v>10</v>
       </c>
       <c r="G657" t="n">
-        <v>9.00939846038818</v>
+        <v>9.0093994140625</v>
       </c>
       <c r="H657" t="s">
         <v>8</v>
@@ -17477,7 +17477,7 @@
         <v>10</v>
       </c>
       <c r="G658" t="n">
-        <v>9.00939846038818</v>
+        <v>9.0093994140625</v>
       </c>
       <c r="H658" t="s">
         <v>8</v>
@@ -17503,7 +17503,7 @@
         <v>10.1000003814697</v>
       </c>
       <c r="G659" t="n">
-        <v>9.09949398040771</v>
+        <v>9.0994930267334</v>
       </c>
       <c r="H659" t="s">
         <v>8</v>
@@ -17529,7 +17529,7 @@
         <v>10.1000003814697</v>
       </c>
       <c r="G660" t="n">
-        <v>9.09949398040771</v>
+        <v>9.0994930267334</v>
       </c>
       <c r="H660" t="s">
         <v>8</v>
@@ -17555,7 +17555,7 @@
         <v>10.1000003814697</v>
       </c>
       <c r="G661" t="n">
-        <v>9.09949398040771</v>
+        <v>9.0994930267334</v>
       </c>
       <c r="H661" t="s">
         <v>8</v>
@@ -17581,7 +17581,7 @@
         <v>10</v>
       </c>
       <c r="G662" t="n">
-        <v>9.00939846038818</v>
+        <v>9.0093994140625</v>
       </c>
       <c r="H662" t="s">
         <v>8</v>
@@ -17607,7 +17607,7 @@
         <v>10.1000003814697</v>
       </c>
       <c r="G663" t="n">
-        <v>9.09949398040771</v>
+        <v>9.0994930267334</v>
       </c>
       <c r="H663" t="s">
         <v>8</v>
@@ -17633,7 +17633,7 @@
         <v>10.1000003814697</v>
       </c>
       <c r="G664" t="n">
-        <v>9.09949398040771</v>
+        <v>9.0994930267334</v>
       </c>
       <c r="H664" t="s">
         <v>8</v>
@@ -17659,7 +17659,7 @@
         <v>10.1000003814697</v>
       </c>
       <c r="G665" t="n">
-        <v>9.09949398040771</v>
+        <v>9.0994930267334</v>
       </c>
       <c r="H665" t="s">
         <v>8</v>
@@ -17685,7 +17685,7 @@
         <v>10.1000003814697</v>
       </c>
       <c r="G666" t="n">
-        <v>9.09949398040771</v>
+        <v>9.0994930267334</v>
       </c>
       <c r="H666" t="s">
         <v>8</v>
@@ -17711,7 +17711,7 @@
         <v>10.1000003814697</v>
       </c>
       <c r="G667" t="n">
-        <v>9.09949398040771</v>
+        <v>9.0994930267334</v>
       </c>
       <c r="H667" t="s">
         <v>8</v>
@@ -17737,7 +17737,7 @@
         <v>10.1000003814697</v>
       </c>
       <c r="G668" t="n">
-        <v>9.09949398040771</v>
+        <v>9.0994930267334</v>
       </c>
       <c r="H668" t="s">
         <v>8</v>
@@ -17763,7 +17763,7 @@
         <v>10</v>
       </c>
       <c r="G669" t="n">
-        <v>9.00939846038818</v>
+        <v>9.0093994140625</v>
       </c>
       <c r="H669" t="s">
         <v>8</v>
@@ -17789,7 +17789,7 @@
         <v>10.1000003814697</v>
       </c>
       <c r="G670" t="n">
-        <v>9.09949398040771</v>
+        <v>9.0994930267334</v>
       </c>
       <c r="H670" t="s">
         <v>8</v>
@@ -17815,7 +17815,7 @@
         <v>10.1000003814697</v>
       </c>
       <c r="G671" t="n">
-        <v>9.09949398040771</v>
+        <v>9.0994930267334</v>
       </c>
       <c r="H671" t="s">
         <v>8</v>
@@ -17919,7 +17919,7 @@
         <v>9.85000038146973</v>
       </c>
       <c r="G675" t="n">
-        <v>8.87425708770752</v>
+        <v>8.87425899505615</v>
       </c>
       <c r="H675" t="s">
         <v>8</v>
@@ -17945,7 +17945,7 @@
         <v>10</v>
       </c>
       <c r="G676" t="n">
-        <v>9.00939846038818</v>
+        <v>9.0093994140625</v>
       </c>
       <c r="H676" t="s">
         <v>8</v>
@@ -17971,7 +17971,7 @@
         <v>10</v>
       </c>
       <c r="G677" t="n">
-        <v>9.00939846038818</v>
+        <v>9.0093994140625</v>
       </c>
       <c r="H677" t="s">
         <v>8</v>
@@ -17997,7 +17997,7 @@
         <v>10</v>
       </c>
       <c r="G678" t="n">
-        <v>9.00939846038818</v>
+        <v>9.0093994140625</v>
       </c>
       <c r="H678" t="s">
         <v>8</v>
@@ -18023,7 +18023,7 @@
         <v>10</v>
       </c>
       <c r="G679" t="n">
-        <v>9.00939846038818</v>
+        <v>9.0093994140625</v>
       </c>
       <c r="H679" t="s">
         <v>8</v>
@@ -18049,7 +18049,7 @@
         <v>10</v>
       </c>
       <c r="G680" t="n">
-        <v>9.00939846038818</v>
+        <v>9.0093994140625</v>
       </c>
       <c r="H680" t="s">
         <v>8</v>
@@ -18205,7 +18205,7 @@
         <v>10.3000001907349</v>
       </c>
       <c r="G686" t="n">
-        <v>9.27968215942383</v>
+        <v>9.27968120574951</v>
       </c>
       <c r="H686" t="s">
         <v>8</v>
@@ -18231,7 +18231,7 @@
         <v>10.1999998092651</v>
       </c>
       <c r="G687" t="n">
-        <v>9.18958759307861</v>
+        <v>9.1895866394043</v>
       </c>
       <c r="H687" t="s">
         <v>8</v>
@@ -18257,7 +18257,7 @@
         <v>10.3000001907349</v>
       </c>
       <c r="G688" t="n">
-        <v>9.27968215942383</v>
+        <v>9.27968120574951</v>
       </c>
       <c r="H688" t="s">
         <v>8</v>
@@ -18283,7 +18283,7 @@
         <v>10.3000001907349</v>
       </c>
       <c r="G689" t="n">
-        <v>9.27968215942383</v>
+        <v>9.27968120574951</v>
       </c>
       <c r="H689" t="s">
         <v>8</v>
@@ -18309,7 +18309,7 @@
         <v>10.1000003814697</v>
       </c>
       <c r="G690" t="n">
-        <v>9.09949398040771</v>
+        <v>9.0994930267334</v>
       </c>
       <c r="H690" t="s">
         <v>8</v>
@@ -18335,7 +18335,7 @@
         <v>10.1000003814697</v>
       </c>
       <c r="G691" t="n">
-        <v>9.09949398040771</v>
+        <v>9.0994930267334</v>
       </c>
       <c r="H691" t="s">
         <v>8</v>
@@ -18361,7 +18361,7 @@
         <v>10</v>
       </c>
       <c r="G692" t="n">
-        <v>9.00939846038818</v>
+        <v>9.0093994140625</v>
       </c>
       <c r="H692" t="s">
         <v>8</v>
@@ -18387,7 +18387,7 @@
         <v>10</v>
       </c>
       <c r="G693" t="n">
-        <v>9.00939846038818</v>
+        <v>9.0093994140625</v>
       </c>
       <c r="H693" t="s">
         <v>8</v>
@@ -18413,7 +18413,7 @@
         <v>10.1000003814697</v>
       </c>
       <c r="G694" t="n">
-        <v>9.09949398040771</v>
+        <v>9.0994930267334</v>
       </c>
       <c r="H694" t="s">
         <v>8</v>
@@ -18439,7 +18439,7 @@
         <v>10.1000003814697</v>
       </c>
       <c r="G695" t="n">
-        <v>9.09949398040771</v>
+        <v>9.0994930267334</v>
       </c>
       <c r="H695" t="s">
         <v>8</v>
@@ -18465,7 +18465,7 @@
         <v>10.1999998092651</v>
       </c>
       <c r="G696" t="n">
-        <v>9.18958759307861</v>
+        <v>9.1895866394043</v>
       </c>
       <c r="H696" t="s">
         <v>8</v>
@@ -18491,7 +18491,7 @@
         <v>10</v>
       </c>
       <c r="G697" t="n">
-        <v>9.00939846038818</v>
+        <v>9.0093994140625</v>
       </c>
       <c r="H697" t="s">
         <v>8</v>
@@ -18543,7 +18543,7 @@
         <v>10</v>
       </c>
       <c r="G699" t="n">
-        <v>9.00939846038818</v>
+        <v>9.0093994140625</v>
       </c>
       <c r="H699" t="s">
         <v>8</v>
@@ -18569,7 +18569,7 @@
         <v>10</v>
       </c>
       <c r="G700" t="n">
-        <v>9.00939846038818</v>
+        <v>9.0093994140625</v>
       </c>
       <c r="H700" t="s">
         <v>8</v>
@@ -18595,7 +18595,7 @@
         <v>10</v>
       </c>
       <c r="G701" t="n">
-        <v>9.00939846038818</v>
+        <v>9.0093994140625</v>
       </c>
       <c r="H701" t="s">
         <v>8</v>
@@ -18621,7 +18621,7 @@
         <v>10</v>
       </c>
       <c r="G702" t="n">
-        <v>9.00939846038818</v>
+        <v>9.0093994140625</v>
       </c>
       <c r="H702" t="s">
         <v>8</v>
@@ -18673,7 +18673,7 @@
         <v>10</v>
       </c>
       <c r="G704" t="n">
-        <v>9.00939846038818</v>
+        <v>9.0093994140625</v>
       </c>
       <c r="H704" t="s">
         <v>8</v>
@@ -18803,7 +18803,7 @@
         <v>10</v>
       </c>
       <c r="G709" t="n">
-        <v>9.00939846038818</v>
+        <v>9.0093994140625</v>
       </c>
       <c r="H709" t="s">
         <v>8</v>
@@ -18829,7 +18829,7 @@
         <v>10</v>
       </c>
       <c r="G710" t="n">
-        <v>9.00939846038818</v>
+        <v>9.0093994140625</v>
       </c>
       <c r="H710" t="s">
         <v>8</v>
@@ -18855,7 +18855,7 @@
         <v>10</v>
       </c>
       <c r="G711" t="n">
-        <v>9.00939846038818</v>
+        <v>9.0093994140625</v>
       </c>
       <c r="H711" t="s">
         <v>8</v>
@@ -18907,7 +18907,7 @@
         <v>10</v>
       </c>
       <c r="G713" t="n">
-        <v>9.00939846038818</v>
+        <v>9.0093994140625</v>
       </c>
       <c r="H713" t="s">
         <v>8</v>
@@ -18933,7 +18933,7 @@
         <v>10</v>
       </c>
       <c r="G714" t="n">
-        <v>9.00939846038818</v>
+        <v>9.0093994140625</v>
       </c>
       <c r="H714" t="s">
         <v>8</v>
@@ -19011,7 +19011,7 @@
         <v>10</v>
       </c>
       <c r="G717" t="n">
-        <v>9.00939846038818</v>
+        <v>9.0093994140625</v>
       </c>
       <c r="H717" t="s">
         <v>8</v>
@@ -19037,7 +19037,7 @@
         <v>10</v>
       </c>
       <c r="G718" t="n">
-        <v>9.00939846038818</v>
+        <v>9.0093994140625</v>
       </c>
       <c r="H718" t="s">
         <v>8</v>
@@ -19115,7 +19115,7 @@
         <v>10.1000003814697</v>
       </c>
       <c r="G721" t="n">
-        <v>9.09949398040771</v>
+        <v>9.0994930267334</v>
       </c>
       <c r="H721" t="s">
         <v>8</v>
@@ -19141,7 +19141,7 @@
         <v>10.1999998092651</v>
       </c>
       <c r="G722" t="n">
-        <v>9.18958759307861</v>
+        <v>9.1895866394043</v>
       </c>
       <c r="H722" t="s">
         <v>8</v>
@@ -19167,7 +19167,7 @@
         <v>10.1000003814697</v>
       </c>
       <c r="G723" t="n">
-        <v>9.09949398040771</v>
+        <v>9.0994930267334</v>
       </c>
       <c r="H723" t="s">
         <v>8</v>
@@ -19193,7 +19193,7 @@
         <v>10</v>
       </c>
       <c r="G724" t="n">
-        <v>9.00939846038818</v>
+        <v>9.0093994140625</v>
       </c>
       <c r="H724" t="s">
         <v>8</v>
@@ -19219,7 +19219,7 @@
         <v>10</v>
       </c>
       <c r="G725" t="n">
-        <v>9.00939846038818</v>
+        <v>9.0093994140625</v>
       </c>
       <c r="H725" t="s">
         <v>8</v>
@@ -19245,7 +19245,7 @@
         <v>10</v>
       </c>
       <c r="G726" t="n">
-        <v>9.00939846038818</v>
+        <v>9.0093994140625</v>
       </c>
       <c r="H726" t="s">
         <v>8</v>
@@ -19271,7 +19271,7 @@
         <v>10</v>
       </c>
       <c r="G727" t="n">
-        <v>9.00939846038818</v>
+        <v>9.0093994140625</v>
       </c>
       <c r="H727" t="s">
         <v>8</v>
@@ -19297,7 +19297,7 @@
         <v>10</v>
       </c>
       <c r="G728" t="n">
-        <v>9.00939846038818</v>
+        <v>9.0093994140625</v>
       </c>
       <c r="H728" t="s">
         <v>8</v>
@@ -19323,7 +19323,7 @@
         <v>10</v>
       </c>
       <c r="G729" t="n">
-        <v>9.00939846038818</v>
+        <v>9.0093994140625</v>
       </c>
       <c r="H729" t="s">
         <v>8</v>
@@ -19349,7 +19349,7 @@
         <v>10</v>
       </c>
       <c r="G730" t="n">
-        <v>9.00939846038818</v>
+        <v>9.0093994140625</v>
       </c>
       <c r="H730" t="s">
         <v>8</v>
@@ -19375,7 +19375,7 @@
         <v>10.1000003814697</v>
       </c>
       <c r="G731" t="n">
-        <v>9.09949398040771</v>
+        <v>9.0994930267334</v>
       </c>
       <c r="H731" t="s">
         <v>8</v>
@@ -19427,7 +19427,7 @@
         <v>10.1000003814697</v>
       </c>
       <c r="G733" t="n">
-        <v>9.09949398040771</v>
+        <v>9.0994930267334</v>
       </c>
       <c r="H733" t="s">
         <v>8</v>
@@ -19453,7 +19453,7 @@
         <v>10.1000003814697</v>
       </c>
       <c r="G734" t="n">
-        <v>9.09949398040771</v>
+        <v>9.0994930267334</v>
       </c>
       <c r="H734" t="s">
         <v>8</v>
@@ -19505,7 +19505,7 @@
         <v>10</v>
       </c>
       <c r="G736" t="n">
-        <v>9.00939846038818</v>
+        <v>9.0093994140625</v>
       </c>
       <c r="H736" t="s">
         <v>8</v>
@@ -19557,7 +19557,7 @@
         <v>10</v>
       </c>
       <c r="G738" t="n">
-        <v>9.00939846038818</v>
+        <v>9.0093994140625</v>
       </c>
       <c r="H738" t="s">
         <v>8</v>
@@ -19583,7 +19583,7 @@
         <v>10</v>
       </c>
       <c r="G739" t="n">
-        <v>9.00939846038818</v>
+        <v>9.0093994140625</v>
       </c>
       <c r="H739" t="s">
         <v>8</v>
@@ -19609,7 +19609,7 @@
         <v>10.1999998092651</v>
       </c>
       <c r="G740" t="n">
-        <v>9.18958759307861</v>
+        <v>9.1895866394043</v>
       </c>
       <c r="H740" t="s">
         <v>8</v>
@@ -19635,7 +19635,7 @@
         <v>10.1999998092651</v>
       </c>
       <c r="G741" t="n">
-        <v>9.18958759307861</v>
+        <v>9.1895866394043</v>
       </c>
       <c r="H741" t="s">
         <v>8</v>
@@ -19661,7 +19661,7 @@
         <v>10.3000001907349</v>
       </c>
       <c r="G742" t="n">
-        <v>9.27968215942383</v>
+        <v>9.27968120574951</v>
       </c>
       <c r="H742" t="s">
         <v>8</v>
@@ -19687,7 +19687,7 @@
         <v>10.3999996185303</v>
       </c>
       <c r="G743" t="n">
-        <v>9.36977577209473</v>
+        <v>9.36977481842041</v>
       </c>
       <c r="H743" t="s">
         <v>8</v>
@@ -19713,7 +19713,7 @@
         <v>10.1999998092651</v>
       </c>
       <c r="G744" t="n">
-        <v>9.18958759307861</v>
+        <v>9.1895866394043</v>
       </c>
       <c r="H744" t="s">
         <v>8</v>
@@ -19739,7 +19739,7 @@
         <v>10.1999998092651</v>
       </c>
       <c r="G745" t="n">
-        <v>9.18958759307861</v>
+        <v>9.1895866394043</v>
       </c>
       <c r="H745" t="s">
         <v>8</v>
@@ -19765,7 +19765,7 @@
         <v>10.1000003814697</v>
       </c>
       <c r="G746" t="n">
-        <v>9.09949398040771</v>
+        <v>9.0994930267334</v>
       </c>
       <c r="H746" t="s">
         <v>8</v>
@@ -19791,7 +19791,7 @@
         <v>10.1999998092651</v>
       </c>
       <c r="G747" t="n">
-        <v>9.18958759307861</v>
+        <v>9.1895866394043</v>
       </c>
       <c r="H747" t="s">
         <v>8</v>
@@ -19817,7 +19817,7 @@
         <v>10.1999998092651</v>
       </c>
       <c r="G748" t="n">
-        <v>9.18958759307861</v>
+        <v>9.1895866394043</v>
       </c>
       <c r="H748" t="s">
         <v>8</v>
@@ -19843,7 +19843,7 @@
         <v>10.1999998092651</v>
       </c>
       <c r="G749" t="n">
-        <v>9.18958759307861</v>
+        <v>9.1895866394043</v>
       </c>
       <c r="H749" t="s">
         <v>8</v>
@@ -19869,7 +19869,7 @@
         <v>10.1999998092651</v>
       </c>
       <c r="G750" t="n">
-        <v>9.18958759307861</v>
+        <v>9.1895866394043</v>
       </c>
       <c r="H750" t="s">
         <v>8</v>
@@ -19895,7 +19895,7 @@
         <v>10.1000003814697</v>
       </c>
       <c r="G751" t="n">
-        <v>9.09949398040771</v>
+        <v>9.0994930267334</v>
       </c>
       <c r="H751" t="s">
         <v>8</v>
@@ -19921,7 +19921,7 @@
         <v>10.1999998092651</v>
       </c>
       <c r="G752" t="n">
-        <v>9.18958759307861</v>
+        <v>9.1895866394043</v>
       </c>
       <c r="H752" t="s">
         <v>8</v>
@@ -19947,7 +19947,7 @@
         <v>10.3000001907349</v>
       </c>
       <c r="G753" t="n">
-        <v>9.27968215942383</v>
+        <v>9.27968120574951</v>
       </c>
       <c r="H753" t="s">
         <v>8</v>
@@ -19973,7 +19973,7 @@
         <v>10.3999996185303</v>
       </c>
       <c r="G754" t="n">
-        <v>9.36977577209473</v>
+        <v>9.36977481842041</v>
       </c>
       <c r="H754" t="s">
         <v>8</v>
@@ -19999,7 +19999,7 @@
         <v>10.5</v>
       </c>
       <c r="G755" t="n">
-        <v>9.45986938476562</v>
+        <v>9.45986843109131</v>
       </c>
       <c r="H755" t="s">
         <v>8</v>
@@ -20025,7 +20025,7 @@
         <v>10.6999998092651</v>
       </c>
       <c r="G756" t="n">
-        <v>9.64005661010742</v>
+        <v>9.64005756378174</v>
       </c>
       <c r="H756" t="s">
         <v>8</v>
@@ -20337,7 +20337,7 @@
         <v>10.6999998092651</v>
       </c>
       <c r="G768" t="n">
-        <v>9.64005661010742</v>
+        <v>9.64005756378174</v>
       </c>
       <c r="H768" t="s">
         <v>8</v>
@@ -20363,7 +20363,7 @@
         <v>10.6999998092651</v>
       </c>
       <c r="G769" t="n">
-        <v>9.64005661010742</v>
+        <v>9.64005756378174</v>
       </c>
       <c r="H769" t="s">
         <v>8</v>
@@ -20857,7 +20857,7 @@
         <v>11.1000003814697</v>
       </c>
       <c r="G788" t="n">
-        <v>10.0004329681396</v>
+        <v>10.000433921814</v>
       </c>
       <c r="H788" t="s">
         <v>8</v>
@@ -21169,7 +21169,7 @@
         <v>11.8000001907349</v>
       </c>
       <c r="G800" t="n">
-        <v>10.6310930252075</v>
+        <v>10.6310911178589</v>
       </c>
       <c r="H800" t="s">
         <v>8</v>
@@ -21195,7 +21195,7 @@
         <v>11.6999998092651</v>
       </c>
       <c r="G801" t="n">
-        <v>10.540997505188</v>
+        <v>10.5409965515137</v>
       </c>
       <c r="H801" t="s">
         <v>8</v>
@@ -21221,7 +21221,7 @@
         <v>11.8000001907349</v>
       </c>
       <c r="G802" t="n">
-        <v>10.6310930252075</v>
+        <v>10.6310911178589</v>
       </c>
       <c r="H802" t="s">
         <v>8</v>
@@ -21247,7 +21247,7 @@
         <v>11.8000001907349</v>
       </c>
       <c r="G803" t="n">
-        <v>10.6310930252075</v>
+        <v>10.6310911178589</v>
       </c>
       <c r="H803" t="s">
         <v>8</v>
@@ -21273,7 +21273,7 @@
         <v>11.8000001907349</v>
       </c>
       <c r="G804" t="n">
-        <v>10.6310930252075</v>
+        <v>10.6310911178589</v>
       </c>
       <c r="H804" t="s">
         <v>8</v>
@@ -21299,7 +21299,7 @@
         <v>11.8999996185303</v>
       </c>
       <c r="G805" t="n">
-        <v>10.7211856842041</v>
+        <v>10.7211847305298</v>
       </c>
       <c r="H805" t="s">
         <v>8</v>
@@ -21325,7 +21325,7 @@
         <v>11.8000001907349</v>
       </c>
       <c r="G806" t="n">
-        <v>10.6310930252075</v>
+        <v>10.6310911178589</v>
       </c>
       <c r="H806" t="s">
         <v>8</v>
@@ -21351,7 +21351,7 @@
         <v>11.8999996185303</v>
       </c>
       <c r="G807" t="n">
-        <v>10.7211856842041</v>
+        <v>10.7211847305298</v>
       </c>
       <c r="H807" t="s">
         <v>8</v>
@@ -21377,7 +21377,7 @@
         <v>11.8999996185303</v>
       </c>
       <c r="G808" t="n">
-        <v>10.7211856842041</v>
+        <v>10.7211847305298</v>
       </c>
       <c r="H808" t="s">
         <v>8</v>
@@ -21403,7 +21403,7 @@
         <v>11.6999998092651</v>
       </c>
       <c r="G809" t="n">
-        <v>10.540997505188</v>
+        <v>10.5409965515137</v>
       </c>
       <c r="H809" t="s">
         <v>8</v>
@@ -22131,7 +22131,7 @@
         <v>12.5</v>
       </c>
       <c r="G837" t="n">
-        <v>11.2617483139038</v>
+        <v>11.2617502212524</v>
       </c>
       <c r="H837" t="s">
         <v>8</v>
@@ -22443,7 +22443,7 @@
         <v>11.8999996185303</v>
       </c>
       <c r="G849" t="n">
-        <v>10.7211856842041</v>
+        <v>10.7211847305298</v>
       </c>
       <c r="H849" t="s">
         <v>8</v>
@@ -22469,7 +22469,7 @@
         <v>11.8000001907349</v>
       </c>
       <c r="G850" t="n">
-        <v>10.6310930252075</v>
+        <v>10.6310911178589</v>
       </c>
       <c r="H850" t="s">
         <v>8</v>
@@ -22495,7 +22495,7 @@
         <v>11.8000001907349</v>
       </c>
       <c r="G851" t="n">
-        <v>10.6310930252075</v>
+        <v>10.6310911178589</v>
       </c>
       <c r="H851" t="s">
         <v>8</v>
@@ -22599,7 +22599,7 @@
         <v>11.3999996185303</v>
       </c>
       <c r="G855" t="n">
-        <v>10.2707147598267</v>
+        <v>10.270715713501</v>
       </c>
       <c r="H855" t="s">
         <v>8</v>
@@ -22651,7 +22651,7 @@
         <v>11.1000003814697</v>
       </c>
       <c r="G857" t="n">
-        <v>10.0004329681396</v>
+        <v>10.000433921814</v>
       </c>
       <c r="H857" t="s">
         <v>8</v>
@@ -22677,7 +22677,7 @@
         <v>10.6000003814697</v>
       </c>
       <c r="G858" t="n">
-        <v>9.54996490478516</v>
+        <v>9.54996395111084</v>
       </c>
       <c r="H858" t="s">
         <v>8</v>
@@ -22703,7 +22703,7 @@
         <v>10.1000003814697</v>
       </c>
       <c r="G859" t="n">
-        <v>9.09949398040771</v>
+        <v>9.0994930267334</v>
       </c>
       <c r="H859" t="s">
         <v>8</v>
@@ -22729,7 +22729,7 @@
         <v>10</v>
       </c>
       <c r="G860" t="n">
-        <v>9.00939846038818</v>
+        <v>9.0093994140625</v>
       </c>
       <c r="H860" t="s">
         <v>8</v>
@@ -22755,7 +22755,7 @@
         <v>9.85000038146973</v>
       </c>
       <c r="G861" t="n">
-        <v>8.87425708770752</v>
+        <v>8.87425899505615</v>
       </c>
       <c r="H861" t="s">
         <v>8</v>
@@ -22807,7 +22807,7 @@
         <v>10</v>
       </c>
       <c r="G863" t="n">
-        <v>9.00939846038818</v>
+        <v>9.0093994140625</v>
       </c>
       <c r="H863" t="s">
         <v>8</v>
@@ -22833,7 +22833,7 @@
         <v>9</v>
       </c>
       <c r="G864" t="n">
-        <v>8.10846042633057</v>
+        <v>8.10845947265625</v>
       </c>
       <c r="H864" t="s">
         <v>8</v>
@@ -22859,7 +22859,7 @@
         <v>9</v>
       </c>
       <c r="G865" t="n">
-        <v>8.10846042633057</v>
+        <v>8.10845947265625</v>
       </c>
       <c r="H865" t="s">
         <v>8</v>
@@ -22885,7 +22885,7 @@
         <v>10.1999998092651</v>
       </c>
       <c r="G866" t="n">
-        <v>9.18958759307861</v>
+        <v>9.1895866394043</v>
       </c>
       <c r="H866" t="s">
         <v>8</v>
@@ -22911,7 +22911,7 @@
         <v>10</v>
       </c>
       <c r="G867" t="n">
-        <v>9.00939846038818</v>
+        <v>9.0093994140625</v>
       </c>
       <c r="H867" t="s">
         <v>8</v>
@@ -22937,7 +22937,7 @@
         <v>10</v>
       </c>
       <c r="G868" t="n">
-        <v>9.00939846038818</v>
+        <v>9.0093994140625</v>
       </c>
       <c r="H868" t="s">
         <v>8</v>
@@ -22989,7 +22989,7 @@
         <v>10.1000003814697</v>
       </c>
       <c r="G870" t="n">
-        <v>9.09949398040771</v>
+        <v>9.0994930267334</v>
       </c>
       <c r="H870" t="s">
         <v>8</v>
@@ -23015,7 +23015,7 @@
         <v>10.5</v>
       </c>
       <c r="G871" t="n">
-        <v>9.45986938476562</v>
+        <v>9.45986843109131</v>
       </c>
       <c r="H871" t="s">
         <v>8</v>
@@ -23067,7 +23067,7 @@
         <v>10.3000001907349</v>
       </c>
       <c r="G873" t="n">
-        <v>9.27968215942383</v>
+        <v>9.27968120574951</v>
       </c>
       <c r="H873" t="s">
         <v>8</v>
@@ -23093,7 +23093,7 @@
         <v>10.1999998092651</v>
       </c>
       <c r="G874" t="n">
-        <v>9.18958759307861</v>
+        <v>9.1895866394043</v>
       </c>
       <c r="H874" t="s">
         <v>8</v>
@@ -23145,7 +23145,7 @@
         <v>10.1000003814697</v>
       </c>
       <c r="G876" t="n">
-        <v>9.09949398040771</v>
+        <v>9.0994930267334</v>
       </c>
       <c r="H876" t="s">
         <v>8</v>
@@ -23223,7 +23223,7 @@
         <v>9.85999965667725</v>
       </c>
       <c r="G879" t="n">
-        <v>8.88326740264893</v>
+        <v>8.88326835632324</v>
       </c>
       <c r="H879" t="s">
         <v>8</v>
@@ -23249,7 +23249,7 @@
         <v>10</v>
       </c>
       <c r="G880" t="n">
-        <v>9.00939846038818</v>
+        <v>9.0093994140625</v>
       </c>
       <c r="H880" t="s">
         <v>8</v>
@@ -23275,7 +23275,7 @@
         <v>10.3000001907349</v>
       </c>
       <c r="G881" t="n">
-        <v>9.27968215942383</v>
+        <v>9.27968120574951</v>
       </c>
       <c r="H881" t="s">
         <v>8</v>
@@ -23327,7 +23327,7 @@
         <v>10.5</v>
       </c>
       <c r="G883" t="n">
-        <v>9.45986938476562</v>
+        <v>9.45986843109131</v>
       </c>
       <c r="H883" t="s">
         <v>8</v>
@@ -23353,7 +23353,7 @@
         <v>10.6000003814697</v>
       </c>
       <c r="G884" t="n">
-        <v>9.54996490478516</v>
+        <v>9.54996395111084</v>
       </c>
       <c r="H884" t="s">
         <v>8</v>
@@ -23379,7 +23379,7 @@
         <v>10.6499996185303</v>
       </c>
       <c r="G885" t="n">
-        <v>9.59500980377197</v>
+        <v>9.59501075744629</v>
       </c>
       <c r="H885" t="s">
         <v>8</v>
@@ -23405,7 +23405,7 @@
         <v>10.6999998092651</v>
       </c>
       <c r="G886" t="n">
-        <v>9.64005661010742</v>
+        <v>9.64005756378174</v>
       </c>
       <c r="H886" t="s">
         <v>8</v>
@@ -23431,7 +23431,7 @@
         <v>10.6999998092651</v>
       </c>
       <c r="G887" t="n">
-        <v>9.64005661010742</v>
+        <v>9.64005756378174</v>
       </c>
       <c r="H887" t="s">
         <v>8</v>
@@ -23457,7 +23457,7 @@
         <v>10.6999998092651</v>
       </c>
       <c r="G888" t="n">
-        <v>9.64005661010742</v>
+        <v>9.64005756378174</v>
       </c>
       <c r="H888" t="s">
         <v>8</v>
@@ -23509,7 +23509,7 @@
         <v>10.6000003814697</v>
       </c>
       <c r="G890" t="n">
-        <v>9.54996490478516</v>
+        <v>9.54996395111084</v>
       </c>
       <c r="H890" t="s">
         <v>8</v>
@@ -23587,7 +23587,7 @@
         <v>10.6000003814697</v>
       </c>
       <c r="G893" t="n">
-        <v>9.54996490478516</v>
+        <v>9.54996395111084</v>
       </c>
       <c r="H893" t="s">
         <v>8</v>
@@ -23613,7 +23613,7 @@
         <v>10.6499996185303</v>
       </c>
       <c r="G894" t="n">
-        <v>9.59500980377197</v>
+        <v>9.59501075744629</v>
       </c>
       <c r="H894" t="s">
         <v>8</v>
@@ -23639,7 +23639,7 @@
         <v>10.6999998092651</v>
       </c>
       <c r="G895" t="n">
-        <v>9.64005661010742</v>
+        <v>9.64005756378174</v>
       </c>
       <c r="H895" t="s">
         <v>8</v>
@@ -23665,7 +23665,7 @@
         <v>10.6000003814697</v>
       </c>
       <c r="G896" t="n">
-        <v>9.54996490478516</v>
+        <v>9.54996395111084</v>
       </c>
       <c r="H896" t="s">
         <v>8</v>
@@ -23691,7 +23691,7 @@
         <v>10.9499998092651</v>
       </c>
       <c r="G897" t="n">
-        <v>9.86529159545898</v>
+        <v>9.8652925491333</v>
       </c>
       <c r="H897" t="s">
         <v>8</v>
@@ -23717,7 +23717,7 @@
         <v>10.8500003814697</v>
       </c>
       <c r="G898" t="n">
-        <v>9.77519798278809</v>
+        <v>9.7751989364624</v>
       </c>
       <c r="H898" t="s">
         <v>8</v>
@@ -23743,7 +23743,7 @@
         <v>10.5</v>
       </c>
       <c r="G899" t="n">
-        <v>9.45986938476562</v>
+        <v>9.45986843109131</v>
       </c>
       <c r="H899" t="s">
         <v>8</v>
@@ -23769,7 +23769,7 @@
         <v>10.6999998092651</v>
       </c>
       <c r="G900" t="n">
-        <v>9.64005661010742</v>
+        <v>9.64005756378174</v>
       </c>
       <c r="H900" t="s">
         <v>8</v>
@@ -23873,7 +23873,7 @@
         <v>10.75</v>
       </c>
       <c r="G904" t="n">
-        <v>9.79495429992676</v>
+        <v>9.79495620727539</v>
       </c>
       <c r="H904" t="s">
         <v>8</v>
@@ -23899,7 +23899,7 @@
         <v>10.6999998092651</v>
       </c>
       <c r="G905" t="n">
-        <v>9.74939632415771</v>
+        <v>9.74939727783203</v>
       </c>
       <c r="H905" t="s">
         <v>8</v>
@@ -23977,7 +23977,7 @@
         <v>10.8000001907349</v>
       </c>
       <c r="G908" t="n">
-        <v>9.8405122756958</v>
+        <v>9.84051322937012</v>
       </c>
       <c r="H908" t="s">
         <v>8</v>
@@ -24003,7 +24003,7 @@
         <v>10.8000001907349</v>
       </c>
       <c r="G909" t="n">
-        <v>9.8405122756958</v>
+        <v>9.84051322937012</v>
       </c>
       <c r="H909" t="s">
         <v>8</v>
@@ -24029,7 +24029,7 @@
         <v>10.8000001907349</v>
       </c>
       <c r="G910" t="n">
-        <v>9.8405122756958</v>
+        <v>9.84051322937012</v>
       </c>
       <c r="H910" t="s">
         <v>8</v>
@@ -24055,7 +24055,7 @@
         <v>10.8999996185303</v>
       </c>
       <c r="G911" t="n">
-        <v>9.93162822723389</v>
+        <v>9.9316291809082</v>
       </c>
       <c r="H911" t="s">
         <v>8</v>
@@ -24081,7 +24081,7 @@
         <v>10.8999996185303</v>
       </c>
       <c r="G912" t="n">
-        <v>9.93162822723389</v>
+        <v>9.9316291809082</v>
       </c>
       <c r="H912" t="s">
         <v>8</v>
@@ -24107,7 +24107,7 @@
         <v>10.8999996185303</v>
       </c>
       <c r="G913" t="n">
-        <v>9.93162822723389</v>
+        <v>9.9316291809082</v>
       </c>
       <c r="H913" t="s">
         <v>8</v>
@@ -24133,7 +24133,7 @@
         <v>10.9499998092651</v>
       </c>
       <c r="G914" t="n">
-        <v>9.97718620300293</v>
+        <v>9.97718715667725</v>
       </c>
       <c r="H914" t="s">
         <v>8</v>
@@ -24159,7 +24159,7 @@
         <v>10.8999996185303</v>
       </c>
       <c r="G915" t="n">
-        <v>9.93162822723389</v>
+        <v>9.9316291809082</v>
       </c>
       <c r="H915" t="s">
         <v>8</v>
@@ -24185,7 +24185,7 @@
         <v>10.9499998092651</v>
       </c>
       <c r="G916" t="n">
-        <v>9.97718620300293</v>
+        <v>9.97718715667725</v>
       </c>
       <c r="H916" t="s">
         <v>8</v>
@@ -24211,7 +24211,7 @@
         <v>11</v>
       </c>
       <c r="G917" t="n">
-        <v>10.022744178772</v>
+        <v>10.0227451324463</v>
       </c>
       <c r="H917" t="s">
         <v>8</v>
@@ -24237,7 +24237,7 @@
         <v>10.8999996185303</v>
       </c>
       <c r="G918" t="n">
-        <v>9.93162822723389</v>
+        <v>9.9316291809082</v>
       </c>
       <c r="H918" t="s">
         <v>8</v>
@@ -24263,7 +24263,7 @@
         <v>10.8000001907349</v>
       </c>
       <c r="G919" t="n">
-        <v>9.8405122756958</v>
+        <v>9.84051322937012</v>
       </c>
       <c r="H919" t="s">
         <v>8</v>
@@ -24341,7 +24341,7 @@
         <v>10.75</v>
       </c>
       <c r="G922" t="n">
-        <v>9.79495429992676</v>
+        <v>9.79495620727539</v>
       </c>
       <c r="H922" t="s">
         <v>8</v>
@@ -24367,7 +24367,7 @@
         <v>10.75</v>
       </c>
       <c r="G923" t="n">
-        <v>9.79495429992676</v>
+        <v>9.79495620727539</v>
       </c>
       <c r="H923" t="s">
         <v>8</v>
@@ -24393,7 +24393,7 @@
         <v>10.6999998092651</v>
       </c>
       <c r="G924" t="n">
-        <v>9.74939632415771</v>
+        <v>9.74939727783203</v>
       </c>
       <c r="H924" t="s">
         <v>8</v>
@@ -24419,7 +24419,7 @@
         <v>10.6999998092651</v>
       </c>
       <c r="G925" t="n">
-        <v>9.74939632415771</v>
+        <v>9.74939727783203</v>
       </c>
       <c r="H925" t="s">
         <v>8</v>
@@ -24445,7 +24445,7 @@
         <v>10.75</v>
       </c>
       <c r="G926" t="n">
-        <v>9.79495429992676</v>
+        <v>9.79495620727539</v>
       </c>
       <c r="H926" t="s">
         <v>8</v>
@@ -24471,7 +24471,7 @@
         <v>11</v>
       </c>
       <c r="G927" t="n">
-        <v>10.022744178772</v>
+        <v>10.0227451324463</v>
       </c>
       <c r="H927" t="s">
         <v>8</v>
@@ -24497,7 +24497,7 @@
         <v>10.9499998092651</v>
       </c>
       <c r="G928" t="n">
-        <v>9.97718620300293</v>
+        <v>9.97718715667725</v>
       </c>
       <c r="H928" t="s">
         <v>8</v>
@@ -24523,7 +24523,7 @@
         <v>10.9499998092651</v>
       </c>
       <c r="G929" t="n">
-        <v>9.97718620300293</v>
+        <v>9.97718715667725</v>
       </c>
       <c r="H929" t="s">
         <v>8</v>
@@ -24549,7 +24549,7 @@
         <v>11</v>
       </c>
       <c r="G930" t="n">
-        <v>10.022744178772</v>
+        <v>10.0227451324463</v>
       </c>
       <c r="H930" t="s">
         <v>8</v>
@@ -24575,7 +24575,7 @@
         <v>10.8999996185303</v>
       </c>
       <c r="G931" t="n">
-        <v>9.93162822723389</v>
+        <v>9.9316291809082</v>
       </c>
       <c r="H931" t="s">
         <v>8</v>
@@ -24601,7 +24601,7 @@
         <v>10.8999996185303</v>
       </c>
       <c r="G932" t="n">
-        <v>9.93162822723389</v>
+        <v>9.9316291809082</v>
       </c>
       <c r="H932" t="s">
         <v>8</v>
@@ -24627,7 +24627,7 @@
         <v>10.8999996185303</v>
       </c>
       <c r="G933" t="n">
-        <v>9.93162822723389</v>
+        <v>9.9316291809082</v>
       </c>
       <c r="H933" t="s">
         <v>8</v>
@@ -24653,7 +24653,7 @@
         <v>10.8999996185303</v>
       </c>
       <c r="G934" t="n">
-        <v>9.93162822723389</v>
+        <v>9.9316291809082</v>
       </c>
       <c r="H934" t="s">
         <v>8</v>
@@ -24679,7 +24679,7 @@
         <v>10.8999996185303</v>
       </c>
       <c r="G935" t="n">
-        <v>9.93162822723389</v>
+        <v>9.9316291809082</v>
       </c>
       <c r="H935" t="s">
         <v>8</v>
@@ -24705,7 +24705,7 @@
         <v>10.8999996185303</v>
       </c>
       <c r="G936" t="n">
-        <v>9.93162822723389</v>
+        <v>9.9316291809082</v>
       </c>
       <c r="H936" t="s">
         <v>8</v>
@@ -24731,7 +24731,7 @@
         <v>10.8999996185303</v>
       </c>
       <c r="G937" t="n">
-        <v>9.93162822723389</v>
+        <v>9.9316291809082</v>
       </c>
       <c r="H937" t="s">
         <v>8</v>
@@ -24757,7 +24757,7 @@
         <v>10.8000001907349</v>
       </c>
       <c r="G938" t="n">
-        <v>9.8405122756958</v>
+        <v>9.84051322937012</v>
       </c>
       <c r="H938" t="s">
         <v>8</v>
@@ -24783,7 +24783,7 @@
         <v>10.8000001907349</v>
       </c>
       <c r="G939" t="n">
-        <v>9.8405122756958</v>
+        <v>9.84051322937012</v>
       </c>
       <c r="H939" t="s">
         <v>8</v>
@@ -24809,7 +24809,7 @@
         <v>10.8000001907349</v>
       </c>
       <c r="G940" t="n">
-        <v>9.8405122756958</v>
+        <v>9.84051322937012</v>
       </c>
       <c r="H940" t="s">
         <v>8</v>
@@ -24835,7 +24835,7 @@
         <v>10.6999998092651</v>
       </c>
       <c r="G941" t="n">
-        <v>9.74939632415771</v>
+        <v>9.74939727783203</v>
       </c>
       <c r="H941" t="s">
         <v>8</v>
@@ -24887,7 +24887,7 @@
         <v>10.6499996185303</v>
       </c>
       <c r="G943" t="n">
-        <v>9.70383930206299</v>
+        <v>9.70383834838867</v>
       </c>
       <c r="H943" t="s">
         <v>8</v>
@@ -24939,7 +24939,7 @@
         <v>10.6499996185303</v>
       </c>
       <c r="G945" t="n">
-        <v>9.70383930206299</v>
+        <v>9.70383834838867</v>
       </c>
       <c r="H945" t="s">
         <v>8</v>
@@ -24965,7 +24965,7 @@
         <v>10.8000001907349</v>
       </c>
       <c r="G946" t="n">
-        <v>9.8405122756958</v>
+        <v>9.84051322937012</v>
       </c>
       <c r="H946" t="s">
         <v>8</v>
@@ -24991,7 +24991,7 @@
         <v>10.9499998092651</v>
       </c>
       <c r="G947" t="n">
-        <v>9.97718620300293</v>
+        <v>9.97718715667725</v>
       </c>
       <c r="H947" t="s">
         <v>8</v>
@@ -25017,7 +25017,7 @@
         <v>10.8999996185303</v>
       </c>
       <c r="G948" t="n">
-        <v>9.93162822723389</v>
+        <v>9.9316291809082</v>
       </c>
       <c r="H948" t="s">
         <v>8</v>
@@ -25121,7 +25121,7 @@
         <v>11.3000001907349</v>
       </c>
       <c r="G952" t="n">
-        <v>10.2960929870605</v>
+        <v>10.2960920333862</v>
       </c>
       <c r="H952" t="s">
         <v>8</v>
@@ -25147,7 +25147,7 @@
         <v>11.0500001907349</v>
       </c>
       <c r="G953" t="n">
-        <v>10.0683012008667</v>
+        <v>10.0683031082153</v>
       </c>
       <c r="H953" t="s">
         <v>8</v>
@@ -25225,7 +25225,7 @@
         <v>11.0500001907349</v>
       </c>
       <c r="G956" t="n">
-        <v>10.0683012008667</v>
+        <v>10.0683031082153</v>
       </c>
       <c r="H956" t="s">
         <v>8</v>
@@ -25303,7 +25303,7 @@
         <v>11</v>
       </c>
       <c r="G959" t="n">
-        <v>10.022744178772</v>
+        <v>10.0227451324463</v>
       </c>
       <c r="H959" t="s">
         <v>8</v>
@@ -25563,7 +25563,7 @@
         <v>11</v>
       </c>
       <c r="G969" t="n">
-        <v>10.022744178772</v>
+        <v>10.0227451324463</v>
       </c>
       <c r="H969" t="s">
         <v>8</v>
@@ -25589,7 +25589,7 @@
         <v>11</v>
       </c>
       <c r="G970" t="n">
-        <v>10.022744178772</v>
+        <v>10.0227451324463</v>
       </c>
       <c r="H970" t="s">
         <v>8</v>
@@ -25615,7 +25615,7 @@
         <v>11</v>
       </c>
       <c r="G971" t="n">
-        <v>10.022744178772</v>
+        <v>10.0227451324463</v>
       </c>
       <c r="H971" t="s">
         <v>8</v>
@@ -25641,7 +25641,7 @@
         <v>11</v>
       </c>
       <c r="G972" t="n">
-        <v>10.022744178772</v>
+        <v>10.0227451324463</v>
       </c>
       <c r="H972" t="s">
         <v>8</v>
@@ -25667,7 +25667,7 @@
         <v>11</v>
       </c>
       <c r="G973" t="n">
-        <v>10.022744178772</v>
+        <v>10.0227451324463</v>
       </c>
       <c r="H973" t="s">
         <v>8</v>
@@ -25693,7 +25693,7 @@
         <v>10.9499998092651</v>
       </c>
       <c r="G974" t="n">
-        <v>9.97718620300293</v>
+        <v>9.97718715667725</v>
       </c>
       <c r="H974" t="s">
         <v>8</v>
@@ -25719,7 +25719,7 @@
         <v>11</v>
       </c>
       <c r="G975" t="n">
-        <v>10.022744178772</v>
+        <v>10.0227451324463</v>
       </c>
       <c r="H975" t="s">
         <v>8</v>
@@ -25823,7 +25823,7 @@
         <v>11</v>
       </c>
       <c r="G979" t="n">
-        <v>10.022744178772</v>
+        <v>10.0227451324463</v>
       </c>
       <c r="H979" t="s">
         <v>8</v>
@@ -25849,7 +25849,7 @@
         <v>11</v>
       </c>
       <c r="G980" t="n">
-        <v>10.022744178772</v>
+        <v>10.0227451324463</v>
       </c>
       <c r="H980" t="s">
         <v>8</v>
@@ -25875,7 +25875,7 @@
         <v>11</v>
       </c>
       <c r="G981" t="n">
-        <v>10.022744178772</v>
+        <v>10.0227451324463</v>
       </c>
       <c r="H981" t="s">
         <v>8</v>
@@ -25901,7 +25901,7 @@
         <v>10.9499998092651</v>
       </c>
       <c r="G982" t="n">
-        <v>9.97718620300293</v>
+        <v>9.97718715667725</v>
       </c>
       <c r="H982" t="s">
         <v>8</v>
@@ -25927,7 +25927,7 @@
         <v>10.9499998092651</v>
       </c>
       <c r="G983" t="n">
-        <v>9.97718620300293</v>
+        <v>9.97718715667725</v>
       </c>
       <c r="H983" t="s">
         <v>8</v>
@@ -25953,7 +25953,7 @@
         <v>10.9499998092651</v>
       </c>
       <c r="G984" t="n">
-        <v>9.97718620300293</v>
+        <v>9.97718715667725</v>
       </c>
       <c r="H984" t="s">
         <v>8</v>
@@ -25979,7 +25979,7 @@
         <v>10.9499998092651</v>
       </c>
       <c r="G985" t="n">
-        <v>9.97718620300293</v>
+        <v>9.97718715667725</v>
       </c>
       <c r="H985" t="s">
         <v>8</v>
@@ -26005,7 +26005,7 @@
         <v>10.8999996185303</v>
       </c>
       <c r="G986" t="n">
-        <v>9.93162822723389</v>
+        <v>9.9316291809082</v>
       </c>
       <c r="H986" t="s">
         <v>8</v>
@@ -26031,7 +26031,7 @@
         <v>10.8999996185303</v>
       </c>
       <c r="G987" t="n">
-        <v>9.93162822723389</v>
+        <v>9.9316291809082</v>
       </c>
       <c r="H987" t="s">
         <v>8</v>
@@ -26057,7 +26057,7 @@
         <v>10.8999996185303</v>
       </c>
       <c r="G988" t="n">
-        <v>9.93162822723389</v>
+        <v>9.9316291809082</v>
       </c>
       <c r="H988" t="s">
         <v>8</v>
@@ -26083,7 +26083,7 @@
         <v>10.8000001907349</v>
       </c>
       <c r="G989" t="n">
-        <v>9.8405122756958</v>
+        <v>9.84051322937012</v>
       </c>
       <c r="H989" t="s">
         <v>8</v>
@@ -26109,7 +26109,7 @@
         <v>10.6999998092651</v>
       </c>
       <c r="G990" t="n">
-        <v>9.74939632415771</v>
+        <v>9.74939727783203</v>
       </c>
       <c r="H990" t="s">
         <v>8</v>
@@ -26135,7 +26135,7 @@
         <v>10.6999998092651</v>
       </c>
       <c r="G991" t="n">
-        <v>9.74939632415771</v>
+        <v>9.74939727783203</v>
       </c>
       <c r="H991" t="s">
         <v>8</v>
@@ -26161,7 +26161,7 @@
         <v>10.8000001907349</v>
       </c>
       <c r="G992" t="n">
-        <v>9.8405122756958</v>
+        <v>9.84051322937012</v>
       </c>
       <c r="H992" t="s">
         <v>8</v>
@@ -26187,7 +26187,7 @@
         <v>10.6999998092651</v>
       </c>
       <c r="G993" t="n">
-        <v>9.74939632415771</v>
+        <v>9.74939727783203</v>
       </c>
       <c r="H993" t="s">
         <v>8</v>
@@ -26213,7 +26213,7 @@
         <v>10.6999998092651</v>
       </c>
       <c r="G994" t="n">
-        <v>9.74939632415771</v>
+        <v>9.74939727783203</v>
       </c>
       <c r="H994" t="s">
         <v>8</v>
@@ -26239,7 +26239,7 @@
         <v>10.6999998092651</v>
       </c>
       <c r="G995" t="n">
-        <v>9.74939632415771</v>
+        <v>9.74939727783203</v>
       </c>
       <c r="H995" t="s">
         <v>8</v>
@@ -26291,7 +26291,7 @@
         <v>10.6499996185303</v>
       </c>
       <c r="G997" t="n">
-        <v>9.70383930206299</v>
+        <v>9.70383834838867</v>
       </c>
       <c r="H997" t="s">
         <v>8</v>
@@ -26369,7 +26369,7 @@
         <v>10.6499996185303</v>
       </c>
       <c r="G1000" t="n">
-        <v>9.70383930206299</v>
+        <v>9.70383834838867</v>
       </c>
       <c r="H1000" t="s">
         <v>8</v>
@@ -26473,7 +26473,7 @@
         <v>10.3999996185303</v>
       </c>
       <c r="G1004" t="n">
-        <v>9.47604751586914</v>
+        <v>9.47604846954346</v>
       </c>
       <c r="H1004" t="s">
         <v>8</v>
@@ -26551,7 +26551,7 @@
         <v>10.0500001907349</v>
       </c>
       <c r="G1007" t="n">
-        <v>9.15714359283447</v>
+        <v>9.15714263916016</v>
       </c>
       <c r="H1007" t="s">
         <v>8</v>
@@ -26577,7 +26577,7 @@
         <v>9.96000003814697</v>
       </c>
       <c r="G1008" t="n">
-        <v>9.07513999938965</v>
+        <v>9.07513809204102</v>
       </c>
       <c r="H1008" t="s">
         <v>8</v>
@@ -26603,7 +26603,7 @@
         <v>9.92000007629395</v>
       </c>
       <c r="G1009" t="n">
-        <v>9.03869342803955</v>
+        <v>9.03869247436523</v>
       </c>
       <c r="H1009" t="s">
         <v>8</v>
@@ -26629,7 +26629,7 @@
         <v>9.97999954223633</v>
       </c>
       <c r="G1010" t="n">
-        <v>9.09336090087891</v>
+        <v>9.09336280822754</v>
       </c>
       <c r="H1010" t="s">
         <v>8</v>
@@ -26655,7 +26655,7 @@
         <v>10</v>
       </c>
       <c r="G1011" t="n">
-        <v>9.11158657073975</v>
+        <v>9.11158466339111</v>
       </c>
       <c r="H1011" t="s">
         <v>8</v>
@@ -26681,7 +26681,7 @@
         <v>9.97999954223633</v>
       </c>
       <c r="G1012" t="n">
-        <v>9.09336090087891</v>
+        <v>9.09336280822754</v>
       </c>
       <c r="H1012" t="s">
         <v>8</v>
@@ -26707,7 +26707,7 @@
         <v>10</v>
       </c>
       <c r="G1013" t="n">
-        <v>9.11158657073975</v>
+        <v>9.11158466339111</v>
       </c>
       <c r="H1013" t="s">
         <v>8</v>
@@ -26785,7 +26785,7 @@
         <v>9.76000022888184</v>
       </c>
       <c r="G1016" t="n">
-        <v>8.89290714263916</v>
+        <v>8.89290618896484</v>
       </c>
       <c r="H1016" t="s">
         <v>8</v>
@@ -26863,7 +26863,7 @@
         <v>9.68000030517578</v>
       </c>
       <c r="G1019" t="n">
-        <v>8.82001686096191</v>
+        <v>8.82001495361328</v>
       </c>
       <c r="H1019" t="s">
         <v>8</v>
@@ -26889,7 +26889,7 @@
         <v>9.89999961853027</v>
       </c>
       <c r="G1020" t="n">
-        <v>9.02046871185303</v>
+        <v>9.02046966552734</v>
       </c>
       <c r="H1020" t="s">
         <v>8</v>
@@ -26915,7 +26915,7 @@
         <v>9.73999977111816</v>
       </c>
       <c r="G1021" t="n">
-        <v>8.87468338012695</v>
+        <v>8.87468528747559</v>
       </c>
       <c r="H1021" t="s">
         <v>8</v>
@@ -26967,7 +26967,7 @@
         <v>9.39999961853027</v>
       </c>
       <c r="G1023" t="n">
-        <v>8.56489086151123</v>
+        <v>8.56488990783691</v>
       </c>
       <c r="H1023" t="s">
         <v>8</v>
@@ -26993,7 +26993,7 @@
         <v>9.68000030517578</v>
       </c>
       <c r="G1024" t="n">
-        <v>8.82001686096191</v>
+        <v>8.82001495361328</v>
       </c>
       <c r="H1024" t="s">
         <v>8</v>
@@ -27019,7 +27019,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G1025" t="n">
-        <v>8.83823776245117</v>
+        <v>8.83823871612549</v>
       </c>
       <c r="H1025" t="s">
         <v>8</v>
@@ -27045,7 +27045,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G1026" t="n">
-        <v>8.83823776245117</v>
+        <v>8.83823871612549</v>
       </c>
       <c r="H1026" t="s">
         <v>8</v>
@@ -27123,7 +27123,7 @@
         <v>9.64000034332275</v>
       </c>
       <c r="G1029" t="n">
-        <v>8.7835693359375</v>
+        <v>8.78356838226318</v>
       </c>
       <c r="H1029" t="s">
         <v>8</v>
@@ -27149,7 +27149,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G1030" t="n">
-        <v>8.83823776245117</v>
+        <v>8.83823871612549</v>
       </c>
       <c r="H1030" t="s">
         <v>8</v>
@@ -27227,7 +27227,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G1033" t="n">
-        <v>8.83823776245117</v>
+        <v>8.83823871612549</v>
       </c>
       <c r="H1033" t="s">
         <v>8</v>
@@ -27253,7 +27253,7 @@
         <v>9.97999954223633</v>
       </c>
       <c r="G1034" t="n">
-        <v>9.09336090087891</v>
+        <v>9.09336280822754</v>
       </c>
       <c r="H1034" t="s">
         <v>8</v>
@@ -27279,7 +27279,7 @@
         <v>9.97999954223633</v>
       </c>
       <c r="G1035" t="n">
-        <v>9.09336090087891</v>
+        <v>9.09336280822754</v>
       </c>
       <c r="H1035" t="s">
         <v>8</v>
@@ -27305,7 +27305,7 @@
         <v>9.89999961853027</v>
       </c>
       <c r="G1036" t="n">
-        <v>9.02046871185303</v>
+        <v>9.02046966552734</v>
       </c>
       <c r="H1036" t="s">
         <v>8</v>
@@ -27331,7 +27331,7 @@
         <v>10.6499996185303</v>
       </c>
       <c r="G1037" t="n">
-        <v>9.70383930206299</v>
+        <v>9.70383834838867</v>
       </c>
       <c r="H1037" t="s">
         <v>8</v>
@@ -27383,7 +27383,7 @@
         <v>11.0500001907349</v>
       </c>
       <c r="G1039" t="n">
-        <v>10.0683012008667</v>
+        <v>10.0683031082153</v>
       </c>
       <c r="H1039" t="s">
         <v>8</v>
@@ -27409,7 +27409,7 @@
         <v>11</v>
       </c>
       <c r="G1040" t="n">
-        <v>10.022744178772</v>
+        <v>10.0227451324463</v>
       </c>
       <c r="H1040" t="s">
         <v>8</v>
@@ -27539,7 +27539,7 @@
         <v>11.3000001907349</v>
       </c>
       <c r="G1045" t="n">
-        <v>10.2960929870605</v>
+        <v>10.2960920333862</v>
       </c>
       <c r="H1045" t="s">
         <v>8</v>
@@ -27565,7 +27565,7 @@
         <v>11.3000001907349</v>
       </c>
       <c r="G1046" t="n">
-        <v>10.2960929870605</v>
+        <v>10.2960920333862</v>
       </c>
       <c r="H1046" t="s">
         <v>8</v>
@@ -27591,7 +27591,7 @@
         <v>11.1499996185303</v>
       </c>
       <c r="G1047" t="n">
-        <v>10.1594181060791</v>
+        <v>10.1594171524048</v>
       </c>
       <c r="H1047" t="s">
         <v>8</v>
@@ -27617,7 +27617,7 @@
         <v>10.9499998092651</v>
       </c>
       <c r="G1048" t="n">
-        <v>9.97718620300293</v>
+        <v>9.97718715667725</v>
       </c>
       <c r="H1048" t="s">
         <v>8</v>
@@ -27643,7 +27643,7 @@
         <v>10.9499998092651</v>
       </c>
       <c r="G1049" t="n">
-        <v>9.97718620300293</v>
+        <v>9.97718715667725</v>
       </c>
       <c r="H1049" t="s">
         <v>8</v>
@@ -27669,7 +27669,7 @@
         <v>10.9499998092651</v>
       </c>
       <c r="G1050" t="n">
-        <v>9.97718620300293</v>
+        <v>9.97718715667725</v>
       </c>
       <c r="H1050" t="s">
         <v>8</v>
@@ -27695,7 +27695,7 @@
         <v>10.8999996185303</v>
       </c>
       <c r="G1051" t="n">
-        <v>9.93162822723389</v>
+        <v>9.9316291809082</v>
       </c>
       <c r="H1051" t="s">
         <v>8</v>
@@ -27721,7 +27721,7 @@
         <v>11</v>
       </c>
       <c r="G1052" t="n">
-        <v>10.022744178772</v>
+        <v>10.0227451324463</v>
       </c>
       <c r="H1052" t="s">
         <v>8</v>
@@ -27747,7 +27747,7 @@
         <v>10.9499998092651</v>
       </c>
       <c r="G1053" t="n">
-        <v>9.97718620300293</v>
+        <v>9.97718715667725</v>
       </c>
       <c r="H1053" t="s">
         <v>8</v>
@@ -27773,7 +27773,7 @@
         <v>10.6999998092651</v>
       </c>
       <c r="G1054" t="n">
-        <v>9.74939632415771</v>
+        <v>9.74939727783203</v>
       </c>
       <c r="H1054" t="s">
         <v>8</v>
@@ -27799,7 +27799,7 @@
         <v>10.9499998092651</v>
       </c>
       <c r="G1055" t="n">
-        <v>9.97718620300293</v>
+        <v>9.97718715667725</v>
       </c>
       <c r="H1055" t="s">
         <v>8</v>
@@ -27825,7 +27825,7 @@
         <v>10.8000001907349</v>
       </c>
       <c r="G1056" t="n">
-        <v>9.8405122756958</v>
+        <v>9.84051322937012</v>
       </c>
       <c r="H1056" t="s">
         <v>8</v>
@@ -27851,7 +27851,7 @@
         <v>10.9499998092651</v>
       </c>
       <c r="G1057" t="n">
-        <v>9.97718620300293</v>
+        <v>9.97718715667725</v>
       </c>
       <c r="H1057" t="s">
         <v>8</v>
@@ -27903,7 +27903,7 @@
         <v>10.8000001907349</v>
       </c>
       <c r="G1059" t="n">
-        <v>9.8405122756958</v>
+        <v>9.84051322937012</v>
       </c>
       <c r="H1059" t="s">
         <v>8</v>
@@ -27929,7 +27929,7 @@
         <v>10.75</v>
       </c>
       <c r="G1060" t="n">
-        <v>9.79495429992676</v>
+        <v>9.79495620727539</v>
       </c>
       <c r="H1060" t="s">
         <v>8</v>
@@ -27981,7 +27981,7 @@
         <v>10.6999998092651</v>
       </c>
       <c r="G1062" t="n">
-        <v>9.74939632415771</v>
+        <v>9.74939727783203</v>
       </c>
       <c r="H1062" t="s">
         <v>8</v>
@@ -28007,7 +28007,7 @@
         <v>10.75</v>
       </c>
       <c r="G1063" t="n">
-        <v>9.79495429992676</v>
+        <v>9.79495620727539</v>
       </c>
       <c r="H1063" t="s">
         <v>8</v>
@@ -28059,7 +28059,7 @@
         <v>10.3999996185303</v>
       </c>
       <c r="G1065" t="n">
-        <v>9.47604751586914</v>
+        <v>9.47604846954346</v>
       </c>
       <c r="H1065" t="s">
         <v>8</v>
@@ -28189,7 +28189,7 @@
         <v>10.8000001907349</v>
       </c>
       <c r="G1070" t="n">
-        <v>9.8405122756958</v>
+        <v>9.84051322937012</v>
       </c>
       <c r="H1070" t="s">
         <v>8</v>
@@ -28215,7 +28215,7 @@
         <v>10.8999996185303</v>
       </c>
       <c r="G1071" t="n">
-        <v>9.93162822723389</v>
+        <v>9.9316291809082</v>
       </c>
       <c r="H1071" t="s">
         <v>8</v>
@@ -28241,7 +28241,7 @@
         <v>10.75</v>
       </c>
       <c r="G1072" t="n">
-        <v>9.79495429992676</v>
+        <v>9.79495620727539</v>
       </c>
       <c r="H1072" t="s">
         <v>8</v>
@@ -28267,7 +28267,7 @@
         <v>10.8000001907349</v>
       </c>
       <c r="G1073" t="n">
-        <v>9.8405122756958</v>
+        <v>9.84051322937012</v>
       </c>
       <c r="H1073" t="s">
         <v>8</v>
@@ -28371,7 +28371,7 @@
         <v>10.75</v>
       </c>
       <c r="G1077" t="n">
-        <v>9.79495429992676</v>
+        <v>9.79495620727539</v>
       </c>
       <c r="H1077" t="s">
         <v>8</v>
@@ -28397,7 +28397,7 @@
         <v>10.75</v>
       </c>
       <c r="G1078" t="n">
-        <v>9.79495429992676</v>
+        <v>9.79495620727539</v>
       </c>
       <c r="H1078" t="s">
         <v>8</v>
@@ -28423,7 +28423,7 @@
         <v>10.75</v>
       </c>
       <c r="G1079" t="n">
-        <v>9.79495429992676</v>
+        <v>9.79495620727539</v>
       </c>
       <c r="H1079" t="s">
         <v>8</v>
@@ -28449,7 +28449,7 @@
         <v>10.6499996185303</v>
       </c>
       <c r="G1080" t="n">
-        <v>9.70383930206299</v>
+        <v>9.70383834838867</v>
       </c>
       <c r="H1080" t="s">
         <v>8</v>
@@ -28631,7 +28631,7 @@
         <v>10.6499996185303</v>
       </c>
       <c r="G1087" t="n">
-        <v>9.70383930206299</v>
+        <v>9.70383834838867</v>
       </c>
       <c r="H1087" t="s">
         <v>8</v>
@@ -28683,7 +28683,7 @@
         <v>10.8000001907349</v>
       </c>
       <c r="G1089" t="n">
-        <v>9.8405122756958</v>
+        <v>9.84051322937012</v>
       </c>
       <c r="H1089" t="s">
         <v>8</v>
@@ -28709,7 +28709,7 @@
         <v>10.8000001907349</v>
       </c>
       <c r="G1090" t="n">
-        <v>9.8405122756958</v>
+        <v>9.84051322937012</v>
       </c>
       <c r="H1090" t="s">
         <v>8</v>
@@ -28735,7 +28735,7 @@
         <v>10.8999996185303</v>
       </c>
       <c r="G1091" t="n">
-        <v>9.93162822723389</v>
+        <v>9.9316291809082</v>
       </c>
       <c r="H1091" t="s">
         <v>8</v>
@@ -28813,7 +28813,7 @@
         <v>10.8999996185303</v>
       </c>
       <c r="G1094" t="n">
-        <v>9.93162822723389</v>
+        <v>9.9316291809082</v>
       </c>
       <c r="H1094" t="s">
         <v>8</v>
@@ -28839,7 +28839,7 @@
         <v>10.6999998092651</v>
       </c>
       <c r="G1095" t="n">
-        <v>9.74939632415771</v>
+        <v>9.74939727783203</v>
       </c>
       <c r="H1095" t="s">
         <v>8</v>
@@ -28865,7 +28865,7 @@
         <v>10.6999998092651</v>
       </c>
       <c r="G1096" t="n">
-        <v>9.74939632415771</v>
+        <v>9.74939727783203</v>
       </c>
       <c r="H1096" t="s">
         <v>8</v>
@@ -28917,7 +28917,7 @@
         <v>10.75</v>
       </c>
       <c r="G1098" t="n">
-        <v>9.79495429992676</v>
+        <v>9.79495620727539</v>
       </c>
       <c r="H1098" t="s">
         <v>8</v>
@@ -28943,7 +28943,7 @@
         <v>10.8000001907349</v>
       </c>
       <c r="G1099" t="n">
-        <v>9.8405122756958</v>
+        <v>9.84051322937012</v>
       </c>
       <c r="H1099" t="s">
         <v>8</v>
@@ -28969,7 +28969,7 @@
         <v>10.8000001907349</v>
       </c>
       <c r="G1100" t="n">
-        <v>9.8405122756958</v>
+        <v>9.84051322937012</v>
       </c>
       <c r="H1100" t="s">
         <v>8</v>
@@ -28995,7 +28995,7 @@
         <v>10.75</v>
       </c>
       <c r="G1101" t="n">
-        <v>9.79495429992676</v>
+        <v>9.79495620727539</v>
       </c>
       <c r="H1101" t="s">
         <v>8</v>
@@ -29021,7 +29021,7 @@
         <v>10.8999996185303</v>
       </c>
       <c r="G1102" t="n">
-        <v>9.93162822723389</v>
+        <v>9.9316291809082</v>
       </c>
       <c r="H1102" t="s">
         <v>8</v>
@@ -29047,7 +29047,7 @@
         <v>10.9499998092651</v>
       </c>
       <c r="G1103" t="n">
-        <v>9.97718620300293</v>
+        <v>9.97718715667725</v>
       </c>
       <c r="H1103" t="s">
         <v>8</v>
@@ -29073,7 +29073,7 @@
         <v>10.8999996185303</v>
       </c>
       <c r="G1104" t="n">
-        <v>9.93162822723389</v>
+        <v>9.9316291809082</v>
       </c>
       <c r="H1104" t="s">
         <v>8</v>
@@ -29099,7 +29099,7 @@
         <v>10.8000001907349</v>
       </c>
       <c r="G1105" t="n">
-        <v>9.8405122756958</v>
+        <v>9.84051322937012</v>
       </c>
       <c r="H1105" t="s">
         <v>8</v>
@@ -29125,7 +29125,7 @@
         <v>10.6999998092651</v>
       </c>
       <c r="G1106" t="n">
-        <v>9.74939632415771</v>
+        <v>9.74939727783203</v>
       </c>
       <c r="H1106" t="s">
         <v>8</v>
@@ -29151,7 +29151,7 @@
         <v>10.8000001907349</v>
       </c>
       <c r="G1107" t="n">
-        <v>9.8405122756958</v>
+        <v>9.84051322937012</v>
       </c>
       <c r="H1107" t="s">
         <v>8</v>
@@ -29177,7 +29177,7 @@
         <v>10.8000001907349</v>
       </c>
       <c r="G1108" t="n">
-        <v>9.8405122756958</v>
+        <v>9.84051322937012</v>
       </c>
       <c r="H1108" t="s">
         <v>8</v>
@@ -29203,7 +29203,7 @@
         <v>10.8999996185303</v>
       </c>
       <c r="G1109" t="n">
-        <v>9.93162822723389</v>
+        <v>9.9316291809082</v>
       </c>
       <c r="H1109" t="s">
         <v>8</v>
@@ -29229,7 +29229,7 @@
         <v>10.8000001907349</v>
       </c>
       <c r="G1110" t="n">
-        <v>9.8405122756958</v>
+        <v>9.84051322937012</v>
       </c>
       <c r="H1110" t="s">
         <v>8</v>
@@ -29255,7 +29255,7 @@
         <v>10.6999998092651</v>
       </c>
       <c r="G1111" t="n">
-        <v>9.74939632415771</v>
+        <v>9.74939727783203</v>
       </c>
       <c r="H1111" t="s">
         <v>8</v>
@@ -29281,7 +29281,7 @@
         <v>10.8000001907349</v>
       </c>
       <c r="G1112" t="n">
-        <v>9.8405122756958</v>
+        <v>9.84051322937012</v>
       </c>
       <c r="H1112" t="s">
         <v>8</v>
@@ -29307,7 +29307,7 @@
         <v>10.8999996185303</v>
       </c>
       <c r="G1113" t="n">
-        <v>9.93162822723389</v>
+        <v>9.9316291809082</v>
       </c>
       <c r="H1113" t="s">
         <v>8</v>
@@ -29333,7 +29333,7 @@
         <v>10.8000001907349</v>
       </c>
       <c r="G1114" t="n">
-        <v>9.8405122756958</v>
+        <v>9.84051322937012</v>
       </c>
       <c r="H1114" t="s">
         <v>8</v>
@@ -29359,7 +29359,7 @@
         <v>10.75</v>
       </c>
       <c r="G1115" t="n">
-        <v>9.79495429992676</v>
+        <v>9.79495620727539</v>
       </c>
       <c r="H1115" t="s">
         <v>8</v>
@@ -29385,7 +29385,7 @@
         <v>10.75</v>
       </c>
       <c r="G1116" t="n">
-        <v>9.79495429992676</v>
+        <v>9.79495620727539</v>
       </c>
       <c r="H1116" t="s">
         <v>8</v>
@@ -29411,7 +29411,7 @@
         <v>10.9499998092651</v>
       </c>
       <c r="G1117" t="n">
-        <v>9.97718620300293</v>
+        <v>9.97718715667725</v>
       </c>
       <c r="H1117" t="s">
         <v>8</v>
@@ -29437,7 +29437,7 @@
         <v>10.8999996185303</v>
       </c>
       <c r="G1118" t="n">
-        <v>9.93162822723389</v>
+        <v>9.9316291809082</v>
       </c>
       <c r="H1118" t="s">
         <v>8</v>
@@ -29463,7 +29463,7 @@
         <v>11</v>
       </c>
       <c r="G1119" t="n">
-        <v>10.022744178772</v>
+        <v>10.0227451324463</v>
       </c>
       <c r="H1119" t="s">
         <v>8</v>
@@ -29489,7 +29489,7 @@
         <v>11</v>
       </c>
       <c r="G1120" t="n">
-        <v>10.022744178772</v>
+        <v>10.0227451324463</v>
       </c>
       <c r="H1120" t="s">
         <v>8</v>
@@ -29515,7 +29515,7 @@
         <v>11.0500001907349</v>
       </c>
       <c r="G1121" t="n">
-        <v>10.0683012008667</v>
+        <v>10.0683031082153</v>
       </c>
       <c r="H1121" t="s">
         <v>8</v>
@@ -29541,7 +29541,7 @@
         <v>11.1499996185303</v>
       </c>
       <c r="G1122" t="n">
-        <v>10.1594181060791</v>
+        <v>10.1594171524048</v>
       </c>
       <c r="H1122" t="s">
         <v>8</v>
@@ -29645,7 +29645,7 @@
         <v>10.9499998092651</v>
       </c>
       <c r="G1126" t="n">
-        <v>9.97718620300293</v>
+        <v>9.97718715667725</v>
       </c>
       <c r="H1126" t="s">
         <v>8</v>
@@ -29671,7 +29671,7 @@
         <v>11.0500001907349</v>
       </c>
       <c r="G1127" t="n">
-        <v>10.0683012008667</v>
+        <v>10.0683031082153</v>
       </c>
       <c r="H1127" t="s">
         <v>8</v>
@@ -29749,7 +29749,7 @@
         <v>11.8999996185303</v>
       </c>
       <c r="G1130" t="n">
-        <v>10.8427858352661</v>
+        <v>10.8427867889404</v>
       </c>
       <c r="H1130" t="s">
         <v>8</v>
@@ -29775,7 +29775,7 @@
         <v>12.1000003814697</v>
       </c>
       <c r="G1131" t="n">
-        <v>11.0250186920166</v>
+        <v>11.0250196456909</v>
       </c>
       <c r="H1131" t="s">
         <v>8</v>
@@ -29801,7 +29801,7 @@
         <v>12.3999996185303</v>
       </c>
       <c r="G1132" t="n">
-        <v>11.2983655929565</v>
+        <v>11.2983646392822</v>
       </c>
       <c r="H1132" t="s">
         <v>8</v>
@@ -29853,7 +29853,7 @@
         <v>12.5</v>
       </c>
       <c r="G1134" t="n">
-        <v>11.3894815444946</v>
+        <v>11.3894824981689</v>
       </c>
       <c r="H1134" t="s">
         <v>8</v>
@@ -29905,7 +29905,7 @@
         <v>12.6499996185303</v>
       </c>
       <c r="G1136" t="n">
-        <v>11.5261564254761</v>
+        <v>11.5261554718018</v>
       </c>
       <c r="H1136" t="s">
         <v>8</v>
@@ -29931,7 +29931,7 @@
         <v>12.6499996185303</v>
       </c>
       <c r="G1137" t="n">
-        <v>11.5261564254761</v>
+        <v>11.5261554718018</v>
       </c>
       <c r="H1137" t="s">
         <v>8</v>
@@ -29983,7 +29983,7 @@
         <v>12.8500003814697</v>
       </c>
       <c r="G1139" t="n">
-        <v>11.7083883285522</v>
+        <v>11.7083873748779</v>
       </c>
       <c r="H1139" t="s">
         <v>8</v>
@@ -30009,7 +30009,7 @@
         <v>12.8999996185303</v>
       </c>
       <c r="G1140" t="n">
-        <v>11.7539463043213</v>
+        <v>11.753945350647</v>
       </c>
       <c r="H1140" t="s">
         <v>8</v>
@@ -30035,7 +30035,7 @@
         <v>12.8999996185303</v>
       </c>
       <c r="G1141" t="n">
-        <v>11.7539463043213</v>
+        <v>11.753945350647</v>
       </c>
       <c r="H1141" t="s">
         <v>8</v>
@@ -30061,7 +30061,7 @@
         <v>13.1499996185303</v>
       </c>
       <c r="G1142" t="n">
-        <v>11.9817342758179</v>
+        <v>11.9817352294922</v>
       </c>
       <c r="H1142" t="s">
         <v>8</v>
@@ -30087,7 +30087,7 @@
         <v>13.25</v>
       </c>
       <c r="G1143" t="n">
-        <v>12.0728521347046</v>
+        <v>12.0728511810303</v>
       </c>
       <c r="H1143" t="s">
         <v>8</v>
@@ -30113,7 +30113,7 @@
         <v>13.3500003814697</v>
       </c>
       <c r="G1144" t="n">
-        <v>12.1639671325684</v>
+        <v>12.1639680862427</v>
       </c>
       <c r="H1144" t="s">
         <v>8</v>
@@ -30139,7 +30139,7 @@
         <v>13.5</v>
       </c>
       <c r="G1145" t="n">
-        <v>12.3006410598755</v>
+        <v>12.3006401062012</v>
       </c>
       <c r="H1145" t="s">
         <v>8</v>
@@ -30165,7 +30165,7 @@
         <v>13.3000001907349</v>
       </c>
       <c r="G1146" t="n">
-        <v>12.1184091567993</v>
+        <v>12.1184101104736</v>
       </c>
       <c r="H1146" t="s">
         <v>8</v>
@@ -30191,7 +30191,7 @@
         <v>13.1000003814697</v>
       </c>
       <c r="G1147" t="n">
-        <v>11.9361772537231</v>
+        <v>11.9361782073975</v>
       </c>
       <c r="H1147" t="s">
         <v>8</v>
@@ -30217,7 +30217,7 @@
         <v>13.0500001907349</v>
       </c>
       <c r="G1148" t="n">
-        <v>11.8906183242798</v>
+        <v>11.8906192779541</v>
       </c>
       <c r="H1148" t="s">
         <v>8</v>
@@ -30243,7 +30243,7 @@
         <v>13.1000003814697</v>
       </c>
       <c r="G1149" t="n">
-        <v>11.9361772537231</v>
+        <v>11.9361782073975</v>
       </c>
       <c r="H1149" t="s">
         <v>8</v>
@@ -30269,7 +30269,7 @@
         <v>13.3999996185303</v>
       </c>
       <c r="G1150" t="n">
-        <v>12.3414163589478</v>
+        <v>12.3414173126221</v>
       </c>
       <c r="H1150" t="s">
         <v>8</v>
@@ -30295,7 +30295,7 @@
         <v>13.3500003814697</v>
       </c>
       <c r="G1151" t="n">
-        <v>12.2953691482544</v>
+        <v>12.2953681945801</v>
       </c>
       <c r="H1151" t="s">
         <v>8</v>
@@ -30425,7 +30425,7 @@
         <v>13.6000003814697</v>
       </c>
       <c r="G1156" t="n">
-        <v>12.5256185531616</v>
+        <v>12.5256175994873</v>
       </c>
       <c r="H1156" t="s">
         <v>8</v>
@@ -30477,7 +30477,7 @@
         <v>13.6000003814697</v>
       </c>
       <c r="G1158" t="n">
-        <v>12.5256185531616</v>
+        <v>12.5256175994873</v>
       </c>
       <c r="H1158" t="s">
         <v>8</v>
@@ -30503,7 +30503,7 @@
         <v>13.3999996185303</v>
       </c>
       <c r="G1159" t="n">
-        <v>12.3414163589478</v>
+        <v>12.3414173126221</v>
       </c>
       <c r="H1159" t="s">
         <v>8</v>
@@ -30529,7 +30529,7 @@
         <v>13.5500001907349</v>
       </c>
       <c r="G1160" t="n">
-        <v>12.4795684814453</v>
+        <v>12.479567527771</v>
       </c>
       <c r="H1160" t="s">
         <v>8</v>
@@ -30555,7 +30555,7 @@
         <v>13.6000003814697</v>
       </c>
       <c r="G1161" t="n">
-        <v>12.5256185531616</v>
+        <v>12.5256175994873</v>
       </c>
       <c r="H1161" t="s">
         <v>8</v>
@@ -30659,7 +30659,7 @@
         <v>13.0500001907349</v>
       </c>
       <c r="G1165" t="n">
-        <v>12.0190677642822</v>
+        <v>12.0190668106079</v>
       </c>
       <c r="H1165" t="s">
         <v>8</v>
@@ -30685,7 +30685,7 @@
         <v>13</v>
       </c>
       <c r="G1166" t="n">
-        <v>11.9730157852173</v>
+        <v>11.9730167388916</v>
       </c>
       <c r="H1166" t="s">
         <v>8</v>
@@ -30737,7 +30737,7 @@
         <v>13.1499996185303</v>
       </c>
       <c r="G1168" t="n">
-        <v>12.1111660003662</v>
+        <v>12.1111669540405</v>
       </c>
       <c r="H1168" t="s">
         <v>8</v>
@@ -30789,7 +30789,7 @@
         <v>13.3500003814697</v>
       </c>
       <c r="G1170" t="n">
-        <v>12.2953691482544</v>
+        <v>12.2953681945801</v>
       </c>
       <c r="H1170" t="s">
         <v>8</v>
@@ -30841,7 +30841,7 @@
         <v>13.3999996185303</v>
       </c>
       <c r="G1172" t="n">
-        <v>12.3414163589478</v>
+        <v>12.3414173126221</v>
       </c>
       <c r="H1172" t="s">
         <v>8</v>
@@ -30867,7 +30867,7 @@
         <v>13.6000003814697</v>
       </c>
       <c r="G1173" t="n">
-        <v>12.5256185531616</v>
+        <v>12.5256175994873</v>
       </c>
       <c r="H1173" t="s">
         <v>8</v>
@@ -30893,7 +30893,7 @@
         <v>13.5500001907349</v>
       </c>
       <c r="G1174" t="n">
-        <v>12.4795684814453</v>
+        <v>12.479567527771</v>
       </c>
       <c r="H1174" t="s">
         <v>8</v>
@@ -30997,7 +30997,7 @@
         <v>13.4499998092651</v>
       </c>
       <c r="G1178" t="n">
-        <v>12.3874673843384</v>
+        <v>12.3874664306641</v>
       </c>
       <c r="H1178" t="s">
         <v>8</v>
@@ -31023,7 +31023,7 @@
         <v>13.6000003814697</v>
       </c>
       <c r="G1179" t="n">
-        <v>12.5256185531616</v>
+        <v>12.5256175994873</v>
       </c>
       <c r="H1179" t="s">
         <v>8</v>
@@ -31049,7 +31049,7 @@
         <v>13.6000003814697</v>
       </c>
       <c r="G1180" t="n">
-        <v>12.5256185531616</v>
+        <v>12.5256175994873</v>
       </c>
       <c r="H1180" t="s">
         <v>8</v>
@@ -31075,7 +31075,7 @@
         <v>13.6000003814697</v>
       </c>
       <c r="G1181" t="n">
-        <v>12.5256185531616</v>
+        <v>12.5256175994873</v>
       </c>
       <c r="H1181" t="s">
         <v>8</v>
@@ -31101,7 +31101,7 @@
         <v>13.6000003814697</v>
       </c>
       <c r="G1182" t="n">
-        <v>12.5256185531616</v>
+        <v>12.5256175994873</v>
       </c>
       <c r="H1182" t="s">
         <v>8</v>
@@ -31127,7 +31127,7 @@
         <v>13.5500001907349</v>
       </c>
       <c r="G1183" t="n">
-        <v>12.4795684814453</v>
+        <v>12.479567527771</v>
       </c>
       <c r="H1183" t="s">
         <v>8</v>
@@ -31153,7 +31153,7 @@
         <v>13.4499998092651</v>
       </c>
       <c r="G1184" t="n">
-        <v>12.3874673843384</v>
+        <v>12.3874664306641</v>
       </c>
       <c r="H1184" t="s">
         <v>8</v>
@@ -31179,7 +31179,7 @@
         <v>13.6000003814697</v>
       </c>
       <c r="G1185" t="n">
-        <v>12.5256185531616</v>
+        <v>12.5256175994873</v>
       </c>
       <c r="H1185" t="s">
         <v>8</v>
@@ -31205,7 +31205,7 @@
         <v>13.6000003814697</v>
       </c>
       <c r="G1186" t="n">
-        <v>12.5256185531616</v>
+        <v>12.5256175994873</v>
       </c>
       <c r="H1186" t="s">
         <v>8</v>
@@ -31257,7 +31257,7 @@
         <v>13.5500001907349</v>
       </c>
       <c r="G1188" t="n">
-        <v>12.4795684814453</v>
+        <v>12.479567527771</v>
       </c>
       <c r="H1188" t="s">
         <v>8</v>
@@ -31283,7 +31283,7 @@
         <v>13.3500003814697</v>
       </c>
       <c r="G1189" t="n">
-        <v>12.2953691482544</v>
+        <v>12.2953681945801</v>
       </c>
       <c r="H1189" t="s">
         <v>8</v>
@@ -31309,7 +31309,7 @@
         <v>13.4499998092651</v>
       </c>
       <c r="G1190" t="n">
-        <v>12.3874673843384</v>
+        <v>12.3874664306641</v>
       </c>
       <c r="H1190" t="s">
         <v>8</v>
@@ -31335,7 +31335,7 @@
         <v>13.3500003814697</v>
       </c>
       <c r="G1191" t="n">
-        <v>12.2953691482544</v>
+        <v>12.2953681945801</v>
       </c>
       <c r="H1191" t="s">
         <v>8</v>
@@ -31361,7 +31361,7 @@
         <v>13.3999996185303</v>
       </c>
       <c r="G1192" t="n">
-        <v>12.3414163589478</v>
+        <v>12.3414173126221</v>
       </c>
       <c r="H1192" t="s">
         <v>8</v>
@@ -31387,7 +31387,7 @@
         <v>13.3500003814697</v>
       </c>
       <c r="G1193" t="n">
-        <v>12.2953691482544</v>
+        <v>12.2953681945801</v>
       </c>
       <c r="H1193" t="s">
         <v>8</v>
@@ -31413,7 +31413,7 @@
         <v>13.3500003814697</v>
       </c>
       <c r="G1194" t="n">
-        <v>12.2953691482544</v>
+        <v>12.2953681945801</v>
       </c>
       <c r="H1194" t="s">
         <v>8</v>
@@ -31517,7 +31517,7 @@
         <v>13.4499998092651</v>
       </c>
       <c r="G1198" t="n">
-        <v>12.3874673843384</v>
+        <v>12.3874664306641</v>
       </c>
       <c r="H1198" t="s">
         <v>8</v>
@@ -31543,7 +31543,7 @@
         <v>13.6000003814697</v>
       </c>
       <c r="G1199" t="n">
-        <v>12.5256185531616</v>
+        <v>12.5256175994873</v>
       </c>
       <c r="H1199" t="s">
         <v>8</v>
@@ -31569,7 +31569,7 @@
         <v>13.8000001907349</v>
       </c>
       <c r="G1200" t="n">
-        <v>12.7098188400269</v>
+        <v>12.7098178863525</v>
       </c>
       <c r="H1200" t="s">
         <v>8</v>
@@ -31673,7 +31673,7 @@
         <v>13.6000003814697</v>
       </c>
       <c r="G1204" t="n">
-        <v>12.5256185531616</v>
+        <v>12.5256175994873</v>
       </c>
       <c r="H1204" t="s">
         <v>8</v>
@@ -31699,7 +31699,7 @@
         <v>13.3500003814697</v>
       </c>
       <c r="G1205" t="n">
-        <v>12.2953691482544</v>
+        <v>12.2953681945801</v>
       </c>
       <c r="H1205" t="s">
         <v>8</v>
@@ -31751,7 +31751,7 @@
         <v>13.4499998092651</v>
       </c>
       <c r="G1207" t="n">
-        <v>12.3874673843384</v>
+        <v>12.3874664306641</v>
       </c>
       <c r="H1207" t="s">
         <v>8</v>
@@ -31777,7 +31777,7 @@
         <v>13.3999996185303</v>
       </c>
       <c r="G1208" t="n">
-        <v>12.3414163589478</v>
+        <v>12.3414173126221</v>
       </c>
       <c r="H1208" t="s">
         <v>8</v>
@@ -31829,7 +31829,7 @@
         <v>13.3500003814697</v>
       </c>
       <c r="G1210" t="n">
-        <v>12.2953691482544</v>
+        <v>12.2953681945801</v>
       </c>
       <c r="H1210" t="s">
         <v>8</v>
@@ -31907,7 +31907,7 @@
         <v>13.8000001907349</v>
       </c>
       <c r="G1213" t="n">
-        <v>12.7098188400269</v>
+        <v>12.7098178863525</v>
       </c>
       <c r="H1213" t="s">
         <v>8</v>
@@ -31933,7 +31933,7 @@
         <v>13.9499998092651</v>
       </c>
       <c r="G1214" t="n">
-        <v>12.8479671478271</v>
+        <v>12.8479681015015</v>
       </c>
       <c r="H1214" t="s">
         <v>8</v>
@@ -31985,7 +31985,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G1216" t="n">
-        <v>13.6308212280273</v>
+        <v>13.6308193206787</v>
       </c>
       <c r="H1216" t="s">
         <v>8</v>
@@ -32063,7 +32063,7 @@
         <v>15.3000001907349</v>
       </c>
       <c r="G1219" t="n">
-        <v>14.0913209915161</v>
+        <v>14.0913200378418</v>
       </c>
       <c r="H1219" t="s">
         <v>8</v>
@@ -32089,7 +32089,7 @@
         <v>15.5500001907349</v>
       </c>
       <c r="G1220" t="n">
-        <v>14.3215713500977</v>
+        <v>14.321569442749</v>
       </c>
       <c r="H1220" t="s">
         <v>8</v>
@@ -32219,7 +32219,7 @@
         <v>16.0499992370605</v>
       </c>
       <c r="G1225" t="n">
-        <v>14.7820711135864</v>
+        <v>14.7820701599121</v>
       </c>
       <c r="H1225" t="s">
         <v>8</v>
@@ -32245,7 +32245,7 @@
         <v>16.2000007629395</v>
       </c>
       <c r="G1226" t="n">
-        <v>14.9202213287354</v>
+        <v>14.920220375061</v>
       </c>
       <c r="H1226" t="s">
         <v>8</v>
@@ -32271,7 +32271,7 @@
         <v>16.3500003814697</v>
       </c>
       <c r="G1227" t="n">
-        <v>15.0583715438843</v>
+        <v>15.0583734512329</v>
       </c>
       <c r="H1227" t="s">
         <v>8</v>
@@ -32323,7 +32323,7 @@
         <v>16.2000007629395</v>
       </c>
       <c r="G1229" t="n">
-        <v>14.9202213287354</v>
+        <v>14.920220375061</v>
       </c>
       <c r="H1229" t="s">
         <v>8</v>
@@ -32427,7 +32427,7 @@
         <v>17.1499996185303</v>
       </c>
       <c r="G1233" t="n">
-        <v>15.7951707839966</v>
+        <v>15.7951726913452</v>
       </c>
       <c r="H1233" t="s">
         <v>8</v>
@@ -32453,7 +32453,7 @@
         <v>18</v>
       </c>
       <c r="G1234" t="n">
-        <v>16.5780220031738</v>
+        <v>16.5780239105225</v>
       </c>
       <c r="H1234" t="s">
         <v>8</v>
@@ -32505,7 +32505,7 @@
         <v>18</v>
       </c>
       <c r="G1236" t="n">
-        <v>16.5780220031738</v>
+        <v>16.5780239105225</v>
       </c>
       <c r="H1236" t="s">
         <v>8</v>
@@ -32531,7 +32531,7 @@
         <v>17.8999996185303</v>
       </c>
       <c r="G1237" t="n">
-        <v>16.4859218597412</v>
+        <v>16.4859256744385</v>
       </c>
       <c r="H1237" t="s">
         <v>8</v>
@@ -32557,7 +32557,7 @@
         <v>18.3500003814697</v>
       </c>
       <c r="G1238" t="n">
-        <v>16.9003734588623</v>
+        <v>16.9003753662109</v>
       </c>
       <c r="H1238" t="s">
         <v>8</v>
@@ -32583,7 +32583,7 @@
         <v>18.2000007629395</v>
       </c>
       <c r="G1239" t="n">
-        <v>16.7622241973877</v>
+        <v>16.7622261047363</v>
       </c>
       <c r="H1239" t="s">
         <v>8</v>
@@ -32609,7 +32609,7 @@
         <v>18.1000003814697</v>
       </c>
       <c r="G1240" t="n">
-        <v>16.6701221466064</v>
+        <v>16.6701240539551</v>
       </c>
       <c r="H1240" t="s">
         <v>8</v>
@@ -32635,7 +32635,7 @@
         <v>17.8500003814697</v>
       </c>
       <c r="G1241" t="n">
-        <v>16.4398727416992</v>
+        <v>16.4398746490479</v>
       </c>
       <c r="H1241" t="s">
         <v>8</v>
@@ -32661,7 +32661,7 @@
         <v>17.8999996185303</v>
       </c>
       <c r="G1242" t="n">
-        <v>16.4859218597412</v>
+        <v>16.4859256744385</v>
       </c>
       <c r="H1242" t="s">
         <v>8</v>
@@ -32687,7 +32687,7 @@
         <v>18</v>
       </c>
       <c r="G1243" t="n">
-        <v>16.5780220031738</v>
+        <v>16.5780239105225</v>
       </c>
       <c r="H1243" t="s">
         <v>8</v>
@@ -32739,7 +32739,7 @@
         <v>17.8500003814697</v>
       </c>
       <c r="G1245" t="n">
-        <v>16.4398727416992</v>
+        <v>16.4398746490479</v>
       </c>
       <c r="H1245" t="s">
         <v>8</v>
@@ -32817,7 +32817,7 @@
         <v>17.8500003814697</v>
       </c>
       <c r="G1248" t="n">
-        <v>16.4398727416992</v>
+        <v>16.4398746490479</v>
       </c>
       <c r="H1248" t="s">
         <v>8</v>
@@ -32843,7 +32843,7 @@
         <v>18.3500003814697</v>
       </c>
       <c r="G1249" t="n">
-        <v>16.9003734588623</v>
+        <v>16.9003753662109</v>
       </c>
       <c r="H1249" t="s">
         <v>8</v>
@@ -32869,7 +32869,7 @@
         <v>17.2999992370605</v>
       </c>
       <c r="G1250" t="n">
-        <v>15.9333229064941</v>
+        <v>15.9333219528198</v>
       </c>
       <c r="H1250" t="s">
         <v>8</v>
@@ -32999,7 +32999,7 @@
         <v>17.5</v>
       </c>
       <c r="G1255" t="n">
-        <v>16.1175212860107</v>
+        <v>16.1175231933594</v>
       </c>
       <c r="H1255" t="s">
         <v>8</v>
@@ -33025,7 +33025,7 @@
         <v>17.1499996185303</v>
       </c>
       <c r="G1256" t="n">
-        <v>15.7951707839966</v>
+        <v>15.7951726913452</v>
       </c>
       <c r="H1256" t="s">
         <v>8</v>
@@ -33129,7 +33129,7 @@
         <v>17.1000003814697</v>
       </c>
       <c r="G1260" t="n">
-        <v>15.7491216659546</v>
+        <v>15.7491235733032</v>
       </c>
       <c r="H1260" t="s">
         <v>8</v>
@@ -33155,7 +33155,7 @@
         <v>17.25</v>
       </c>
       <c r="G1261" t="n">
-        <v>15.8872718811035</v>
+        <v>15.8872728347778</v>
       </c>
       <c r="H1261" t="s">
         <v>8</v>
@@ -33207,7 +33207,7 @@
         <v>17.0499992370605</v>
       </c>
       <c r="G1263" t="n">
-        <v>15.7030715942383</v>
+        <v>15.703070640564</v>
       </c>
       <c r="H1263" t="s">
         <v>8</v>
@@ -33259,7 +33259,7 @@
         <v>16.7999992370605</v>
       </c>
       <c r="G1265" t="n">
-        <v>15.4728221893311</v>
+        <v>15.4728231430054</v>
       </c>
       <c r="H1265" t="s">
         <v>8</v>
@@ -33311,7 +33311,7 @@
         <v>17.5499992370605</v>
       </c>
       <c r="G1267" t="n">
-        <v>16.16357421875</v>
+        <v>16.1635723114014</v>
       </c>
       <c r="H1267" t="s">
         <v>8</v>
@@ -33363,7 +33363,7 @@
         <v>18.1000003814697</v>
       </c>
       <c r="G1269" t="n">
-        <v>16.6701221466064</v>
+        <v>16.6701240539551</v>
       </c>
       <c r="H1269" t="s">
         <v>8</v>
@@ -33415,7 +33415,7 @@
         <v>18.1000003814697</v>
       </c>
       <c r="G1271" t="n">
-        <v>16.6701221466064</v>
+        <v>16.6701240539551</v>
       </c>
       <c r="H1271" t="s">
         <v>8</v>
@@ -33519,7 +33519,7 @@
         <v>18.3500003814697</v>
       </c>
       <c r="G1275" t="n">
-        <v>16.9003734588623</v>
+        <v>16.9003753662109</v>
       </c>
       <c r="H1275" t="s">
         <v>8</v>
@@ -33571,7 +33571,7 @@
         <v>17.7999992370605</v>
       </c>
       <c r="G1277" t="n">
-        <v>16.3938236236572</v>
+        <v>16.3938255310059</v>
       </c>
       <c r="H1277" t="s">
         <v>8</v>
@@ -33597,7 +33597,7 @@
         <v>17.9500007629395</v>
       </c>
       <c r="G1278" t="n">
-        <v>16.5319747924805</v>
+        <v>16.5319766998291</v>
       </c>
       <c r="H1278" t="s">
         <v>8</v>
@@ -33623,7 +33623,7 @@
         <v>17.8500003814697</v>
       </c>
       <c r="G1279" t="n">
-        <v>16.4398727416992</v>
+        <v>16.4398746490479</v>
       </c>
       <c r="H1279" t="s">
         <v>8</v>
@@ -33649,7 +33649,7 @@
         <v>17.9500007629395</v>
       </c>
       <c r="G1280" t="n">
-        <v>16.5319747924805</v>
+        <v>16.5319766998291</v>
       </c>
       <c r="H1280" t="s">
         <v>8</v>
@@ -33675,7 +33675,7 @@
         <v>17.9500007629395</v>
       </c>
       <c r="G1281" t="n">
-        <v>16.5319747924805</v>
+        <v>16.5319766998291</v>
       </c>
       <c r="H1281" t="s">
         <v>8</v>
@@ -33727,7 +33727,7 @@
         <v>17.8999996185303</v>
       </c>
       <c r="G1283" t="n">
-        <v>16.4859218597412</v>
+        <v>16.4859256744385</v>
       </c>
       <c r="H1283" t="s">
         <v>8</v>
@@ -33753,7 +33753,7 @@
         <v>17.7999992370605</v>
       </c>
       <c r="G1284" t="n">
-        <v>16.3938236236572</v>
+        <v>16.3938255310059</v>
       </c>
       <c r="H1284" t="s">
         <v>8</v>
@@ -33779,7 +33779,7 @@
         <v>17.8999996185303</v>
       </c>
       <c r="G1285" t="n">
-        <v>16.4859218597412</v>
+        <v>16.4859256744385</v>
       </c>
       <c r="H1285" t="s">
         <v>8</v>
@@ -33961,7 +33961,7 @@
         <v>16.1000003814697</v>
       </c>
       <c r="G1292" t="n">
-        <v>14.8281211853027</v>
+        <v>14.8281202316284</v>
       </c>
       <c r="H1292" t="s">
         <v>8</v>
@@ -34039,7 +34039,7 @@
         <v>15.8000001907349</v>
       </c>
       <c r="G1295" t="n">
-        <v>14.5518217086792</v>
+        <v>14.5518198013306</v>
       </c>
       <c r="H1295" t="s">
         <v>8</v>
@@ -34143,7 +34143,7 @@
         <v>15.3500003814697</v>
       </c>
       <c r="G1299" t="n">
-        <v>14.1373691558838</v>
+        <v>14.1373701095581</v>
       </c>
       <c r="H1299" t="s">
         <v>8</v>
@@ -34169,7 +34169,7 @@
         <v>15.0500001907349</v>
       </c>
       <c r="G1300" t="n">
-        <v>13.8610706329346</v>
+        <v>13.8610696792603</v>
       </c>
       <c r="H1300" t="s">
         <v>8</v>
@@ -34247,7 +34247,7 @@
         <v>15.3500003814697</v>
       </c>
       <c r="G1303" t="n">
-        <v>14.1373691558838</v>
+        <v>14.1373701095581</v>
       </c>
       <c r="H1303" t="s">
         <v>8</v>
@@ -34273,7 +34273,7 @@
         <v>14.8999996185303</v>
       </c>
       <c r="G1304" t="n">
-        <v>13.7229194641113</v>
+        <v>13.722918510437</v>
       </c>
       <c r="H1304" t="s">
         <v>8</v>
@@ -34299,7 +34299,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G1305" t="n">
-        <v>13.6308212280273</v>
+        <v>13.6308193206787</v>
       </c>
       <c r="H1305" t="s">
         <v>8</v>
@@ -34325,7 +34325,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G1306" t="n">
-        <v>13.9992198944092</v>
+        <v>13.9992189407349</v>
       </c>
       <c r="H1306" t="s">
         <v>8</v>
@@ -34377,7 +34377,7 @@
         <v>15.1499996185303</v>
       </c>
       <c r="G1308" t="n">
-        <v>13.9531688690186</v>
+        <v>13.9531698226929</v>
       </c>
       <c r="H1308" t="s">
         <v>8</v>
@@ -34429,7 +34429,7 @@
         <v>14.8999996185303</v>
       </c>
       <c r="G1310" t="n">
-        <v>13.7229194641113</v>
+        <v>13.722918510437</v>
       </c>
       <c r="H1310" t="s">
         <v>8</v>
@@ -34481,7 +34481,7 @@
         <v>15.0500001907349</v>
       </c>
       <c r="G1312" t="n">
-        <v>13.8610706329346</v>
+        <v>13.8610696792603</v>
       </c>
       <c r="H1312" t="s">
         <v>8</v>
@@ -34507,7 +34507,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G1313" t="n">
-        <v>13.9992198944092</v>
+        <v>13.9992189407349</v>
       </c>
       <c r="H1313" t="s">
         <v>8</v>
@@ -34533,7 +34533,7 @@
         <v>14.9499998092651</v>
       </c>
       <c r="G1314" t="n">
-        <v>13.7689695358276</v>
+        <v>13.7689685821533</v>
       </c>
       <c r="H1314" t="s">
         <v>8</v>
@@ -34611,7 +34611,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G1317" t="n">
-        <v>13.9071197509766</v>
+        <v>13.9071207046509</v>
       </c>
       <c r="H1317" t="s">
         <v>8</v>
@@ -34637,7 +34637,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G1318" t="n">
-        <v>13.9071197509766</v>
+        <v>13.9071207046509</v>
       </c>
       <c r="H1318" t="s">
         <v>8</v>
@@ -34715,7 +34715,7 @@
         <v>15.5500001907349</v>
       </c>
       <c r="G1321" t="n">
-        <v>14.3215713500977</v>
+        <v>14.321569442749</v>
       </c>
       <c r="H1321" t="s">
         <v>8</v>
@@ -34767,7 +34767,7 @@
         <v>15.6000003814697</v>
       </c>
       <c r="G1323" t="n">
-        <v>14.3676204681396</v>
+        <v>14.3676195144653</v>
       </c>
       <c r="H1323" t="s">
         <v>8</v>
@@ -34819,7 +34819,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G1325" t="n">
-        <v>13.9992198944092</v>
+        <v>13.9992189407349</v>
       </c>
       <c r="H1325" t="s">
         <v>8</v>
@@ -34845,7 +34845,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G1326" t="n">
-        <v>13.5387182235718</v>
+        <v>13.5387191772461</v>
       </c>
       <c r="H1326" t="s">
         <v>8</v>
@@ -34871,7 +34871,7 @@
         <v>15.1499996185303</v>
       </c>
       <c r="G1327" t="n">
-        <v>13.9531688690186</v>
+        <v>13.9531698226929</v>
       </c>
       <c r="H1327" t="s">
         <v>8</v>
@@ -34897,7 +34897,7 @@
         <v>14.25</v>
       </c>
       <c r="G1328" t="n">
-        <v>13.1242685317993</v>
+        <v>13.124267578125</v>
       </c>
       <c r="H1328" t="s">
         <v>8</v>
@@ -34923,7 +34923,7 @@
         <v>14.1999998092651</v>
       </c>
       <c r="G1329" t="n">
-        <v>13.078218460083</v>
+        <v>13.0782175064087</v>
       </c>
       <c r="H1329" t="s">
         <v>8</v>
@@ -34949,7 +34949,7 @@
         <v>14.3000001907349</v>
       </c>
       <c r="G1330" t="n">
-        <v>13.1703195571899</v>
+        <v>13.1703186035156</v>
       </c>
       <c r="H1330" t="s">
         <v>8</v>
@@ -34975,7 +34975,7 @@
         <v>13.8999996185303</v>
       </c>
       <c r="G1331" t="n">
-        <v>12.8019170761108</v>
+        <v>12.8019180297852</v>
       </c>
       <c r="H1331" t="s">
         <v>8</v>
@@ -35001,7 +35001,7 @@
         <v>14.1999998092651</v>
       </c>
       <c r="G1332" t="n">
-        <v>13.078218460083</v>
+        <v>13.0782175064087</v>
       </c>
       <c r="H1332" t="s">
         <v>8</v>
@@ -35027,7 +35027,7 @@
         <v>14.1999998092651</v>
       </c>
       <c r="G1333" t="n">
-        <v>13.078218460083</v>
+        <v>13.0782175064087</v>
       </c>
       <c r="H1333" t="s">
         <v>8</v>
@@ -35053,7 +35053,7 @@
         <v>13.9499998092651</v>
       </c>
       <c r="G1334" t="n">
-        <v>12.8479671478271</v>
+        <v>12.8479681015015</v>
       </c>
       <c r="H1334" t="s">
         <v>8</v>
@@ -35157,7 +35157,7 @@
         <v>13.5500001907349</v>
       </c>
       <c r="G1338" t="n">
-        <v>12.4795684814453</v>
+        <v>12.479567527771</v>
       </c>
       <c r="H1338" t="s">
         <v>8</v>
@@ -35183,7 +35183,7 @@
         <v>13.3999996185303</v>
       </c>
       <c r="G1339" t="n">
-        <v>12.3414163589478</v>
+        <v>12.3414173126221</v>
       </c>
       <c r="H1339" t="s">
         <v>8</v>
@@ -35209,7 +35209,7 @@
         <v>13.6000003814697</v>
       </c>
       <c r="G1340" t="n">
-        <v>12.5256185531616</v>
+        <v>12.5256175994873</v>
       </c>
       <c r="H1340" t="s">
         <v>8</v>
@@ -35339,7 +35339,7 @@
         <v>13.5500001907349</v>
       </c>
       <c r="G1345" t="n">
-        <v>12.4795684814453</v>
+        <v>12.479567527771</v>
       </c>
       <c r="H1345" t="s">
         <v>8</v>
@@ -35391,7 +35391,7 @@
         <v>13.0500001907349</v>
       </c>
       <c r="G1347" t="n">
-        <v>12.0190677642822</v>
+        <v>12.0190668106079</v>
       </c>
       <c r="H1347" t="s">
         <v>8</v>
@@ -35417,7 +35417,7 @@
         <v>12.8999996185303</v>
       </c>
       <c r="G1348" t="n">
-        <v>11.8809156417847</v>
+        <v>11.880916595459</v>
       </c>
       <c r="H1348" t="s">
         <v>8</v>
@@ -35495,7 +35495,7 @@
         <v>13</v>
       </c>
       <c r="G1351" t="n">
-        <v>11.9730157852173</v>
+        <v>11.9730167388916</v>
       </c>
       <c r="H1351" t="s">
         <v>8</v>
@@ -35521,7 +35521,7 @@
         <v>13.0500001907349</v>
       </c>
       <c r="G1352" t="n">
-        <v>12.0190677642822</v>
+        <v>12.0190668106079</v>
       </c>
       <c r="H1352" t="s">
         <v>8</v>
@@ -35547,7 +35547,7 @@
         <v>12.6999998092651</v>
       </c>
       <c r="G1353" t="n">
-        <v>11.6967163085938</v>
+        <v>11.6967172622681</v>
       </c>
       <c r="H1353" t="s">
         <v>8</v>
@@ -35573,7 +35573,7 @@
         <v>12.8500003814697</v>
       </c>
       <c r="G1354" t="n">
-        <v>11.834867477417</v>
+        <v>11.8348665237427</v>
       </c>
       <c r="H1354" t="s">
         <v>8</v>
@@ -35677,7 +35677,7 @@
         <v>12.6999998092651</v>
       </c>
       <c r="G1358" t="n">
-        <v>11.6967163085938</v>
+        <v>11.6967172622681</v>
       </c>
       <c r="H1358" t="s">
         <v>8</v>
@@ -35729,7 +35729,7 @@
         <v>12</v>
       </c>
       <c r="G1360" t="n">
-        <v>11.0520143508911</v>
+        <v>11.0520153045654</v>
       </c>
       <c r="H1360" t="s">
         <v>8</v>
@@ -35911,7 +35911,7 @@
         <v>11.4499998092651</v>
       </c>
       <c r="G1367" t="n">
-        <v>10.5454635620117</v>
+        <v>10.545464515686</v>
       </c>
       <c r="H1367" t="s">
         <v>8</v>
@@ -36015,7 +36015,7 @@
         <v>12</v>
       </c>
       <c r="G1371" t="n">
-        <v>11.0520143508911</v>
+        <v>11.0520153045654</v>
       </c>
       <c r="H1371" t="s">
         <v>8</v>
@@ -36041,7 +36041,7 @@
         <v>12.3500003814697</v>
       </c>
       <c r="G1372" t="n">
-        <v>11.3743667602539</v>
+        <v>11.3743658065796</v>
       </c>
       <c r="H1372" t="s">
         <v>8</v>
@@ -36093,7 +36093,7 @@
         <v>12.0500001907349</v>
       </c>
       <c r="G1374" t="n">
-        <v>11.0980663299561</v>
+        <v>11.0980653762817</v>
       </c>
       <c r="H1374" t="s">
         <v>8</v>
@@ -36119,7 +36119,7 @@
         <v>12.5</v>
       </c>
       <c r="G1375" t="n">
-        <v>11.5125160217285</v>
+        <v>11.5125169754028</v>
       </c>
       <c r="H1375" t="s">
         <v>8</v>
@@ -36197,7 +36197,7 @@
         <v>12.8500003814697</v>
       </c>
       <c r="G1378" t="n">
-        <v>11.834867477417</v>
+        <v>11.8348665237427</v>
       </c>
       <c r="H1378" t="s">
         <v>8</v>
@@ -36223,7 +36223,7 @@
         <v>13.0500001907349</v>
       </c>
       <c r="G1379" t="n">
-        <v>12.0190677642822</v>
+        <v>12.0190668106079</v>
       </c>
       <c r="H1379" t="s">
         <v>8</v>
@@ -36249,7 +36249,7 @@
         <v>12.8999996185303</v>
       </c>
       <c r="G1380" t="n">
-        <v>11.8809156417847</v>
+        <v>11.880916595459</v>
       </c>
       <c r="H1380" t="s">
         <v>8</v>
@@ -36275,7 +36275,7 @@
         <v>12.6000003814697</v>
       </c>
       <c r="G1381" t="n">
-        <v>11.6046180725098</v>
+        <v>11.6046171188354</v>
       </c>
       <c r="H1381" t="s">
         <v>8</v>
@@ -36301,7 +36301,7 @@
         <v>13</v>
       </c>
       <c r="G1382" t="n">
-        <v>11.9730157852173</v>
+        <v>11.9730167388916</v>
       </c>
       <c r="H1382" t="s">
         <v>8</v>
@@ -36327,7 +36327,7 @@
         <v>13</v>
       </c>
       <c r="G1383" t="n">
-        <v>11.9730157852173</v>
+        <v>11.9730167388916</v>
       </c>
       <c r="H1383" t="s">
         <v>8</v>
@@ -36353,7 +36353,7 @@
         <v>13.3999996185303</v>
       </c>
       <c r="G1384" t="n">
-        <v>12.3414163589478</v>
+        <v>12.3414173126221</v>
       </c>
       <c r="H1384" t="s">
         <v>8</v>
@@ -36379,7 +36379,7 @@
         <v>13.5500001907349</v>
       </c>
       <c r="G1385" t="n">
-        <v>12.4795684814453</v>
+        <v>12.479567527771</v>
       </c>
       <c r="H1385" t="s">
         <v>8</v>
@@ -36405,7 +36405,7 @@
         <v>11.75</v>
       </c>
       <c r="G1386" t="n">
-        <v>10.8217658996582</v>
+        <v>10.8217649459839</v>
       </c>
       <c r="H1386" t="s">
         <v>8</v>
@@ -36431,7 +36431,7 @@
         <v>10.1000003814697</v>
       </c>
       <c r="G1387" t="n">
-        <v>9.30211448669434</v>
+        <v>9.30211353302002</v>
       </c>
       <c r="H1387" t="s">
         <v>8</v>
@@ -36457,7 +36457,7 @@
         <v>8.89999961853027</v>
       </c>
       <c r="G1388" t="n">
-        <v>8.19691181182861</v>
+        <v>8.19691276550293</v>
       </c>
       <c r="H1388" t="s">
         <v>8</v>
@@ -36509,7 +36509,7 @@
         <v>8.86999988555908</v>
       </c>
       <c r="G1390" t="n">
-        <v>8.16928100585938</v>
+        <v>8.16928195953369</v>
       </c>
       <c r="H1390" t="s">
         <v>8</v>
@@ -36665,7 +36665,7 @@
         <v>9</v>
       </c>
       <c r="G1396" t="n">
-        <v>8.28901100158691</v>
+        <v>8.28901195526123</v>
       </c>
       <c r="H1396" t="s">
         <v>8</v>
@@ -36691,7 +36691,7 @@
         <v>9.03999996185303</v>
       </c>
       <c r="G1397" t="n">
-        <v>8.325852394104</v>
+        <v>8.32585144042969</v>
       </c>
       <c r="H1397" t="s">
         <v>8</v>
@@ -36717,7 +36717,7 @@
         <v>8.88000011444092</v>
       </c>
       <c r="G1398" t="n">
-        <v>8.17849254608154</v>
+        <v>8.17849159240723</v>
       </c>
       <c r="H1398" t="s">
         <v>8</v>
@@ -36795,7 +36795,7 @@
         <v>8.3100004196167</v>
       </c>
       <c r="G1401" t="n">
-        <v>7.6535210609436</v>
+        <v>7.65352153778076</v>
       </c>
       <c r="H1401" t="s">
         <v>8</v>
@@ -36847,7 +36847,7 @@
         <v>7.82999992370605</v>
       </c>
       <c r="G1403" t="n">
-        <v>7.21143960952759</v>
+        <v>7.21144008636475</v>
       </c>
       <c r="H1403" t="s">
         <v>8</v>
@@ -36899,7 +36899,7 @@
         <v>8.35999965667725</v>
       </c>
       <c r="G1405" t="n">
-        <v>7.69957113265991</v>
+        <v>7.69957065582275</v>
       </c>
       <c r="H1405" t="s">
         <v>8</v>
@@ -36925,7 +36925,7 @@
         <v>8.4399995803833</v>
       </c>
       <c r="G1406" t="n">
-        <v>7.77325105667114</v>
+        <v>7.77325010299683</v>
       </c>
       <c r="H1406" t="s">
         <v>8</v>
@@ -36951,7 +36951,7 @@
         <v>8.01000022888184</v>
       </c>
       <c r="G1407" t="n">
-        <v>7.37722063064575</v>
+        <v>7.37722110748291</v>
       </c>
       <c r="H1407" t="s">
         <v>8</v>
@@ -36977,7 +36977,7 @@
         <v>7.86999988555908</v>
       </c>
       <c r="G1408" t="n">
-        <v>7.24828052520752</v>
+        <v>7.24828004837036</v>
       </c>
       <c r="H1408" t="s">
         <v>8</v>
@@ -37003,7 +37003,7 @@
         <v>7.59999990463257</v>
       </c>
       <c r="G1409" t="n">
-        <v>6.99960994720459</v>
+        <v>6.99960947036743</v>
       </c>
       <c r="H1409" t="s">
         <v>8</v>
@@ -37029,7 +37029,7 @@
         <v>7.76999998092651</v>
       </c>
       <c r="G1410" t="n">
-        <v>7.1561803817749</v>
+        <v>7.15617990493774</v>
       </c>
       <c r="H1410" t="s">
         <v>8</v>
@@ -37055,7 +37055,7 @@
         <v>7.44999980926514</v>
       </c>
       <c r="G1411" t="n">
-        <v>6.86145973205566</v>
+        <v>6.86145925521851</v>
       </c>
       <c r="H1411" t="s">
         <v>8</v>
@@ -37081,7 +37081,7 @@
         <v>7.40000009536743</v>
       </c>
       <c r="G1412" t="n">
-        <v>6.81541061401367</v>
+        <v>6.81540966033936</v>
       </c>
       <c r="H1412" t="s">
         <v>8</v>
@@ -37159,7 +37159,7 @@
         <v>7.84000015258789</v>
       </c>
       <c r="G1415" t="n">
-        <v>7.2206506729126</v>
+        <v>7.22065019607544</v>
       </c>
       <c r="H1415" t="s">
         <v>8</v>
@@ -37185,7 +37185,7 @@
         <v>8.05000019073486</v>
       </c>
       <c r="G1416" t="n">
-        <v>7.41406059265137</v>
+        <v>7.41406011581421</v>
       </c>
       <c r="H1416" t="s">
         <v>8</v>
@@ -37237,7 +37237,7 @@
         <v>8.75</v>
       </c>
       <c r="G1418" t="n">
-        <v>8.05876064300537</v>
+        <v>8.05876159667969</v>
       </c>
       <c r="H1418" t="s">
         <v>8</v>
@@ -37263,7 +37263,7 @@
         <v>8.77000045776367</v>
       </c>
       <c r="G1419" t="n">
-        <v>8.07718276977539</v>
+        <v>8.07718181610107</v>
       </c>
       <c r="H1419" t="s">
         <v>8</v>
@@ -37289,7 +37289,7 @@
         <v>9</v>
       </c>
       <c r="G1420" t="n">
-        <v>8.28901100158691</v>
+        <v>8.28901195526123</v>
       </c>
       <c r="H1420" t="s">
         <v>8</v>
@@ -37341,7 +37341,7 @@
         <v>8.86999988555908</v>
       </c>
       <c r="G1422" t="n">
-        <v>8.31714153289795</v>
+        <v>8.31714248657227</v>
       </c>
       <c r="H1422" t="s">
         <v>8</v>
@@ -37367,7 +37367,7 @@
         <v>8.94999980926514</v>
       </c>
       <c r="G1423" t="n">
-        <v>8.39215564727783</v>
+        <v>8.39215660095215</v>
       </c>
       <c r="H1423" t="s">
         <v>8</v>
@@ -37393,7 +37393,7 @@
         <v>9.10000038146973</v>
       </c>
       <c r="G1424" t="n">
-        <v>8.53280639648438</v>
+        <v>8.53280735015869</v>
       </c>
       <c r="H1424" t="s">
         <v>8</v>
@@ -37419,7 +37419,7 @@
         <v>9.19999980926514</v>
       </c>
       <c r="G1425" t="n">
-        <v>8.62657260894775</v>
+        <v>8.62657356262207</v>
       </c>
       <c r="H1425" t="s">
         <v>8</v>
@@ -37445,7 +37445,7 @@
         <v>9.27000045776367</v>
       </c>
       <c r="G1426" t="n">
-        <v>8.69221115112305</v>
+        <v>8.69221210479736</v>
       </c>
       <c r="H1426" t="s">
         <v>8</v>
@@ -37471,7 +37471,7 @@
         <v>9.10000038146973</v>
       </c>
       <c r="G1427" t="n">
-        <v>8.53280639648438</v>
+        <v>8.53280735015869</v>
       </c>
       <c r="H1427" t="s">
         <v>8</v>
@@ -37497,7 +37497,7 @@
         <v>9.14999961853027</v>
       </c>
       <c r="G1428" t="n">
-        <v>8.57968902587891</v>
+        <v>8.57968997955322</v>
       </c>
       <c r="H1428" t="s">
         <v>8</v>
@@ -37549,7 +37549,7 @@
         <v>8.90999984741211</v>
       </c>
       <c r="G1430" t="n">
-        <v>8.35464859008789</v>
+        <v>8.35464954376221</v>
       </c>
       <c r="H1430" t="s">
         <v>8</v>
@@ -37653,7 +37653,7 @@
         <v>8.89999961853027</v>
       </c>
       <c r="G1434" t="n">
-        <v>8.34527206420898</v>
+        <v>8.3452730178833</v>
       </c>
       <c r="H1434" t="s">
         <v>8</v>
@@ -37705,7 +37705,7 @@
         <v>8.52000045776367</v>
       </c>
       <c r="G1436" t="n">
-        <v>7.98895788192749</v>
+        <v>7.98895740509033</v>
       </c>
       <c r="H1436" t="s">
         <v>8</v>
@@ -37731,7 +37731,7 @@
         <v>8.27999973297119</v>
       </c>
       <c r="G1437" t="n">
-        <v>7.76391649246216</v>
+        <v>7.763916015625</v>
       </c>
       <c r="H1437" t="s">
         <v>8</v>
@@ -37757,7 +37757,7 @@
         <v>8.5</v>
       </c>
       <c r="G1438" t="n">
-        <v>7.9702033996582</v>
+        <v>7.97020435333252</v>
       </c>
       <c r="H1438" t="s">
         <v>8</v>
@@ -37809,7 +37809,7 @@
         <v>8.73999977111816</v>
       </c>
       <c r="G1440" t="n">
-        <v>8.19524383544922</v>
+        <v>8.19524478912354</v>
       </c>
       <c r="H1440" t="s">
         <v>8</v>
@@ -37835,7 +37835,7 @@
         <v>8.52000045776367</v>
       </c>
       <c r="G1441" t="n">
-        <v>7.98895788192749</v>
+        <v>7.98895740509033</v>
       </c>
       <c r="H1441" t="s">
         <v>8</v>
@@ -37861,7 +37861,7 @@
         <v>8.5</v>
       </c>
       <c r="G1442" t="n">
-        <v>7.9702033996582</v>
+        <v>7.97020435333252</v>
       </c>
       <c r="H1442" t="s">
         <v>8</v>
@@ -37887,7 +37887,7 @@
         <v>8.60000038146973</v>
       </c>
       <c r="G1443" t="n">
-        <v>8.0639705657959</v>
+        <v>8.06397151947021</v>
       </c>
       <c r="H1443" t="s">
         <v>8</v>
@@ -37913,7 +37913,7 @@
         <v>8.60000038146973</v>
       </c>
       <c r="G1444" t="n">
-        <v>8.0639705657959</v>
+        <v>8.06397151947021</v>
       </c>
       <c r="H1444" t="s">
         <v>8</v>
@@ -37939,7 +37939,7 @@
         <v>8.5</v>
       </c>
       <c r="G1445" t="n">
-        <v>7.9702033996582</v>
+        <v>7.97020435333252</v>
       </c>
       <c r="H1445" t="s">
         <v>8</v>
@@ -37991,7 +37991,7 @@
         <v>8.47000026702881</v>
       </c>
       <c r="G1447" t="n">
-        <v>7.94207334518433</v>
+        <v>7.94207429885864</v>
       </c>
       <c r="H1447" t="s">
         <v>8</v>
@@ -38017,7 +38017,7 @@
         <v>8.46000003814697</v>
       </c>
       <c r="G1448" t="n">
-        <v>7.93269729614258</v>
+        <v>7.93269634246826</v>
       </c>
       <c r="H1448" t="s">
         <v>8</v>
@@ -38043,7 +38043,7 @@
         <v>8.3100004196167</v>
       </c>
       <c r="G1449" t="n">
-        <v>7.79204654693604</v>
+        <v>7.79204702377319</v>
       </c>
       <c r="H1449" t="s">
         <v>8</v>
@@ -38069,7 +38069,7 @@
         <v>8.36999988555908</v>
       </c>
       <c r="G1450" t="n">
-        <v>7.84830617904663</v>
+        <v>7.84830665588379</v>
       </c>
       <c r="H1450" t="s">
         <v>8</v>
@@ -38095,7 +38095,7 @@
         <v>8.71000003814697</v>
       </c>
       <c r="G1451" t="n">
-        <v>8.1671142578125</v>
+        <v>8.16711521148682</v>
       </c>
       <c r="H1451" t="s">
         <v>8</v>
@@ -38121,7 +38121,7 @@
         <v>8.65999984741211</v>
       </c>
       <c r="G1452" t="n">
-        <v>8.12022972106934</v>
+        <v>8.12023162841797</v>
       </c>
       <c r="H1452" t="s">
         <v>8</v>
@@ -38147,7 +38147,7 @@
         <v>8.67000007629395</v>
       </c>
       <c r="G1453" t="n">
-        <v>8.12960910797119</v>
+        <v>8.12960815429688</v>
       </c>
       <c r="H1453" t="s">
         <v>8</v>
@@ -38199,7 +38199,7 @@
         <v>8.5</v>
       </c>
       <c r="G1455" t="n">
-        <v>7.9702033996582</v>
+        <v>7.97020435333252</v>
       </c>
       <c r="H1455" t="s">
         <v>8</v>
@@ -38225,7 +38225,7 @@
         <v>8.60000038146973</v>
       </c>
       <c r="G1456" t="n">
-        <v>8.0639705657959</v>
+        <v>8.06397151947021</v>
       </c>
       <c r="H1456" t="s">
         <v>8</v>
@@ -38251,7 +38251,7 @@
         <v>8.42000007629395</v>
       </c>
       <c r="G1457" t="n">
-        <v>7.89519071578979</v>
+        <v>7.89519023895264</v>
       </c>
       <c r="H1457" t="s">
         <v>8</v>
@@ -38277,7 +38277,7 @@
         <v>8.36999988555908</v>
       </c>
       <c r="G1458" t="n">
-        <v>7.84830617904663</v>
+        <v>7.84830665588379</v>
       </c>
       <c r="H1458" t="s">
         <v>8</v>
@@ -38303,7 +38303,7 @@
         <v>8.35000038146973</v>
       </c>
       <c r="G1459" t="n">
-        <v>7.82955312728882</v>
+        <v>7.82955360412598</v>
       </c>
       <c r="H1459" t="s">
         <v>8</v>
@@ -38329,7 +38329,7 @@
         <v>8.27999973297119</v>
       </c>
       <c r="G1460" t="n">
-        <v>7.76391649246216</v>
+        <v>7.763916015625</v>
       </c>
       <c r="H1460" t="s">
         <v>8</v>
@@ -38355,7 +38355,7 @@
         <v>8.23999977111816</v>
       </c>
       <c r="G1461" t="n">
-        <v>7.7264084815979</v>
+        <v>7.72640943527222</v>
       </c>
       <c r="H1461" t="s">
         <v>8</v>
@@ -38433,7 +38433,7 @@
         <v>8.30000019073486</v>
       </c>
       <c r="G1464" t="n">
-        <v>7.78267049789429</v>
+        <v>7.78267002105713</v>
       </c>
       <c r="H1464" t="s">
         <v>8</v>
@@ -38459,7 +38459,7 @@
         <v>8.30000019073486</v>
       </c>
       <c r="G1465" t="n">
-        <v>7.78267049789429</v>
+        <v>7.78267002105713</v>
       </c>
       <c r="H1465" t="s">
         <v>8</v>
@@ -38485,7 +38485,7 @@
         <v>8.30000019073486</v>
       </c>
       <c r="G1466" t="n">
-        <v>7.78267049789429</v>
+        <v>7.78267002105713</v>
       </c>
       <c r="H1466" t="s">
         <v>8</v>
@@ -38511,7 +38511,7 @@
         <v>8.14000034332275</v>
       </c>
       <c r="G1467" t="n">
-        <v>7.63264226913452</v>
+        <v>7.63264274597168</v>
       </c>
       <c r="H1467" t="s">
         <v>8</v>
@@ -38537,7 +38537,7 @@
         <v>8.10000038146973</v>
       </c>
       <c r="G1468" t="n">
-        <v>7.59513568878174</v>
+        <v>7.59513521194458</v>
       </c>
       <c r="H1468" t="s">
         <v>8</v>
@@ -38589,7 +38589,7 @@
         <v>8</v>
       </c>
       <c r="G1470" t="n">
-        <v>7.50136852264404</v>
+        <v>7.50136804580688</v>
       </c>
       <c r="H1470" t="s">
         <v>8</v>
@@ -38615,7 +38615,7 @@
         <v>8.02999973297119</v>
       </c>
       <c r="G1471" t="n">
-        <v>7.52949810028076</v>
+        <v>7.52949857711792</v>
       </c>
       <c r="H1471" t="s">
         <v>8</v>
@@ -38641,7 +38641,7 @@
         <v>8.5600004196167</v>
       </c>
       <c r="G1472" t="n">
-        <v>8.02646446228027</v>
+        <v>8.02646350860596</v>
       </c>
       <c r="H1472" t="s">
         <v>8</v>
@@ -38667,7 +38667,7 @@
         <v>8.72999954223633</v>
       </c>
       <c r="G1473" t="n">
-        <v>8.18586826324463</v>
+        <v>8.185866355896</v>
       </c>
       <c r="H1473" t="s">
         <v>8</v>
@@ -38771,7 +38771,7 @@
         <v>8.5</v>
       </c>
       <c r="G1477" t="n">
-        <v>7.9702033996582</v>
+        <v>7.97020435333252</v>
       </c>
       <c r="H1477" t="s">
         <v>8</v>
@@ -38823,7 +38823,7 @@
         <v>8.72000026702881</v>
       </c>
       <c r="G1479" t="n">
-        <v>8.17649173736572</v>
+        <v>8.17649078369141</v>
       </c>
       <c r="H1479" t="s">
         <v>8</v>
@@ -38901,7 +38901,7 @@
         <v>8.60000038146973</v>
       </c>
       <c r="G1482" t="n">
-        <v>8.0639705657959</v>
+        <v>8.06397151947021</v>
       </c>
       <c r="H1482" t="s">
         <v>8</v>
@@ -38927,7 +38927,7 @@
         <v>8.71000003814697</v>
       </c>
       <c r="G1483" t="n">
-        <v>8.1671142578125</v>
+        <v>8.16711521148682</v>
       </c>
       <c r="H1483" t="s">
         <v>8</v>
@@ -38953,7 +38953,7 @@
         <v>8.5</v>
       </c>
       <c r="G1484" t="n">
-        <v>7.9702033996582</v>
+        <v>7.97020435333252</v>
       </c>
       <c r="H1484" t="s">
         <v>8</v>
@@ -39109,7 +39109,7 @@
         <v>8.34000015258789</v>
       </c>
       <c r="G1490" t="n">
-        <v>7.82017707824707</v>
+        <v>7.82017660140991</v>
       </c>
       <c r="H1490" t="s">
         <v>8</v>
@@ -39135,7 +39135,7 @@
         <v>8.3100004196167</v>
       </c>
       <c r="G1491" t="n">
-        <v>7.79204654693604</v>
+        <v>7.79204702377319</v>
       </c>
       <c r="H1491" t="s">
         <v>8</v>
@@ -39161,7 +39161,7 @@
         <v>8.23999977111816</v>
       </c>
       <c r="G1492" t="n">
-        <v>7.7264084815979</v>
+        <v>7.72640943527222</v>
       </c>
       <c r="H1492" t="s">
         <v>8</v>
@@ -39213,7 +39213,7 @@
         <v>8.19999980926514</v>
       </c>
       <c r="G1494" t="n">
-        <v>7.68890190124512</v>
+        <v>7.68890237808228</v>
       </c>
       <c r="H1494" t="s">
         <v>8</v>
@@ -39239,7 +39239,7 @@
         <v>8.19999980926514</v>
       </c>
       <c r="G1495" t="n">
-        <v>7.68890190124512</v>
+        <v>7.68890237808228</v>
       </c>
       <c r="H1495" t="s">
         <v>8</v>
@@ -39265,7 +39265,7 @@
         <v>8.35999965667725</v>
       </c>
       <c r="G1496" t="n">
-        <v>7.83893013000488</v>
+        <v>7.83892965316772</v>
       </c>
       <c r="H1496" t="s">
         <v>8</v>
@@ -39291,7 +39291,7 @@
         <v>8.3100004196167</v>
       </c>
       <c r="G1497" t="n">
-        <v>7.79204654693604</v>
+        <v>7.79204702377319</v>
       </c>
       <c r="H1497" t="s">
         <v>8</v>
@@ -39317,7 +39317,7 @@
         <v>8.36999988555908</v>
       </c>
       <c r="G1498" t="n">
-        <v>7.84830617904663</v>
+        <v>7.84830665588379</v>
       </c>
       <c r="H1498" t="s">
         <v>8</v>
@@ -39343,7 +39343,7 @@
         <v>8.39999961853027</v>
       </c>
       <c r="G1499" t="n">
-        <v>7.87643671035767</v>
+        <v>7.87643718719482</v>
       </c>
       <c r="H1499" t="s">
         <v>8</v>
@@ -39369,7 +39369,7 @@
         <v>8.4399995803833</v>
       </c>
       <c r="G1500" t="n">
-        <v>7.91394329071045</v>
+        <v>7.91394281387329</v>
       </c>
       <c r="H1500" t="s">
         <v>8</v>
@@ -39395,7 +39395,7 @@
         <v>8.30000019073486</v>
       </c>
       <c r="G1501" t="n">
-        <v>7.78267049789429</v>
+        <v>7.78267002105713</v>
       </c>
       <c r="H1501" t="s">
         <v>8</v>
@@ -39421,7 +39421,7 @@
         <v>8.39999961853027</v>
       </c>
       <c r="G1502" t="n">
-        <v>7.87643671035767</v>
+        <v>7.87643718719482</v>
       </c>
       <c r="H1502" t="s">
         <v>8</v>
@@ -39447,7 +39447,7 @@
         <v>8.30000019073486</v>
       </c>
       <c r="G1503" t="n">
-        <v>7.78267049789429</v>
+        <v>7.78267002105713</v>
       </c>
       <c r="H1503" t="s">
         <v>8</v>
@@ -39473,7 +39473,7 @@
         <v>8.30000019073486</v>
       </c>
       <c r="G1504" t="n">
-        <v>7.78267049789429</v>
+        <v>7.78267002105713</v>
       </c>
       <c r="H1504" t="s">
         <v>8</v>
@@ -39499,7 +39499,7 @@
         <v>8.35000038146973</v>
       </c>
       <c r="G1505" t="n">
-        <v>7.82955312728882</v>
+        <v>7.82955360412598</v>
       </c>
       <c r="H1505" t="s">
         <v>8</v>
@@ -39525,7 +39525,7 @@
         <v>8.05000019073486</v>
       </c>
       <c r="G1506" t="n">
-        <v>7.54825210571289</v>
+        <v>7.54825162887573</v>
       </c>
       <c r="H1506" t="s">
         <v>8</v>
@@ -39551,7 +39551,7 @@
         <v>8.10000038146973</v>
       </c>
       <c r="G1507" t="n">
-        <v>7.59513568878174</v>
+        <v>7.59513521194458</v>
       </c>
       <c r="H1507" t="s">
         <v>8</v>
@@ -39577,7 +39577,7 @@
         <v>8.19999980926514</v>
       </c>
       <c r="G1508" t="n">
-        <v>7.68890190124512</v>
+        <v>7.68890237808228</v>
       </c>
       <c r="H1508" t="s">
         <v>8</v>
@@ -39629,7 +39629,7 @@
         <v>8.06999969482422</v>
       </c>
       <c r="G1510" t="n">
-        <v>7.56700420379639</v>
+        <v>7.56700468063354</v>
       </c>
       <c r="H1510" t="s">
         <v>8</v>
@@ -39655,7 +39655,7 @@
         <v>7.88000011444092</v>
       </c>
       <c r="G1511" t="n">
-        <v>7.38884830474854</v>
+        <v>7.38884782791138</v>
       </c>
       <c r="H1511" t="s">
         <v>8</v>
@@ -39707,7 +39707,7 @@
         <v>7.80000019073486</v>
       </c>
       <c r="G1513" t="n">
-        <v>7.31383419036865</v>
+        <v>7.31383371353149</v>
       </c>
       <c r="H1513" t="s">
         <v>8</v>
@@ -39733,7 +39733,7 @@
         <v>7.90000009536743</v>
       </c>
       <c r="G1514" t="n">
-        <v>7.40760135650635</v>
+        <v>7.40760087966919</v>
       </c>
       <c r="H1514" t="s">
         <v>8</v>
@@ -39759,7 +39759,7 @@
         <v>7.80000019073486</v>
       </c>
       <c r="G1515" t="n">
-        <v>7.31383419036865</v>
+        <v>7.31383371353149</v>
       </c>
       <c r="H1515" t="s">
         <v>8</v>
@@ -39811,7 +39811,7 @@
         <v>8</v>
       </c>
       <c r="G1517" t="n">
-        <v>7.50136852264404</v>
+        <v>7.50136804580688</v>
       </c>
       <c r="H1517" t="s">
         <v>8</v>
@@ -39837,7 +39837,7 @@
         <v>8</v>
       </c>
       <c r="G1518" t="n">
-        <v>7.50136852264404</v>
+        <v>7.50136804580688</v>
       </c>
       <c r="H1518" t="s">
         <v>8</v>
@@ -39863,7 +39863,7 @@
         <v>7.8899998664856</v>
       </c>
       <c r="G1519" t="n">
-        <v>7.39822483062744</v>
+        <v>7.39822387695312</v>
       </c>
       <c r="H1519" t="s">
         <v>8</v>
@@ -39915,7 +39915,7 @@
         <v>7.55000019073486</v>
       </c>
       <c r="G1521" t="n">
-        <v>7.07941627502441</v>
+        <v>7.07941675186157</v>
       </c>
       <c r="H1521" t="s">
         <v>8</v>
@@ -39941,7 +39941,7 @@
         <v>7.53000020980835</v>
       </c>
       <c r="G1522" t="n">
-        <v>7.06066274642944</v>
+        <v>7.0606632232666</v>
       </c>
       <c r="H1522" t="s">
         <v>8</v>
@@ -40019,7 +40019,7 @@
         <v>7.57999992370605</v>
       </c>
       <c r="G1525" t="n">
-        <v>7.10754585266113</v>
+        <v>7.10754632949829</v>
       </c>
       <c r="H1525" t="s">
         <v>8</v>
@@ -40123,7 +40123,7 @@
         <v>7.59999990463257</v>
       </c>
       <c r="G1529" t="n">
-        <v>7.12629985809326</v>
+        <v>7.1262993812561</v>
       </c>
       <c r="H1529" t="s">
         <v>8</v>
@@ -40253,7 +40253,7 @@
         <v>7.6399998664856</v>
       </c>
       <c r="G1534" t="n">
-        <v>7.16380643844604</v>
+        <v>7.16380596160889</v>
       </c>
       <c r="H1534" t="s">
         <v>8</v>
@@ -40435,7 +40435,7 @@
         <v>7.98000001907349</v>
       </c>
       <c r="G1541" t="n">
-        <v>7.48261499404907</v>
+        <v>7.48261451721191</v>
       </c>
       <c r="H1541" t="s">
         <v>8</v>
@@ -40539,7 +40539,7 @@
         <v>8.10000038146973</v>
       </c>
       <c r="G1545" t="n">
-        <v>7.59513568878174</v>
+        <v>7.59513521194458</v>
       </c>
       <c r="H1545" t="s">
         <v>8</v>
@@ -40565,7 +40565,7 @@
         <v>7.80000019073486</v>
       </c>
       <c r="G1546" t="n">
-        <v>7.31383419036865</v>
+        <v>7.31383371353149</v>
       </c>
       <c r="H1546" t="s">
         <v>8</v>
@@ -40669,7 +40669,7 @@
         <v>8.30000019073486</v>
       </c>
       <c r="G1550" t="n">
-        <v>7.78267049789429</v>
+        <v>7.78267002105713</v>
       </c>
       <c r="H1550" t="s">
         <v>8</v>
@@ -40695,7 +40695,7 @@
         <v>8.27999973297119</v>
       </c>
       <c r="G1551" t="n">
-        <v>7.76391649246216</v>
+        <v>7.763916015625</v>
       </c>
       <c r="H1551" t="s">
         <v>8</v>
@@ -40721,7 +40721,7 @@
         <v>8.30000019073486</v>
       </c>
       <c r="G1552" t="n">
-        <v>7.78267049789429</v>
+        <v>7.78267002105713</v>
       </c>
       <c r="H1552" t="s">
         <v>8</v>
@@ -40747,7 +40747,7 @@
         <v>8.26000022888184</v>
       </c>
       <c r="G1553" t="n">
-        <v>7.74516248703003</v>
+        <v>7.74516296386719</v>
       </c>
       <c r="H1553" t="s">
         <v>8</v>
@@ -40773,7 +40773,7 @@
         <v>8.19999980926514</v>
       </c>
       <c r="G1554" t="n">
-        <v>7.68890190124512</v>
+        <v>7.68890237808228</v>
       </c>
       <c r="H1554" t="s">
         <v>8</v>
@@ -40799,7 +40799,7 @@
         <v>8.35000038146973</v>
       </c>
       <c r="G1555" t="n">
-        <v>7.82955312728882</v>
+        <v>7.82955360412598</v>
       </c>
       <c r="H1555" t="s">
         <v>8</v>
@@ -40877,7 +40877,7 @@
         <v>8.35000038146973</v>
       </c>
       <c r="G1558" t="n">
-        <v>7.82955312728882</v>
+        <v>7.82955360412598</v>
       </c>
       <c r="H1558" t="s">
         <v>8</v>
@@ -40903,7 +40903,7 @@
         <v>8.35000038146973</v>
       </c>
       <c r="G1559" t="n">
-        <v>7.82955312728882</v>
+        <v>7.82955360412598</v>
       </c>
       <c r="H1559" t="s">
         <v>8</v>
@@ -40929,7 +40929,7 @@
         <v>8.39999961853027</v>
       </c>
       <c r="G1560" t="n">
-        <v>7.87643671035767</v>
+        <v>7.87643718719482</v>
       </c>
       <c r="H1560" t="s">
         <v>8</v>
@@ -41007,7 +41007,7 @@
         <v>8.38000011444092</v>
       </c>
       <c r="G1563" t="n">
-        <v>7.8576831817627</v>
+        <v>7.85768365859985</v>
       </c>
       <c r="H1563" t="s">
         <v>8</v>
@@ -41059,7 +41059,7 @@
         <v>8.30000019073486</v>
       </c>
       <c r="G1565" t="n">
-        <v>7.78267049789429</v>
+        <v>7.78267002105713</v>
       </c>
       <c r="H1565" t="s">
         <v>8</v>
@@ -41085,7 +41085,7 @@
         <v>8.39999961853027</v>
       </c>
       <c r="G1566" t="n">
-        <v>7.87643671035767</v>
+        <v>7.87643718719482</v>
       </c>
       <c r="H1566" t="s">
         <v>8</v>
@@ -41111,7 +41111,7 @@
         <v>8.35999965667725</v>
       </c>
       <c r="G1567" t="n">
-        <v>7.83893013000488</v>
+        <v>7.83892965316772</v>
       </c>
       <c r="H1567" t="s">
         <v>8</v>
@@ -41137,7 +41137,7 @@
         <v>8.30000019073486</v>
       </c>
       <c r="G1568" t="n">
-        <v>7.78267049789429</v>
+        <v>7.78267002105713</v>
       </c>
       <c r="H1568" t="s">
         <v>8</v>
@@ -41163,7 +41163,7 @@
         <v>8.30000019073486</v>
       </c>
       <c r="G1569" t="n">
-        <v>7.78267049789429</v>
+        <v>7.78267002105713</v>
       </c>
       <c r="H1569" t="s">
         <v>8</v>
@@ -41189,7 +41189,7 @@
         <v>8.30000019073486</v>
       </c>
       <c r="G1570" t="n">
-        <v>7.78267049789429</v>
+        <v>7.78267002105713</v>
       </c>
       <c r="H1570" t="s">
         <v>8</v>
@@ -41241,7 +41241,7 @@
         <v>8.1899995803833</v>
       </c>
       <c r="G1572" t="n">
-        <v>7.67952537536621</v>
+        <v>7.67952489852905</v>
       </c>
       <c r="H1572" t="s">
         <v>8</v>
@@ -41319,7 +41319,7 @@
         <v>8.67000007629395</v>
       </c>
       <c r="G1575" t="n">
-        <v>8.12960910797119</v>
+        <v>8.12960815429688</v>
       </c>
       <c r="H1575" t="s">
         <v>8</v>
@@ -41345,7 +41345,7 @@
         <v>8.5</v>
       </c>
       <c r="G1576" t="n">
-        <v>7.9702033996582</v>
+        <v>7.97020435333252</v>
       </c>
       <c r="H1576" t="s">
         <v>8</v>
@@ -41397,7 +41397,7 @@
         <v>8.34000015258789</v>
       </c>
       <c r="G1578" t="n">
-        <v>7.82017707824707</v>
+        <v>7.82017660140991</v>
       </c>
       <c r="H1578" t="s">
         <v>8</v>
@@ -41423,7 +41423,7 @@
         <v>8.35000038146973</v>
       </c>
       <c r="G1579" t="n">
-        <v>7.82955312728882</v>
+        <v>7.82955360412598</v>
       </c>
       <c r="H1579" t="s">
         <v>8</v>
@@ -41553,7 +41553,7 @@
         <v>8.26000022888184</v>
       </c>
       <c r="G1584" t="n">
-        <v>7.74516248703003</v>
+        <v>7.74516296386719</v>
       </c>
       <c r="H1584" t="s">
         <v>8</v>
@@ -41605,7 +41605,7 @@
         <v>8.23999977111816</v>
       </c>
       <c r="G1586" t="n">
-        <v>7.7264084815979</v>
+        <v>7.72640943527222</v>
       </c>
       <c r="H1586" t="s">
         <v>8</v>
@@ -41631,7 +41631,7 @@
         <v>8.23999977111816</v>
       </c>
       <c r="G1587" t="n">
-        <v>7.7264084815979</v>
+        <v>7.72640943527222</v>
       </c>
       <c r="H1587" t="s">
         <v>8</v>
@@ -41657,7 +41657,7 @@
         <v>8.10000038146973</v>
       </c>
       <c r="G1588" t="n">
-        <v>7.59513568878174</v>
+        <v>7.59513521194458</v>
       </c>
       <c r="H1588" t="s">
         <v>8</v>
@@ -41683,7 +41683,7 @@
         <v>8.18000030517578</v>
       </c>
       <c r="G1589" t="n">
-        <v>7.6701488494873</v>
+        <v>7.67014932632446</v>
       </c>
       <c r="H1589" t="s">
         <v>8</v>
@@ -41735,7 +41735,7 @@
         <v>8.10000038146973</v>
       </c>
       <c r="G1591" t="n">
-        <v>7.59513568878174</v>
+        <v>7.59513521194458</v>
       </c>
       <c r="H1591" t="s">
         <v>8</v>
@@ -41761,7 +41761,7 @@
         <v>8.18000030517578</v>
       </c>
       <c r="G1592" t="n">
-        <v>7.6701488494873</v>
+        <v>7.67014932632446</v>
       </c>
       <c r="H1592" t="s">
         <v>8</v>
@@ -41787,7 +41787,7 @@
         <v>8.18000030517578</v>
       </c>
       <c r="G1593" t="n">
-        <v>7.6701488494873</v>
+        <v>7.67014932632446</v>
       </c>
       <c r="H1593" t="s">
         <v>8</v>
@@ -41813,7 +41813,7 @@
         <v>8.19999980926514</v>
       </c>
       <c r="G1594" t="n">
-        <v>7.68890190124512</v>
+        <v>7.68890237808228</v>
       </c>
       <c r="H1594" t="s">
         <v>8</v>
@@ -41865,7 +41865,7 @@
         <v>8.22999954223633</v>
       </c>
       <c r="G1596" t="n">
-        <v>7.71703243255615</v>
+        <v>7.71703147888184</v>
       </c>
       <c r="H1596" t="s">
         <v>8</v>
@@ -41891,7 +41891,7 @@
         <v>8.19999980926514</v>
       </c>
       <c r="G1597" t="n">
-        <v>7.68890190124512</v>
+        <v>7.68890237808228</v>
       </c>
       <c r="H1597" t="s">
         <v>8</v>
@@ -41917,7 +41917,7 @@
         <v>8.19999980926514</v>
       </c>
       <c r="G1598" t="n">
-        <v>7.68890190124512</v>
+        <v>7.68890237808228</v>
       </c>
       <c r="H1598" t="s">
         <v>8</v>
@@ -41969,7 +41969,7 @@
         <v>8.19999980926514</v>
       </c>
       <c r="G1600" t="n">
-        <v>7.68890190124512</v>
+        <v>7.68890237808228</v>
       </c>
       <c r="H1600" t="s">
         <v>8</v>
@@ -41995,7 +41995,7 @@
         <v>8.19999980926514</v>
       </c>
       <c r="G1601" t="n">
-        <v>7.68890190124512</v>
+        <v>7.68890237808228</v>
       </c>
       <c r="H1601" t="s">
         <v>8</v>
@@ -42021,7 +42021,7 @@
         <v>8.19999980926514</v>
       </c>
       <c r="G1602" t="n">
-        <v>7.68890190124512</v>
+        <v>7.68890237808228</v>
       </c>
       <c r="H1602" t="s">
         <v>8</v>
@@ -42073,7 +42073,7 @@
         <v>8.19999980926514</v>
       </c>
       <c r="G1604" t="n">
-        <v>7.68890190124512</v>
+        <v>7.68890237808228</v>
       </c>
       <c r="H1604" t="s">
         <v>8</v>
@@ -42099,7 +42099,7 @@
         <v>8.21000003814697</v>
       </c>
       <c r="G1605" t="n">
-        <v>7.69827890396118</v>
+        <v>7.69827938079834</v>
       </c>
       <c r="H1605" t="s">
         <v>8</v>
@@ -42151,7 +42151,7 @@
         <v>8.14000034332275</v>
       </c>
       <c r="G1607" t="n">
-        <v>7.63264226913452</v>
+        <v>7.63264274597168</v>
       </c>
       <c r="H1607" t="s">
         <v>8</v>
@@ -42177,7 +42177,7 @@
         <v>8.10000038146973</v>
       </c>
       <c r="G1608" t="n">
-        <v>7.59513568878174</v>
+        <v>7.59513521194458</v>
       </c>
       <c r="H1608" t="s">
         <v>8</v>
@@ -42203,7 +42203,7 @@
         <v>8.18000030517578</v>
       </c>
       <c r="G1609" t="n">
-        <v>7.6701488494873</v>
+        <v>7.67014932632446</v>
       </c>
       <c r="H1609" t="s">
         <v>8</v>
@@ -42385,7 +42385,7 @@
         <v>8.14000034332275</v>
       </c>
       <c r="G1616" t="n">
-        <v>7.63264226913452</v>
+        <v>7.63264274597168</v>
       </c>
       <c r="H1616" t="s">
         <v>8</v>
@@ -42411,7 +42411,7 @@
         <v>8.27000045776367</v>
       </c>
       <c r="G1617" t="n">
-        <v>7.75453996658325</v>
+        <v>7.75454044342041</v>
       </c>
       <c r="H1617" t="s">
         <v>8</v>
@@ -42463,7 +42463,7 @@
         <v>8.23999977111816</v>
       </c>
       <c r="G1619" t="n">
-        <v>7.7264084815979</v>
+        <v>7.72640943527222</v>
       </c>
       <c r="H1619" t="s">
         <v>8</v>
@@ -42489,7 +42489,7 @@
         <v>8.26000022888184</v>
       </c>
       <c r="G1620" t="n">
-        <v>7.74516248703003</v>
+        <v>7.74516296386719</v>
       </c>
       <c r="H1620" t="s">
         <v>8</v>
@@ -42515,7 +42515,7 @@
         <v>8.30000019073486</v>
       </c>
       <c r="G1621" t="n">
-        <v>7.78267049789429</v>
+        <v>7.78267002105713</v>
       </c>
       <c r="H1621" t="s">
         <v>8</v>
@@ -42567,7 +42567,7 @@
         <v>8.39999961853027</v>
       </c>
       <c r="G1623" t="n">
-        <v>7.87643671035767</v>
+        <v>7.87643718719482</v>
       </c>
       <c r="H1623" t="s">
         <v>8</v>
@@ -42645,7 +42645,7 @@
         <v>8.39999961853027</v>
       </c>
       <c r="G1626" t="n">
-        <v>7.87643671035767</v>
+        <v>7.87643718719482</v>
       </c>
       <c r="H1626" t="s">
         <v>8</v>
@@ -42671,7 +42671,7 @@
         <v>8.38000011444092</v>
       </c>
       <c r="G1627" t="n">
-        <v>7.8576831817627</v>
+        <v>7.85768365859985</v>
       </c>
       <c r="H1627" t="s">
         <v>8</v>
@@ -42697,7 +42697,7 @@
         <v>8.30000019073486</v>
       </c>
       <c r="G1628" t="n">
-        <v>7.78267049789429</v>
+        <v>7.78267002105713</v>
       </c>
       <c r="H1628" t="s">
         <v>8</v>
@@ -42749,7 +42749,7 @@
         <v>8.39999961853027</v>
       </c>
       <c r="G1630" t="n">
-        <v>7.87643671035767</v>
+        <v>7.87643718719482</v>
       </c>
       <c r="H1630" t="s">
         <v>8</v>
@@ -42775,7 +42775,7 @@
         <v>8.39000034332275</v>
       </c>
       <c r="G1631" t="n">
-        <v>7.86706066131592</v>
+        <v>7.86706018447876</v>
       </c>
       <c r="H1631" t="s">
         <v>8</v>
@@ -42879,7 +42879,7 @@
         <v>8.3100004196167</v>
       </c>
       <c r="G1635" t="n">
-        <v>7.79204654693604</v>
+        <v>7.79204702377319</v>
       </c>
       <c r="H1635" t="s">
         <v>8</v>
@@ -42957,7 +42957,7 @@
         <v>8.34000015258789</v>
       </c>
       <c r="G1638" t="n">
-        <v>7.82017707824707</v>
+        <v>7.82017660140991</v>
       </c>
       <c r="H1638" t="s">
         <v>8</v>
@@ -42983,7 +42983,7 @@
         <v>8.30000019073486</v>
       </c>
       <c r="G1639" t="n">
-        <v>7.78267049789429</v>
+        <v>7.78267002105713</v>
       </c>
       <c r="H1639" t="s">
         <v>8</v>
@@ -43009,7 +43009,7 @@
         <v>8.30000019073486</v>
       </c>
       <c r="G1640" t="n">
-        <v>7.78267049789429</v>
+        <v>7.78267002105713</v>
       </c>
       <c r="H1640" t="s">
         <v>8</v>
@@ -43035,7 +43035,7 @@
         <v>8.3100004196167</v>
       </c>
       <c r="G1641" t="n">
-        <v>7.79204654693604</v>
+        <v>7.79204702377319</v>
       </c>
       <c r="H1641" t="s">
         <v>8</v>
@@ -43061,7 +43061,7 @@
         <v>8.30000019073486</v>
       </c>
       <c r="G1642" t="n">
-        <v>7.78267049789429</v>
+        <v>7.78267002105713</v>
       </c>
       <c r="H1642" t="s">
         <v>8</v>
@@ -43087,7 +43087,7 @@
         <v>8.35999965667725</v>
       </c>
       <c r="G1643" t="n">
-        <v>7.83893013000488</v>
+        <v>7.83892965316772</v>
       </c>
       <c r="H1643" t="s">
         <v>8</v>
@@ -43165,7 +43165,7 @@
         <v>8.36999988555908</v>
       </c>
       <c r="G1646" t="n">
-        <v>7.84830617904663</v>
+        <v>7.84830665588379</v>
       </c>
       <c r="H1646" t="s">
         <v>8</v>
@@ -43191,7 +43191,7 @@
         <v>8.35000038146973</v>
       </c>
       <c r="G1647" t="n">
-        <v>7.82955312728882</v>
+        <v>7.82955360412598</v>
       </c>
       <c r="H1647" t="s">
         <v>8</v>
@@ -43269,7 +43269,7 @@
         <v>8.35000038146973</v>
       </c>
       <c r="G1650" t="n">
-        <v>7.82955312728882</v>
+        <v>7.82955360412598</v>
       </c>
       <c r="H1650" t="s">
         <v>8</v>
@@ -43295,7 +43295,7 @@
         <v>8.34000015258789</v>
       </c>
       <c r="G1651" t="n">
-        <v>7.82017707824707</v>
+        <v>7.82017660140991</v>
       </c>
       <c r="H1651" t="s">
         <v>8</v>
@@ -43347,7 +43347,7 @@
         <v>8.35999965667725</v>
       </c>
       <c r="G1653" t="n">
-        <v>7.83893013000488</v>
+        <v>7.83892965316772</v>
       </c>
       <c r="H1653" t="s">
         <v>8</v>
@@ -43373,7 +43373,7 @@
         <v>8.35000038146973</v>
       </c>
       <c r="G1654" t="n">
-        <v>7.82955312728882</v>
+        <v>7.82955360412598</v>
       </c>
       <c r="H1654" t="s">
         <v>8</v>
@@ -43399,7 +43399,7 @@
         <v>8.10000038146973</v>
       </c>
       <c r="G1655" t="n">
-        <v>7.59513568878174</v>
+        <v>7.59513521194458</v>
       </c>
       <c r="H1655" t="s">
         <v>8</v>
@@ -43425,7 +43425,7 @@
         <v>8.15999984741211</v>
       </c>
       <c r="G1656" t="n">
-        <v>7.65139484405518</v>
+        <v>7.65139532089233</v>
       </c>
       <c r="H1656" t="s">
         <v>8</v>
@@ -43451,7 +43451,7 @@
         <v>8.14000034332275</v>
       </c>
       <c r="G1657" t="n">
-        <v>7.63264226913452</v>
+        <v>7.63264274597168</v>
       </c>
       <c r="H1657" t="s">
         <v>8</v>
@@ -43477,7 +43477,7 @@
         <v>8.14000034332275</v>
       </c>
       <c r="G1658" t="n">
-        <v>7.63264226913452</v>
+        <v>7.63264274597168</v>
       </c>
       <c r="H1658" t="s">
         <v>8</v>
@@ -43555,7 +43555,7 @@
         <v>7.98000001907349</v>
       </c>
       <c r="G1661" t="n">
-        <v>7.48261499404907</v>
+        <v>7.48261451721191</v>
       </c>
       <c r="H1661" t="s">
         <v>8</v>
@@ -43607,7 +43607,7 @@
         <v>7.55000019073486</v>
       </c>
       <c r="G1663" t="n">
-        <v>7.07941627502441</v>
+        <v>7.07941675186157</v>
       </c>
       <c r="H1663" t="s">
         <v>8</v>
@@ -43633,7 +43633,7 @@
         <v>7.55000019073486</v>
       </c>
       <c r="G1664" t="n">
-        <v>7.07941627502441</v>
+        <v>7.07941675186157</v>
       </c>
       <c r="H1664" t="s">
         <v>8</v>
@@ -43711,7 +43711,7 @@
         <v>7.59999990463257</v>
       </c>
       <c r="G1667" t="n">
-        <v>7.12629985809326</v>
+        <v>7.1262993812561</v>
       </c>
       <c r="H1667" t="s">
         <v>8</v>
@@ -43737,7 +43737,7 @@
         <v>7.44999980926514</v>
       </c>
       <c r="G1668" t="n">
-        <v>6.98564910888672</v>
+        <v>6.98564863204956</v>
       </c>
       <c r="H1668" t="s">
         <v>8</v>
@@ -43763,7 +43763,7 @@
         <v>7.44999980926514</v>
       </c>
       <c r="G1669" t="n">
-        <v>6.98564910888672</v>
+        <v>6.98564863204956</v>
       </c>
       <c r="H1669" t="s">
         <v>8</v>
@@ -43789,7 +43789,7 @@
         <v>7.63000011444092</v>
       </c>
       <c r="G1670" t="n">
-        <v>7.1544303894043</v>
+        <v>7.15442991256714</v>
       </c>
       <c r="H1670" t="s">
         <v>8</v>
@@ -43815,7 +43815,7 @@
         <v>7.44999980926514</v>
       </c>
       <c r="G1671" t="n">
-        <v>6.98564910888672</v>
+        <v>6.98564863204956</v>
       </c>
       <c r="H1671" t="s">
         <v>8</v>
@@ -43867,7 +43867,7 @@
         <v>7.42999982833862</v>
       </c>
       <c r="G1673" t="n">
-        <v>6.96689558029175</v>
+        <v>6.96689605712891</v>
       </c>
       <c r="H1673" t="s">
         <v>8</v>
@@ -43893,7 +43893,7 @@
         <v>7.40000009536743</v>
       </c>
       <c r="G1674" t="n">
-        <v>6.93876600265503</v>
+        <v>6.93876552581787</v>
       </c>
       <c r="H1674" t="s">
         <v>8</v>
@@ -43919,7 +43919,7 @@
         <v>7.40000009536743</v>
       </c>
       <c r="G1675" t="n">
-        <v>6.93876600265503</v>
+        <v>6.93876552581787</v>
       </c>
       <c r="H1675" t="s">
         <v>8</v>
@@ -43945,7 +43945,7 @@
         <v>7.76000022888184</v>
       </c>
       <c r="G1676" t="n">
-        <v>7.3760027885437</v>
+        <v>7.37600326538086</v>
       </c>
       <c r="H1676" t="s">
         <v>8</v>
@@ -43971,7 +43971,7 @@
         <v>8.26000022888184</v>
       </c>
       <c r="G1677" t="n">
-        <v>7.85126066207886</v>
+        <v>7.85126161575317</v>
       </c>
       <c r="H1677" t="s">
         <v>8</v>
@@ -43997,7 +43997,7 @@
         <v>8.30000019073486</v>
       </c>
       <c r="G1678" t="n">
-        <v>7.8892822265625</v>
+        <v>7.88928127288818</v>
       </c>
       <c r="H1678" t="s">
         <v>8</v>
@@ -44023,7 +44023,7 @@
         <v>8.31999969482422</v>
       </c>
       <c r="G1679" t="n">
-        <v>7.90829133987427</v>
+        <v>7.90829086303711</v>
       </c>
       <c r="H1679" t="s">
         <v>8</v>
@@ -44049,7 +44049,7 @@
         <v>8.27000045776367</v>
       </c>
       <c r="G1680" t="n">
-        <v>7.86076641082764</v>
+        <v>7.86076688766479</v>
       </c>
       <c r="H1680" t="s">
         <v>8</v>
@@ -44075,7 +44075,7 @@
         <v>8.30000019073486</v>
       </c>
       <c r="G1681" t="n">
-        <v>7.8892822265625</v>
+        <v>7.88928127288818</v>
       </c>
       <c r="H1681" t="s">
         <v>8</v>
@@ -44127,7 +44127,7 @@
         <v>8.30000019073486</v>
       </c>
       <c r="G1683" t="n">
-        <v>7.8892822265625</v>
+        <v>7.88928127288818</v>
       </c>
       <c r="H1683" t="s">
         <v>8</v>
@@ -44179,7 +44179,7 @@
         <v>8.39999961853027</v>
       </c>
       <c r="G1685" t="n">
-        <v>7.98433303833008</v>
+        <v>7.98433208465576</v>
       </c>
       <c r="H1685" t="s">
         <v>8</v>
@@ -44205,7 +44205,7 @@
         <v>8.31999969482422</v>
       </c>
       <c r="G1686" t="n">
-        <v>7.90829133987427</v>
+        <v>7.90829086303711</v>
       </c>
       <c r="H1686" t="s">
         <v>8</v>
@@ -44231,7 +44231,7 @@
         <v>8.32999992370605</v>
       </c>
       <c r="G1687" t="n">
-        <v>7.91779708862305</v>
+        <v>7.91779661178589</v>
       </c>
       <c r="H1687" t="s">
         <v>8</v>
@@ -44283,7 +44283,7 @@
         <v>8.22000026702881</v>
       </c>
       <c r="G1689" t="n">
-        <v>7.81324005126953</v>
+        <v>7.81324052810669</v>
       </c>
       <c r="H1689" t="s">
         <v>8</v>
@@ -44309,7 +44309,7 @@
         <v>8.32999992370605</v>
       </c>
       <c r="G1690" t="n">
-        <v>7.91779708862305</v>
+        <v>7.91779661178589</v>
       </c>
       <c r="H1690" t="s">
         <v>8</v>
@@ -44361,7 +44361,7 @@
         <v>8.34000015258789</v>
       </c>
       <c r="G1692" t="n">
-        <v>7.92730236053467</v>
+        <v>7.92730188369751</v>
       </c>
       <c r="H1692" t="s">
         <v>8</v>
@@ -44387,7 +44387,7 @@
         <v>8.35999965667725</v>
       </c>
       <c r="G1693" t="n">
-        <v>7.94631290435791</v>
+        <v>7.94631147384644</v>
       </c>
       <c r="H1693" t="s">
         <v>8</v>
@@ -44413,7 +44413,7 @@
         <v>8.25</v>
       </c>
       <c r="G1694" t="n">
-        <v>7.84175539016724</v>
+        <v>7.84175586700439</v>
       </c>
       <c r="H1694" t="s">
         <v>8</v>
@@ -44439,7 +44439,7 @@
         <v>8.31999969482422</v>
       </c>
       <c r="G1695" t="n">
-        <v>7.90829133987427</v>
+        <v>7.90829086303711</v>
       </c>
       <c r="H1695" t="s">
         <v>8</v>
@@ -44465,7 +44465,7 @@
         <v>8.21000003814697</v>
       </c>
       <c r="G1696" t="n">
-        <v>7.80373477935791</v>
+        <v>7.80373525619507</v>
       </c>
       <c r="H1696" t="s">
         <v>8</v>
@@ -44491,7 +44491,7 @@
         <v>8.26000022888184</v>
       </c>
       <c r="G1697" t="n">
-        <v>7.85126066207886</v>
+        <v>7.85126161575317</v>
       </c>
       <c r="H1697" t="s">
         <v>8</v>
@@ -44517,7 +44517,7 @@
         <v>8.35999965667725</v>
       </c>
       <c r="G1698" t="n">
-        <v>7.94631290435791</v>
+        <v>7.94631147384644</v>
       </c>
       <c r="H1698" t="s">
         <v>8</v>
@@ -44543,7 +44543,7 @@
         <v>8.35999965667725</v>
       </c>
       <c r="G1699" t="n">
-        <v>7.94631290435791</v>
+        <v>7.94631147384644</v>
       </c>
       <c r="H1699" t="s">
         <v>8</v>
@@ -44569,7 +44569,7 @@
         <v>8.22000026702881</v>
       </c>
       <c r="G1700" t="n">
-        <v>7.81324005126953</v>
+        <v>7.81324052810669</v>
       </c>
       <c r="H1700" t="s">
         <v>8</v>
@@ -44751,7 +44751,7 @@
         <v>8.39999961853027</v>
       </c>
       <c r="G1707" t="n">
-        <v>7.98433303833008</v>
+        <v>7.98433208465576</v>
       </c>
       <c r="H1707" t="s">
         <v>8</v>
@@ -44777,7 +44777,7 @@
         <v>8.34000015258789</v>
       </c>
       <c r="G1708" t="n">
-        <v>7.92730236053467</v>
+        <v>7.92730188369751</v>
       </c>
       <c r="H1708" t="s">
         <v>8</v>
@@ -44803,7 +44803,7 @@
         <v>8.10999965667725</v>
       </c>
       <c r="G1709" t="n">
-        <v>7.70868301391602</v>
+        <v>7.70868253707886</v>
       </c>
       <c r="H1709" t="s">
         <v>8</v>
@@ -44829,7 +44829,7 @@
         <v>8.03999996185303</v>
       </c>
       <c r="G1710" t="n">
-        <v>7.64214706420898</v>
+        <v>7.64214754104614</v>
       </c>
       <c r="H1710" t="s">
         <v>8</v>
@@ -44855,7 +44855,7 @@
         <v>8.18000030517578</v>
       </c>
       <c r="G1711" t="n">
-        <v>7.77521944046021</v>
+        <v>7.77521991729736</v>
       </c>
       <c r="H1711" t="s">
         <v>8</v>
@@ -44881,7 +44881,7 @@
         <v>8.11999988555908</v>
       </c>
       <c r="G1712" t="n">
-        <v>7.71818828582764</v>
+        <v>7.71818876266479</v>
       </c>
       <c r="H1712" t="s">
         <v>8</v>
@@ -45063,7 +45063,7 @@
         <v>8.05000019073486</v>
       </c>
       <c r="G1719" t="n">
-        <v>7.65165233612061</v>
+        <v>7.65165281295776</v>
       </c>
       <c r="H1719" t="s">
         <v>8</v>
@@ -45089,7 +45089,7 @@
         <v>7.92999982833862</v>
       </c>
       <c r="G1720" t="n">
-        <v>7.53759050369263</v>
+        <v>7.53759002685547</v>
       </c>
       <c r="H1720" t="s">
         <v>8</v>
@@ -45115,7 +45115,7 @@
         <v>7.98999977111816</v>
       </c>
       <c r="G1721" t="n">
-        <v>7.59462118148804</v>
+        <v>7.5946216583252</v>
       </c>
       <c r="H1721" t="s">
         <v>8</v>
@@ -45141,7 +45141,7 @@
         <v>7.98000001907349</v>
       </c>
       <c r="G1722" t="n">
-        <v>7.58511638641357</v>
+        <v>7.58511590957642</v>
       </c>
       <c r="H1722" t="s">
         <v>8</v>
@@ -45219,7 +45219,7 @@
         <v>8.01000022888184</v>
       </c>
       <c r="G1725" t="n">
-        <v>7.61363172531128</v>
+        <v>7.61363220214844</v>
       </c>
       <c r="H1725" t="s">
         <v>8</v>
@@ -45245,7 +45245,7 @@
         <v>8.03999996185303</v>
       </c>
       <c r="G1726" t="n">
-        <v>7.64214706420898</v>
+        <v>7.64214754104614</v>
       </c>
       <c r="H1726" t="s">
         <v>8</v>
@@ -45271,7 +45271,7 @@
         <v>7.92999982833862</v>
       </c>
       <c r="G1727" t="n">
-        <v>7.53759050369263</v>
+        <v>7.53759002685547</v>
       </c>
       <c r="H1727" t="s">
         <v>8</v>
@@ -45297,7 +45297,7 @@
         <v>8.01000022888184</v>
       </c>
       <c r="G1728" t="n">
-        <v>7.61363172531128</v>
+        <v>7.61363220214844</v>
       </c>
       <c r="H1728" t="s">
         <v>8</v>
@@ -45349,7 +45349,7 @@
         <v>7.98999977111816</v>
       </c>
       <c r="G1730" t="n">
-        <v>7.59462118148804</v>
+        <v>7.5946216583252</v>
       </c>
       <c r="H1730" t="s">
         <v>8</v>
@@ -45479,7 +45479,7 @@
         <v>8.05000019073486</v>
       </c>
       <c r="G1735" t="n">
-        <v>7.65165233612061</v>
+        <v>7.65165281295776</v>
       </c>
       <c r="H1735" t="s">
         <v>8</v>
@@ -45505,7 +45505,7 @@
         <v>8.05000019073486</v>
       </c>
       <c r="G1736" t="n">
-        <v>7.65165233612061</v>
+        <v>7.65165281295776</v>
       </c>
       <c r="H1736" t="s">
         <v>8</v>
@@ -45531,7 +45531,7 @@
         <v>8.13000011444092</v>
       </c>
       <c r="G1737" t="n">
-        <v>7.72769355773926</v>
+        <v>7.72769403457642</v>
       </c>
       <c r="H1737" t="s">
         <v>8</v>
@@ -45557,7 +45557,7 @@
         <v>8.15999984741211</v>
       </c>
       <c r="G1738" t="n">
-        <v>7.75620889663696</v>
+        <v>7.75620937347412</v>
       </c>
       <c r="H1738" t="s">
         <v>8</v>
@@ -45583,7 +45583,7 @@
         <v>8.11999988555908</v>
       </c>
       <c r="G1739" t="n">
-        <v>7.71818828582764</v>
+        <v>7.71818876266479</v>
       </c>
       <c r="H1739" t="s">
         <v>8</v>
@@ -45609,7 +45609,7 @@
         <v>8.11999988555908</v>
       </c>
       <c r="G1740" t="n">
-        <v>7.71818828582764</v>
+        <v>7.71818876266479</v>
       </c>
       <c r="H1740" t="s">
         <v>8</v>
@@ -45739,7 +45739,7 @@
         <v>8.09000015258789</v>
       </c>
       <c r="G1745" t="n">
-        <v>7.68967342376709</v>
+        <v>7.68967294692993</v>
       </c>
       <c r="H1745" t="s">
         <v>8</v>
@@ -45765,7 +45765,7 @@
         <v>7.98999977111816</v>
       </c>
       <c r="G1746" t="n">
-        <v>7.59462118148804</v>
+        <v>7.5946216583252</v>
       </c>
       <c r="H1746" t="s">
         <v>8</v>
@@ -45791,7 +45791,7 @@
         <v>8.14000034332275</v>
       </c>
       <c r="G1747" t="n">
-        <v>7.73719882965088</v>
+        <v>7.73719930648804</v>
       </c>
       <c r="H1747" t="s">
         <v>8</v>
@@ -45895,7 +45895,7 @@
         <v>8.38000011444092</v>
       </c>
       <c r="G1751" t="n">
-        <v>7.96532297134399</v>
+        <v>7.96532249450684</v>
       </c>
       <c r="H1751" t="s">
         <v>8</v>
@@ -45921,7 +45921,7 @@
         <v>8.38000011444092</v>
       </c>
       <c r="G1752" t="n">
-        <v>7.96532297134399</v>
+        <v>7.96532249450684</v>
       </c>
       <c r="H1752" t="s">
         <v>8</v>
@@ -45947,7 +45947,7 @@
         <v>8.36999988555908</v>
       </c>
       <c r="G1753" t="n">
-        <v>7.95581722259521</v>
+        <v>7.95581674575806</v>
       </c>
       <c r="H1753" t="s">
         <v>8</v>
@@ -45973,7 +45973,7 @@
         <v>8.38000011444092</v>
       </c>
       <c r="G1754" t="n">
-        <v>7.96532297134399</v>
+        <v>7.96532249450684</v>
       </c>
       <c r="H1754" t="s">
         <v>8</v>
@@ -45999,7 +45999,7 @@
         <v>8.38000011444092</v>
       </c>
       <c r="G1755" t="n">
-        <v>7.96532297134399</v>
+        <v>7.96532249450684</v>
       </c>
       <c r="H1755" t="s">
         <v>8</v>
@@ -46025,7 +46025,7 @@
         <v>8.39999961853027</v>
       </c>
       <c r="G1756" t="n">
-        <v>7.98433303833008</v>
+        <v>7.98433208465576</v>
       </c>
       <c r="H1756" t="s">
         <v>8</v>
@@ -46051,7 +46051,7 @@
         <v>8.39999961853027</v>
       </c>
       <c r="G1757" t="n">
-        <v>7.98433303833008</v>
+        <v>7.98433208465576</v>
       </c>
       <c r="H1757" t="s">
         <v>8</v>
@@ -46103,7 +46103,7 @@
         <v>8.43000030517578</v>
       </c>
       <c r="G1759" t="n">
-        <v>8.01284885406494</v>
+        <v>8.01284790039062</v>
       </c>
       <c r="H1759" t="s">
         <v>8</v>
@@ -46129,7 +46129,7 @@
         <v>8.34000015258789</v>
       </c>
       <c r="G1760" t="n">
-        <v>7.92730236053467</v>
+        <v>7.92730188369751</v>
       </c>
       <c r="H1760" t="s">
         <v>8</v>
@@ -46155,7 +46155,7 @@
         <v>8.39000034332275</v>
       </c>
       <c r="G1761" t="n">
-        <v>7.97482824325562</v>
+        <v>7.97482776641846</v>
       </c>
       <c r="H1761" t="s">
         <v>8</v>
@@ -46181,7 +46181,7 @@
         <v>8.38000011444092</v>
       </c>
       <c r="G1762" t="n">
-        <v>7.96532297134399</v>
+        <v>7.96532249450684</v>
       </c>
       <c r="H1762" t="s">
         <v>8</v>
@@ -46207,7 +46207,7 @@
         <v>8.3100004196167</v>
       </c>
       <c r="G1763" t="n">
-        <v>7.89878702163696</v>
+        <v>7.8987865447998</v>
       </c>
       <c r="H1763" t="s">
         <v>8</v>
@@ -46233,7 +46233,7 @@
         <v>8.22000026702881</v>
       </c>
       <c r="G1764" t="n">
-        <v>7.81324005126953</v>
+        <v>7.81324052810669</v>
       </c>
       <c r="H1764" t="s">
         <v>8</v>
@@ -46259,7 +46259,7 @@
         <v>8.26000022888184</v>
       </c>
       <c r="G1765" t="n">
-        <v>7.85126066207886</v>
+        <v>7.85126161575317</v>
       </c>
       <c r="H1765" t="s">
         <v>8</v>
@@ -46285,7 +46285,7 @@
         <v>8.32999992370605</v>
       </c>
       <c r="G1766" t="n">
-        <v>7.91779708862305</v>
+        <v>7.91779661178589</v>
       </c>
       <c r="H1766" t="s">
         <v>8</v>
@@ -46311,7 +46311,7 @@
         <v>8.21000003814697</v>
       </c>
       <c r="G1767" t="n">
-        <v>7.80373477935791</v>
+        <v>7.80373525619507</v>
       </c>
       <c r="H1767" t="s">
         <v>8</v>
@@ -46337,7 +46337,7 @@
         <v>8.11999988555908</v>
       </c>
       <c r="G1768" t="n">
-        <v>7.71818828582764</v>
+        <v>7.71818876266479</v>
       </c>
       <c r="H1768" t="s">
         <v>8</v>
@@ -46363,7 +46363,7 @@
         <v>8.39000034332275</v>
       </c>
       <c r="G1769" t="n">
-        <v>7.97482824325562</v>
+        <v>7.97482776641846</v>
       </c>
       <c r="H1769" t="s">
         <v>8</v>
@@ -46415,7 +46415,7 @@
         <v>8.3100004196167</v>
       </c>
       <c r="G1771" t="n">
-        <v>7.89878702163696</v>
+        <v>7.8987865447998</v>
       </c>
       <c r="H1771" t="s">
         <v>8</v>
@@ -46597,7 +46597,7 @@
         <v>8.09000015258789</v>
       </c>
       <c r="G1778" t="n">
-        <v>7.68967342376709</v>
+        <v>7.68967294692993</v>
       </c>
       <c r="H1778" t="s">
         <v>8</v>
@@ -46883,7 +46883,7 @@
         <v>7.65999984741211</v>
       </c>
       <c r="G1789" t="n">
-        <v>7.28095149993896</v>
+        <v>7.28095102310181</v>
       </c>
       <c r="H1789" t="s">
         <v>8</v>
@@ -46909,7 +46909,7 @@
         <v>7.59999990463257</v>
       </c>
       <c r="G1790" t="n">
-        <v>7.22392082214355</v>
+        <v>7.22391986846924</v>
       </c>
       <c r="H1790" t="s">
         <v>8</v>
@@ -47013,7 +47013,7 @@
         <v>7.59999990463257</v>
       </c>
       <c r="G1794" t="n">
-        <v>7.22392082214355</v>
+        <v>7.22391986846924</v>
       </c>
       <c r="H1794" t="s">
         <v>8</v>
@@ -47065,7 +47065,7 @@
         <v>7.78000020980835</v>
       </c>
       <c r="G1796" t="n">
-        <v>7.39501333236694</v>
+        <v>7.3950138092041</v>
       </c>
       <c r="H1796" t="s">
         <v>8</v>
@@ -47117,7 +47117,7 @@
         <v>7.80000019073486</v>
       </c>
       <c r="G1798" t="n">
-        <v>7.41402387619019</v>
+        <v>7.41402339935303</v>
       </c>
       <c r="H1798" t="s">
         <v>8</v>
@@ -47143,7 +47143,7 @@
         <v>7.73999977111816</v>
       </c>
       <c r="G1799" t="n">
-        <v>7.35699224472046</v>
+        <v>7.35699272155762</v>
       </c>
       <c r="H1799" t="s">
         <v>8</v>
@@ -47169,7 +47169,7 @@
         <v>7.96999979019165</v>
       </c>
       <c r="G1800" t="n">
-        <v>7.57561111450195</v>
+        <v>7.57561063766479</v>
       </c>
       <c r="H1800" t="s">
         <v>8</v>
@@ -47247,7 +47247,7 @@
         <v>7.98000001907349</v>
       </c>
       <c r="G1803" t="n">
-        <v>7.58511638641357</v>
+        <v>7.58511590957642</v>
       </c>
       <c r="H1803" t="s">
         <v>8</v>
@@ -47325,7 +47325,7 @@
         <v>7.92999982833862</v>
       </c>
       <c r="G1806" t="n">
-        <v>7.53759050369263</v>
+        <v>7.53759002685547</v>
       </c>
       <c r="H1806" t="s">
         <v>8</v>
@@ -47351,7 +47351,7 @@
         <v>7.78000020980835</v>
       </c>
       <c r="G1807" t="n">
-        <v>7.39501333236694</v>
+        <v>7.3950138092041</v>
       </c>
       <c r="H1807" t="s">
         <v>8</v>
@@ -47403,7 +47403,7 @@
         <v>7.8899998664856</v>
       </c>
       <c r="G1809" t="n">
-        <v>7.49957036972046</v>
+        <v>7.4995698928833</v>
       </c>
       <c r="H1809" t="s">
         <v>8</v>
@@ -47429,7 +47429,7 @@
         <v>7.94000005722046</v>
       </c>
       <c r="G1810" t="n">
-        <v>7.54709577560425</v>
+        <v>7.54709529876709</v>
       </c>
       <c r="H1810" t="s">
         <v>8</v>
@@ -47455,7 +47455,7 @@
         <v>7.92999982833862</v>
       </c>
       <c r="G1811" t="n">
-        <v>7.53759050369263</v>
+        <v>7.53759002685547</v>
       </c>
       <c r="H1811" t="s">
         <v>8</v>
@@ -47533,7 +47533,7 @@
         <v>7.94000005722046</v>
       </c>
       <c r="G1814" t="n">
-        <v>7.54709577560425</v>
+        <v>7.54709529876709</v>
       </c>
       <c r="H1814" t="s">
         <v>8</v>
@@ -47585,7 +47585,7 @@
         <v>8.21000003814697</v>
       </c>
       <c r="G1816" t="n">
-        <v>7.80373477935791</v>
+        <v>7.80373525619507</v>
       </c>
       <c r="H1816" t="s">
         <v>8</v>
@@ -47637,7 +47637,7 @@
         <v>8.34000015258789</v>
       </c>
       <c r="G1818" t="n">
-        <v>7.92730236053467</v>
+        <v>7.92730188369751</v>
       </c>
       <c r="H1818" t="s">
         <v>8</v>
@@ -47663,7 +47663,7 @@
         <v>8.36999988555908</v>
       </c>
       <c r="G1819" t="n">
-        <v>7.95581722259521</v>
+        <v>7.95581674575806</v>
       </c>
       <c r="H1819" t="s">
         <v>8</v>
@@ -47689,7 +47689,7 @@
         <v>8.23999977111816</v>
       </c>
       <c r="G1820" t="n">
-        <v>7.83224964141846</v>
+        <v>7.83225011825562</v>
       </c>
       <c r="H1820" t="s">
         <v>8</v>
@@ -47767,7 +47767,7 @@
         <v>8.28999996185303</v>
       </c>
       <c r="G1823" t="n">
-        <v>7.87977647781372</v>
+        <v>7.87977695465088</v>
       </c>
       <c r="H1823" t="s">
         <v>8</v>
@@ -47793,7 +47793,7 @@
         <v>8.36999988555908</v>
       </c>
       <c r="G1824" t="n">
-        <v>7.95581722259521</v>
+        <v>7.95581674575806</v>
       </c>
       <c r="H1824" t="s">
         <v>8</v>
@@ -47897,7 +47897,7 @@
         <v>8.47000026702881</v>
       </c>
       <c r="G1828" t="n">
-        <v>8.05086898803711</v>
+        <v>8.05086994171143</v>
       </c>
       <c r="H1828" t="s">
         <v>8</v>
@@ -47923,7 +47923,7 @@
         <v>8.39999961853027</v>
       </c>
       <c r="G1829" t="n">
-        <v>7.98433303833008</v>
+        <v>7.98433208465576</v>
       </c>
       <c r="H1829" t="s">
         <v>8</v>
@@ -47975,7 +47975,7 @@
         <v>8.73999977111816</v>
       </c>
       <c r="G1831" t="n">
-        <v>8.30750751495361</v>
+        <v>8.30750846862793</v>
       </c>
       <c r="H1831" t="s">
         <v>8</v>
@@ -48027,7 +48027,7 @@
         <v>8.73999977111816</v>
       </c>
       <c r="G1833" t="n">
-        <v>8.30750751495361</v>
+        <v>8.30750846862793</v>
       </c>
       <c r="H1833" t="s">
         <v>8</v>
@@ -48105,7 +48105,7 @@
         <v>8.5600004196167</v>
       </c>
       <c r="G1836" t="n">
-        <v>8.13641548156738</v>
+        <v>8.1364164352417</v>
       </c>
       <c r="H1836" t="s">
         <v>8</v>
@@ -48209,7 +48209,7 @@
         <v>8.9399995803833</v>
       </c>
       <c r="G1840" t="n">
-        <v>8.4976110458374</v>
+        <v>8.49761009216309</v>
       </c>
       <c r="H1840" t="s">
         <v>8</v>
@@ -48235,7 +48235,7 @@
         <v>8.9399995803833</v>
       </c>
       <c r="G1841" t="n">
-        <v>8.4976110458374</v>
+        <v>8.49761009216309</v>
       </c>
       <c r="H1841" t="s">
         <v>8</v>
@@ -48261,7 +48261,7 @@
         <v>8.89999961853027</v>
       </c>
       <c r="G1842" t="n">
-        <v>8.45959091186523</v>
+        <v>8.45958995819092</v>
       </c>
       <c r="H1842" t="s">
         <v>8</v>
@@ -48287,7 +48287,7 @@
         <v>8.80000019073486</v>
       </c>
       <c r="G1843" t="n">
-        <v>8.36453914642334</v>
+        <v>8.36454010009766</v>
       </c>
       <c r="H1843" t="s">
         <v>8</v>
@@ -48339,7 +48339,7 @@
         <v>8.71000003814697</v>
       </c>
       <c r="G1845" t="n">
-        <v>8.27899265289307</v>
+        <v>8.27899360656738</v>
       </c>
       <c r="H1845" t="s">
         <v>8</v>
@@ -48443,7 +48443,7 @@
         <v>8.80000019073486</v>
       </c>
       <c r="G1849" t="n">
-        <v>8.36453914642334</v>
+        <v>8.36454010009766</v>
       </c>
       <c r="H1849" t="s">
         <v>8</v>
@@ -48521,7 +48521,7 @@
         <v>9.0600004196167</v>
       </c>
       <c r="G1852" t="n">
-        <v>8.61167335510254</v>
+        <v>8.61167430877686</v>
       </c>
       <c r="H1852" t="s">
         <v>8</v>
@@ -48573,7 +48573,7 @@
         <v>9.05000019073486</v>
       </c>
       <c r="G1854" t="n">
-        <v>8.60216808319092</v>
+        <v>8.60216903686523</v>
       </c>
       <c r="H1854" t="s">
         <v>8</v>
@@ -48599,7 +48599,7 @@
         <v>9</v>
       </c>
       <c r="G1855" t="n">
-        <v>8.55464172363281</v>
+        <v>8.55464267730713</v>
       </c>
       <c r="H1855" t="s">
         <v>8</v>
@@ -48651,7 +48651,7 @@
         <v>8.86999988555908</v>
       </c>
       <c r="G1857" t="n">
-        <v>8.43107509613037</v>
+        <v>8.43107604980469</v>
       </c>
       <c r="H1857" t="s">
         <v>8</v>
@@ -48677,7 +48677,7 @@
         <v>8.9399995803833</v>
       </c>
       <c r="G1858" t="n">
-        <v>8.4976110458374</v>
+        <v>8.49761009216309</v>
       </c>
       <c r="H1858" t="s">
         <v>8</v>
@@ -48729,7 +48729,7 @@
         <v>8.89999961853027</v>
       </c>
       <c r="G1860" t="n">
-        <v>8.45959091186523</v>
+        <v>8.45958995819092</v>
       </c>
       <c r="H1860" t="s">
         <v>8</v>
@@ -48755,7 +48755,7 @@
         <v>8.89999961853027</v>
       </c>
       <c r="G1861" t="n">
-        <v>8.45959091186523</v>
+        <v>8.45958995819092</v>
       </c>
       <c r="H1861" t="s">
         <v>8</v>
@@ -48781,7 +48781,7 @@
         <v>8.9399995803833</v>
       </c>
       <c r="G1862" t="n">
-        <v>8.4976110458374</v>
+        <v>8.49761009216309</v>
       </c>
       <c r="H1862" t="s">
         <v>8</v>
@@ -48859,7 +48859,7 @@
         <v>8.8100004196167</v>
       </c>
       <c r="G1865" t="n">
-        <v>8.37404441833496</v>
+        <v>8.37404537200928</v>
       </c>
       <c r="H1865" t="s">
         <v>8</v>
@@ -48911,7 +48911,7 @@
         <v>8.64000034332275</v>
       </c>
       <c r="G1867" t="n">
-        <v>8.21245765686035</v>
+        <v>8.21245670318604</v>
       </c>
       <c r="H1867" t="s">
         <v>8</v>
@@ -48937,7 +48937,7 @@
         <v>8.64999961853027</v>
       </c>
       <c r="G1868" t="n">
-        <v>8.22196197509766</v>
+        <v>8.22196102142334</v>
       </c>
       <c r="H1868" t="s">
         <v>8</v>
@@ -48963,7 +48963,7 @@
         <v>8.64999961853027</v>
       </c>
       <c r="G1869" t="n">
-        <v>8.22196197509766</v>
+        <v>8.22196102142334</v>
       </c>
       <c r="H1869" t="s">
         <v>8</v>
@@ -49015,7 +49015,7 @@
         <v>8.93000030517578</v>
       </c>
       <c r="G1871" t="n">
-        <v>8.4881067276001</v>
+        <v>8.48810577392578</v>
       </c>
       <c r="H1871" t="s">
         <v>8</v>
@@ -49041,7 +49041,7 @@
         <v>8.89999961853027</v>
       </c>
       <c r="G1872" t="n">
-        <v>8.45959091186523</v>
+        <v>8.45958995819092</v>
       </c>
       <c r="H1872" t="s">
         <v>8</v>
@@ -49067,7 +49067,7 @@
         <v>8.80000019073486</v>
       </c>
       <c r="G1873" t="n">
-        <v>8.36453914642334</v>
+        <v>8.36454010009766</v>
       </c>
       <c r="H1873" t="s">
         <v>8</v>
@@ -49093,7 +49093,7 @@
         <v>8.60999965667725</v>
       </c>
       <c r="G1874" t="n">
-        <v>8.18394184112549</v>
+        <v>8.18394088745117</v>
       </c>
       <c r="H1874" t="s">
         <v>8</v>
@@ -49145,7 +49145,7 @@
         <v>8.59000015258789</v>
       </c>
       <c r="G1876" t="n">
-        <v>8.16493129730225</v>
+        <v>8.16493034362793</v>
       </c>
       <c r="H1876" t="s">
         <v>8</v>
@@ -49171,7 +49171,7 @@
         <v>8.44999980926514</v>
       </c>
       <c r="G1877" t="n">
-        <v>8.03185844421387</v>
+        <v>8.03185939788818</v>
       </c>
       <c r="H1877" t="s">
         <v>8</v>
@@ -49197,7 +49197,7 @@
         <v>8.35999965667725</v>
       </c>
       <c r="G1878" t="n">
-        <v>7.94631290435791</v>
+        <v>7.94631147384644</v>
       </c>
       <c r="H1878" t="s">
         <v>8</v>
@@ -49223,7 +49223,7 @@
         <v>8.39000034332275</v>
       </c>
       <c r="G1879" t="n">
-        <v>7.97482824325562</v>
+        <v>7.97482776641846</v>
       </c>
       <c r="H1879" t="s">
         <v>8</v>
@@ -49249,7 +49249,7 @@
         <v>8.39000034332275</v>
       </c>
       <c r="G1880" t="n">
-        <v>7.97482824325562</v>
+        <v>7.97482776641846</v>
       </c>
       <c r="H1880" t="s">
         <v>8</v>
@@ -49301,7 +49301,7 @@
         <v>8.22000026702881</v>
       </c>
       <c r="G1882" t="n">
-        <v>7.81324005126953</v>
+        <v>7.81324052810669</v>
       </c>
       <c r="H1882" t="s">
         <v>8</v>
@@ -49353,7 +49353,7 @@
         <v>8.25</v>
       </c>
       <c r="G1884" t="n">
-        <v>7.84175539016724</v>
+        <v>7.84175586700439</v>
       </c>
       <c r="H1884" t="s">
         <v>8</v>
@@ -49379,7 +49379,7 @@
         <v>8.26000022888184</v>
       </c>
       <c r="G1885" t="n">
-        <v>7.85126066207886</v>
+        <v>7.85126161575317</v>
       </c>
       <c r="H1885" t="s">
         <v>8</v>
@@ -49431,7 +49431,7 @@
         <v>8.22000026702881</v>
       </c>
       <c r="G1887" t="n">
-        <v>7.81324005126953</v>
+        <v>7.81324052810669</v>
       </c>
       <c r="H1887" t="s">
         <v>8</v>
@@ -49483,7 +49483,7 @@
         <v>8.32999992370605</v>
       </c>
       <c r="G1889" t="n">
-        <v>7.91779708862305</v>
+        <v>7.91779661178589</v>
       </c>
       <c r="H1889" t="s">
         <v>8</v>
@@ -49509,7 +49509,7 @@
         <v>8.38000011444092</v>
       </c>
       <c r="G1890" t="n">
-        <v>7.96532297134399</v>
+        <v>7.96532249450684</v>
       </c>
       <c r="H1890" t="s">
         <v>8</v>
@@ -49535,7 +49535,7 @@
         <v>8.38000011444092</v>
       </c>
       <c r="G1891" t="n">
-        <v>7.96532297134399</v>
+        <v>7.96532249450684</v>
       </c>
       <c r="H1891" t="s">
         <v>8</v>
@@ -49561,7 +49561,7 @@
         <v>8.5600004196167</v>
       </c>
       <c r="G1892" t="n">
-        <v>8.13641548156738</v>
+        <v>8.1364164352417</v>
       </c>
       <c r="H1892" t="s">
         <v>8</v>
@@ -49613,7 +49613,7 @@
         <v>8.34000015258789</v>
       </c>
       <c r="G1894" t="n">
-        <v>7.92730236053467</v>
+        <v>7.92730188369751</v>
       </c>
       <c r="H1894" t="s">
         <v>8</v>
@@ -49639,7 +49639,7 @@
         <v>8.30000019073486</v>
       </c>
       <c r="G1895" t="n">
-        <v>7.8892822265625</v>
+        <v>7.88928127288818</v>
       </c>
       <c r="H1895" t="s">
         <v>8</v>
@@ -49665,7 +49665,7 @@
         <v>8.30000019073486</v>
       </c>
       <c r="G1896" t="n">
-        <v>7.8892822265625</v>
+        <v>7.88928127288818</v>
       </c>
       <c r="H1896" t="s">
         <v>8</v>
@@ -49691,7 +49691,7 @@
         <v>8.30000019073486</v>
       </c>
       <c r="G1897" t="n">
-        <v>7.8892822265625</v>
+        <v>7.88928127288818</v>
       </c>
       <c r="H1897" t="s">
         <v>8</v>
@@ -49717,7 +49717,7 @@
         <v>8.31999969482422</v>
       </c>
       <c r="G1898" t="n">
-        <v>7.90829133987427</v>
+        <v>7.90829086303711</v>
       </c>
       <c r="H1898" t="s">
         <v>8</v>
@@ -49743,7 +49743,7 @@
         <v>8.38000011444092</v>
       </c>
       <c r="G1899" t="n">
-        <v>7.96532297134399</v>
+        <v>7.96532249450684</v>
       </c>
       <c r="H1899" t="s">
         <v>8</v>
@@ -49769,7 +49769,7 @@
         <v>8.31999969482422</v>
       </c>
       <c r="G1900" t="n">
-        <v>7.90829133987427</v>
+        <v>7.90829086303711</v>
       </c>
       <c r="H1900" t="s">
         <v>8</v>
@@ -49795,7 +49795,7 @@
         <v>8.35999965667725</v>
       </c>
       <c r="G1901" t="n">
-        <v>7.94631290435791</v>
+        <v>7.94631147384644</v>
       </c>
       <c r="H1901" t="s">
         <v>8</v>
@@ -49821,7 +49821,7 @@
         <v>8.15999984741211</v>
       </c>
       <c r="G1902" t="n">
-        <v>7.75620889663696</v>
+        <v>7.75620937347412</v>
       </c>
       <c r="H1902" t="s">
         <v>8</v>
@@ -49847,7 +49847,7 @@
         <v>8.11999988555908</v>
       </c>
       <c r="G1903" t="n">
-        <v>7.71818828582764</v>
+        <v>7.71818876266479</v>
       </c>
       <c r="H1903" t="s">
         <v>8</v>
@@ -49899,7 +49899,7 @@
         <v>8.34000015258789</v>
       </c>
       <c r="G1905" t="n">
-        <v>7.92730236053467</v>
+        <v>7.92730188369751</v>
       </c>
       <c r="H1905" t="s">
         <v>8</v>
@@ -49925,7 +49925,7 @@
         <v>8.34000015258789</v>
       </c>
       <c r="G1906" t="n">
-        <v>7.92730236053467</v>
+        <v>7.92730188369751</v>
       </c>
       <c r="H1906" t="s">
         <v>8</v>
@@ -49951,7 +49951,7 @@
         <v>8.35999965667725</v>
       </c>
       <c r="G1907" t="n">
-        <v>7.94631290435791</v>
+        <v>7.94631147384644</v>
       </c>
       <c r="H1907" t="s">
         <v>8</v>
@@ -49977,7 +49977,7 @@
         <v>8.39999961853027</v>
       </c>
       <c r="G1908" t="n">
-        <v>7.98433303833008</v>
+        <v>7.98433208465576</v>
       </c>
       <c r="H1908" t="s">
         <v>8</v>
@@ -50003,7 +50003,7 @@
         <v>8.31999969482422</v>
       </c>
       <c r="G1909" t="n">
-        <v>7.90829133987427</v>
+        <v>7.90829086303711</v>
       </c>
       <c r="H1909" t="s">
         <v>8</v>
@@ -50055,7 +50055,7 @@
         <v>8.38000011444092</v>
       </c>
       <c r="G1911" t="n">
-        <v>7.96532297134399</v>
+        <v>7.96532249450684</v>
       </c>
       <c r="H1911" t="s">
         <v>8</v>
@@ -50081,7 +50081,7 @@
         <v>8.35999965667725</v>
       </c>
       <c r="G1912" t="n">
-        <v>7.94631290435791</v>
+        <v>7.94631147384644</v>
       </c>
       <c r="H1912" t="s">
         <v>8</v>
@@ -50107,7 +50107,7 @@
         <v>8.35999965667725</v>
       </c>
       <c r="G1913" t="n">
-        <v>7.94631290435791</v>
+        <v>7.94631147384644</v>
       </c>
       <c r="H1913" t="s">
         <v>8</v>
@@ -50133,7 +50133,7 @@
         <v>8.39999961853027</v>
       </c>
       <c r="G1914" t="n">
-        <v>7.98433303833008</v>
+        <v>7.98433208465576</v>
       </c>
       <c r="H1914" t="s">
         <v>8</v>
@@ -50341,7 +50341,7 @@
         <v>8.30000019073486</v>
       </c>
       <c r="G1922" t="n">
-        <v>7.8892822265625</v>
+        <v>7.88928127288818</v>
       </c>
       <c r="H1922" t="s">
         <v>8</v>
@@ -50497,7 +50497,7 @@
         <v>8.5600004196167</v>
       </c>
       <c r="G1928" t="n">
-        <v>8.13641548156738</v>
+        <v>8.1364164352417</v>
       </c>
       <c r="H1928" t="s">
         <v>8</v>
@@ -50549,7 +50549,7 @@
         <v>8.80000019073486</v>
       </c>
       <c r="G1930" t="n">
-        <v>8.36453914642334</v>
+        <v>8.36454010009766</v>
       </c>
       <c r="H1930" t="s">
         <v>8</v>
@@ -50575,7 +50575,7 @@
         <v>8.80000019073486</v>
       </c>
       <c r="G1931" t="n">
-        <v>8.36453914642334</v>
+        <v>8.36454010009766</v>
       </c>
       <c r="H1931" t="s">
         <v>8</v>
@@ -50601,7 +50601,7 @@
         <v>8.80000019073486</v>
       </c>
       <c r="G1932" t="n">
-        <v>8.36453914642334</v>
+        <v>8.36454010009766</v>
       </c>
       <c r="H1932" t="s">
         <v>8</v>
@@ -50627,7 +50627,7 @@
         <v>8.73999977111816</v>
       </c>
       <c r="G1933" t="n">
-        <v>8.30750751495361</v>
+        <v>8.30750846862793</v>
       </c>
       <c r="H1933" t="s">
         <v>8</v>
@@ -50679,7 +50679,7 @@
         <v>8.73999977111816</v>
       </c>
       <c r="G1935" t="n">
-        <v>8.30750751495361</v>
+        <v>8.30750846862793</v>
       </c>
       <c r="H1935" t="s">
         <v>8</v>
@@ -50705,7 +50705,7 @@
         <v>8.73999977111816</v>
       </c>
       <c r="G1936" t="n">
-        <v>8.30750751495361</v>
+        <v>8.30750846862793</v>
       </c>
       <c r="H1936" t="s">
         <v>8</v>
@@ -65970,6 +65970,32 @@
         <v>7.26000022888184</v>
       </c>
       <c r="H2523" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="2524">
+      <c r="A2524" s="1" t="n">
+        <v>46289.2916666667</v>
+      </c>
+      <c r="B2524" t="n">
+        <v>18314</v>
+      </c>
+      <c r="C2524" t="n">
+        <v>7.30000019073486</v>
+      </c>
+      <c r="D2524" t="n">
+        <v>7.15999984741211</v>
+      </c>
+      <c r="E2524" t="n">
+        <v>7.26000022888184</v>
+      </c>
+      <c r="F2524" t="n">
+        <v>7.17999982833862</v>
+      </c>
+      <c r="G2524" t="n">
+        <v>7.17999982833862</v>
+      </c>
+      <c r="H2524" t="s">
         <v>8</v>
       </c>
     </row>

--- a/data/FF.MI.xlsx
+++ b/data/FF.MI.xlsx
@@ -58578,8 +58578,31 @@
       <c r="E2531" t="n">
         <v>6.8600001335144</v>
       </c>
-      <c r="F2531"/>
+      <c r="F2531" t="n">
+        <v>6.90000009536743</v>
+      </c>
       <c r="G2531" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2532">
+      <c r="A2532" s="1" t="n">
+        <v>46301.2916666667</v>
+      </c>
+      <c r="B2532" t="n">
+        <v>32797</v>
+      </c>
+      <c r="C2532" t="n">
+        <v>7.1399998664856</v>
+      </c>
+      <c r="D2532" t="n">
+        <v>6.88000011444092</v>
+      </c>
+      <c r="E2532" t="n">
+        <v>6.88000011444092</v>
+      </c>
+      <c r="F2532"/>
+      <c r="G2532" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/FF.MI.xlsx
+++ b/data/FF.MI.xlsx
@@ -58601,8 +58601,31 @@
       <c r="E2532" t="n">
         <v>6.88000011444092</v>
       </c>
-      <c r="F2532"/>
+      <c r="F2532" t="n">
+        <v>7.01999998092651</v>
+      </c>
       <c r="G2532" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2533">
+      <c r="A2533" s="1" t="n">
+        <v>46302.2916666667</v>
+      </c>
+      <c r="B2533" t="n">
+        <v>14528</v>
+      </c>
+      <c r="C2533" t="n">
+        <v>7.01999998092651</v>
+      </c>
+      <c r="D2533" t="n">
+        <v>6.80000019073486</v>
+      </c>
+      <c r="E2533" t="n">
+        <v>7</v>
+      </c>
+      <c r="F2533"/>
+      <c r="G2533" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/FF.MI.xlsx
+++ b/data/FF.MI.xlsx
@@ -58624,8 +58624,31 @@
       <c r="E2533" t="n">
         <v>7</v>
       </c>
-      <c r="F2533"/>
+      <c r="F2533" t="n">
+        <v>6.94000005722046</v>
+      </c>
       <c r="G2533" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2534">
+      <c r="A2534" s="1" t="n">
+        <v>46303.2916666667</v>
+      </c>
+      <c r="B2534" t="n">
+        <v>25337</v>
+      </c>
+      <c r="C2534" t="n">
+        <v>7.03999996185303</v>
+      </c>
+      <c r="D2534" t="n">
+        <v>6.69999980926514</v>
+      </c>
+      <c r="E2534" t="n">
+        <v>7.03999996185303</v>
+      </c>
+      <c r="F2534"/>
+      <c r="G2534" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/FF.MI.xlsx
+++ b/data/FF.MI.xlsx
@@ -58647,8 +58647,31 @@
       <c r="E2534" t="n">
         <v>7.03999996185303</v>
       </c>
-      <c r="F2534"/>
+      <c r="F2534" t="n">
+        <v>6.76000022888184</v>
+      </c>
       <c r="G2534" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2535">
+      <c r="A2535" s="1" t="n">
+        <v>46304.2916666667</v>
+      </c>
+      <c r="B2535" t="n">
+        <v>22531</v>
+      </c>
+      <c r="C2535" t="n">
+        <v>6.90000009536743</v>
+      </c>
+      <c r="D2535" t="n">
+        <v>6.67999982833862</v>
+      </c>
+      <c r="E2535" t="n">
+        <v>6.78000020980835</v>
+      </c>
+      <c r="F2535"/>
+      <c r="G2535" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/FF.MI.xlsx
+++ b/data/FF.MI.xlsx
@@ -58677,6 +58677,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="2536">
+      <c r="A2536" s="1" t="n">
+        <v>46307.2916666667</v>
+      </c>
+      <c r="B2536" t="n">
+        <v>43919</v>
+      </c>
+      <c r="C2536" t="n">
+        <v>6.80000019073486</v>
+      </c>
+      <c r="D2536" t="n">
+        <v>6.51999998092651</v>
+      </c>
+      <c r="E2536" t="n">
+        <v>6.65999984741211</v>
+      </c>
+      <c r="F2536" t="n">
+        <v>6.61999988555908</v>
+      </c>
+      <c r="G2536" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/FF.MI.xlsx
+++ b/data/FF.MI.xlsx
@@ -456,7 +456,7 @@
         <v>9.89999961853027</v>
       </c>
       <c r="G3" t="n">
-        <v>8.83270931243896</v>
+        <v>8.83271026611328</v>
       </c>
       <c r="H3" t="n">
         <v>2600</v>
@@ -804,7 +804,7 @@
         <v>10.1899995803833</v>
       </c>
       <c r="G15" t="n">
-        <v>9.09144592285156</v>
+        <v>9.09144496917725</v>
       </c>
       <c r="H15" t="n">
         <v>200</v>
@@ -833,7 +833,7 @@
         <v>10.1899995803833</v>
       </c>
       <c r="G16" t="n">
-        <v>9.09144592285156</v>
+        <v>9.09144496917725</v>
       </c>
       <c r="H16" t="n">
         <v>0</v>
@@ -1036,7 +1036,7 @@
         <v>9.86499977111816</v>
       </c>
       <c r="G23" t="n">
-        <v>8.80148410797119</v>
+        <v>8.80148315429688</v>
       </c>
       <c r="H23" t="n">
         <v>1000</v>
@@ -1065,7 +1065,7 @@
         <v>9.86499977111816</v>
       </c>
       <c r="G24" t="n">
-        <v>8.80148410797119</v>
+        <v>8.80148315429688</v>
       </c>
       <c r="H24" t="n">
         <v>0</v>
@@ -1094,7 +1094,7 @@
         <v>9.86499977111816</v>
       </c>
       <c r="G25" t="n">
-        <v>8.80148410797119</v>
+        <v>8.80148315429688</v>
       </c>
       <c r="H25" t="n">
         <v>0</v>
@@ -1529,7 +1529,7 @@
         <v>9.80000019073486</v>
       </c>
       <c r="G40" t="n">
-        <v>8.74349021911621</v>
+        <v>8.74349117279053</v>
       </c>
       <c r="H40" t="n">
         <v>200</v>
@@ -1558,7 +1558,7 @@
         <v>9.80000019073486</v>
       </c>
       <c r="G41" t="n">
-        <v>8.74349021911621</v>
+        <v>8.74349117279053</v>
       </c>
       <c r="H41" t="n">
         <v>21400</v>
@@ -1587,7 +1587,7 @@
         <v>9.80000019073486</v>
       </c>
       <c r="G42" t="n">
-        <v>8.74349021911621</v>
+        <v>8.74349117279053</v>
       </c>
       <c r="H42" t="n">
         <v>0</v>
@@ -1616,7 +1616,7 @@
         <v>9.80000019073486</v>
       </c>
       <c r="G43" t="n">
-        <v>8.74349021911621</v>
+        <v>8.74349117279053</v>
       </c>
       <c r="H43" t="n">
         <v>0</v>
@@ -1645,7 +1645,7 @@
         <v>9.80000019073486</v>
       </c>
       <c r="G44" t="n">
-        <v>8.74349021911621</v>
+        <v>8.74349117279053</v>
       </c>
       <c r="H44" t="n">
         <v>0</v>
@@ -1674,7 +1674,7 @@
         <v>9.80000019073486</v>
       </c>
       <c r="G45" t="n">
-        <v>8.74349021911621</v>
+        <v>8.74349117279053</v>
       </c>
       <c r="H45" t="n">
         <v>0</v>
@@ -1703,7 +1703,7 @@
         <v>9.80000019073486</v>
       </c>
       <c r="G46" t="n">
-        <v>8.74349021911621</v>
+        <v>8.74349117279053</v>
       </c>
       <c r="H46" t="n">
         <v>400</v>
@@ -1732,7 +1732,7 @@
         <v>9.80000019073486</v>
       </c>
       <c r="G47" t="n">
-        <v>8.74349021911621</v>
+        <v>8.74349117279053</v>
       </c>
       <c r="H47" t="n">
         <v>0</v>
@@ -1761,7 +1761,7 @@
         <v>9.80000019073486</v>
       </c>
       <c r="G48" t="n">
-        <v>8.74349021911621</v>
+        <v>8.74349117279053</v>
       </c>
       <c r="H48" t="n">
         <v>0</v>
@@ -1848,7 +1848,7 @@
         <v>9.80000019073486</v>
       </c>
       <c r="G51" t="n">
-        <v>8.74349021911621</v>
+        <v>8.74349117279053</v>
       </c>
       <c r="H51" t="n">
         <v>400</v>
@@ -1877,7 +1877,7 @@
         <v>9.80000019073486</v>
       </c>
       <c r="G52" t="n">
-        <v>8.74349021911621</v>
+        <v>8.74349117279053</v>
       </c>
       <c r="H52" t="n">
         <v>0</v>
@@ -2080,7 +2080,7 @@
         <v>9.80000019073486</v>
       </c>
       <c r="G59" t="n">
-        <v>8.74349021911621</v>
+        <v>8.74349117279053</v>
       </c>
       <c r="H59" t="n">
         <v>200</v>
@@ -2109,7 +2109,7 @@
         <v>9.80000019073486</v>
       </c>
       <c r="G60" t="n">
-        <v>8.74349021911621</v>
+        <v>8.74349117279053</v>
       </c>
       <c r="H60" t="n">
         <v>0</v>
@@ -2138,7 +2138,7 @@
         <v>9.80000019073486</v>
       </c>
       <c r="G61" t="n">
-        <v>8.74349021911621</v>
+        <v>8.74349117279053</v>
       </c>
       <c r="H61" t="n">
         <v>0</v>
@@ -2283,7 +2283,7 @@
         <v>9.76000022888184</v>
       </c>
       <c r="G66" t="n">
-        <v>8.70780372619629</v>
+        <v>8.70780467987061</v>
       </c>
       <c r="H66" t="n">
         <v>200</v>
@@ -2312,7 +2312,7 @@
         <v>9.76000022888184</v>
       </c>
       <c r="G67" t="n">
-        <v>8.70780372619629</v>
+        <v>8.70780467987061</v>
       </c>
       <c r="H67" t="n">
         <v>0</v>
@@ -2341,7 +2341,7 @@
         <v>9.77999973297119</v>
       </c>
       <c r="G68" t="n">
-        <v>8.72564601898193</v>
+        <v>8.72564697265625</v>
       </c>
       <c r="H68" t="n">
         <v>200</v>
@@ -2370,7 +2370,7 @@
         <v>9.77999973297119</v>
       </c>
       <c r="G69" t="n">
-        <v>8.72564601898193</v>
+        <v>8.72564697265625</v>
       </c>
       <c r="H69" t="n">
         <v>200</v>
@@ -2399,7 +2399,7 @@
         <v>9.77999973297119</v>
       </c>
       <c r="G70" t="n">
-        <v>8.72564601898193</v>
+        <v>8.72564697265625</v>
       </c>
       <c r="H70" t="n">
         <v>0</v>
@@ -2863,7 +2863,7 @@
         <v>9.97000026702881</v>
       </c>
       <c r="G86" t="n">
-        <v>8.89516448974609</v>
+        <v>8.89516353607178</v>
       </c>
       <c r="H86" t="n">
         <v>600</v>
@@ -2892,7 +2892,7 @@
         <v>9.97000026702881</v>
       </c>
       <c r="G87" t="n">
-        <v>8.89516448974609</v>
+        <v>8.89516353607178</v>
       </c>
       <c r="H87" t="n">
         <v>0</v>
@@ -2921,7 +2921,7 @@
         <v>9.97000026702881</v>
       </c>
       <c r="G88" t="n">
-        <v>8.89516448974609</v>
+        <v>8.89516353607178</v>
       </c>
       <c r="H88" t="n">
         <v>0</v>
@@ -2950,7 +2950,7 @@
         <v>9.97000026702881</v>
       </c>
       <c r="G89" t="n">
-        <v>8.89516448974609</v>
+        <v>8.89516353607178</v>
       </c>
       <c r="H89" t="n">
         <v>0</v>
@@ -2979,7 +2979,7 @@
         <v>9.97000026702881</v>
       </c>
       <c r="G90" t="n">
-        <v>8.89516448974609</v>
+        <v>8.89516353607178</v>
       </c>
       <c r="H90" t="n">
         <v>0</v>
@@ -3008,7 +3008,7 @@
         <v>9.97000026702881</v>
       </c>
       <c r="G91" t="n">
-        <v>8.89516448974609</v>
+        <v>8.89516353607178</v>
       </c>
       <c r="H91" t="n">
         <v>0</v>
@@ -3037,7 +3037,7 @@
         <v>9.97000026702881</v>
       </c>
       <c r="G92" t="n">
-        <v>8.89516448974609</v>
+        <v>8.89516353607178</v>
       </c>
       <c r="H92" t="n">
         <v>0</v>
@@ -3443,7 +3443,7 @@
         <v>10.039999961853</v>
       </c>
       <c r="G106" t="n">
-        <v>8.95761680603027</v>
+        <v>8.95761871337891</v>
       </c>
       <c r="H106" t="n">
         <v>600</v>
@@ -3472,7 +3472,7 @@
         <v>10.039999961853</v>
       </c>
       <c r="G107" t="n">
-        <v>8.95761680603027</v>
+        <v>8.95761871337891</v>
       </c>
       <c r="H107" t="n">
         <v>0</v>
@@ -3501,7 +3501,7 @@
         <v>10.039999961853</v>
       </c>
       <c r="G108" t="n">
-        <v>8.95761680603027</v>
+        <v>8.95761871337891</v>
       </c>
       <c r="H108" t="n">
         <v>0</v>
@@ -3704,7 +3704,7 @@
         <v>9.88000011444092</v>
       </c>
       <c r="G115" t="n">
-        <v>8.81486701965332</v>
+        <v>8.814866065979</v>
       </c>
       <c r="H115" t="n">
         <v>400</v>
@@ -3733,7 +3733,7 @@
         <v>9.88000011444092</v>
       </c>
       <c r="G116" t="n">
-        <v>8.81486701965332</v>
+        <v>8.814866065979</v>
       </c>
       <c r="H116" t="n">
         <v>4400</v>
@@ -3820,7 +3820,7 @@
         <v>9.88000011444092</v>
       </c>
       <c r="G119" t="n">
-        <v>8.81486701965332</v>
+        <v>8.814866065979</v>
       </c>
       <c r="H119" t="n">
         <v>1000</v>
@@ -3849,7 +3849,7 @@
         <v>9.88000011444092</v>
       </c>
       <c r="G120" t="n">
-        <v>8.81486701965332</v>
+        <v>8.814866065979</v>
       </c>
       <c r="H120" t="n">
         <v>0</v>
@@ -3878,7 +3878,7 @@
         <v>9.80000019073486</v>
       </c>
       <c r="G121" t="n">
-        <v>8.74349021911621</v>
+        <v>8.74349117279053</v>
       </c>
       <c r="H121" t="n">
         <v>400</v>
@@ -3907,7 +3907,7 @@
         <v>9.80000019073486</v>
       </c>
       <c r="G122" t="n">
-        <v>8.74349021911621</v>
+        <v>8.74349117279053</v>
       </c>
       <c r="H122" t="n">
         <v>0</v>
@@ -3936,7 +3936,7 @@
         <v>9.82999992370605</v>
       </c>
       <c r="G123" t="n">
-        <v>8.77025604248047</v>
+        <v>8.77025699615479</v>
       </c>
       <c r="H123" t="n">
         <v>2600</v>
@@ -4081,7 +4081,7 @@
         <v>9.97000026702881</v>
       </c>
       <c r="G128" t="n">
-        <v>8.89516448974609</v>
+        <v>8.89516353607178</v>
       </c>
       <c r="H128" t="n">
         <v>200</v>
@@ -4110,7 +4110,7 @@
         <v>9.92000007629395</v>
       </c>
       <c r="G129" t="n">
-        <v>8.85055541992188</v>
+        <v>8.85055446624756</v>
       </c>
       <c r="H129" t="n">
         <v>3800</v>
@@ -4139,7 +4139,7 @@
         <v>9.89999961853027</v>
       </c>
       <c r="G130" t="n">
-        <v>8.83270931243896</v>
+        <v>8.83271026611328</v>
       </c>
       <c r="H130" t="n">
         <v>2400</v>
@@ -4168,7 +4168,7 @@
         <v>9.89999961853027</v>
       </c>
       <c r="G131" t="n">
-        <v>8.83270931243896</v>
+        <v>8.83271026611328</v>
       </c>
       <c r="H131" t="n">
         <v>3400</v>
@@ -4226,7 +4226,7 @@
         <v>9.89999961853027</v>
       </c>
       <c r="G133" t="n">
-        <v>8.83270931243896</v>
+        <v>8.83271026611328</v>
       </c>
       <c r="H133" t="n">
         <v>52800</v>
@@ -4255,7 +4255,7 @@
         <v>10.0900001525879</v>
       </c>
       <c r="G134" t="n">
-        <v>9.00222682952881</v>
+        <v>9.00222587585449</v>
       </c>
       <c r="H134" t="n">
         <v>80000</v>
@@ -4313,7 +4313,7 @@
         <v>10.3999996185303</v>
       </c>
       <c r="G136" t="n">
-        <v>9.27880573272705</v>
+        <v>9.27880668640137</v>
       </c>
       <c r="H136" t="n">
         <v>82000</v>
@@ -4371,7 +4371,7 @@
         <v>10.6000003814697</v>
       </c>
       <c r="G138" t="n">
-        <v>9.45724487304688</v>
+        <v>9.45724582672119</v>
       </c>
       <c r="H138" t="n">
         <v>28000</v>
@@ -4400,7 +4400,7 @@
         <v>10.6000003814697</v>
       </c>
       <c r="G139" t="n">
-        <v>9.45724487304688</v>
+        <v>9.45724582672119</v>
       </c>
       <c r="H139" t="n">
         <v>28400</v>
@@ -4429,7 +4429,7 @@
         <v>10.6000003814697</v>
       </c>
       <c r="G140" t="n">
-        <v>9.45724487304688</v>
+        <v>9.45724582672119</v>
       </c>
       <c r="H140" t="n">
         <v>10000</v>
@@ -4545,7 +4545,7 @@
         <v>10.539999961853</v>
       </c>
       <c r="G144" t="n">
-        <v>9.40371417999268</v>
+        <v>9.40371322631836</v>
       </c>
       <c r="H144" t="n">
         <v>3400</v>
@@ -4603,7 +4603,7 @@
         <v>10.5500001907349</v>
       </c>
       <c r="G146" t="n">
-        <v>9.41263580322266</v>
+        <v>9.41263484954834</v>
       </c>
       <c r="H146" t="n">
         <v>10800</v>
@@ -4632,7 +4632,7 @@
         <v>10.6000003814697</v>
       </c>
       <c r="G147" t="n">
-        <v>9.45724487304688</v>
+        <v>9.45724582672119</v>
       </c>
       <c r="H147" t="n">
         <v>4400</v>
@@ -4661,7 +4661,7 @@
         <v>10.5</v>
       </c>
       <c r="G148" t="n">
-        <v>9.36802673339844</v>
+        <v>9.36802577972412</v>
       </c>
       <c r="H148" t="n">
         <v>19800</v>
@@ -4719,7 +4719,7 @@
         <v>10.5</v>
       </c>
       <c r="G150" t="n">
-        <v>9.36802673339844</v>
+        <v>9.36802577972412</v>
       </c>
       <c r="H150" t="n">
         <v>4400</v>
@@ -4777,7 +4777,7 @@
         <v>10.5799999237061</v>
       </c>
       <c r="G152" t="n">
-        <v>9.43940162658691</v>
+        <v>9.43940258026123</v>
       </c>
       <c r="H152" t="n">
         <v>1000</v>
@@ -4806,7 +4806,7 @@
         <v>10.5500001907349</v>
       </c>
       <c r="G153" t="n">
-        <v>9.41263580322266</v>
+        <v>9.41263484954834</v>
       </c>
       <c r="H153" t="n">
         <v>2000</v>
@@ -4835,7 +4835,7 @@
         <v>10.6199998855591</v>
       </c>
       <c r="G154" t="n">
-        <v>9.47508811950684</v>
+        <v>9.47508907318115</v>
       </c>
       <c r="H154" t="n">
         <v>6000</v>
@@ -4893,7 +4893,7 @@
         <v>10.6000003814697</v>
       </c>
       <c r="G156" t="n">
-        <v>9.45724487304688</v>
+        <v>9.45724582672119</v>
       </c>
       <c r="H156" t="n">
         <v>3600</v>
@@ -4922,7 +4922,7 @@
         <v>10.789999961853</v>
       </c>
       <c r="G157" t="n">
-        <v>9.62676334381104</v>
+        <v>9.62676239013672</v>
       </c>
       <c r="H157" t="n">
         <v>32400</v>
@@ -4951,7 +4951,7 @@
         <v>10.9700002670288</v>
       </c>
       <c r="G158" t="n">
-        <v>9.78735637664795</v>
+        <v>9.78735733032227</v>
       </c>
       <c r="H158" t="n">
         <v>5800</v>
@@ -5125,7 +5125,7 @@
         <v>10.7600002288818</v>
       </c>
       <c r="G164" t="n">
-        <v>9.59999656677246</v>
+        <v>9.59999561309814</v>
       </c>
       <c r="H164" t="n">
         <v>4200</v>
@@ -5183,7 +5183,7 @@
         <v>10.7399997711182</v>
       </c>
       <c r="G166" t="n">
-        <v>9.58215236663818</v>
+        <v>9.58215141296387</v>
       </c>
       <c r="H166" t="n">
         <v>2400</v>
@@ -5241,7 +5241,7 @@
         <v>10.789999961853</v>
       </c>
       <c r="G168" t="n">
-        <v>9.62676334381104</v>
+        <v>9.62676239013672</v>
       </c>
       <c r="H168" t="n">
         <v>8000</v>
@@ -5270,7 +5270,7 @@
         <v>10.6300001144409</v>
       </c>
       <c r="G169" t="n">
-        <v>9.48400974273682</v>
+        <v>9.48401069641113</v>
       </c>
       <c r="H169" t="n">
         <v>8600</v>
@@ -5357,7 +5357,7 @@
         <v>10.8199996948242</v>
       </c>
       <c r="G172" t="n">
-        <v>9.65352630615234</v>
+        <v>9.65352725982666</v>
       </c>
       <c r="H172" t="n">
         <v>6400</v>
@@ -5386,7 +5386,7 @@
         <v>10.6899995803833</v>
       </c>
       <c r="G173" t="n">
-        <v>9.53754329681396</v>
+        <v>9.53754234313965</v>
       </c>
       <c r="H173" t="n">
         <v>10800</v>
@@ -5473,7 +5473,7 @@
         <v>10.7399997711182</v>
       </c>
       <c r="G176" t="n">
-        <v>9.58215236663818</v>
+        <v>9.58215141296387</v>
       </c>
       <c r="H176" t="n">
         <v>7600</v>
@@ -5502,7 +5502,7 @@
         <v>10.6599998474121</v>
       </c>
       <c r="G177" t="n">
-        <v>9.51077747344971</v>
+        <v>9.51077651977539</v>
       </c>
       <c r="H177" t="n">
         <v>11200</v>
@@ -5618,7 +5618,7 @@
         <v>10.6099996566772</v>
       </c>
       <c r="G181" t="n">
-        <v>9.46616554260254</v>
+        <v>9.46616649627686</v>
       </c>
       <c r="H181" t="n">
         <v>2600</v>
@@ -5647,7 +5647,7 @@
         <v>10.6199998855591</v>
       </c>
       <c r="G182" t="n">
-        <v>9.47508811950684</v>
+        <v>9.47508907318115</v>
       </c>
       <c r="H182" t="n">
         <v>400</v>
@@ -5705,7 +5705,7 @@
         <v>10.6000003814697</v>
       </c>
       <c r="G184" t="n">
-        <v>9.45724487304688</v>
+        <v>9.45724582672119</v>
       </c>
       <c r="H184" t="n">
         <v>200</v>
@@ -5734,7 +5734,7 @@
         <v>10.5500001907349</v>
       </c>
       <c r="G185" t="n">
-        <v>9.41263580322266</v>
+        <v>9.41263484954834</v>
       </c>
       <c r="H185" t="n">
         <v>2400</v>
@@ -5763,7 +5763,7 @@
         <v>10.5</v>
       </c>
       <c r="G186" t="n">
-        <v>9.36802673339844</v>
+        <v>9.36802577972412</v>
       </c>
       <c r="H186" t="n">
         <v>2600</v>
@@ -5792,7 +5792,7 @@
         <v>10.5</v>
       </c>
       <c r="G187" t="n">
-        <v>9.36802673339844</v>
+        <v>9.36802577972412</v>
       </c>
       <c r="H187" t="n">
         <v>0</v>
@@ -5821,7 +5821,7 @@
         <v>10.789999961853</v>
       </c>
       <c r="G188" t="n">
-        <v>9.62676334381104</v>
+        <v>9.62676239013672</v>
       </c>
       <c r="H188" t="n">
         <v>5200</v>
@@ -5850,7 +5850,7 @@
         <v>10.789999961853</v>
       </c>
       <c r="G189" t="n">
-        <v>9.62676334381104</v>
+        <v>9.62676239013672</v>
       </c>
       <c r="H189" t="n">
         <v>7200</v>
@@ -5879,7 +5879,7 @@
         <v>10.6000003814697</v>
       </c>
       <c r="G190" t="n">
-        <v>9.45724487304688</v>
+        <v>9.45724582672119</v>
       </c>
       <c r="H190" t="n">
         <v>9000</v>
@@ -5908,7 +5908,7 @@
         <v>10.6000003814697</v>
       </c>
       <c r="G191" t="n">
-        <v>9.45724487304688</v>
+        <v>9.45724582672119</v>
       </c>
       <c r="H191" t="n">
         <v>6600</v>
@@ -5937,7 +5937,7 @@
         <v>10.6000003814697</v>
       </c>
       <c r="G192" t="n">
-        <v>9.45724487304688</v>
+        <v>9.45724582672119</v>
       </c>
       <c r="H192" t="n">
         <v>10400</v>
@@ -5966,7 +5966,7 @@
         <v>10.6899995803833</v>
       </c>
       <c r="G193" t="n">
-        <v>9.53754329681396</v>
+        <v>9.53754234313965</v>
       </c>
       <c r="H193" t="n">
         <v>2600</v>
@@ -5995,7 +5995,7 @@
         <v>10.6899995803833</v>
       </c>
       <c r="G194" t="n">
-        <v>9.53754329681396</v>
+        <v>9.53754234313965</v>
       </c>
       <c r="H194" t="n">
         <v>3000</v>
@@ -6024,7 +6024,7 @@
         <v>10.6099996566772</v>
       </c>
       <c r="G195" t="n">
-        <v>9.46616554260254</v>
+        <v>9.46616649627686</v>
       </c>
       <c r="H195" t="n">
         <v>600</v>
@@ -6111,7 +6111,7 @@
         <v>10.5</v>
       </c>
       <c r="G198" t="n">
-        <v>9.36802673339844</v>
+        <v>9.36802577972412</v>
       </c>
       <c r="H198" t="n">
         <v>41200</v>
@@ -6140,7 +6140,7 @@
         <v>10.5500001907349</v>
       </c>
       <c r="G199" t="n">
-        <v>9.41263580322266</v>
+        <v>9.41263484954834</v>
       </c>
       <c r="H199" t="n">
         <v>4800</v>
@@ -6169,7 +6169,7 @@
         <v>10.5</v>
       </c>
       <c r="G200" t="n">
-        <v>9.36802673339844</v>
+        <v>9.36802577972412</v>
       </c>
       <c r="H200" t="n">
         <v>12000</v>
@@ -6198,7 +6198,7 @@
         <v>10.539999961853</v>
       </c>
       <c r="G201" t="n">
-        <v>9.40371417999268</v>
+        <v>9.40371322631836</v>
       </c>
       <c r="H201" t="n">
         <v>1600</v>
@@ -6256,7 +6256,7 @@
         <v>10.6899995803833</v>
       </c>
       <c r="G203" t="n">
-        <v>9.53754329681396</v>
+        <v>9.53754234313965</v>
       </c>
       <c r="H203" t="n">
         <v>5400</v>
@@ -6285,7 +6285,7 @@
         <v>10.6599998474121</v>
       </c>
       <c r="G204" t="n">
-        <v>9.51077747344971</v>
+        <v>9.51077651977539</v>
       </c>
       <c r="H204" t="n">
         <v>20200</v>
@@ -6314,7 +6314,7 @@
         <v>10.6199998855591</v>
       </c>
       <c r="G205" t="n">
-        <v>9.47508811950684</v>
+        <v>9.47508907318115</v>
       </c>
       <c r="H205" t="n">
         <v>17200</v>
@@ -6343,7 +6343,7 @@
         <v>10.6700000762939</v>
       </c>
       <c r="G206" t="n">
-        <v>9.519700050354</v>
+        <v>9.51969909667969</v>
       </c>
       <c r="H206" t="n">
         <v>10800</v>
@@ -6372,7 +6372,7 @@
         <v>10.6199998855591</v>
       </c>
       <c r="G207" t="n">
-        <v>9.47508811950684</v>
+        <v>9.47508907318115</v>
       </c>
       <c r="H207" t="n">
         <v>3000</v>
@@ -6430,7 +6430,7 @@
         <v>10.6300001144409</v>
       </c>
       <c r="G209" t="n">
-        <v>9.48400974273682</v>
+        <v>9.48401069641113</v>
       </c>
       <c r="H209" t="n">
         <v>600</v>
@@ -6488,7 +6488,7 @@
         <v>10.789999961853</v>
       </c>
       <c r="G211" t="n">
-        <v>9.62676334381104</v>
+        <v>9.62676239013672</v>
       </c>
       <c r="H211" t="n">
         <v>1600</v>
@@ -6517,7 +6517,7 @@
         <v>10.8100004196167</v>
       </c>
       <c r="G212" t="n">
-        <v>9.64460754394531</v>
+        <v>9.644606590271</v>
       </c>
       <c r="H212" t="n">
         <v>7200</v>
@@ -6546,7 +6546,7 @@
         <v>10.8100004196167</v>
       </c>
       <c r="G213" t="n">
-        <v>9.64460754394531</v>
+        <v>9.644606590271</v>
       </c>
       <c r="H213" t="n">
         <v>0</v>
@@ -6662,7 +6662,7 @@
         <v>10.7600002288818</v>
       </c>
       <c r="G217" t="n">
-        <v>9.59999656677246</v>
+        <v>9.59999561309814</v>
       </c>
       <c r="H217" t="n">
         <v>2400</v>
@@ -6691,7 +6691,7 @@
         <v>10.7399997711182</v>
       </c>
       <c r="G218" t="n">
-        <v>9.58215236663818</v>
+        <v>9.58215141296387</v>
       </c>
       <c r="H218" t="n">
         <v>400</v>
@@ -6720,7 +6720,7 @@
         <v>10.7399997711182</v>
       </c>
       <c r="G219" t="n">
-        <v>9.58215236663818</v>
+        <v>9.58215141296387</v>
       </c>
       <c r="H219" t="n">
         <v>0</v>
@@ -6778,7 +6778,7 @@
         <v>10.6199998855591</v>
       </c>
       <c r="G221" t="n">
-        <v>9.47508811950684</v>
+        <v>9.47508907318115</v>
       </c>
       <c r="H221" t="n">
         <v>5800</v>
@@ -6836,7 +6836,7 @@
         <v>10.8199996948242</v>
       </c>
       <c r="G223" t="n">
-        <v>9.65352630615234</v>
+        <v>9.65352725982666</v>
       </c>
       <c r="H223" t="n">
         <v>3600</v>
@@ -6952,7 +6952,7 @@
         <v>10.7600002288818</v>
       </c>
       <c r="G227" t="n">
-        <v>9.59999656677246</v>
+        <v>9.59999561309814</v>
       </c>
       <c r="H227" t="n">
         <v>3400</v>
@@ -7039,7 +7039,7 @@
         <v>10.7799997329712</v>
       </c>
       <c r="G230" t="n">
-        <v>9.61783885955811</v>
+        <v>9.61783981323242</v>
       </c>
       <c r="H230" t="n">
         <v>11400</v>
@@ -7213,7 +7213,7 @@
         <v>10.6000003814697</v>
       </c>
       <c r="G236" t="n">
-        <v>9.45724487304688</v>
+        <v>9.45724582672119</v>
       </c>
       <c r="H236" t="n">
         <v>1200</v>
@@ -7300,7 +7300,7 @@
         <v>10.6000003814697</v>
       </c>
       <c r="G239" t="n">
-        <v>9.45724487304688</v>
+        <v>9.45724582672119</v>
       </c>
       <c r="H239" t="n">
         <v>3800</v>
@@ -7329,7 +7329,7 @@
         <v>10.6000003814697</v>
       </c>
       <c r="G240" t="n">
-        <v>9.45724487304688</v>
+        <v>9.45724582672119</v>
       </c>
       <c r="H240" t="n">
         <v>0</v>
@@ -7358,7 +7358,7 @@
         <v>10.6000003814697</v>
       </c>
       <c r="G241" t="n">
-        <v>9.45724487304688</v>
+        <v>9.45724582672119</v>
       </c>
       <c r="H241" t="n">
         <v>27800</v>
@@ -7387,7 +7387,7 @@
         <v>10.3999996185303</v>
       </c>
       <c r="G242" t="n">
-        <v>9.27880573272705</v>
+        <v>9.27880668640137</v>
       </c>
       <c r="H242" t="n">
         <v>23800</v>
@@ -7416,7 +7416,7 @@
         <v>10.5299997329712</v>
       </c>
       <c r="G243" t="n">
-        <v>9.3947925567627</v>
+        <v>9.39479064941406</v>
       </c>
       <c r="H243" t="n">
         <v>8000</v>
@@ -7445,7 +7445,7 @@
         <v>10.3000001907349</v>
       </c>
       <c r="G244" t="n">
-        <v>9.18958759307861</v>
+        <v>9.18958854675293</v>
       </c>
       <c r="H244" t="n">
         <v>9000</v>
@@ -7474,7 +7474,7 @@
         <v>10.3999996185303</v>
       </c>
       <c r="G245" t="n">
-        <v>9.27880573272705</v>
+        <v>9.27880668640137</v>
       </c>
       <c r="H245" t="n">
         <v>8800</v>
@@ -7503,7 +7503,7 @@
         <v>10.289999961853</v>
       </c>
       <c r="G246" t="n">
-        <v>9.18066596984863</v>
+        <v>9.18066692352295</v>
       </c>
       <c r="H246" t="n">
         <v>11000</v>
@@ -7532,7 +7532,7 @@
         <v>10.2200002670288</v>
       </c>
       <c r="G247" t="n">
-        <v>9.1182107925415</v>
+        <v>9.11821174621582</v>
       </c>
       <c r="H247" t="n">
         <v>15200</v>
@@ -7706,7 +7706,7 @@
         <v>10.289999961853</v>
       </c>
       <c r="G253" t="n">
-        <v>9.18066596984863</v>
+        <v>9.18066692352295</v>
       </c>
       <c r="H253" t="n">
         <v>8400</v>
@@ -7735,7 +7735,7 @@
         <v>10.3699998855591</v>
       </c>
       <c r="G254" t="n">
-        <v>9.25203895568848</v>
+        <v>9.25203990936279</v>
       </c>
       <c r="H254" t="n">
         <v>400</v>
@@ -7764,7 +7764,7 @@
         <v>10.1599998474121</v>
       </c>
       <c r="G255" t="n">
-        <v>9.0646800994873</v>
+        <v>9.06468105316162</v>
       </c>
       <c r="H255" t="n">
         <v>17200</v>
@@ -7793,7 +7793,7 @@
         <v>10.2600002288818</v>
       </c>
       <c r="G256" t="n">
-        <v>9.15390014648438</v>
+        <v>9.15389919281006</v>
       </c>
       <c r="H256" t="n">
         <v>600</v>
@@ -7851,7 +7851,7 @@
         <v>10.2399997711182</v>
       </c>
       <c r="G258" t="n">
-        <v>9.13605499267578</v>
+        <v>9.13605403900146</v>
       </c>
       <c r="H258" t="n">
         <v>2200</v>
@@ -7880,7 +7880,7 @@
         <v>10.3000001907349</v>
       </c>
       <c r="G259" t="n">
-        <v>9.18958759307861</v>
+        <v>9.18958854675293</v>
       </c>
       <c r="H259" t="n">
         <v>3400</v>
@@ -7909,7 +7909,7 @@
         <v>10.2299995422363</v>
       </c>
       <c r="G260" t="n">
-        <v>9.12713241577148</v>
+        <v>9.1271333694458</v>
       </c>
       <c r="H260" t="n">
         <v>11000</v>
@@ -7938,7 +7938,7 @@
         <v>10.2299995422363</v>
       </c>
       <c r="G261" t="n">
-        <v>9.12713241577148</v>
+        <v>9.1271333694458</v>
       </c>
       <c r="H261" t="n">
         <v>0</v>
@@ -7996,7 +7996,7 @@
         <v>10.3199996948242</v>
       </c>
       <c r="G263" t="n">
-        <v>9.20743083953857</v>
+        <v>9.20743179321289</v>
       </c>
       <c r="H263" t="n">
         <v>2600</v>
@@ -8025,7 +8025,7 @@
         <v>10.3000001907349</v>
       </c>
       <c r="G264" t="n">
-        <v>9.18958759307861</v>
+        <v>9.18958854675293</v>
       </c>
       <c r="H264" t="n">
         <v>11400</v>
@@ -8054,7 +8054,7 @@
         <v>10.3400001525879</v>
       </c>
       <c r="G265" t="n">
-        <v>9.22527503967285</v>
+        <v>9.22527408599854</v>
       </c>
       <c r="H265" t="n">
         <v>1200</v>
@@ -8112,7 +8112,7 @@
         <v>10.4200000762939</v>
       </c>
       <c r="G267" t="n">
-        <v>9.29664993286133</v>
+        <v>9.29665088653564</v>
       </c>
       <c r="H267" t="n">
         <v>4000</v>
@@ -8141,7 +8141,7 @@
         <v>10.3500003814697</v>
       </c>
       <c r="G268" t="n">
-        <v>9.23419570922852</v>
+        <v>9.23419666290283</v>
       </c>
       <c r="H268" t="n">
         <v>2000</v>
@@ -8170,7 +8170,7 @@
         <v>10.4200000762939</v>
       </c>
       <c r="G269" t="n">
-        <v>9.29664993286133</v>
+        <v>9.29665088653564</v>
       </c>
       <c r="H269" t="n">
         <v>15000</v>
@@ -8199,7 +8199,7 @@
         <v>10.4499998092651</v>
       </c>
       <c r="G270" t="n">
-        <v>9.3234167098999</v>
+        <v>9.32341575622559</v>
       </c>
       <c r="H270" t="n">
         <v>11200</v>
@@ -8228,7 +8228,7 @@
         <v>10.460000038147</v>
       </c>
       <c r="G271" t="n">
-        <v>9.33233833312988</v>
+        <v>9.3323392868042</v>
       </c>
       <c r="H271" t="n">
         <v>3000</v>
@@ -8286,7 +8286,7 @@
         <v>10.539999961853</v>
       </c>
       <c r="G273" t="n">
-        <v>9.40371417999268</v>
+        <v>9.40371322631836</v>
       </c>
       <c r="H273" t="n">
         <v>3400</v>
@@ -8315,7 +8315,7 @@
         <v>10.4399995803833</v>
       </c>
       <c r="G274" t="n">
-        <v>9.31449413299561</v>
+        <v>9.31449508666992</v>
       </c>
       <c r="H274" t="n">
         <v>12800</v>
@@ -8344,7 +8344,7 @@
         <v>10.3000001907349</v>
       </c>
       <c r="G275" t="n">
-        <v>9.18958759307861</v>
+        <v>9.18958854675293</v>
       </c>
       <c r="H275" t="n">
         <v>1200</v>
@@ -8402,7 +8402,7 @@
         <v>10.0799999237061</v>
       </c>
       <c r="G277" t="n">
-        <v>8.99330425262451</v>
+        <v>8.99330520629883</v>
       </c>
       <c r="H277" t="n">
         <v>21800</v>
@@ -8431,7 +8431,7 @@
         <v>10.1499996185303</v>
       </c>
       <c r="G278" t="n">
-        <v>9.05575752258301</v>
+        <v>9.05575847625732</v>
       </c>
       <c r="H278" t="n">
         <v>10200</v>
@@ -8460,7 +8460,7 @@
         <v>10.1400003433228</v>
       </c>
       <c r="G279" t="n">
-        <v>9.04683780670166</v>
+        <v>9.04683685302734</v>
       </c>
       <c r="H279" t="n">
         <v>20400</v>
@@ -8547,7 +8547,7 @@
         <v>10.2299995422363</v>
       </c>
       <c r="G282" t="n">
-        <v>9.12713241577148</v>
+        <v>9.1271333694458</v>
       </c>
       <c r="H282" t="n">
         <v>6000</v>
@@ -8605,7 +8605,7 @@
         <v>10.1599998474121</v>
       </c>
       <c r="G284" t="n">
-        <v>9.0646800994873</v>
+        <v>9.06468105316162</v>
       </c>
       <c r="H284" t="n">
         <v>5000</v>
@@ -8634,7 +8634,7 @@
         <v>10.1599998474121</v>
       </c>
       <c r="G285" t="n">
-        <v>9.0646800994873</v>
+        <v>9.06468105316162</v>
       </c>
       <c r="H285" t="n">
         <v>2400</v>
@@ -8663,7 +8663,7 @@
         <v>10.0600004196167</v>
       </c>
       <c r="G286" t="n">
-        <v>8.97546100616455</v>
+        <v>8.97546195983887</v>
       </c>
       <c r="H286" t="n">
         <v>15200</v>
@@ -8692,7 +8692,7 @@
         <v>10.0900001525879</v>
       </c>
       <c r="G287" t="n">
-        <v>9.00222682952881</v>
+        <v>9.00222587585449</v>
       </c>
       <c r="H287" t="n">
         <v>200</v>
@@ -8721,7 +8721,7 @@
         <v>10.1400003433228</v>
       </c>
       <c r="G288" t="n">
-        <v>9.04683780670166</v>
+        <v>9.04683685302734</v>
       </c>
       <c r="H288" t="n">
         <v>5200</v>
@@ -8750,7 +8750,7 @@
         <v>10.1400003433228</v>
       </c>
       <c r="G289" t="n">
-        <v>9.04683780670166</v>
+        <v>9.04683685302734</v>
       </c>
       <c r="H289" t="n">
         <v>10000</v>
@@ -8779,7 +8779,7 @@
         <v>10.1599998474121</v>
       </c>
       <c r="G290" t="n">
-        <v>9.0646800994873</v>
+        <v>9.06468105316162</v>
       </c>
       <c r="H290" t="n">
         <v>6200</v>
@@ -8866,7 +8866,7 @@
         <v>10.0900001525879</v>
       </c>
       <c r="G293" t="n">
-        <v>9.00222682952881</v>
+        <v>9.00222587585449</v>
       </c>
       <c r="H293" t="n">
         <v>6600</v>
@@ -8895,7 +8895,7 @@
         <v>10.0900001525879</v>
       </c>
       <c r="G294" t="n">
-        <v>9.00222682952881</v>
+        <v>9.00222587585449</v>
       </c>
       <c r="H294" t="n">
         <v>0</v>
@@ -8924,7 +8924,7 @@
         <v>10.0699996948242</v>
       </c>
       <c r="G295" t="n">
-        <v>8.98438262939453</v>
+        <v>8.98438167572021</v>
       </c>
       <c r="H295" t="n">
         <v>5000</v>
@@ -9011,7 +9011,7 @@
         <v>10.0799999237061</v>
       </c>
       <c r="G298" t="n">
-        <v>8.99330425262451</v>
+        <v>8.99330520629883</v>
       </c>
       <c r="H298" t="n">
         <v>200</v>
@@ -9040,7 +9040,7 @@
         <v>10.0600004196167</v>
       </c>
       <c r="G299" t="n">
-        <v>8.97546100616455</v>
+        <v>8.97546195983887</v>
       </c>
       <c r="H299" t="n">
         <v>17200</v>
@@ -9069,7 +9069,7 @@
         <v>10.0600004196167</v>
       </c>
       <c r="G300" t="n">
-        <v>8.97546100616455</v>
+        <v>8.97546195983887</v>
       </c>
       <c r="H300" t="n">
         <v>1000</v>
@@ -9098,7 +9098,7 @@
         <v>10.0600004196167</v>
       </c>
       <c r="G301" t="n">
-        <v>8.97546100616455</v>
+        <v>8.97546195983887</v>
       </c>
       <c r="H301" t="n">
         <v>12600</v>
@@ -9127,7 +9127,7 @@
         <v>10.0600004196167</v>
       </c>
       <c r="G302" t="n">
-        <v>8.97546100616455</v>
+        <v>8.97546195983887</v>
       </c>
       <c r="H302" t="n">
         <v>2000</v>
@@ -9156,7 +9156,7 @@
         <v>10.0600004196167</v>
       </c>
       <c r="G303" t="n">
-        <v>8.97546100616455</v>
+        <v>8.97546195983887</v>
       </c>
       <c r="H303" t="n">
         <v>0</v>
@@ -9185,7 +9185,7 @@
         <v>10.0900001525879</v>
       </c>
       <c r="G304" t="n">
-        <v>9.00222682952881</v>
+        <v>9.00222587585449</v>
       </c>
       <c r="H304" t="n">
         <v>18400</v>
@@ -9214,7 +9214,7 @@
         <v>10.0600004196167</v>
       </c>
       <c r="G305" t="n">
-        <v>8.97546100616455</v>
+        <v>8.97546195983887</v>
       </c>
       <c r="H305" t="n">
         <v>200</v>
@@ -9243,7 +9243,7 @@
         <v>10.0799999237061</v>
       </c>
       <c r="G306" t="n">
-        <v>8.99330425262451</v>
+        <v>8.99330520629883</v>
       </c>
       <c r="H306" t="n">
         <v>11200</v>
@@ -9272,7 +9272,7 @@
         <v>10.0600004196167</v>
       </c>
       <c r="G307" t="n">
-        <v>8.97546100616455</v>
+        <v>8.97546195983887</v>
       </c>
       <c r="H307" t="n">
         <v>4200</v>
@@ -10258,7 +10258,7 @@
         <v>9.89999961853027</v>
       </c>
       <c r="G341" t="n">
-        <v>8.83270931243896</v>
+        <v>8.83271026611328</v>
       </c>
       <c r="H341" t="n">
         <v>5400</v>
@@ -10664,7 +10664,7 @@
         <v>9.89999961853027</v>
       </c>
       <c r="G355" t="n">
-        <v>8.83270931243896</v>
+        <v>8.83271026611328</v>
       </c>
       <c r="H355" t="n">
         <v>17800</v>
@@ -10693,7 +10693,7 @@
         <v>9.89999961853027</v>
       </c>
       <c r="G356" t="n">
-        <v>8.83270931243896</v>
+        <v>8.83271026611328</v>
       </c>
       <c r="H356" t="n">
         <v>18800</v>
@@ -10722,7 +10722,7 @@
         <v>9.89999961853027</v>
       </c>
       <c r="G357" t="n">
-        <v>8.83270931243896</v>
+        <v>8.83271026611328</v>
       </c>
       <c r="H357" t="n">
         <v>6800</v>
@@ -10751,7 +10751,7 @@
         <v>9.89999961853027</v>
       </c>
       <c r="G358" t="n">
-        <v>8.83270931243896</v>
+        <v>8.83271026611328</v>
       </c>
       <c r="H358" t="n">
         <v>0</v>
@@ -10780,7 +10780,7 @@
         <v>9.89999961853027</v>
       </c>
       <c r="G359" t="n">
-        <v>8.83270931243896</v>
+        <v>8.83271026611328</v>
       </c>
       <c r="H359" t="n">
         <v>0</v>
@@ -10809,7 +10809,7 @@
         <v>9.89999961853027</v>
       </c>
       <c r="G360" t="n">
-        <v>8.83270931243896</v>
+        <v>8.83271026611328</v>
       </c>
       <c r="H360" t="n">
         <v>0</v>
@@ -10838,7 +10838,7 @@
         <v>9.89999961853027</v>
       </c>
       <c r="G361" t="n">
-        <v>8.83270931243896</v>
+        <v>8.83271026611328</v>
       </c>
       <c r="H361" t="n">
         <v>1000</v>
@@ -10983,7 +10983,7 @@
         <v>9.85000038146973</v>
       </c>
       <c r="G366" t="n">
-        <v>8.78810024261475</v>
+        <v>8.78810119628906</v>
       </c>
       <c r="H366" t="n">
         <v>1200</v>
@@ -11012,7 +11012,7 @@
         <v>9.80000019073486</v>
       </c>
       <c r="G367" t="n">
-        <v>8.74349021911621</v>
+        <v>8.74349117279053</v>
       </c>
       <c r="H367" t="n">
         <v>2000</v>
@@ -11041,7 +11041,7 @@
         <v>9.89999961853027</v>
       </c>
       <c r="G368" t="n">
-        <v>8.83270931243896</v>
+        <v>8.83271026611328</v>
       </c>
       <c r="H368" t="n">
         <v>400</v>
@@ -11070,7 +11070,7 @@
         <v>9.89999961853027</v>
       </c>
       <c r="G369" t="n">
-        <v>8.83270931243896</v>
+        <v>8.83271026611328</v>
       </c>
       <c r="H369" t="n">
         <v>1600</v>
@@ -11099,7 +11099,7 @@
         <v>9.89999961853027</v>
       </c>
       <c r="G370" t="n">
-        <v>8.83270931243896</v>
+        <v>8.83271026611328</v>
       </c>
       <c r="H370" t="n">
         <v>0</v>
@@ -11157,7 +11157,7 @@
         <v>9.85000038146973</v>
       </c>
       <c r="G372" t="n">
-        <v>8.78810024261475</v>
+        <v>8.78810119628906</v>
       </c>
       <c r="H372" t="n">
         <v>6800</v>
@@ -11186,7 +11186,7 @@
         <v>9.89999961853027</v>
       </c>
       <c r="G373" t="n">
-        <v>8.83270931243896</v>
+        <v>8.83271026611328</v>
       </c>
       <c r="H373" t="n">
         <v>10800</v>
@@ -11592,7 +11592,7 @@
         <v>9.89999961853027</v>
       </c>
       <c r="G387" t="n">
-        <v>8.83270931243896</v>
+        <v>8.83271026611328</v>
       </c>
       <c r="H387" t="n">
         <v>14200</v>
@@ -11621,7 +11621,7 @@
         <v>9.80000019073486</v>
       </c>
       <c r="G388" t="n">
-        <v>8.74349021911621</v>
+        <v>8.74349117279053</v>
       </c>
       <c r="H388" t="n">
         <v>18400</v>
@@ -11650,7 +11650,7 @@
         <v>9.80000019073486</v>
       </c>
       <c r="G389" t="n">
-        <v>8.74349021911621</v>
+        <v>8.74349117279053</v>
       </c>
       <c r="H389" t="n">
         <v>0</v>
@@ -11679,7 +11679,7 @@
         <v>9.85000038146973</v>
       </c>
       <c r="G390" t="n">
-        <v>8.78810024261475</v>
+        <v>8.78810119628906</v>
       </c>
       <c r="H390" t="n">
         <v>400</v>
@@ -11708,7 +11708,7 @@
         <v>9.85000038146973</v>
       </c>
       <c r="G391" t="n">
-        <v>8.78810024261475</v>
+        <v>8.78810119628906</v>
       </c>
       <c r="H391" t="n">
         <v>10000</v>
@@ -11737,7 +11737,7 @@
         <v>9.85000038146973</v>
       </c>
       <c r="G392" t="n">
-        <v>8.78810024261475</v>
+        <v>8.78810119628906</v>
       </c>
       <c r="H392" t="n">
         <v>0</v>
@@ -11766,7 +11766,7 @@
         <v>9.85000038146973</v>
       </c>
       <c r="G393" t="n">
-        <v>8.78810024261475</v>
+        <v>8.78810119628906</v>
       </c>
       <c r="H393" t="n">
         <v>0</v>
@@ -11795,7 +11795,7 @@
         <v>9.85000038146973</v>
       </c>
       <c r="G394" t="n">
-        <v>8.78810024261475</v>
+        <v>8.78810119628906</v>
       </c>
       <c r="H394" t="n">
         <v>24000</v>
@@ -11824,7 +11824,7 @@
         <v>9.89999961853027</v>
       </c>
       <c r="G395" t="n">
-        <v>8.83270931243896</v>
+        <v>8.83271026611328</v>
       </c>
       <c r="H395" t="n">
         <v>21000</v>
@@ -11911,7 +11911,7 @@
         <v>9.89999961853027</v>
       </c>
       <c r="G398" t="n">
-        <v>8.83270931243896</v>
+        <v>8.83271026611328</v>
       </c>
       <c r="H398" t="n">
         <v>44000</v>
@@ -12056,7 +12056,7 @@
         <v>9.89999961853027</v>
       </c>
       <c r="G403" t="n">
-        <v>8.83270931243896</v>
+        <v>8.83271026611328</v>
       </c>
       <c r="H403" t="n">
         <v>400</v>
@@ -12085,7 +12085,7 @@
         <v>9.89999961853027</v>
       </c>
       <c r="G404" t="n">
-        <v>8.83270931243896</v>
+        <v>8.83271026611328</v>
       </c>
       <c r="H404" t="n">
         <v>3200</v>
@@ -12114,7 +12114,7 @@
         <v>9.85000038146973</v>
       </c>
       <c r="G405" t="n">
-        <v>8.78810024261475</v>
+        <v>8.78810119628906</v>
       </c>
       <c r="H405" t="n">
         <v>200</v>
@@ -12143,7 +12143,7 @@
         <v>9.85000038146973</v>
       </c>
       <c r="G406" t="n">
-        <v>8.78810024261475</v>
+        <v>8.78810119628906</v>
       </c>
       <c r="H406" t="n">
         <v>13800</v>
@@ -12172,7 +12172,7 @@
         <v>9.89999961853027</v>
       </c>
       <c r="G407" t="n">
-        <v>8.83270931243896</v>
+        <v>8.83271026611328</v>
       </c>
       <c r="H407" t="n">
         <v>2200</v>
@@ -12346,7 +12346,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G413" t="n">
-        <v>8.65427207946777</v>
+        <v>8.65427017211914</v>
       </c>
       <c r="H413" t="n">
         <v>400</v>
@@ -12375,7 +12375,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G414" t="n">
-        <v>8.65427207946777</v>
+        <v>8.65427017211914</v>
       </c>
       <c r="H414" t="n">
         <v>0</v>
@@ -12404,7 +12404,7 @@
         <v>9.80000019073486</v>
       </c>
       <c r="G415" t="n">
-        <v>8.74349021911621</v>
+        <v>8.74349117279053</v>
       </c>
       <c r="H415" t="n">
         <v>2400</v>
@@ -12433,7 +12433,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G416" t="n">
-        <v>8.65427207946777</v>
+        <v>8.65427017211914</v>
       </c>
       <c r="H416" t="n">
         <v>800</v>
@@ -12462,7 +12462,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G417" t="n">
-        <v>8.65427207946777</v>
+        <v>8.65427017211914</v>
       </c>
       <c r="H417" t="n">
         <v>0</v>
@@ -12491,7 +12491,7 @@
         <v>9.80000019073486</v>
       </c>
       <c r="G418" t="n">
-        <v>8.74349021911621</v>
+        <v>8.74349117279053</v>
       </c>
       <c r="H418" t="n">
         <v>35200</v>
@@ -12607,7 +12607,7 @@
         <v>9.80000019073486</v>
       </c>
       <c r="G422" t="n">
-        <v>8.74349021911621</v>
+        <v>8.74349117279053</v>
       </c>
       <c r="H422" t="n">
         <v>600</v>
@@ -12636,7 +12636,7 @@
         <v>9.85000038146973</v>
       </c>
       <c r="G423" t="n">
-        <v>8.78810024261475</v>
+        <v>8.78810119628906</v>
       </c>
       <c r="H423" t="n">
         <v>28400</v>
@@ -12665,7 +12665,7 @@
         <v>9.89999961853027</v>
       </c>
       <c r="G424" t="n">
-        <v>8.83270931243896</v>
+        <v>8.83271026611328</v>
       </c>
       <c r="H424" t="n">
         <v>12600</v>
@@ -13129,7 +13129,7 @@
         <v>10.3000001907349</v>
       </c>
       <c r="G440" t="n">
-        <v>9.18958759307861</v>
+        <v>9.18958854675293</v>
       </c>
       <c r="H440" t="n">
         <v>5000</v>
@@ -13158,7 +13158,7 @@
         <v>10.3000001907349</v>
       </c>
       <c r="G441" t="n">
-        <v>9.18958759307861</v>
+        <v>9.18958854675293</v>
       </c>
       <c r="H441" t="n">
         <v>27000</v>
@@ -13187,7 +13187,7 @@
         <v>10.3000001907349</v>
       </c>
       <c r="G442" t="n">
-        <v>9.18958759307861</v>
+        <v>9.18958854675293</v>
       </c>
       <c r="H442" t="n">
         <v>1400</v>
@@ -13216,7 +13216,7 @@
         <v>10.3000001907349</v>
       </c>
       <c r="G443" t="n">
-        <v>9.18958759307861</v>
+        <v>9.18958854675293</v>
       </c>
       <c r="H443" t="n">
         <v>2400</v>
@@ -13245,7 +13245,7 @@
         <v>10.3999996185303</v>
       </c>
       <c r="G444" t="n">
-        <v>9.27880573272705</v>
+        <v>9.27880668640137</v>
       </c>
       <c r="H444" t="n">
         <v>9000</v>
@@ -13274,7 +13274,7 @@
         <v>10.3999996185303</v>
       </c>
       <c r="G445" t="n">
-        <v>9.27880573272705</v>
+        <v>9.27880668640137</v>
       </c>
       <c r="H445" t="n">
         <v>1000</v>
@@ -13303,7 +13303,7 @@
         <v>10.3999996185303</v>
       </c>
       <c r="G446" t="n">
-        <v>9.27880573272705</v>
+        <v>9.27880668640137</v>
       </c>
       <c r="H446" t="n">
         <v>0</v>
@@ -13332,7 +13332,7 @@
         <v>10.3999996185303</v>
       </c>
       <c r="G447" t="n">
-        <v>9.27880573272705</v>
+        <v>9.27880668640137</v>
       </c>
       <c r="H447" t="n">
         <v>18200</v>
@@ -13361,7 +13361,7 @@
         <v>10.3999996185303</v>
       </c>
       <c r="G448" t="n">
-        <v>9.27880573272705</v>
+        <v>9.27880668640137</v>
       </c>
       <c r="H448" t="n">
         <v>3000</v>
@@ -13419,7 +13419,7 @@
         <v>10.3000001907349</v>
       </c>
       <c r="G450" t="n">
-        <v>9.18958759307861</v>
+        <v>9.18958854675293</v>
       </c>
       <c r="H450" t="n">
         <v>21000</v>
@@ -13448,7 +13448,7 @@
         <v>10.3999996185303</v>
       </c>
       <c r="G451" t="n">
-        <v>9.27880573272705</v>
+        <v>9.27880668640137</v>
       </c>
       <c r="H451" t="n">
         <v>16400</v>
@@ -13477,7 +13477,7 @@
         <v>10.3999996185303</v>
       </c>
       <c r="G452" t="n">
-        <v>9.27880573272705</v>
+        <v>9.27880668640137</v>
       </c>
       <c r="H452" t="n">
         <v>10800</v>
@@ -13506,7 +13506,7 @@
         <v>10.3999996185303</v>
       </c>
       <c r="G453" t="n">
-        <v>9.27880573272705</v>
+        <v>9.27880668640137</v>
       </c>
       <c r="H453" t="n">
         <v>30600</v>
@@ -13535,7 +13535,7 @@
         <v>10.3000001907349</v>
       </c>
       <c r="G454" t="n">
-        <v>9.18958759307861</v>
+        <v>9.18958854675293</v>
       </c>
       <c r="H454" t="n">
         <v>7000</v>
@@ -13564,7 +13564,7 @@
         <v>10.3999996185303</v>
       </c>
       <c r="G455" t="n">
-        <v>9.27880573272705</v>
+        <v>9.27880668640137</v>
       </c>
       <c r="H455" t="n">
         <v>7600</v>
@@ -13593,7 +13593,7 @@
         <v>10.3000001907349</v>
       </c>
       <c r="G456" t="n">
-        <v>9.18958759307861</v>
+        <v>9.18958854675293</v>
       </c>
       <c r="H456" t="n">
         <v>5000</v>
@@ -13622,7 +13622,7 @@
         <v>10.3999996185303</v>
       </c>
       <c r="G457" t="n">
-        <v>9.27880573272705</v>
+        <v>9.27880668640137</v>
       </c>
       <c r="H457" t="n">
         <v>34200</v>
@@ -13651,7 +13651,7 @@
         <v>10.3000001907349</v>
       </c>
       <c r="G458" t="n">
-        <v>9.18958759307861</v>
+        <v>9.18958854675293</v>
       </c>
       <c r="H458" t="n">
         <v>600</v>
@@ -13680,7 +13680,7 @@
         <v>10.3000001907349</v>
       </c>
       <c r="G459" t="n">
-        <v>9.18958759307861</v>
+        <v>9.18958854675293</v>
       </c>
       <c r="H459" t="n">
         <v>600</v>
@@ -13709,7 +13709,7 @@
         <v>10.3999996185303</v>
       </c>
       <c r="G460" t="n">
-        <v>9.27880573272705</v>
+        <v>9.27880668640137</v>
       </c>
       <c r="H460" t="n">
         <v>10000</v>
@@ -13738,7 +13738,7 @@
         <v>10.3999996185303</v>
       </c>
       <c r="G461" t="n">
-        <v>9.27880573272705</v>
+        <v>9.27880668640137</v>
       </c>
       <c r="H461" t="n">
         <v>0</v>
@@ -13767,7 +13767,7 @@
         <v>10.3000001907349</v>
       </c>
       <c r="G462" t="n">
-        <v>9.18958759307861</v>
+        <v>9.18958854675293</v>
       </c>
       <c r="H462" t="n">
         <v>2400</v>
@@ -13796,7 +13796,7 @@
         <v>10.3000001907349</v>
       </c>
       <c r="G463" t="n">
-        <v>9.18958759307861</v>
+        <v>9.18958854675293</v>
       </c>
       <c r="H463" t="n">
         <v>9600</v>
@@ -13854,7 +13854,7 @@
         <v>10.3000001907349</v>
       </c>
       <c r="G465" t="n">
-        <v>9.18958759307861</v>
+        <v>9.18958854675293</v>
       </c>
       <c r="H465" t="n">
         <v>200</v>
@@ -14144,7 +14144,7 @@
         <v>10.3000001907349</v>
       </c>
       <c r="G475" t="n">
-        <v>9.18958759307861</v>
+        <v>9.18958854675293</v>
       </c>
       <c r="H475" t="n">
         <v>2000</v>
@@ -14811,7 +14811,7 @@
         <v>9.64999961853027</v>
       </c>
       <c r="G498" t="n">
-        <v>8.60966014862061</v>
+        <v>8.60966205596924</v>
       </c>
       <c r="H498" t="n">
         <v>65200</v>
@@ -14840,7 +14840,7 @@
         <v>9.80000019073486</v>
       </c>
       <c r="G499" t="n">
-        <v>8.74349021911621</v>
+        <v>8.74349117279053</v>
       </c>
       <c r="H499" t="n">
         <v>17600</v>
@@ -14898,7 +14898,7 @@
         <v>9.85000038146973</v>
       </c>
       <c r="G501" t="n">
-        <v>8.78810024261475</v>
+        <v>8.78810119628906</v>
       </c>
       <c r="H501" t="n">
         <v>18200</v>
@@ -14927,7 +14927,7 @@
         <v>9.85000038146973</v>
       </c>
       <c r="G502" t="n">
-        <v>8.78810024261475</v>
+        <v>8.78810119628906</v>
       </c>
       <c r="H502" t="n">
         <v>0</v>
@@ -14956,7 +14956,7 @@
         <v>9.80000019073486</v>
       </c>
       <c r="G503" t="n">
-        <v>8.74349021911621</v>
+        <v>8.74349117279053</v>
       </c>
       <c r="H503" t="n">
         <v>1800</v>
@@ -14985,7 +14985,7 @@
         <v>9.80000019073486</v>
       </c>
       <c r="G504" t="n">
-        <v>8.74349021911621</v>
+        <v>8.74349117279053</v>
       </c>
       <c r="H504" t="n">
         <v>23000</v>
@@ -15014,7 +15014,7 @@
         <v>9.89999961853027</v>
       </c>
       <c r="G505" t="n">
-        <v>8.83270931243896</v>
+        <v>8.83271026611328</v>
       </c>
       <c r="H505" t="n">
         <v>9600</v>
@@ -15043,7 +15043,7 @@
         <v>9.80000019073486</v>
       </c>
       <c r="G506" t="n">
-        <v>8.74349021911621</v>
+        <v>8.74349117279053</v>
       </c>
       <c r="H506" t="n">
         <v>6800</v>
@@ -15072,7 +15072,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G507" t="n">
-        <v>8.65427207946777</v>
+        <v>8.65427017211914</v>
       </c>
       <c r="H507" t="n">
         <v>12200</v>
@@ -15101,7 +15101,7 @@
         <v>9.80000019073486</v>
       </c>
       <c r="G508" t="n">
-        <v>8.74349021911621</v>
+        <v>8.74349117279053</v>
       </c>
       <c r="H508" t="n">
         <v>1000</v>
@@ -15130,7 +15130,7 @@
         <v>9.89999961853027</v>
       </c>
       <c r="G509" t="n">
-        <v>8.83270931243896</v>
+        <v>8.83271026611328</v>
       </c>
       <c r="H509" t="n">
         <v>1400</v>
@@ -15159,7 +15159,7 @@
         <v>9.85000038146973</v>
       </c>
       <c r="G510" t="n">
-        <v>8.78810024261475</v>
+        <v>8.78810119628906</v>
       </c>
       <c r="H510" t="n">
         <v>5000</v>
@@ -15188,7 +15188,7 @@
         <v>9.80000019073486</v>
       </c>
       <c r="G511" t="n">
-        <v>8.74349021911621</v>
+        <v>8.74349117279053</v>
       </c>
       <c r="H511" t="n">
         <v>1200</v>
@@ -15217,7 +15217,7 @@
         <v>9.80000019073486</v>
       </c>
       <c r="G512" t="n">
-        <v>8.74349021911621</v>
+        <v>8.74349117279053</v>
       </c>
       <c r="H512" t="n">
         <v>21800</v>
@@ -15246,7 +15246,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G513" t="n">
-        <v>8.65427207946777</v>
+        <v>8.65427017211914</v>
       </c>
       <c r="H513" t="n">
         <v>600</v>
@@ -15275,7 +15275,7 @@
         <v>9.64999961853027</v>
       </c>
       <c r="G514" t="n">
-        <v>8.60966014862061</v>
+        <v>8.60966205596924</v>
       </c>
       <c r="H514" t="n">
         <v>10200</v>
@@ -15304,7 +15304,7 @@
         <v>9.64999961853027</v>
       </c>
       <c r="G515" t="n">
-        <v>8.60966014862061</v>
+        <v>8.60966205596924</v>
       </c>
       <c r="H515" t="n">
         <v>3800</v>
@@ -15333,7 +15333,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G516" t="n">
-        <v>8.65427207946777</v>
+        <v>8.65427017211914</v>
       </c>
       <c r="H516" t="n">
         <v>11400</v>
@@ -15362,7 +15362,7 @@
         <v>9.64999961853027</v>
       </c>
       <c r="G517" t="n">
-        <v>8.60966014862061</v>
+        <v>8.60966205596924</v>
       </c>
       <c r="H517" t="n">
         <v>2200</v>
@@ -15391,7 +15391,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G518" t="n">
-        <v>8.65427207946777</v>
+        <v>8.65427017211914</v>
       </c>
       <c r="H518" t="n">
         <v>2600</v>
@@ -15420,7 +15420,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G519" t="n">
-        <v>8.65427207946777</v>
+        <v>8.65427017211914</v>
       </c>
       <c r="H519" t="n">
         <v>0</v>
@@ -15536,7 +15536,7 @@
         <v>9.64999961853027</v>
       </c>
       <c r="G523" t="n">
-        <v>8.60966014862061</v>
+        <v>8.60966205596924</v>
       </c>
       <c r="H523" t="n">
         <v>200</v>
@@ -15565,7 +15565,7 @@
         <v>9.80000019073486</v>
       </c>
       <c r="G524" t="n">
-        <v>8.74349021911621</v>
+        <v>8.74349117279053</v>
       </c>
       <c r="H524" t="n">
         <v>200</v>
@@ -15594,7 +15594,7 @@
         <v>9.80000019073486</v>
       </c>
       <c r="G525" t="n">
-        <v>8.74349021911621</v>
+        <v>8.74349117279053</v>
       </c>
       <c r="H525" t="n">
         <v>6200</v>
@@ -15623,7 +15623,7 @@
         <v>9.64999961853027</v>
       </c>
       <c r="G526" t="n">
-        <v>8.60966014862061</v>
+        <v>8.60966205596924</v>
       </c>
       <c r="H526" t="n">
         <v>4200</v>
@@ -15652,7 +15652,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G527" t="n">
-        <v>8.65427207946777</v>
+        <v>8.65427017211914</v>
       </c>
       <c r="H527" t="n">
         <v>600</v>
@@ -15710,7 +15710,7 @@
         <v>9.5</v>
       </c>
       <c r="G529" t="n">
-        <v>8.47583293914795</v>
+        <v>8.47583389282227</v>
       </c>
       <c r="H529" t="n">
         <v>10600</v>
@@ -15739,7 +15739,7 @@
         <v>9.39999961853027</v>
       </c>
       <c r="G530" t="n">
-        <v>8.3866138458252</v>
+        <v>8.38661289215088</v>
       </c>
       <c r="H530" t="n">
         <v>20000</v>
@@ -15768,7 +15768,7 @@
         <v>9.19999980926514</v>
       </c>
       <c r="G531" t="n">
-        <v>8.20817470550537</v>
+        <v>8.20817565917969</v>
       </c>
       <c r="H531" t="n">
         <v>12800</v>
@@ -15855,7 +15855,7 @@
         <v>8.80000019073486</v>
       </c>
       <c r="G534" t="n">
-        <v>7.85129880905151</v>
+        <v>7.8512978553772</v>
       </c>
       <c r="H534" t="n">
         <v>9600</v>
@@ -15884,7 +15884,7 @@
         <v>8.85000038146973</v>
       </c>
       <c r="G535" t="n">
-        <v>7.89590835571289</v>
+        <v>7.89590740203857</v>
       </c>
       <c r="H535" t="n">
         <v>400</v>
@@ -15913,7 +15913,7 @@
         <v>8.85000038146973</v>
       </c>
       <c r="G536" t="n">
-        <v>7.89590835571289</v>
+        <v>7.89590740203857</v>
       </c>
       <c r="H536" t="n">
         <v>0</v>
@@ -16000,7 +16000,7 @@
         <v>9.10000038146973</v>
       </c>
       <c r="G539" t="n">
-        <v>8.11895656585693</v>
+        <v>8.11895561218262</v>
       </c>
       <c r="H539" t="n">
         <v>2200</v>
@@ -16029,7 +16029,7 @@
         <v>9.19999980926514</v>
       </c>
       <c r="G540" t="n">
-        <v>8.20817470550537</v>
+        <v>8.20817565917969</v>
       </c>
       <c r="H540" t="n">
         <v>2400</v>
@@ -16058,7 +16058,7 @@
         <v>9.19999980926514</v>
       </c>
       <c r="G541" t="n">
-        <v>8.20817470550537</v>
+        <v>8.20817565917969</v>
       </c>
       <c r="H541" t="n">
         <v>0</v>
@@ -16087,7 +16087,7 @@
         <v>9.19999980926514</v>
       </c>
       <c r="G542" t="n">
-        <v>8.20817470550537</v>
+        <v>8.20817565917969</v>
       </c>
       <c r="H542" t="n">
         <v>0</v>
@@ -16116,7 +16116,7 @@
         <v>9.10000038146973</v>
       </c>
       <c r="G543" t="n">
-        <v>8.11895656585693</v>
+        <v>8.11895561218262</v>
       </c>
       <c r="H543" t="n">
         <v>2000</v>
@@ -16145,7 +16145,7 @@
         <v>9.10000038146973</v>
       </c>
       <c r="G544" t="n">
-        <v>8.11895656585693</v>
+        <v>8.11895561218262</v>
       </c>
       <c r="H544" t="n">
         <v>0</v>
@@ -16174,7 +16174,7 @@
         <v>9.10000038146973</v>
       </c>
       <c r="G545" t="n">
-        <v>8.11895656585693</v>
+        <v>8.11895561218262</v>
       </c>
       <c r="H545" t="n">
         <v>0</v>
@@ -16232,7 +16232,7 @@
         <v>8.85000038146973</v>
       </c>
       <c r="G547" t="n">
-        <v>7.89590835571289</v>
+        <v>7.89590740203857</v>
       </c>
       <c r="H547" t="n">
         <v>5200</v>
@@ -16261,7 +16261,7 @@
         <v>8.85000038146973</v>
       </c>
       <c r="G548" t="n">
-        <v>7.89590835571289</v>
+        <v>7.89590740203857</v>
       </c>
       <c r="H548" t="n">
         <v>10200</v>
@@ -16290,7 +16290,7 @@
         <v>8.85000038146973</v>
       </c>
       <c r="G549" t="n">
-        <v>7.89590835571289</v>
+        <v>7.89590740203857</v>
       </c>
       <c r="H549" t="n">
         <v>0</v>
@@ -16319,7 +16319,7 @@
         <v>8.85000038146973</v>
       </c>
       <c r="G550" t="n">
-        <v>7.89590835571289</v>
+        <v>7.89590740203857</v>
       </c>
       <c r="H550" t="n">
         <v>0</v>
@@ -16348,7 +16348,7 @@
         <v>8.80000019073486</v>
       </c>
       <c r="G551" t="n">
-        <v>7.85129880905151</v>
+        <v>7.8512978553772</v>
       </c>
       <c r="H551" t="n">
         <v>13400</v>
@@ -16377,7 +16377,7 @@
         <v>8.80000019073486</v>
       </c>
       <c r="G552" t="n">
-        <v>7.85129880905151</v>
+        <v>7.8512978553772</v>
       </c>
       <c r="H552" t="n">
         <v>0</v>
@@ -16406,7 +16406,7 @@
         <v>8.75</v>
       </c>
       <c r="G553" t="n">
-        <v>7.80668973922729</v>
+        <v>7.80668878555298</v>
       </c>
       <c r="H553" t="n">
         <v>1400</v>
@@ -16435,7 +16435,7 @@
         <v>8.75</v>
       </c>
       <c r="G554" t="n">
-        <v>7.80668973922729</v>
+        <v>7.80668878555298</v>
       </c>
       <c r="H554" t="n">
         <v>0</v>
@@ -16464,7 +16464,7 @@
         <v>8.75</v>
       </c>
       <c r="G555" t="n">
-        <v>7.80668973922729</v>
+        <v>7.80668878555298</v>
       </c>
       <c r="H555" t="n">
         <v>0</v>
@@ -16493,7 +16493,7 @@
         <v>9.14999961853027</v>
       </c>
       <c r="G556" t="n">
-        <v>8.16356468200684</v>
+        <v>8.16356563568115</v>
       </c>
       <c r="H556" t="n">
         <v>20400</v>
@@ -16522,7 +16522,7 @@
         <v>9.05000019073486</v>
       </c>
       <c r="G557" t="n">
-        <v>8.07434749603271</v>
+        <v>8.07434558868408</v>
       </c>
       <c r="H557" t="n">
         <v>11600</v>
@@ -16696,7 +16696,7 @@
         <v>9.64999961853027</v>
       </c>
       <c r="G563" t="n">
-        <v>8.60966014862061</v>
+        <v>8.60966205596924</v>
       </c>
       <c r="H563" t="n">
         <v>3200</v>
@@ -16841,7 +16841,7 @@
         <v>9.64999961853027</v>
       </c>
       <c r="G568" t="n">
-        <v>8.60966014862061</v>
+        <v>8.60966205596924</v>
       </c>
       <c r="H568" t="n">
         <v>10000</v>
@@ -16986,7 +16986,7 @@
         <v>9.64999961853027</v>
       </c>
       <c r="G573" t="n">
-        <v>8.60966014862061</v>
+        <v>8.60966205596924</v>
       </c>
       <c r="H573" t="n">
         <v>5600</v>
@@ -17015,7 +17015,7 @@
         <v>9.64999961853027</v>
       </c>
       <c r="G574" t="n">
-        <v>8.60966014862061</v>
+        <v>8.60966205596924</v>
       </c>
       <c r="H574" t="n">
         <v>8200</v>
@@ -17044,7 +17044,7 @@
         <v>9.64999961853027</v>
       </c>
       <c r="G575" t="n">
-        <v>8.60966014862061</v>
+        <v>8.60966205596924</v>
       </c>
       <c r="H575" t="n">
         <v>17800</v>
@@ -17073,7 +17073,7 @@
         <v>9.64999961853027</v>
       </c>
       <c r="G576" t="n">
-        <v>8.60966014862061</v>
+        <v>8.60966205596924</v>
       </c>
       <c r="H576" t="n">
         <v>13800</v>
@@ -17102,7 +17102,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G577" t="n">
-        <v>8.65427207946777</v>
+        <v>8.65427017211914</v>
       </c>
       <c r="H577" t="n">
         <v>17200</v>
@@ -17131,7 +17131,7 @@
         <v>9.80000019073486</v>
       </c>
       <c r="G578" t="n">
-        <v>8.74349021911621</v>
+        <v>8.74349117279053</v>
       </c>
       <c r="H578" t="n">
         <v>5200</v>
@@ -17160,7 +17160,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G579" t="n">
-        <v>8.65427207946777</v>
+        <v>8.65427017211914</v>
       </c>
       <c r="H579" t="n">
         <v>32400</v>
@@ -17189,7 +17189,7 @@
         <v>9.80000019073486</v>
       </c>
       <c r="G580" t="n">
-        <v>8.74349021911621</v>
+        <v>8.74349117279053</v>
       </c>
       <c r="H580" t="n">
         <v>9800</v>
@@ -17218,7 +17218,7 @@
         <v>9.80000019073486</v>
       </c>
       <c r="G581" t="n">
-        <v>8.74349021911621</v>
+        <v>8.74349117279053</v>
       </c>
       <c r="H581" t="n">
         <v>21200</v>
@@ -17247,7 +17247,7 @@
         <v>9.85000038146973</v>
       </c>
       <c r="G582" t="n">
-        <v>8.78810024261475</v>
+        <v>8.78810119628906</v>
       </c>
       <c r="H582" t="n">
         <v>35600</v>
@@ -17276,7 +17276,7 @@
         <v>9.85000038146973</v>
       </c>
       <c r="G583" t="n">
-        <v>8.78810024261475</v>
+        <v>8.78810119628906</v>
       </c>
       <c r="H583" t="n">
         <v>3600</v>
@@ -17305,7 +17305,7 @@
         <v>9.89999961853027</v>
       </c>
       <c r="G584" t="n">
-        <v>8.83270931243896</v>
+        <v>8.83271026611328</v>
       </c>
       <c r="H584" t="n">
         <v>15800</v>
@@ -17334,7 +17334,7 @@
         <v>9.85000038146973</v>
       </c>
       <c r="G585" t="n">
-        <v>8.78810024261475</v>
+        <v>8.78810119628906</v>
       </c>
       <c r="H585" t="n">
         <v>121400</v>
@@ -17363,7 +17363,7 @@
         <v>9.85000038146973</v>
       </c>
       <c r="G586" t="n">
-        <v>8.78810024261475</v>
+        <v>8.78810119628906</v>
       </c>
       <c r="H586" t="n">
         <v>6200</v>
@@ -17392,7 +17392,7 @@
         <v>9.85000038146973</v>
       </c>
       <c r="G587" t="n">
-        <v>8.78810024261475</v>
+        <v>8.78810119628906</v>
       </c>
       <c r="H587" t="n">
         <v>19200</v>
@@ -17421,7 +17421,7 @@
         <v>9.85000038146973</v>
       </c>
       <c r="G588" t="n">
-        <v>8.78810024261475</v>
+        <v>8.78810119628906</v>
       </c>
       <c r="H588" t="n">
         <v>2600</v>
@@ -18117,7 +18117,7 @@
         <v>10.3000001907349</v>
       </c>
       <c r="G612" t="n">
-        <v>9.18958759307861</v>
+        <v>9.18958854675293</v>
       </c>
       <c r="H612" t="n">
         <v>24600</v>
@@ -18175,7 +18175,7 @@
         <v>10.3000001907349</v>
       </c>
       <c r="G614" t="n">
-        <v>9.18958759307861</v>
+        <v>9.18958854675293</v>
       </c>
       <c r="H614" t="n">
         <v>6800</v>
@@ -18204,7 +18204,7 @@
         <v>10.3999996185303</v>
       </c>
       <c r="G615" t="n">
-        <v>9.27880573272705</v>
+        <v>9.27880668640137</v>
       </c>
       <c r="H615" t="n">
         <v>14600</v>
@@ -18233,7 +18233,7 @@
         <v>10.3999996185303</v>
       </c>
       <c r="G616" t="n">
-        <v>9.27880573272705</v>
+        <v>9.27880668640137</v>
       </c>
       <c r="H616" t="n">
         <v>13600</v>
@@ -18291,7 +18291,7 @@
         <v>10.5</v>
       </c>
       <c r="G618" t="n">
-        <v>9.36802673339844</v>
+        <v>9.36802577972412</v>
       </c>
       <c r="H618" t="n">
         <v>26400</v>
@@ -18320,7 +18320,7 @@
         <v>10.5</v>
       </c>
       <c r="G619" t="n">
-        <v>9.36802673339844</v>
+        <v>9.36802577972412</v>
       </c>
       <c r="H619" t="n">
         <v>76800</v>
@@ -18407,7 +18407,7 @@
         <v>10.6000003814697</v>
       </c>
       <c r="G622" t="n">
-        <v>9.45724487304688</v>
+        <v>9.45724582672119</v>
       </c>
       <c r="H622" t="n">
         <v>19200</v>
@@ -18436,7 +18436,7 @@
         <v>10.5</v>
       </c>
       <c r="G623" t="n">
-        <v>9.36802673339844</v>
+        <v>9.36802577972412</v>
       </c>
       <c r="H623" t="n">
         <v>39400</v>
@@ -18465,7 +18465,7 @@
         <v>10.3999996185303</v>
       </c>
       <c r="G624" t="n">
-        <v>9.27880573272705</v>
+        <v>9.27880668640137</v>
       </c>
       <c r="H624" t="n">
         <v>6000</v>
@@ -18494,7 +18494,7 @@
         <v>10.3999996185303</v>
       </c>
       <c r="G625" t="n">
-        <v>9.27880573272705</v>
+        <v>9.27880668640137</v>
       </c>
       <c r="H625" t="n">
         <v>3600</v>
@@ -18523,7 +18523,7 @@
         <v>10.5</v>
       </c>
       <c r="G626" t="n">
-        <v>9.36802673339844</v>
+        <v>9.36802577972412</v>
       </c>
       <c r="H626" t="n">
         <v>18800</v>
@@ -18552,7 +18552,7 @@
         <v>10.5</v>
       </c>
       <c r="G627" t="n">
-        <v>9.36802673339844</v>
+        <v>9.36802577972412</v>
       </c>
       <c r="H627" t="n">
         <v>17400</v>
@@ -18581,7 +18581,7 @@
         <v>10.5</v>
       </c>
       <c r="G628" t="n">
-        <v>9.36802673339844</v>
+        <v>9.36802577972412</v>
       </c>
       <c r="H628" t="n">
         <v>5800</v>
@@ -18610,7 +18610,7 @@
         <v>10.5</v>
       </c>
       <c r="G629" t="n">
-        <v>9.36802673339844</v>
+        <v>9.36802577972412</v>
       </c>
       <c r="H629" t="n">
         <v>11400</v>
@@ -18639,7 +18639,7 @@
         <v>10.5</v>
       </c>
       <c r="G630" t="n">
-        <v>9.36802673339844</v>
+        <v>9.36802577972412</v>
       </c>
       <c r="H630" t="n">
         <v>5800</v>
@@ -18668,7 +18668,7 @@
         <v>10.5</v>
       </c>
       <c r="G631" t="n">
-        <v>9.36802673339844</v>
+        <v>9.36802577972412</v>
       </c>
       <c r="H631" t="n">
         <v>2600</v>
@@ -18697,7 +18697,7 @@
         <v>10.3999996185303</v>
       </c>
       <c r="G632" t="n">
-        <v>9.27880573272705</v>
+        <v>9.27880668640137</v>
       </c>
       <c r="H632" t="n">
         <v>4600</v>
@@ -18726,7 +18726,7 @@
         <v>10.5</v>
       </c>
       <c r="G633" t="n">
-        <v>9.36802673339844</v>
+        <v>9.36802577972412</v>
       </c>
       <c r="H633" t="n">
         <v>32552</v>
@@ -18755,7 +18755,7 @@
         <v>10.5</v>
       </c>
       <c r="G634" t="n">
-        <v>9.36802673339844</v>
+        <v>9.36802577972412</v>
       </c>
       <c r="H634" t="n">
         <v>38554</v>
@@ -18784,7 +18784,7 @@
         <v>10.3999996185303</v>
       </c>
       <c r="G635" t="n">
-        <v>9.27880573272705</v>
+        <v>9.27880668640137</v>
       </c>
       <c r="H635" t="n">
         <v>26940</v>
@@ -18813,7 +18813,7 @@
         <v>10.5</v>
       </c>
       <c r="G636" t="n">
-        <v>9.36802673339844</v>
+        <v>9.36802577972412</v>
       </c>
       <c r="H636" t="n">
         <v>4300</v>
@@ -18842,7 +18842,7 @@
         <v>10.5</v>
       </c>
       <c r="G637" t="n">
-        <v>9.36802673339844</v>
+        <v>9.36802577972412</v>
       </c>
       <c r="H637" t="n">
         <v>18422</v>
@@ -18871,7 +18871,7 @@
         <v>10.3999996185303</v>
       </c>
       <c r="G638" t="n">
-        <v>9.27880573272705</v>
+        <v>9.27880668640137</v>
       </c>
       <c r="H638" t="n">
         <v>20479</v>
@@ -18900,7 +18900,7 @@
         <v>10.5</v>
       </c>
       <c r="G639" t="n">
-        <v>9.36802673339844</v>
+        <v>9.36802577972412</v>
       </c>
       <c r="H639" t="n">
         <v>14946</v>
@@ -18929,7 +18929,7 @@
         <v>10.3999996185303</v>
       </c>
       <c r="G640" t="n">
-        <v>9.27880573272705</v>
+        <v>9.27880668640137</v>
       </c>
       <c r="H640" t="n">
         <v>20526</v>
@@ -18958,7 +18958,7 @@
         <v>10.3999996185303</v>
       </c>
       <c r="G641" t="n">
-        <v>9.27880573272705</v>
+        <v>9.27880668640137</v>
       </c>
       <c r="H641" t="n">
         <v>16273</v>
@@ -18987,7 +18987,7 @@
         <v>10.3999996185303</v>
       </c>
       <c r="G642" t="n">
-        <v>9.27880573272705</v>
+        <v>9.27880668640137</v>
       </c>
       <c r="H642" t="n">
         <v>24392</v>
@@ -19016,7 +19016,7 @@
         <v>10.3000001907349</v>
       </c>
       <c r="G643" t="n">
-        <v>9.18958759307861</v>
+        <v>9.18958854675293</v>
       </c>
       <c r="H643" t="n">
         <v>13916</v>
@@ -19074,7 +19074,7 @@
         <v>10.1999998092651</v>
       </c>
       <c r="G645" t="n">
-        <v>9.18958759307861</v>
+        <v>9.18958854675293</v>
       </c>
       <c r="H645" t="n">
         <v>17435</v>
@@ -19103,7 +19103,7 @@
         <v>10.1000003814697</v>
       </c>
       <c r="G646" t="n">
-        <v>9.09949398040771</v>
+        <v>9.0994930267334</v>
       </c>
       <c r="H646" t="n">
         <v>3279</v>
@@ -19161,7 +19161,7 @@
         <v>10.1000003814697</v>
       </c>
       <c r="G648" t="n">
-        <v>9.09949398040771</v>
+        <v>9.0994930267334</v>
       </c>
       <c r="H648" t="n">
         <v>8142</v>
@@ -19190,7 +19190,7 @@
         <v>10</v>
       </c>
       <c r="G649" t="n">
-        <v>9.00939846038818</v>
+        <v>9.0093994140625</v>
       </c>
       <c r="H649" t="n">
         <v>8239</v>
@@ -19219,7 +19219,7 @@
         <v>10</v>
       </c>
       <c r="G650" t="n">
-        <v>9.00939846038818</v>
+        <v>9.0093994140625</v>
       </c>
       <c r="H650" t="n">
         <v>1359</v>
@@ -19248,7 +19248,7 @@
         <v>10</v>
       </c>
       <c r="G651" t="n">
-        <v>9.00939846038818</v>
+        <v>9.0093994140625</v>
       </c>
       <c r="H651" t="n">
         <v>1881</v>
@@ -19277,7 +19277,7 @@
         <v>10</v>
       </c>
       <c r="G652" t="n">
-        <v>9.00939846038818</v>
+        <v>9.0093994140625</v>
       </c>
       <c r="H652" t="n">
         <v>5346</v>
@@ -19306,7 +19306,7 @@
         <v>10</v>
       </c>
       <c r="G653" t="n">
-        <v>9.00939846038818</v>
+        <v>9.0093994140625</v>
       </c>
       <c r="H653" t="n">
         <v>5847</v>
@@ -19335,7 +19335,7 @@
         <v>10.1000003814697</v>
       </c>
       <c r="G654" t="n">
-        <v>9.09949398040771</v>
+        <v>9.0994930267334</v>
       </c>
       <c r="H654" t="n">
         <v>20832</v>
@@ -19364,7 +19364,7 @@
         <v>10</v>
       </c>
       <c r="G655" t="n">
-        <v>9.00939846038818</v>
+        <v>9.0093994140625</v>
       </c>
       <c r="H655" t="n">
         <v>6200</v>
@@ -19393,7 +19393,7 @@
         <v>10</v>
       </c>
       <c r="G656" t="n">
-        <v>9.00939846038818</v>
+        <v>9.0093994140625</v>
       </c>
       <c r="H656" t="n">
         <v>4396</v>
@@ -19422,7 +19422,7 @@
         <v>10</v>
       </c>
       <c r="G657" t="n">
-        <v>9.00939846038818</v>
+        <v>9.0093994140625</v>
       </c>
       <c r="H657" t="n">
         <v>252</v>
@@ -19451,7 +19451,7 @@
         <v>10</v>
       </c>
       <c r="G658" t="n">
-        <v>9.00939846038818</v>
+        <v>9.0093994140625</v>
       </c>
       <c r="H658" t="n">
         <v>97</v>
@@ -19480,7 +19480,7 @@
         <v>10.1000003814697</v>
       </c>
       <c r="G659" t="n">
-        <v>9.09949398040771</v>
+        <v>9.0994930267334</v>
       </c>
       <c r="H659" t="n">
         <v>600</v>
@@ -19509,7 +19509,7 @@
         <v>10.1000003814697</v>
       </c>
       <c r="G660" t="n">
-        <v>9.09949398040771</v>
+        <v>9.0994930267334</v>
       </c>
       <c r="H660" t="n">
         <v>933</v>
@@ -19538,7 +19538,7 @@
         <v>10.1000003814697</v>
       </c>
       <c r="G661" t="n">
-        <v>9.09949398040771</v>
+        <v>9.0994930267334</v>
       </c>
       <c r="H661" t="n">
         <v>4319</v>
@@ -19567,7 +19567,7 @@
         <v>10</v>
       </c>
       <c r="G662" t="n">
-        <v>9.00939846038818</v>
+        <v>9.0093994140625</v>
       </c>
       <c r="H662" t="n">
         <v>3769</v>
@@ -19596,7 +19596,7 @@
         <v>10.1000003814697</v>
       </c>
       <c r="G663" t="n">
-        <v>9.09949398040771</v>
+        <v>9.0994930267334</v>
       </c>
       <c r="H663" t="n">
         <v>12669</v>
@@ -19625,7 +19625,7 @@
         <v>10.1000003814697</v>
       </c>
       <c r="G664" t="n">
-        <v>9.09949398040771</v>
+        <v>9.0994930267334</v>
       </c>
       <c r="H664" t="n">
         <v>11554</v>
@@ -19654,7 +19654,7 @@
         <v>10.1000003814697</v>
       </c>
       <c r="G665" t="n">
-        <v>9.09949398040771</v>
+        <v>9.0994930267334</v>
       </c>
       <c r="H665" t="n">
         <v>9780</v>
@@ -19683,7 +19683,7 @@
         <v>10.1000003814697</v>
       </c>
       <c r="G666" t="n">
-        <v>9.09949398040771</v>
+        <v>9.0994930267334</v>
       </c>
       <c r="H666" t="n">
         <v>1066</v>
@@ -19712,7 +19712,7 @@
         <v>10.1000003814697</v>
       </c>
       <c r="G667" t="n">
-        <v>9.09949398040771</v>
+        <v>9.0994930267334</v>
       </c>
       <c r="H667" t="n">
         <v>3333</v>
@@ -19741,7 +19741,7 @@
         <v>10.1000003814697</v>
       </c>
       <c r="G668" t="n">
-        <v>9.09949398040771</v>
+        <v>9.0994930267334</v>
       </c>
       <c r="H668" t="n">
         <v>1001</v>
@@ -19770,7 +19770,7 @@
         <v>10</v>
       </c>
       <c r="G669" t="n">
-        <v>9.00939846038818</v>
+        <v>9.0093994140625</v>
       </c>
       <c r="H669" t="n">
         <v>9000</v>
@@ -19799,7 +19799,7 @@
         <v>10.1000003814697</v>
       </c>
       <c r="G670" t="n">
-        <v>9.09949398040771</v>
+        <v>9.0994930267334</v>
       </c>
       <c r="H670" t="n">
         <v>1307</v>
@@ -19828,7 +19828,7 @@
         <v>10.1000003814697</v>
       </c>
       <c r="G671" t="n">
-        <v>9.09949398040771</v>
+        <v>9.0994930267334</v>
       </c>
       <c r="H671" t="n">
         <v>1333</v>
@@ -19857,7 +19857,7 @@
         <v>9.89999961853027</v>
       </c>
       <c r="G672" t="n">
-        <v>8.91930389404297</v>
+        <v>8.91930484771729</v>
       </c>
       <c r="H672" t="n">
         <v>2834</v>
@@ -19973,7 +19973,7 @@
         <v>10</v>
       </c>
       <c r="G676" t="n">
-        <v>9.00939846038818</v>
+        <v>9.0093994140625</v>
       </c>
       <c r="H676" t="n">
         <v>8425</v>
@@ -20002,7 +20002,7 @@
         <v>10</v>
       </c>
       <c r="G677" t="n">
-        <v>9.00939846038818</v>
+        <v>9.0093994140625</v>
       </c>
       <c r="H677" t="n">
         <v>0</v>
@@ -20031,7 +20031,7 @@
         <v>10</v>
       </c>
       <c r="G678" t="n">
-        <v>9.00939846038818</v>
+        <v>9.0093994140625</v>
       </c>
       <c r="H678" t="n">
         <v>1967</v>
@@ -20060,7 +20060,7 @@
         <v>10</v>
       </c>
       <c r="G679" t="n">
-        <v>9.00939846038818</v>
+        <v>9.0093994140625</v>
       </c>
       <c r="H679" t="n">
         <v>1008</v>
@@ -20089,7 +20089,7 @@
         <v>10</v>
       </c>
       <c r="G680" t="n">
-        <v>9.00939846038818</v>
+        <v>9.0093994140625</v>
       </c>
       <c r="H680" t="n">
         <v>9553</v>
@@ -20118,7 +20118,7 @@
         <v>9.89999961853027</v>
       </c>
       <c r="G681" t="n">
-        <v>8.91930389404297</v>
+        <v>8.91930484771729</v>
       </c>
       <c r="H681" t="n">
         <v>17800</v>
@@ -20234,7 +20234,7 @@
         <v>9.89999961853027</v>
       </c>
       <c r="G685" t="n">
-        <v>8.91930389404297</v>
+        <v>8.91930484771729</v>
       </c>
       <c r="H685" t="n">
         <v>1637</v>
@@ -20292,7 +20292,7 @@
         <v>10.1999998092651</v>
       </c>
       <c r="G687" t="n">
-        <v>9.18958759307861</v>
+        <v>9.18958854675293</v>
       </c>
       <c r="H687" t="n">
         <v>307</v>
@@ -20379,7 +20379,7 @@
         <v>10.1000003814697</v>
       </c>
       <c r="G690" t="n">
-        <v>9.09949398040771</v>
+        <v>9.0994930267334</v>
       </c>
       <c r="H690" t="n">
         <v>16801</v>
@@ -20408,7 +20408,7 @@
         <v>10.1000003814697</v>
       </c>
       <c r="G691" t="n">
-        <v>9.09949398040771</v>
+        <v>9.0994930267334</v>
       </c>
       <c r="H691" t="n">
         <v>350</v>
@@ -20437,7 +20437,7 @@
         <v>10</v>
       </c>
       <c r="G692" t="n">
-        <v>9.00939846038818</v>
+        <v>9.0093994140625</v>
       </c>
       <c r="H692" t="n">
         <v>666</v>
@@ -20466,7 +20466,7 @@
         <v>10</v>
       </c>
       <c r="G693" t="n">
-        <v>9.00939846038818</v>
+        <v>9.0093994140625</v>
       </c>
       <c r="H693" t="n">
         <v>634</v>
@@ -20495,7 +20495,7 @@
         <v>10.1000003814697</v>
       </c>
       <c r="G694" t="n">
-        <v>9.09949398040771</v>
+        <v>9.0994930267334</v>
       </c>
       <c r="H694" t="n">
         <v>610</v>
@@ -20524,7 +20524,7 @@
         <v>10.1000003814697</v>
       </c>
       <c r="G695" t="n">
-        <v>9.09949398040771</v>
+        <v>9.0994930267334</v>
       </c>
       <c r="H695" t="n">
         <v>1890</v>
@@ -20553,7 +20553,7 @@
         <v>10.1999998092651</v>
       </c>
       <c r="G696" t="n">
-        <v>9.18958759307861</v>
+        <v>9.18958854675293</v>
       </c>
       <c r="H696" t="n">
         <v>100</v>
@@ -20582,7 +20582,7 @@
         <v>10</v>
       </c>
       <c r="G697" t="n">
-        <v>9.00939846038818</v>
+        <v>9.0093994140625</v>
       </c>
       <c r="H697" t="n">
         <v>21791</v>
@@ -20640,7 +20640,7 @@
         <v>10</v>
       </c>
       <c r="G699" t="n">
-        <v>9.00939846038818</v>
+        <v>9.0093994140625</v>
       </c>
       <c r="H699" t="n">
         <v>10723</v>
@@ -20669,7 +20669,7 @@
         <v>10</v>
       </c>
       <c r="G700" t="n">
-        <v>9.00939846038818</v>
+        <v>9.0093994140625</v>
       </c>
       <c r="H700" t="n">
         <v>935</v>
@@ -20698,7 +20698,7 @@
         <v>10</v>
       </c>
       <c r="G701" t="n">
-        <v>9.00939846038818</v>
+        <v>9.0093994140625</v>
       </c>
       <c r="H701" t="n">
         <v>18421</v>
@@ -20727,7 +20727,7 @@
         <v>10</v>
       </c>
       <c r="G702" t="n">
-        <v>9.00939846038818</v>
+        <v>9.0093994140625</v>
       </c>
       <c r="H702" t="n">
         <v>13847</v>
@@ -20756,7 +20756,7 @@
         <v>9.89999961853027</v>
       </c>
       <c r="G703" t="n">
-        <v>8.91930389404297</v>
+        <v>8.91930484771729</v>
       </c>
       <c r="H703" t="n">
         <v>35</v>
@@ -20785,7 +20785,7 @@
         <v>10</v>
       </c>
       <c r="G704" t="n">
-        <v>9.00939846038818</v>
+        <v>9.0093994140625</v>
       </c>
       <c r="H704" t="n">
         <v>417</v>
@@ -20930,7 +20930,7 @@
         <v>10</v>
       </c>
       <c r="G709" t="n">
-        <v>9.00939846038818</v>
+        <v>9.0093994140625</v>
       </c>
       <c r="H709" t="n">
         <v>11574</v>
@@ -20959,7 +20959,7 @@
         <v>10</v>
       </c>
       <c r="G710" t="n">
-        <v>9.00939846038818</v>
+        <v>9.0093994140625</v>
       </c>
       <c r="H710" t="n">
         <v>11313</v>
@@ -20988,7 +20988,7 @@
         <v>10</v>
       </c>
       <c r="G711" t="n">
-        <v>9.00939846038818</v>
+        <v>9.0093994140625</v>
       </c>
       <c r="H711" t="n">
         <v>2011</v>
@@ -21046,7 +21046,7 @@
         <v>10</v>
       </c>
       <c r="G713" t="n">
-        <v>9.00939846038818</v>
+        <v>9.0093994140625</v>
       </c>
       <c r="H713" t="n">
         <v>3561</v>
@@ -21075,7 +21075,7 @@
         <v>10</v>
       </c>
       <c r="G714" t="n">
-        <v>9.00939846038818</v>
+        <v>9.0093994140625</v>
       </c>
       <c r="H714" t="n">
         <v>370</v>
@@ -21162,7 +21162,7 @@
         <v>10</v>
       </c>
       <c r="G717" t="n">
-        <v>9.00939846038818</v>
+        <v>9.0093994140625</v>
       </c>
       <c r="H717" t="n">
         <v>4760</v>
@@ -21191,7 +21191,7 @@
         <v>10</v>
       </c>
       <c r="G718" t="n">
-        <v>9.00939846038818</v>
+        <v>9.0093994140625</v>
       </c>
       <c r="H718" t="n">
         <v>100</v>
@@ -21220,7 +21220,7 @@
         <v>9.89999961853027</v>
       </c>
       <c r="G719" t="n">
-        <v>8.91930389404297</v>
+        <v>8.91930484771729</v>
       </c>
       <c r="H719" t="n">
         <v>200</v>
@@ -21249,7 +21249,7 @@
         <v>9.89999961853027</v>
       </c>
       <c r="G720" t="n">
-        <v>8.91930389404297</v>
+        <v>8.91930484771729</v>
       </c>
       <c r="H720" t="n">
         <v>0</v>
@@ -21278,7 +21278,7 @@
         <v>10.1000003814697</v>
       </c>
       <c r="G721" t="n">
-        <v>9.09949398040771</v>
+        <v>9.0994930267334</v>
       </c>
       <c r="H721" t="n">
         <v>6432</v>
@@ -21307,7 +21307,7 @@
         <v>10.1999998092651</v>
       </c>
       <c r="G722" t="n">
-        <v>9.18958759307861</v>
+        <v>9.18958854675293</v>
       </c>
       <c r="H722" t="n">
         <v>2060</v>
@@ -21336,7 +21336,7 @@
         <v>10.1000003814697</v>
       </c>
       <c r="G723" t="n">
-        <v>9.09949398040771</v>
+        <v>9.0994930267334</v>
       </c>
       <c r="H723" t="n">
         <v>1050</v>
@@ -21365,7 +21365,7 @@
         <v>10</v>
       </c>
       <c r="G724" t="n">
-        <v>9.00939846038818</v>
+        <v>9.0093994140625</v>
       </c>
       <c r="H724" t="n">
         <v>997</v>
@@ -21394,7 +21394,7 @@
         <v>10</v>
       </c>
       <c r="G725" t="n">
-        <v>9.00939846038818</v>
+        <v>9.0093994140625</v>
       </c>
       <c r="H725" t="n">
         <v>1</v>
@@ -21423,7 +21423,7 @@
         <v>10</v>
       </c>
       <c r="G726" t="n">
-        <v>9.00939846038818</v>
+        <v>9.0093994140625</v>
       </c>
       <c r="H726" t="n">
         <v>0</v>
@@ -21452,7 +21452,7 @@
         <v>10</v>
       </c>
       <c r="G727" t="n">
-        <v>9.00939846038818</v>
+        <v>9.0093994140625</v>
       </c>
       <c r="H727" t="n">
         <v>1455</v>
@@ -21481,7 +21481,7 @@
         <v>10</v>
       </c>
       <c r="G728" t="n">
-        <v>9.00939846038818</v>
+        <v>9.0093994140625</v>
       </c>
       <c r="H728" t="n">
         <v>500</v>
@@ -21510,7 +21510,7 @@
         <v>10</v>
       </c>
       <c r="G729" t="n">
-        <v>9.00939846038818</v>
+        <v>9.0093994140625</v>
       </c>
       <c r="H729" t="n">
         <v>541</v>
@@ -21539,7 +21539,7 @@
         <v>10</v>
       </c>
       <c r="G730" t="n">
-        <v>9.00939846038818</v>
+        <v>9.0093994140625</v>
       </c>
       <c r="H730" t="n">
         <v>0</v>
@@ -21568,7 +21568,7 @@
         <v>10.1000003814697</v>
       </c>
       <c r="G731" t="n">
-        <v>9.09949398040771</v>
+        <v>9.0994930267334</v>
       </c>
       <c r="H731" t="n">
         <v>200</v>
@@ -21626,7 +21626,7 @@
         <v>10.1000003814697</v>
       </c>
       <c r="G733" t="n">
-        <v>9.09949398040771</v>
+        <v>9.0994930267334</v>
       </c>
       <c r="H733" t="n">
         <v>12534</v>
@@ -21655,7 +21655,7 @@
         <v>10.1000003814697</v>
       </c>
       <c r="G734" t="n">
-        <v>9.09949398040771</v>
+        <v>9.0994930267334</v>
       </c>
       <c r="H734" t="n">
         <v>850</v>
@@ -21713,7 +21713,7 @@
         <v>10</v>
       </c>
       <c r="G736" t="n">
-        <v>9.00939846038818</v>
+        <v>9.0093994140625</v>
       </c>
       <c r="H736" t="n">
         <v>4145</v>
@@ -21771,7 +21771,7 @@
         <v>10</v>
       </c>
       <c r="G738" t="n">
-        <v>9.00939846038818</v>
+        <v>9.0093994140625</v>
       </c>
       <c r="H738" t="n">
         <v>8175</v>
@@ -21800,7 +21800,7 @@
         <v>10</v>
       </c>
       <c r="G739" t="n">
-        <v>9.00939846038818</v>
+        <v>9.0093994140625</v>
       </c>
       <c r="H739" t="n">
         <v>9256</v>
@@ -21829,7 +21829,7 @@
         <v>10.1999998092651</v>
       </c>
       <c r="G740" t="n">
-        <v>9.18958759307861</v>
+        <v>9.18958854675293</v>
       </c>
       <c r="H740" t="n">
         <v>10666</v>
@@ -21858,7 +21858,7 @@
         <v>10.1999998092651</v>
       </c>
       <c r="G741" t="n">
-        <v>9.18958759307861</v>
+        <v>9.18958854675293</v>
       </c>
       <c r="H741" t="n">
         <v>27063</v>
@@ -21945,7 +21945,7 @@
         <v>10.1999998092651</v>
       </c>
       <c r="G744" t="n">
-        <v>9.18958759307861</v>
+        <v>9.18958854675293</v>
       </c>
       <c r="H744" t="n">
         <v>1531</v>
@@ -21974,7 +21974,7 @@
         <v>10.1999998092651</v>
       </c>
       <c r="G745" t="n">
-        <v>9.18958759307861</v>
+        <v>9.18958854675293</v>
       </c>
       <c r="H745" t="n">
         <v>6590</v>
@@ -22003,7 +22003,7 @@
         <v>10.1000003814697</v>
       </c>
       <c r="G746" t="n">
-        <v>9.09949398040771</v>
+        <v>9.0994930267334</v>
       </c>
       <c r="H746" t="n">
         <v>17350</v>
@@ -22032,7 +22032,7 @@
         <v>10.1999998092651</v>
       </c>
       <c r="G747" t="n">
-        <v>9.18958759307861</v>
+        <v>9.18958854675293</v>
       </c>
       <c r="H747" t="n">
         <v>20523</v>
@@ -22061,7 +22061,7 @@
         <v>10.1999998092651</v>
       </c>
       <c r="G748" t="n">
-        <v>9.18958759307861</v>
+        <v>9.18958854675293</v>
       </c>
       <c r="H748" t="n">
         <v>4747</v>
@@ -22090,7 +22090,7 @@
         <v>10.1999998092651</v>
       </c>
       <c r="G749" t="n">
-        <v>9.18958759307861</v>
+        <v>9.18958854675293</v>
       </c>
       <c r="H749" t="n">
         <v>1702</v>
@@ -22119,7 +22119,7 @@
         <v>10.1999998092651</v>
       </c>
       <c r="G750" t="n">
-        <v>9.18958759307861</v>
+        <v>9.18958854675293</v>
       </c>
       <c r="H750" t="n">
         <v>10549</v>
@@ -22148,7 +22148,7 @@
         <v>10.1000003814697</v>
       </c>
       <c r="G751" t="n">
-        <v>9.09949398040771</v>
+        <v>9.0994930267334</v>
       </c>
       <c r="H751" t="n">
         <v>2450</v>
@@ -22177,7 +22177,7 @@
         <v>10.1999998092651</v>
       </c>
       <c r="G752" t="n">
-        <v>9.18958759307861</v>
+        <v>9.18958854675293</v>
       </c>
       <c r="H752" t="n">
         <v>5228</v>
@@ -22264,7 +22264,7 @@
         <v>10.5</v>
       </c>
       <c r="G755" t="n">
-        <v>9.45986938476562</v>
+        <v>9.45986843109131</v>
       </c>
       <c r="H755" t="n">
         <v>109777</v>
@@ -22293,7 +22293,7 @@
         <v>10.6999998092651</v>
       </c>
       <c r="G756" t="n">
-        <v>9.64005565643311</v>
+        <v>9.64005661010742</v>
       </c>
       <c r="H756" t="n">
         <v>47290</v>
@@ -22322,7 +22322,7 @@
         <v>10.8000001907349</v>
       </c>
       <c r="G757" t="n">
-        <v>9.73015213012695</v>
+        <v>9.73015117645264</v>
       </c>
       <c r="H757" t="n">
         <v>28047</v>
@@ -22351,7 +22351,7 @@
         <v>10.8000001907349</v>
       </c>
       <c r="G758" t="n">
-        <v>9.73015213012695</v>
+        <v>9.73015117645264</v>
       </c>
       <c r="H758" t="n">
         <v>102716</v>
@@ -22380,7 +22380,7 @@
         <v>10.8000001907349</v>
       </c>
       <c r="G759" t="n">
-        <v>9.73015213012695</v>
+        <v>9.73015117645264</v>
       </c>
       <c r="H759" t="n">
         <v>48440</v>
@@ -22409,7 +22409,7 @@
         <v>10.8000001907349</v>
       </c>
       <c r="G760" t="n">
-        <v>9.73015213012695</v>
+        <v>9.73015117645264</v>
       </c>
       <c r="H760" t="n">
         <v>4992</v>
@@ -22438,7 +22438,7 @@
         <v>10.8000001907349</v>
       </c>
       <c r="G761" t="n">
-        <v>9.73015213012695</v>
+        <v>9.73015117645264</v>
       </c>
       <c r="H761" t="n">
         <v>13315</v>
@@ -22467,7 +22467,7 @@
         <v>10.8000001907349</v>
       </c>
       <c r="G762" t="n">
-        <v>9.73015213012695</v>
+        <v>9.73015117645264</v>
       </c>
       <c r="H762" t="n">
         <v>7457</v>
@@ -22496,7 +22496,7 @@
         <v>10.8000001907349</v>
       </c>
       <c r="G763" t="n">
-        <v>9.73015213012695</v>
+        <v>9.73015117645264</v>
       </c>
       <c r="H763" t="n">
         <v>6361</v>
@@ -22525,7 +22525,7 @@
         <v>10.8000001907349</v>
       </c>
       <c r="G764" t="n">
-        <v>9.73015213012695</v>
+        <v>9.73015117645264</v>
       </c>
       <c r="H764" t="n">
         <v>13846</v>
@@ -22554,7 +22554,7 @@
         <v>10.8000001907349</v>
       </c>
       <c r="G765" t="n">
-        <v>9.73015213012695</v>
+        <v>9.73015117645264</v>
       </c>
       <c r="H765" t="n">
         <v>920</v>
@@ -22583,7 +22583,7 @@
         <v>10.8000001907349</v>
       </c>
       <c r="G766" t="n">
-        <v>9.73015213012695</v>
+        <v>9.73015117645264</v>
       </c>
       <c r="H766" t="n">
         <v>73691</v>
@@ -22612,7 +22612,7 @@
         <v>10.8000001907349</v>
       </c>
       <c r="G767" t="n">
-        <v>9.73015213012695</v>
+        <v>9.73015117645264</v>
       </c>
       <c r="H767" t="n">
         <v>7694</v>
@@ -22641,7 +22641,7 @@
         <v>10.6999998092651</v>
       </c>
       <c r="G768" t="n">
-        <v>9.64005565643311</v>
+        <v>9.64005661010742</v>
       </c>
       <c r="H768" t="n">
         <v>8347</v>
@@ -22670,7 +22670,7 @@
         <v>10.6999998092651</v>
       </c>
       <c r="G769" t="n">
-        <v>9.64005565643311</v>
+        <v>9.64005661010742</v>
       </c>
       <c r="H769" t="n">
         <v>237264</v>
@@ -22699,7 +22699,7 @@
         <v>10.8000001907349</v>
       </c>
       <c r="G770" t="n">
-        <v>9.73015213012695</v>
+        <v>9.73015117645264</v>
       </c>
       <c r="H770" t="n">
         <v>12542</v>
@@ -22728,7 +22728,7 @@
         <v>10.8000001907349</v>
       </c>
       <c r="G771" t="n">
-        <v>9.73015213012695</v>
+        <v>9.73015117645264</v>
       </c>
       <c r="H771" t="n">
         <v>3850</v>
@@ -22757,7 +22757,7 @@
         <v>10.8000001907349</v>
       </c>
       <c r="G772" t="n">
-        <v>9.73015213012695</v>
+        <v>9.73015117645264</v>
       </c>
       <c r="H772" t="n">
         <v>1100</v>
@@ -22786,7 +22786,7 @@
         <v>10.8000001907349</v>
       </c>
       <c r="G773" t="n">
-        <v>9.73015213012695</v>
+        <v>9.73015117645264</v>
       </c>
       <c r="H773" t="n">
         <v>431</v>
@@ -22844,7 +22844,7 @@
         <v>10.8000001907349</v>
       </c>
       <c r="G775" t="n">
-        <v>9.73015213012695</v>
+        <v>9.73015117645264</v>
       </c>
       <c r="H775" t="n">
         <v>1458</v>
@@ -22873,7 +22873,7 @@
         <v>10.8000001907349</v>
       </c>
       <c r="G776" t="n">
-        <v>9.73015213012695</v>
+        <v>9.73015117645264</v>
       </c>
       <c r="H776" t="n">
         <v>2601</v>
@@ -22902,7 +22902,7 @@
         <v>10.8000001907349</v>
       </c>
       <c r="G777" t="n">
-        <v>9.73015213012695</v>
+        <v>9.73015117645264</v>
       </c>
       <c r="H777" t="n">
         <v>4513</v>
@@ -22931,7 +22931,7 @@
         <v>10.8000001907349</v>
       </c>
       <c r="G778" t="n">
-        <v>9.73015213012695</v>
+        <v>9.73015117645264</v>
       </c>
       <c r="H778" t="n">
         <v>27010</v>
@@ -22960,7 +22960,7 @@
         <v>10.8000001907349</v>
       </c>
       <c r="G779" t="n">
-        <v>9.73015213012695</v>
+        <v>9.73015117645264</v>
       </c>
       <c r="H779" t="n">
         <v>100</v>
@@ -22989,7 +22989,7 @@
         <v>10.8000001907349</v>
       </c>
       <c r="G780" t="n">
-        <v>9.73015213012695</v>
+        <v>9.73015117645264</v>
       </c>
       <c r="H780" t="n">
         <v>2825</v>
@@ -23018,7 +23018,7 @@
         <v>10.8000001907349</v>
       </c>
       <c r="G781" t="n">
-        <v>9.73015213012695</v>
+        <v>9.73015117645264</v>
       </c>
       <c r="H781" t="n">
         <v>19730</v>
@@ -23047,7 +23047,7 @@
         <v>10.8000001907349</v>
       </c>
       <c r="G782" t="n">
-        <v>9.73015213012695</v>
+        <v>9.73015117645264</v>
       </c>
       <c r="H782" t="n">
         <v>2793</v>
@@ -23076,7 +23076,7 @@
         <v>10.8000001907349</v>
       </c>
       <c r="G783" t="n">
-        <v>9.73015213012695</v>
+        <v>9.73015117645264</v>
       </c>
       <c r="H783" t="n">
         <v>46623</v>
@@ -23105,7 +23105,7 @@
         <v>10.8000001907349</v>
       </c>
       <c r="G784" t="n">
-        <v>9.73015213012695</v>
+        <v>9.73015117645264</v>
       </c>
       <c r="H784" t="n">
         <v>72080</v>
@@ -23221,7 +23221,7 @@
         <v>11.1000003814697</v>
       </c>
       <c r="G788" t="n">
-        <v>10.0004329681396</v>
+        <v>10.000433921814</v>
       </c>
       <c r="H788" t="n">
         <v>19242</v>
@@ -23453,7 +23453,7 @@
         <v>11.5</v>
       </c>
       <c r="G796" t="n">
-        <v>10.3608093261719</v>
+        <v>10.3608102798462</v>
       </c>
       <c r="H796" t="n">
         <v>50499</v>
@@ -23482,7 +23482,7 @@
         <v>11.6000003814697</v>
       </c>
       <c r="G797" t="n">
-        <v>10.4509038925171</v>
+        <v>10.4509048461914</v>
       </c>
       <c r="H797" t="n">
         <v>23568</v>
@@ -23511,7 +23511,7 @@
         <v>11.5</v>
       </c>
       <c r="G798" t="n">
-        <v>10.3608093261719</v>
+        <v>10.3608102798462</v>
       </c>
       <c r="H798" t="n">
         <v>57131</v>
@@ -23540,7 +23540,7 @@
         <v>11.6000003814697</v>
       </c>
       <c r="G799" t="n">
-        <v>10.4509038925171</v>
+        <v>10.4509048461914</v>
       </c>
       <c r="H799" t="n">
         <v>12081</v>
@@ -23569,7 +23569,7 @@
         <v>11.8000001907349</v>
       </c>
       <c r="G800" t="n">
-        <v>10.6310920715332</v>
+        <v>10.6310911178589</v>
       </c>
       <c r="H800" t="n">
         <v>49722</v>
@@ -23627,7 +23627,7 @@
         <v>11.8000001907349</v>
       </c>
       <c r="G802" t="n">
-        <v>10.6310920715332</v>
+        <v>10.6310911178589</v>
       </c>
       <c r="H802" t="n">
         <v>46365</v>
@@ -23656,7 +23656,7 @@
         <v>11.8000001907349</v>
       </c>
       <c r="G803" t="n">
-        <v>10.6310920715332</v>
+        <v>10.6310911178589</v>
       </c>
       <c r="H803" t="n">
         <v>22026</v>
@@ -23685,7 +23685,7 @@
         <v>11.8000001907349</v>
       </c>
       <c r="G804" t="n">
-        <v>10.6310920715332</v>
+        <v>10.6310911178589</v>
       </c>
       <c r="H804" t="n">
         <v>22008</v>
@@ -23714,7 +23714,7 @@
         <v>11.8999996185303</v>
       </c>
       <c r="G805" t="n">
-        <v>10.7211856842041</v>
+        <v>10.7211847305298</v>
       </c>
       <c r="H805" t="n">
         <v>30450</v>
@@ -23743,7 +23743,7 @@
         <v>11.8000001907349</v>
       </c>
       <c r="G806" t="n">
-        <v>10.6310920715332</v>
+        <v>10.6310911178589</v>
       </c>
       <c r="H806" t="n">
         <v>10733</v>
@@ -23772,7 +23772,7 @@
         <v>11.8999996185303</v>
       </c>
       <c r="G807" t="n">
-        <v>10.7211856842041</v>
+        <v>10.7211847305298</v>
       </c>
       <c r="H807" t="n">
         <v>59524</v>
@@ -23801,7 +23801,7 @@
         <v>11.8999996185303</v>
       </c>
       <c r="G808" t="n">
-        <v>10.7211856842041</v>
+        <v>10.7211847305298</v>
       </c>
       <c r="H808" t="n">
         <v>896</v>
@@ -23859,7 +23859,7 @@
         <v>12</v>
       </c>
       <c r="G810" t="n">
-        <v>10.811279296875</v>
+        <v>10.8112783432007</v>
       </c>
       <c r="H810" t="n">
         <v>111993</v>
@@ -23888,7 +23888,7 @@
         <v>12</v>
       </c>
       <c r="G811" t="n">
-        <v>10.811279296875</v>
+        <v>10.8112783432007</v>
       </c>
       <c r="H811" t="n">
         <v>17424</v>
@@ -23917,7 +23917,7 @@
         <v>12.1000003814697</v>
       </c>
       <c r="G812" t="n">
-        <v>10.9013729095459</v>
+        <v>10.9013738632202</v>
       </c>
       <c r="H812" t="n">
         <v>19065</v>
@@ -23946,7 +23946,7 @@
         <v>12.1000003814697</v>
       </c>
       <c r="G813" t="n">
-        <v>10.9013729095459</v>
+        <v>10.9013738632202</v>
       </c>
       <c r="H813" t="n">
         <v>3622</v>
@@ -23975,7 +23975,7 @@
         <v>12.1000003814697</v>
       </c>
       <c r="G814" t="n">
-        <v>10.9013729095459</v>
+        <v>10.9013738632202</v>
       </c>
       <c r="H814" t="n">
         <v>5715</v>
@@ -24004,7 +24004,7 @@
         <v>12</v>
       </c>
       <c r="G815" t="n">
-        <v>10.811279296875</v>
+        <v>10.8112783432007</v>
       </c>
       <c r="H815" t="n">
         <v>147502</v>
@@ -24033,7 +24033,7 @@
         <v>12.1000003814697</v>
       </c>
       <c r="G816" t="n">
-        <v>10.9013729095459</v>
+        <v>10.9013738632202</v>
       </c>
       <c r="H816" t="n">
         <v>12451</v>
@@ -24062,7 +24062,7 @@
         <v>12.1000003814697</v>
       </c>
       <c r="G817" t="n">
-        <v>10.9013729095459</v>
+        <v>10.9013738632202</v>
       </c>
       <c r="H817" t="n">
         <v>8094</v>
@@ -24091,7 +24091,7 @@
         <v>12.1999998092651</v>
       </c>
       <c r="G818" t="n">
-        <v>10.9914674758911</v>
+        <v>10.9914665222168</v>
       </c>
       <c r="H818" t="n">
         <v>28509</v>
@@ -24120,7 +24120,7 @@
         <v>12.1999998092651</v>
       </c>
       <c r="G819" t="n">
-        <v>10.9914674758911</v>
+        <v>10.9914665222168</v>
       </c>
       <c r="H819" t="n">
         <v>3696</v>
@@ -24149,7 +24149,7 @@
         <v>12</v>
       </c>
       <c r="G820" t="n">
-        <v>10.811279296875</v>
+        <v>10.8112783432007</v>
       </c>
       <c r="H820" t="n">
         <v>37372</v>
@@ -24178,7 +24178,7 @@
         <v>12</v>
       </c>
       <c r="G821" t="n">
-        <v>10.811279296875</v>
+        <v>10.8112783432007</v>
       </c>
       <c r="H821" t="n">
         <v>20396</v>
@@ -24207,7 +24207,7 @@
         <v>12.1000003814697</v>
       </c>
       <c r="G822" t="n">
-        <v>10.9013729095459</v>
+        <v>10.9013738632202</v>
       </c>
       <c r="H822" t="n">
         <v>8221</v>
@@ -24265,7 +24265,7 @@
         <v>12.1999998092651</v>
       </c>
       <c r="G824" t="n">
-        <v>10.9914674758911</v>
+        <v>10.9914665222168</v>
       </c>
       <c r="H824" t="n">
         <v>30353</v>
@@ -24323,7 +24323,7 @@
         <v>12.1999998092651</v>
       </c>
       <c r="G826" t="n">
-        <v>10.9914674758911</v>
+        <v>10.9914665222168</v>
       </c>
       <c r="H826" t="n">
         <v>14080</v>
@@ -24352,7 +24352,7 @@
         <v>12.1000003814697</v>
       </c>
       <c r="G827" t="n">
-        <v>10.9013729095459</v>
+        <v>10.9013738632202</v>
       </c>
       <c r="H827" t="n">
         <v>13104</v>
@@ -24381,7 +24381,7 @@
         <v>12</v>
       </c>
       <c r="G828" t="n">
-        <v>10.811279296875</v>
+        <v>10.8112783432007</v>
       </c>
       <c r="H828" t="n">
         <v>31355</v>
@@ -24439,7 +24439,7 @@
         <v>12.1999998092651</v>
       </c>
       <c r="G830" t="n">
-        <v>10.9914674758911</v>
+        <v>10.9914665222168</v>
       </c>
       <c r="H830" t="n">
         <v>14447</v>
@@ -24497,7 +24497,7 @@
         <v>12.1999998092651</v>
       </c>
       <c r="G832" t="n">
-        <v>10.9914674758911</v>
+        <v>10.9914665222168</v>
       </c>
       <c r="H832" t="n">
         <v>1958</v>
@@ -24526,7 +24526,7 @@
         <v>12.1999998092651</v>
       </c>
       <c r="G833" t="n">
-        <v>10.9914674758911</v>
+        <v>10.9914665222168</v>
       </c>
       <c r="H833" t="n">
         <v>19330</v>
@@ -24555,7 +24555,7 @@
         <v>12.1999998092651</v>
       </c>
       <c r="G834" t="n">
-        <v>10.9914674758911</v>
+        <v>10.9914665222168</v>
       </c>
       <c r="H834" t="n">
         <v>11083</v>
@@ -24584,7 +24584,7 @@
         <v>12.1999998092651</v>
       </c>
       <c r="G835" t="n">
-        <v>10.9914674758911</v>
+        <v>10.9914665222168</v>
       </c>
       <c r="H835" t="n">
         <v>10809</v>
@@ -24642,7 +24642,7 @@
         <v>12.5</v>
       </c>
       <c r="G837" t="n">
-        <v>11.2617502212524</v>
+        <v>11.2617492675781</v>
       </c>
       <c r="H837" t="n">
         <v>18032</v>
@@ -24700,7 +24700,7 @@
         <v>12.1999998092651</v>
       </c>
       <c r="G839" t="n">
-        <v>10.9914674758911</v>
+        <v>10.9914665222168</v>
       </c>
       <c r="H839" t="n">
         <v>7897</v>
@@ -24758,7 +24758,7 @@
         <v>12.3999996185303</v>
       </c>
       <c r="G841" t="n">
-        <v>11.1716556549072</v>
+        <v>11.1716547012329</v>
       </c>
       <c r="H841" t="n">
         <v>40850</v>
@@ -24874,7 +24874,7 @@
         <v>12.1999998092651</v>
       </c>
       <c r="G845" t="n">
-        <v>10.9914674758911</v>
+        <v>10.9914665222168</v>
       </c>
       <c r="H845" t="n">
         <v>6045</v>
@@ -24903,7 +24903,7 @@
         <v>12.1000003814697</v>
       </c>
       <c r="G846" t="n">
-        <v>10.9013729095459</v>
+        <v>10.9013738632202</v>
       </c>
       <c r="H846" t="n">
         <v>24081</v>
@@ -24932,7 +24932,7 @@
         <v>12.1999998092651</v>
       </c>
       <c r="G847" t="n">
-        <v>10.9914674758911</v>
+        <v>10.9914665222168</v>
       </c>
       <c r="H847" t="n">
         <v>16080</v>
@@ -24961,7 +24961,7 @@
         <v>12</v>
       </c>
       <c r="G848" t="n">
-        <v>10.811279296875</v>
+        <v>10.8112783432007</v>
       </c>
       <c r="H848" t="n">
         <v>19006</v>
@@ -24990,7 +24990,7 @@
         <v>11.8999996185303</v>
       </c>
       <c r="G849" t="n">
-        <v>10.7211856842041</v>
+        <v>10.7211847305298</v>
       </c>
       <c r="H849" t="n">
         <v>33307</v>
@@ -25019,7 +25019,7 @@
         <v>11.8000001907349</v>
       </c>
       <c r="G850" t="n">
-        <v>10.6310920715332</v>
+        <v>10.6310911178589</v>
       </c>
       <c r="H850" t="n">
         <v>111180</v>
@@ -25048,7 +25048,7 @@
         <v>11.8000001907349</v>
       </c>
       <c r="G851" t="n">
-        <v>10.6310920715332</v>
+        <v>10.6310911178589</v>
       </c>
       <c r="H851" t="n">
         <v>21012</v>
@@ -25077,7 +25077,7 @@
         <v>11.6000003814697</v>
       </c>
       <c r="G852" t="n">
-        <v>10.4509038925171</v>
+        <v>10.4509048461914</v>
       </c>
       <c r="H852" t="n">
         <v>24301</v>
@@ -25106,7 +25106,7 @@
         <v>11.5</v>
       </c>
       <c r="G853" t="n">
-        <v>10.3608093261719</v>
+        <v>10.3608102798462</v>
       </c>
       <c r="H853" t="n">
         <v>19258</v>
@@ -25222,7 +25222,7 @@
         <v>11.1000003814697</v>
       </c>
       <c r="G857" t="n">
-        <v>10.0004329681396</v>
+        <v>10.000433921814</v>
       </c>
       <c r="H857" t="n">
         <v>18055</v>
@@ -25280,7 +25280,7 @@
         <v>10.1000003814697</v>
       </c>
       <c r="G859" t="n">
-        <v>9.09949398040771</v>
+        <v>9.0994930267334</v>
       </c>
       <c r="H859" t="n">
         <v>21455</v>
@@ -25309,7 +25309,7 @@
         <v>10</v>
       </c>
       <c r="G860" t="n">
-        <v>9.00939846038818</v>
+        <v>9.0093994140625</v>
       </c>
       <c r="H860" t="n">
         <v>7755</v>
@@ -25396,7 +25396,7 @@
         <v>10</v>
       </c>
       <c r="G863" t="n">
-        <v>9.00939846038818</v>
+        <v>9.0093994140625</v>
       </c>
       <c r="H863" t="n">
         <v>9235</v>
@@ -25425,7 +25425,7 @@
         <v>9</v>
       </c>
       <c r="G864" t="n">
-        <v>8.10845947265625</v>
+        <v>8.10846042633057</v>
       </c>
       <c r="H864" t="n">
         <v>14181</v>
@@ -25454,7 +25454,7 @@
         <v>9</v>
       </c>
       <c r="G865" t="n">
-        <v>8.10845947265625</v>
+        <v>8.10846042633057</v>
       </c>
       <c r="H865" t="n">
         <v>19428</v>
@@ -25483,7 +25483,7 @@
         <v>10.1999998092651</v>
       </c>
       <c r="G866" t="n">
-        <v>9.18958759307861</v>
+        <v>9.18958854675293</v>
       </c>
       <c r="H866" t="n">
         <v>11716</v>
@@ -25512,7 +25512,7 @@
         <v>10</v>
       </c>
       <c r="G867" t="n">
-        <v>9.00939846038818</v>
+        <v>9.0093994140625</v>
       </c>
       <c r="H867" t="n">
         <v>7510</v>
@@ -25541,7 +25541,7 @@
         <v>10</v>
       </c>
       <c r="G868" t="n">
-        <v>9.00939846038818</v>
+        <v>9.0093994140625</v>
       </c>
       <c r="H868" t="n">
         <v>5244</v>
@@ -25570,7 +25570,7 @@
         <v>9.89999961853027</v>
       </c>
       <c r="G869" t="n">
-        <v>8.91930389404297</v>
+        <v>8.91930484771729</v>
       </c>
       <c r="H869" t="n">
         <v>1924</v>
@@ -25599,7 +25599,7 @@
         <v>10.1000003814697</v>
       </c>
       <c r="G870" t="n">
-        <v>9.09949398040771</v>
+        <v>9.0994930267334</v>
       </c>
       <c r="H870" t="n">
         <v>6877</v>
@@ -25628,7 +25628,7 @@
         <v>10.5</v>
       </c>
       <c r="G871" t="n">
-        <v>9.45986938476562</v>
+        <v>9.45986843109131</v>
       </c>
       <c r="H871" t="n">
         <v>4639</v>
@@ -25657,7 +25657,7 @@
         <v>10.8000001907349</v>
       </c>
       <c r="G872" t="n">
-        <v>9.73015213012695</v>
+        <v>9.73015117645264</v>
       </c>
       <c r="H872" t="n">
         <v>14639</v>
@@ -25715,7 +25715,7 @@
         <v>10.1999998092651</v>
       </c>
       <c r="G874" t="n">
-        <v>9.18958759307861</v>
+        <v>9.18958854675293</v>
       </c>
       <c r="H874" t="n">
         <v>7094</v>
@@ -25744,7 +25744,7 @@
         <v>10.8000001907349</v>
       </c>
       <c r="G875" t="n">
-        <v>9.73015213012695</v>
+        <v>9.73015117645264</v>
       </c>
       <c r="H875" t="n">
         <v>2220</v>
@@ -25773,7 +25773,7 @@
         <v>10.1000003814697</v>
       </c>
       <c r="G876" t="n">
-        <v>9.09949398040771</v>
+        <v>9.0994930267334</v>
       </c>
       <c r="H876" t="n">
         <v>16782</v>
@@ -25802,7 +25802,7 @@
         <v>10.0500001907349</v>
       </c>
       <c r="G877" t="n">
-        <v>9.05444526672363</v>
+        <v>9.05444622039795</v>
       </c>
       <c r="H877" t="n">
         <v>11800</v>
@@ -25831,7 +25831,7 @@
         <v>10.1499996185303</v>
       </c>
       <c r="G878" t="n">
-        <v>9.14453983306885</v>
+        <v>9.14454078674316</v>
       </c>
       <c r="H878" t="n">
         <v>1300</v>
@@ -25889,7 +25889,7 @@
         <v>10</v>
       </c>
       <c r="G880" t="n">
-        <v>9.00939846038818</v>
+        <v>9.0093994140625</v>
       </c>
       <c r="H880" t="n">
         <v>14131</v>
@@ -25976,7 +25976,7 @@
         <v>10.5</v>
       </c>
       <c r="G883" t="n">
-        <v>9.45986938476562</v>
+        <v>9.45986843109131</v>
       </c>
       <c r="H883" t="n">
         <v>18374</v>
@@ -26063,7 +26063,7 @@
         <v>10.6999998092651</v>
       </c>
       <c r="G886" t="n">
-        <v>9.64005565643311</v>
+        <v>9.64005661010742</v>
       </c>
       <c r="H886" t="n">
         <v>2620</v>
@@ -26092,7 +26092,7 @@
         <v>10.6999998092651</v>
       </c>
       <c r="G887" t="n">
-        <v>9.64005565643311</v>
+        <v>9.64005661010742</v>
       </c>
       <c r="H887" t="n">
         <v>1220</v>
@@ -26121,7 +26121,7 @@
         <v>10.6999998092651</v>
       </c>
       <c r="G888" t="n">
-        <v>9.64005565643311</v>
+        <v>9.64005661010742</v>
       </c>
       <c r="H888" t="n">
         <v>299</v>
@@ -26324,7 +26324,7 @@
         <v>10.6999998092651</v>
       </c>
       <c r="G895" t="n">
-        <v>9.64005565643311</v>
+        <v>9.64005661010742</v>
       </c>
       <c r="H895" t="n">
         <v>4500</v>
@@ -26382,7 +26382,7 @@
         <v>10.9499998092651</v>
       </c>
       <c r="G897" t="n">
-        <v>9.8652925491333</v>
+        <v>9.86529350280762</v>
       </c>
       <c r="H897" t="n">
         <v>3575</v>
@@ -26411,7 +26411,7 @@
         <v>10.8500003814697</v>
       </c>
       <c r="G898" t="n">
-        <v>9.7751989364624</v>
+        <v>9.77519989013672</v>
       </c>
       <c r="H898" t="n">
         <v>18584</v>
@@ -26440,7 +26440,7 @@
         <v>10.5</v>
       </c>
       <c r="G899" t="n">
-        <v>9.45986938476562</v>
+        <v>9.45986843109131</v>
       </c>
       <c r="H899" t="n">
         <v>2580</v>
@@ -26469,7 +26469,7 @@
         <v>10.6999998092651</v>
       </c>
       <c r="G900" t="n">
-        <v>9.64005565643311</v>
+        <v>9.64005661010742</v>
       </c>
       <c r="H900" t="n">
         <v>6008</v>
@@ -26498,7 +26498,7 @@
         <v>10.6000003814697</v>
       </c>
       <c r="G901" t="n">
-        <v>9.65828037261963</v>
+        <v>9.65828132629395</v>
       </c>
       <c r="H901" t="n">
         <v>2022</v>
@@ -26585,7 +26585,7 @@
         <v>10.75</v>
       </c>
       <c r="G904" t="n">
-        <v>9.79495334625244</v>
+        <v>9.79495429992676</v>
       </c>
       <c r="H904" t="n">
         <v>758</v>
@@ -26643,7 +26643,7 @@
         <v>10.6000003814697</v>
       </c>
       <c r="G906" t="n">
-        <v>9.65828037261963</v>
+        <v>9.65828132629395</v>
       </c>
       <c r="H906" t="n">
         <v>360</v>
@@ -26701,7 +26701,7 @@
         <v>10.8000001907349</v>
       </c>
       <c r="G908" t="n">
-        <v>9.84051132202148</v>
+        <v>9.8405122756958</v>
       </c>
       <c r="H908" t="n">
         <v>4550</v>
@@ -26730,7 +26730,7 @@
         <v>10.8000001907349</v>
       </c>
       <c r="G909" t="n">
-        <v>9.84051132202148</v>
+        <v>9.8405122756958</v>
       </c>
       <c r="H909" t="n">
         <v>238</v>
@@ -26759,7 +26759,7 @@
         <v>10.8000001907349</v>
       </c>
       <c r="G910" t="n">
-        <v>9.84051132202148</v>
+        <v>9.8405122756958</v>
       </c>
       <c r="H910" t="n">
         <v>2050</v>
@@ -26788,7 +26788,7 @@
         <v>10.8999996185303</v>
       </c>
       <c r="G911" t="n">
-        <v>9.93162727355957</v>
+        <v>9.93162822723389</v>
       </c>
       <c r="H911" t="n">
         <v>2924</v>
@@ -26817,7 +26817,7 @@
         <v>10.8999996185303</v>
       </c>
       <c r="G912" t="n">
-        <v>9.93162727355957</v>
+        <v>9.93162822723389</v>
       </c>
       <c r="H912" t="n">
         <v>1808</v>
@@ -26846,7 +26846,7 @@
         <v>10.8999996185303</v>
       </c>
       <c r="G913" t="n">
-        <v>9.93162727355957</v>
+        <v>9.93162822723389</v>
       </c>
       <c r="H913" t="n">
         <v>4730</v>
@@ -26904,7 +26904,7 @@
         <v>10.8999996185303</v>
       </c>
       <c r="G915" t="n">
-        <v>9.93162727355957</v>
+        <v>9.93162822723389</v>
       </c>
       <c r="H915" t="n">
         <v>706</v>
@@ -26991,7 +26991,7 @@
         <v>10.8999996185303</v>
       </c>
       <c r="G918" t="n">
-        <v>9.93162727355957</v>
+        <v>9.93162822723389</v>
       </c>
       <c r="H918" t="n">
         <v>7283</v>
@@ -27020,7 +27020,7 @@
         <v>10.8000001907349</v>
       </c>
       <c r="G919" t="n">
-        <v>9.84051132202148</v>
+        <v>9.8405122756958</v>
       </c>
       <c r="H919" t="n">
         <v>899</v>
@@ -27107,7 +27107,7 @@
         <v>10.75</v>
       </c>
       <c r="G922" t="n">
-        <v>9.79495334625244</v>
+        <v>9.79495429992676</v>
       </c>
       <c r="H922" t="n">
         <v>33283</v>
@@ -27136,7 +27136,7 @@
         <v>10.75</v>
       </c>
       <c r="G923" t="n">
-        <v>9.79495334625244</v>
+        <v>9.79495429992676</v>
       </c>
       <c r="H923" t="n">
         <v>26805</v>
@@ -27223,7 +27223,7 @@
         <v>10.75</v>
       </c>
       <c r="G926" t="n">
-        <v>9.79495334625244</v>
+        <v>9.79495429992676</v>
       </c>
       <c r="H926" t="n">
         <v>2330</v>
@@ -27368,7 +27368,7 @@
         <v>10.8999996185303</v>
       </c>
       <c r="G931" t="n">
-        <v>9.93162727355957</v>
+        <v>9.93162822723389</v>
       </c>
       <c r="H931" t="n">
         <v>8316</v>
@@ -27397,7 +27397,7 @@
         <v>10.8999996185303</v>
       </c>
       <c r="G932" t="n">
-        <v>9.93162727355957</v>
+        <v>9.93162822723389</v>
       </c>
       <c r="H932" t="n">
         <v>4203</v>
@@ -27426,7 +27426,7 @@
         <v>10.8999996185303</v>
       </c>
       <c r="G933" t="n">
-        <v>9.93162727355957</v>
+        <v>9.93162822723389</v>
       </c>
       <c r="H933" t="n">
         <v>1219</v>
@@ -27455,7 +27455,7 @@
         <v>10.8999996185303</v>
       </c>
       <c r="G934" t="n">
-        <v>9.93162727355957</v>
+        <v>9.93162822723389</v>
       </c>
       <c r="H934" t="n">
         <v>5600</v>
@@ -27484,7 +27484,7 @@
         <v>10.8999996185303</v>
       </c>
       <c r="G935" t="n">
-        <v>9.93162727355957</v>
+        <v>9.93162822723389</v>
       </c>
       <c r="H935" t="n">
         <v>3105</v>
@@ -27513,7 +27513,7 @@
         <v>10.8999996185303</v>
       </c>
       <c r="G936" t="n">
-        <v>9.93162727355957</v>
+        <v>9.93162822723389</v>
       </c>
       <c r="H936" t="n">
         <v>0</v>
@@ -27542,7 +27542,7 @@
         <v>10.8999996185303</v>
       </c>
       <c r="G937" t="n">
-        <v>9.93162727355957</v>
+        <v>9.93162822723389</v>
       </c>
       <c r="H937" t="n">
         <v>47</v>
@@ -27571,7 +27571,7 @@
         <v>10.8000001907349</v>
       </c>
       <c r="G938" t="n">
-        <v>9.84051132202148</v>
+        <v>9.8405122756958</v>
       </c>
       <c r="H938" t="n">
         <v>1861</v>
@@ -27600,7 +27600,7 @@
         <v>10.8000001907349</v>
       </c>
       <c r="G939" t="n">
-        <v>9.84051132202148</v>
+        <v>9.8405122756958</v>
       </c>
       <c r="H939" t="n">
         <v>472</v>
@@ -27629,7 +27629,7 @@
         <v>10.8000001907349</v>
       </c>
       <c r="G940" t="n">
-        <v>9.84051132202148</v>
+        <v>9.8405122756958</v>
       </c>
       <c r="H940" t="n">
         <v>357</v>
@@ -27687,7 +27687,7 @@
         <v>10.6000003814697</v>
       </c>
       <c r="G942" t="n">
-        <v>9.65828037261963</v>
+        <v>9.65828132629395</v>
       </c>
       <c r="H942" t="n">
         <v>311</v>
@@ -27745,7 +27745,7 @@
         <v>10.6000003814697</v>
       </c>
       <c r="G944" t="n">
-        <v>9.65828037261963</v>
+        <v>9.65828132629395</v>
       </c>
       <c r="H944" t="n">
         <v>869</v>
@@ -27803,7 +27803,7 @@
         <v>10.8000001907349</v>
       </c>
       <c r="G946" t="n">
-        <v>9.84051132202148</v>
+        <v>9.8405122756958</v>
       </c>
       <c r="H946" t="n">
         <v>5337</v>
@@ -27861,7 +27861,7 @@
         <v>10.8999996185303</v>
       </c>
       <c r="G948" t="n">
-        <v>9.93162727355957</v>
+        <v>9.93162822723389</v>
       </c>
       <c r="H948" t="n">
         <v>28960</v>
@@ -27890,7 +27890,7 @@
         <v>10.8500003814697</v>
       </c>
       <c r="G949" t="n">
-        <v>9.88607025146484</v>
+        <v>9.88607120513916</v>
       </c>
       <c r="H949" t="n">
         <v>1399</v>
@@ -27977,7 +27977,7 @@
         <v>11.3000001907349</v>
       </c>
       <c r="G952" t="n">
-        <v>10.2960920333862</v>
+        <v>10.2960910797119</v>
       </c>
       <c r="H952" t="n">
         <v>38245</v>
@@ -28035,7 +28035,7 @@
         <v>11.1999998092651</v>
       </c>
       <c r="G954" t="n">
-        <v>10.2049760818481</v>
+        <v>10.2049741744995</v>
       </c>
       <c r="H954" t="n">
         <v>18997</v>
@@ -28238,7 +28238,7 @@
         <v>11.1999998092651</v>
       </c>
       <c r="G961" t="n">
-        <v>10.2049760818481</v>
+        <v>10.2049741744995</v>
       </c>
       <c r="H961" t="n">
         <v>5288</v>
@@ -28296,7 +28296,7 @@
         <v>11.1999998092651</v>
       </c>
       <c r="G963" t="n">
-        <v>10.2049760818481</v>
+        <v>10.2049741744995</v>
       </c>
       <c r="H963" t="n">
         <v>8124</v>
@@ -28325,7 +28325,7 @@
         <v>11.1999998092651</v>
       </c>
       <c r="G964" t="n">
-        <v>10.2049760818481</v>
+        <v>10.2049741744995</v>
       </c>
       <c r="H964" t="n">
         <v>236</v>
@@ -28354,7 +28354,7 @@
         <v>11.1999998092651</v>
       </c>
       <c r="G965" t="n">
-        <v>10.2049760818481</v>
+        <v>10.2049741744995</v>
       </c>
       <c r="H965" t="n">
         <v>10203</v>
@@ -28383,7 +28383,7 @@
         <v>11.1999998092651</v>
       </c>
       <c r="G966" t="n">
-        <v>10.2049760818481</v>
+        <v>10.2049741744995</v>
       </c>
       <c r="H966" t="n">
         <v>547</v>
@@ -28963,7 +28963,7 @@
         <v>10.8999996185303</v>
       </c>
       <c r="G986" t="n">
-        <v>9.93162727355957</v>
+        <v>9.93162822723389</v>
       </c>
       <c r="H986" t="n">
         <v>350</v>
@@ -28992,7 +28992,7 @@
         <v>10.8999996185303</v>
       </c>
       <c r="G987" t="n">
-        <v>9.93162727355957</v>
+        <v>9.93162822723389</v>
       </c>
       <c r="H987" t="n">
         <v>293</v>
@@ -29021,7 +29021,7 @@
         <v>10.8999996185303</v>
       </c>
       <c r="G988" t="n">
-        <v>9.93162727355957</v>
+        <v>9.93162822723389</v>
       </c>
       <c r="H988" t="n">
         <v>2158</v>
@@ -29050,7 +29050,7 @@
         <v>10.8000001907349</v>
       </c>
       <c r="G989" t="n">
-        <v>9.84051132202148</v>
+        <v>9.8405122756958</v>
       </c>
       <c r="H989" t="n">
         <v>2879</v>
@@ -29137,7 +29137,7 @@
         <v>10.8000001907349</v>
       </c>
       <c r="G992" t="n">
-        <v>9.84051132202148</v>
+        <v>9.8405122756958</v>
       </c>
       <c r="H992" t="n">
         <v>1802</v>
@@ -29253,7 +29253,7 @@
         <v>10.4499998092651</v>
       </c>
       <c r="G996" t="n">
-        <v>9.52160739898682</v>
+        <v>9.5216064453125</v>
       </c>
       <c r="H996" t="n">
         <v>1795</v>
@@ -29311,7 +29311,7 @@
         <v>10.6000003814697</v>
       </c>
       <c r="G998" t="n">
-        <v>9.65828037261963</v>
+        <v>9.65828132629395</v>
       </c>
       <c r="H998" t="n">
         <v>6553</v>
@@ -29340,7 +29340,7 @@
         <v>10.6000003814697</v>
       </c>
       <c r="G999" t="n">
-        <v>9.65828037261963</v>
+        <v>9.65828132629395</v>
       </c>
       <c r="H999" t="n">
         <v>134</v>
@@ -29427,7 +29427,7 @@
         <v>10.4499998092651</v>
       </c>
       <c r="G1002" t="n">
-        <v>9.52160739898682</v>
+        <v>9.5216064453125</v>
       </c>
       <c r="H1002" t="n">
         <v>5462</v>
@@ -29456,7 +29456,7 @@
         <v>10.6000003814697</v>
       </c>
       <c r="G1003" t="n">
-        <v>9.65828037261963</v>
+        <v>9.65828132629395</v>
       </c>
       <c r="H1003" t="n">
         <v>5015</v>
@@ -29485,7 +29485,7 @@
         <v>10.3999996185303</v>
       </c>
       <c r="G1004" t="n">
-        <v>9.47604846954346</v>
+        <v>9.47604942321777</v>
       </c>
       <c r="H1004" t="n">
         <v>1509</v>
@@ -29601,7 +29601,7 @@
         <v>9.96000003814697</v>
       </c>
       <c r="G1008" t="n">
-        <v>9.07513809204102</v>
+        <v>9.07513904571533</v>
       </c>
       <c r="H1008" t="n">
         <v>250</v>
@@ -29659,7 +29659,7 @@
         <v>9.97999954223633</v>
       </c>
       <c r="G1010" t="n">
-        <v>9.09336185455322</v>
+        <v>9.09336280822754</v>
       </c>
       <c r="H1010" t="n">
         <v>10919</v>
@@ -29688,7 +29688,7 @@
         <v>10</v>
       </c>
       <c r="G1011" t="n">
-        <v>9.11158466339111</v>
+        <v>9.11158561706543</v>
       </c>
       <c r="H1011" t="n">
         <v>42205</v>
@@ -29717,7 +29717,7 @@
         <v>9.97999954223633</v>
       </c>
       <c r="G1012" t="n">
-        <v>9.09336185455322</v>
+        <v>9.09336280822754</v>
       </c>
       <c r="H1012" t="n">
         <v>29977</v>
@@ -29746,7 +29746,7 @@
         <v>10</v>
       </c>
       <c r="G1013" t="n">
-        <v>9.11158466339111</v>
+        <v>9.11158561706543</v>
       </c>
       <c r="H1013" t="n">
         <v>40699</v>
@@ -29775,7 +29775,7 @@
         <v>9.9399995803833</v>
       </c>
       <c r="G1014" t="n">
-        <v>9.05691623687744</v>
+        <v>9.05691719055176</v>
       </c>
       <c r="H1014" t="n">
         <v>4200</v>
@@ -29804,7 +29804,7 @@
         <v>9.9399995803833</v>
       </c>
       <c r="G1015" t="n">
-        <v>9.05691623687744</v>
+        <v>9.05691719055176</v>
       </c>
       <c r="H1015" t="n">
         <v>7972</v>
@@ -29891,7 +29891,7 @@
         <v>9.77999973297119</v>
       </c>
       <c r="G1018" t="n">
-        <v>8.91112899780273</v>
+        <v>8.91113090515137</v>
       </c>
       <c r="H1018" t="n">
         <v>2309</v>
@@ -29920,7 +29920,7 @@
         <v>9.68000030517578</v>
       </c>
       <c r="G1019" t="n">
-        <v>8.82001495361328</v>
+        <v>8.8200159072876</v>
       </c>
       <c r="H1019" t="n">
         <v>1580</v>
@@ -29949,7 +29949,7 @@
         <v>9.89999961853027</v>
       </c>
       <c r="G1020" t="n">
-        <v>9.02046871185303</v>
+        <v>9.02047061920166</v>
       </c>
       <c r="H1020" t="n">
         <v>3852</v>
@@ -29978,7 +29978,7 @@
         <v>9.73999977111816</v>
       </c>
       <c r="G1021" t="n">
-        <v>8.87468338012695</v>
+        <v>8.87468433380127</v>
       </c>
       <c r="H1021" t="n">
         <v>21365</v>
@@ -30065,7 +30065,7 @@
         <v>9.68000030517578</v>
       </c>
       <c r="G1024" t="n">
-        <v>8.82001495361328</v>
+        <v>8.8200159072876</v>
       </c>
       <c r="H1024" t="n">
         <v>6017</v>
@@ -30152,7 +30152,7 @@
         <v>9.46000003814697</v>
       </c>
       <c r="G1027" t="n">
-        <v>8.61956024169922</v>
+        <v>8.61956119537354</v>
       </c>
       <c r="H1027" t="n">
         <v>4125</v>
@@ -30181,7 +30181,7 @@
         <v>9.60000038146973</v>
       </c>
       <c r="G1028" t="n">
-        <v>8.74712181091309</v>
+        <v>8.7471227645874</v>
       </c>
       <c r="H1028" t="n">
         <v>2275</v>
@@ -30210,7 +30210,7 @@
         <v>9.64000034332275</v>
       </c>
       <c r="G1029" t="n">
-        <v>8.78356838226318</v>
+        <v>8.7835693359375</v>
       </c>
       <c r="H1029" t="n">
         <v>2510</v>
@@ -30268,7 +30268,7 @@
         <v>9.60000038146973</v>
       </c>
       <c r="G1031" t="n">
-        <v>8.74712181091309</v>
+        <v>8.7471227645874</v>
       </c>
       <c r="H1031" t="n">
         <v>22721</v>
@@ -30297,7 +30297,7 @@
         <v>9.60000038146973</v>
       </c>
       <c r="G1032" t="n">
-        <v>8.74712181091309</v>
+        <v>8.7471227645874</v>
       </c>
       <c r="H1032" t="n">
         <v>11947</v>
@@ -30355,7 +30355,7 @@
         <v>9.97999954223633</v>
       </c>
       <c r="G1034" t="n">
-        <v>9.09336185455322</v>
+        <v>9.09336280822754</v>
       </c>
       <c r="H1034" t="n">
         <v>31247</v>
@@ -30384,7 +30384,7 @@
         <v>9.97999954223633</v>
       </c>
       <c r="G1035" t="n">
-        <v>9.09336185455322</v>
+        <v>9.09336280822754</v>
       </c>
       <c r="H1035" t="n">
         <v>46989</v>
@@ -30413,7 +30413,7 @@
         <v>9.89999961853027</v>
       </c>
       <c r="G1036" t="n">
-        <v>9.02046871185303</v>
+        <v>9.02047061920166</v>
       </c>
       <c r="H1036" t="n">
         <v>18469</v>
@@ -30674,7 +30674,7 @@
         <v>11.3000001907349</v>
       </c>
       <c r="G1045" t="n">
-        <v>10.2960920333862</v>
+        <v>10.2960910797119</v>
       </c>
       <c r="H1045" t="n">
         <v>8842</v>
@@ -30703,7 +30703,7 @@
         <v>11.3000001907349</v>
       </c>
       <c r="G1046" t="n">
-        <v>10.2960920333862</v>
+        <v>10.2960910797119</v>
       </c>
       <c r="H1046" t="n">
         <v>745</v>
@@ -30732,7 +30732,7 @@
         <v>11.1499996185303</v>
       </c>
       <c r="G1047" t="n">
-        <v>10.1594181060791</v>
+        <v>10.1594171524048</v>
       </c>
       <c r="H1047" t="n">
         <v>11652</v>
@@ -30848,7 +30848,7 @@
         <v>10.8999996185303</v>
       </c>
       <c r="G1051" t="n">
-        <v>9.93162727355957</v>
+        <v>9.93162822723389</v>
       </c>
       <c r="H1051" t="n">
         <v>3234</v>
@@ -30993,7 +30993,7 @@
         <v>10.8000001907349</v>
       </c>
       <c r="G1056" t="n">
-        <v>9.84051132202148</v>
+        <v>9.8405122756958</v>
       </c>
       <c r="H1056" t="n">
         <v>19566</v>
@@ -31051,7 +31051,7 @@
         <v>10.8500003814697</v>
       </c>
       <c r="G1058" t="n">
-        <v>9.88607025146484</v>
+        <v>9.88607120513916</v>
       </c>
       <c r="H1058" t="n">
         <v>15783</v>
@@ -31080,7 +31080,7 @@
         <v>10.8000001907349</v>
       </c>
       <c r="G1059" t="n">
-        <v>9.84051132202148</v>
+        <v>9.8405122756958</v>
       </c>
       <c r="H1059" t="n">
         <v>400</v>
@@ -31109,7 +31109,7 @@
         <v>10.75</v>
       </c>
       <c r="G1060" t="n">
-        <v>9.79495334625244</v>
+        <v>9.79495429992676</v>
       </c>
       <c r="H1060" t="n">
         <v>3130</v>
@@ -31138,7 +31138,7 @@
         <v>10.6000003814697</v>
       </c>
       <c r="G1061" t="n">
-        <v>9.65828037261963</v>
+        <v>9.65828132629395</v>
       </c>
       <c r="H1061" t="n">
         <v>5560</v>
@@ -31196,7 +31196,7 @@
         <v>10.75</v>
       </c>
       <c r="G1063" t="n">
-        <v>9.79495334625244</v>
+        <v>9.79495429992676</v>
       </c>
       <c r="H1063" t="n">
         <v>8500</v>
@@ -31254,7 +31254,7 @@
         <v>10.3999996185303</v>
       </c>
       <c r="G1065" t="n">
-        <v>9.47604846954346</v>
+        <v>9.47604942321777</v>
       </c>
       <c r="H1065" t="n">
         <v>9282</v>
@@ -31312,7 +31312,7 @@
         <v>10.6000003814697</v>
       </c>
       <c r="G1067" t="n">
-        <v>9.65828037261963</v>
+        <v>9.65828132629395</v>
       </c>
       <c r="H1067" t="n">
         <v>2591</v>
@@ -31399,7 +31399,7 @@
         <v>10.8000001907349</v>
       </c>
       <c r="G1070" t="n">
-        <v>9.84051132202148</v>
+        <v>9.8405122756958</v>
       </c>
       <c r="H1070" t="n">
         <v>14898</v>
@@ -31428,7 +31428,7 @@
         <v>10.8999996185303</v>
       </c>
       <c r="G1071" t="n">
-        <v>9.93162727355957</v>
+        <v>9.93162822723389</v>
       </c>
       <c r="H1071" t="n">
         <v>8809</v>
@@ -31457,7 +31457,7 @@
         <v>10.75</v>
       </c>
       <c r="G1072" t="n">
-        <v>9.79495334625244</v>
+        <v>9.79495429992676</v>
       </c>
       <c r="H1072" t="n">
         <v>18487</v>
@@ -31486,7 +31486,7 @@
         <v>10.8000001907349</v>
       </c>
       <c r="G1073" t="n">
-        <v>9.84051132202148</v>
+        <v>9.8405122756958</v>
       </c>
       <c r="H1073" t="n">
         <v>1135</v>
@@ -31515,7 +31515,7 @@
         <v>10.8500003814697</v>
       </c>
       <c r="G1074" t="n">
-        <v>9.88607025146484</v>
+        <v>9.88607120513916</v>
       </c>
       <c r="H1074" t="n">
         <v>6030</v>
@@ -31544,7 +31544,7 @@
         <v>10.8500003814697</v>
       </c>
       <c r="G1075" t="n">
-        <v>9.88607025146484</v>
+        <v>9.88607120513916</v>
       </c>
       <c r="H1075" t="n">
         <v>2661</v>
@@ -31573,7 +31573,7 @@
         <v>10.8500003814697</v>
       </c>
       <c r="G1076" t="n">
-        <v>9.88607025146484</v>
+        <v>9.88607120513916</v>
       </c>
       <c r="H1076" t="n">
         <v>3712</v>
@@ -31602,7 +31602,7 @@
         <v>10.75</v>
       </c>
       <c r="G1077" t="n">
-        <v>9.79495334625244</v>
+        <v>9.79495429992676</v>
       </c>
       <c r="H1077" t="n">
         <v>4356</v>
@@ -31631,7 +31631,7 @@
         <v>10.75</v>
       </c>
       <c r="G1078" t="n">
-        <v>9.79495334625244</v>
+        <v>9.79495429992676</v>
       </c>
       <c r="H1078" t="n">
         <v>45</v>
@@ -31660,7 +31660,7 @@
         <v>10.75</v>
       </c>
       <c r="G1079" t="n">
-        <v>9.79495334625244</v>
+        <v>9.79495429992676</v>
       </c>
       <c r="H1079" t="n">
         <v>9723</v>
@@ -31747,7 +31747,7 @@
         <v>10.6000003814697</v>
       </c>
       <c r="G1082" t="n">
-        <v>9.65828037261963</v>
+        <v>9.65828132629395</v>
       </c>
       <c r="H1082" t="n">
         <v>10531</v>
@@ -31776,7 +31776,7 @@
         <v>10.6000003814697</v>
       </c>
       <c r="G1083" t="n">
-        <v>9.65828037261963</v>
+        <v>9.65828132629395</v>
       </c>
       <c r="H1083" t="n">
         <v>3666</v>
@@ -31921,7 +31921,7 @@
         <v>10.6000003814697</v>
       </c>
       <c r="G1088" t="n">
-        <v>9.65828037261963</v>
+        <v>9.65828132629395</v>
       </c>
       <c r="H1088" t="n">
         <v>1963</v>
@@ -31950,7 +31950,7 @@
         <v>10.8000001907349</v>
       </c>
       <c r="G1089" t="n">
-        <v>9.84051132202148</v>
+        <v>9.8405122756958</v>
       </c>
       <c r="H1089" t="n">
         <v>14366</v>
@@ -31979,7 +31979,7 @@
         <v>10.8000001907349</v>
       </c>
       <c r="G1090" t="n">
-        <v>9.84051132202148</v>
+        <v>9.8405122756958</v>
       </c>
       <c r="H1090" t="n">
         <v>906</v>
@@ -32008,7 +32008,7 @@
         <v>10.8999996185303</v>
       </c>
       <c r="G1091" t="n">
-        <v>9.93162727355957</v>
+        <v>9.93162822723389</v>
       </c>
       <c r="H1091" t="n">
         <v>2852</v>
@@ -32037,7 +32037,7 @@
         <v>10.8500003814697</v>
       </c>
       <c r="G1092" t="n">
-        <v>9.88607025146484</v>
+        <v>9.88607120513916</v>
       </c>
       <c r="H1092" t="n">
         <v>6196</v>
@@ -32066,7 +32066,7 @@
         <v>10.8500003814697</v>
       </c>
       <c r="G1093" t="n">
-        <v>9.88607025146484</v>
+        <v>9.88607120513916</v>
       </c>
       <c r="H1093" t="n">
         <v>9361</v>
@@ -32095,7 +32095,7 @@
         <v>10.8999996185303</v>
       </c>
       <c r="G1094" t="n">
-        <v>9.93162727355957</v>
+        <v>9.93162822723389</v>
       </c>
       <c r="H1094" t="n">
         <v>1016</v>
@@ -32182,7 +32182,7 @@
         <v>10.6000003814697</v>
       </c>
       <c r="G1097" t="n">
-        <v>9.65828037261963</v>
+        <v>9.65828132629395</v>
       </c>
       <c r="H1097" t="n">
         <v>5284</v>
@@ -32211,7 +32211,7 @@
         <v>10.75</v>
       </c>
       <c r="G1098" t="n">
-        <v>9.79495334625244</v>
+        <v>9.79495429992676</v>
       </c>
       <c r="H1098" t="n">
         <v>5377</v>
@@ -32240,7 +32240,7 @@
         <v>10.8000001907349</v>
       </c>
       <c r="G1099" t="n">
-        <v>9.84051132202148</v>
+        <v>9.8405122756958</v>
       </c>
       <c r="H1099" t="n">
         <v>9104</v>
@@ -32269,7 +32269,7 @@
         <v>10.8000001907349</v>
       </c>
       <c r="G1100" t="n">
-        <v>9.84051132202148</v>
+        <v>9.8405122756958</v>
       </c>
       <c r="H1100" t="n">
         <v>24254</v>
@@ -32298,7 +32298,7 @@
         <v>10.75</v>
       </c>
       <c r="G1101" t="n">
-        <v>9.79495334625244</v>
+        <v>9.79495429992676</v>
       </c>
       <c r="H1101" t="n">
         <v>13932</v>
@@ -32327,7 +32327,7 @@
         <v>10.8999996185303</v>
       </c>
       <c r="G1102" t="n">
-        <v>9.93162727355957</v>
+        <v>9.93162822723389</v>
       </c>
       <c r="H1102" t="n">
         <v>16059</v>
@@ -32385,7 +32385,7 @@
         <v>10.8999996185303</v>
       </c>
       <c r="G1104" t="n">
-        <v>9.93162727355957</v>
+        <v>9.93162822723389</v>
       </c>
       <c r="H1104" t="n">
         <v>1346</v>
@@ -32414,7 +32414,7 @@
         <v>10.8000001907349</v>
       </c>
       <c r="G1105" t="n">
-        <v>9.84051132202148</v>
+        <v>9.8405122756958</v>
       </c>
       <c r="H1105" t="n">
         <v>3539</v>
@@ -32472,7 +32472,7 @@
         <v>10.8000001907349</v>
       </c>
       <c r="G1107" t="n">
-        <v>9.84051132202148</v>
+        <v>9.8405122756958</v>
       </c>
       <c r="H1107" t="n">
         <v>4910</v>
@@ -32501,7 +32501,7 @@
         <v>10.8000001907349</v>
       </c>
       <c r="G1108" t="n">
-        <v>9.84051132202148</v>
+        <v>9.8405122756958</v>
       </c>
       <c r="H1108" t="n">
         <v>3654</v>
@@ -32530,7 +32530,7 @@
         <v>10.8999996185303</v>
       </c>
       <c r="G1109" t="n">
-        <v>9.93162727355957</v>
+        <v>9.93162822723389</v>
       </c>
       <c r="H1109" t="n">
         <v>534</v>
@@ -32559,7 +32559,7 @@
         <v>10.8000001907349</v>
       </c>
       <c r="G1110" t="n">
-        <v>9.84051132202148</v>
+        <v>9.8405122756958</v>
       </c>
       <c r="H1110" t="n">
         <v>2457</v>
@@ -32617,7 +32617,7 @@
         <v>10.8000001907349</v>
       </c>
       <c r="G1112" t="n">
-        <v>9.84051132202148</v>
+        <v>9.8405122756958</v>
       </c>
       <c r="H1112" t="n">
         <v>4426</v>
@@ -32646,7 +32646,7 @@
         <v>10.8999996185303</v>
       </c>
       <c r="G1113" t="n">
-        <v>9.93162727355957</v>
+        <v>9.93162822723389</v>
       </c>
       <c r="H1113" t="n">
         <v>1001</v>
@@ -32675,7 +32675,7 @@
         <v>10.8000001907349</v>
       </c>
       <c r="G1114" t="n">
-        <v>9.84051132202148</v>
+        <v>9.8405122756958</v>
       </c>
       <c r="H1114" t="n">
         <v>1323</v>
@@ -32704,7 +32704,7 @@
         <v>10.75</v>
       </c>
       <c r="G1115" t="n">
-        <v>9.79495334625244</v>
+        <v>9.79495429992676</v>
       </c>
       <c r="H1115" t="n">
         <v>6893</v>
@@ -32733,7 +32733,7 @@
         <v>10.75</v>
       </c>
       <c r="G1116" t="n">
-        <v>9.79495334625244</v>
+        <v>9.79495429992676</v>
       </c>
       <c r="H1116" t="n">
         <v>6550</v>
@@ -32791,7 +32791,7 @@
         <v>10.8999996185303</v>
       </c>
       <c r="G1118" t="n">
-        <v>9.93162727355957</v>
+        <v>9.93162822723389</v>
       </c>
       <c r="H1118" t="n">
         <v>7385</v>
@@ -32907,7 +32907,7 @@
         <v>11.1499996185303</v>
       </c>
       <c r="G1122" t="n">
-        <v>10.1594181060791</v>
+        <v>10.1594171524048</v>
       </c>
       <c r="H1122" t="n">
         <v>15698</v>
@@ -33168,7 +33168,7 @@
         <v>12.1000003814697</v>
       </c>
       <c r="G1131" t="n">
-        <v>11.0250186920166</v>
+        <v>11.0250196456909</v>
       </c>
       <c r="H1131" t="n">
         <v>13540</v>
@@ -33197,7 +33197,7 @@
         <v>12.3999996185303</v>
       </c>
       <c r="G1132" t="n">
-        <v>11.2983665466309</v>
+        <v>11.2983655929565</v>
       </c>
       <c r="H1132" t="n">
         <v>74102</v>
@@ -33255,7 +33255,7 @@
         <v>12.5</v>
       </c>
       <c r="G1134" t="n">
-        <v>11.3894834518433</v>
+        <v>11.3894824981689</v>
       </c>
       <c r="H1134" t="n">
         <v>13196</v>
@@ -33313,7 +33313,7 @@
         <v>12.6499996185303</v>
       </c>
       <c r="G1136" t="n">
-        <v>11.5261554718018</v>
+        <v>11.5261545181274</v>
       </c>
       <c r="H1136" t="n">
         <v>14112</v>
@@ -33342,7 +33342,7 @@
         <v>12.6499996185303</v>
       </c>
       <c r="G1137" t="n">
-        <v>11.5261554718018</v>
+        <v>11.5261545181274</v>
       </c>
       <c r="H1137" t="n">
         <v>13090</v>
@@ -33400,7 +33400,7 @@
         <v>12.8500003814697</v>
       </c>
       <c r="G1139" t="n">
-        <v>11.7083873748779</v>
+        <v>11.7083892822266</v>
       </c>
       <c r="H1139" t="n">
         <v>22061</v>
@@ -33487,7 +33487,7 @@
         <v>13.1499996185303</v>
       </c>
       <c r="G1142" t="n">
-        <v>11.9817352294922</v>
+        <v>11.9817342758179</v>
       </c>
       <c r="H1142" t="n">
         <v>17446</v>
@@ -33516,7 +33516,7 @@
         <v>13.25</v>
       </c>
       <c r="G1143" t="n">
-        <v>12.0728521347046</v>
+        <v>12.0728511810303</v>
       </c>
       <c r="H1143" t="n">
         <v>34754</v>
@@ -33545,7 +33545,7 @@
         <v>13.3500003814697</v>
       </c>
       <c r="G1144" t="n">
-        <v>12.163966178894</v>
+        <v>12.1639671325684</v>
       </c>
       <c r="H1144" t="n">
         <v>12489</v>
@@ -33574,7 +33574,7 @@
         <v>13.5</v>
       </c>
       <c r="G1145" t="n">
-        <v>12.3006391525269</v>
+        <v>12.3006401062012</v>
       </c>
       <c r="H1145" t="n">
         <v>75731</v>
@@ -33748,7 +33748,7 @@
         <v>13.3500003814697</v>
       </c>
       <c r="G1151" t="n">
-        <v>12.2953672409058</v>
+        <v>12.2953681945801</v>
       </c>
       <c r="H1151" t="n">
         <v>12253</v>
@@ -33777,7 +33777,7 @@
         <v>13.5</v>
       </c>
       <c r="G1152" t="n">
-        <v>12.4335165023804</v>
+        <v>12.4335174560547</v>
       </c>
       <c r="H1152" t="n">
         <v>6951</v>
@@ -33835,7 +33835,7 @@
         <v>13.25</v>
       </c>
       <c r="G1154" t="n">
-        <v>12.2032680511475</v>
+        <v>12.2032670974731</v>
       </c>
       <c r="H1154" t="n">
         <v>6770</v>
@@ -33864,7 +33864,7 @@
         <v>13.5</v>
       </c>
       <c r="G1155" t="n">
-        <v>12.4335165023804</v>
+        <v>12.4335174560547</v>
       </c>
       <c r="H1155" t="n">
         <v>40169</v>
@@ -33893,7 +33893,7 @@
         <v>13.6000003814697</v>
       </c>
       <c r="G1156" t="n">
-        <v>12.5256175994873</v>
+        <v>12.5256185531616</v>
       </c>
       <c r="H1156" t="n">
         <v>18328</v>
@@ -33922,7 +33922,7 @@
         <v>13.5</v>
       </c>
       <c r="G1157" t="n">
-        <v>12.4335165023804</v>
+        <v>12.4335174560547</v>
       </c>
       <c r="H1157" t="n">
         <v>24760</v>
@@ -33951,7 +33951,7 @@
         <v>13.6000003814697</v>
       </c>
       <c r="G1158" t="n">
-        <v>12.5256175994873</v>
+        <v>12.5256185531616</v>
       </c>
       <c r="H1158" t="n">
         <v>13524</v>
@@ -34009,7 +34009,7 @@
         <v>13.5500001907349</v>
       </c>
       <c r="G1160" t="n">
-        <v>12.479567527771</v>
+        <v>12.4795684814453</v>
       </c>
       <c r="H1160" t="n">
         <v>28389</v>
@@ -34038,7 +34038,7 @@
         <v>13.6000003814697</v>
       </c>
       <c r="G1161" t="n">
-        <v>12.5256175994873</v>
+        <v>12.5256185531616</v>
       </c>
       <c r="H1161" t="n">
         <v>12700</v>
@@ -34096,7 +34096,7 @@
         <v>13.25</v>
       </c>
       <c r="G1163" t="n">
-        <v>12.2032680511475</v>
+        <v>12.2032670974731</v>
       </c>
       <c r="H1163" t="n">
         <v>29089</v>
@@ -34125,7 +34125,7 @@
         <v>13.25</v>
       </c>
       <c r="G1164" t="n">
-        <v>12.2032680511475</v>
+        <v>12.2032670974731</v>
       </c>
       <c r="H1164" t="n">
         <v>25726</v>
@@ -34212,7 +34212,7 @@
         <v>13.25</v>
       </c>
       <c r="G1167" t="n">
-        <v>12.2032680511475</v>
+        <v>12.2032670974731</v>
       </c>
       <c r="H1167" t="n">
         <v>15931</v>
@@ -34241,7 +34241,7 @@
         <v>13.1499996185303</v>
       </c>
       <c r="G1168" t="n">
-        <v>12.1111669540405</v>
+        <v>12.1111660003662</v>
       </c>
       <c r="H1168" t="n">
         <v>13997</v>
@@ -34299,7 +34299,7 @@
         <v>13.3500003814697</v>
       </c>
       <c r="G1170" t="n">
-        <v>12.2953672409058</v>
+        <v>12.2953681945801</v>
       </c>
       <c r="H1170" t="n">
         <v>10823</v>
@@ -34328,7 +34328,7 @@
         <v>13.25</v>
       </c>
       <c r="G1171" t="n">
-        <v>12.2032680511475</v>
+        <v>12.2032670974731</v>
       </c>
       <c r="H1171" t="n">
         <v>29663</v>
@@ -34386,7 +34386,7 @@
         <v>13.6000003814697</v>
       </c>
       <c r="G1173" t="n">
-        <v>12.5256175994873</v>
+        <v>12.5256185531616</v>
       </c>
       <c r="H1173" t="n">
         <v>110733</v>
@@ -34415,7 +34415,7 @@
         <v>13.5500001907349</v>
       </c>
       <c r="G1174" t="n">
-        <v>12.479567527771</v>
+        <v>12.4795684814453</v>
       </c>
       <c r="H1174" t="n">
         <v>17802</v>
@@ -34444,7 +34444,7 @@
         <v>13.6999998092651</v>
       </c>
       <c r="G1175" t="n">
-        <v>12.6177167892456</v>
+        <v>12.6177177429199</v>
       </c>
       <c r="H1175" t="n">
         <v>6670</v>
@@ -34502,7 +34502,7 @@
         <v>13.5</v>
       </c>
       <c r="G1177" t="n">
-        <v>12.4335165023804</v>
+        <v>12.4335174560547</v>
       </c>
       <c r="H1177" t="n">
         <v>6774</v>
@@ -34560,7 +34560,7 @@
         <v>13.6000003814697</v>
       </c>
       <c r="G1179" t="n">
-        <v>12.5256175994873</v>
+        <v>12.5256185531616</v>
       </c>
       <c r="H1179" t="n">
         <v>3641</v>
@@ -34589,7 +34589,7 @@
         <v>13.6000003814697</v>
       </c>
       <c r="G1180" t="n">
-        <v>12.5256175994873</v>
+        <v>12.5256185531616</v>
       </c>
       <c r="H1180" t="n">
         <v>17307</v>
@@ -34618,7 +34618,7 @@
         <v>13.6000003814697</v>
       </c>
       <c r="G1181" t="n">
-        <v>12.5256175994873</v>
+        <v>12.5256185531616</v>
       </c>
       <c r="H1181" t="n">
         <v>2093</v>
@@ -34647,7 +34647,7 @@
         <v>13.6000003814697</v>
       </c>
       <c r="G1182" t="n">
-        <v>12.5256175994873</v>
+        <v>12.5256185531616</v>
       </c>
       <c r="H1182" t="n">
         <v>8035</v>
@@ -34676,7 +34676,7 @@
         <v>13.5500001907349</v>
       </c>
       <c r="G1183" t="n">
-        <v>12.479567527771</v>
+        <v>12.4795684814453</v>
       </c>
       <c r="H1183" t="n">
         <v>16220</v>
@@ -34734,7 +34734,7 @@
         <v>13.6000003814697</v>
       </c>
       <c r="G1185" t="n">
-        <v>12.5256175994873</v>
+        <v>12.5256185531616</v>
       </c>
       <c r="H1185" t="n">
         <v>6448</v>
@@ -34763,7 +34763,7 @@
         <v>13.6000003814697</v>
       </c>
       <c r="G1186" t="n">
-        <v>12.5256175994873</v>
+        <v>12.5256185531616</v>
       </c>
       <c r="H1186" t="n">
         <v>7807</v>
@@ -34792,7 +34792,7 @@
         <v>13.5</v>
       </c>
       <c r="G1187" t="n">
-        <v>12.4335165023804</v>
+        <v>12.4335174560547</v>
       </c>
       <c r="H1187" t="n">
         <v>6462</v>
@@ -34821,7 +34821,7 @@
         <v>13.5500001907349</v>
       </c>
       <c r="G1188" t="n">
-        <v>12.479567527771</v>
+        <v>12.4795684814453</v>
       </c>
       <c r="H1188" t="n">
         <v>22832</v>
@@ -34850,7 +34850,7 @@
         <v>13.3500003814697</v>
       </c>
       <c r="G1189" t="n">
-        <v>12.2953672409058</v>
+        <v>12.2953681945801</v>
       </c>
       <c r="H1189" t="n">
         <v>92732</v>
@@ -34908,7 +34908,7 @@
         <v>13.3500003814697</v>
       </c>
       <c r="G1191" t="n">
-        <v>12.2953672409058</v>
+        <v>12.2953681945801</v>
       </c>
       <c r="H1191" t="n">
         <v>13113</v>
@@ -34966,7 +34966,7 @@
         <v>13.3500003814697</v>
       </c>
       <c r="G1193" t="n">
-        <v>12.2953672409058</v>
+        <v>12.2953681945801</v>
       </c>
       <c r="H1193" t="n">
         <v>9634</v>
@@ -34995,7 +34995,7 @@
         <v>13.3500003814697</v>
       </c>
       <c r="G1194" t="n">
-        <v>12.2953672409058</v>
+        <v>12.2953681945801</v>
       </c>
       <c r="H1194" t="n">
         <v>8343</v>
@@ -35140,7 +35140,7 @@
         <v>13.6000003814697</v>
       </c>
       <c r="G1199" t="n">
-        <v>12.5256175994873</v>
+        <v>12.5256185531616</v>
       </c>
       <c r="H1199" t="n">
         <v>24469</v>
@@ -35198,7 +35198,7 @@
         <v>13.6999998092651</v>
       </c>
       <c r="G1201" t="n">
-        <v>12.6177167892456</v>
+        <v>12.6177177429199</v>
       </c>
       <c r="H1201" t="n">
         <v>13723</v>
@@ -35227,7 +35227,7 @@
         <v>13.6999998092651</v>
       </c>
       <c r="G1202" t="n">
-        <v>12.6177167892456</v>
+        <v>12.6177177429199</v>
       </c>
       <c r="H1202" t="n">
         <v>5288</v>
@@ -35285,7 +35285,7 @@
         <v>13.6000003814697</v>
       </c>
       <c r="G1204" t="n">
-        <v>12.5256175994873</v>
+        <v>12.5256185531616</v>
       </c>
       <c r="H1204" t="n">
         <v>10928</v>
@@ -35314,7 +35314,7 @@
         <v>13.3500003814697</v>
       </c>
       <c r="G1205" t="n">
-        <v>12.2953672409058</v>
+        <v>12.2953681945801</v>
       </c>
       <c r="H1205" t="n">
         <v>22149</v>
@@ -35343,7 +35343,7 @@
         <v>13.5</v>
       </c>
       <c r="G1206" t="n">
-        <v>12.4335165023804</v>
+        <v>12.4335174560547</v>
       </c>
       <c r="H1206" t="n">
         <v>7665</v>
@@ -35459,7 +35459,7 @@
         <v>13.3500003814697</v>
       </c>
       <c r="G1210" t="n">
-        <v>12.2953672409058</v>
+        <v>12.2953681945801</v>
       </c>
       <c r="H1210" t="n">
         <v>14763</v>
@@ -35488,7 +35488,7 @@
         <v>13.5</v>
       </c>
       <c r="G1211" t="n">
-        <v>12.4335165023804</v>
+        <v>12.4335174560547</v>
       </c>
       <c r="H1211" t="n">
         <v>20277</v>
@@ -35575,7 +35575,7 @@
         <v>13.9499998092651</v>
       </c>
       <c r="G1214" t="n">
-        <v>12.8479681015015</v>
+        <v>12.8479671478271</v>
       </c>
       <c r="H1214" t="n">
         <v>37997</v>
@@ -35633,7 +35633,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G1216" t="n">
-        <v>13.6308193206787</v>
+        <v>13.630820274353</v>
       </c>
       <c r="H1216" t="n">
         <v>30840</v>
@@ -35662,7 +35662,7 @@
         <v>15</v>
       </c>
       <c r="G1217" t="n">
-        <v>13.8150186538696</v>
+        <v>13.8150196075439</v>
       </c>
       <c r="H1217" t="n">
         <v>23642</v>
@@ -35720,7 +35720,7 @@
         <v>15.3000001907349</v>
       </c>
       <c r="G1219" t="n">
-        <v>14.0913190841675</v>
+        <v>14.0913209915161</v>
       </c>
       <c r="H1219" t="n">
         <v>29107</v>
@@ -35749,7 +35749,7 @@
         <v>15.5500001907349</v>
       </c>
       <c r="G1220" t="n">
-        <v>14.3215703964233</v>
+        <v>14.3215713500977</v>
       </c>
       <c r="H1220" t="n">
         <v>39798</v>
@@ -35894,7 +35894,7 @@
         <v>16.0499992370605</v>
       </c>
       <c r="G1225" t="n">
-        <v>14.7820701599121</v>
+        <v>14.7820711135864</v>
       </c>
       <c r="H1225" t="n">
         <v>15960</v>
@@ -35923,7 +35923,7 @@
         <v>16.2000007629395</v>
       </c>
       <c r="G1226" t="n">
-        <v>14.9202222824097</v>
+        <v>14.9202213287354</v>
       </c>
       <c r="H1226" t="n">
         <v>16853</v>
@@ -35981,7 +35981,7 @@
         <v>15.8999996185303</v>
       </c>
       <c r="G1228" t="n">
-        <v>14.6439208984375</v>
+        <v>14.6439199447632</v>
       </c>
       <c r="H1228" t="n">
         <v>13706</v>
@@ -36010,7 +36010,7 @@
         <v>16.2000007629395</v>
       </c>
       <c r="G1229" t="n">
-        <v>14.9202222824097</v>
+        <v>14.9202213287354</v>
       </c>
       <c r="H1229" t="n">
         <v>15791</v>
@@ -36039,7 +36039,7 @@
         <v>16.5</v>
       </c>
       <c r="G1230" t="n">
-        <v>15.1965227127075</v>
+        <v>15.1965208053589</v>
       </c>
       <c r="H1230" t="n">
         <v>19537</v>
@@ -36068,7 +36068,7 @@
         <v>16.4500007629395</v>
       </c>
       <c r="G1231" t="n">
-        <v>15.1504726409912</v>
+        <v>15.1504707336426</v>
       </c>
       <c r="H1231" t="n">
         <v>17502</v>
@@ -36097,7 +36097,7 @@
         <v>16.6000003814697</v>
       </c>
       <c r="G1232" t="n">
-        <v>15.2886228561401</v>
+        <v>15.2886219024658</v>
       </c>
       <c r="H1232" t="n">
         <v>26978</v>
@@ -36155,7 +36155,7 @@
         <v>18</v>
       </c>
       <c r="G1234" t="n">
-        <v>16.5780239105225</v>
+        <v>16.5780220031738</v>
       </c>
       <c r="H1234" t="n">
         <v>55851</v>
@@ -36213,7 +36213,7 @@
         <v>18</v>
       </c>
       <c r="G1236" t="n">
-        <v>16.5780239105225</v>
+        <v>16.5780220031738</v>
       </c>
       <c r="H1236" t="n">
         <v>29143</v>
@@ -36242,7 +36242,7 @@
         <v>17.8999996185303</v>
       </c>
       <c r="G1237" t="n">
-        <v>16.4859237670898</v>
+        <v>16.4859218597412</v>
       </c>
       <c r="H1237" t="n">
         <v>37360</v>
@@ -36271,7 +36271,7 @@
         <v>18.3500003814697</v>
       </c>
       <c r="G1238" t="n">
-        <v>16.9003734588623</v>
+        <v>16.9003753662109</v>
       </c>
       <c r="H1238" t="n">
         <v>63945</v>
@@ -36329,7 +36329,7 @@
         <v>18.1000003814697</v>
       </c>
       <c r="G1240" t="n">
-        <v>16.6701259613037</v>
+        <v>16.6701221466064</v>
       </c>
       <c r="H1240" t="n">
         <v>35362</v>
@@ -36387,7 +36387,7 @@
         <v>17.8999996185303</v>
       </c>
       <c r="G1242" t="n">
-        <v>16.4859237670898</v>
+        <v>16.4859218597412</v>
       </c>
       <c r="H1242" t="n">
         <v>32070</v>
@@ -36416,7 +36416,7 @@
         <v>18</v>
       </c>
       <c r="G1243" t="n">
-        <v>16.5780239105225</v>
+        <v>16.5780220031738</v>
       </c>
       <c r="H1243" t="n">
         <v>23468</v>
@@ -36445,7 +36445,7 @@
         <v>17.75</v>
       </c>
       <c r="G1244" t="n">
-        <v>16.3477725982666</v>
+        <v>16.3477745056152</v>
       </c>
       <c r="H1244" t="n">
         <v>8695</v>
@@ -36532,7 +36532,7 @@
         <v>17.7000007629395</v>
       </c>
       <c r="G1247" t="n">
-        <v>16.3017253875732</v>
+        <v>16.3017234802246</v>
       </c>
       <c r="H1247" t="n">
         <v>26545</v>
@@ -36590,7 +36590,7 @@
         <v>18.3500003814697</v>
       </c>
       <c r="G1249" t="n">
-        <v>16.9003734588623</v>
+        <v>16.9003753662109</v>
       </c>
       <c r="H1249" t="n">
         <v>83186</v>
@@ -36648,7 +36648,7 @@
         <v>17.3500003814697</v>
       </c>
       <c r="G1251" t="n">
-        <v>15.9793729782104</v>
+        <v>15.9793748855591</v>
       </c>
       <c r="H1251" t="n">
         <v>17720</v>
@@ -36764,7 +36764,7 @@
         <v>17.5</v>
       </c>
       <c r="G1255" t="n">
-        <v>16.1175231933594</v>
+        <v>16.1175212860107</v>
       </c>
       <c r="H1255" t="n">
         <v>42708</v>
@@ -36822,7 +36822,7 @@
         <v>17.3999996185303</v>
       </c>
       <c r="G1257" t="n">
-        <v>16.0254230499268</v>
+        <v>16.0254211425781</v>
       </c>
       <c r="H1257" t="n">
         <v>18760</v>
@@ -36851,7 +36851,7 @@
         <v>16.8999996185303</v>
       </c>
       <c r="G1258" t="n">
-        <v>15.5649213790894</v>
+        <v>15.5649223327637</v>
       </c>
       <c r="H1258" t="n">
         <v>66123</v>
@@ -36880,7 +36880,7 @@
         <v>17.2000007629395</v>
       </c>
       <c r="G1259" t="n">
-        <v>15.8412237167358</v>
+        <v>15.8412218093872</v>
       </c>
       <c r="H1259" t="n">
         <v>34176</v>
@@ -36967,7 +36967,7 @@
         <v>16.8999996185303</v>
       </c>
       <c r="G1262" t="n">
-        <v>15.5649213790894</v>
+        <v>15.5649223327637</v>
       </c>
       <c r="H1262" t="n">
         <v>11633</v>
@@ -37025,7 +37025,7 @@
         <v>17.2000007629395</v>
       </c>
       <c r="G1264" t="n">
-        <v>15.8412237167358</v>
+        <v>15.8412218093872</v>
       </c>
       <c r="H1264" t="n">
         <v>8184</v>
@@ -37054,7 +37054,7 @@
         <v>16.7999992370605</v>
       </c>
       <c r="G1265" t="n">
-        <v>15.4728202819824</v>
+        <v>15.4728221893311</v>
       </c>
       <c r="H1265" t="n">
         <v>8522</v>
@@ -37083,7 +37083,7 @@
         <v>17.3500003814697</v>
       </c>
       <c r="G1266" t="n">
-        <v>15.9793729782104</v>
+        <v>15.9793748855591</v>
       </c>
       <c r="H1266" t="n">
         <v>17689</v>
@@ -37141,7 +37141,7 @@
         <v>17.75</v>
       </c>
       <c r="G1268" t="n">
-        <v>16.3477725982666</v>
+        <v>16.3477745056152</v>
       </c>
       <c r="H1268" t="n">
         <v>31701</v>
@@ -37170,7 +37170,7 @@
         <v>18.1000003814697</v>
       </c>
       <c r="G1269" t="n">
-        <v>16.6701259613037</v>
+        <v>16.6701221466064</v>
       </c>
       <c r="H1269" t="n">
         <v>26641</v>
@@ -37228,7 +37228,7 @@
         <v>18.1000003814697</v>
       </c>
       <c r="G1271" t="n">
-        <v>16.6701259613037</v>
+        <v>16.6701221466064</v>
       </c>
       <c r="H1271" t="n">
         <v>24651</v>
@@ -37315,7 +37315,7 @@
         <v>18.25</v>
       </c>
       <c r="G1274" t="n">
-        <v>16.8082733154297</v>
+        <v>16.8082752227783</v>
       </c>
       <c r="H1274" t="n">
         <v>38466</v>
@@ -37344,7 +37344,7 @@
         <v>18.3500003814697</v>
       </c>
       <c r="G1275" t="n">
-        <v>16.9003734588623</v>
+        <v>16.9003753662109</v>
       </c>
       <c r="H1275" t="n">
         <v>24529</v>
@@ -37547,7 +37547,7 @@
         <v>17.7000007629395</v>
       </c>
       <c r="G1282" t="n">
-        <v>16.3017253875732</v>
+        <v>16.3017234802246</v>
       </c>
       <c r="H1282" t="n">
         <v>9795</v>
@@ -37576,7 +37576,7 @@
         <v>17.8999996185303</v>
       </c>
       <c r="G1283" t="n">
-        <v>16.4859237670898</v>
+        <v>16.4859218597412</v>
       </c>
       <c r="H1283" t="n">
         <v>10193</v>
@@ -37634,7 +37634,7 @@
         <v>17.8999996185303</v>
       </c>
       <c r="G1285" t="n">
-        <v>16.4859237670898</v>
+        <v>16.4859218597412</v>
       </c>
       <c r="H1285" t="n">
         <v>11787</v>
@@ -37663,7 +37663,7 @@
         <v>17.7000007629395</v>
       </c>
       <c r="G1286" t="n">
-        <v>16.3017253875732</v>
+        <v>16.3017234802246</v>
       </c>
       <c r="H1286" t="n">
         <v>8700</v>
@@ -37750,7 +37750,7 @@
         <v>17.7000007629395</v>
       </c>
       <c r="G1289" t="n">
-        <v>16.3017253875732</v>
+        <v>16.3017234802246</v>
       </c>
       <c r="H1289" t="n">
         <v>5832</v>
@@ -37779,7 +37779,7 @@
         <v>16.5</v>
       </c>
       <c r="G1290" t="n">
-        <v>15.1965227127075</v>
+        <v>15.1965208053589</v>
       </c>
       <c r="H1290" t="n">
         <v>76031</v>
@@ -37837,7 +37837,7 @@
         <v>16.1000003814697</v>
       </c>
       <c r="G1292" t="n">
-        <v>14.8281221389771</v>
+        <v>14.8281211853027</v>
       </c>
       <c r="H1292" t="n">
         <v>32547</v>
@@ -38069,7 +38069,7 @@
         <v>15.0500001907349</v>
       </c>
       <c r="G1300" t="n">
-        <v>13.8610696792603</v>
+        <v>13.8610706329346</v>
       </c>
       <c r="H1300" t="n">
         <v>16158</v>
@@ -38214,7 +38214,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G1305" t="n">
-        <v>13.6308193206787</v>
+        <v>13.630820274353</v>
       </c>
       <c r="H1305" t="n">
         <v>6433</v>
@@ -38243,7 +38243,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G1306" t="n">
-        <v>13.9992189407349</v>
+        <v>13.9992198944092</v>
       </c>
       <c r="H1306" t="n">
         <v>33686</v>
@@ -38330,7 +38330,7 @@
         <v>15</v>
       </c>
       <c r="G1309" t="n">
-        <v>13.8150186538696</v>
+        <v>13.8150196075439</v>
       </c>
       <c r="H1309" t="n">
         <v>32486</v>
@@ -38388,7 +38388,7 @@
         <v>15</v>
       </c>
       <c r="G1311" t="n">
-        <v>13.8150186538696</v>
+        <v>13.8150196075439</v>
       </c>
       <c r="H1311" t="n">
         <v>23397</v>
@@ -38417,7 +38417,7 @@
         <v>15.0500001907349</v>
       </c>
       <c r="G1312" t="n">
-        <v>13.8610696792603</v>
+        <v>13.8610706329346</v>
       </c>
       <c r="H1312" t="n">
         <v>19109</v>
@@ -38446,7 +38446,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G1313" t="n">
-        <v>13.9992189407349</v>
+        <v>13.9992198944092</v>
       </c>
       <c r="H1313" t="n">
         <v>22212</v>
@@ -38475,7 +38475,7 @@
         <v>14.9499998092651</v>
       </c>
       <c r="G1314" t="n">
-        <v>13.7689685821533</v>
+        <v>13.7689695358276</v>
       </c>
       <c r="H1314" t="n">
         <v>10398</v>
@@ -38533,7 +38533,7 @@
         <v>15</v>
       </c>
       <c r="G1316" t="n">
-        <v>13.8150186538696</v>
+        <v>13.8150196075439</v>
       </c>
       <c r="H1316" t="n">
         <v>22564</v>
@@ -38678,7 +38678,7 @@
         <v>15.5500001907349</v>
       </c>
       <c r="G1321" t="n">
-        <v>14.3215703964233</v>
+        <v>14.3215713500977</v>
       </c>
       <c r="H1321" t="n">
         <v>12139</v>
@@ -38736,7 +38736,7 @@
         <v>15.6000003814697</v>
       </c>
       <c r="G1323" t="n">
-        <v>14.367621421814</v>
+        <v>14.3676195144653</v>
       </c>
       <c r="H1323" t="n">
         <v>7547</v>
@@ -38794,7 +38794,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G1325" t="n">
-        <v>13.9992189407349</v>
+        <v>13.9992198944092</v>
       </c>
       <c r="H1325" t="n">
         <v>19479</v>
@@ -38823,7 +38823,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G1326" t="n">
-        <v>13.5387182235718</v>
+        <v>13.5387191772461</v>
       </c>
       <c r="H1326" t="n">
         <v>9817</v>
@@ -38910,7 +38910,7 @@
         <v>14.1999998092651</v>
       </c>
       <c r="G1329" t="n">
-        <v>13.0782175064087</v>
+        <v>13.078218460083</v>
       </c>
       <c r="H1329" t="n">
         <v>22122</v>
@@ -38939,7 +38939,7 @@
         <v>14.3000001907349</v>
       </c>
       <c r="G1330" t="n">
-        <v>13.1703176498413</v>
+        <v>13.1703186035156</v>
       </c>
       <c r="H1330" t="n">
         <v>5806</v>
@@ -38968,7 +38968,7 @@
         <v>13.8999996185303</v>
       </c>
       <c r="G1331" t="n">
-        <v>12.8019180297852</v>
+        <v>12.8019170761108</v>
       </c>
       <c r="H1331" t="n">
         <v>4498</v>
@@ -38997,7 +38997,7 @@
         <v>14.1999998092651</v>
       </c>
       <c r="G1332" t="n">
-        <v>13.0782175064087</v>
+        <v>13.078218460083</v>
       </c>
       <c r="H1332" t="n">
         <v>14523</v>
@@ -39026,7 +39026,7 @@
         <v>14.1999998092651</v>
       </c>
       <c r="G1333" t="n">
-        <v>13.0782175064087</v>
+        <v>13.078218460083</v>
       </c>
       <c r="H1333" t="n">
         <v>11624</v>
@@ -39055,7 +39055,7 @@
         <v>13.9499998092651</v>
       </c>
       <c r="G1334" t="n">
-        <v>12.8479681015015</v>
+        <v>12.8479671478271</v>
       </c>
       <c r="H1334" t="n">
         <v>9361</v>
@@ -39142,7 +39142,7 @@
         <v>13.8500003814697</v>
       </c>
       <c r="G1337" t="n">
-        <v>12.7558689117432</v>
+        <v>12.7558679580688</v>
       </c>
       <c r="H1337" t="n">
         <v>18208</v>
@@ -39171,7 +39171,7 @@
         <v>13.5500001907349</v>
       </c>
       <c r="G1338" t="n">
-        <v>12.479567527771</v>
+        <v>12.4795684814453</v>
       </c>
       <c r="H1338" t="n">
         <v>30533</v>
@@ -39229,7 +39229,7 @@
         <v>13.6000003814697</v>
       </c>
       <c r="G1340" t="n">
-        <v>12.5256175994873</v>
+        <v>12.5256185531616</v>
       </c>
       <c r="H1340" t="n">
         <v>6667</v>
@@ -39287,7 +39287,7 @@
         <v>13.5</v>
       </c>
       <c r="G1342" t="n">
-        <v>12.4335165023804</v>
+        <v>12.4335174560547</v>
       </c>
       <c r="H1342" t="n">
         <v>3861</v>
@@ -39345,7 +39345,7 @@
         <v>13.6999998092651</v>
       </c>
       <c r="G1344" t="n">
-        <v>12.6177167892456</v>
+        <v>12.6177177429199</v>
       </c>
       <c r="H1344" t="n">
         <v>15976</v>
@@ -39374,7 +39374,7 @@
         <v>13.5500001907349</v>
       </c>
       <c r="G1345" t="n">
-        <v>12.479567527771</v>
+        <v>12.4795684814453</v>
       </c>
       <c r="H1345" t="n">
         <v>19625</v>
@@ -39403,7 +39403,7 @@
         <v>13.1999998092651</v>
       </c>
       <c r="G1346" t="n">
-        <v>12.1572179794312</v>
+        <v>12.1572170257568</v>
       </c>
       <c r="H1346" t="n">
         <v>24360</v>
@@ -39490,7 +39490,7 @@
         <v>12.8000001907349</v>
       </c>
       <c r="G1349" t="n">
-        <v>11.7888164520264</v>
+        <v>11.7888174057007</v>
       </c>
       <c r="H1349" t="n">
         <v>24319</v>
@@ -39635,7 +39635,7 @@
         <v>12.8500003814697</v>
       </c>
       <c r="G1354" t="n">
-        <v>11.8348665237427</v>
+        <v>11.8348684310913</v>
       </c>
       <c r="H1354" t="n">
         <v>8453</v>
@@ -39809,7 +39809,7 @@
         <v>12</v>
       </c>
       <c r="G1360" t="n">
-        <v>11.0520172119141</v>
+        <v>11.0520153045654</v>
       </c>
       <c r="H1360" t="n">
         <v>9891</v>
@@ -39838,7 +39838,7 @@
         <v>12.1499996185303</v>
       </c>
       <c r="G1361" t="n">
-        <v>11.19016456604</v>
+        <v>11.1901655197144</v>
       </c>
       <c r="H1361" t="n">
         <v>23112</v>
@@ -39925,7 +39925,7 @@
         <v>12.1499996185303</v>
       </c>
       <c r="G1364" t="n">
-        <v>11.19016456604</v>
+        <v>11.1901655197144</v>
       </c>
       <c r="H1364" t="n">
         <v>4942</v>
@@ -39954,7 +39954,7 @@
         <v>12.1499996185303</v>
       </c>
       <c r="G1365" t="n">
-        <v>11.19016456604</v>
+        <v>11.1901655197144</v>
       </c>
       <c r="H1365" t="n">
         <v>7074</v>
@@ -39983,7 +39983,7 @@
         <v>11.6999998092651</v>
       </c>
       <c r="G1366" t="n">
-        <v>10.7757158279419</v>
+        <v>10.7757148742676</v>
       </c>
       <c r="H1366" t="n">
         <v>4839</v>
@@ -40041,7 +40041,7 @@
         <v>11.6999998092651</v>
       </c>
       <c r="G1368" t="n">
-        <v>10.7757158279419</v>
+        <v>10.7757148742676</v>
       </c>
       <c r="H1368" t="n">
         <v>10060</v>
@@ -40070,7 +40070,7 @@
         <v>11.6999998092651</v>
       </c>
       <c r="G1369" t="n">
-        <v>10.7757158279419</v>
+        <v>10.7757148742676</v>
       </c>
       <c r="H1369" t="n">
         <v>8696</v>
@@ -40099,7 +40099,7 @@
         <v>11.9499998092651</v>
       </c>
       <c r="G1370" t="n">
-        <v>11.0059661865234</v>
+        <v>11.0059652328491</v>
       </c>
       <c r="H1370" t="n">
         <v>8903</v>
@@ -40128,7 +40128,7 @@
         <v>12</v>
       </c>
       <c r="G1371" t="n">
-        <v>11.0520172119141</v>
+        <v>11.0520153045654</v>
       </c>
       <c r="H1371" t="n">
         <v>4332</v>
@@ -40157,7 +40157,7 @@
         <v>12.3500003814697</v>
       </c>
       <c r="G1372" t="n">
-        <v>11.3743667602539</v>
+        <v>11.3743677139282</v>
       </c>
       <c r="H1372" t="n">
         <v>2891</v>
@@ -40186,7 +40186,7 @@
         <v>12.1000003814697</v>
       </c>
       <c r="G1373" t="n">
-        <v>11.144115447998</v>
+        <v>11.1441164016724</v>
       </c>
       <c r="H1373" t="n">
         <v>3062</v>
@@ -40215,7 +40215,7 @@
         <v>12.0500001907349</v>
       </c>
       <c r="G1374" t="n">
-        <v>11.0980653762817</v>
+        <v>11.0980663299561</v>
       </c>
       <c r="H1374" t="n">
         <v>6759</v>
@@ -40244,7 +40244,7 @@
         <v>12.5</v>
       </c>
       <c r="G1375" t="n">
-        <v>11.5125169754028</v>
+        <v>11.5125160217285</v>
       </c>
       <c r="H1375" t="n">
         <v>3725</v>
@@ -40331,7 +40331,7 @@
         <v>12.8500003814697</v>
       </c>
       <c r="G1378" t="n">
-        <v>11.8348665237427</v>
+        <v>11.8348684310913</v>
       </c>
       <c r="H1378" t="n">
         <v>2949</v>
@@ -40534,7 +40534,7 @@
         <v>13.5500001907349</v>
       </c>
       <c r="G1385" t="n">
-        <v>12.479567527771</v>
+        <v>12.4795684814453</v>
       </c>
       <c r="H1385" t="n">
         <v>10551</v>
@@ -40592,7 +40592,7 @@
         <v>10.1000003814697</v>
       </c>
       <c r="G1387" t="n">
-        <v>9.3021125793457</v>
+        <v>9.30211448669434</v>
       </c>
       <c r="H1387" t="n">
         <v>241281</v>
@@ -40679,7 +40679,7 @@
         <v>8.86999988555908</v>
       </c>
       <c r="G1390" t="n">
-        <v>8.16928195953369</v>
+        <v>8.16928005218506</v>
       </c>
       <c r="H1390" t="n">
         <v>87871</v>
@@ -40708,7 +40708,7 @@
         <v>9.02000045776367</v>
       </c>
       <c r="G1391" t="n">
-        <v>8.30743312835693</v>
+        <v>8.30743217468262</v>
       </c>
       <c r="H1391" t="n">
         <v>49666</v>
@@ -40766,7 +40766,7 @@
         <v>9.01000022888184</v>
       </c>
       <c r="G1393" t="n">
-        <v>8.29822158813477</v>
+        <v>8.29822063446045</v>
       </c>
       <c r="H1393" t="n">
         <v>15513</v>
@@ -40795,7 +40795,7 @@
         <v>8.89000034332275</v>
       </c>
       <c r="G1394" t="n">
-        <v>8.18770217895508</v>
+        <v>8.18770122528076</v>
       </c>
       <c r="H1394" t="n">
         <v>15541</v>
@@ -40853,7 +40853,7 @@
         <v>9</v>
       </c>
       <c r="G1396" t="n">
-        <v>8.28901195526123</v>
+        <v>8.28901100158691</v>
       </c>
       <c r="H1396" t="n">
         <v>6827</v>
@@ -40940,7 +40940,7 @@
         <v>8.76000022888184</v>
       </c>
       <c r="G1399" t="n">
-        <v>8.06797122955322</v>
+        <v>8.06797027587891</v>
       </c>
       <c r="H1399" t="n">
         <v>29904</v>
@@ -40998,7 +40998,7 @@
         <v>8.3100004196167</v>
       </c>
       <c r="G1401" t="n">
-        <v>7.65352058410645</v>
+        <v>7.6535210609436</v>
       </c>
       <c r="H1401" t="n">
         <v>21362</v>
@@ -41114,7 +41114,7 @@
         <v>8.35999965667725</v>
       </c>
       <c r="G1405" t="n">
-        <v>7.6995701789856</v>
+        <v>7.69957113265991</v>
       </c>
       <c r="H1405" t="n">
         <v>38004</v>
@@ -41172,7 +41172,7 @@
         <v>8.01000022888184</v>
       </c>
       <c r="G1407" t="n">
-        <v>7.37722063064575</v>
+        <v>7.37722015380859</v>
       </c>
       <c r="H1407" t="n">
         <v>9665</v>
@@ -41230,7 +41230,7 @@
         <v>7.59999990463257</v>
       </c>
       <c r="G1409" t="n">
-        <v>6.99960947036743</v>
+        <v>6.99960994720459</v>
       </c>
       <c r="H1409" t="n">
         <v>28306</v>
@@ -41317,7 +41317,7 @@
         <v>7.40000009536743</v>
       </c>
       <c r="G1412" t="n">
-        <v>6.81540966033936</v>
+        <v>6.81541013717651</v>
       </c>
       <c r="H1412" t="n">
         <v>13765</v>
@@ -41346,7 +41346,7 @@
         <v>7.53999996185303</v>
       </c>
       <c r="G1413" t="n">
-        <v>6.94434928894043</v>
+        <v>6.94434976577759</v>
       </c>
       <c r="H1413" t="n">
         <v>25992</v>
@@ -41375,7 +41375,7 @@
         <v>7.5</v>
       </c>
       <c r="G1414" t="n">
-        <v>6.90750932693481</v>
+        <v>6.90750980377197</v>
       </c>
       <c r="H1414" t="n">
         <v>11598</v>
@@ -41433,7 +41433,7 @@
         <v>8.05000019073486</v>
       </c>
       <c r="G1416" t="n">
-        <v>7.41406106948853</v>
+        <v>7.41406059265137</v>
       </c>
       <c r="H1416" t="n">
         <v>14741</v>
@@ -41491,7 +41491,7 @@
         <v>8.75</v>
       </c>
       <c r="G1418" t="n">
-        <v>8.05876159667969</v>
+        <v>8.05876064300537</v>
       </c>
       <c r="H1418" t="n">
         <v>24664</v>
@@ -41520,7 +41520,7 @@
         <v>8.77000045776367</v>
       </c>
       <c r="G1419" t="n">
-        <v>8.07718086242676</v>
+        <v>8.07718181610107</v>
       </c>
       <c r="H1419" t="n">
         <v>21481</v>
@@ -41549,7 +41549,7 @@
         <v>9</v>
       </c>
       <c r="G1420" t="n">
-        <v>8.28901195526123</v>
+        <v>8.28901100158691</v>
       </c>
       <c r="H1420" t="n">
         <v>62353</v>
@@ -41665,7 +41665,7 @@
         <v>9.10000038146973</v>
       </c>
       <c r="G1424" t="n">
-        <v>8.53280735015869</v>
+        <v>8.53280639648438</v>
       </c>
       <c r="H1424" t="n">
         <v>15786</v>
@@ -41694,7 +41694,7 @@
         <v>9.19999980926514</v>
       </c>
       <c r="G1425" t="n">
-        <v>8.62657260894775</v>
+        <v>8.62657356262207</v>
       </c>
       <c r="H1425" t="n">
         <v>17323</v>
@@ -41723,7 +41723,7 @@
         <v>9.27000045776367</v>
       </c>
       <c r="G1426" t="n">
-        <v>8.69221115112305</v>
+        <v>8.69221210479736</v>
       </c>
       <c r="H1426" t="n">
         <v>12689</v>
@@ -41752,7 +41752,7 @@
         <v>9.10000038146973</v>
       </c>
       <c r="G1427" t="n">
-        <v>8.53280735015869</v>
+        <v>8.53280639648438</v>
       </c>
       <c r="H1427" t="n">
         <v>17846</v>
@@ -41839,7 +41839,7 @@
         <v>8.90999984741211</v>
       </c>
       <c r="G1430" t="n">
-        <v>8.35464859008789</v>
+        <v>8.35464954376221</v>
       </c>
       <c r="H1430" t="n">
         <v>25920</v>
@@ -41868,7 +41868,7 @@
         <v>8.82999992370605</v>
       </c>
       <c r="G1431" t="n">
-        <v>8.27963638305664</v>
+        <v>8.27963542938232</v>
       </c>
       <c r="H1431" t="n">
         <v>3860</v>
@@ -41926,7 +41926,7 @@
         <v>9.02000045776367</v>
       </c>
       <c r="G1433" t="n">
-        <v>8.45779418945312</v>
+        <v>8.45779323577881</v>
       </c>
       <c r="H1433" t="n">
         <v>12940</v>
@@ -42013,7 +42013,7 @@
         <v>8.52000045776367</v>
       </c>
       <c r="G1436" t="n">
-        <v>7.98895835876465</v>
+        <v>7.98895740509033</v>
       </c>
       <c r="H1436" t="n">
         <v>10806</v>
@@ -42158,7 +42158,7 @@
         <v>8.52000045776367</v>
       </c>
       <c r="G1441" t="n">
-        <v>7.98895835876465</v>
+        <v>7.98895740509033</v>
       </c>
       <c r="H1441" t="n">
         <v>2908</v>
@@ -42216,7 +42216,7 @@
         <v>8.60000038146973</v>
       </c>
       <c r="G1443" t="n">
-        <v>8.0639705657959</v>
+        <v>8.06397151947021</v>
       </c>
       <c r="H1443" t="n">
         <v>7343</v>
@@ -42245,7 +42245,7 @@
         <v>8.60000038146973</v>
       </c>
       <c r="G1444" t="n">
-        <v>8.0639705657959</v>
+        <v>8.06397151947021</v>
       </c>
       <c r="H1444" t="n">
         <v>8751</v>
@@ -42390,7 +42390,7 @@
         <v>8.3100004196167</v>
       </c>
       <c r="G1449" t="n">
-        <v>7.79204607009888</v>
+        <v>7.79204654693604</v>
       </c>
       <c r="H1449" t="n">
         <v>2606</v>
@@ -42477,7 +42477,7 @@
         <v>8.65999984741211</v>
       </c>
       <c r="G1452" t="n">
-        <v>8.12023162841797</v>
+        <v>8.12023067474365</v>
       </c>
       <c r="H1452" t="n">
         <v>4014</v>
@@ -42593,7 +42593,7 @@
         <v>8.60000038146973</v>
       </c>
       <c r="G1456" t="n">
-        <v>8.0639705657959</v>
+        <v>8.06397151947021</v>
       </c>
       <c r="H1456" t="n">
         <v>4390</v>
@@ -42622,7 +42622,7 @@
         <v>8.42000007629395</v>
       </c>
       <c r="G1457" t="n">
-        <v>7.89519071578979</v>
+        <v>7.89519023895264</v>
       </c>
       <c r="H1457" t="n">
         <v>3526</v>
@@ -42680,7 +42680,7 @@
         <v>8.35000038146973</v>
       </c>
       <c r="G1459" t="n">
-        <v>7.82955265045166</v>
+        <v>7.82955312728882</v>
       </c>
       <c r="H1459" t="n">
         <v>609</v>
@@ -42738,7 +42738,7 @@
         <v>8.23999977111816</v>
       </c>
       <c r="G1461" t="n">
-        <v>7.72640943527222</v>
+        <v>7.72640895843506</v>
       </c>
       <c r="H1461" t="n">
         <v>7810</v>
@@ -43028,7 +43028,7 @@
         <v>8.02999973297119</v>
       </c>
       <c r="G1471" t="n">
-        <v>7.52949857711792</v>
+        <v>7.52949810028076</v>
       </c>
       <c r="H1471" t="n">
         <v>8187</v>
@@ -43115,7 +43115,7 @@
         <v>8.51000022888184</v>
       </c>
       <c r="G1474" t="n">
-        <v>7.97958040237427</v>
+        <v>7.97957944869995</v>
       </c>
       <c r="H1474" t="n">
         <v>17996</v>
@@ -43231,7 +43231,7 @@
         <v>8.63000011444092</v>
       </c>
       <c r="G1478" t="n">
-        <v>8.09210109710693</v>
+        <v>8.09210205078125</v>
       </c>
       <c r="H1478" t="n">
         <v>2527</v>
@@ -43260,7 +43260,7 @@
         <v>8.72000026702881</v>
       </c>
       <c r="G1479" t="n">
-        <v>8.17649173736572</v>
+        <v>8.17649078369141</v>
       </c>
       <c r="H1479" t="n">
         <v>2805</v>
@@ -43318,7 +43318,7 @@
         <v>8.61999988555908</v>
       </c>
       <c r="G1481" t="n">
-        <v>8.08272457122803</v>
+        <v>8.08272361755371</v>
       </c>
       <c r="H1481" t="n">
         <v>4281</v>
@@ -43347,7 +43347,7 @@
         <v>8.60000038146973</v>
       </c>
       <c r="G1482" t="n">
-        <v>8.0639705657959</v>
+        <v>8.06397151947021</v>
       </c>
       <c r="H1482" t="n">
         <v>3831</v>
@@ -43434,7 +43434,7 @@
         <v>8.64999961853027</v>
       </c>
       <c r="G1485" t="n">
-        <v>8.11085319519043</v>
+        <v>8.11085414886475</v>
       </c>
       <c r="H1485" t="n">
         <v>5493</v>
@@ -43492,7 +43492,7 @@
         <v>8.76000022888184</v>
       </c>
       <c r="G1487" t="n">
-        <v>8.21399879455566</v>
+        <v>8.21399784088135</v>
       </c>
       <c r="H1487" t="n">
         <v>2098</v>
@@ -43579,7 +43579,7 @@
         <v>8.34000015258789</v>
       </c>
       <c r="G1490" t="n">
-        <v>7.82017612457275</v>
+        <v>7.82017660140991</v>
       </c>
       <c r="H1490" t="n">
         <v>9472</v>
@@ -43608,7 +43608,7 @@
         <v>8.3100004196167</v>
       </c>
       <c r="G1491" t="n">
-        <v>7.79204607009888</v>
+        <v>7.79204654693604</v>
       </c>
       <c r="H1491" t="n">
         <v>4655</v>
@@ -43637,7 +43637,7 @@
         <v>8.23999977111816</v>
       </c>
       <c r="G1492" t="n">
-        <v>7.72640943527222</v>
+        <v>7.72640895843506</v>
       </c>
       <c r="H1492" t="n">
         <v>7241</v>
@@ -43666,7 +43666,7 @@
         <v>8.14999961853027</v>
       </c>
       <c r="G1493" t="n">
-        <v>7.64201879501343</v>
+        <v>7.64201831817627</v>
       </c>
       <c r="H1493" t="n">
         <v>3731</v>
@@ -43753,7 +43753,7 @@
         <v>8.35999965667725</v>
       </c>
       <c r="G1496" t="n">
-        <v>7.83892965316772</v>
+        <v>7.83893013000488</v>
       </c>
       <c r="H1496" t="n">
         <v>3456</v>
@@ -43782,7 +43782,7 @@
         <v>8.3100004196167</v>
       </c>
       <c r="G1497" t="n">
-        <v>7.79204607009888</v>
+        <v>7.79204654693604</v>
       </c>
       <c r="H1497" t="n">
         <v>2445</v>
@@ -44014,7 +44014,7 @@
         <v>8.35000038146973</v>
       </c>
       <c r="G1505" t="n">
-        <v>7.82955265045166</v>
+        <v>7.82955312728882</v>
       </c>
       <c r="H1505" t="n">
         <v>4398</v>
@@ -44043,7 +44043,7 @@
         <v>8.05000019073486</v>
       </c>
       <c r="G1506" t="n">
-        <v>7.54825210571289</v>
+        <v>7.54825162887573</v>
       </c>
       <c r="H1506" t="n">
         <v>2378</v>
@@ -44130,7 +44130,7 @@
         <v>8.10999965667725</v>
       </c>
       <c r="G1509" t="n">
-        <v>7.60451126098633</v>
+        <v>7.60451173782349</v>
       </c>
       <c r="H1509" t="n">
         <v>3386</v>
@@ -44159,7 +44159,7 @@
         <v>8.06999969482422</v>
       </c>
       <c r="G1510" t="n">
-        <v>7.5670051574707</v>
+        <v>7.56700468063354</v>
       </c>
       <c r="H1510" t="n">
         <v>5657</v>
@@ -44246,7 +44246,7 @@
         <v>7.80000019073486</v>
       </c>
       <c r="G1513" t="n">
-        <v>7.31383371353149</v>
+        <v>7.31383419036865</v>
       </c>
       <c r="H1513" t="n">
         <v>662</v>
@@ -44304,7 +44304,7 @@
         <v>7.80000019073486</v>
       </c>
       <c r="G1515" t="n">
-        <v>7.31383371353149</v>
+        <v>7.31383419036865</v>
       </c>
       <c r="H1515" t="n">
         <v>4982</v>
@@ -44333,7 +44333,7 @@
         <v>7.98999977111816</v>
       </c>
       <c r="G1516" t="n">
-        <v>7.49199104309082</v>
+        <v>7.49199151992798</v>
       </c>
       <c r="H1516" t="n">
         <v>1046</v>
@@ -44478,7 +44478,7 @@
         <v>7.55000019073486</v>
       </c>
       <c r="G1521" t="n">
-        <v>7.07941675186157</v>
+        <v>7.07941627502441</v>
       </c>
       <c r="H1521" t="n">
         <v>1148</v>
@@ -44536,7 +44536,7 @@
         <v>7.48999977111816</v>
       </c>
       <c r="G1523" t="n">
-        <v>7.02315616607666</v>
+        <v>7.0231556892395</v>
       </c>
       <c r="H1523" t="n">
         <v>3388</v>
@@ -44768,7 +44768,7 @@
         <v>7.82999992370605</v>
       </c>
       <c r="G1531" t="n">
-        <v>7.34196424484253</v>
+        <v>7.34196376800537</v>
       </c>
       <c r="H1531" t="n">
         <v>2574</v>
@@ -44797,7 +44797,7 @@
         <v>7.76999998092651</v>
       </c>
       <c r="G1532" t="n">
-        <v>7.28570413589478</v>
+        <v>7.28570365905762</v>
       </c>
       <c r="H1532" t="n">
         <v>3526</v>
@@ -44826,7 +44826,7 @@
         <v>7.80999994277954</v>
       </c>
       <c r="G1533" t="n">
-        <v>7.3232102394104</v>
+        <v>7.32321071624756</v>
       </c>
       <c r="H1533" t="n">
         <v>459</v>
@@ -44855,7 +44855,7 @@
         <v>7.6399998664856</v>
       </c>
       <c r="G1534" t="n">
-        <v>7.16380596160889</v>
+        <v>7.16380643844604</v>
       </c>
       <c r="H1534" t="n">
         <v>7564</v>
@@ -44884,7 +44884,7 @@
         <v>7.75</v>
       </c>
       <c r="G1535" t="n">
-        <v>7.2669506072998</v>
+        <v>7.26695013046265</v>
       </c>
       <c r="H1535" t="n">
         <v>4595</v>
@@ -44942,7 +44942,7 @@
         <v>7.69000005722046</v>
       </c>
       <c r="G1537" t="n">
-        <v>7.21069002151489</v>
+        <v>7.21069049835205</v>
       </c>
       <c r="H1537" t="n">
         <v>210</v>
@@ -45000,7 +45000,7 @@
         <v>7.69000005722046</v>
       </c>
       <c r="G1539" t="n">
-        <v>7.21069002151489</v>
+        <v>7.21069049835205</v>
       </c>
       <c r="H1539" t="n">
         <v>60</v>
@@ -45116,7 +45116,7 @@
         <v>8.28999996185303</v>
       </c>
       <c r="G1543" t="n">
-        <v>7.77329349517822</v>
+        <v>7.77329301834106</v>
       </c>
       <c r="H1543" t="n">
         <v>12100</v>
@@ -45145,7 +45145,7 @@
         <v>8.32999992370605</v>
       </c>
       <c r="G1544" t="n">
-        <v>7.81079959869385</v>
+        <v>7.81080007553101</v>
       </c>
       <c r="H1544" t="n">
         <v>6825</v>
@@ -45203,7 +45203,7 @@
         <v>7.80000019073486</v>
       </c>
       <c r="G1546" t="n">
-        <v>7.31383371353149</v>
+        <v>7.31383419036865</v>
       </c>
       <c r="H1546" t="n">
         <v>5724</v>
@@ -45406,7 +45406,7 @@
         <v>8.26000022888184</v>
       </c>
       <c r="G1553" t="n">
-        <v>7.74516344070435</v>
+        <v>7.74516296386719</v>
       </c>
       <c r="H1553" t="n">
         <v>3488</v>
@@ -45464,7 +45464,7 @@
         <v>8.35000038146973</v>
       </c>
       <c r="G1555" t="n">
-        <v>7.82955265045166</v>
+        <v>7.82955312728882</v>
       </c>
       <c r="H1555" t="n">
         <v>6040</v>
@@ -45522,7 +45522,7 @@
         <v>8.28999996185303</v>
       </c>
       <c r="G1557" t="n">
-        <v>7.77329349517822</v>
+        <v>7.77329301834106</v>
       </c>
       <c r="H1557" t="n">
         <v>1372</v>
@@ -45551,7 +45551,7 @@
         <v>8.35000038146973</v>
       </c>
       <c r="G1558" t="n">
-        <v>7.82955265045166</v>
+        <v>7.82955312728882</v>
       </c>
       <c r="H1558" t="n">
         <v>1827</v>
@@ -45580,7 +45580,7 @@
         <v>8.35000038146973</v>
       </c>
       <c r="G1559" t="n">
-        <v>7.82955265045166</v>
+        <v>7.82955312728882</v>
       </c>
       <c r="H1559" t="n">
         <v>240</v>
@@ -45638,7 +45638,7 @@
         <v>8.28999996185303</v>
       </c>
       <c r="G1561" t="n">
-        <v>7.77329349517822</v>
+        <v>7.77329301834106</v>
       </c>
       <c r="H1561" t="n">
         <v>1367</v>
@@ -45667,7 +45667,7 @@
         <v>8.28999996185303</v>
       </c>
       <c r="G1562" t="n">
-        <v>7.77329349517822</v>
+        <v>7.77329301834106</v>
       </c>
       <c r="H1562" t="n">
         <v>58</v>
@@ -45696,7 +45696,7 @@
         <v>8.38000011444092</v>
       </c>
       <c r="G1563" t="n">
-        <v>7.8576831817627</v>
+        <v>7.85768365859985</v>
       </c>
       <c r="H1563" t="n">
         <v>502</v>
@@ -45812,7 +45812,7 @@
         <v>8.35999965667725</v>
       </c>
       <c r="G1567" t="n">
-        <v>7.83892965316772</v>
+        <v>7.83893013000488</v>
       </c>
       <c r="H1567" t="n">
         <v>10959</v>
@@ -46015,7 +46015,7 @@
         <v>8.28999996185303</v>
       </c>
       <c r="G1574" t="n">
-        <v>7.77329349517822</v>
+        <v>7.77329301834106</v>
       </c>
       <c r="H1574" t="n">
         <v>64</v>
@@ -46131,7 +46131,7 @@
         <v>8.34000015258789</v>
       </c>
       <c r="G1578" t="n">
-        <v>7.82017612457275</v>
+        <v>7.82017660140991</v>
       </c>
       <c r="H1578" t="n">
         <v>250</v>
@@ -46160,7 +46160,7 @@
         <v>8.35000038146973</v>
       </c>
       <c r="G1579" t="n">
-        <v>7.82955265045166</v>
+        <v>7.82955312728882</v>
       </c>
       <c r="H1579" t="n">
         <v>2100</v>
@@ -46189,7 +46189,7 @@
         <v>8.32999992370605</v>
       </c>
       <c r="G1580" t="n">
-        <v>7.81079959869385</v>
+        <v>7.81080007553101</v>
       </c>
       <c r="H1580" t="n">
         <v>12</v>
@@ -46247,7 +46247,7 @@
         <v>8.32999992370605</v>
       </c>
       <c r="G1582" t="n">
-        <v>7.81079959869385</v>
+        <v>7.81080007553101</v>
       </c>
       <c r="H1582" t="n">
         <v>1433</v>
@@ -46305,7 +46305,7 @@
         <v>8.26000022888184</v>
       </c>
       <c r="G1584" t="n">
-        <v>7.74516344070435</v>
+        <v>7.74516296386719</v>
       </c>
       <c r="H1584" t="n">
         <v>4844</v>
@@ -46363,7 +46363,7 @@
         <v>8.23999977111816</v>
       </c>
       <c r="G1586" t="n">
-        <v>7.72640943527222</v>
+        <v>7.72640895843506</v>
       </c>
       <c r="H1586" t="n">
         <v>370</v>
@@ -46392,7 +46392,7 @@
         <v>8.23999977111816</v>
       </c>
       <c r="G1587" t="n">
-        <v>7.72640943527222</v>
+        <v>7.72640895843506</v>
       </c>
       <c r="H1587" t="n">
         <v>1309</v>
@@ -46450,7 +46450,7 @@
         <v>8.18000030517578</v>
       </c>
       <c r="G1589" t="n">
-        <v>7.67014932632446</v>
+        <v>7.6701488494873</v>
       </c>
       <c r="H1589" t="n">
         <v>2104</v>
@@ -46479,7 +46479,7 @@
         <v>8.10999965667725</v>
       </c>
       <c r="G1590" t="n">
-        <v>7.60451126098633</v>
+        <v>7.60451173782349</v>
       </c>
       <c r="H1590" t="n">
         <v>1937</v>
@@ -46537,7 +46537,7 @@
         <v>8.18000030517578</v>
       </c>
       <c r="G1592" t="n">
-        <v>7.67014932632446</v>
+        <v>7.6701488494873</v>
       </c>
       <c r="H1592" t="n">
         <v>5541</v>
@@ -46566,7 +46566,7 @@
         <v>8.18000030517578</v>
       </c>
       <c r="G1593" t="n">
-        <v>7.67014932632446</v>
+        <v>7.6701488494873</v>
       </c>
       <c r="H1593" t="n">
         <v>8319</v>
@@ -47030,7 +47030,7 @@
         <v>8.18000030517578</v>
       </c>
       <c r="G1609" t="n">
-        <v>7.67014932632446</v>
+        <v>7.6701488494873</v>
       </c>
       <c r="H1609" t="n">
         <v>6376</v>
@@ -47262,7 +47262,7 @@
         <v>8.27000045776367</v>
       </c>
       <c r="G1617" t="n">
-        <v>7.75454044342041</v>
+        <v>7.75453948974609</v>
       </c>
       <c r="H1617" t="n">
         <v>27464</v>
@@ -47291,7 +47291,7 @@
         <v>8.10999965667725</v>
       </c>
       <c r="G1618" t="n">
-        <v>7.60451126098633</v>
+        <v>7.60451173782349</v>
       </c>
       <c r="H1618" t="n">
         <v>1085</v>
@@ -47320,7 +47320,7 @@
         <v>8.23999977111816</v>
       </c>
       <c r="G1619" t="n">
-        <v>7.72640943527222</v>
+        <v>7.72640895843506</v>
       </c>
       <c r="H1619" t="n">
         <v>22090</v>
@@ -47349,7 +47349,7 @@
         <v>8.26000022888184</v>
       </c>
       <c r="G1620" t="n">
-        <v>7.74516344070435</v>
+        <v>7.74516296386719</v>
       </c>
       <c r="H1620" t="n">
         <v>9204</v>
@@ -47552,7 +47552,7 @@
         <v>8.38000011444092</v>
       </c>
       <c r="G1627" t="n">
-        <v>7.8576831817627</v>
+        <v>7.85768365859985</v>
       </c>
       <c r="H1627" t="n">
         <v>1694</v>
@@ -47755,7 +47755,7 @@
         <v>8.14999961853027</v>
       </c>
       <c r="G1634" t="n">
-        <v>7.64201879501343</v>
+        <v>7.64201831817627</v>
       </c>
       <c r="H1634" t="n">
         <v>3757</v>
@@ -47784,7 +47784,7 @@
         <v>8.3100004196167</v>
       </c>
       <c r="G1635" t="n">
-        <v>7.79204607009888</v>
+        <v>7.79204654693604</v>
       </c>
       <c r="H1635" t="n">
         <v>2274</v>
@@ -47871,7 +47871,7 @@
         <v>8.34000015258789</v>
       </c>
       <c r="G1638" t="n">
-        <v>7.82017612457275</v>
+        <v>7.82017660140991</v>
       </c>
       <c r="H1638" t="n">
         <v>16528</v>
@@ -47958,7 +47958,7 @@
         <v>8.3100004196167</v>
       </c>
       <c r="G1641" t="n">
-        <v>7.79204607009888</v>
+        <v>7.79204654693604</v>
       </c>
       <c r="H1641" t="n">
         <v>18704</v>
@@ -48016,7 +48016,7 @@
         <v>8.35999965667725</v>
       </c>
       <c r="G1643" t="n">
-        <v>7.83892965316772</v>
+        <v>7.83893013000488</v>
       </c>
       <c r="H1643" t="n">
         <v>14035</v>
@@ -48045,7 +48045,7 @@
         <v>8.32999992370605</v>
       </c>
       <c r="G1644" t="n">
-        <v>7.81079959869385</v>
+        <v>7.81080007553101</v>
       </c>
       <c r="H1644" t="n">
         <v>10427</v>
@@ -48132,7 +48132,7 @@
         <v>8.35000038146973</v>
       </c>
       <c r="G1647" t="n">
-        <v>7.82955265045166</v>
+        <v>7.82955312728882</v>
       </c>
       <c r="H1647" t="n">
         <v>4322</v>
@@ -48219,7 +48219,7 @@
         <v>8.35000038146973</v>
       </c>
       <c r="G1650" t="n">
-        <v>7.82955265045166</v>
+        <v>7.82955312728882</v>
       </c>
       <c r="H1650" t="n">
         <v>4718</v>
@@ -48248,7 +48248,7 @@
         <v>8.34000015258789</v>
       </c>
       <c r="G1651" t="n">
-        <v>7.82017612457275</v>
+        <v>7.82017660140991</v>
       </c>
       <c r="H1651" t="n">
         <v>5002</v>
@@ -48306,7 +48306,7 @@
         <v>8.35999965667725</v>
       </c>
       <c r="G1653" t="n">
-        <v>7.83892965316772</v>
+        <v>7.83893013000488</v>
       </c>
       <c r="H1653" t="n">
         <v>19707</v>
@@ -48335,7 +48335,7 @@
         <v>8.35000038146973</v>
       </c>
       <c r="G1654" t="n">
-        <v>7.82955265045166</v>
+        <v>7.82955312728882</v>
       </c>
       <c r="H1654" t="n">
         <v>2310</v>
@@ -48567,7 +48567,7 @@
         <v>7.75</v>
       </c>
       <c r="G1662" t="n">
-        <v>7.2669506072998</v>
+        <v>7.26695013046265</v>
       </c>
       <c r="H1662" t="n">
         <v>5323</v>
@@ -48596,7 +48596,7 @@
         <v>7.55000019073486</v>
       </c>
       <c r="G1663" t="n">
-        <v>7.07941675186157</v>
+        <v>7.07941627502441</v>
       </c>
       <c r="H1663" t="n">
         <v>8336</v>
@@ -48625,7 +48625,7 @@
         <v>7.55000019073486</v>
       </c>
       <c r="G1664" t="n">
-        <v>7.07941675186157</v>
+        <v>7.07941627502441</v>
       </c>
       <c r="H1664" t="n">
         <v>4363</v>
@@ -48857,7 +48857,7 @@
         <v>7.48999977111816</v>
       </c>
       <c r="G1672" t="n">
-        <v>7.02315616607666</v>
+        <v>7.0231556892395</v>
       </c>
       <c r="H1672" t="n">
         <v>143713</v>
@@ -48915,7 +48915,7 @@
         <v>7.40000009536743</v>
       </c>
       <c r="G1674" t="n">
-        <v>6.93876552581787</v>
+        <v>6.93876600265503</v>
       </c>
       <c r="H1674" t="n">
         <v>15401</v>
@@ -48944,7 +48944,7 @@
         <v>7.40000009536743</v>
       </c>
       <c r="G1675" t="n">
-        <v>6.93876552581787</v>
+        <v>6.93876600265503</v>
       </c>
       <c r="H1675" t="n">
         <v>118167</v>
@@ -48973,7 +48973,7 @@
         <v>7.76000022888184</v>
       </c>
       <c r="G1676" t="n">
-        <v>7.37600326538086</v>
+        <v>7.3760027885437</v>
       </c>
       <c r="H1676" t="n">
         <v>31170</v>
@@ -49002,7 +49002,7 @@
         <v>8.26000022888184</v>
       </c>
       <c r="G1677" t="n">
-        <v>7.85126161575317</v>
+        <v>7.85126066207886</v>
       </c>
       <c r="H1677" t="n">
         <v>20296</v>
@@ -49031,7 +49031,7 @@
         <v>8.30000019073486</v>
       </c>
       <c r="G1678" t="n">
-        <v>7.88928127288818</v>
+        <v>7.8892822265625</v>
       </c>
       <c r="H1678" t="n">
         <v>11988</v>
@@ -49060,7 +49060,7 @@
         <v>8.31999969482422</v>
       </c>
       <c r="G1679" t="n">
-        <v>7.90829086303711</v>
+        <v>7.90829181671143</v>
       </c>
       <c r="H1679" t="n">
         <v>2625</v>
@@ -49089,7 +49089,7 @@
         <v>8.27000045776367</v>
       </c>
       <c r="G1680" t="n">
-        <v>7.86076688766479</v>
+        <v>7.86076593399048</v>
       </c>
       <c r="H1680" t="n">
         <v>6258</v>
@@ -49118,7 +49118,7 @@
         <v>8.30000019073486</v>
       </c>
       <c r="G1681" t="n">
-        <v>7.88928127288818</v>
+        <v>7.8892822265625</v>
       </c>
       <c r="H1681" t="n">
         <v>3569</v>
@@ -49176,7 +49176,7 @@
         <v>8.30000019073486</v>
       </c>
       <c r="G1683" t="n">
-        <v>7.88928127288818</v>
+        <v>7.8892822265625</v>
       </c>
       <c r="H1683" t="n">
         <v>2214</v>
@@ -49234,7 +49234,7 @@
         <v>8.39999961853027</v>
       </c>
       <c r="G1685" t="n">
-        <v>7.98433208465576</v>
+        <v>7.98433303833008</v>
       </c>
       <c r="H1685" t="n">
         <v>4145</v>
@@ -49263,7 +49263,7 @@
         <v>8.31999969482422</v>
       </c>
       <c r="G1686" t="n">
-        <v>7.90829086303711</v>
+        <v>7.90829181671143</v>
       </c>
       <c r="H1686" t="n">
         <v>890</v>
@@ -49350,7 +49350,7 @@
         <v>8.22000026702881</v>
       </c>
       <c r="G1689" t="n">
-        <v>7.81324052810669</v>
+        <v>7.81324005126953</v>
       </c>
       <c r="H1689" t="n">
         <v>4671</v>
@@ -49437,7 +49437,7 @@
         <v>8.34000015258789</v>
       </c>
       <c r="G1692" t="n">
-        <v>7.92730188369751</v>
+        <v>7.92730283737183</v>
       </c>
       <c r="H1692" t="n">
         <v>4250</v>
@@ -49466,7 +49466,7 @@
         <v>8.35999965667725</v>
       </c>
       <c r="G1693" t="n">
-        <v>7.94631147384644</v>
+        <v>7.94631242752075</v>
       </c>
       <c r="H1693" t="n">
         <v>3628</v>
@@ -49524,7 +49524,7 @@
         <v>8.31999969482422</v>
       </c>
       <c r="G1695" t="n">
-        <v>7.90829086303711</v>
+        <v>7.90829181671143</v>
       </c>
       <c r="H1695" t="n">
         <v>2041</v>
@@ -49582,7 +49582,7 @@
         <v>8.26000022888184</v>
       </c>
       <c r="G1697" t="n">
-        <v>7.85126161575317</v>
+        <v>7.85126066207886</v>
       </c>
       <c r="H1697" t="n">
         <v>2593</v>
@@ -49611,7 +49611,7 @@
         <v>8.35999965667725</v>
       </c>
       <c r="G1698" t="n">
-        <v>7.94631147384644</v>
+        <v>7.94631242752075</v>
       </c>
       <c r="H1698" t="n">
         <v>2397</v>
@@ -49640,7 +49640,7 @@
         <v>8.35999965667725</v>
       </c>
       <c r="G1699" t="n">
-        <v>7.94631147384644</v>
+        <v>7.94631242752075</v>
       </c>
       <c r="H1699" t="n">
         <v>3627</v>
@@ -49669,7 +49669,7 @@
         <v>8.22000026702881</v>
       </c>
       <c r="G1700" t="n">
-        <v>7.81324052810669</v>
+        <v>7.81324005126953</v>
       </c>
       <c r="H1700" t="n">
         <v>2198</v>
@@ -49698,7 +49698,7 @@
         <v>8.0600004196167</v>
       </c>
       <c r="G1701" t="n">
-        <v>7.66115808486938</v>
+        <v>7.66115760803223</v>
       </c>
       <c r="H1701" t="n">
         <v>2683</v>
@@ -49727,7 +49727,7 @@
         <v>8.0600004196167</v>
       </c>
       <c r="G1702" t="n">
-        <v>7.66115808486938</v>
+        <v>7.66115760803223</v>
       </c>
       <c r="H1702" t="n">
         <v>2528</v>
@@ -49756,7 +49756,7 @@
         <v>7.94999980926514</v>
       </c>
       <c r="G1703" t="n">
-        <v>7.55660057067871</v>
+        <v>7.55660104751587</v>
       </c>
       <c r="H1703" t="n">
         <v>1124</v>
@@ -49872,7 +49872,7 @@
         <v>8.39999961853027</v>
       </c>
       <c r="G1707" t="n">
-        <v>7.98433208465576</v>
+        <v>7.98433303833008</v>
       </c>
       <c r="H1707" t="n">
         <v>5821</v>
@@ -49901,7 +49901,7 @@
         <v>8.34000015258789</v>
       </c>
       <c r="G1708" t="n">
-        <v>7.92730188369751</v>
+        <v>7.92730283737183</v>
       </c>
       <c r="H1708" t="n">
         <v>719</v>
@@ -49959,7 +49959,7 @@
         <v>8.03999996185303</v>
       </c>
       <c r="G1710" t="n">
-        <v>7.64214754104614</v>
+        <v>7.64214706420898</v>
       </c>
       <c r="H1710" t="n">
         <v>14944</v>
@@ -49988,7 +49988,7 @@
         <v>8.18000030517578</v>
       </c>
       <c r="G1711" t="n">
-        <v>7.77521991729736</v>
+        <v>7.77521944046021</v>
       </c>
       <c r="H1711" t="n">
         <v>4562</v>
@@ -50017,7 +50017,7 @@
         <v>8.11999988555908</v>
       </c>
       <c r="G1712" t="n">
-        <v>7.71818876266479</v>
+        <v>7.71818828582764</v>
       </c>
       <c r="H1712" t="n">
         <v>2868</v>
@@ -50104,7 +50104,7 @@
         <v>8.06999969482422</v>
       </c>
       <c r="G1715" t="n">
-        <v>7.67066240310669</v>
+        <v>7.67066192626953</v>
       </c>
       <c r="H1715" t="n">
         <v>3573</v>
@@ -50133,7 +50133,7 @@
         <v>8.0600004196167</v>
       </c>
       <c r="G1716" t="n">
-        <v>7.66115808486938</v>
+        <v>7.66115760803223</v>
       </c>
       <c r="H1716" t="n">
         <v>349</v>
@@ -50220,7 +50220,7 @@
         <v>8.05000019073486</v>
       </c>
       <c r="G1719" t="n">
-        <v>7.65165281295776</v>
+        <v>7.65165233612061</v>
       </c>
       <c r="H1719" t="n">
         <v>10394</v>
@@ -50249,7 +50249,7 @@
         <v>7.92999982833862</v>
       </c>
       <c r="G1720" t="n">
-        <v>7.53759002685547</v>
+        <v>7.53759050369263</v>
       </c>
       <c r="H1720" t="n">
         <v>27976</v>
@@ -50307,7 +50307,7 @@
         <v>7.98000001907349</v>
       </c>
       <c r="G1722" t="n">
-        <v>7.58511590957642</v>
+        <v>7.58511638641357</v>
       </c>
       <c r="H1722" t="n">
         <v>909</v>
@@ -50423,7 +50423,7 @@
         <v>8.03999996185303</v>
       </c>
       <c r="G1726" t="n">
-        <v>7.64214754104614</v>
+        <v>7.64214706420898</v>
       </c>
       <c r="H1726" t="n">
         <v>2161</v>
@@ -50452,7 +50452,7 @@
         <v>7.92999982833862</v>
       </c>
       <c r="G1727" t="n">
-        <v>7.53759002685547</v>
+        <v>7.53759050369263</v>
       </c>
       <c r="H1727" t="n">
         <v>5098</v>
@@ -50510,7 +50510,7 @@
         <v>8.06999969482422</v>
       </c>
       <c r="G1729" t="n">
-        <v>7.67066240310669</v>
+        <v>7.67066192626953</v>
       </c>
       <c r="H1729" t="n">
         <v>32727</v>
@@ -50568,7 +50568,7 @@
         <v>7.94999980926514</v>
       </c>
       <c r="G1731" t="n">
-        <v>7.55660057067871</v>
+        <v>7.55660104751587</v>
       </c>
       <c r="H1731" t="n">
         <v>655</v>
@@ -50655,7 +50655,7 @@
         <v>8.0600004196167</v>
       </c>
       <c r="G1734" t="n">
-        <v>7.66115808486938</v>
+        <v>7.66115760803223</v>
       </c>
       <c r="H1734" t="n">
         <v>3725</v>
@@ -50684,7 +50684,7 @@
         <v>8.05000019073486</v>
       </c>
       <c r="G1735" t="n">
-        <v>7.65165281295776</v>
+        <v>7.65165233612061</v>
       </c>
       <c r="H1735" t="n">
         <v>866</v>
@@ -50713,7 +50713,7 @@
         <v>8.05000019073486</v>
       </c>
       <c r="G1736" t="n">
-        <v>7.65165281295776</v>
+        <v>7.65165233612061</v>
       </c>
       <c r="H1736" t="n">
         <v>1386</v>
@@ -50742,7 +50742,7 @@
         <v>8.13000011444092</v>
       </c>
       <c r="G1737" t="n">
-        <v>7.72769403457642</v>
+        <v>7.72769355773926</v>
       </c>
       <c r="H1737" t="n">
         <v>2130</v>
@@ -50771,7 +50771,7 @@
         <v>8.15999984741211</v>
       </c>
       <c r="G1738" t="n">
-        <v>7.75620937347412</v>
+        <v>7.75620889663696</v>
       </c>
       <c r="H1738" t="n">
         <v>2476</v>
@@ -50800,7 +50800,7 @@
         <v>8.11999988555908</v>
       </c>
       <c r="G1739" t="n">
-        <v>7.71818876266479</v>
+        <v>7.71818828582764</v>
       </c>
       <c r="H1739" t="n">
         <v>1132</v>
@@ -50829,7 +50829,7 @@
         <v>8.11999988555908</v>
       </c>
       <c r="G1740" t="n">
-        <v>7.71818876266479</v>
+        <v>7.71818828582764</v>
       </c>
       <c r="H1740" t="n">
         <v>824</v>
@@ -50916,7 +50916,7 @@
         <v>8.0600004196167</v>
       </c>
       <c r="G1743" t="n">
-        <v>7.66115808486938</v>
+        <v>7.66115760803223</v>
       </c>
       <c r="H1743" t="n">
         <v>788</v>
@@ -50945,7 +50945,7 @@
         <v>7.94999980926514</v>
       </c>
       <c r="G1744" t="n">
-        <v>7.55660057067871</v>
+        <v>7.55660104751587</v>
       </c>
       <c r="H1744" t="n">
         <v>528</v>
@@ -51032,7 +51032,7 @@
         <v>8.14000034332275</v>
       </c>
       <c r="G1747" t="n">
-        <v>7.73719930648804</v>
+        <v>7.73719882965088</v>
       </c>
       <c r="H1747" t="n">
         <v>3583</v>
@@ -51148,7 +51148,7 @@
         <v>8.38000011444092</v>
       </c>
       <c r="G1751" t="n">
-        <v>7.96532249450684</v>
+        <v>7.96532344818115</v>
       </c>
       <c r="H1751" t="n">
         <v>5406</v>
@@ -51177,7 +51177,7 @@
         <v>8.38000011444092</v>
       </c>
       <c r="G1752" t="n">
-        <v>7.96532249450684</v>
+        <v>7.96532344818115</v>
       </c>
       <c r="H1752" t="n">
         <v>2930</v>
@@ -51235,7 +51235,7 @@
         <v>8.38000011444092</v>
       </c>
       <c r="G1754" t="n">
-        <v>7.96532249450684</v>
+        <v>7.96532344818115</v>
       </c>
       <c r="H1754" t="n">
         <v>810</v>
@@ -51264,7 +51264,7 @@
         <v>8.38000011444092</v>
       </c>
       <c r="G1755" t="n">
-        <v>7.96532249450684</v>
+        <v>7.96532344818115</v>
       </c>
       <c r="H1755" t="n">
         <v>3242</v>
@@ -51293,7 +51293,7 @@
         <v>8.39999961853027</v>
       </c>
       <c r="G1756" t="n">
-        <v>7.98433208465576</v>
+        <v>7.98433303833008</v>
       </c>
       <c r="H1756" t="n">
         <v>4049</v>
@@ -51322,7 +51322,7 @@
         <v>8.39999961853027</v>
       </c>
       <c r="G1757" t="n">
-        <v>7.98433208465576</v>
+        <v>7.98433303833008</v>
       </c>
       <c r="H1757" t="n">
         <v>4339</v>
@@ -51409,7 +51409,7 @@
         <v>8.34000015258789</v>
       </c>
       <c r="G1760" t="n">
-        <v>7.92730188369751</v>
+        <v>7.92730283737183</v>
       </c>
       <c r="H1760" t="n">
         <v>27458</v>
@@ -51467,7 +51467,7 @@
         <v>8.38000011444092</v>
       </c>
       <c r="G1762" t="n">
-        <v>7.96532249450684</v>
+        <v>7.96532344818115</v>
       </c>
       <c r="H1762" t="n">
         <v>14068</v>
@@ -51525,7 +51525,7 @@
         <v>8.22000026702881</v>
       </c>
       <c r="G1764" t="n">
-        <v>7.81324052810669</v>
+        <v>7.81324005126953</v>
       </c>
       <c r="H1764" t="n">
         <v>5163</v>
@@ -51554,7 +51554,7 @@
         <v>8.26000022888184</v>
       </c>
       <c r="G1765" t="n">
-        <v>7.85126161575317</v>
+        <v>7.85126066207886</v>
       </c>
       <c r="H1765" t="n">
         <v>4626</v>
@@ -51641,7 +51641,7 @@
         <v>8.11999988555908</v>
       </c>
       <c r="G1768" t="n">
-        <v>7.71818876266479</v>
+        <v>7.71818828582764</v>
       </c>
       <c r="H1768" t="n">
         <v>7002</v>
@@ -51757,7 +51757,7 @@
         <v>8.19999980926514</v>
       </c>
       <c r="G1772" t="n">
-        <v>7.79422950744629</v>
+        <v>7.79422903060913</v>
       </c>
       <c r="H1772" t="n">
         <v>2345</v>
@@ -51873,7 +51873,7 @@
         <v>8.19999980926514</v>
       </c>
       <c r="G1776" t="n">
-        <v>7.79422950744629</v>
+        <v>7.79422903060913</v>
       </c>
       <c r="H1776" t="n">
         <v>5275</v>
@@ -51960,7 +51960,7 @@
         <v>7.96000003814697</v>
       </c>
       <c r="G1779" t="n">
-        <v>7.56610584259033</v>
+        <v>7.56610631942749</v>
       </c>
       <c r="H1779" t="n">
         <v>3623</v>
@@ -52076,7 +52076,7 @@
         <v>7.94999980926514</v>
       </c>
       <c r="G1783" t="n">
-        <v>7.55660057067871</v>
+        <v>7.55660104751587</v>
       </c>
       <c r="H1783" t="n">
         <v>2250</v>
@@ -52192,7 +52192,7 @@
         <v>7.96000003814697</v>
       </c>
       <c r="G1787" t="n">
-        <v>7.56610584259033</v>
+        <v>7.56610631942749</v>
       </c>
       <c r="H1787" t="n">
         <v>3533</v>
@@ -52250,7 +52250,7 @@
         <v>7.65999984741211</v>
       </c>
       <c r="G1789" t="n">
-        <v>7.28095102310181</v>
+        <v>7.28095149993896</v>
       </c>
       <c r="H1789" t="n">
         <v>9761</v>
@@ -52279,7 +52279,7 @@
         <v>7.59999990463257</v>
       </c>
       <c r="G1790" t="n">
-        <v>7.22391986846924</v>
+        <v>7.2239203453064</v>
       </c>
       <c r="H1790" t="n">
         <v>12785</v>
@@ -52395,7 +52395,7 @@
         <v>7.59999990463257</v>
       </c>
       <c r="G1794" t="n">
-        <v>7.22391986846924</v>
+        <v>7.2239203453064</v>
       </c>
       <c r="H1794" t="n">
         <v>4546</v>
@@ -52424,7 +52424,7 @@
         <v>7.67000007629395</v>
       </c>
       <c r="G1795" t="n">
-        <v>7.29045629501343</v>
+        <v>7.29045677185059</v>
       </c>
       <c r="H1795" t="n">
         <v>3428</v>
@@ -52453,7 +52453,7 @@
         <v>7.78000020980835</v>
       </c>
       <c r="G1796" t="n">
-        <v>7.3950138092041</v>
+        <v>7.39501333236694</v>
       </c>
       <c r="H1796" t="n">
         <v>4529</v>
@@ -52540,7 +52540,7 @@
         <v>7.73999977111816</v>
       </c>
       <c r="G1799" t="n">
-        <v>7.35699272155762</v>
+        <v>7.35699224472046</v>
       </c>
       <c r="H1799" t="n">
         <v>3436</v>
@@ -52569,7 +52569,7 @@
         <v>7.96999979019165</v>
       </c>
       <c r="G1800" t="n">
-        <v>7.57561063766479</v>
+        <v>7.57561111450195</v>
       </c>
       <c r="H1800" t="n">
         <v>9316</v>
@@ -52656,7 +52656,7 @@
         <v>7.98000001907349</v>
       </c>
       <c r="G1803" t="n">
-        <v>7.58511590957642</v>
+        <v>7.58511638641357</v>
       </c>
       <c r="H1803" t="n">
         <v>2841</v>
@@ -52743,7 +52743,7 @@
         <v>7.92999982833862</v>
       </c>
       <c r="G1806" t="n">
-        <v>7.53759002685547</v>
+        <v>7.53759050369263</v>
       </c>
       <c r="H1806" t="n">
         <v>105</v>
@@ -52772,7 +52772,7 @@
         <v>7.78000020980835</v>
       </c>
       <c r="G1807" t="n">
-        <v>7.3950138092041</v>
+        <v>7.39501333236694</v>
       </c>
       <c r="H1807" t="n">
         <v>8456</v>
@@ -52859,7 +52859,7 @@
         <v>7.94000005722046</v>
       </c>
       <c r="G1810" t="n">
-        <v>7.54709529876709</v>
+        <v>7.54709577560425</v>
       </c>
       <c r="H1810" t="n">
         <v>712</v>
@@ -52888,7 +52888,7 @@
         <v>7.92999982833862</v>
       </c>
       <c r="G1811" t="n">
-        <v>7.53759002685547</v>
+        <v>7.53759050369263</v>
       </c>
       <c r="H1811" t="n">
         <v>2256</v>
@@ -52946,7 +52946,7 @@
         <v>7.94999980926514</v>
       </c>
       <c r="G1813" t="n">
-        <v>7.55660057067871</v>
+        <v>7.55660104751587</v>
       </c>
       <c r="H1813" t="n">
         <v>3284</v>
@@ -52975,7 +52975,7 @@
         <v>7.94000005722046</v>
       </c>
       <c r="G1814" t="n">
-        <v>7.54709529876709</v>
+        <v>7.54709577560425</v>
       </c>
       <c r="H1814" t="n">
         <v>966</v>
@@ -53091,7 +53091,7 @@
         <v>8.34000015258789</v>
       </c>
       <c r="G1818" t="n">
-        <v>7.92730188369751</v>
+        <v>7.92730283737183</v>
       </c>
       <c r="H1818" t="n">
         <v>7946</v>
@@ -53149,7 +53149,7 @@
         <v>8.23999977111816</v>
       </c>
       <c r="G1820" t="n">
-        <v>7.83225011825562</v>
+        <v>7.83224964141846</v>
       </c>
       <c r="H1820" t="n">
         <v>5964</v>
@@ -53207,7 +53207,7 @@
         <v>8.19999980926514</v>
       </c>
       <c r="G1822" t="n">
-        <v>7.79422950744629</v>
+        <v>7.79422903060913</v>
       </c>
       <c r="H1822" t="n">
         <v>1753</v>
@@ -53236,7 +53236,7 @@
         <v>8.28999996185303</v>
       </c>
       <c r="G1823" t="n">
-        <v>7.87977695465088</v>
+        <v>7.87977600097656</v>
       </c>
       <c r="H1823" t="n">
         <v>8348</v>
@@ -53381,7 +53381,7 @@
         <v>8.47000026702881</v>
       </c>
       <c r="G1828" t="n">
-        <v>8.05086994171143</v>
+        <v>8.05086898803711</v>
       </c>
       <c r="H1828" t="n">
         <v>7166</v>
@@ -53410,7 +53410,7 @@
         <v>8.39999961853027</v>
       </c>
       <c r="G1829" t="n">
-        <v>7.98433208465576</v>
+        <v>7.98433303833008</v>
       </c>
       <c r="H1829" t="n">
         <v>20054</v>
@@ -53439,7 +53439,7 @@
         <v>8.57999992370605</v>
       </c>
       <c r="G1830" t="n">
-        <v>8.15542602539062</v>
+        <v>8.15542507171631</v>
       </c>
       <c r="H1830" t="n">
         <v>8492</v>
@@ -53468,7 +53468,7 @@
         <v>8.73999977111816</v>
       </c>
       <c r="G1831" t="n">
-        <v>8.30750846862793</v>
+        <v>8.30750751495361</v>
       </c>
       <c r="H1831" t="n">
         <v>9159</v>
@@ -53526,7 +53526,7 @@
         <v>8.73999977111816</v>
       </c>
       <c r="G1833" t="n">
-        <v>8.30750846862793</v>
+        <v>8.30750751495361</v>
       </c>
       <c r="H1833" t="n">
         <v>5014</v>
@@ -53613,7 +53613,7 @@
         <v>8.5600004196167</v>
       </c>
       <c r="G1836" t="n">
-        <v>8.1364164352417</v>
+        <v>8.13641548156738</v>
       </c>
       <c r="H1836" t="n">
         <v>11706</v>
@@ -53729,7 +53729,7 @@
         <v>8.9399995803833</v>
       </c>
       <c r="G1840" t="n">
-        <v>8.49761009216309</v>
+        <v>8.4976110458374</v>
       </c>
       <c r="H1840" t="n">
         <v>19298</v>
@@ -53758,7 +53758,7 @@
         <v>8.9399995803833</v>
       </c>
       <c r="G1841" t="n">
-        <v>8.49761009216309</v>
+        <v>8.4976110458374</v>
       </c>
       <c r="H1841" t="n">
         <v>8250</v>
@@ -53787,7 +53787,7 @@
         <v>8.89999961853027</v>
       </c>
       <c r="G1842" t="n">
-        <v>8.45958995819092</v>
+        <v>8.45959091186523</v>
       </c>
       <c r="H1842" t="n">
         <v>5908</v>
@@ -53816,7 +53816,7 @@
         <v>8.80000019073486</v>
       </c>
       <c r="G1843" t="n">
-        <v>8.36454010009766</v>
+        <v>8.36453914642334</v>
       </c>
       <c r="H1843" t="n">
         <v>6963</v>
@@ -53990,7 +53990,7 @@
         <v>8.80000019073486</v>
       </c>
       <c r="G1849" t="n">
-        <v>8.36454010009766</v>
+        <v>8.36453914642334</v>
       </c>
       <c r="H1849" t="n">
         <v>3434</v>
@@ -54135,7 +54135,7 @@
         <v>9.05000019073486</v>
       </c>
       <c r="G1854" t="n">
-        <v>8.60216903686523</v>
+        <v>8.60216808319092</v>
       </c>
       <c r="H1854" t="n">
         <v>1498</v>
@@ -54193,7 +54193,7 @@
         <v>8.96000003814697</v>
       </c>
       <c r="G1856" t="n">
-        <v>8.51662158966064</v>
+        <v>8.51662254333496</v>
       </c>
       <c r="H1856" t="n">
         <v>5291</v>
@@ -54251,7 +54251,7 @@
         <v>8.9399995803833</v>
       </c>
       <c r="G1858" t="n">
-        <v>8.49761009216309</v>
+        <v>8.4976110458374</v>
       </c>
       <c r="H1858" t="n">
         <v>458</v>
@@ -54280,7 +54280,7 @@
         <v>8.96000003814697</v>
       </c>
       <c r="G1859" t="n">
-        <v>8.51662158966064</v>
+        <v>8.51662254333496</v>
       </c>
       <c r="H1859" t="n">
         <v>4856</v>
@@ -54309,7 +54309,7 @@
         <v>8.89999961853027</v>
       </c>
       <c r="G1860" t="n">
-        <v>8.45958995819092</v>
+        <v>8.45959091186523</v>
       </c>
       <c r="H1860" t="n">
         <v>476</v>
@@ -54338,7 +54338,7 @@
         <v>8.89999961853027</v>
       </c>
       <c r="G1861" t="n">
-        <v>8.45958995819092</v>
+        <v>8.45959091186523</v>
       </c>
       <c r="H1861" t="n">
         <v>9439</v>
@@ -54367,7 +54367,7 @@
         <v>8.9399995803833</v>
       </c>
       <c r="G1862" t="n">
-        <v>8.49761009216309</v>
+        <v>8.4976110458374</v>
       </c>
       <c r="H1862" t="n">
         <v>1140</v>
@@ -54541,7 +54541,7 @@
         <v>8.64999961853027</v>
       </c>
       <c r="G1868" t="n">
-        <v>8.22196102142334</v>
+        <v>8.22196197509766</v>
       </c>
       <c r="H1868" t="n">
         <v>3665</v>
@@ -54570,7 +54570,7 @@
         <v>8.64999961853027</v>
       </c>
       <c r="G1869" t="n">
-        <v>8.22196102142334</v>
+        <v>8.22196197509766</v>
       </c>
       <c r="H1869" t="n">
         <v>526</v>
@@ -54657,7 +54657,7 @@
         <v>8.89999961853027</v>
       </c>
       <c r="G1872" t="n">
-        <v>8.45958995819092</v>
+        <v>8.45959091186523</v>
       </c>
       <c r="H1872" t="n">
         <v>3615</v>
@@ -54686,7 +54686,7 @@
         <v>8.80000019073486</v>
       </c>
       <c r="G1873" t="n">
-        <v>8.36454010009766</v>
+        <v>8.36453914642334</v>
       </c>
       <c r="H1873" t="n">
         <v>1784</v>
@@ -54715,7 +54715,7 @@
         <v>8.60999965667725</v>
       </c>
       <c r="G1874" t="n">
-        <v>8.18394088745117</v>
+        <v>8.18394184112549</v>
       </c>
       <c r="H1874" t="n">
         <v>6374</v>
@@ -54773,7 +54773,7 @@
         <v>8.59000015258789</v>
       </c>
       <c r="G1876" t="n">
-        <v>8.16493034362793</v>
+        <v>8.16493129730225</v>
       </c>
       <c r="H1876" t="n">
         <v>2645</v>
@@ -54802,7 +54802,7 @@
         <v>8.44999980926514</v>
       </c>
       <c r="G1877" t="n">
-        <v>8.03185939788818</v>
+        <v>8.03185844421387</v>
       </c>
       <c r="H1877" t="n">
         <v>1800</v>
@@ -54831,7 +54831,7 @@
         <v>8.35999965667725</v>
       </c>
       <c r="G1878" t="n">
-        <v>7.94631147384644</v>
+        <v>7.94631242752075</v>
       </c>
       <c r="H1878" t="n">
         <v>1898</v>
@@ -54947,7 +54947,7 @@
         <v>8.22000026702881</v>
       </c>
       <c r="G1882" t="n">
-        <v>7.81324052810669</v>
+        <v>7.81324005126953</v>
       </c>
       <c r="H1882" t="n">
         <v>1484</v>
@@ -55034,7 +55034,7 @@
         <v>8.26000022888184</v>
       </c>
       <c r="G1885" t="n">
-        <v>7.85126161575317</v>
+        <v>7.85126066207886</v>
       </c>
       <c r="H1885" t="n">
         <v>1714</v>
@@ -55063,7 +55063,7 @@
         <v>8.4399995803833</v>
       </c>
       <c r="G1886" t="n">
-        <v>8.02235317230225</v>
+        <v>8.02235412597656</v>
       </c>
       <c r="H1886" t="n">
         <v>703</v>
@@ -55092,7 +55092,7 @@
         <v>8.22000026702881</v>
       </c>
       <c r="G1887" t="n">
-        <v>7.81324052810669</v>
+        <v>7.81324005126953</v>
       </c>
       <c r="H1887" t="n">
         <v>3709</v>
@@ -55179,7 +55179,7 @@
         <v>8.38000011444092</v>
       </c>
       <c r="G1890" t="n">
-        <v>7.96532249450684</v>
+        <v>7.96532344818115</v>
       </c>
       <c r="H1890" t="n">
         <v>3012</v>
@@ -55208,7 +55208,7 @@
         <v>8.38000011444092</v>
       </c>
       <c r="G1891" t="n">
-        <v>7.96532249450684</v>
+        <v>7.96532344818115</v>
       </c>
       <c r="H1891" t="n">
         <v>1754</v>
@@ -55237,7 +55237,7 @@
         <v>8.5600004196167</v>
       </c>
       <c r="G1892" t="n">
-        <v>8.1364164352417</v>
+        <v>8.13641548156738</v>
       </c>
       <c r="H1892" t="n">
         <v>2935</v>
@@ -55295,7 +55295,7 @@
         <v>8.34000015258789</v>
       </c>
       <c r="G1894" t="n">
-        <v>7.92730188369751</v>
+        <v>7.92730283737183</v>
       </c>
       <c r="H1894" t="n">
         <v>7491</v>
@@ -55324,7 +55324,7 @@
         <v>8.30000019073486</v>
       </c>
       <c r="G1895" t="n">
-        <v>7.88928127288818</v>
+        <v>7.8892822265625</v>
       </c>
       <c r="H1895" t="n">
         <v>2181</v>
@@ -55353,7 +55353,7 @@
         <v>8.30000019073486</v>
       </c>
       <c r="G1896" t="n">
-        <v>7.88928127288818</v>
+        <v>7.8892822265625</v>
       </c>
       <c r="H1896" t="n">
         <v>19647</v>
@@ -55382,7 +55382,7 @@
         <v>8.30000019073486</v>
       </c>
       <c r="G1897" t="n">
-        <v>7.88928127288818</v>
+        <v>7.8892822265625</v>
       </c>
       <c r="H1897" t="n">
         <v>12119</v>
@@ -55411,7 +55411,7 @@
         <v>8.31999969482422</v>
       </c>
       <c r="G1898" t="n">
-        <v>7.90829086303711</v>
+        <v>7.90829181671143</v>
       </c>
       <c r="H1898" t="n">
         <v>33951</v>
@@ -55440,7 +55440,7 @@
         <v>8.38000011444092</v>
       </c>
       <c r="G1899" t="n">
-        <v>7.96532249450684</v>
+        <v>7.96532344818115</v>
       </c>
       <c r="H1899" t="n">
         <v>7603</v>
@@ -55469,7 +55469,7 @@
         <v>8.31999969482422</v>
       </c>
       <c r="G1900" t="n">
-        <v>7.90829086303711</v>
+        <v>7.90829181671143</v>
       </c>
       <c r="H1900" t="n">
         <v>10485</v>
@@ -55498,7 +55498,7 @@
         <v>8.35999965667725</v>
       </c>
       <c r="G1901" t="n">
-        <v>7.94631147384644</v>
+        <v>7.94631242752075</v>
       </c>
       <c r="H1901" t="n">
         <v>1812</v>
@@ -55527,7 +55527,7 @@
         <v>8.15999984741211</v>
       </c>
       <c r="G1902" t="n">
-        <v>7.75620937347412</v>
+        <v>7.75620889663696</v>
       </c>
       <c r="H1902" t="n">
         <v>4188</v>
@@ -55556,7 +55556,7 @@
         <v>8.11999988555908</v>
       </c>
       <c r="G1903" t="n">
-        <v>7.71818876266479</v>
+        <v>7.71818828582764</v>
       </c>
       <c r="H1903" t="n">
         <v>4305</v>
@@ -55614,7 +55614,7 @@
         <v>8.34000015258789</v>
       </c>
       <c r="G1905" t="n">
-        <v>7.92730188369751</v>
+        <v>7.92730283737183</v>
       </c>
       <c r="H1905" t="n">
         <v>2971</v>
@@ -55643,7 +55643,7 @@
         <v>8.34000015258789</v>
       </c>
       <c r="G1906" t="n">
-        <v>7.92730188369751</v>
+        <v>7.92730283737183</v>
       </c>
       <c r="H1906" t="n">
         <v>2230</v>
@@ -55672,7 +55672,7 @@
         <v>8.35999965667725</v>
       </c>
       <c r="G1907" t="n">
-        <v>7.94631147384644</v>
+        <v>7.94631242752075</v>
       </c>
       <c r="H1907" t="n">
         <v>14554</v>
@@ -55701,7 +55701,7 @@
         <v>8.39999961853027</v>
       </c>
       <c r="G1908" t="n">
-        <v>7.98433208465576</v>
+        <v>7.98433303833008</v>
       </c>
       <c r="H1908" t="n">
         <v>581</v>
@@ -55730,7 +55730,7 @@
         <v>8.31999969482422</v>
       </c>
       <c r="G1909" t="n">
-        <v>7.90829086303711</v>
+        <v>7.90829181671143</v>
       </c>
       <c r="H1909" t="n">
         <v>12586</v>
@@ -55759,7 +55759,7 @@
         <v>8.19999980926514</v>
       </c>
       <c r="G1910" t="n">
-        <v>7.79422950744629</v>
+        <v>7.79422903060913</v>
       </c>
       <c r="H1910" t="n">
         <v>49001</v>
@@ -55788,7 +55788,7 @@
         <v>8.38000011444092</v>
       </c>
       <c r="G1911" t="n">
-        <v>7.96532249450684</v>
+        <v>7.96532344818115</v>
       </c>
       <c r="H1911" t="n">
         <v>1961</v>
@@ -55817,7 +55817,7 @@
         <v>8.35999965667725</v>
       </c>
       <c r="G1912" t="n">
-        <v>7.94631147384644</v>
+        <v>7.94631242752075</v>
       </c>
       <c r="H1912" t="n">
         <v>6201</v>
@@ -55846,7 +55846,7 @@
         <v>8.35999965667725</v>
       </c>
       <c r="G1913" t="n">
-        <v>7.94631147384644</v>
+        <v>7.94631242752075</v>
       </c>
       <c r="H1913" t="n">
         <v>383</v>
@@ -55875,7 +55875,7 @@
         <v>8.39999961853027</v>
       </c>
       <c r="G1914" t="n">
-        <v>7.98433208465576</v>
+        <v>7.98433303833008</v>
       </c>
       <c r="H1914" t="n">
         <v>4927</v>
@@ -56107,7 +56107,7 @@
         <v>8.30000019073486</v>
       </c>
       <c r="G1922" t="n">
-        <v>7.88928127288818</v>
+        <v>7.8892822265625</v>
       </c>
       <c r="H1922" t="n">
         <v>8255</v>
@@ -56281,7 +56281,7 @@
         <v>8.5600004196167</v>
       </c>
       <c r="G1928" t="n">
-        <v>8.1364164352417</v>
+        <v>8.13641548156738</v>
       </c>
       <c r="H1928" t="n">
         <v>4904</v>
@@ -56339,7 +56339,7 @@
         <v>8.80000019073486</v>
       </c>
       <c r="G1930" t="n">
-        <v>8.36454010009766</v>
+        <v>8.36453914642334</v>
       </c>
       <c r="H1930" t="n">
         <v>4206</v>
@@ -56368,7 +56368,7 @@
         <v>8.80000019073486</v>
       </c>
       <c r="G1931" t="n">
-        <v>8.36454010009766</v>
+        <v>8.36453914642334</v>
       </c>
       <c r="H1931" t="n">
         <v>9768</v>
@@ -56397,7 +56397,7 @@
         <v>8.80000019073486</v>
       </c>
       <c r="G1932" t="n">
-        <v>8.36454010009766</v>
+        <v>8.36453914642334</v>
       </c>
       <c r="H1932" t="n">
         <v>2160</v>
@@ -56426,7 +56426,7 @@
         <v>8.73999977111816</v>
       </c>
       <c r="G1933" t="n">
-        <v>8.30750846862793</v>
+        <v>8.30750751495361</v>
       </c>
       <c r="H1933" t="n">
         <v>1810</v>
@@ -56484,7 +56484,7 @@
         <v>8.73999977111816</v>
       </c>
       <c r="G1935" t="n">
-        <v>8.30750846862793</v>
+        <v>8.30750751495361</v>
       </c>
       <c r="H1935" t="n">
         <v>1227</v>
@@ -56513,7 +56513,7 @@
         <v>8.73999977111816</v>
       </c>
       <c r="G1936" t="n">
-        <v>8.30750846862793</v>
+        <v>8.30750751495361</v>
       </c>
       <c r="H1936" t="n">
         <v>647</v>
@@ -74035,6 +74035,64 @@
         <v>11881</v>
       </c>
       <c r="I2540" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2541">
+      <c r="A2541" t="s">
+        <v>9</v>
+      </c>
+      <c r="B2541" s="1" t="n">
+        <v>46314.2916666667</v>
+      </c>
+      <c r="C2541" t="n">
+        <v>6.46000003814697</v>
+      </c>
+      <c r="D2541" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="E2541" t="n">
+        <v>6.3600001335144</v>
+      </c>
+      <c r="F2541" t="n">
+        <v>6.48000001907349</v>
+      </c>
+      <c r="G2541" t="n">
+        <v>6.48000001907349</v>
+      </c>
+      <c r="H2541" t="n">
+        <v>25261</v>
+      </c>
+      <c r="I2541" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2542">
+      <c r="A2542" t="s">
+        <v>9</v>
+      </c>
+      <c r="B2542" s="1" t="n">
+        <v>46315.2916666667</v>
+      </c>
+      <c r="C2542" t="n">
+        <v>6.55999994277954</v>
+      </c>
+      <c r="D2542" t="n">
+        <v>6.61999988555908</v>
+      </c>
+      <c r="E2542" t="n">
+        <v>6.44000005722046</v>
+      </c>
+      <c r="F2542" t="n">
+        <v>6.53999996185303</v>
+      </c>
+      <c r="G2542" t="n">
+        <v>6.53999996185303</v>
+      </c>
+      <c r="H2542" t="n">
+        <v>16852</v>
+      </c>
+      <c r="I2542" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/FF.MI.xlsx
+++ b/data/FF.MI.xlsx
@@ -427,7 +427,7 @@
         <v>10</v>
       </c>
       <c r="G2" t="n">
-        <v>8.92192935943604</v>
+        <v>8.92192840576172</v>
       </c>
       <c r="H2" t="n">
         <v>2800</v>
@@ -456,7 +456,7 @@
         <v>9.89999961853027</v>
       </c>
       <c r="G3" t="n">
-        <v>8.83271026611328</v>
+        <v>8.83270931243896</v>
       </c>
       <c r="H3" t="n">
         <v>2600</v>
@@ -485,7 +485,7 @@
         <v>10</v>
       </c>
       <c r="G4" t="n">
-        <v>8.92192935943604</v>
+        <v>8.92192840576172</v>
       </c>
       <c r="H4" t="n">
         <v>600</v>
@@ -514,7 +514,7 @@
         <v>10</v>
       </c>
       <c r="G5" t="n">
-        <v>8.92192935943604</v>
+        <v>8.92192840576172</v>
       </c>
       <c r="H5" t="n">
         <v>0</v>
@@ -543,7 +543,7 @@
         <v>10</v>
       </c>
       <c r="G6" t="n">
-        <v>8.92192935943604</v>
+        <v>8.92192840576172</v>
       </c>
       <c r="H6" t="n">
         <v>600</v>
@@ -572,7 +572,7 @@
         <v>10</v>
       </c>
       <c r="G7" t="n">
-        <v>8.92192935943604</v>
+        <v>8.92192840576172</v>
       </c>
       <c r="H7" t="n">
         <v>200</v>
@@ -601,7 +601,7 @@
         <v>10.0100002288818</v>
       </c>
       <c r="G8" t="n">
-        <v>8.93085193634033</v>
+        <v>8.93085098266602</v>
       </c>
       <c r="H8" t="n">
         <v>200</v>
@@ -630,7 +630,7 @@
         <v>10.0100002288818</v>
       </c>
       <c r="G9" t="n">
-        <v>8.93085193634033</v>
+        <v>8.93085098266602</v>
       </c>
       <c r="H9" t="n">
         <v>0</v>
@@ -659,7 +659,7 @@
         <v>10</v>
       </c>
       <c r="G10" t="n">
-        <v>8.92192935943604</v>
+        <v>8.92192840576172</v>
       </c>
       <c r="H10" t="n">
         <v>200</v>
@@ -688,7 +688,7 @@
         <v>10</v>
       </c>
       <c r="G11" t="n">
-        <v>8.92192935943604</v>
+        <v>8.92192840576172</v>
       </c>
       <c r="H11" t="n">
         <v>0</v>
@@ -717,7 +717,7 @@
         <v>10</v>
       </c>
       <c r="G12" t="n">
-        <v>8.92192935943604</v>
+        <v>8.92192840576172</v>
       </c>
       <c r="H12" t="n">
         <v>0</v>
@@ -746,7 +746,7 @@
         <v>10</v>
       </c>
       <c r="G13" t="n">
-        <v>8.92192935943604</v>
+        <v>8.92192840576172</v>
       </c>
       <c r="H13" t="n">
         <v>0</v>
@@ -775,7 +775,7 @@
         <v>10</v>
       </c>
       <c r="G14" t="n">
-        <v>8.92192935943604</v>
+        <v>8.92192840576172</v>
       </c>
       <c r="H14" t="n">
         <v>0</v>
@@ -804,7 +804,7 @@
         <v>10.1899995803833</v>
       </c>
       <c r="G15" t="n">
-        <v>9.09144592285156</v>
+        <v>9.09144401550293</v>
       </c>
       <c r="H15" t="n">
         <v>200</v>
@@ -833,7 +833,7 @@
         <v>10.1899995803833</v>
       </c>
       <c r="G16" t="n">
-        <v>9.09144592285156</v>
+        <v>9.09144401550293</v>
       </c>
       <c r="H16" t="n">
         <v>0</v>
@@ -862,7 +862,7 @@
         <v>10.0200004577637</v>
       </c>
       <c r="G17" t="n">
-        <v>8.939772605896</v>
+        <v>8.93977355957031</v>
       </c>
       <c r="H17" t="n">
         <v>800</v>
@@ -891,7 +891,7 @@
         <v>10.0500001907349</v>
       </c>
       <c r="G18" t="n">
-        <v>8.96653842926025</v>
+        <v>8.96653938293457</v>
       </c>
       <c r="H18" t="n">
         <v>1200</v>
@@ -920,7 +920,7 @@
         <v>9.94999980926514</v>
       </c>
       <c r="G19" t="n">
-        <v>8.8773193359375</v>
+        <v>8.87731838226318</v>
       </c>
       <c r="H19" t="n">
         <v>1400</v>
@@ -949,7 +949,7 @@
         <v>9.94999980926514</v>
       </c>
       <c r="G20" t="n">
-        <v>8.8773193359375</v>
+        <v>8.87731838226318</v>
       </c>
       <c r="H20" t="n">
         <v>0</v>
@@ -978,7 +978,7 @@
         <v>9.94999980926514</v>
       </c>
       <c r="G21" t="n">
-        <v>8.8773193359375</v>
+        <v>8.87731838226318</v>
       </c>
       <c r="H21" t="n">
         <v>0</v>
@@ -1007,7 +1007,7 @@
         <v>9.94999980926514</v>
       </c>
       <c r="G22" t="n">
-        <v>8.8773193359375</v>
+        <v>8.87731838226318</v>
       </c>
       <c r="H22" t="n">
         <v>0</v>
@@ -1036,7 +1036,7 @@
         <v>9.86499977111816</v>
       </c>
       <c r="G23" t="n">
-        <v>8.80148315429688</v>
+        <v>8.80148410797119</v>
       </c>
       <c r="H23" t="n">
         <v>1000</v>
@@ -1065,7 +1065,7 @@
         <v>9.86499977111816</v>
       </c>
       <c r="G24" t="n">
-        <v>8.80148315429688</v>
+        <v>8.80148410797119</v>
       </c>
       <c r="H24" t="n">
         <v>0</v>
@@ -1094,7 +1094,7 @@
         <v>9.86499977111816</v>
       </c>
       <c r="G25" t="n">
-        <v>8.80148315429688</v>
+        <v>8.80148410797119</v>
       </c>
       <c r="H25" t="n">
         <v>0</v>
@@ -1123,7 +1123,7 @@
         <v>10</v>
       </c>
       <c r="G26" t="n">
-        <v>8.92192935943604</v>
+        <v>8.92192840576172</v>
       </c>
       <c r="H26" t="n">
         <v>400</v>
@@ -1152,7 +1152,7 @@
         <v>9.80500030517578</v>
       </c>
       <c r="G27" t="n">
-        <v>8.74795150756836</v>
+        <v>8.74795246124268</v>
       </c>
       <c r="H27" t="n">
         <v>200</v>
@@ -1181,7 +1181,7 @@
         <v>9.80500030517578</v>
       </c>
       <c r="G28" t="n">
-        <v>8.74795150756836</v>
+        <v>8.74795246124268</v>
       </c>
       <c r="H28" t="n">
         <v>0</v>
@@ -1210,7 +1210,7 @@
         <v>9.80500030517578</v>
       </c>
       <c r="G29" t="n">
-        <v>8.74795150756836</v>
+        <v>8.74795246124268</v>
       </c>
       <c r="H29" t="n">
         <v>0</v>
@@ -1239,7 +1239,7 @@
         <v>9.80500030517578</v>
       </c>
       <c r="G30" t="n">
-        <v>8.74795150756836</v>
+        <v>8.74795246124268</v>
       </c>
       <c r="H30" t="n">
         <v>0</v>
@@ -1268,7 +1268,7 @@
         <v>9.80500030517578</v>
       </c>
       <c r="G31" t="n">
-        <v>8.74795150756836</v>
+        <v>8.74795246124268</v>
       </c>
       <c r="H31" t="n">
         <v>0</v>
@@ -1297,7 +1297,7 @@
         <v>9.80500030517578</v>
       </c>
       <c r="G32" t="n">
-        <v>8.74795150756836</v>
+        <v>8.74795246124268</v>
       </c>
       <c r="H32" t="n">
         <v>0</v>
@@ -1326,7 +1326,7 @@
         <v>9.80500030517578</v>
       </c>
       <c r="G33" t="n">
-        <v>8.74795150756836</v>
+        <v>8.74795246124268</v>
       </c>
       <c r="H33" t="n">
         <v>0</v>
@@ -1355,7 +1355,7 @@
         <v>9.80500030517578</v>
       </c>
       <c r="G34" t="n">
-        <v>8.74795150756836</v>
+        <v>8.74795246124268</v>
       </c>
       <c r="H34" t="n">
         <v>0</v>
@@ -1384,7 +1384,7 @@
         <v>9.80500030517578</v>
       </c>
       <c r="G35" t="n">
-        <v>8.74795150756836</v>
+        <v>8.74795246124268</v>
       </c>
       <c r="H35" t="n">
         <v>0</v>
@@ -1413,7 +1413,7 @@
         <v>9.80500030517578</v>
       </c>
       <c r="G36" t="n">
-        <v>8.74795150756836</v>
+        <v>8.74795246124268</v>
       </c>
       <c r="H36" t="n">
         <v>0</v>
@@ -1442,7 +1442,7 @@
         <v>9.80500030517578</v>
       </c>
       <c r="G37" t="n">
-        <v>8.74795150756836</v>
+        <v>8.74795246124268</v>
       </c>
       <c r="H37" t="n">
         <v>0</v>
@@ -1471,7 +1471,7 @@
         <v>9.80500030517578</v>
       </c>
       <c r="G38" t="n">
-        <v>8.74795150756836</v>
+        <v>8.74795246124268</v>
       </c>
       <c r="H38" t="n">
         <v>0</v>
@@ -1500,7 +1500,7 @@
         <v>9.80500030517578</v>
       </c>
       <c r="G39" t="n">
-        <v>8.74795150756836</v>
+        <v>8.74795246124268</v>
       </c>
       <c r="H39" t="n">
         <v>0</v>
@@ -1790,7 +1790,7 @@
         <v>10</v>
       </c>
       <c r="G49" t="n">
-        <v>8.92192935943604</v>
+        <v>8.92192840576172</v>
       </c>
       <c r="H49" t="n">
         <v>200</v>
@@ -1819,7 +1819,7 @@
         <v>10</v>
       </c>
       <c r="G50" t="n">
-        <v>8.92192935943604</v>
+        <v>8.92192840576172</v>
       </c>
       <c r="H50" t="n">
         <v>0</v>
@@ -2167,7 +2167,7 @@
         <v>9.80500030517578</v>
       </c>
       <c r="G62" t="n">
-        <v>8.74795150756836</v>
+        <v>8.74795246124268</v>
       </c>
       <c r="H62" t="n">
         <v>200</v>
@@ -2196,7 +2196,7 @@
         <v>9.80500030517578</v>
       </c>
       <c r="G63" t="n">
-        <v>8.74795150756836</v>
+        <v>8.74795246124268</v>
       </c>
       <c r="H63" t="n">
         <v>0</v>
@@ -2225,7 +2225,7 @@
         <v>9.80500030517578</v>
       </c>
       <c r="G64" t="n">
-        <v>8.74795150756836</v>
+        <v>8.74795246124268</v>
       </c>
       <c r="H64" t="n">
         <v>0</v>
@@ -2254,7 +2254,7 @@
         <v>9.80500030517578</v>
       </c>
       <c r="G65" t="n">
-        <v>8.74795150756836</v>
+        <v>8.74795246124268</v>
       </c>
       <c r="H65" t="n">
         <v>0</v>
@@ -2283,7 +2283,7 @@
         <v>9.76000022888184</v>
       </c>
       <c r="G66" t="n">
-        <v>8.70780277252197</v>
+        <v>8.70780372619629</v>
       </c>
       <c r="H66" t="n">
         <v>200</v>
@@ -2312,7 +2312,7 @@
         <v>9.76000022888184</v>
       </c>
       <c r="G67" t="n">
-        <v>8.70780277252197</v>
+        <v>8.70780372619629</v>
       </c>
       <c r="H67" t="n">
         <v>0</v>
@@ -2428,7 +2428,7 @@
         <v>9.65999984741211</v>
       </c>
       <c r="G71" t="n">
-        <v>8.6185827255249</v>
+        <v>8.61858367919922</v>
       </c>
       <c r="H71" t="n">
         <v>20200</v>
@@ -2457,7 +2457,7 @@
         <v>9.65999984741211</v>
       </c>
       <c r="G72" t="n">
-        <v>8.6185827255249</v>
+        <v>8.61858367919922</v>
       </c>
       <c r="H72" t="n">
         <v>0</v>
@@ -2486,7 +2486,7 @@
         <v>9.65999984741211</v>
       </c>
       <c r="G73" t="n">
-        <v>8.6185827255249</v>
+        <v>8.61858367919922</v>
       </c>
       <c r="H73" t="n">
         <v>0</v>
@@ -2515,7 +2515,7 @@
         <v>9.77000045776367</v>
       </c>
       <c r="G74" t="n">
-        <v>8.71672630310059</v>
+        <v>8.71672439575195</v>
       </c>
       <c r="H74" t="n">
         <v>400</v>
@@ -2544,7 +2544,7 @@
         <v>9.77000045776367</v>
       </c>
       <c r="G75" t="n">
-        <v>8.71672630310059</v>
+        <v>8.71672439575195</v>
       </c>
       <c r="H75" t="n">
         <v>0</v>
@@ -2573,7 +2573,7 @@
         <v>9.77000045776367</v>
       </c>
       <c r="G76" t="n">
-        <v>8.71672630310059</v>
+        <v>8.71672439575195</v>
       </c>
       <c r="H76" t="n">
         <v>0</v>
@@ -2602,7 +2602,7 @@
         <v>9.77000045776367</v>
       </c>
       <c r="G77" t="n">
-        <v>8.71672630310059</v>
+        <v>8.71672439575195</v>
       </c>
       <c r="H77" t="n">
         <v>0</v>
@@ -2631,7 +2631,7 @@
         <v>9.77000045776367</v>
       </c>
       <c r="G78" t="n">
-        <v>8.71672630310059</v>
+        <v>8.71672439575195</v>
       </c>
       <c r="H78" t="n">
         <v>0</v>
@@ -2660,7 +2660,7 @@
         <v>9.77000045776367</v>
       </c>
       <c r="G79" t="n">
-        <v>8.71672630310059</v>
+        <v>8.71672439575195</v>
       </c>
       <c r="H79" t="n">
         <v>0</v>
@@ -2689,7 +2689,7 @@
         <v>9.77000045776367</v>
       </c>
       <c r="G80" t="n">
-        <v>8.71672630310059</v>
+        <v>8.71672439575195</v>
       </c>
       <c r="H80" t="n">
         <v>0</v>
@@ -2718,7 +2718,7 @@
         <v>9.77000045776367</v>
       </c>
       <c r="G81" t="n">
-        <v>8.71672630310059</v>
+        <v>8.71672439575195</v>
       </c>
       <c r="H81" t="n">
         <v>0</v>
@@ -2747,7 +2747,7 @@
         <v>9.77000045776367</v>
       </c>
       <c r="G82" t="n">
-        <v>8.71672630310059</v>
+        <v>8.71672439575195</v>
       </c>
       <c r="H82" t="n">
         <v>0</v>
@@ -2776,7 +2776,7 @@
         <v>9.77000045776367</v>
       </c>
       <c r="G83" t="n">
-        <v>8.71672630310059</v>
+        <v>8.71672439575195</v>
       </c>
       <c r="H83" t="n">
         <v>0</v>
@@ -2805,7 +2805,7 @@
         <v>9.77000045776367</v>
       </c>
       <c r="G84" t="n">
-        <v>8.71672630310059</v>
+        <v>8.71672439575195</v>
       </c>
       <c r="H84" t="n">
         <v>0</v>
@@ -2834,7 +2834,7 @@
         <v>9.77000045776367</v>
       </c>
       <c r="G85" t="n">
-        <v>8.71672630310059</v>
+        <v>8.71672439575195</v>
       </c>
       <c r="H85" t="n">
         <v>0</v>
@@ -2863,7 +2863,7 @@
         <v>9.97000026702881</v>
       </c>
       <c r="G86" t="n">
-        <v>8.89516258239746</v>
+        <v>8.89516353607178</v>
       </c>
       <c r="H86" t="n">
         <v>600</v>
@@ -2892,7 +2892,7 @@
         <v>9.97000026702881</v>
       </c>
       <c r="G87" t="n">
-        <v>8.89516258239746</v>
+        <v>8.89516353607178</v>
       </c>
       <c r="H87" t="n">
         <v>0</v>
@@ -2921,7 +2921,7 @@
         <v>9.97000026702881</v>
       </c>
       <c r="G88" t="n">
-        <v>8.89516258239746</v>
+        <v>8.89516353607178</v>
       </c>
       <c r="H88" t="n">
         <v>0</v>
@@ -2950,7 +2950,7 @@
         <v>9.97000026702881</v>
       </c>
       <c r="G89" t="n">
-        <v>8.89516258239746</v>
+        <v>8.89516353607178</v>
       </c>
       <c r="H89" t="n">
         <v>0</v>
@@ -2979,7 +2979,7 @@
         <v>9.97000026702881</v>
       </c>
       <c r="G90" t="n">
-        <v>8.89516258239746</v>
+        <v>8.89516353607178</v>
       </c>
       <c r="H90" t="n">
         <v>0</v>
@@ -3008,7 +3008,7 @@
         <v>9.97000026702881</v>
       </c>
       <c r="G91" t="n">
-        <v>8.89516258239746</v>
+        <v>8.89516353607178</v>
       </c>
       <c r="H91" t="n">
         <v>0</v>
@@ -3037,7 +3037,7 @@
         <v>9.97000026702881</v>
       </c>
       <c r="G92" t="n">
-        <v>8.89516258239746</v>
+        <v>8.89516353607178</v>
       </c>
       <c r="H92" t="n">
         <v>0</v>
@@ -3327,7 +3327,7 @@
         <v>10.0500001907349</v>
       </c>
       <c r="G102" t="n">
-        <v>8.96653842926025</v>
+        <v>8.96653938293457</v>
       </c>
       <c r="H102" t="n">
         <v>200</v>
@@ -3356,7 +3356,7 @@
         <v>10.0500001907349</v>
       </c>
       <c r="G103" t="n">
-        <v>8.96653842926025</v>
+        <v>8.96653938293457</v>
       </c>
       <c r="H103" t="n">
         <v>0</v>
@@ -3385,7 +3385,7 @@
         <v>10</v>
       </c>
       <c r="G104" t="n">
-        <v>8.92192935943604</v>
+        <v>8.92192840576172</v>
       </c>
       <c r="H104" t="n">
         <v>400</v>
@@ -3414,7 +3414,7 @@
         <v>10</v>
       </c>
       <c r="G105" t="n">
-        <v>8.92192935943604</v>
+        <v>8.92192840576172</v>
       </c>
       <c r="H105" t="n">
         <v>200</v>
@@ -3443,7 +3443,7 @@
         <v>10.039999961853</v>
       </c>
       <c r="G106" t="n">
-        <v>8.95761775970459</v>
+        <v>8.95761680603027</v>
       </c>
       <c r="H106" t="n">
         <v>600</v>
@@ -3472,7 +3472,7 @@
         <v>10.039999961853</v>
       </c>
       <c r="G107" t="n">
-        <v>8.95761775970459</v>
+        <v>8.95761680603027</v>
       </c>
       <c r="H107" t="n">
         <v>0</v>
@@ -3501,7 +3501,7 @@
         <v>10.039999961853</v>
       </c>
       <c r="G108" t="n">
-        <v>8.95761775970459</v>
+        <v>8.95761680603027</v>
       </c>
       <c r="H108" t="n">
         <v>0</v>
@@ -3530,7 +3530,7 @@
         <v>10.0500001907349</v>
       </c>
       <c r="G109" t="n">
-        <v>8.96653842926025</v>
+        <v>8.96653938293457</v>
       </c>
       <c r="H109" t="n">
         <v>400</v>
@@ -3559,7 +3559,7 @@
         <v>10</v>
       </c>
       <c r="G110" t="n">
-        <v>8.92192935943604</v>
+        <v>8.92192840576172</v>
       </c>
       <c r="H110" t="n">
         <v>200</v>
@@ -3588,7 +3588,7 @@
         <v>10</v>
       </c>
       <c r="G111" t="n">
-        <v>8.92192935943604</v>
+        <v>8.92192840576172</v>
       </c>
       <c r="H111" t="n">
         <v>0</v>
@@ -3617,7 +3617,7 @@
         <v>10</v>
       </c>
       <c r="G112" t="n">
-        <v>8.92192935943604</v>
+        <v>8.92192840576172</v>
       </c>
       <c r="H112" t="n">
         <v>0</v>
@@ -3646,7 +3646,7 @@
         <v>10.0100002288818</v>
       </c>
       <c r="G113" t="n">
-        <v>8.93085193634033</v>
+        <v>8.93085098266602</v>
       </c>
       <c r="H113" t="n">
         <v>200</v>
@@ -3675,7 +3675,7 @@
         <v>10.0100002288818</v>
       </c>
       <c r="G114" t="n">
-        <v>8.93085193634033</v>
+        <v>8.93085098266602</v>
       </c>
       <c r="H114" t="n">
         <v>0</v>
@@ -3704,7 +3704,7 @@
         <v>9.88000011444092</v>
       </c>
       <c r="G115" t="n">
-        <v>8.81486701965332</v>
+        <v>8.814866065979</v>
       </c>
       <c r="H115" t="n">
         <v>400</v>
@@ -3733,7 +3733,7 @@
         <v>9.88000011444092</v>
       </c>
       <c r="G116" t="n">
-        <v>8.81486701965332</v>
+        <v>8.814866065979</v>
       </c>
       <c r="H116" t="n">
         <v>4400</v>
@@ -3762,7 +3762,7 @@
         <v>9.81999969482422</v>
       </c>
       <c r="G117" t="n">
-        <v>8.76133441925049</v>
+        <v>8.7613353729248</v>
       </c>
       <c r="H117" t="n">
         <v>6000</v>
@@ -3791,7 +3791,7 @@
         <v>10</v>
       </c>
       <c r="G118" t="n">
-        <v>8.92192935943604</v>
+        <v>8.92192840576172</v>
       </c>
       <c r="H118" t="n">
         <v>200</v>
@@ -3820,7 +3820,7 @@
         <v>9.88000011444092</v>
       </c>
       <c r="G119" t="n">
-        <v>8.81486701965332</v>
+        <v>8.814866065979</v>
       </c>
       <c r="H119" t="n">
         <v>1000</v>
@@ -3849,7 +3849,7 @@
         <v>9.88000011444092</v>
       </c>
       <c r="G120" t="n">
-        <v>8.81486701965332</v>
+        <v>8.814866065979</v>
       </c>
       <c r="H120" t="n">
         <v>0</v>
@@ -3965,7 +3965,7 @@
         <v>9.81999969482422</v>
       </c>
       <c r="G124" t="n">
-        <v>8.76133441925049</v>
+        <v>8.7613353729248</v>
       </c>
       <c r="H124" t="n">
         <v>2400</v>
@@ -3994,7 +3994,7 @@
         <v>10</v>
       </c>
       <c r="G125" t="n">
-        <v>8.92192935943604</v>
+        <v>8.92192840576172</v>
       </c>
       <c r="H125" t="n">
         <v>1000</v>
@@ -4023,7 +4023,7 @@
         <v>10.0500001907349</v>
       </c>
       <c r="G126" t="n">
-        <v>8.96653842926025</v>
+        <v>8.96653938293457</v>
       </c>
       <c r="H126" t="n">
         <v>1000</v>
@@ -4052,7 +4052,7 @@
         <v>10</v>
       </c>
       <c r="G127" t="n">
-        <v>8.92192935943604</v>
+        <v>8.92192840576172</v>
       </c>
       <c r="H127" t="n">
         <v>200</v>
@@ -4081,7 +4081,7 @@
         <v>9.97000026702881</v>
       </c>
       <c r="G128" t="n">
-        <v>8.89516258239746</v>
+        <v>8.89516353607178</v>
       </c>
       <c r="H128" t="n">
         <v>200</v>
@@ -4139,7 +4139,7 @@
         <v>9.89999961853027</v>
       </c>
       <c r="G130" t="n">
-        <v>8.83271026611328</v>
+        <v>8.83270931243896</v>
       </c>
       <c r="H130" t="n">
         <v>2400</v>
@@ -4168,7 +4168,7 @@
         <v>9.89999961853027</v>
       </c>
       <c r="G131" t="n">
-        <v>8.83271026611328</v>
+        <v>8.83270931243896</v>
       </c>
       <c r="H131" t="n">
         <v>3400</v>
@@ -4197,7 +4197,7 @@
         <v>10</v>
       </c>
       <c r="G132" t="n">
-        <v>8.92192935943604</v>
+        <v>8.92192840576172</v>
       </c>
       <c r="H132" t="n">
         <v>1400</v>
@@ -4226,7 +4226,7 @@
         <v>9.89999961853027</v>
       </c>
       <c r="G133" t="n">
-        <v>8.83271026611328</v>
+        <v>8.83270931243896</v>
       </c>
       <c r="H133" t="n">
         <v>52800</v>
@@ -4313,7 +4313,7 @@
         <v>10.3999996185303</v>
       </c>
       <c r="G136" t="n">
-        <v>9.27880764007568</v>
+        <v>9.27880573272705</v>
       </c>
       <c r="H136" t="n">
         <v>82000</v>
@@ -4342,7 +4342,7 @@
         <v>10.5200004577637</v>
       </c>
       <c r="G137" t="n">
-        <v>9.3858699798584</v>
+        <v>9.38587093353271</v>
       </c>
       <c r="H137" t="n">
         <v>44600</v>
@@ -4603,7 +4603,7 @@
         <v>10.5500001907349</v>
       </c>
       <c r="G146" t="n">
-        <v>9.41263484954834</v>
+        <v>9.41263675689697</v>
       </c>
       <c r="H146" t="n">
         <v>10800</v>
@@ -4661,7 +4661,7 @@
         <v>10.5</v>
       </c>
       <c r="G148" t="n">
-        <v>9.3680248260498</v>
+        <v>9.36802673339844</v>
       </c>
       <c r="H148" t="n">
         <v>19800</v>
@@ -4690,7 +4690,7 @@
         <v>10.4700002670288</v>
       </c>
       <c r="G149" t="n">
-        <v>9.34126091003418</v>
+        <v>9.34125995635986</v>
       </c>
       <c r="H149" t="n">
         <v>24800</v>
@@ -4719,7 +4719,7 @@
         <v>10.5</v>
       </c>
       <c r="G150" t="n">
-        <v>9.3680248260498</v>
+        <v>9.36802673339844</v>
       </c>
       <c r="H150" t="n">
         <v>4400</v>
@@ -4777,7 +4777,7 @@
         <v>10.5799999237061</v>
       </c>
       <c r="G152" t="n">
-        <v>9.43940162658691</v>
+        <v>9.4394006729126</v>
       </c>
       <c r="H152" t="n">
         <v>1000</v>
@@ -4806,7 +4806,7 @@
         <v>10.5500001907349</v>
       </c>
       <c r="G153" t="n">
-        <v>9.41263484954834</v>
+        <v>9.41263675689697</v>
       </c>
       <c r="H153" t="n">
         <v>2000</v>
@@ -4835,7 +4835,7 @@
         <v>10.6199998855591</v>
       </c>
       <c r="G154" t="n">
-        <v>9.47509002685547</v>
+        <v>9.47508811950684</v>
       </c>
       <c r="H154" t="n">
         <v>6000</v>
@@ -4922,7 +4922,7 @@
         <v>10.789999961853</v>
       </c>
       <c r="G157" t="n">
-        <v>9.62676239013672</v>
+        <v>9.6267614364624</v>
       </c>
       <c r="H157" t="n">
         <v>32400</v>
@@ -4951,7 +4951,7 @@
         <v>10.9700002670288</v>
       </c>
       <c r="G158" t="n">
-        <v>9.78735637664795</v>
+        <v>9.78735828399658</v>
       </c>
       <c r="H158" t="n">
         <v>5800</v>
@@ -5038,7 +5038,7 @@
         <v>10.9499998092651</v>
       </c>
       <c r="G161" t="n">
-        <v>9.7695140838623</v>
+        <v>9.76951313018799</v>
       </c>
       <c r="H161" t="n">
         <v>5800</v>
@@ -5096,7 +5096,7 @@
         <v>10.7299995422363</v>
       </c>
       <c r="G163" t="n">
-        <v>9.5732307434082</v>
+        <v>9.57322978973389</v>
       </c>
       <c r="H163" t="n">
         <v>11400</v>
@@ -5125,7 +5125,7 @@
         <v>10.7600002288818</v>
       </c>
       <c r="G164" t="n">
-        <v>9.59999752044678</v>
+        <v>9.59999656677246</v>
       </c>
       <c r="H164" t="n">
         <v>4200</v>
@@ -5154,7 +5154,7 @@
         <v>10.7299995422363</v>
       </c>
       <c r="G165" t="n">
-        <v>9.5732307434082</v>
+        <v>9.57322978973389</v>
       </c>
       <c r="H165" t="n">
         <v>600</v>
@@ -5183,7 +5183,7 @@
         <v>10.7399997711182</v>
       </c>
       <c r="G166" t="n">
-        <v>9.58215045928955</v>
+        <v>9.58215141296387</v>
       </c>
       <c r="H166" t="n">
         <v>2400</v>
@@ -5241,7 +5241,7 @@
         <v>10.789999961853</v>
       </c>
       <c r="G168" t="n">
-        <v>9.62676239013672</v>
+        <v>9.6267614364624</v>
       </c>
       <c r="H168" t="n">
         <v>8000</v>
@@ -5270,7 +5270,7 @@
         <v>10.6300001144409</v>
       </c>
       <c r="G169" t="n">
-        <v>9.48401165008545</v>
+        <v>9.48401069641113</v>
       </c>
       <c r="H169" t="n">
         <v>8600</v>
@@ -5357,7 +5357,7 @@
         <v>10.8199996948242</v>
       </c>
       <c r="G172" t="n">
-        <v>9.65352535247803</v>
+        <v>9.65352916717529</v>
       </c>
       <c r="H172" t="n">
         <v>6400</v>
@@ -5473,7 +5473,7 @@
         <v>10.7399997711182</v>
       </c>
       <c r="G176" t="n">
-        <v>9.58215045928955</v>
+        <v>9.58215141296387</v>
       </c>
       <c r="H176" t="n">
         <v>7600</v>
@@ -5531,7 +5531,7 @@
         <v>10.6499996185303</v>
       </c>
       <c r="G178" t="n">
-        <v>9.50185489654541</v>
+        <v>9.50185394287109</v>
       </c>
       <c r="H178" t="n">
         <v>7400</v>
@@ -5589,7 +5589,7 @@
         <v>10.4700002670288</v>
       </c>
       <c r="G180" t="n">
-        <v>9.34126091003418</v>
+        <v>9.34125995635986</v>
       </c>
       <c r="H180" t="n">
         <v>10000</v>
@@ -5647,7 +5647,7 @@
         <v>10.6199998855591</v>
       </c>
       <c r="G182" t="n">
-        <v>9.47509002685547</v>
+        <v>9.47508811950684</v>
       </c>
       <c r="H182" t="n">
         <v>400</v>
@@ -5676,7 +5676,7 @@
         <v>10.6400003433228</v>
       </c>
       <c r="G183" t="n">
-        <v>9.49293327331543</v>
+        <v>9.49293422698975</v>
       </c>
       <c r="H183" t="n">
         <v>200</v>
@@ -5734,7 +5734,7 @@
         <v>10.5500001907349</v>
       </c>
       <c r="G185" t="n">
-        <v>9.41263484954834</v>
+        <v>9.41263675689697</v>
       </c>
       <c r="H185" t="n">
         <v>2400</v>
@@ -5763,7 +5763,7 @@
         <v>10.5</v>
       </c>
       <c r="G186" t="n">
-        <v>9.3680248260498</v>
+        <v>9.36802673339844</v>
       </c>
       <c r="H186" t="n">
         <v>2600</v>
@@ -5792,7 +5792,7 @@
         <v>10.5</v>
       </c>
       <c r="G187" t="n">
-        <v>9.3680248260498</v>
+        <v>9.36802673339844</v>
       </c>
       <c r="H187" t="n">
         <v>0</v>
@@ -5821,7 +5821,7 @@
         <v>10.789999961853</v>
       </c>
       <c r="G188" t="n">
-        <v>9.62676239013672</v>
+        <v>9.6267614364624</v>
       </c>
       <c r="H188" t="n">
         <v>5200</v>
@@ -5850,7 +5850,7 @@
         <v>10.789999961853</v>
       </c>
       <c r="G189" t="n">
-        <v>9.62676239013672</v>
+        <v>9.6267614364624</v>
       </c>
       <c r="H189" t="n">
         <v>7200</v>
@@ -6082,7 +6082,7 @@
         <v>10.7299995422363</v>
       </c>
       <c r="G197" t="n">
-        <v>9.5732307434082</v>
+        <v>9.57322978973389</v>
       </c>
       <c r="H197" t="n">
         <v>200</v>
@@ -6111,7 +6111,7 @@
         <v>10.5</v>
       </c>
       <c r="G198" t="n">
-        <v>9.3680248260498</v>
+        <v>9.36802673339844</v>
       </c>
       <c r="H198" t="n">
         <v>41200</v>
@@ -6140,7 +6140,7 @@
         <v>10.5500001907349</v>
       </c>
       <c r="G199" t="n">
-        <v>9.41263484954834</v>
+        <v>9.41263675689697</v>
       </c>
       <c r="H199" t="n">
         <v>4800</v>
@@ -6169,7 +6169,7 @@
         <v>10.5</v>
       </c>
       <c r="G200" t="n">
-        <v>9.3680248260498</v>
+        <v>9.36802673339844</v>
       </c>
       <c r="H200" t="n">
         <v>12000</v>
@@ -6227,7 +6227,7 @@
         <v>10.6400003433228</v>
       </c>
       <c r="G202" t="n">
-        <v>9.49293327331543</v>
+        <v>9.49293422698975</v>
       </c>
       <c r="H202" t="n">
         <v>17000</v>
@@ -6314,7 +6314,7 @@
         <v>10.6199998855591</v>
       </c>
       <c r="G205" t="n">
-        <v>9.47509002685547</v>
+        <v>9.47508811950684</v>
       </c>
       <c r="H205" t="n">
         <v>17200</v>
@@ -6372,7 +6372,7 @@
         <v>10.6199998855591</v>
       </c>
       <c r="G207" t="n">
-        <v>9.47509002685547</v>
+        <v>9.47508811950684</v>
       </c>
       <c r="H207" t="n">
         <v>3000</v>
@@ -6401,7 +6401,7 @@
         <v>10.6499996185303</v>
       </c>
       <c r="G208" t="n">
-        <v>9.50185489654541</v>
+        <v>9.50185394287109</v>
       </c>
       <c r="H208" t="n">
         <v>400</v>
@@ -6430,7 +6430,7 @@
         <v>10.6300001144409</v>
       </c>
       <c r="G209" t="n">
-        <v>9.48401165008545</v>
+        <v>9.48401069641113</v>
       </c>
       <c r="H209" t="n">
         <v>600</v>
@@ -6488,7 +6488,7 @@
         <v>10.789999961853</v>
       </c>
       <c r="G211" t="n">
-        <v>9.62676239013672</v>
+        <v>9.6267614364624</v>
       </c>
       <c r="H211" t="n">
         <v>1600</v>
@@ -6517,7 +6517,7 @@
         <v>10.8100004196167</v>
       </c>
       <c r="G212" t="n">
-        <v>9.644606590271</v>
+        <v>9.64460563659668</v>
       </c>
       <c r="H212" t="n">
         <v>7200</v>
@@ -6546,7 +6546,7 @@
         <v>10.8100004196167</v>
       </c>
       <c r="G213" t="n">
-        <v>9.644606590271</v>
+        <v>9.64460563659668</v>
       </c>
       <c r="H213" t="n">
         <v>0</v>
@@ -6575,7 +6575,7 @@
         <v>10.8299999237061</v>
       </c>
       <c r="G214" t="n">
-        <v>9.66244983673096</v>
+        <v>9.66244888305664</v>
       </c>
       <c r="H214" t="n">
         <v>600</v>
@@ -6604,7 +6604,7 @@
         <v>10.8500003814697</v>
       </c>
       <c r="G215" t="n">
-        <v>9.68029403686523</v>
+        <v>9.68029499053955</v>
       </c>
       <c r="H215" t="n">
         <v>1600</v>
@@ -6633,7 +6633,7 @@
         <v>10.8400001525879</v>
       </c>
       <c r="G216" t="n">
-        <v>9.67137145996094</v>
+        <v>9.67137241363525</v>
       </c>
       <c r="H216" t="n">
         <v>3000</v>
@@ -6662,7 +6662,7 @@
         <v>10.7600002288818</v>
       </c>
       <c r="G217" t="n">
-        <v>9.59999752044678</v>
+        <v>9.59999656677246</v>
       </c>
       <c r="H217" t="n">
         <v>2400</v>
@@ -6691,7 +6691,7 @@
         <v>10.7399997711182</v>
       </c>
       <c r="G218" t="n">
-        <v>9.58215045928955</v>
+        <v>9.58215141296387</v>
       </c>
       <c r="H218" t="n">
         <v>400</v>
@@ -6720,7 +6720,7 @@
         <v>10.7399997711182</v>
       </c>
       <c r="G219" t="n">
-        <v>9.58215045928955</v>
+        <v>9.58215141296387</v>
       </c>
       <c r="H219" t="n">
         <v>0</v>
@@ -6749,7 +6749,7 @@
         <v>10.7299995422363</v>
       </c>
       <c r="G220" t="n">
-        <v>9.5732307434082</v>
+        <v>9.57322978973389</v>
       </c>
       <c r="H220" t="n">
         <v>1600</v>
@@ -6778,7 +6778,7 @@
         <v>10.6199998855591</v>
       </c>
       <c r="G221" t="n">
-        <v>9.47509002685547</v>
+        <v>9.47508811950684</v>
       </c>
       <c r="H221" t="n">
         <v>5800</v>
@@ -6836,7 +6836,7 @@
         <v>10.8199996948242</v>
       </c>
       <c r="G223" t="n">
-        <v>9.65352535247803</v>
+        <v>9.65352916717529</v>
       </c>
       <c r="H223" t="n">
         <v>3600</v>
@@ -6952,7 +6952,7 @@
         <v>10.7600002288818</v>
       </c>
       <c r="G227" t="n">
-        <v>9.59999752044678</v>
+        <v>9.59999656677246</v>
       </c>
       <c r="H227" t="n">
         <v>3400</v>
@@ -7184,7 +7184,7 @@
         <v>10.6400003433228</v>
       </c>
       <c r="G235" t="n">
-        <v>9.49293327331543</v>
+        <v>9.49293422698975</v>
       </c>
       <c r="H235" t="n">
         <v>10600</v>
@@ -7242,7 +7242,7 @@
         <v>10.7299995422363</v>
       </c>
       <c r="G237" t="n">
-        <v>9.5732307434082</v>
+        <v>9.57322978973389</v>
       </c>
       <c r="H237" t="n">
         <v>4400</v>
@@ -7387,7 +7387,7 @@
         <v>10.3999996185303</v>
       </c>
       <c r="G242" t="n">
-        <v>9.27880764007568</v>
+        <v>9.27880573272705</v>
       </c>
       <c r="H242" t="n">
         <v>23800</v>
@@ -7416,7 +7416,7 @@
         <v>10.5299997329712</v>
       </c>
       <c r="G243" t="n">
-        <v>9.39479064941406</v>
+        <v>9.39479160308838</v>
       </c>
       <c r="H243" t="n">
         <v>8000</v>
@@ -7474,7 +7474,7 @@
         <v>10.3999996185303</v>
       </c>
       <c r="G245" t="n">
-        <v>9.27880764007568</v>
+        <v>9.27880573272705</v>
       </c>
       <c r="H245" t="n">
         <v>8800</v>
@@ -7561,7 +7561,7 @@
         <v>10.1999998092651</v>
       </c>
       <c r="G248" t="n">
-        <v>9.10036659240723</v>
+        <v>9.10036849975586</v>
       </c>
       <c r="H248" t="n">
         <v>2000</v>
@@ -7590,7 +7590,7 @@
         <v>10.1999998092651</v>
       </c>
       <c r="G249" t="n">
-        <v>9.10036659240723</v>
+        <v>9.10036849975586</v>
       </c>
       <c r="H249" t="n">
         <v>0</v>
@@ -7619,7 +7619,7 @@
         <v>10.1999998092651</v>
       </c>
       <c r="G250" t="n">
-        <v>9.10036659240723</v>
+        <v>9.10036849975586</v>
       </c>
       <c r="H250" t="n">
         <v>11000</v>
@@ -7648,7 +7648,7 @@
         <v>10.1300001144409</v>
       </c>
       <c r="G251" t="n">
-        <v>9.03791332244873</v>
+        <v>9.03791427612305</v>
       </c>
       <c r="H251" t="n">
         <v>67600</v>
@@ -7677,7 +7677,7 @@
         <v>10.1199998855591</v>
       </c>
       <c r="G252" t="n">
-        <v>9.02899265289307</v>
+        <v>9.02899074554443</v>
       </c>
       <c r="H252" t="n">
         <v>42600</v>
@@ -7735,7 +7735,7 @@
         <v>10.3699998855591</v>
       </c>
       <c r="G254" t="n">
-        <v>9.25204086303711</v>
+        <v>9.25203990936279</v>
       </c>
       <c r="H254" t="n">
         <v>400</v>
@@ -7793,7 +7793,7 @@
         <v>10.2600002288818</v>
       </c>
       <c r="G256" t="n">
-        <v>9.15390014648438</v>
+        <v>9.15390110015869</v>
       </c>
       <c r="H256" t="n">
         <v>600</v>
@@ -7822,7 +7822,7 @@
         <v>10.210000038147</v>
       </c>
       <c r="G257" t="n">
-        <v>9.10929012298584</v>
+        <v>9.10928916931152</v>
       </c>
       <c r="H257" t="n">
         <v>14400</v>
@@ -7851,7 +7851,7 @@
         <v>10.2399997711182</v>
       </c>
       <c r="G258" t="n">
-        <v>9.1360559463501</v>
+        <v>9.13605499267578</v>
       </c>
       <c r="H258" t="n">
         <v>2200</v>
@@ -7967,7 +7967,7 @@
         <v>10.3299999237061</v>
       </c>
       <c r="G262" t="n">
-        <v>9.21635246276855</v>
+        <v>9.21635341644287</v>
       </c>
       <c r="H262" t="n">
         <v>400</v>
@@ -8054,7 +8054,7 @@
         <v>10.3400001525879</v>
       </c>
       <c r="G265" t="n">
-        <v>9.22527503967285</v>
+        <v>9.22527408599854</v>
       </c>
       <c r="H265" t="n">
         <v>1200</v>
@@ -8083,7 +8083,7 @@
         <v>10.3299999237061</v>
       </c>
       <c r="G266" t="n">
-        <v>9.21635246276855</v>
+        <v>9.21635341644287</v>
       </c>
       <c r="H266" t="n">
         <v>3000</v>
@@ -8112,7 +8112,7 @@
         <v>10.4200000762939</v>
       </c>
       <c r="G267" t="n">
-        <v>9.29665088653564</v>
+        <v>9.29664993286133</v>
       </c>
       <c r="H267" t="n">
         <v>4000</v>
@@ -8141,7 +8141,7 @@
         <v>10.3500003814697</v>
       </c>
       <c r="G268" t="n">
-        <v>9.23419761657715</v>
+        <v>9.23419952392578</v>
       </c>
       <c r="H268" t="n">
         <v>2000</v>
@@ -8170,7 +8170,7 @@
         <v>10.4200000762939</v>
       </c>
       <c r="G269" t="n">
-        <v>9.29665088653564</v>
+        <v>9.29664993286133</v>
       </c>
       <c r="H269" t="n">
         <v>15000</v>
@@ -8228,7 +8228,7 @@
         <v>10.460000038147</v>
       </c>
       <c r="G271" t="n">
-        <v>9.33233833312988</v>
+        <v>9.3323392868042</v>
       </c>
       <c r="H271" t="n">
         <v>3000</v>
@@ -8315,7 +8315,7 @@
         <v>10.4399995803833</v>
       </c>
       <c r="G274" t="n">
-        <v>9.31449508666992</v>
+        <v>9.31449413299561</v>
       </c>
       <c r="H274" t="n">
         <v>12800</v>
@@ -8373,7 +8373,7 @@
         <v>10.1800003051758</v>
       </c>
       <c r="G276" t="n">
-        <v>9.08252429962158</v>
+        <v>9.0825252532959</v>
       </c>
       <c r="H276" t="n">
         <v>25000</v>
@@ -8402,7 +8402,7 @@
         <v>10.0799999237061</v>
       </c>
       <c r="G277" t="n">
-        <v>8.99330520629883</v>
+        <v>8.99330425262451</v>
       </c>
       <c r="H277" t="n">
         <v>21800</v>
@@ -8460,7 +8460,7 @@
         <v>10.1400003433228</v>
       </c>
       <c r="G279" t="n">
-        <v>9.04683589935303</v>
+        <v>9.04683780670166</v>
       </c>
       <c r="H279" t="n">
         <v>20400</v>
@@ -8489,7 +8489,7 @@
         <v>10.1199998855591</v>
       </c>
       <c r="G280" t="n">
-        <v>9.02899265289307</v>
+        <v>9.02899074554443</v>
       </c>
       <c r="H280" t="n">
         <v>12200</v>
@@ -8576,7 +8576,7 @@
         <v>10.1999998092651</v>
       </c>
       <c r="G283" t="n">
-        <v>9.10036659240723</v>
+        <v>9.10036849975586</v>
       </c>
       <c r="H283" t="n">
         <v>1400</v>
@@ -8663,7 +8663,7 @@
         <v>10.0600004196167</v>
       </c>
       <c r="G286" t="n">
-        <v>8.97546195983887</v>
+        <v>8.97546100616455</v>
       </c>
       <c r="H286" t="n">
         <v>15200</v>
@@ -8721,7 +8721,7 @@
         <v>10.1400003433228</v>
       </c>
       <c r="G288" t="n">
-        <v>9.04683589935303</v>
+        <v>9.04683780670166</v>
       </c>
       <c r="H288" t="n">
         <v>5200</v>
@@ -8750,7 +8750,7 @@
         <v>10.1400003433228</v>
       </c>
       <c r="G289" t="n">
-        <v>9.04683589935303</v>
+        <v>9.04683780670166</v>
       </c>
       <c r="H289" t="n">
         <v>10000</v>
@@ -8808,7 +8808,7 @@
         <v>10.1300001144409</v>
       </c>
       <c r="G291" t="n">
-        <v>9.03791332244873</v>
+        <v>9.03791427612305</v>
       </c>
       <c r="H291" t="n">
         <v>7400</v>
@@ -8837,7 +8837,7 @@
         <v>10.1199998855591</v>
       </c>
       <c r="G292" t="n">
-        <v>9.02899265289307</v>
+        <v>9.02899074554443</v>
       </c>
       <c r="H292" t="n">
         <v>200</v>
@@ -8924,7 +8924,7 @@
         <v>10.0699996948242</v>
       </c>
       <c r="G295" t="n">
-        <v>8.98438358306885</v>
+        <v>8.98438167572021</v>
       </c>
       <c r="H295" t="n">
         <v>5000</v>
@@ -8953,7 +8953,7 @@
         <v>10.1199998855591</v>
       </c>
       <c r="G296" t="n">
-        <v>9.02899265289307</v>
+        <v>9.02899074554443</v>
       </c>
       <c r="H296" t="n">
         <v>5600</v>
@@ -8982,7 +8982,7 @@
         <v>10.1199998855591</v>
       </c>
       <c r="G297" t="n">
-        <v>9.02899265289307</v>
+        <v>9.02899074554443</v>
       </c>
       <c r="H297" t="n">
         <v>2600</v>
@@ -9011,7 +9011,7 @@
         <v>10.0799999237061</v>
       </c>
       <c r="G298" t="n">
-        <v>8.99330520629883</v>
+        <v>8.99330425262451</v>
       </c>
       <c r="H298" t="n">
         <v>200</v>
@@ -9040,7 +9040,7 @@
         <v>10.0600004196167</v>
       </c>
       <c r="G299" t="n">
-        <v>8.97546195983887</v>
+        <v>8.97546100616455</v>
       </c>
       <c r="H299" t="n">
         <v>17200</v>
@@ -9069,7 +9069,7 @@
         <v>10.0600004196167</v>
       </c>
       <c r="G300" t="n">
-        <v>8.97546195983887</v>
+        <v>8.97546100616455</v>
       </c>
       <c r="H300" t="n">
         <v>1000</v>
@@ -9098,7 +9098,7 @@
         <v>10.0600004196167</v>
       </c>
       <c r="G301" t="n">
-        <v>8.97546195983887</v>
+        <v>8.97546100616455</v>
       </c>
       <c r="H301" t="n">
         <v>12600</v>
@@ -9127,7 +9127,7 @@
         <v>10.0600004196167</v>
       </c>
       <c r="G302" t="n">
-        <v>8.97546195983887</v>
+        <v>8.97546100616455</v>
       </c>
       <c r="H302" t="n">
         <v>2000</v>
@@ -9156,7 +9156,7 @@
         <v>10.0600004196167</v>
       </c>
       <c r="G303" t="n">
-        <v>8.97546195983887</v>
+        <v>8.97546100616455</v>
       </c>
       <c r="H303" t="n">
         <v>0</v>
@@ -9214,7 +9214,7 @@
         <v>10.0600004196167</v>
       </c>
       <c r="G305" t="n">
-        <v>8.97546195983887</v>
+        <v>8.97546100616455</v>
       </c>
       <c r="H305" t="n">
         <v>200</v>
@@ -9243,7 +9243,7 @@
         <v>10.0799999237061</v>
       </c>
       <c r="G306" t="n">
-        <v>8.99330520629883</v>
+        <v>8.99330425262451</v>
       </c>
       <c r="H306" t="n">
         <v>11200</v>
@@ -9272,7 +9272,7 @@
         <v>10.0600004196167</v>
       </c>
       <c r="G307" t="n">
-        <v>8.97546195983887</v>
+        <v>8.97546100616455</v>
       </c>
       <c r="H307" t="n">
         <v>4200</v>
@@ -9301,7 +9301,7 @@
         <v>10.0100002288818</v>
       </c>
       <c r="G308" t="n">
-        <v>8.93085193634033</v>
+        <v>8.93085098266602</v>
       </c>
       <c r="H308" t="n">
         <v>25000</v>
@@ -9330,7 +9330,7 @@
         <v>10.0100002288818</v>
       </c>
       <c r="G309" t="n">
-        <v>8.93085193634033</v>
+        <v>8.93085098266602</v>
       </c>
       <c r="H309" t="n">
         <v>0</v>
@@ -9388,7 +9388,7 @@
         <v>10</v>
       </c>
       <c r="G311" t="n">
-        <v>8.92192935943604</v>
+        <v>8.92192840576172</v>
       </c>
       <c r="H311" t="n">
         <v>2800</v>
@@ -9417,7 +9417,7 @@
         <v>10</v>
       </c>
       <c r="G312" t="n">
-        <v>8.92192935943604</v>
+        <v>8.92192840576172</v>
       </c>
       <c r="H312" t="n">
         <v>0</v>
@@ -9446,7 +9446,7 @@
         <v>10</v>
       </c>
       <c r="G313" t="n">
-        <v>8.92192935943604</v>
+        <v>8.92192840576172</v>
       </c>
       <c r="H313" t="n">
         <v>2800</v>
@@ -9475,7 +9475,7 @@
         <v>10</v>
       </c>
       <c r="G314" t="n">
-        <v>8.92192935943604</v>
+        <v>8.92192840576172</v>
       </c>
       <c r="H314" t="n">
         <v>0</v>
@@ -9591,7 +9591,7 @@
         <v>10.1999998092651</v>
       </c>
       <c r="G318" t="n">
-        <v>9.10036659240723</v>
+        <v>9.10036849975586</v>
       </c>
       <c r="H318" t="n">
         <v>8600</v>
@@ -9620,7 +9620,7 @@
         <v>10.1999998092651</v>
       </c>
       <c r="G319" t="n">
-        <v>9.10036659240723</v>
+        <v>9.10036849975586</v>
       </c>
       <c r="H319" t="n">
         <v>0</v>
@@ -9649,7 +9649,7 @@
         <v>10</v>
       </c>
       <c r="G320" t="n">
-        <v>8.92192935943604</v>
+        <v>8.92192840576172</v>
       </c>
       <c r="H320" t="n">
         <v>30800</v>
@@ -9678,7 +9678,7 @@
         <v>10.1999998092651</v>
       </c>
       <c r="G321" t="n">
-        <v>9.10036659240723</v>
+        <v>9.10036849975586</v>
       </c>
       <c r="H321" t="n">
         <v>24600</v>
@@ -9707,7 +9707,7 @@
         <v>10.1999998092651</v>
       </c>
       <c r="G322" t="n">
-        <v>9.10036659240723</v>
+        <v>9.10036849975586</v>
       </c>
       <c r="H322" t="n">
         <v>12200</v>
@@ -9794,7 +9794,7 @@
         <v>10.1999998092651</v>
       </c>
       <c r="G325" t="n">
-        <v>9.10036659240723</v>
+        <v>9.10036849975586</v>
       </c>
       <c r="H325" t="n">
         <v>1800</v>
@@ -9823,7 +9823,7 @@
         <v>10.1999998092651</v>
       </c>
       <c r="G326" t="n">
-        <v>9.10036659240723</v>
+        <v>9.10036849975586</v>
       </c>
       <c r="H326" t="n">
         <v>2400</v>
@@ -9881,7 +9881,7 @@
         <v>10</v>
       </c>
       <c r="G328" t="n">
-        <v>8.92192935943604</v>
+        <v>8.92192840576172</v>
       </c>
       <c r="H328" t="n">
         <v>6400</v>
@@ -9968,7 +9968,7 @@
         <v>9.94999980926514</v>
       </c>
       <c r="G331" t="n">
-        <v>8.8773193359375</v>
+        <v>8.87731838226318</v>
       </c>
       <c r="H331" t="n">
         <v>9000</v>
@@ -9997,7 +9997,7 @@
         <v>10</v>
       </c>
       <c r="G332" t="n">
-        <v>8.92192935943604</v>
+        <v>8.92192840576172</v>
       </c>
       <c r="H332" t="n">
         <v>600</v>
@@ -10026,7 +10026,7 @@
         <v>10</v>
       </c>
       <c r="G333" t="n">
-        <v>8.92192935943604</v>
+        <v>8.92192840576172</v>
       </c>
       <c r="H333" t="n">
         <v>1200</v>
@@ -10055,7 +10055,7 @@
         <v>10</v>
       </c>
       <c r="G334" t="n">
-        <v>8.92192935943604</v>
+        <v>8.92192840576172</v>
       </c>
       <c r="H334" t="n">
         <v>200</v>
@@ -10084,7 +10084,7 @@
         <v>10</v>
       </c>
       <c r="G335" t="n">
-        <v>8.92192935943604</v>
+        <v>8.92192840576172</v>
       </c>
       <c r="H335" t="n">
         <v>0</v>
@@ -10113,7 +10113,7 @@
         <v>9.94999980926514</v>
       </c>
       <c r="G336" t="n">
-        <v>8.8773193359375</v>
+        <v>8.87731838226318</v>
       </c>
       <c r="H336" t="n">
         <v>7000</v>
@@ -10142,7 +10142,7 @@
         <v>9.94999980926514</v>
       </c>
       <c r="G337" t="n">
-        <v>8.8773193359375</v>
+        <v>8.87731838226318</v>
       </c>
       <c r="H337" t="n">
         <v>0</v>
@@ -10171,7 +10171,7 @@
         <v>9.94999980926514</v>
       </c>
       <c r="G338" t="n">
-        <v>8.8773193359375</v>
+        <v>8.87731838226318</v>
       </c>
       <c r="H338" t="n">
         <v>0</v>
@@ -10200,7 +10200,7 @@
         <v>10</v>
       </c>
       <c r="G339" t="n">
-        <v>8.92192935943604</v>
+        <v>8.92192840576172</v>
       </c>
       <c r="H339" t="n">
         <v>8000</v>
@@ -10229,7 +10229,7 @@
         <v>9.94999980926514</v>
       </c>
       <c r="G340" t="n">
-        <v>8.8773193359375</v>
+        <v>8.87731838226318</v>
       </c>
       <c r="H340" t="n">
         <v>6600</v>
@@ -10258,7 +10258,7 @@
         <v>9.89999961853027</v>
       </c>
       <c r="G341" t="n">
-        <v>8.83271026611328</v>
+        <v>8.83270931243896</v>
       </c>
       <c r="H341" t="n">
         <v>5400</v>
@@ -10287,7 +10287,7 @@
         <v>10</v>
       </c>
       <c r="G342" t="n">
-        <v>8.92192935943604</v>
+        <v>8.92192840576172</v>
       </c>
       <c r="H342" t="n">
         <v>4400</v>
@@ -10316,7 +10316,7 @@
         <v>10</v>
       </c>
       <c r="G343" t="n">
-        <v>8.92192935943604</v>
+        <v>8.92192840576172</v>
       </c>
       <c r="H343" t="n">
         <v>1400</v>
@@ -10345,7 +10345,7 @@
         <v>10</v>
       </c>
       <c r="G344" t="n">
-        <v>8.92192935943604</v>
+        <v>8.92192840576172</v>
       </c>
       <c r="H344" t="n">
         <v>0</v>
@@ -10374,7 +10374,7 @@
         <v>10</v>
       </c>
       <c r="G345" t="n">
-        <v>8.92192935943604</v>
+        <v>8.92192840576172</v>
       </c>
       <c r="H345" t="n">
         <v>2000</v>
@@ -10403,7 +10403,7 @@
         <v>10</v>
       </c>
       <c r="G346" t="n">
-        <v>8.92192935943604</v>
+        <v>8.92192840576172</v>
       </c>
       <c r="H346" t="n">
         <v>14400</v>
@@ -10432,7 +10432,7 @@
         <v>10</v>
       </c>
       <c r="G347" t="n">
-        <v>8.92192935943604</v>
+        <v>8.92192840576172</v>
       </c>
       <c r="H347" t="n">
         <v>0</v>
@@ -10461,7 +10461,7 @@
         <v>10</v>
       </c>
       <c r="G348" t="n">
-        <v>8.92192935943604</v>
+        <v>8.92192840576172</v>
       </c>
       <c r="H348" t="n">
         <v>2000</v>
@@ -10490,7 +10490,7 @@
         <v>10</v>
       </c>
       <c r="G349" t="n">
-        <v>8.92192935943604</v>
+        <v>8.92192840576172</v>
       </c>
       <c r="H349" t="n">
         <v>3600</v>
@@ -10548,7 +10548,7 @@
         <v>10</v>
       </c>
       <c r="G351" t="n">
-        <v>8.92192935943604</v>
+        <v>8.92192840576172</v>
       </c>
       <c r="H351" t="n">
         <v>4000</v>
@@ -10577,7 +10577,7 @@
         <v>10</v>
       </c>
       <c r="G352" t="n">
-        <v>8.92192935943604</v>
+        <v>8.92192840576172</v>
       </c>
       <c r="H352" t="n">
         <v>0</v>
@@ -10606,7 +10606,7 @@
         <v>10</v>
       </c>
       <c r="G353" t="n">
-        <v>8.92192935943604</v>
+        <v>8.92192840576172</v>
       </c>
       <c r="H353" t="n">
         <v>400</v>
@@ -10635,7 +10635,7 @@
         <v>10</v>
       </c>
       <c r="G354" t="n">
-        <v>8.92192935943604</v>
+        <v>8.92192840576172</v>
       </c>
       <c r="H354" t="n">
         <v>4200</v>
@@ -10664,7 +10664,7 @@
         <v>9.89999961853027</v>
       </c>
       <c r="G355" t="n">
-        <v>8.83271026611328</v>
+        <v>8.83270931243896</v>
       </c>
       <c r="H355" t="n">
         <v>17800</v>
@@ -10693,7 +10693,7 @@
         <v>9.89999961853027</v>
       </c>
       <c r="G356" t="n">
-        <v>8.83271026611328</v>
+        <v>8.83270931243896</v>
       </c>
       <c r="H356" t="n">
         <v>18800</v>
@@ -10722,7 +10722,7 @@
         <v>9.89999961853027</v>
       </c>
       <c r="G357" t="n">
-        <v>8.83271026611328</v>
+        <v>8.83270931243896</v>
       </c>
       <c r="H357" t="n">
         <v>6800</v>
@@ -10751,7 +10751,7 @@
         <v>9.89999961853027</v>
       </c>
       <c r="G358" t="n">
-        <v>8.83271026611328</v>
+        <v>8.83270931243896</v>
       </c>
       <c r="H358" t="n">
         <v>0</v>
@@ -10780,7 +10780,7 @@
         <v>9.89999961853027</v>
       </c>
       <c r="G359" t="n">
-        <v>8.83271026611328</v>
+        <v>8.83270931243896</v>
       </c>
       <c r="H359" t="n">
         <v>0</v>
@@ -10809,7 +10809,7 @@
         <v>9.89999961853027</v>
       </c>
       <c r="G360" t="n">
-        <v>8.83271026611328</v>
+        <v>8.83270931243896</v>
       </c>
       <c r="H360" t="n">
         <v>0</v>
@@ -10838,7 +10838,7 @@
         <v>9.89999961853027</v>
       </c>
       <c r="G361" t="n">
-        <v>8.83271026611328</v>
+        <v>8.83270931243896</v>
       </c>
       <c r="H361" t="n">
         <v>1000</v>
@@ -10867,7 +10867,7 @@
         <v>9.94999980926514</v>
       </c>
       <c r="G362" t="n">
-        <v>8.8773193359375</v>
+        <v>8.87731838226318</v>
       </c>
       <c r="H362" t="n">
         <v>2200</v>
@@ -10896,7 +10896,7 @@
         <v>10</v>
       </c>
       <c r="G363" t="n">
-        <v>8.92192935943604</v>
+        <v>8.92192840576172</v>
       </c>
       <c r="H363" t="n">
         <v>1000</v>
@@ -10925,7 +10925,7 @@
         <v>9.94999980926514</v>
       </c>
       <c r="G364" t="n">
-        <v>8.8773193359375</v>
+        <v>8.87731838226318</v>
       </c>
       <c r="H364" t="n">
         <v>6400</v>
@@ -10954,7 +10954,7 @@
         <v>9.94999980926514</v>
       </c>
       <c r="G365" t="n">
-        <v>8.8773193359375</v>
+        <v>8.87731838226318</v>
       </c>
       <c r="H365" t="n">
         <v>1000</v>
@@ -11041,7 +11041,7 @@
         <v>9.89999961853027</v>
       </c>
       <c r="G368" t="n">
-        <v>8.83271026611328</v>
+        <v>8.83270931243896</v>
       </c>
       <c r="H368" t="n">
         <v>400</v>
@@ -11070,7 +11070,7 @@
         <v>9.89999961853027</v>
       </c>
       <c r="G369" t="n">
-        <v>8.83271026611328</v>
+        <v>8.83270931243896</v>
       </c>
       <c r="H369" t="n">
         <v>1600</v>
@@ -11099,7 +11099,7 @@
         <v>9.89999961853027</v>
       </c>
       <c r="G370" t="n">
-        <v>8.83271026611328</v>
+        <v>8.83270931243896</v>
       </c>
       <c r="H370" t="n">
         <v>0</v>
@@ -11128,7 +11128,7 @@
         <v>9.94999980926514</v>
       </c>
       <c r="G371" t="n">
-        <v>8.8773193359375</v>
+        <v>8.87731838226318</v>
       </c>
       <c r="H371" t="n">
         <v>19600</v>
@@ -11186,7 +11186,7 @@
         <v>9.89999961853027</v>
       </c>
       <c r="G373" t="n">
-        <v>8.83271026611328</v>
+        <v>8.83270931243896</v>
       </c>
       <c r="H373" t="n">
         <v>10800</v>
@@ -11244,7 +11244,7 @@
         <v>10</v>
       </c>
       <c r="G375" t="n">
-        <v>8.92192935943604</v>
+        <v>8.92192840576172</v>
       </c>
       <c r="H375" t="n">
         <v>2000</v>
@@ -11273,7 +11273,7 @@
         <v>10</v>
       </c>
       <c r="G376" t="n">
-        <v>8.92192935943604</v>
+        <v>8.92192840576172</v>
       </c>
       <c r="H376" t="n">
         <v>1400</v>
@@ -11302,7 +11302,7 @@
         <v>9.94999980926514</v>
       </c>
       <c r="G377" t="n">
-        <v>8.8773193359375</v>
+        <v>8.87731838226318</v>
       </c>
       <c r="H377" t="n">
         <v>200</v>
@@ -11331,7 +11331,7 @@
         <v>10</v>
       </c>
       <c r="G378" t="n">
-        <v>8.92192935943604</v>
+        <v>8.92192840576172</v>
       </c>
       <c r="H378" t="n">
         <v>200</v>
@@ -11360,7 +11360,7 @@
         <v>10</v>
       </c>
       <c r="G379" t="n">
-        <v>8.92192935943604</v>
+        <v>8.92192840576172</v>
       </c>
       <c r="H379" t="n">
         <v>800</v>
@@ -11389,7 +11389,7 @@
         <v>10</v>
       </c>
       <c r="G380" t="n">
-        <v>8.92192935943604</v>
+        <v>8.92192840576172</v>
       </c>
       <c r="H380" t="n">
         <v>6600</v>
@@ -11418,7 +11418,7 @@
         <v>10</v>
       </c>
       <c r="G381" t="n">
-        <v>8.92192935943604</v>
+        <v>8.92192840576172</v>
       </c>
       <c r="H381" t="n">
         <v>0</v>
@@ -11447,7 +11447,7 @@
         <v>10</v>
       </c>
       <c r="G382" t="n">
-        <v>8.92192935943604</v>
+        <v>8.92192840576172</v>
       </c>
       <c r="H382" t="n">
         <v>0</v>
@@ -11476,7 +11476,7 @@
         <v>9.94999980926514</v>
       </c>
       <c r="G383" t="n">
-        <v>8.8773193359375</v>
+        <v>8.87731838226318</v>
       </c>
       <c r="H383" t="n">
         <v>800</v>
@@ -11505,7 +11505,7 @@
         <v>9.94999980926514</v>
       </c>
       <c r="G384" t="n">
-        <v>8.8773193359375</v>
+        <v>8.87731838226318</v>
       </c>
       <c r="H384" t="n">
         <v>1600</v>
@@ -11534,7 +11534,7 @@
         <v>9.94999980926514</v>
       </c>
       <c r="G385" t="n">
-        <v>8.8773193359375</v>
+        <v>8.87731838226318</v>
       </c>
       <c r="H385" t="n">
         <v>0</v>
@@ -11563,7 +11563,7 @@
         <v>9.94999980926514</v>
       </c>
       <c r="G386" t="n">
-        <v>8.8773193359375</v>
+        <v>8.87731838226318</v>
       </c>
       <c r="H386" t="n">
         <v>14200</v>
@@ -11592,7 +11592,7 @@
         <v>9.89999961853027</v>
       </c>
       <c r="G387" t="n">
-        <v>8.83271026611328</v>
+        <v>8.83270931243896</v>
       </c>
       <c r="H387" t="n">
         <v>14200</v>
@@ -11824,7 +11824,7 @@
         <v>9.89999961853027</v>
       </c>
       <c r="G395" t="n">
-        <v>8.83271026611328</v>
+        <v>8.83270931243896</v>
       </c>
       <c r="H395" t="n">
         <v>21000</v>
@@ -11853,7 +11853,7 @@
         <v>9.94999980926514</v>
       </c>
       <c r="G396" t="n">
-        <v>8.8773193359375</v>
+        <v>8.87731838226318</v>
       </c>
       <c r="H396" t="n">
         <v>39000</v>
@@ -11882,7 +11882,7 @@
         <v>9.94999980926514</v>
       </c>
       <c r="G397" t="n">
-        <v>8.8773193359375</v>
+        <v>8.87731838226318</v>
       </c>
       <c r="H397" t="n">
         <v>3800</v>
@@ -11911,7 +11911,7 @@
         <v>9.89999961853027</v>
       </c>
       <c r="G398" t="n">
-        <v>8.83271026611328</v>
+        <v>8.83270931243896</v>
       </c>
       <c r="H398" t="n">
         <v>44000</v>
@@ -11940,7 +11940,7 @@
         <v>9.94999980926514</v>
       </c>
       <c r="G399" t="n">
-        <v>8.8773193359375</v>
+        <v>8.87731838226318</v>
       </c>
       <c r="H399" t="n">
         <v>5400</v>
@@ -11969,7 +11969,7 @@
         <v>9.94999980926514</v>
       </c>
       <c r="G400" t="n">
-        <v>8.8773193359375</v>
+        <v>8.87731838226318</v>
       </c>
       <c r="H400" t="n">
         <v>1000</v>
@@ -11998,7 +11998,7 @@
         <v>9.94999980926514</v>
       </c>
       <c r="G401" t="n">
-        <v>8.8773193359375</v>
+        <v>8.87731838226318</v>
       </c>
       <c r="H401" t="n">
         <v>5600</v>
@@ -12027,7 +12027,7 @@
         <v>9.94999980926514</v>
       </c>
       <c r="G402" t="n">
-        <v>8.8773193359375</v>
+        <v>8.87731838226318</v>
       </c>
       <c r="H402" t="n">
         <v>43600</v>
@@ -12056,7 +12056,7 @@
         <v>9.89999961853027</v>
       </c>
       <c r="G403" t="n">
-        <v>8.83271026611328</v>
+        <v>8.83270931243896</v>
       </c>
       <c r="H403" t="n">
         <v>400</v>
@@ -12085,7 +12085,7 @@
         <v>9.89999961853027</v>
       </c>
       <c r="G404" t="n">
-        <v>8.83271026611328</v>
+        <v>8.83270931243896</v>
       </c>
       <c r="H404" t="n">
         <v>3200</v>
@@ -12172,7 +12172,7 @@
         <v>9.89999961853027</v>
       </c>
       <c r="G407" t="n">
-        <v>8.83271026611328</v>
+        <v>8.83270931243896</v>
       </c>
       <c r="H407" t="n">
         <v>2200</v>
@@ -12201,7 +12201,7 @@
         <v>9.94999980926514</v>
       </c>
       <c r="G408" t="n">
-        <v>8.8773193359375</v>
+        <v>8.87731838226318</v>
       </c>
       <c r="H408" t="n">
         <v>3000</v>
@@ -12665,7 +12665,7 @@
         <v>9.89999961853027</v>
       </c>
       <c r="G424" t="n">
-        <v>8.83271026611328</v>
+        <v>8.83270931243896</v>
       </c>
       <c r="H424" t="n">
         <v>12600</v>
@@ -12694,7 +12694,7 @@
         <v>9.94999980926514</v>
       </c>
       <c r="G425" t="n">
-        <v>8.8773193359375</v>
+        <v>8.87731838226318</v>
       </c>
       <c r="H425" t="n">
         <v>7000</v>
@@ -12723,7 +12723,7 @@
         <v>9.94999980926514</v>
       </c>
       <c r="G426" t="n">
-        <v>8.8773193359375</v>
+        <v>8.87731838226318</v>
       </c>
       <c r="H426" t="n">
         <v>6200</v>
@@ -12984,7 +12984,7 @@
         <v>10.1999998092651</v>
       </c>
       <c r="G435" t="n">
-        <v>9.10036659240723</v>
+        <v>9.10036849975586</v>
       </c>
       <c r="H435" t="n">
         <v>10800</v>
@@ -13013,7 +13013,7 @@
         <v>10.1999998092651</v>
       </c>
       <c r="G436" t="n">
-        <v>9.10036659240723</v>
+        <v>9.10036849975586</v>
       </c>
       <c r="H436" t="n">
         <v>800</v>
@@ -13042,7 +13042,7 @@
         <v>10.1999998092651</v>
       </c>
       <c r="G437" t="n">
-        <v>9.10036659240723</v>
+        <v>9.10036849975586</v>
       </c>
       <c r="H437" t="n">
         <v>205800</v>
@@ -13071,7 +13071,7 @@
         <v>10.1999998092651</v>
       </c>
       <c r="G438" t="n">
-        <v>9.10036659240723</v>
+        <v>9.10036849975586</v>
       </c>
       <c r="H438" t="n">
         <v>4400</v>
@@ -13100,7 +13100,7 @@
         <v>10.1999998092651</v>
       </c>
       <c r="G439" t="n">
-        <v>9.10036659240723</v>
+        <v>9.10036849975586</v>
       </c>
       <c r="H439" t="n">
         <v>328400</v>
@@ -13245,7 +13245,7 @@
         <v>10.3999996185303</v>
       </c>
       <c r="G444" t="n">
-        <v>9.27880764007568</v>
+        <v>9.27880573272705</v>
       </c>
       <c r="H444" t="n">
         <v>9000</v>
@@ -13274,7 +13274,7 @@
         <v>10.3999996185303</v>
       </c>
       <c r="G445" t="n">
-        <v>9.27880764007568</v>
+        <v>9.27880573272705</v>
       </c>
       <c r="H445" t="n">
         <v>1000</v>
@@ -13303,7 +13303,7 @@
         <v>10.3999996185303</v>
       </c>
       <c r="G446" t="n">
-        <v>9.27880764007568</v>
+        <v>9.27880573272705</v>
       </c>
       <c r="H446" t="n">
         <v>0</v>
@@ -13332,7 +13332,7 @@
         <v>10.3999996185303</v>
       </c>
       <c r="G447" t="n">
-        <v>9.27880764007568</v>
+        <v>9.27880573272705</v>
       </c>
       <c r="H447" t="n">
         <v>18200</v>
@@ -13361,7 +13361,7 @@
         <v>10.3999996185303</v>
       </c>
       <c r="G448" t="n">
-        <v>9.27880764007568</v>
+        <v>9.27880573272705</v>
       </c>
       <c r="H448" t="n">
         <v>3000</v>
@@ -13390,7 +13390,7 @@
         <v>10.1999998092651</v>
       </c>
       <c r="G449" t="n">
-        <v>9.10036659240723</v>
+        <v>9.10036849975586</v>
       </c>
       <c r="H449" t="n">
         <v>8000</v>
@@ -13448,7 +13448,7 @@
         <v>10.3999996185303</v>
       </c>
       <c r="G451" t="n">
-        <v>9.27880764007568</v>
+        <v>9.27880573272705</v>
       </c>
       <c r="H451" t="n">
         <v>16400</v>
@@ -13477,7 +13477,7 @@
         <v>10.3999996185303</v>
       </c>
       <c r="G452" t="n">
-        <v>9.27880764007568</v>
+        <v>9.27880573272705</v>
       </c>
       <c r="H452" t="n">
         <v>10800</v>
@@ -13506,7 +13506,7 @@
         <v>10.3999996185303</v>
       </c>
       <c r="G453" t="n">
-        <v>9.27880764007568</v>
+        <v>9.27880573272705</v>
       </c>
       <c r="H453" t="n">
         <v>30600</v>
@@ -13564,7 +13564,7 @@
         <v>10.3999996185303</v>
       </c>
       <c r="G455" t="n">
-        <v>9.27880764007568</v>
+        <v>9.27880573272705</v>
       </c>
       <c r="H455" t="n">
         <v>7600</v>
@@ -13622,7 +13622,7 @@
         <v>10.3999996185303</v>
       </c>
       <c r="G457" t="n">
-        <v>9.27880764007568</v>
+        <v>9.27880573272705</v>
       </c>
       <c r="H457" t="n">
         <v>34200</v>
@@ -13709,7 +13709,7 @@
         <v>10.3999996185303</v>
       </c>
       <c r="G460" t="n">
-        <v>9.27880764007568</v>
+        <v>9.27880573272705</v>
       </c>
       <c r="H460" t="n">
         <v>10000</v>
@@ -13738,7 +13738,7 @@
         <v>10.3999996185303</v>
       </c>
       <c r="G461" t="n">
-        <v>9.27880764007568</v>
+        <v>9.27880573272705</v>
       </c>
       <c r="H461" t="n">
         <v>0</v>
@@ -13941,7 +13941,7 @@
         <v>10.1999998092651</v>
       </c>
       <c r="G468" t="n">
-        <v>9.10036659240723</v>
+        <v>9.10036849975586</v>
       </c>
       <c r="H468" t="n">
         <v>12000</v>
@@ -13970,7 +13970,7 @@
         <v>10.1999998092651</v>
       </c>
       <c r="G469" t="n">
-        <v>9.10036659240723</v>
+        <v>9.10036849975586</v>
       </c>
       <c r="H469" t="n">
         <v>3000</v>
@@ -13999,7 +13999,7 @@
         <v>10.1999998092651</v>
       </c>
       <c r="G470" t="n">
-        <v>9.10036659240723</v>
+        <v>9.10036849975586</v>
       </c>
       <c r="H470" t="n">
         <v>40000</v>
@@ -14028,7 +14028,7 @@
         <v>10.1999998092651</v>
       </c>
       <c r="G471" t="n">
-        <v>9.10036659240723</v>
+        <v>9.10036849975586</v>
       </c>
       <c r="H471" t="n">
         <v>0</v>
@@ -14086,7 +14086,7 @@
         <v>10.1999998092651</v>
       </c>
       <c r="G473" t="n">
-        <v>9.10036659240723</v>
+        <v>9.10036849975586</v>
       </c>
       <c r="H473" t="n">
         <v>5000</v>
@@ -14115,7 +14115,7 @@
         <v>10.1999998092651</v>
       </c>
       <c r="G474" t="n">
-        <v>9.10036659240723</v>
+        <v>9.10036849975586</v>
       </c>
       <c r="H474" t="n">
         <v>29200</v>
@@ -14173,7 +14173,7 @@
         <v>10.1999998092651</v>
       </c>
       <c r="G476" t="n">
-        <v>9.10036659240723</v>
+        <v>9.10036849975586</v>
       </c>
       <c r="H476" t="n">
         <v>400</v>
@@ -14202,7 +14202,7 @@
         <v>10.1999998092651</v>
       </c>
       <c r="G477" t="n">
-        <v>9.10036659240723</v>
+        <v>9.10036849975586</v>
       </c>
       <c r="H477" t="n">
         <v>10600</v>
@@ -14231,7 +14231,7 @@
         <v>10.1999998092651</v>
       </c>
       <c r="G478" t="n">
-        <v>9.10036659240723</v>
+        <v>9.10036849975586</v>
       </c>
       <c r="H478" t="n">
         <v>0</v>
@@ -14260,7 +14260,7 @@
         <v>10.1999998092651</v>
       </c>
       <c r="G479" t="n">
-        <v>9.10036659240723</v>
+        <v>9.10036849975586</v>
       </c>
       <c r="H479" t="n">
         <v>1600</v>
@@ -14289,7 +14289,7 @@
         <v>10.1999998092651</v>
       </c>
       <c r="G480" t="n">
-        <v>9.10036659240723</v>
+        <v>9.10036849975586</v>
       </c>
       <c r="H480" t="n">
         <v>1000</v>
@@ -14318,7 +14318,7 @@
         <v>10.1999998092651</v>
       </c>
       <c r="G481" t="n">
-        <v>9.10036659240723</v>
+        <v>9.10036849975586</v>
       </c>
       <c r="H481" t="n">
         <v>4200</v>
@@ -14376,7 +14376,7 @@
         <v>10.1999998092651</v>
       </c>
       <c r="G483" t="n">
-        <v>9.10036659240723</v>
+        <v>9.10036849975586</v>
       </c>
       <c r="H483" t="n">
         <v>11800</v>
@@ -14405,7 +14405,7 @@
         <v>10.1999998092651</v>
       </c>
       <c r="G484" t="n">
-        <v>9.10036659240723</v>
+        <v>9.10036849975586</v>
       </c>
       <c r="H484" t="n">
         <v>0</v>
@@ -14463,7 +14463,7 @@
         <v>10</v>
       </c>
       <c r="G486" t="n">
-        <v>8.92192935943604</v>
+        <v>8.92192840576172</v>
       </c>
       <c r="H486" t="n">
         <v>7200</v>
@@ -14550,7 +14550,7 @@
         <v>10.1999998092651</v>
       </c>
       <c r="G489" t="n">
-        <v>9.10036659240723</v>
+        <v>9.10036849975586</v>
       </c>
       <c r="H489" t="n">
         <v>1000</v>
@@ -14579,7 +14579,7 @@
         <v>10.1999998092651</v>
       </c>
       <c r="G490" t="n">
-        <v>9.10036659240723</v>
+        <v>9.10036849975586</v>
       </c>
       <c r="H490" t="n">
         <v>400</v>
@@ -14637,7 +14637,7 @@
         <v>10.1999998092651</v>
       </c>
       <c r="G492" t="n">
-        <v>9.10036659240723</v>
+        <v>9.10036849975586</v>
       </c>
       <c r="H492" t="n">
         <v>3200</v>
@@ -14666,7 +14666,7 @@
         <v>10</v>
       </c>
       <c r="G493" t="n">
-        <v>8.92192935943604</v>
+        <v>8.92192840576172</v>
       </c>
       <c r="H493" t="n">
         <v>800</v>
@@ -14782,7 +14782,7 @@
         <v>10</v>
       </c>
       <c r="G497" t="n">
-        <v>8.92192935943604</v>
+        <v>8.92192840576172</v>
       </c>
       <c r="H497" t="n">
         <v>9000</v>
@@ -15014,7 +15014,7 @@
         <v>9.89999961853027</v>
       </c>
       <c r="G505" t="n">
-        <v>8.83271026611328</v>
+        <v>8.83270931243896</v>
       </c>
       <c r="H505" t="n">
         <v>9600</v>
@@ -15130,7 +15130,7 @@
         <v>9.89999961853027</v>
       </c>
       <c r="G509" t="n">
-        <v>8.83271026611328</v>
+        <v>8.83270931243896</v>
       </c>
       <c r="H509" t="n">
         <v>1400</v>
@@ -15681,7 +15681,7 @@
         <v>9.55000019073486</v>
       </c>
       <c r="G528" t="n">
-        <v>8.52044296264648</v>
+        <v>8.52044200897217</v>
       </c>
       <c r="H528" t="n">
         <v>3400</v>
@@ -15710,7 +15710,7 @@
         <v>9.5</v>
       </c>
       <c r="G529" t="n">
-        <v>8.47583293914795</v>
+        <v>8.47583198547363</v>
       </c>
       <c r="H529" t="n">
         <v>10600</v>
@@ -15855,7 +15855,7 @@
         <v>8.80000019073486</v>
       </c>
       <c r="G534" t="n">
-        <v>7.85129880905151</v>
+        <v>7.85129737854004</v>
       </c>
       <c r="H534" t="n">
         <v>9600</v>
@@ -16000,7 +16000,7 @@
         <v>9.10000038146973</v>
       </c>
       <c r="G539" t="n">
-        <v>8.11895656585693</v>
+        <v>8.11895561218262</v>
       </c>
       <c r="H539" t="n">
         <v>2200</v>
@@ -16116,7 +16116,7 @@
         <v>9.10000038146973</v>
       </c>
       <c r="G543" t="n">
-        <v>8.11895656585693</v>
+        <v>8.11895561218262</v>
       </c>
       <c r="H543" t="n">
         <v>2000</v>
@@ -16145,7 +16145,7 @@
         <v>9.10000038146973</v>
       </c>
       <c r="G544" t="n">
-        <v>8.11895656585693</v>
+        <v>8.11895561218262</v>
       </c>
       <c r="H544" t="n">
         <v>0</v>
@@ -16174,7 +16174,7 @@
         <v>9.10000038146973</v>
       </c>
       <c r="G545" t="n">
-        <v>8.11895656585693</v>
+        <v>8.11895561218262</v>
       </c>
       <c r="H545" t="n">
         <v>0</v>
@@ -16348,7 +16348,7 @@
         <v>8.80000019073486</v>
       </c>
       <c r="G551" t="n">
-        <v>7.85129880905151</v>
+        <v>7.85129737854004</v>
       </c>
       <c r="H551" t="n">
         <v>13400</v>
@@ -16377,7 +16377,7 @@
         <v>8.80000019073486</v>
       </c>
       <c r="G552" t="n">
-        <v>7.85129880905151</v>
+        <v>7.85129737854004</v>
       </c>
       <c r="H552" t="n">
         <v>0</v>
@@ -16406,7 +16406,7 @@
         <v>8.75</v>
       </c>
       <c r="G553" t="n">
-        <v>7.80668878555298</v>
+        <v>7.80668783187866</v>
       </c>
       <c r="H553" t="n">
         <v>1400</v>
@@ -16435,7 +16435,7 @@
         <v>8.75</v>
       </c>
       <c r="G554" t="n">
-        <v>7.80668878555298</v>
+        <v>7.80668783187866</v>
       </c>
       <c r="H554" t="n">
         <v>0</v>
@@ -16464,7 +16464,7 @@
         <v>8.75</v>
       </c>
       <c r="G555" t="n">
-        <v>7.80668878555298</v>
+        <v>7.80668783187866</v>
       </c>
       <c r="H555" t="n">
         <v>0</v>
@@ -16493,7 +16493,7 @@
         <v>9.14999961853027</v>
       </c>
       <c r="G556" t="n">
-        <v>8.16356563568115</v>
+        <v>8.16356468200684</v>
       </c>
       <c r="H556" t="n">
         <v>20400</v>
@@ -16667,7 +16667,7 @@
         <v>9.44999980926514</v>
       </c>
       <c r="G562" t="n">
-        <v>8.43122291564941</v>
+        <v>8.4312219619751</v>
       </c>
       <c r="H562" t="n">
         <v>600</v>
@@ -16725,7 +16725,7 @@
         <v>9.55000019073486</v>
       </c>
       <c r="G564" t="n">
-        <v>8.52044296264648</v>
+        <v>8.52044200897217</v>
       </c>
       <c r="H564" t="n">
         <v>4600</v>
@@ -16754,7 +16754,7 @@
         <v>9.60000038146973</v>
       </c>
       <c r="G565" t="n">
-        <v>8.56505298614502</v>
+        <v>8.5650520324707</v>
       </c>
       <c r="H565" t="n">
         <v>3200</v>
@@ -16783,7 +16783,7 @@
         <v>9.60000038146973</v>
       </c>
       <c r="G566" t="n">
-        <v>8.56505298614502</v>
+        <v>8.5650520324707</v>
       </c>
       <c r="H566" t="n">
         <v>9400</v>
@@ -16812,7 +16812,7 @@
         <v>9.60000038146973</v>
       </c>
       <c r="G567" t="n">
-        <v>8.56505298614502</v>
+        <v>8.5650520324707</v>
       </c>
       <c r="H567" t="n">
         <v>11000</v>
@@ -16870,7 +16870,7 @@
         <v>9.55000019073486</v>
       </c>
       <c r="G569" t="n">
-        <v>8.52044296264648</v>
+        <v>8.52044200897217</v>
       </c>
       <c r="H569" t="n">
         <v>6800</v>
@@ -16899,7 +16899,7 @@
         <v>9.60000038146973</v>
       </c>
       <c r="G570" t="n">
-        <v>8.56505298614502</v>
+        <v>8.5650520324707</v>
       </c>
       <c r="H570" t="n">
         <v>1600</v>
@@ -16928,7 +16928,7 @@
         <v>9.60000038146973</v>
       </c>
       <c r="G571" t="n">
-        <v>8.56505298614502</v>
+        <v>8.5650520324707</v>
       </c>
       <c r="H571" t="n">
         <v>4200</v>
@@ -16957,7 +16957,7 @@
         <v>9.60000038146973</v>
       </c>
       <c r="G572" t="n">
-        <v>8.56505298614502</v>
+        <v>8.5650520324707</v>
       </c>
       <c r="H572" t="n">
         <v>13200</v>
@@ -17305,7 +17305,7 @@
         <v>9.89999961853027</v>
       </c>
       <c r="G584" t="n">
-        <v>8.83271026611328</v>
+        <v>8.83270931243896</v>
       </c>
       <c r="H584" t="n">
         <v>15800</v>
@@ -17450,7 +17450,7 @@
         <v>9.94999980926514</v>
       </c>
       <c r="G589" t="n">
-        <v>8.8773193359375</v>
+        <v>8.87731838226318</v>
       </c>
       <c r="H589" t="n">
         <v>1800</v>
@@ -17479,7 +17479,7 @@
         <v>9.94999980926514</v>
       </c>
       <c r="G590" t="n">
-        <v>8.8773193359375</v>
+        <v>8.87731838226318</v>
       </c>
       <c r="H590" t="n">
         <v>10800</v>
@@ -17508,7 +17508,7 @@
         <v>9.94999980926514</v>
       </c>
       <c r="G591" t="n">
-        <v>8.8773193359375</v>
+        <v>8.87731838226318</v>
       </c>
       <c r="H591" t="n">
         <v>9800</v>
@@ -17537,7 +17537,7 @@
         <v>9.94999980926514</v>
       </c>
       <c r="G592" t="n">
-        <v>8.8773193359375</v>
+        <v>8.87731838226318</v>
       </c>
       <c r="H592" t="n">
         <v>21400</v>
@@ -17566,7 +17566,7 @@
         <v>10</v>
       </c>
       <c r="G593" t="n">
-        <v>8.92192935943604</v>
+        <v>8.92192840576172</v>
       </c>
       <c r="H593" t="n">
         <v>49400</v>
@@ -17595,7 +17595,7 @@
         <v>10</v>
       </c>
       <c r="G594" t="n">
-        <v>8.92192935943604</v>
+        <v>8.92192840576172</v>
       </c>
       <c r="H594" t="n">
         <v>45800</v>
@@ -17624,7 +17624,7 @@
         <v>10</v>
       </c>
       <c r="G595" t="n">
-        <v>8.92192935943604</v>
+        <v>8.92192840576172</v>
       </c>
       <c r="H595" t="n">
         <v>25000</v>
@@ -17682,7 +17682,7 @@
         <v>10.1999998092651</v>
       </c>
       <c r="G597" t="n">
-        <v>9.10036659240723</v>
+        <v>9.10036849975586</v>
       </c>
       <c r="H597" t="n">
         <v>20600</v>
@@ -17711,7 +17711,7 @@
         <v>10.1999998092651</v>
       </c>
       <c r="G598" t="n">
-        <v>9.10036659240723</v>
+        <v>9.10036849975586</v>
       </c>
       <c r="H598" t="n">
         <v>14200</v>
@@ -17769,7 +17769,7 @@
         <v>10.1999998092651</v>
       </c>
       <c r="G600" t="n">
-        <v>9.10036659240723</v>
+        <v>9.10036849975586</v>
       </c>
       <c r="H600" t="n">
         <v>4800</v>
@@ -17856,7 +17856,7 @@
         <v>10.1999998092651</v>
       </c>
       <c r="G603" t="n">
-        <v>9.10036659240723</v>
+        <v>9.10036849975586</v>
       </c>
       <c r="H603" t="n">
         <v>21800</v>
@@ -17914,7 +17914,7 @@
         <v>10.1999998092651</v>
       </c>
       <c r="G605" t="n">
-        <v>9.10036659240723</v>
+        <v>9.10036849975586</v>
       </c>
       <c r="H605" t="n">
         <v>63000</v>
@@ -18001,7 +18001,7 @@
         <v>10.1999998092651</v>
       </c>
       <c r="G608" t="n">
-        <v>9.10036659240723</v>
+        <v>9.10036849975586</v>
       </c>
       <c r="H608" t="n">
         <v>400</v>
@@ -18030,7 +18030,7 @@
         <v>10.1999998092651</v>
       </c>
       <c r="G609" t="n">
-        <v>9.10036659240723</v>
+        <v>9.10036849975586</v>
       </c>
       <c r="H609" t="n">
         <v>5200</v>
@@ -18088,7 +18088,7 @@
         <v>10.1999998092651</v>
       </c>
       <c r="G611" t="n">
-        <v>9.10036659240723</v>
+        <v>9.10036849975586</v>
       </c>
       <c r="H611" t="n">
         <v>22400</v>
@@ -18146,7 +18146,7 @@
         <v>10.1999998092651</v>
       </c>
       <c r="G613" t="n">
-        <v>9.10036659240723</v>
+        <v>9.10036849975586</v>
       </c>
       <c r="H613" t="n">
         <v>50200</v>
@@ -18204,7 +18204,7 @@
         <v>10.3999996185303</v>
       </c>
       <c r="G615" t="n">
-        <v>9.27880764007568</v>
+        <v>9.27880573272705</v>
       </c>
       <c r="H615" t="n">
         <v>14600</v>
@@ -18233,7 +18233,7 @@
         <v>10.3999996185303</v>
       </c>
       <c r="G616" t="n">
-        <v>9.27880764007568</v>
+        <v>9.27880573272705</v>
       </c>
       <c r="H616" t="n">
         <v>13600</v>
@@ -18291,7 +18291,7 @@
         <v>10.5</v>
       </c>
       <c r="G618" t="n">
-        <v>9.3680248260498</v>
+        <v>9.36802673339844</v>
       </c>
       <c r="H618" t="n">
         <v>26400</v>
@@ -18320,7 +18320,7 @@
         <v>10.5</v>
       </c>
       <c r="G619" t="n">
-        <v>9.3680248260498</v>
+        <v>9.36802673339844</v>
       </c>
       <c r="H619" t="n">
         <v>76800</v>
@@ -18436,7 +18436,7 @@
         <v>10.5</v>
       </c>
       <c r="G623" t="n">
-        <v>9.3680248260498</v>
+        <v>9.36802673339844</v>
       </c>
       <c r="H623" t="n">
         <v>39400</v>
@@ -18465,7 +18465,7 @@
         <v>10.3999996185303</v>
       </c>
       <c r="G624" t="n">
-        <v>9.27880764007568</v>
+        <v>9.27880573272705</v>
       </c>
       <c r="H624" t="n">
         <v>6000</v>
@@ -18494,7 +18494,7 @@
         <v>10.3999996185303</v>
       </c>
       <c r="G625" t="n">
-        <v>9.27880764007568</v>
+        <v>9.27880573272705</v>
       </c>
       <c r="H625" t="n">
         <v>3600</v>
@@ -18523,7 +18523,7 @@
         <v>10.5</v>
       </c>
       <c r="G626" t="n">
-        <v>9.3680248260498</v>
+        <v>9.36802673339844</v>
       </c>
       <c r="H626" t="n">
         <v>18800</v>
@@ -18552,7 +18552,7 @@
         <v>10.5</v>
       </c>
       <c r="G627" t="n">
-        <v>9.3680248260498</v>
+        <v>9.36802673339844</v>
       </c>
       <c r="H627" t="n">
         <v>17400</v>
@@ -18581,7 +18581,7 @@
         <v>10.5</v>
       </c>
       <c r="G628" t="n">
-        <v>9.3680248260498</v>
+        <v>9.36802673339844</v>
       </c>
       <c r="H628" t="n">
         <v>5800</v>
@@ -18610,7 +18610,7 @@
         <v>10.5</v>
       </c>
       <c r="G629" t="n">
-        <v>9.3680248260498</v>
+        <v>9.36802673339844</v>
       </c>
       <c r="H629" t="n">
         <v>11400</v>
@@ -18639,7 +18639,7 @@
         <v>10.5</v>
       </c>
       <c r="G630" t="n">
-        <v>9.3680248260498</v>
+        <v>9.36802673339844</v>
       </c>
       <c r="H630" t="n">
         <v>5800</v>
@@ -18668,7 +18668,7 @@
         <v>10.5</v>
       </c>
       <c r="G631" t="n">
-        <v>9.3680248260498</v>
+        <v>9.36802673339844</v>
       </c>
       <c r="H631" t="n">
         <v>2600</v>
@@ -18697,7 +18697,7 @@
         <v>10.3999996185303</v>
       </c>
       <c r="G632" t="n">
-        <v>9.27880764007568</v>
+        <v>9.27880573272705</v>
       </c>
       <c r="H632" t="n">
         <v>4600</v>
@@ -18726,7 +18726,7 @@
         <v>10.5</v>
       </c>
       <c r="G633" t="n">
-        <v>9.3680248260498</v>
+        <v>9.36802673339844</v>
       </c>
       <c r="H633" t="n">
         <v>32552</v>
@@ -18755,7 +18755,7 @@
         <v>10.5</v>
       </c>
       <c r="G634" t="n">
-        <v>9.3680248260498</v>
+        <v>9.36802673339844</v>
       </c>
       <c r="H634" t="n">
         <v>38554</v>
@@ -18784,7 +18784,7 @@
         <v>10.3999996185303</v>
       </c>
       <c r="G635" t="n">
-        <v>9.27880764007568</v>
+        <v>9.27880573272705</v>
       </c>
       <c r="H635" t="n">
         <v>26940</v>
@@ -18813,7 +18813,7 @@
         <v>10.5</v>
       </c>
       <c r="G636" t="n">
-        <v>9.3680248260498</v>
+        <v>9.36802673339844</v>
       </c>
       <c r="H636" t="n">
         <v>4300</v>
@@ -18842,7 +18842,7 @@
         <v>10.5</v>
       </c>
       <c r="G637" t="n">
-        <v>9.3680248260498</v>
+        <v>9.36802673339844</v>
       </c>
       <c r="H637" t="n">
         <v>18422</v>
@@ -18871,7 +18871,7 @@
         <v>10.3999996185303</v>
       </c>
       <c r="G638" t="n">
-        <v>9.27880764007568</v>
+        <v>9.27880573272705</v>
       </c>
       <c r="H638" t="n">
         <v>20479</v>
@@ -18900,7 +18900,7 @@
         <v>10.5</v>
       </c>
       <c r="G639" t="n">
-        <v>9.3680248260498</v>
+        <v>9.36802673339844</v>
       </c>
       <c r="H639" t="n">
         <v>14946</v>
@@ -18929,7 +18929,7 @@
         <v>10.3999996185303</v>
       </c>
       <c r="G640" t="n">
-        <v>9.27880764007568</v>
+        <v>9.27880573272705</v>
       </c>
       <c r="H640" t="n">
         <v>20526</v>
@@ -18958,7 +18958,7 @@
         <v>10.3999996185303</v>
       </c>
       <c r="G641" t="n">
-        <v>9.27880764007568</v>
+        <v>9.27880573272705</v>
       </c>
       <c r="H641" t="n">
         <v>16273</v>
@@ -18987,7 +18987,7 @@
         <v>10.3999996185303</v>
       </c>
       <c r="G642" t="n">
-        <v>9.27880764007568</v>
+        <v>9.27880573272705</v>
       </c>
       <c r="H642" t="n">
         <v>24392</v>
@@ -19045,7 +19045,7 @@
         <v>10.3999996185303</v>
       </c>
       <c r="G644" t="n">
-        <v>9.36977672576904</v>
+        <v>9.36977577209473</v>
       </c>
       <c r="H644" t="n">
         <v>9716</v>
@@ -19132,7 +19132,7 @@
         <v>10.3000001907349</v>
       </c>
       <c r="G647" t="n">
-        <v>9.27968120574951</v>
+        <v>9.2796802520752</v>
       </c>
       <c r="H647" t="n">
         <v>5125</v>
@@ -19857,7 +19857,7 @@
         <v>9.89999961853027</v>
       </c>
       <c r="G672" t="n">
-        <v>8.91930484771729</v>
+        <v>8.91930389404297</v>
       </c>
       <c r="H672" t="n">
         <v>2834</v>
@@ -19915,7 +19915,7 @@
         <v>9.80000019073486</v>
       </c>
       <c r="G674" t="n">
-        <v>8.8292121887207</v>
+        <v>8.82921123504639</v>
       </c>
       <c r="H674" t="n">
         <v>41176</v>
@@ -20118,7 +20118,7 @@
         <v>9.89999961853027</v>
       </c>
       <c r="G681" t="n">
-        <v>8.91930484771729</v>
+        <v>8.91930389404297</v>
       </c>
       <c r="H681" t="n">
         <v>17800</v>
@@ -20234,7 +20234,7 @@
         <v>9.89999961853027</v>
       </c>
       <c r="G685" t="n">
-        <v>8.91930484771729</v>
+        <v>8.91930389404297</v>
       </c>
       <c r="H685" t="n">
         <v>1637</v>
@@ -20263,7 +20263,7 @@
         <v>10.3000001907349</v>
       </c>
       <c r="G686" t="n">
-        <v>9.27968120574951</v>
+        <v>9.2796802520752</v>
       </c>
       <c r="H686" t="n">
         <v>6745</v>
@@ -20321,7 +20321,7 @@
         <v>10.3000001907349</v>
       </c>
       <c r="G688" t="n">
-        <v>9.27968120574951</v>
+        <v>9.2796802520752</v>
       </c>
       <c r="H688" t="n">
         <v>19506</v>
@@ -20350,7 +20350,7 @@
         <v>10.3000001907349</v>
       </c>
       <c r="G689" t="n">
-        <v>9.27968120574951</v>
+        <v>9.2796802520752</v>
       </c>
       <c r="H689" t="n">
         <v>601</v>
@@ -20756,7 +20756,7 @@
         <v>9.89999961853027</v>
       </c>
       <c r="G703" t="n">
-        <v>8.91930484771729</v>
+        <v>8.91930389404297</v>
       </c>
       <c r="H703" t="n">
         <v>35</v>
@@ -21220,7 +21220,7 @@
         <v>9.89999961853027</v>
       </c>
       <c r="G719" t="n">
-        <v>8.91930484771729</v>
+        <v>8.91930389404297</v>
       </c>
       <c r="H719" t="n">
         <v>200</v>
@@ -21249,7 +21249,7 @@
         <v>9.89999961853027</v>
       </c>
       <c r="G720" t="n">
-        <v>8.91930484771729</v>
+        <v>8.91930389404297</v>
       </c>
       <c r="H720" t="n">
         <v>0</v>
@@ -21887,7 +21887,7 @@
         <v>10.3000001907349</v>
       </c>
       <c r="G742" t="n">
-        <v>9.27968120574951</v>
+        <v>9.2796802520752</v>
       </c>
       <c r="H742" t="n">
         <v>17701</v>
@@ -21916,7 +21916,7 @@
         <v>10.3999996185303</v>
       </c>
       <c r="G743" t="n">
-        <v>9.36977672576904</v>
+        <v>9.36977577209473</v>
       </c>
       <c r="H743" t="n">
         <v>5001</v>
@@ -22206,7 +22206,7 @@
         <v>10.3000001907349</v>
       </c>
       <c r="G753" t="n">
-        <v>9.27968120574951</v>
+        <v>9.2796802520752</v>
       </c>
       <c r="H753" t="n">
         <v>8871</v>
@@ -22235,7 +22235,7 @@
         <v>10.3999996185303</v>
       </c>
       <c r="G754" t="n">
-        <v>9.36977672576904</v>
+        <v>9.36977577209473</v>
       </c>
       <c r="H754" t="n">
         <v>3043</v>
@@ -22264,7 +22264,7 @@
         <v>10.5</v>
       </c>
       <c r="G755" t="n">
-        <v>9.45986843109131</v>
+        <v>9.45987033843994</v>
       </c>
       <c r="H755" t="n">
         <v>109777</v>
@@ -23221,7 +23221,7 @@
         <v>11.1000003814697</v>
       </c>
       <c r="G788" t="n">
-        <v>10.0004348754883</v>
+        <v>10.0004320144653</v>
       </c>
       <c r="H788" t="n">
         <v>19242</v>
@@ -23453,7 +23453,7 @@
         <v>11.5</v>
       </c>
       <c r="G796" t="n">
-        <v>10.3608102798462</v>
+        <v>10.3608093261719</v>
       </c>
       <c r="H796" t="n">
         <v>50499</v>
@@ -23511,7 +23511,7 @@
         <v>11.5</v>
       </c>
       <c r="G798" t="n">
-        <v>10.3608102798462</v>
+        <v>10.3608093261719</v>
       </c>
       <c r="H798" t="n">
         <v>57131</v>
@@ -23569,7 +23569,7 @@
         <v>11.8000001907349</v>
       </c>
       <c r="G800" t="n">
-        <v>10.6310920715332</v>
+        <v>10.6310911178589</v>
       </c>
       <c r="H800" t="n">
         <v>49722</v>
@@ -23598,7 +23598,7 @@
         <v>11.6999998092651</v>
       </c>
       <c r="G801" t="n">
-        <v>10.540997505188</v>
+        <v>10.5409965515137</v>
       </c>
       <c r="H801" t="n">
         <v>69604</v>
@@ -23627,7 +23627,7 @@
         <v>11.8000001907349</v>
       </c>
       <c r="G802" t="n">
-        <v>10.6310920715332</v>
+        <v>10.6310911178589</v>
       </c>
       <c r="H802" t="n">
         <v>46365</v>
@@ -23656,7 +23656,7 @@
         <v>11.8000001907349</v>
       </c>
       <c r="G803" t="n">
-        <v>10.6310920715332</v>
+        <v>10.6310911178589</v>
       </c>
       <c r="H803" t="n">
         <v>22026</v>
@@ -23685,7 +23685,7 @@
         <v>11.8000001907349</v>
       </c>
       <c r="G804" t="n">
-        <v>10.6310920715332</v>
+        <v>10.6310911178589</v>
       </c>
       <c r="H804" t="n">
         <v>22008</v>
@@ -23714,7 +23714,7 @@
         <v>11.8999996185303</v>
       </c>
       <c r="G805" t="n">
-        <v>10.7211847305298</v>
+        <v>10.7211837768555</v>
       </c>
       <c r="H805" t="n">
         <v>30450</v>
@@ -23743,7 +23743,7 @@
         <v>11.8000001907349</v>
       </c>
       <c r="G806" t="n">
-        <v>10.6310920715332</v>
+        <v>10.6310911178589</v>
       </c>
       <c r="H806" t="n">
         <v>10733</v>
@@ -23772,7 +23772,7 @@
         <v>11.8999996185303</v>
       </c>
       <c r="G807" t="n">
-        <v>10.7211847305298</v>
+        <v>10.7211837768555</v>
       </c>
       <c r="H807" t="n">
         <v>59524</v>
@@ -23801,7 +23801,7 @@
         <v>11.8999996185303</v>
       </c>
       <c r="G808" t="n">
-        <v>10.7211847305298</v>
+        <v>10.7211837768555</v>
       </c>
       <c r="H808" t="n">
         <v>896</v>
@@ -23830,7 +23830,7 @@
         <v>11.6999998092651</v>
       </c>
       <c r="G809" t="n">
-        <v>10.540997505188</v>
+        <v>10.5409965515137</v>
       </c>
       <c r="H809" t="n">
         <v>7445</v>
@@ -24236,7 +24236,7 @@
         <v>12.3000001907349</v>
       </c>
       <c r="G823" t="n">
-        <v>11.0815620422363</v>
+        <v>11.081561088562</v>
       </c>
       <c r="H823" t="n">
         <v>13559</v>
@@ -24294,7 +24294,7 @@
         <v>12.3000001907349</v>
       </c>
       <c r="G825" t="n">
-        <v>11.0815620422363</v>
+        <v>11.081561088562</v>
       </c>
       <c r="H825" t="n">
         <v>56143</v>
@@ -24410,7 +24410,7 @@
         <v>12.3000001907349</v>
       </c>
       <c r="G829" t="n">
-        <v>11.0815620422363</v>
+        <v>11.081561088562</v>
       </c>
       <c r="H829" t="n">
         <v>13811</v>
@@ -24468,7 +24468,7 @@
         <v>12.3000001907349</v>
       </c>
       <c r="G831" t="n">
-        <v>11.0815620422363</v>
+        <v>11.081561088562</v>
       </c>
       <c r="H831" t="n">
         <v>4605</v>
@@ -24613,7 +24613,7 @@
         <v>12.3000001907349</v>
       </c>
       <c r="G836" t="n">
-        <v>11.0815620422363</v>
+        <v>11.081561088562</v>
       </c>
       <c r="H836" t="n">
         <v>4238</v>
@@ -24671,7 +24671,7 @@
         <v>12.3000001907349</v>
       </c>
       <c r="G838" t="n">
-        <v>11.0815620422363</v>
+        <v>11.081561088562</v>
       </c>
       <c r="H838" t="n">
         <v>9765</v>
@@ -24729,7 +24729,7 @@
         <v>12.3000001907349</v>
       </c>
       <c r="G840" t="n">
-        <v>11.0815620422363</v>
+        <v>11.081561088562</v>
       </c>
       <c r="H840" t="n">
         <v>23765</v>
@@ -24758,7 +24758,7 @@
         <v>12.3999996185303</v>
       </c>
       <c r="G841" t="n">
-        <v>11.1716556549072</v>
+        <v>11.1716547012329</v>
       </c>
       <c r="H841" t="n">
         <v>40850</v>
@@ -24787,7 +24787,7 @@
         <v>12.3000001907349</v>
       </c>
       <c r="G842" t="n">
-        <v>11.0815620422363</v>
+        <v>11.081561088562</v>
       </c>
       <c r="H842" t="n">
         <v>14735</v>
@@ -24816,7 +24816,7 @@
         <v>12.3000001907349</v>
       </c>
       <c r="G843" t="n">
-        <v>11.0815620422363</v>
+        <v>11.081561088562</v>
       </c>
       <c r="H843" t="n">
         <v>23374</v>
@@ -24845,7 +24845,7 @@
         <v>12.3000001907349</v>
       </c>
       <c r="G844" t="n">
-        <v>11.0815620422363</v>
+        <v>11.081561088562</v>
       </c>
       <c r="H844" t="n">
         <v>1714</v>
@@ -24990,7 +24990,7 @@
         <v>11.8999996185303</v>
       </c>
       <c r="G849" t="n">
-        <v>10.7211847305298</v>
+        <v>10.7211837768555</v>
       </c>
       <c r="H849" t="n">
         <v>33307</v>
@@ -25019,7 +25019,7 @@
         <v>11.8000001907349</v>
       </c>
       <c r="G850" t="n">
-        <v>10.6310920715332</v>
+        <v>10.6310911178589</v>
       </c>
       <c r="H850" t="n">
         <v>111180</v>
@@ -25048,7 +25048,7 @@
         <v>11.8000001907349</v>
       </c>
       <c r="G851" t="n">
-        <v>10.6310920715332</v>
+        <v>10.6310911178589</v>
       </c>
       <c r="H851" t="n">
         <v>21012</v>
@@ -25106,7 +25106,7 @@
         <v>11.5</v>
       </c>
       <c r="G853" t="n">
-        <v>10.3608102798462</v>
+        <v>10.3608093261719</v>
       </c>
       <c r="H853" t="n">
         <v>19258</v>
@@ -25164,7 +25164,7 @@
         <v>11.3999996185303</v>
       </c>
       <c r="G855" t="n">
-        <v>10.2707147598267</v>
+        <v>10.270715713501</v>
       </c>
       <c r="H855" t="n">
         <v>6144</v>
@@ -25222,7 +25222,7 @@
         <v>11.1000003814697</v>
       </c>
       <c r="G857" t="n">
-        <v>10.0004348754883</v>
+        <v>10.0004320144653</v>
       </c>
       <c r="H857" t="n">
         <v>18055</v>
@@ -25367,7 +25367,7 @@
         <v>9.60000038146973</v>
       </c>
       <c r="G862" t="n">
-        <v>8.64902400970459</v>
+        <v>8.64902305603027</v>
       </c>
       <c r="H862" t="n">
         <v>13499</v>
@@ -25425,7 +25425,7 @@
         <v>9</v>
       </c>
       <c r="G864" t="n">
-        <v>8.10846042633057</v>
+        <v>8.10845947265625</v>
       </c>
       <c r="H864" t="n">
         <v>14181</v>
@@ -25454,7 +25454,7 @@
         <v>9</v>
       </c>
       <c r="G865" t="n">
-        <v>8.10846042633057</v>
+        <v>8.10845947265625</v>
       </c>
       <c r="H865" t="n">
         <v>19428</v>
@@ -25570,7 +25570,7 @@
         <v>9.89999961853027</v>
       </c>
       <c r="G869" t="n">
-        <v>8.91930484771729</v>
+        <v>8.91930389404297</v>
       </c>
       <c r="H869" t="n">
         <v>1924</v>
@@ -25628,7 +25628,7 @@
         <v>10.5</v>
       </c>
       <c r="G871" t="n">
-        <v>9.45986843109131</v>
+        <v>9.45987033843994</v>
       </c>
       <c r="H871" t="n">
         <v>4639</v>
@@ -25686,7 +25686,7 @@
         <v>10.3000001907349</v>
       </c>
       <c r="G873" t="n">
-        <v>9.27968120574951</v>
+        <v>9.2796802520752</v>
       </c>
       <c r="H873" t="n">
         <v>2220</v>
@@ -25802,7 +25802,7 @@
         <v>10.0500001907349</v>
       </c>
       <c r="G877" t="n">
-        <v>9.05444622039795</v>
+        <v>9.05444717407227</v>
       </c>
       <c r="H877" t="n">
         <v>11800</v>
@@ -25831,7 +25831,7 @@
         <v>10.1499996185303</v>
       </c>
       <c r="G878" t="n">
-        <v>9.14454078674316</v>
+        <v>9.14453983306885</v>
       </c>
       <c r="H878" t="n">
         <v>1300</v>
@@ -25918,7 +25918,7 @@
         <v>10.3000001907349</v>
       </c>
       <c r="G881" t="n">
-        <v>9.27968120574951</v>
+        <v>9.2796802520752</v>
       </c>
       <c r="H881" t="n">
         <v>18487</v>
@@ -25976,7 +25976,7 @@
         <v>10.5</v>
       </c>
       <c r="G883" t="n">
-        <v>9.45986843109131</v>
+        <v>9.45987033843994</v>
       </c>
       <c r="H883" t="n">
         <v>18374</v>
@@ -26034,7 +26034,7 @@
         <v>10.6499996185303</v>
       </c>
       <c r="G885" t="n">
-        <v>9.59500980377197</v>
+        <v>9.59501075744629</v>
       </c>
       <c r="H885" t="n">
         <v>676</v>
@@ -26150,7 +26150,7 @@
         <v>10.5500001907349</v>
       </c>
       <c r="G889" t="n">
-        <v>9.50491619110107</v>
+        <v>9.50491714477539</v>
       </c>
       <c r="H889" t="n">
         <v>1500</v>
@@ -26295,7 +26295,7 @@
         <v>10.6499996185303</v>
       </c>
       <c r="G894" t="n">
-        <v>9.59500980377197</v>
+        <v>9.59501075744629</v>
       </c>
       <c r="H894" t="n">
         <v>19250</v>
@@ -26382,7 +26382,7 @@
         <v>10.9499998092651</v>
       </c>
       <c r="G897" t="n">
-        <v>9.8652925491333</v>
+        <v>9.86529159545898</v>
       </c>
       <c r="H897" t="n">
         <v>3575</v>
@@ -26440,7 +26440,7 @@
         <v>10.5</v>
       </c>
       <c r="G899" t="n">
-        <v>9.45986843109131</v>
+        <v>9.45987033843994</v>
       </c>
       <c r="H899" t="n">
         <v>2580</v>
@@ -26498,7 +26498,7 @@
         <v>10.6000003814697</v>
       </c>
       <c r="G901" t="n">
-        <v>9.65828132629395</v>
+        <v>9.65828037261963</v>
       </c>
       <c r="H901" t="n">
         <v>2022</v>
@@ -26556,7 +26556,7 @@
         <v>10.3500003814697</v>
       </c>
       <c r="G903" t="n">
-        <v>9.43049049377441</v>
+        <v>9.43049144744873</v>
       </c>
       <c r="H903" t="n">
         <v>36431</v>
@@ -26585,7 +26585,7 @@
         <v>10.75</v>
       </c>
       <c r="G904" t="n">
-        <v>9.79495525360107</v>
+        <v>9.79495429992676</v>
       </c>
       <c r="H904" t="n">
         <v>758</v>
@@ -26643,7 +26643,7 @@
         <v>10.6000003814697</v>
       </c>
       <c r="G906" t="n">
-        <v>9.65828132629395</v>
+        <v>9.65828037261963</v>
       </c>
       <c r="H906" t="n">
         <v>360</v>
@@ -26672,7 +26672,7 @@
         <v>10.3000001907349</v>
       </c>
       <c r="G907" t="n">
-        <v>9.38493251800537</v>
+        <v>9.38493347167969</v>
       </c>
       <c r="H907" t="n">
         <v>1834</v>
@@ -26701,7 +26701,7 @@
         <v>10.8000001907349</v>
       </c>
       <c r="G908" t="n">
-        <v>9.84051322937012</v>
+        <v>9.8405122756958</v>
       </c>
       <c r="H908" t="n">
         <v>4550</v>
@@ -26730,7 +26730,7 @@
         <v>10.8000001907349</v>
       </c>
       <c r="G909" t="n">
-        <v>9.84051322937012</v>
+        <v>9.8405122756958</v>
       </c>
       <c r="H909" t="n">
         <v>238</v>
@@ -26759,7 +26759,7 @@
         <v>10.8000001907349</v>
       </c>
       <c r="G910" t="n">
-        <v>9.84051322937012</v>
+        <v>9.8405122756958</v>
       </c>
       <c r="H910" t="n">
         <v>2050</v>
@@ -26788,7 +26788,7 @@
         <v>10.8999996185303</v>
       </c>
       <c r="G911" t="n">
-        <v>9.93162727355957</v>
+        <v>9.93162822723389</v>
       </c>
       <c r="H911" t="n">
         <v>2924</v>
@@ -26817,7 +26817,7 @@
         <v>10.8999996185303</v>
       </c>
       <c r="G912" t="n">
-        <v>9.93162727355957</v>
+        <v>9.93162822723389</v>
       </c>
       <c r="H912" t="n">
         <v>1808</v>
@@ -26846,7 +26846,7 @@
         <v>10.8999996185303</v>
       </c>
       <c r="G913" t="n">
-        <v>9.93162727355957</v>
+        <v>9.93162822723389</v>
       </c>
       <c r="H913" t="n">
         <v>4730</v>
@@ -26875,7 +26875,7 @@
         <v>10.9499998092651</v>
       </c>
       <c r="G914" t="n">
-        <v>9.97718620300293</v>
+        <v>9.97718715667725</v>
       </c>
       <c r="H914" t="n">
         <v>11302</v>
@@ -26904,7 +26904,7 @@
         <v>10.8999996185303</v>
       </c>
       <c r="G915" t="n">
-        <v>9.93162727355957</v>
+        <v>9.93162822723389</v>
       </c>
       <c r="H915" t="n">
         <v>706</v>
@@ -26933,7 +26933,7 @@
         <v>10.9499998092651</v>
       </c>
       <c r="G916" t="n">
-        <v>9.97718620300293</v>
+        <v>9.97718715667725</v>
       </c>
       <c r="H916" t="n">
         <v>143</v>
@@ -26991,7 +26991,7 @@
         <v>10.8999996185303</v>
       </c>
       <c r="G918" t="n">
-        <v>9.93162727355957</v>
+        <v>9.93162822723389</v>
       </c>
       <c r="H918" t="n">
         <v>7283</v>
@@ -27020,7 +27020,7 @@
         <v>10.8000001907349</v>
       </c>
       <c r="G919" t="n">
-        <v>9.84051322937012</v>
+        <v>9.8405122756958</v>
       </c>
       <c r="H919" t="n">
         <v>899</v>
@@ -27107,7 +27107,7 @@
         <v>10.75</v>
       </c>
       <c r="G922" t="n">
-        <v>9.79495525360107</v>
+        <v>9.79495429992676</v>
       </c>
       <c r="H922" t="n">
         <v>33283</v>
@@ -27136,7 +27136,7 @@
         <v>10.75</v>
       </c>
       <c r="G923" t="n">
-        <v>9.79495525360107</v>
+        <v>9.79495429992676</v>
       </c>
       <c r="H923" t="n">
         <v>26805</v>
@@ -27223,7 +27223,7 @@
         <v>10.75</v>
       </c>
       <c r="G926" t="n">
-        <v>9.79495525360107</v>
+        <v>9.79495429992676</v>
       </c>
       <c r="H926" t="n">
         <v>2330</v>
@@ -27281,7 +27281,7 @@
         <v>10.9499998092651</v>
       </c>
       <c r="G928" t="n">
-        <v>9.97718620300293</v>
+        <v>9.97718715667725</v>
       </c>
       <c r="H928" t="n">
         <v>502</v>
@@ -27310,7 +27310,7 @@
         <v>10.9499998092651</v>
       </c>
       <c r="G929" t="n">
-        <v>9.97718620300293</v>
+        <v>9.97718715667725</v>
       </c>
       <c r="H929" t="n">
         <v>1290</v>
@@ -27368,7 +27368,7 @@
         <v>10.8999996185303</v>
       </c>
       <c r="G931" t="n">
-        <v>9.93162727355957</v>
+        <v>9.93162822723389</v>
       </c>
       <c r="H931" t="n">
         <v>8316</v>
@@ -27397,7 +27397,7 @@
         <v>10.8999996185303</v>
       </c>
       <c r="G932" t="n">
-        <v>9.93162727355957</v>
+        <v>9.93162822723389</v>
       </c>
       <c r="H932" t="n">
         <v>4203</v>
@@ -27426,7 +27426,7 @@
         <v>10.8999996185303</v>
       </c>
       <c r="G933" t="n">
-        <v>9.93162727355957</v>
+        <v>9.93162822723389</v>
       </c>
       <c r="H933" t="n">
         <v>1219</v>
@@ -27455,7 +27455,7 @@
         <v>10.8999996185303</v>
       </c>
       <c r="G934" t="n">
-        <v>9.93162727355957</v>
+        <v>9.93162822723389</v>
       </c>
       <c r="H934" t="n">
         <v>5600</v>
@@ -27484,7 +27484,7 @@
         <v>10.8999996185303</v>
       </c>
       <c r="G935" t="n">
-        <v>9.93162727355957</v>
+        <v>9.93162822723389</v>
       </c>
       <c r="H935" t="n">
         <v>3105</v>
@@ -27513,7 +27513,7 @@
         <v>10.8999996185303</v>
       </c>
       <c r="G936" t="n">
-        <v>9.93162727355957</v>
+        <v>9.93162822723389</v>
       </c>
       <c r="H936" t="n">
         <v>0</v>
@@ -27542,7 +27542,7 @@
         <v>10.8999996185303</v>
       </c>
       <c r="G937" t="n">
-        <v>9.93162727355957</v>
+        <v>9.93162822723389</v>
       </c>
       <c r="H937" t="n">
         <v>47</v>
@@ -27571,7 +27571,7 @@
         <v>10.8000001907349</v>
       </c>
       <c r="G938" t="n">
-        <v>9.84051322937012</v>
+        <v>9.8405122756958</v>
       </c>
       <c r="H938" t="n">
         <v>1861</v>
@@ -27600,7 +27600,7 @@
         <v>10.8000001907349</v>
       </c>
       <c r="G939" t="n">
-        <v>9.84051322937012</v>
+        <v>9.8405122756958</v>
       </c>
       <c r="H939" t="n">
         <v>472</v>
@@ -27629,7 +27629,7 @@
         <v>10.8000001907349</v>
       </c>
       <c r="G940" t="n">
-        <v>9.84051322937012</v>
+        <v>9.8405122756958</v>
       </c>
       <c r="H940" t="n">
         <v>357</v>
@@ -27687,7 +27687,7 @@
         <v>10.6000003814697</v>
       </c>
       <c r="G942" t="n">
-        <v>9.65828132629395</v>
+        <v>9.65828037261963</v>
       </c>
       <c r="H942" t="n">
         <v>311</v>
@@ -27745,7 +27745,7 @@
         <v>10.6000003814697</v>
       </c>
       <c r="G944" t="n">
-        <v>9.65828132629395</v>
+        <v>9.65828037261963</v>
       </c>
       <c r="H944" t="n">
         <v>869</v>
@@ -27803,7 +27803,7 @@
         <v>10.8000001907349</v>
       </c>
       <c r="G946" t="n">
-        <v>9.84051322937012</v>
+        <v>9.8405122756958</v>
       </c>
       <c r="H946" t="n">
         <v>5337</v>
@@ -27832,7 +27832,7 @@
         <v>10.9499998092651</v>
       </c>
       <c r="G947" t="n">
-        <v>9.97718620300293</v>
+        <v>9.97718715667725</v>
       </c>
       <c r="H947" t="n">
         <v>59288</v>
@@ -27861,7 +27861,7 @@
         <v>10.8999996185303</v>
       </c>
       <c r="G948" t="n">
-        <v>9.93162727355957</v>
+        <v>9.93162822723389</v>
       </c>
       <c r="H948" t="n">
         <v>28960</v>
@@ -27919,7 +27919,7 @@
         <v>11.1000003814697</v>
       </c>
       <c r="G950" t="n">
-        <v>10.1138610839844</v>
+        <v>10.1138601303101</v>
       </c>
       <c r="H950" t="n">
         <v>83822</v>
@@ -27948,7 +27948,7 @@
         <v>11.1000003814697</v>
       </c>
       <c r="G951" t="n">
-        <v>10.1138610839844</v>
+        <v>10.1138601303101</v>
       </c>
       <c r="H951" t="n">
         <v>3488</v>
@@ -27977,7 +27977,7 @@
         <v>11.3000001907349</v>
       </c>
       <c r="G952" t="n">
-        <v>10.2960920333862</v>
+        <v>10.2960910797119</v>
       </c>
       <c r="H952" t="n">
         <v>38245</v>
@@ -28006,7 +28006,7 @@
         <v>11.0500001907349</v>
       </c>
       <c r="G953" t="n">
-        <v>10.068302154541</v>
+        <v>10.0683031082153</v>
       </c>
       <c r="H953" t="n">
         <v>31606</v>
@@ -28064,7 +28064,7 @@
         <v>11.1000003814697</v>
       </c>
       <c r="G955" t="n">
-        <v>10.1138610839844</v>
+        <v>10.1138601303101</v>
       </c>
       <c r="H955" t="n">
         <v>238</v>
@@ -28093,7 +28093,7 @@
         <v>11.0500001907349</v>
       </c>
       <c r="G956" t="n">
-        <v>10.068302154541</v>
+        <v>10.0683031082153</v>
       </c>
       <c r="H956" t="n">
         <v>282</v>
@@ -28122,7 +28122,7 @@
         <v>11.1000003814697</v>
       </c>
       <c r="G957" t="n">
-        <v>10.1138610839844</v>
+        <v>10.1138601303101</v>
       </c>
       <c r="H957" t="n">
         <v>232</v>
@@ -28151,7 +28151,7 @@
         <v>11.1000003814697</v>
       </c>
       <c r="G958" t="n">
-        <v>10.1138610839844</v>
+        <v>10.1138601303101</v>
       </c>
       <c r="H958" t="n">
         <v>1489</v>
@@ -28209,7 +28209,7 @@
         <v>11.1000003814697</v>
       </c>
       <c r="G960" t="n">
-        <v>10.1138610839844</v>
+        <v>10.1138601303101</v>
       </c>
       <c r="H960" t="n">
         <v>1582</v>
@@ -28267,7 +28267,7 @@
         <v>11.1000003814697</v>
       </c>
       <c r="G962" t="n">
-        <v>10.1138610839844</v>
+        <v>10.1138601303101</v>
       </c>
       <c r="H962" t="n">
         <v>6803</v>
@@ -28412,7 +28412,7 @@
         <v>11.1000003814697</v>
       </c>
       <c r="G967" t="n">
-        <v>10.1138610839844</v>
+        <v>10.1138601303101</v>
       </c>
       <c r="H967" t="n">
         <v>4985</v>
@@ -28441,7 +28441,7 @@
         <v>11.1000003814697</v>
       </c>
       <c r="G968" t="n">
-        <v>10.1138610839844</v>
+        <v>10.1138601303101</v>
       </c>
       <c r="H968" t="n">
         <v>921</v>
@@ -28615,7 +28615,7 @@
         <v>10.9499998092651</v>
       </c>
       <c r="G974" t="n">
-        <v>9.97718620300293</v>
+        <v>9.97718715667725</v>
       </c>
       <c r="H974" t="n">
         <v>900</v>
@@ -28673,7 +28673,7 @@
         <v>11.1000003814697</v>
       </c>
       <c r="G976" t="n">
-        <v>10.1138610839844</v>
+        <v>10.1138601303101</v>
       </c>
       <c r="H976" t="n">
         <v>1510</v>
@@ -28702,7 +28702,7 @@
         <v>11.1000003814697</v>
       </c>
       <c r="G977" t="n">
-        <v>10.1138610839844</v>
+        <v>10.1138601303101</v>
       </c>
       <c r="H977" t="n">
         <v>479</v>
@@ -28731,7 +28731,7 @@
         <v>11.1000003814697</v>
       </c>
       <c r="G978" t="n">
-        <v>10.1138610839844</v>
+        <v>10.1138601303101</v>
       </c>
       <c r="H978" t="n">
         <v>365</v>
@@ -28847,7 +28847,7 @@
         <v>10.9499998092651</v>
       </c>
       <c r="G982" t="n">
-        <v>9.97718620300293</v>
+        <v>9.97718715667725</v>
       </c>
       <c r="H982" t="n">
         <v>4050</v>
@@ -28876,7 +28876,7 @@
         <v>10.9499998092651</v>
       </c>
       <c r="G983" t="n">
-        <v>9.97718620300293</v>
+        <v>9.97718715667725</v>
       </c>
       <c r="H983" t="n">
         <v>2157</v>
@@ -28905,7 +28905,7 @@
         <v>10.9499998092651</v>
       </c>
       <c r="G984" t="n">
-        <v>9.97718620300293</v>
+        <v>9.97718715667725</v>
       </c>
       <c r="H984" t="n">
         <v>0</v>
@@ -28934,7 +28934,7 @@
         <v>10.9499998092651</v>
       </c>
       <c r="G985" t="n">
-        <v>9.97718620300293</v>
+        <v>9.97718715667725</v>
       </c>
       <c r="H985" t="n">
         <v>3713</v>
@@ -28963,7 +28963,7 @@
         <v>10.8999996185303</v>
       </c>
       <c r="G986" t="n">
-        <v>9.93162727355957</v>
+        <v>9.93162822723389</v>
       </c>
       <c r="H986" t="n">
         <v>350</v>
@@ -28992,7 +28992,7 @@
         <v>10.8999996185303</v>
       </c>
       <c r="G987" t="n">
-        <v>9.93162727355957</v>
+        <v>9.93162822723389</v>
       </c>
       <c r="H987" t="n">
         <v>293</v>
@@ -29021,7 +29021,7 @@
         <v>10.8999996185303</v>
       </c>
       <c r="G988" t="n">
-        <v>9.93162727355957</v>
+        <v>9.93162822723389</v>
       </c>
       <c r="H988" t="n">
         <v>2158</v>
@@ -29050,7 +29050,7 @@
         <v>10.8000001907349</v>
       </c>
       <c r="G989" t="n">
-        <v>9.84051322937012</v>
+        <v>9.8405122756958</v>
       </c>
       <c r="H989" t="n">
         <v>2879</v>
@@ -29137,7 +29137,7 @@
         <v>10.8000001907349</v>
       </c>
       <c r="G992" t="n">
-        <v>9.84051322937012</v>
+        <v>9.8405122756958</v>
       </c>
       <c r="H992" t="n">
         <v>1802</v>
@@ -29253,7 +29253,7 @@
         <v>10.4499998092651</v>
       </c>
       <c r="G996" t="n">
-        <v>9.52160739898682</v>
+        <v>9.52160835266113</v>
       </c>
       <c r="H996" t="n">
         <v>1795</v>
@@ -29311,7 +29311,7 @@
         <v>10.6000003814697</v>
       </c>
       <c r="G998" t="n">
-        <v>9.65828132629395</v>
+        <v>9.65828037261963</v>
       </c>
       <c r="H998" t="n">
         <v>6553</v>
@@ -29340,7 +29340,7 @@
         <v>10.6000003814697</v>
       </c>
       <c r="G999" t="n">
-        <v>9.65828132629395</v>
+        <v>9.65828037261963</v>
       </c>
       <c r="H999" t="n">
         <v>134</v>
@@ -29427,7 +29427,7 @@
         <v>10.4499998092651</v>
       </c>
       <c r="G1002" t="n">
-        <v>9.52160739898682</v>
+        <v>9.52160835266113</v>
       </c>
       <c r="H1002" t="n">
         <v>5462</v>
@@ -29456,7 +29456,7 @@
         <v>10.6000003814697</v>
       </c>
       <c r="G1003" t="n">
-        <v>9.65828132629395</v>
+        <v>9.65828037261963</v>
       </c>
       <c r="H1003" t="n">
         <v>5015</v>
@@ -29485,7 +29485,7 @@
         <v>10.3999996185303</v>
       </c>
       <c r="G1004" t="n">
-        <v>9.47604846954346</v>
+        <v>9.47604942321777</v>
       </c>
       <c r="H1004" t="n">
         <v>1509</v>
@@ -29543,7 +29543,7 @@
         <v>10.3500003814697</v>
       </c>
       <c r="G1006" t="n">
-        <v>9.43049049377441</v>
+        <v>9.43049144744873</v>
       </c>
       <c r="H1006" t="n">
         <v>3628</v>
@@ -29572,7 +29572,7 @@
         <v>10.0500001907349</v>
       </c>
       <c r="G1007" t="n">
-        <v>9.15714359283447</v>
+        <v>9.15714263916016</v>
       </c>
       <c r="H1007" t="n">
         <v>29748</v>
@@ -29601,7 +29601,7 @@
         <v>9.96000003814697</v>
       </c>
       <c r="G1008" t="n">
-        <v>9.07513999938965</v>
+        <v>9.07513904571533</v>
       </c>
       <c r="H1008" t="n">
         <v>250</v>
@@ -29688,7 +29688,7 @@
         <v>10</v>
       </c>
       <c r="G1011" t="n">
-        <v>9.11158657073975</v>
+        <v>9.11158561706543</v>
       </c>
       <c r="H1011" t="n">
         <v>42205</v>
@@ -29746,7 +29746,7 @@
         <v>10</v>
       </c>
       <c r="G1013" t="n">
-        <v>9.11158657073975</v>
+        <v>9.11158561706543</v>
       </c>
       <c r="H1013" t="n">
         <v>40699</v>
@@ -29775,7 +29775,7 @@
         <v>9.9399995803833</v>
       </c>
       <c r="G1014" t="n">
-        <v>9.05691528320312</v>
+        <v>9.05691623687744</v>
       </c>
       <c r="H1014" t="n">
         <v>4200</v>
@@ -29804,7 +29804,7 @@
         <v>9.9399995803833</v>
       </c>
       <c r="G1015" t="n">
-        <v>9.05691528320312</v>
+        <v>9.05691623687744</v>
       </c>
       <c r="H1015" t="n">
         <v>7972</v>
@@ -29862,7 +29862,7 @@
         <v>9.84000015258789</v>
       </c>
       <c r="G1017" t="n">
-        <v>8.96579933166504</v>
+        <v>8.96580123901367</v>
       </c>
       <c r="H1017" t="n">
         <v>2452</v>
@@ -29891,7 +29891,7 @@
         <v>9.77999973297119</v>
       </c>
       <c r="G1018" t="n">
-        <v>8.91113090515137</v>
+        <v>8.91112995147705</v>
       </c>
       <c r="H1018" t="n">
         <v>2309</v>
@@ -29920,7 +29920,7 @@
         <v>9.68000030517578</v>
       </c>
       <c r="G1019" t="n">
-        <v>8.82001495361328</v>
+        <v>8.82001399993896</v>
       </c>
       <c r="H1019" t="n">
         <v>1580</v>
@@ -30007,7 +30007,7 @@
         <v>9.65999984741211</v>
       </c>
       <c r="G1022" t="n">
-        <v>8.80179119110107</v>
+        <v>8.80179214477539</v>
       </c>
       <c r="H1022" t="n">
         <v>12995</v>
@@ -30036,7 +30036,7 @@
         <v>9.39999961853027</v>
       </c>
       <c r="G1023" t="n">
-        <v>8.56489086151123</v>
+        <v>8.56488990783691</v>
       </c>
       <c r="H1023" t="n">
         <v>5113</v>
@@ -30065,7 +30065,7 @@
         <v>9.68000030517578</v>
       </c>
       <c r="G1024" t="n">
-        <v>8.82001495361328</v>
+        <v>8.82001399993896</v>
       </c>
       <c r="H1024" t="n">
         <v>6017</v>
@@ -30094,7 +30094,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G1025" t="n">
-        <v>8.83823680877686</v>
+        <v>8.83823871612549</v>
       </c>
       <c r="H1025" t="n">
         <v>12478</v>
@@ -30123,7 +30123,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G1026" t="n">
-        <v>8.83823680877686</v>
+        <v>8.83823871612549</v>
       </c>
       <c r="H1026" t="n">
         <v>1517</v>
@@ -30152,7 +30152,7 @@
         <v>9.46000003814697</v>
       </c>
       <c r="G1027" t="n">
-        <v>8.61956024169922</v>
+        <v>8.61956119537354</v>
       </c>
       <c r="H1027" t="n">
         <v>4125</v>
@@ -30239,7 +30239,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G1030" t="n">
-        <v>8.83823680877686</v>
+        <v>8.83823871612549</v>
       </c>
       <c r="H1030" t="n">
         <v>1104</v>
@@ -30326,7 +30326,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G1033" t="n">
-        <v>8.83823680877686</v>
+        <v>8.83823871612549</v>
       </c>
       <c r="H1033" t="n">
         <v>6924</v>
@@ -30471,7 +30471,7 @@
         <v>11.1000003814697</v>
       </c>
       <c r="G1038" t="n">
-        <v>10.1138610839844</v>
+        <v>10.1138601303101</v>
       </c>
       <c r="H1038" t="n">
         <v>46895</v>
@@ -30500,7 +30500,7 @@
         <v>11.0500001907349</v>
       </c>
       <c r="G1039" t="n">
-        <v>10.068302154541</v>
+        <v>10.0683031082153</v>
       </c>
       <c r="H1039" t="n">
         <v>16443</v>
@@ -30558,7 +30558,7 @@
         <v>11.1000003814697</v>
       </c>
       <c r="G1041" t="n">
-        <v>10.1138610839844</v>
+        <v>10.1138601303101</v>
       </c>
       <c r="H1041" t="n">
         <v>10830</v>
@@ -30587,7 +30587,7 @@
         <v>11.1000003814697</v>
       </c>
       <c r="G1042" t="n">
-        <v>10.1138610839844</v>
+        <v>10.1138601303101</v>
       </c>
       <c r="H1042" t="n">
         <v>4407</v>
@@ -30616,7 +30616,7 @@
         <v>11.1000003814697</v>
       </c>
       <c r="G1043" t="n">
-        <v>10.1138610839844</v>
+        <v>10.1138601303101</v>
       </c>
       <c r="H1043" t="n">
         <v>22057</v>
@@ -30645,7 +30645,7 @@
         <v>11.1000003814697</v>
       </c>
       <c r="G1044" t="n">
-        <v>10.1138610839844</v>
+        <v>10.1138601303101</v>
       </c>
       <c r="H1044" t="n">
         <v>3314</v>
@@ -30674,7 +30674,7 @@
         <v>11.3000001907349</v>
       </c>
       <c r="G1045" t="n">
-        <v>10.2960920333862</v>
+        <v>10.2960910797119</v>
       </c>
       <c r="H1045" t="n">
         <v>8842</v>
@@ -30703,7 +30703,7 @@
         <v>11.3000001907349</v>
       </c>
       <c r="G1046" t="n">
-        <v>10.2960920333862</v>
+        <v>10.2960910797119</v>
       </c>
       <c r="H1046" t="n">
         <v>745</v>
@@ -30761,7 +30761,7 @@
         <v>10.9499998092651</v>
       </c>
       <c r="G1048" t="n">
-        <v>9.97718620300293</v>
+        <v>9.97718715667725</v>
       </c>
       <c r="H1048" t="n">
         <v>16113</v>
@@ -30790,7 +30790,7 @@
         <v>10.9499998092651</v>
       </c>
       <c r="G1049" t="n">
-        <v>9.97718620300293</v>
+        <v>9.97718715667725</v>
       </c>
       <c r="H1049" t="n">
         <v>7113</v>
@@ -30819,7 +30819,7 @@
         <v>10.9499998092651</v>
       </c>
       <c r="G1050" t="n">
-        <v>9.97718620300293</v>
+        <v>9.97718715667725</v>
       </c>
       <c r="H1050" t="n">
         <v>6511</v>
@@ -30848,7 +30848,7 @@
         <v>10.8999996185303</v>
       </c>
       <c r="G1051" t="n">
-        <v>9.93162727355957</v>
+        <v>9.93162822723389</v>
       </c>
       <c r="H1051" t="n">
         <v>3234</v>
@@ -30906,7 +30906,7 @@
         <v>10.9499998092651</v>
       </c>
       <c r="G1053" t="n">
-        <v>9.97718620300293</v>
+        <v>9.97718715667725</v>
       </c>
       <c r="H1053" t="n">
         <v>4421</v>
@@ -30964,7 +30964,7 @@
         <v>10.9499998092651</v>
       </c>
       <c r="G1055" t="n">
-        <v>9.97718620300293</v>
+        <v>9.97718715667725</v>
       </c>
       <c r="H1055" t="n">
         <v>4602</v>
@@ -30993,7 +30993,7 @@
         <v>10.8000001907349</v>
       </c>
       <c r="G1056" t="n">
-        <v>9.84051322937012</v>
+        <v>9.8405122756958</v>
       </c>
       <c r="H1056" t="n">
         <v>19566</v>
@@ -31022,7 +31022,7 @@
         <v>10.9499998092651</v>
       </c>
       <c r="G1057" t="n">
-        <v>9.97718620300293</v>
+        <v>9.97718715667725</v>
       </c>
       <c r="H1057" t="n">
         <v>613</v>
@@ -31080,7 +31080,7 @@
         <v>10.8000001907349</v>
       </c>
       <c r="G1059" t="n">
-        <v>9.84051322937012</v>
+        <v>9.8405122756958</v>
       </c>
       <c r="H1059" t="n">
         <v>400</v>
@@ -31109,7 +31109,7 @@
         <v>10.75</v>
       </c>
       <c r="G1060" t="n">
-        <v>9.79495525360107</v>
+        <v>9.79495429992676</v>
       </c>
       <c r="H1060" t="n">
         <v>3130</v>
@@ -31138,7 +31138,7 @@
         <v>10.6000003814697</v>
       </c>
       <c r="G1061" t="n">
-        <v>9.65828132629395</v>
+        <v>9.65828037261963</v>
       </c>
       <c r="H1061" t="n">
         <v>5560</v>
@@ -31196,7 +31196,7 @@
         <v>10.75</v>
       </c>
       <c r="G1063" t="n">
-        <v>9.79495525360107</v>
+        <v>9.79495429992676</v>
       </c>
       <c r="H1063" t="n">
         <v>8500</v>
@@ -31254,7 +31254,7 @@
         <v>10.3999996185303</v>
       </c>
       <c r="G1065" t="n">
-        <v>9.47604846954346</v>
+        <v>9.47604942321777</v>
       </c>
       <c r="H1065" t="n">
         <v>9282</v>
@@ -31312,7 +31312,7 @@
         <v>10.6000003814697</v>
       </c>
       <c r="G1067" t="n">
-        <v>9.65828132629395</v>
+        <v>9.65828037261963</v>
       </c>
       <c r="H1067" t="n">
         <v>2591</v>
@@ -31399,7 +31399,7 @@
         <v>10.8000001907349</v>
       </c>
       <c r="G1070" t="n">
-        <v>9.84051322937012</v>
+        <v>9.8405122756958</v>
       </c>
       <c r="H1070" t="n">
         <v>14898</v>
@@ -31428,7 +31428,7 @@
         <v>10.8999996185303</v>
       </c>
       <c r="G1071" t="n">
-        <v>9.93162727355957</v>
+        <v>9.93162822723389</v>
       </c>
       <c r="H1071" t="n">
         <v>8809</v>
@@ -31457,7 +31457,7 @@
         <v>10.75</v>
       </c>
       <c r="G1072" t="n">
-        <v>9.79495525360107</v>
+        <v>9.79495429992676</v>
       </c>
       <c r="H1072" t="n">
         <v>18487</v>
@@ -31486,7 +31486,7 @@
         <v>10.8000001907349</v>
       </c>
       <c r="G1073" t="n">
-        <v>9.84051322937012</v>
+        <v>9.8405122756958</v>
       </c>
       <c r="H1073" t="n">
         <v>1135</v>
@@ -31602,7 +31602,7 @@
         <v>10.75</v>
       </c>
       <c r="G1077" t="n">
-        <v>9.79495525360107</v>
+        <v>9.79495429992676</v>
       </c>
       <c r="H1077" t="n">
         <v>4356</v>
@@ -31631,7 +31631,7 @@
         <v>10.75</v>
       </c>
       <c r="G1078" t="n">
-        <v>9.79495525360107</v>
+        <v>9.79495429992676</v>
       </c>
       <c r="H1078" t="n">
         <v>45</v>
@@ -31660,7 +31660,7 @@
         <v>10.75</v>
       </c>
       <c r="G1079" t="n">
-        <v>9.79495525360107</v>
+        <v>9.79495429992676</v>
       </c>
       <c r="H1079" t="n">
         <v>9723</v>
@@ -31747,7 +31747,7 @@
         <v>10.6000003814697</v>
       </c>
       <c r="G1082" t="n">
-        <v>9.65828132629395</v>
+        <v>9.65828037261963</v>
       </c>
       <c r="H1082" t="n">
         <v>10531</v>
@@ -31776,7 +31776,7 @@
         <v>10.6000003814697</v>
       </c>
       <c r="G1083" t="n">
-        <v>9.65828132629395</v>
+        <v>9.65828037261963</v>
       </c>
       <c r="H1083" t="n">
         <v>3666</v>
@@ -31805,7 +31805,7 @@
         <v>10.3500003814697</v>
       </c>
       <c r="G1084" t="n">
-        <v>9.43049049377441</v>
+        <v>9.43049144744873</v>
       </c>
       <c r="H1084" t="n">
         <v>6448</v>
@@ -31834,7 +31834,7 @@
         <v>10.3000001907349</v>
       </c>
       <c r="G1085" t="n">
-        <v>9.38493251800537</v>
+        <v>9.38493347167969</v>
       </c>
       <c r="H1085" t="n">
         <v>34653</v>
@@ -31921,7 +31921,7 @@
         <v>10.6000003814697</v>
       </c>
       <c r="G1088" t="n">
-        <v>9.65828132629395</v>
+        <v>9.65828037261963</v>
       </c>
       <c r="H1088" t="n">
         <v>1963</v>
@@ -31950,7 +31950,7 @@
         <v>10.8000001907349</v>
       </c>
       <c r="G1089" t="n">
-        <v>9.84051322937012</v>
+        <v>9.8405122756958</v>
       </c>
       <c r="H1089" t="n">
         <v>14366</v>
@@ -31979,7 +31979,7 @@
         <v>10.8000001907349</v>
       </c>
       <c r="G1090" t="n">
-        <v>9.84051322937012</v>
+        <v>9.8405122756958</v>
       </c>
       <c r="H1090" t="n">
         <v>906</v>
@@ -32008,7 +32008,7 @@
         <v>10.8999996185303</v>
       </c>
       <c r="G1091" t="n">
-        <v>9.93162727355957</v>
+        <v>9.93162822723389</v>
       </c>
       <c r="H1091" t="n">
         <v>2852</v>
@@ -32095,7 +32095,7 @@
         <v>10.8999996185303</v>
       </c>
       <c r="G1094" t="n">
-        <v>9.93162727355957</v>
+        <v>9.93162822723389</v>
       </c>
       <c r="H1094" t="n">
         <v>1016</v>
@@ -32182,7 +32182,7 @@
         <v>10.6000003814697</v>
       </c>
       <c r="G1097" t="n">
-        <v>9.65828132629395</v>
+        <v>9.65828037261963</v>
       </c>
       <c r="H1097" t="n">
         <v>5284</v>
@@ -32211,7 +32211,7 @@
         <v>10.75</v>
       </c>
       <c r="G1098" t="n">
-        <v>9.79495525360107</v>
+        <v>9.79495429992676</v>
       </c>
       <c r="H1098" t="n">
         <v>5377</v>
@@ -32240,7 +32240,7 @@
         <v>10.8000001907349</v>
       </c>
       <c r="G1099" t="n">
-        <v>9.84051322937012</v>
+        <v>9.8405122756958</v>
       </c>
       <c r="H1099" t="n">
         <v>9104</v>
@@ -32269,7 +32269,7 @@
         <v>10.8000001907349</v>
       </c>
       <c r="G1100" t="n">
-        <v>9.84051322937012</v>
+        <v>9.8405122756958</v>
       </c>
       <c r="H1100" t="n">
         <v>24254</v>
@@ -32298,7 +32298,7 @@
         <v>10.75</v>
       </c>
       <c r="G1101" t="n">
-        <v>9.79495525360107</v>
+        <v>9.79495429992676</v>
       </c>
       <c r="H1101" t="n">
         <v>13932</v>
@@ -32327,7 +32327,7 @@
         <v>10.8999996185303</v>
       </c>
       <c r="G1102" t="n">
-        <v>9.93162727355957</v>
+        <v>9.93162822723389</v>
       </c>
       <c r="H1102" t="n">
         <v>16059</v>
@@ -32356,7 +32356,7 @@
         <v>10.9499998092651</v>
       </c>
       <c r="G1103" t="n">
-        <v>9.97718620300293</v>
+        <v>9.97718715667725</v>
       </c>
       <c r="H1103" t="n">
         <v>10723</v>
@@ -32385,7 +32385,7 @@
         <v>10.8999996185303</v>
       </c>
       <c r="G1104" t="n">
-        <v>9.93162727355957</v>
+        <v>9.93162822723389</v>
       </c>
       <c r="H1104" t="n">
         <v>1346</v>
@@ -32414,7 +32414,7 @@
         <v>10.8000001907349</v>
       </c>
       <c r="G1105" t="n">
-        <v>9.84051322937012</v>
+        <v>9.8405122756958</v>
       </c>
       <c r="H1105" t="n">
         <v>3539</v>
@@ -32472,7 +32472,7 @@
         <v>10.8000001907349</v>
       </c>
       <c r="G1107" t="n">
-        <v>9.84051322937012</v>
+        <v>9.8405122756958</v>
       </c>
       <c r="H1107" t="n">
         <v>4910</v>
@@ -32501,7 +32501,7 @@
         <v>10.8000001907349</v>
       </c>
       <c r="G1108" t="n">
-        <v>9.84051322937012</v>
+        <v>9.8405122756958</v>
       </c>
       <c r="H1108" t="n">
         <v>3654</v>
@@ -32530,7 +32530,7 @@
         <v>10.8999996185303</v>
       </c>
       <c r="G1109" t="n">
-        <v>9.93162727355957</v>
+        <v>9.93162822723389</v>
       </c>
       <c r="H1109" t="n">
         <v>534</v>
@@ -32559,7 +32559,7 @@
         <v>10.8000001907349</v>
       </c>
       <c r="G1110" t="n">
-        <v>9.84051322937012</v>
+        <v>9.8405122756958</v>
       </c>
       <c r="H1110" t="n">
         <v>2457</v>
@@ -32617,7 +32617,7 @@
         <v>10.8000001907349</v>
       </c>
       <c r="G1112" t="n">
-        <v>9.84051322937012</v>
+        <v>9.8405122756958</v>
       </c>
       <c r="H1112" t="n">
         <v>4426</v>
@@ -32646,7 +32646,7 @@
         <v>10.8999996185303</v>
       </c>
       <c r="G1113" t="n">
-        <v>9.93162727355957</v>
+        <v>9.93162822723389</v>
       </c>
       <c r="H1113" t="n">
         <v>1001</v>
@@ -32675,7 +32675,7 @@
         <v>10.8000001907349</v>
       </c>
       <c r="G1114" t="n">
-        <v>9.84051322937012</v>
+        <v>9.8405122756958</v>
       </c>
       <c r="H1114" t="n">
         <v>1323</v>
@@ -32704,7 +32704,7 @@
         <v>10.75</v>
       </c>
       <c r="G1115" t="n">
-        <v>9.79495525360107</v>
+        <v>9.79495429992676</v>
       </c>
       <c r="H1115" t="n">
         <v>6893</v>
@@ -32733,7 +32733,7 @@
         <v>10.75</v>
       </c>
       <c r="G1116" t="n">
-        <v>9.79495525360107</v>
+        <v>9.79495429992676</v>
       </c>
       <c r="H1116" t="n">
         <v>6550</v>
@@ -32762,7 +32762,7 @@
         <v>10.9499998092651</v>
       </c>
       <c r="G1117" t="n">
-        <v>9.97718620300293</v>
+        <v>9.97718715667725</v>
       </c>
       <c r="H1117" t="n">
         <v>6390</v>
@@ -32791,7 +32791,7 @@
         <v>10.8999996185303</v>
       </c>
       <c r="G1118" t="n">
-        <v>9.93162727355957</v>
+        <v>9.93162822723389</v>
       </c>
       <c r="H1118" t="n">
         <v>7385</v>
@@ -32878,7 +32878,7 @@
         <v>11.0500001907349</v>
       </c>
       <c r="G1121" t="n">
-        <v>10.068302154541</v>
+        <v>10.0683031082153</v>
       </c>
       <c r="H1121" t="n">
         <v>5584</v>
@@ -32936,7 +32936,7 @@
         <v>11.1000003814697</v>
       </c>
       <c r="G1123" t="n">
-        <v>10.1138610839844</v>
+        <v>10.1138601303101</v>
       </c>
       <c r="H1123" t="n">
         <v>3821</v>
@@ -32965,7 +32965,7 @@
         <v>11.1000003814697</v>
       </c>
       <c r="G1124" t="n">
-        <v>10.1138610839844</v>
+        <v>10.1138601303101</v>
       </c>
       <c r="H1124" t="n">
         <v>3688</v>
@@ -32994,7 +32994,7 @@
         <v>11.1000003814697</v>
       </c>
       <c r="G1125" t="n">
-        <v>10.1138610839844</v>
+        <v>10.1138601303101</v>
       </c>
       <c r="H1125" t="n">
         <v>4792</v>
@@ -33023,7 +33023,7 @@
         <v>10.9499998092651</v>
       </c>
       <c r="G1126" t="n">
-        <v>9.97718620300293</v>
+        <v>9.97718715667725</v>
       </c>
       <c r="H1126" t="n">
         <v>1792</v>
@@ -33052,7 +33052,7 @@
         <v>11.0500001907349</v>
       </c>
       <c r="G1127" t="n">
-        <v>10.068302154541</v>
+        <v>10.0683031082153</v>
       </c>
       <c r="H1127" t="n">
         <v>12329</v>
@@ -33081,7 +33081,7 @@
         <v>11.8500003814697</v>
       </c>
       <c r="G1128" t="n">
-        <v>10.7972288131714</v>
+        <v>10.7972297668457</v>
       </c>
       <c r="H1128" t="n">
         <v>64836</v>
@@ -33110,7 +33110,7 @@
         <v>11.8500003814697</v>
       </c>
       <c r="G1129" t="n">
-        <v>10.7972288131714</v>
+        <v>10.7972297668457</v>
       </c>
       <c r="H1129" t="n">
         <v>20580</v>
@@ -33168,7 +33168,7 @@
         <v>12.1000003814697</v>
       </c>
       <c r="G1131" t="n">
-        <v>11.0250196456909</v>
+        <v>11.0250186920166</v>
       </c>
       <c r="H1131" t="n">
         <v>13540</v>
@@ -33197,7 +33197,7 @@
         <v>12.3999996185303</v>
       </c>
       <c r="G1132" t="n">
-        <v>11.2983655929565</v>
+        <v>11.2983646392822</v>
       </c>
       <c r="H1132" t="n">
         <v>74102</v>
@@ -33226,7 +33226,7 @@
         <v>12.4499998092651</v>
       </c>
       <c r="G1133" t="n">
-        <v>11.3439235687256</v>
+        <v>11.3439245223999</v>
       </c>
       <c r="H1133" t="n">
         <v>60180</v>
@@ -33255,7 +33255,7 @@
         <v>12.5</v>
       </c>
       <c r="G1134" t="n">
-        <v>11.3894815444946</v>
+        <v>11.3894824981689</v>
       </c>
       <c r="H1134" t="n">
         <v>13196</v>
@@ -33284,7 +33284,7 @@
         <v>12.5500001907349</v>
       </c>
       <c r="G1135" t="n">
-        <v>11.435040473938</v>
+        <v>11.4350395202637</v>
       </c>
       <c r="H1135" t="n">
         <v>17670</v>
@@ -33371,7 +33371,7 @@
         <v>12.5500001907349</v>
       </c>
       <c r="G1138" t="n">
-        <v>11.435040473938</v>
+        <v>11.4350395202637</v>
       </c>
       <c r="H1138" t="n">
         <v>9552</v>
@@ -33400,7 +33400,7 @@
         <v>12.8500003814697</v>
       </c>
       <c r="G1139" t="n">
-        <v>11.7083892822266</v>
+        <v>11.7083873748779</v>
       </c>
       <c r="H1139" t="n">
         <v>22061</v>
@@ -33429,7 +33429,7 @@
         <v>12.8999996185303</v>
       </c>
       <c r="G1140" t="n">
-        <v>11.753945350647</v>
+        <v>11.7539443969727</v>
       </c>
       <c r="H1140" t="n">
         <v>36171</v>
@@ -33458,7 +33458,7 @@
         <v>12.8999996185303</v>
       </c>
       <c r="G1141" t="n">
-        <v>11.753945350647</v>
+        <v>11.7539443969727</v>
       </c>
       <c r="H1141" t="n">
         <v>13867</v>
@@ -33487,7 +33487,7 @@
         <v>13.1499996185303</v>
       </c>
       <c r="G1142" t="n">
-        <v>11.9817342758179</v>
+        <v>11.9817352294922</v>
       </c>
       <c r="H1142" t="n">
         <v>17446</v>
@@ -33516,7 +33516,7 @@
         <v>13.25</v>
       </c>
       <c r="G1143" t="n">
-        <v>12.072850227356</v>
+        <v>12.0728521347046</v>
       </c>
       <c r="H1143" t="n">
         <v>34754</v>
@@ -33632,7 +33632,7 @@
         <v>13.1000003814697</v>
       </c>
       <c r="G1147" t="n">
-        <v>11.9361772537231</v>
+        <v>11.9361782073975</v>
       </c>
       <c r="H1147" t="n">
         <v>3372</v>
@@ -33661,7 +33661,7 @@
         <v>13.0500001907349</v>
       </c>
       <c r="G1148" t="n">
-        <v>11.8906183242798</v>
+        <v>11.8906202316284</v>
       </c>
       <c r="H1148" t="n">
         <v>8972</v>
@@ -33690,7 +33690,7 @@
         <v>13.1000003814697</v>
       </c>
       <c r="G1149" t="n">
-        <v>11.9361772537231</v>
+        <v>11.9361782073975</v>
       </c>
       <c r="H1149" t="n">
         <v>7550</v>
@@ -33835,7 +33835,7 @@
         <v>13.25</v>
       </c>
       <c r="G1154" t="n">
-        <v>12.2032661437988</v>
+        <v>12.2032680511475</v>
       </c>
       <c r="H1154" t="n">
         <v>6770</v>
@@ -33893,7 +33893,7 @@
         <v>13.6000003814697</v>
       </c>
       <c r="G1156" t="n">
-        <v>12.5256175994873</v>
+        <v>12.5256185531616</v>
       </c>
       <c r="H1156" t="n">
         <v>18328</v>
@@ -33951,7 +33951,7 @@
         <v>13.6000003814697</v>
       </c>
       <c r="G1158" t="n">
-        <v>12.5256175994873</v>
+        <v>12.5256185531616</v>
       </c>
       <c r="H1158" t="n">
         <v>13524</v>
@@ -34009,7 +34009,7 @@
         <v>13.5500001907349</v>
       </c>
       <c r="G1160" t="n">
-        <v>12.4795665740967</v>
+        <v>12.479567527771</v>
       </c>
       <c r="H1160" t="n">
         <v>28389</v>
@@ -34038,7 +34038,7 @@
         <v>13.6000003814697</v>
       </c>
       <c r="G1161" t="n">
-        <v>12.5256175994873</v>
+        <v>12.5256185531616</v>
       </c>
       <c r="H1161" t="n">
         <v>12700</v>
@@ -34096,7 +34096,7 @@
         <v>13.25</v>
       </c>
       <c r="G1163" t="n">
-        <v>12.2032661437988</v>
+        <v>12.2032680511475</v>
       </c>
       <c r="H1163" t="n">
         <v>29089</v>
@@ -34125,7 +34125,7 @@
         <v>13.25</v>
       </c>
       <c r="G1164" t="n">
-        <v>12.2032661437988</v>
+        <v>12.2032680511475</v>
       </c>
       <c r="H1164" t="n">
         <v>25726</v>
@@ -34154,7 +34154,7 @@
         <v>13.0500001907349</v>
       </c>
       <c r="G1165" t="n">
-        <v>12.0190668106079</v>
+        <v>12.0190677642822</v>
       </c>
       <c r="H1165" t="n">
         <v>3456</v>
@@ -34212,7 +34212,7 @@
         <v>13.25</v>
       </c>
       <c r="G1167" t="n">
-        <v>12.2032661437988</v>
+        <v>12.2032680511475</v>
       </c>
       <c r="H1167" t="n">
         <v>15931</v>
@@ -34241,7 +34241,7 @@
         <v>13.1499996185303</v>
       </c>
       <c r="G1168" t="n">
-        <v>12.1111660003662</v>
+        <v>12.1111669540405</v>
       </c>
       <c r="H1168" t="n">
         <v>13997</v>
@@ -34270,7 +34270,7 @@
         <v>13.1000003814697</v>
       </c>
       <c r="G1169" t="n">
-        <v>12.0651168823242</v>
+        <v>12.0651178359985</v>
       </c>
       <c r="H1169" t="n">
         <v>14679</v>
@@ -34328,7 +34328,7 @@
         <v>13.25</v>
       </c>
       <c r="G1171" t="n">
-        <v>12.2032661437988</v>
+        <v>12.2032680511475</v>
       </c>
       <c r="H1171" t="n">
         <v>29663</v>
@@ -34386,7 +34386,7 @@
         <v>13.6000003814697</v>
       </c>
       <c r="G1173" t="n">
-        <v>12.5256175994873</v>
+        <v>12.5256185531616</v>
       </c>
       <c r="H1173" t="n">
         <v>110733</v>
@@ -34415,7 +34415,7 @@
         <v>13.5500001907349</v>
       </c>
       <c r="G1174" t="n">
-        <v>12.4795665740967</v>
+        <v>12.479567527771</v>
       </c>
       <c r="H1174" t="n">
         <v>17802</v>
@@ -34473,7 +34473,7 @@
         <v>13.6499996185303</v>
       </c>
       <c r="G1176" t="n">
-        <v>12.5716676712036</v>
+        <v>12.5716667175293</v>
       </c>
       <c r="H1176" t="n">
         <v>4818</v>
@@ -34531,7 +34531,7 @@
         <v>13.4499998092651</v>
       </c>
       <c r="G1178" t="n">
-        <v>12.3874664306641</v>
+        <v>12.3874683380127</v>
       </c>
       <c r="H1178" t="n">
         <v>10766</v>
@@ -34560,7 +34560,7 @@
         <v>13.6000003814697</v>
       </c>
       <c r="G1179" t="n">
-        <v>12.5256175994873</v>
+        <v>12.5256185531616</v>
       </c>
       <c r="H1179" t="n">
         <v>3641</v>
@@ -34589,7 +34589,7 @@
         <v>13.6000003814697</v>
       </c>
       <c r="G1180" t="n">
-        <v>12.5256175994873</v>
+        <v>12.5256185531616</v>
       </c>
       <c r="H1180" t="n">
         <v>17307</v>
@@ -34618,7 +34618,7 @@
         <v>13.6000003814697</v>
       </c>
       <c r="G1181" t="n">
-        <v>12.5256175994873</v>
+        <v>12.5256185531616</v>
       </c>
       <c r="H1181" t="n">
         <v>2093</v>
@@ -34647,7 +34647,7 @@
         <v>13.6000003814697</v>
       </c>
       <c r="G1182" t="n">
-        <v>12.5256175994873</v>
+        <v>12.5256185531616</v>
       </c>
       <c r="H1182" t="n">
         <v>8035</v>
@@ -34676,7 +34676,7 @@
         <v>13.5500001907349</v>
       </c>
       <c r="G1183" t="n">
-        <v>12.4795665740967</v>
+        <v>12.479567527771</v>
       </c>
       <c r="H1183" t="n">
         <v>16220</v>
@@ -34705,7 +34705,7 @@
         <v>13.4499998092651</v>
       </c>
       <c r="G1184" t="n">
-        <v>12.3874664306641</v>
+        <v>12.3874683380127</v>
       </c>
       <c r="H1184" t="n">
         <v>7360</v>
@@ -34734,7 +34734,7 @@
         <v>13.6000003814697</v>
       </c>
       <c r="G1185" t="n">
-        <v>12.5256175994873</v>
+        <v>12.5256185531616</v>
       </c>
       <c r="H1185" t="n">
         <v>6448</v>
@@ -34763,7 +34763,7 @@
         <v>13.6000003814697</v>
       </c>
       <c r="G1186" t="n">
-        <v>12.5256175994873</v>
+        <v>12.5256185531616</v>
       </c>
       <c r="H1186" t="n">
         <v>7807</v>
@@ -34821,7 +34821,7 @@
         <v>13.5500001907349</v>
       </c>
       <c r="G1188" t="n">
-        <v>12.4795665740967</v>
+        <v>12.479567527771</v>
       </c>
       <c r="H1188" t="n">
         <v>22832</v>
@@ -34879,7 +34879,7 @@
         <v>13.4499998092651</v>
       </c>
       <c r="G1190" t="n">
-        <v>12.3874664306641</v>
+        <v>12.3874683380127</v>
       </c>
       <c r="H1190" t="n">
         <v>5662</v>
@@ -35053,7 +35053,7 @@
         <v>13.1000003814697</v>
       </c>
       <c r="G1196" t="n">
-        <v>12.0651168823242</v>
+        <v>12.0651178359985</v>
       </c>
       <c r="H1196" t="n">
         <v>5195</v>
@@ -35111,7 +35111,7 @@
         <v>13.4499998092651</v>
       </c>
       <c r="G1198" t="n">
-        <v>12.3874664306641</v>
+        <v>12.3874683380127</v>
       </c>
       <c r="H1198" t="n">
         <v>19804</v>
@@ -35140,7 +35140,7 @@
         <v>13.6000003814697</v>
       </c>
       <c r="G1199" t="n">
-        <v>12.5256175994873</v>
+        <v>12.5256185531616</v>
       </c>
       <c r="H1199" t="n">
         <v>24469</v>
@@ -35285,7 +35285,7 @@
         <v>13.6000003814697</v>
       </c>
       <c r="G1204" t="n">
-        <v>12.5256175994873</v>
+        <v>12.5256185531616</v>
       </c>
       <c r="H1204" t="n">
         <v>10928</v>
@@ -35372,7 +35372,7 @@
         <v>13.4499998092651</v>
       </c>
       <c r="G1207" t="n">
-        <v>12.3874664306641</v>
+        <v>12.3874683380127</v>
       </c>
       <c r="H1207" t="n">
         <v>6781</v>
@@ -35430,7 +35430,7 @@
         <v>13.6499996185303</v>
       </c>
       <c r="G1209" t="n">
-        <v>12.5716676712036</v>
+        <v>12.5716667175293</v>
       </c>
       <c r="H1209" t="n">
         <v>46032</v>
@@ -35517,7 +35517,7 @@
         <v>13.6499996185303</v>
       </c>
       <c r="G1212" t="n">
-        <v>12.5716676712036</v>
+        <v>12.5716667175293</v>
       </c>
       <c r="H1212" t="n">
         <v>6137</v>
@@ -35604,7 +35604,7 @@
         <v>14.6000003814697</v>
       </c>
       <c r="G1215" t="n">
-        <v>13.4466180801392</v>
+        <v>13.4466190338135</v>
       </c>
       <c r="H1215" t="n">
         <v>68411</v>
@@ -35691,7 +35691,7 @@
         <v>14.6000003814697</v>
       </c>
       <c r="G1218" t="n">
-        <v>13.4466180801392</v>
+        <v>13.4466190338135</v>
       </c>
       <c r="H1218" t="n">
         <v>27155</v>
@@ -35749,7 +35749,7 @@
         <v>15.5500001907349</v>
       </c>
       <c r="G1220" t="n">
-        <v>14.3215713500977</v>
+        <v>14.321572303772</v>
       </c>
       <c r="H1220" t="n">
         <v>39798</v>
@@ -35807,7 +35807,7 @@
         <v>16.1499996185303</v>
       </c>
       <c r="G1222" t="n">
-        <v>14.874171257019</v>
+        <v>14.8741703033447</v>
       </c>
       <c r="H1222" t="n">
         <v>56456</v>
@@ -35836,7 +35836,7 @@
         <v>16.1499996185303</v>
       </c>
       <c r="G1223" t="n">
-        <v>14.874171257019</v>
+        <v>14.8741703033447</v>
       </c>
       <c r="H1223" t="n">
         <v>13742</v>
@@ -35952,7 +35952,7 @@
         <v>16.3500003814697</v>
       </c>
       <c r="G1227" t="n">
-        <v>15.0583724975586</v>
+        <v>15.0583715438843</v>
       </c>
       <c r="H1227" t="n">
         <v>31110</v>
@@ -36097,7 +36097,7 @@
         <v>16.6000003814697</v>
       </c>
       <c r="G1232" t="n">
-        <v>15.2886228561401</v>
+        <v>15.2886219024658</v>
       </c>
       <c r="H1232" t="n">
         <v>26978</v>
@@ -36126,7 +36126,7 @@
         <v>17.1499996185303</v>
       </c>
       <c r="G1233" t="n">
-        <v>15.7951707839966</v>
+        <v>15.7951726913452</v>
       </c>
       <c r="H1233" t="n">
         <v>46558</v>
@@ -36155,7 +36155,7 @@
         <v>18</v>
       </c>
       <c r="G1234" t="n">
-        <v>16.5780239105225</v>
+        <v>16.5780258178711</v>
       </c>
       <c r="H1234" t="n">
         <v>55851</v>
@@ -36184,7 +36184,7 @@
         <v>18.1499996185303</v>
       </c>
       <c r="G1235" t="n">
-        <v>16.7161731719971</v>
+        <v>16.7161750793457</v>
       </c>
       <c r="H1235" t="n">
         <v>37688</v>
@@ -36213,7 +36213,7 @@
         <v>18</v>
       </c>
       <c r="G1236" t="n">
-        <v>16.5780239105225</v>
+        <v>16.5780258178711</v>
       </c>
       <c r="H1236" t="n">
         <v>29143</v>
@@ -36300,7 +36300,7 @@
         <v>18.2000007629395</v>
       </c>
       <c r="G1239" t="n">
-        <v>16.7622241973877</v>
+        <v>16.7622222900391</v>
       </c>
       <c r="H1239" t="n">
         <v>31567</v>
@@ -36329,7 +36329,7 @@
         <v>18.1000003814697</v>
       </c>
       <c r="G1240" t="n">
-        <v>16.6701240539551</v>
+        <v>16.6701259613037</v>
       </c>
       <c r="H1240" t="n">
         <v>35362</v>
@@ -36358,7 +36358,7 @@
         <v>17.8500003814697</v>
       </c>
       <c r="G1241" t="n">
-        <v>16.4398727416992</v>
+        <v>16.4398746490479</v>
       </c>
       <c r="H1241" t="n">
         <v>30423</v>
@@ -36416,7 +36416,7 @@
         <v>18</v>
       </c>
       <c r="G1243" t="n">
-        <v>16.5780239105225</v>
+        <v>16.5780258178711</v>
       </c>
       <c r="H1243" t="n">
         <v>23468</v>
@@ -36445,7 +36445,7 @@
         <v>17.75</v>
       </c>
       <c r="G1244" t="n">
-        <v>16.3477725982666</v>
+        <v>16.3477745056152</v>
       </c>
       <c r="H1244" t="n">
         <v>8695</v>
@@ -36474,7 +36474,7 @@
         <v>17.8500003814697</v>
       </c>
       <c r="G1245" t="n">
-        <v>16.4398727416992</v>
+        <v>16.4398746490479</v>
       </c>
       <c r="H1245" t="n">
         <v>32163</v>
@@ -36561,7 +36561,7 @@
         <v>17.8500003814697</v>
       </c>
       <c r="G1248" t="n">
-        <v>16.4398727416992</v>
+        <v>16.4398746490479</v>
       </c>
       <c r="H1248" t="n">
         <v>21176</v>
@@ -36677,7 +36677,7 @@
         <v>18.2999992370605</v>
       </c>
       <c r="G1252" t="n">
-        <v>16.8543262481689</v>
+        <v>16.8543243408203</v>
       </c>
       <c r="H1252" t="n">
         <v>179017</v>
@@ -36706,7 +36706,7 @@
         <v>18.1499996185303</v>
       </c>
       <c r="G1253" t="n">
-        <v>16.7161731719971</v>
+        <v>16.7161750793457</v>
       </c>
       <c r="H1253" t="n">
         <v>51561</v>
@@ -36735,7 +36735,7 @@
         <v>18.1499996185303</v>
       </c>
       <c r="G1254" t="n">
-        <v>16.7161731719971</v>
+        <v>16.7161750793457</v>
       </c>
       <c r="H1254" t="n">
         <v>19292</v>
@@ -36793,7 +36793,7 @@
         <v>17.1499996185303</v>
       </c>
       <c r="G1256" t="n">
-        <v>15.7951707839966</v>
+        <v>15.7951726913452</v>
       </c>
       <c r="H1256" t="n">
         <v>46906</v>
@@ -36851,7 +36851,7 @@
         <v>16.8999996185303</v>
       </c>
       <c r="G1258" t="n">
-        <v>15.5649213790894</v>
+        <v>15.564920425415</v>
       </c>
       <c r="H1258" t="n">
         <v>66123</v>
@@ -36880,7 +36880,7 @@
         <v>17.2000007629395</v>
       </c>
       <c r="G1259" t="n">
-        <v>15.8412237167358</v>
+        <v>15.8412218093872</v>
       </c>
       <c r="H1259" t="n">
         <v>34176</v>
@@ -36909,7 +36909,7 @@
         <v>17.1000003814697</v>
       </c>
       <c r="G1260" t="n">
-        <v>15.7491235733032</v>
+        <v>15.7491226196289</v>
       </c>
       <c r="H1260" t="n">
         <v>17883</v>
@@ -36938,7 +36938,7 @@
         <v>17.25</v>
       </c>
       <c r="G1261" t="n">
-        <v>15.8872737884521</v>
+        <v>15.8872718811035</v>
       </c>
       <c r="H1261" t="n">
         <v>15494</v>
@@ -36967,7 +36967,7 @@
         <v>16.8999996185303</v>
       </c>
       <c r="G1262" t="n">
-        <v>15.5649213790894</v>
+        <v>15.564920425415</v>
       </c>
       <c r="H1262" t="n">
         <v>11633</v>
@@ -37025,7 +37025,7 @@
         <v>17.2000007629395</v>
       </c>
       <c r="G1264" t="n">
-        <v>15.8412237167358</v>
+        <v>15.8412218093872</v>
       </c>
       <c r="H1264" t="n">
         <v>8184</v>
@@ -37054,7 +37054,7 @@
         <v>16.7999992370605</v>
       </c>
       <c r="G1265" t="n">
-        <v>15.4728221893311</v>
+        <v>15.4728212356567</v>
       </c>
       <c r="H1265" t="n">
         <v>8522</v>
@@ -37141,7 +37141,7 @@
         <v>17.75</v>
       </c>
       <c r="G1268" t="n">
-        <v>16.3477725982666</v>
+        <v>16.3477745056152</v>
       </c>
       <c r="H1268" t="n">
         <v>31701</v>
@@ -37170,7 +37170,7 @@
         <v>18.1000003814697</v>
       </c>
       <c r="G1269" t="n">
-        <v>16.6701240539551</v>
+        <v>16.6701259613037</v>
       </c>
       <c r="H1269" t="n">
         <v>26641</v>
@@ -37228,7 +37228,7 @@
         <v>18.1000003814697</v>
       </c>
       <c r="G1271" t="n">
-        <v>16.6701240539551</v>
+        <v>16.6701259613037</v>
       </c>
       <c r="H1271" t="n">
         <v>24651</v>
@@ -37257,7 +37257,7 @@
         <v>18.1499996185303</v>
       </c>
       <c r="G1272" t="n">
-        <v>16.7161731719971</v>
+        <v>16.7161750793457</v>
       </c>
       <c r="H1272" t="n">
         <v>17506</v>
@@ -37315,7 +37315,7 @@
         <v>18.25</v>
       </c>
       <c r="G1274" t="n">
-        <v>16.8082733154297</v>
+        <v>16.8082714080811</v>
       </c>
       <c r="H1274" t="n">
         <v>38466</v>
@@ -37431,7 +37431,7 @@
         <v>17.9500007629395</v>
       </c>
       <c r="G1278" t="n">
-        <v>16.5319728851318</v>
+        <v>16.5319747924805</v>
       </c>
       <c r="H1278" t="n">
         <v>21896</v>
@@ -37460,7 +37460,7 @@
         <v>17.8500003814697</v>
       </c>
       <c r="G1279" t="n">
-        <v>16.4398727416992</v>
+        <v>16.4398746490479</v>
       </c>
       <c r="H1279" t="n">
         <v>10328</v>
@@ -37489,7 +37489,7 @@
         <v>17.9500007629395</v>
       </c>
       <c r="G1280" t="n">
-        <v>16.5319728851318</v>
+        <v>16.5319747924805</v>
       </c>
       <c r="H1280" t="n">
         <v>4603</v>
@@ -37518,7 +37518,7 @@
         <v>17.9500007629395</v>
       </c>
       <c r="G1281" t="n">
-        <v>16.5319728851318</v>
+        <v>16.5319747924805</v>
       </c>
       <c r="H1281" t="n">
         <v>17215</v>
@@ -37808,7 +37808,7 @@
         <v>16.2999992370605</v>
       </c>
       <c r="G1291" t="n">
-        <v>15.012321472168</v>
+        <v>15.0123205184937</v>
       </c>
       <c r="H1291" t="n">
         <v>35185</v>
@@ -37866,7 +37866,7 @@
         <v>16</v>
       </c>
       <c r="G1293" t="n">
-        <v>14.7360210418701</v>
+        <v>14.7360200881958</v>
       </c>
       <c r="H1293" t="n">
         <v>19002</v>
@@ -37895,7 +37895,7 @@
         <v>16</v>
       </c>
       <c r="G1294" t="n">
-        <v>14.7360210418701</v>
+        <v>14.7360200881958</v>
       </c>
       <c r="H1294" t="n">
         <v>17942</v>
@@ -37924,7 +37924,7 @@
         <v>15.8000001907349</v>
       </c>
       <c r="G1295" t="n">
-        <v>14.5518207550049</v>
+        <v>14.5518198013306</v>
       </c>
       <c r="H1295" t="n">
         <v>22331</v>
@@ -38040,7 +38040,7 @@
         <v>15.3500003814697</v>
       </c>
       <c r="G1299" t="n">
-        <v>14.1373701095581</v>
+        <v>14.1373691558838</v>
       </c>
       <c r="H1299" t="n">
         <v>11239</v>
@@ -38069,7 +38069,7 @@
         <v>15.0500001907349</v>
       </c>
       <c r="G1300" t="n">
-        <v>13.8610696792603</v>
+        <v>13.8610687255859</v>
       </c>
       <c r="H1300" t="n">
         <v>16158</v>
@@ -38127,7 +38127,7 @@
         <v>15.5</v>
       </c>
       <c r="G1302" t="n">
-        <v>14.2755193710327</v>
+        <v>14.275520324707</v>
       </c>
       <c r="H1302" t="n">
         <v>9288</v>
@@ -38156,7 +38156,7 @@
         <v>15.3500003814697</v>
       </c>
       <c r="G1303" t="n">
-        <v>14.1373701095581</v>
+        <v>14.1373691558838</v>
       </c>
       <c r="H1303" t="n">
         <v>6390</v>
@@ -38243,7 +38243,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G1306" t="n">
-        <v>13.9992198944092</v>
+        <v>13.9992189407349</v>
       </c>
       <c r="H1306" t="n">
         <v>33686</v>
@@ -38417,7 +38417,7 @@
         <v>15.0500001907349</v>
       </c>
       <c r="G1312" t="n">
-        <v>13.8610696792603</v>
+        <v>13.8610687255859</v>
       </c>
       <c r="H1312" t="n">
         <v>19109</v>
@@ -38446,7 +38446,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G1313" t="n">
-        <v>13.9992198944092</v>
+        <v>13.9992189407349</v>
       </c>
       <c r="H1313" t="n">
         <v>22212</v>
@@ -38562,7 +38562,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G1317" t="n">
-        <v>13.9071197509766</v>
+        <v>13.9071207046509</v>
       </c>
       <c r="H1317" t="n">
         <v>15322</v>
@@ -38591,7 +38591,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G1318" t="n">
-        <v>13.9071197509766</v>
+        <v>13.9071207046509</v>
       </c>
       <c r="H1318" t="n">
         <v>8220</v>
@@ -38620,7 +38620,7 @@
         <v>15.5</v>
       </c>
       <c r="G1319" t="n">
-        <v>14.2755193710327</v>
+        <v>14.275520324707</v>
       </c>
       <c r="H1319" t="n">
         <v>13138</v>
@@ -38649,7 +38649,7 @@
         <v>15.5</v>
       </c>
       <c r="G1320" t="n">
-        <v>14.2755193710327</v>
+        <v>14.275520324707</v>
       </c>
       <c r="H1320" t="n">
         <v>8836</v>
@@ -38678,7 +38678,7 @@
         <v>15.5500001907349</v>
       </c>
       <c r="G1321" t="n">
-        <v>14.3215713500977</v>
+        <v>14.321572303772</v>
       </c>
       <c r="H1321" t="n">
         <v>12139</v>
@@ -38707,7 +38707,7 @@
         <v>15.3999996185303</v>
       </c>
       <c r="G1322" t="n">
-        <v>14.1834192276001</v>
+        <v>14.1834201812744</v>
       </c>
       <c r="H1322" t="n">
         <v>2323</v>
@@ -38736,7 +38736,7 @@
         <v>15.6000003814697</v>
       </c>
       <c r="G1323" t="n">
-        <v>14.3676204681396</v>
+        <v>14.367621421814</v>
       </c>
       <c r="H1323" t="n">
         <v>7547</v>
@@ -38765,7 +38765,7 @@
         <v>15.5</v>
       </c>
       <c r="G1324" t="n">
-        <v>14.2755193710327</v>
+        <v>14.275520324707</v>
       </c>
       <c r="H1324" t="n">
         <v>17577</v>
@@ -38794,7 +38794,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G1325" t="n">
-        <v>13.9992198944092</v>
+        <v>13.9992189407349</v>
       </c>
       <c r="H1325" t="n">
         <v>19479</v>
@@ -38910,7 +38910,7 @@
         <v>14.1999998092651</v>
       </c>
       <c r="G1329" t="n">
-        <v>13.078218460083</v>
+        <v>13.0782175064087</v>
       </c>
       <c r="H1329" t="n">
         <v>22122</v>
@@ -38968,7 +38968,7 @@
         <v>13.8999996185303</v>
       </c>
       <c r="G1331" t="n">
-        <v>12.8019170761108</v>
+        <v>12.8019180297852</v>
       </c>
       <c r="H1331" t="n">
         <v>4498</v>
@@ -38997,7 +38997,7 @@
         <v>14.1999998092651</v>
       </c>
       <c r="G1332" t="n">
-        <v>13.078218460083</v>
+        <v>13.0782175064087</v>
       </c>
       <c r="H1332" t="n">
         <v>14523</v>
@@ -39026,7 +39026,7 @@
         <v>14.1999998092651</v>
       </c>
       <c r="G1333" t="n">
-        <v>13.078218460083</v>
+        <v>13.0782175064087</v>
       </c>
       <c r="H1333" t="n">
         <v>11624</v>
@@ -39084,7 +39084,7 @@
         <v>14</v>
       </c>
       <c r="G1335" t="n">
-        <v>12.8940181732178</v>
+        <v>12.8940191268921</v>
       </c>
       <c r="H1335" t="n">
         <v>29719</v>
@@ -39113,7 +39113,7 @@
         <v>14</v>
       </c>
       <c r="G1336" t="n">
-        <v>12.8940181732178</v>
+        <v>12.8940191268921</v>
       </c>
       <c r="H1336" t="n">
         <v>9780</v>
@@ -39171,7 +39171,7 @@
         <v>13.5500001907349</v>
       </c>
       <c r="G1338" t="n">
-        <v>12.4795665740967</v>
+        <v>12.479567527771</v>
       </c>
       <c r="H1338" t="n">
         <v>30533</v>
@@ -39229,7 +39229,7 @@
         <v>13.6000003814697</v>
       </c>
       <c r="G1340" t="n">
-        <v>12.5256175994873</v>
+        <v>12.5256185531616</v>
       </c>
       <c r="H1340" t="n">
         <v>6667</v>
@@ -39258,7 +39258,7 @@
         <v>13.6499996185303</v>
       </c>
       <c r="G1341" t="n">
-        <v>12.5716676712036</v>
+        <v>12.5716667175293</v>
       </c>
       <c r="H1341" t="n">
         <v>3638</v>
@@ -39316,7 +39316,7 @@
         <v>13.6499996185303</v>
       </c>
       <c r="G1343" t="n">
-        <v>12.5716676712036</v>
+        <v>12.5716667175293</v>
       </c>
       <c r="H1343" t="n">
         <v>11042</v>
@@ -39374,7 +39374,7 @@
         <v>13.5500001907349</v>
       </c>
       <c r="G1345" t="n">
-        <v>12.4795665740967</v>
+        <v>12.479567527771</v>
       </c>
       <c r="H1345" t="n">
         <v>19625</v>
@@ -39432,7 +39432,7 @@
         <v>13.0500001907349</v>
       </c>
       <c r="G1347" t="n">
-        <v>12.0190668106079</v>
+        <v>12.0190677642822</v>
       </c>
       <c r="H1347" t="n">
         <v>10398</v>
@@ -39461,7 +39461,7 @@
         <v>12.8999996185303</v>
       </c>
       <c r="G1348" t="n">
-        <v>11.880916595459</v>
+        <v>11.8809156417847</v>
       </c>
       <c r="H1348" t="n">
         <v>10513</v>
@@ -39490,7 +39490,7 @@
         <v>12.8000001907349</v>
       </c>
       <c r="G1349" t="n">
-        <v>11.7888174057007</v>
+        <v>11.7888164520264</v>
       </c>
       <c r="H1349" t="n">
         <v>24319</v>
@@ -39519,7 +39519,7 @@
         <v>13.1000003814697</v>
       </c>
       <c r="G1350" t="n">
-        <v>12.0651168823242</v>
+        <v>12.0651178359985</v>
       </c>
       <c r="H1350" t="n">
         <v>17127</v>
@@ -39577,7 +39577,7 @@
         <v>13.0500001907349</v>
       </c>
       <c r="G1352" t="n">
-        <v>12.0190668106079</v>
+        <v>12.0190677642822</v>
       </c>
       <c r="H1352" t="n">
         <v>25648</v>
@@ -39606,7 +39606,7 @@
         <v>12.6999998092651</v>
       </c>
       <c r="G1353" t="n">
-        <v>11.6967172622681</v>
+        <v>11.6967163085938</v>
       </c>
       <c r="H1353" t="n">
         <v>18107</v>
@@ -39635,7 +39635,7 @@
         <v>12.8500003814697</v>
       </c>
       <c r="G1354" t="n">
-        <v>11.834867477417</v>
+        <v>11.8348665237427</v>
       </c>
       <c r="H1354" t="n">
         <v>8453</v>
@@ -39664,7 +39664,7 @@
         <v>13.1000003814697</v>
       </c>
       <c r="G1355" t="n">
-        <v>12.0651168823242</v>
+        <v>12.0651178359985</v>
       </c>
       <c r="H1355" t="n">
         <v>16860</v>
@@ -39751,7 +39751,7 @@
         <v>12.6999998092651</v>
       </c>
       <c r="G1358" t="n">
-        <v>11.6967172622681</v>
+        <v>11.6967163085938</v>
       </c>
       <c r="H1358" t="n">
         <v>15150</v>
@@ -39780,7 +39780,7 @@
         <v>12.25</v>
       </c>
       <c r="G1359" t="n">
-        <v>11.282265663147</v>
+        <v>11.2822647094727</v>
       </c>
       <c r="H1359" t="n">
         <v>42261</v>
@@ -39809,7 +39809,7 @@
         <v>12</v>
       </c>
       <c r="G1360" t="n">
-        <v>11.0520153045654</v>
+        <v>11.0520162582397</v>
       </c>
       <c r="H1360" t="n">
         <v>9891</v>
@@ -39867,7 +39867,7 @@
         <v>12.4499998092651</v>
       </c>
       <c r="G1362" t="n">
-        <v>11.4664659500122</v>
+        <v>11.4664669036865</v>
       </c>
       <c r="H1362" t="n">
         <v>9865</v>
@@ -39983,7 +39983,7 @@
         <v>11.6999998092651</v>
       </c>
       <c r="G1366" t="n">
-        <v>10.7757158279419</v>
+        <v>10.7757148742676</v>
       </c>
       <c r="H1366" t="n">
         <v>4839</v>
@@ -40041,7 +40041,7 @@
         <v>11.6999998092651</v>
       </c>
       <c r="G1368" t="n">
-        <v>10.7757158279419</v>
+        <v>10.7757148742676</v>
       </c>
       <c r="H1368" t="n">
         <v>10060</v>
@@ -40070,7 +40070,7 @@
         <v>11.6999998092651</v>
       </c>
       <c r="G1369" t="n">
-        <v>10.7757158279419</v>
+        <v>10.7757148742676</v>
       </c>
       <c r="H1369" t="n">
         <v>8696</v>
@@ -40099,7 +40099,7 @@
         <v>11.9499998092651</v>
       </c>
       <c r="G1370" t="n">
-        <v>11.0059652328491</v>
+        <v>11.0059671401978</v>
       </c>
       <c r="H1370" t="n">
         <v>8903</v>
@@ -40128,7 +40128,7 @@
         <v>12</v>
       </c>
       <c r="G1371" t="n">
-        <v>11.0520153045654</v>
+        <v>11.0520162582397</v>
       </c>
       <c r="H1371" t="n">
         <v>4332</v>
@@ -40157,7 +40157,7 @@
         <v>12.3500003814697</v>
       </c>
       <c r="G1372" t="n">
-        <v>11.3743667602539</v>
+        <v>11.3743658065796</v>
       </c>
       <c r="H1372" t="n">
         <v>2891</v>
@@ -40186,7 +40186,7 @@
         <v>12.1000003814697</v>
       </c>
       <c r="G1373" t="n">
-        <v>11.1441164016724</v>
+        <v>11.144115447998</v>
       </c>
       <c r="H1373" t="n">
         <v>3062</v>
@@ -40215,7 +40215,7 @@
         <v>12.0500001907349</v>
       </c>
       <c r="G1374" t="n">
-        <v>11.0980663299561</v>
+        <v>11.0980653762817</v>
       </c>
       <c r="H1374" t="n">
         <v>6759</v>
@@ -40273,7 +40273,7 @@
         <v>12.4499998092651</v>
       </c>
       <c r="G1376" t="n">
-        <v>11.4664659500122</v>
+        <v>11.4664669036865</v>
       </c>
       <c r="H1376" t="n">
         <v>6250</v>
@@ -40331,7 +40331,7 @@
         <v>12.8500003814697</v>
       </c>
       <c r="G1378" t="n">
-        <v>11.834867477417</v>
+        <v>11.8348665237427</v>
       </c>
       <c r="H1378" t="n">
         <v>2949</v>
@@ -40360,7 +40360,7 @@
         <v>13.0500001907349</v>
       </c>
       <c r="G1379" t="n">
-        <v>12.0190668106079</v>
+        <v>12.0190677642822</v>
       </c>
       <c r="H1379" t="n">
         <v>8883</v>
@@ -40389,7 +40389,7 @@
         <v>12.8999996185303</v>
       </c>
       <c r="G1380" t="n">
-        <v>11.880916595459</v>
+        <v>11.8809156417847</v>
       </c>
       <c r="H1380" t="n">
         <v>3352</v>
@@ -40534,7 +40534,7 @@
         <v>13.5500001907349</v>
       </c>
       <c r="G1385" t="n">
-        <v>12.4795665740967</v>
+        <v>12.479567527771</v>
       </c>
       <c r="H1385" t="n">
         <v>10551</v>
@@ -40563,7 +40563,7 @@
         <v>11.75</v>
       </c>
       <c r="G1386" t="n">
-        <v>10.8217658996582</v>
+        <v>10.8217649459839</v>
       </c>
       <c r="H1386" t="n">
         <v>92513</v>
@@ -40650,7 +40650,7 @@
         <v>9.14999961853027</v>
       </c>
       <c r="G1389" t="n">
-        <v>8.42716312408447</v>
+        <v>8.42716217041016</v>
       </c>
       <c r="H1389" t="n">
         <v>114134</v>
@@ -40737,7 +40737,7 @@
         <v>9.19999980926514</v>
       </c>
       <c r="G1392" t="n">
-        <v>8.47321224212646</v>
+        <v>8.47321128845215</v>
       </c>
       <c r="H1392" t="n">
         <v>43171</v>
@@ -40795,7 +40795,7 @@
         <v>8.89000034332275</v>
       </c>
       <c r="G1394" t="n">
-        <v>8.18770122528076</v>
+        <v>8.18770217895508</v>
       </c>
       <c r="H1394" t="n">
         <v>15541</v>
@@ -40824,7 +40824,7 @@
         <v>8.8100004196167</v>
       </c>
       <c r="G1395" t="n">
-        <v>8.11402320861816</v>
+        <v>8.11402225494385</v>
       </c>
       <c r="H1395" t="n">
         <v>15373</v>
@@ -40853,7 +40853,7 @@
         <v>9</v>
       </c>
       <c r="G1396" t="n">
-        <v>8.28901195526123</v>
+        <v>8.28901290893555</v>
       </c>
       <c r="H1396" t="n">
         <v>6827</v>
@@ -40882,7 +40882,7 @@
         <v>9.03999996185303</v>
       </c>
       <c r="G1397" t="n">
-        <v>8.325852394104</v>
+        <v>8.32585144042969</v>
       </c>
       <c r="H1397" t="n">
         <v>49566</v>
@@ -40969,7 +40969,7 @@
         <v>8.63000011444092</v>
       </c>
       <c r="G1400" t="n">
-        <v>7.9482421875</v>
+        <v>7.94824028015137</v>
       </c>
       <c r="H1400" t="n">
         <v>11269</v>
@@ -40998,7 +40998,7 @@
         <v>8.3100004196167</v>
       </c>
       <c r="G1401" t="n">
-        <v>7.6535210609436</v>
+        <v>7.65352058410645</v>
       </c>
       <c r="H1401" t="n">
         <v>21362</v>
@@ -41027,7 +41027,7 @@
         <v>8</v>
       </c>
       <c r="G1402" t="n">
-        <v>7.36801052093506</v>
+        <v>7.3680100440979</v>
       </c>
       <c r="H1402" t="n">
         <v>23498</v>
@@ -41114,7 +41114,7 @@
         <v>8.35999965667725</v>
       </c>
       <c r="G1405" t="n">
-        <v>7.69957113265991</v>
+        <v>7.6995701789856</v>
       </c>
       <c r="H1405" t="n">
         <v>38004</v>
@@ -41172,7 +41172,7 @@
         <v>8.01000022888184</v>
       </c>
       <c r="G1407" t="n">
-        <v>7.37722063064575</v>
+        <v>7.37722015380859</v>
       </c>
       <c r="H1407" t="n">
         <v>9665</v>
@@ -41201,7 +41201,7 @@
         <v>7.86999988555908</v>
       </c>
       <c r="G1408" t="n">
-        <v>7.24828052520752</v>
+        <v>7.24828004837036</v>
       </c>
       <c r="H1408" t="n">
         <v>10131</v>
@@ -41230,7 +41230,7 @@
         <v>7.59999990463257</v>
       </c>
       <c r="G1409" t="n">
-        <v>6.99960994720459</v>
+        <v>6.99960947036743</v>
       </c>
       <c r="H1409" t="n">
         <v>28306</v>
@@ -41462,7 +41462,7 @@
         <v>8.63000011444092</v>
       </c>
       <c r="G1417" t="n">
-        <v>7.9482421875</v>
+        <v>7.94824028015137</v>
       </c>
       <c r="H1417" t="n">
         <v>40461</v>
@@ -41520,7 +41520,7 @@
         <v>8.77000045776367</v>
       </c>
       <c r="G1419" t="n">
-        <v>8.07718276977539</v>
+        <v>8.07718181610107</v>
       </c>
       <c r="H1419" t="n">
         <v>21481</v>
@@ -41549,7 +41549,7 @@
         <v>9</v>
       </c>
       <c r="G1420" t="n">
-        <v>8.28901195526123</v>
+        <v>8.28901290893555</v>
       </c>
       <c r="H1420" t="n">
         <v>62353</v>
@@ -41665,7 +41665,7 @@
         <v>9.10000038146973</v>
       </c>
       <c r="G1424" t="n">
-        <v>8.53280639648438</v>
+        <v>8.53280735015869</v>
       </c>
       <c r="H1424" t="n">
         <v>15786</v>
@@ -41752,7 +41752,7 @@
         <v>9.10000038146973</v>
       </c>
       <c r="G1427" t="n">
-        <v>8.53280639648438</v>
+        <v>8.53280735015869</v>
       </c>
       <c r="H1427" t="n">
         <v>17846</v>
@@ -41897,7 +41897,7 @@
         <v>8.80000019073486</v>
       </c>
       <c r="G1432" t="n">
-        <v>8.25150489807129</v>
+        <v>8.25150585174561</v>
       </c>
       <c r="H1432" t="n">
         <v>9669</v>
@@ -41926,7 +41926,7 @@
         <v>9.02000045776367</v>
       </c>
       <c r="G1433" t="n">
-        <v>8.45779418945312</v>
+        <v>8.45779323577881</v>
       </c>
       <c r="H1433" t="n">
         <v>12940</v>
@@ -41984,7 +41984,7 @@
         <v>8.69999980926514</v>
       </c>
       <c r="G1435" t="n">
-        <v>8.15773773193359</v>
+        <v>8.15773868560791</v>
       </c>
       <c r="H1435" t="n">
         <v>13463</v>
@@ -42100,7 +42100,7 @@
         <v>8.22000026702881</v>
       </c>
       <c r="G1439" t="n">
-        <v>7.70765590667725</v>
+        <v>7.7076563835144</v>
       </c>
       <c r="H1439" t="n">
         <v>3073</v>
@@ -42361,7 +42361,7 @@
         <v>8.46000003814697</v>
       </c>
       <c r="G1448" t="n">
-        <v>7.93269729614258</v>
+        <v>7.93269634246826</v>
       </c>
       <c r="H1448" t="n">
         <v>7163</v>
@@ -42419,7 +42419,7 @@
         <v>8.36999988555908</v>
       </c>
       <c r="G1450" t="n">
-        <v>7.84830617904663</v>
+        <v>7.84830713272095</v>
       </c>
       <c r="H1450" t="n">
         <v>1746</v>
@@ -42535,7 +42535,7 @@
         <v>8.57999992370605</v>
       </c>
       <c r="G1454" t="n">
-        <v>8.04521751403809</v>
+        <v>8.0452184677124</v>
       </c>
       <c r="H1454" t="n">
         <v>2825</v>
@@ -42651,7 +42651,7 @@
         <v>8.36999988555908</v>
       </c>
       <c r="G1458" t="n">
-        <v>7.84830617904663</v>
+        <v>7.84830713272095</v>
       </c>
       <c r="H1458" t="n">
         <v>5445</v>
@@ -42738,7 +42738,7 @@
         <v>8.23999977111816</v>
       </c>
       <c r="G1461" t="n">
-        <v>7.7264084815979</v>
+        <v>7.72640943527222</v>
       </c>
       <c r="H1461" t="n">
         <v>7810</v>
@@ -42912,7 +42912,7 @@
         <v>8.14000034332275</v>
       </c>
       <c r="G1467" t="n">
-        <v>7.63264226913452</v>
+        <v>7.63264274597168</v>
       </c>
       <c r="H1467" t="n">
         <v>7352</v>
@@ -42941,7 +42941,7 @@
         <v>8.10000038146973</v>
       </c>
       <c r="G1468" t="n">
-        <v>7.59513568878174</v>
+        <v>7.5951361656189</v>
       </c>
       <c r="H1468" t="n">
         <v>10532</v>
@@ -43028,7 +43028,7 @@
         <v>8.02999973297119</v>
       </c>
       <c r="G1471" t="n">
-        <v>7.52949810028076</v>
+        <v>7.52949857711792</v>
       </c>
       <c r="H1471" t="n">
         <v>8187</v>
@@ -43086,7 +43086,7 @@
         <v>8.72999954223633</v>
       </c>
       <c r="G1473" t="n">
-        <v>8.18586826324463</v>
+        <v>8.18586730957031</v>
       </c>
       <c r="H1473" t="n">
         <v>27107</v>
@@ -43115,7 +43115,7 @@
         <v>8.51000022888184</v>
       </c>
       <c r="G1474" t="n">
-        <v>7.97958040237427</v>
+        <v>7.97958087921143</v>
       </c>
       <c r="H1474" t="n">
         <v>17996</v>
@@ -43144,7 +43144,7 @@
         <v>8.31999969482422</v>
       </c>
       <c r="G1475" t="n">
-        <v>7.8014235496521</v>
+        <v>7.80142259597778</v>
       </c>
       <c r="H1475" t="n">
         <v>6885</v>
@@ -43173,7 +43173,7 @@
         <v>8.59000015258789</v>
       </c>
       <c r="G1476" t="n">
-        <v>8.05459499359131</v>
+        <v>8.05459403991699</v>
       </c>
       <c r="H1476" t="n">
         <v>5022</v>
@@ -43231,7 +43231,7 @@
         <v>8.63000011444092</v>
       </c>
       <c r="G1478" t="n">
-        <v>8.09210205078125</v>
+        <v>8.09210109710693</v>
       </c>
       <c r="H1478" t="n">
         <v>2527</v>
@@ -43260,7 +43260,7 @@
         <v>8.72000026702881</v>
       </c>
       <c r="G1479" t="n">
-        <v>8.17649173736572</v>
+        <v>8.17649269104004</v>
       </c>
       <c r="H1479" t="n">
         <v>2805</v>
@@ -43463,7 +43463,7 @@
         <v>8.69999980926514</v>
       </c>
       <c r="G1486" t="n">
-        <v>8.15773773193359</v>
+        <v>8.15773868560791</v>
       </c>
       <c r="H1486" t="n">
         <v>2443</v>
@@ -43637,7 +43637,7 @@
         <v>8.23999977111816</v>
       </c>
       <c r="G1492" t="n">
-        <v>7.7264084815979</v>
+        <v>7.72640943527222</v>
       </c>
       <c r="H1492" t="n">
         <v>7241</v>
@@ -43695,7 +43695,7 @@
         <v>8.19999980926514</v>
       </c>
       <c r="G1494" t="n">
-        <v>7.68890237808228</v>
+        <v>7.68890285491943</v>
       </c>
       <c r="H1494" t="n">
         <v>4819</v>
@@ -43724,7 +43724,7 @@
         <v>8.19999980926514</v>
       </c>
       <c r="G1495" t="n">
-        <v>7.68890237808228</v>
+        <v>7.68890285491943</v>
       </c>
       <c r="H1495" t="n">
         <v>1979</v>
@@ -43753,7 +43753,7 @@
         <v>8.35999965667725</v>
       </c>
       <c r="G1496" t="n">
-        <v>7.83893013000488</v>
+        <v>7.83892917633057</v>
       </c>
       <c r="H1496" t="n">
         <v>3456</v>
@@ -43811,7 +43811,7 @@
         <v>8.36999988555908</v>
       </c>
       <c r="G1498" t="n">
-        <v>7.84830617904663</v>
+        <v>7.84830713272095</v>
       </c>
       <c r="H1498" t="n">
         <v>7184</v>
@@ -44072,7 +44072,7 @@
         <v>8.10000038146973</v>
       </c>
       <c r="G1507" t="n">
-        <v>7.59513568878174</v>
+        <v>7.5951361656189</v>
       </c>
       <c r="H1507" t="n">
         <v>1395</v>
@@ -44101,7 +44101,7 @@
         <v>8.19999980926514</v>
       </c>
       <c r="G1508" t="n">
-        <v>7.68890237808228</v>
+        <v>7.68890285491943</v>
       </c>
       <c r="H1508" t="n">
         <v>831</v>
@@ -44130,7 +44130,7 @@
         <v>8.10999965667725</v>
       </c>
       <c r="G1509" t="n">
-        <v>7.60451173782349</v>
+        <v>7.60451221466064</v>
       </c>
       <c r="H1509" t="n">
         <v>3386</v>
@@ -44217,7 +44217,7 @@
         <v>7.96000003814697</v>
       </c>
       <c r="G1512" t="n">
-        <v>7.4638614654541</v>
+        <v>7.46386194229126</v>
       </c>
       <c r="H1512" t="n">
         <v>1387</v>
@@ -44275,7 +44275,7 @@
         <v>7.90000009536743</v>
       </c>
       <c r="G1514" t="n">
-        <v>7.40760183334351</v>
+        <v>7.40760135650635</v>
       </c>
       <c r="H1514" t="n">
         <v>2950</v>
@@ -44333,7 +44333,7 @@
         <v>7.98999977111816</v>
       </c>
       <c r="G1516" t="n">
-        <v>7.49199151992798</v>
+        <v>7.49199104309082</v>
       </c>
       <c r="H1516" t="n">
         <v>1046</v>
@@ -44507,7 +44507,7 @@
         <v>7.53000020980835</v>
       </c>
       <c r="G1522" t="n">
-        <v>7.06066274642944</v>
+        <v>7.0606632232666</v>
       </c>
       <c r="H1522" t="n">
         <v>4031</v>
@@ -44565,7 +44565,7 @@
         <v>7.46999979019165</v>
       </c>
       <c r="G1524" t="n">
-        <v>7.00440263748169</v>
+        <v>7.00440216064453</v>
       </c>
       <c r="H1524" t="n">
         <v>1166</v>
@@ -44594,7 +44594,7 @@
         <v>7.57999992370605</v>
       </c>
       <c r="G1525" t="n">
-        <v>7.10754585266113</v>
+        <v>7.10754632949829</v>
       </c>
       <c r="H1525" t="n">
         <v>15647</v>
@@ -44826,7 +44826,7 @@
         <v>7.80999994277954</v>
       </c>
       <c r="G1533" t="n">
-        <v>7.32321071624756</v>
+        <v>7.32321119308472</v>
       </c>
       <c r="H1533" t="n">
         <v>459</v>
@@ -44855,7 +44855,7 @@
         <v>7.6399998664856</v>
       </c>
       <c r="G1534" t="n">
-        <v>7.1638069152832</v>
+        <v>7.16380643844604</v>
       </c>
       <c r="H1534" t="n">
         <v>7564</v>
@@ -44884,7 +44884,7 @@
         <v>7.75</v>
       </c>
       <c r="G1535" t="n">
-        <v>7.26695013046265</v>
+        <v>7.2669506072998</v>
       </c>
       <c r="H1535" t="n">
         <v>4595</v>
@@ -44942,7 +44942,7 @@
         <v>7.69000005722046</v>
       </c>
       <c r="G1537" t="n">
-        <v>7.21069049835205</v>
+        <v>7.21069002151489</v>
       </c>
       <c r="H1537" t="n">
         <v>210</v>
@@ -45000,7 +45000,7 @@
         <v>7.69000005722046</v>
       </c>
       <c r="G1539" t="n">
-        <v>7.21069049835205</v>
+        <v>7.21069002151489</v>
       </c>
       <c r="H1539" t="n">
         <v>60</v>
@@ -45087,7 +45087,7 @@
         <v>7.96000003814697</v>
       </c>
       <c r="G1542" t="n">
-        <v>7.4638614654541</v>
+        <v>7.46386194229126</v>
       </c>
       <c r="H1542" t="n">
         <v>2633</v>
@@ -45145,7 +45145,7 @@
         <v>8.32999992370605</v>
       </c>
       <c r="G1544" t="n">
-        <v>7.81080007553101</v>
+        <v>7.81079912185669</v>
       </c>
       <c r="H1544" t="n">
         <v>6825</v>
@@ -45174,7 +45174,7 @@
         <v>8.10000038146973</v>
       </c>
       <c r="G1545" t="n">
-        <v>7.59513568878174</v>
+        <v>7.5951361656189</v>
       </c>
       <c r="H1545" t="n">
         <v>3886</v>
@@ -45232,7 +45232,7 @@
         <v>7.82000017166138</v>
       </c>
       <c r="G1547" t="n">
-        <v>7.33258724212646</v>
+        <v>7.33258771896362</v>
       </c>
       <c r="H1547" t="n">
         <v>4523</v>
@@ -45261,7 +45261,7 @@
         <v>8.07999992370605</v>
       </c>
       <c r="G1548" t="n">
-        <v>7.57638168334961</v>
+        <v>7.57638216018677</v>
       </c>
       <c r="H1548" t="n">
         <v>7143</v>
@@ -45290,7 +45290,7 @@
         <v>8.07999992370605</v>
       </c>
       <c r="G1549" t="n">
-        <v>7.57638168334961</v>
+        <v>7.57638216018677</v>
       </c>
       <c r="H1549" t="n">
         <v>4415</v>
@@ -45435,7 +45435,7 @@
         <v>8.19999980926514</v>
       </c>
       <c r="G1554" t="n">
-        <v>7.68890237808228</v>
+        <v>7.68890285491943</v>
       </c>
       <c r="H1554" t="n">
         <v>798</v>
@@ -45725,7 +45725,7 @@
         <v>8.31999969482422</v>
       </c>
       <c r="G1564" t="n">
-        <v>7.8014235496521</v>
+        <v>7.80142259597778</v>
       </c>
       <c r="H1564" t="n">
         <v>42119</v>
@@ -45812,7 +45812,7 @@
         <v>8.35999965667725</v>
       </c>
       <c r="G1567" t="n">
-        <v>7.83893013000488</v>
+        <v>7.83892917633057</v>
       </c>
       <c r="H1567" t="n">
         <v>10959</v>
@@ -45928,7 +45928,7 @@
         <v>8.13000011444092</v>
       </c>
       <c r="G1571" t="n">
-        <v>7.62326574325562</v>
+        <v>7.62326526641846</v>
       </c>
       <c r="H1571" t="n">
         <v>364</v>
@@ -45957,7 +45957,7 @@
         <v>8.1899995803833</v>
       </c>
       <c r="G1572" t="n">
-        <v>7.67952537536621</v>
+        <v>7.67952489852905</v>
       </c>
       <c r="H1572" t="n">
         <v>1114</v>
@@ -45986,7 +45986,7 @@
         <v>8.17000007629395</v>
       </c>
       <c r="G1573" t="n">
-        <v>7.66077280044556</v>
+        <v>7.66077327728271</v>
       </c>
       <c r="H1573" t="n">
         <v>16</v>
@@ -46189,7 +46189,7 @@
         <v>8.32999992370605</v>
       </c>
       <c r="G1580" t="n">
-        <v>7.81080007553101</v>
+        <v>7.81079912185669</v>
       </c>
       <c r="H1580" t="n">
         <v>12</v>
@@ -46218,7 +46218,7 @@
         <v>8.31999969482422</v>
       </c>
       <c r="G1581" t="n">
-        <v>7.8014235496521</v>
+        <v>7.80142259597778</v>
       </c>
       <c r="H1581" t="n">
         <v>4632</v>
@@ -46247,7 +46247,7 @@
         <v>8.32999992370605</v>
       </c>
       <c r="G1582" t="n">
-        <v>7.81080007553101</v>
+        <v>7.81079912185669</v>
       </c>
       <c r="H1582" t="n">
         <v>1433</v>
@@ -46276,7 +46276,7 @@
         <v>8.31999969482422</v>
       </c>
       <c r="G1583" t="n">
-        <v>7.8014235496521</v>
+        <v>7.80142259597778</v>
       </c>
       <c r="H1583" t="n">
         <v>218</v>
@@ -46363,7 +46363,7 @@
         <v>8.23999977111816</v>
       </c>
       <c r="G1586" t="n">
-        <v>7.7264084815979</v>
+        <v>7.72640943527222</v>
       </c>
       <c r="H1586" t="n">
         <v>370</v>
@@ -46392,7 +46392,7 @@
         <v>8.23999977111816</v>
       </c>
       <c r="G1587" t="n">
-        <v>7.7264084815979</v>
+        <v>7.72640943527222</v>
       </c>
       <c r="H1587" t="n">
         <v>1309</v>
@@ -46421,7 +46421,7 @@
         <v>8.10000038146973</v>
       </c>
       <c r="G1588" t="n">
-        <v>7.59513568878174</v>
+        <v>7.5951361656189</v>
       </c>
       <c r="H1588" t="n">
         <v>2104</v>
@@ -46450,7 +46450,7 @@
         <v>8.18000030517578</v>
       </c>
       <c r="G1589" t="n">
-        <v>7.67014932632446</v>
+        <v>7.67014980316162</v>
       </c>
       <c r="H1589" t="n">
         <v>2104</v>
@@ -46479,7 +46479,7 @@
         <v>8.10999965667725</v>
       </c>
       <c r="G1590" t="n">
-        <v>7.60451173782349</v>
+        <v>7.60451221466064</v>
       </c>
       <c r="H1590" t="n">
         <v>1937</v>
@@ -46508,7 +46508,7 @@
         <v>8.10000038146973</v>
       </c>
       <c r="G1591" t="n">
-        <v>7.59513568878174</v>
+        <v>7.5951361656189</v>
       </c>
       <c r="H1591" t="n">
         <v>5358</v>
@@ -46537,7 +46537,7 @@
         <v>8.18000030517578</v>
       </c>
       <c r="G1592" t="n">
-        <v>7.67014932632446</v>
+        <v>7.67014980316162</v>
       </c>
       <c r="H1592" t="n">
         <v>5541</v>
@@ -46566,7 +46566,7 @@
         <v>8.18000030517578</v>
       </c>
       <c r="G1593" t="n">
-        <v>7.67014932632446</v>
+        <v>7.67014980316162</v>
       </c>
       <c r="H1593" t="n">
         <v>8319</v>
@@ -46595,7 +46595,7 @@
         <v>8.19999980926514</v>
       </c>
       <c r="G1594" t="n">
-        <v>7.68890237808228</v>
+        <v>7.68890285491943</v>
       </c>
       <c r="H1594" t="n">
         <v>200</v>
@@ -46624,7 +46624,7 @@
         <v>8.22000026702881</v>
       </c>
       <c r="G1595" t="n">
-        <v>7.70765590667725</v>
+        <v>7.7076563835144</v>
       </c>
       <c r="H1595" t="n">
         <v>1653</v>
@@ -46653,7 +46653,7 @@
         <v>8.22999954223633</v>
       </c>
       <c r="G1596" t="n">
-        <v>7.71703243255615</v>
+        <v>7.71703195571899</v>
       </c>
       <c r="H1596" t="n">
         <v>1071</v>
@@ -46682,7 +46682,7 @@
         <v>8.19999980926514</v>
       </c>
       <c r="G1597" t="n">
-        <v>7.68890237808228</v>
+        <v>7.68890285491943</v>
       </c>
       <c r="H1597" t="n">
         <v>3243</v>
@@ -46711,7 +46711,7 @@
         <v>8.19999980926514</v>
       </c>
       <c r="G1598" t="n">
-        <v>7.68890237808228</v>
+        <v>7.68890285491943</v>
       </c>
       <c r="H1598" t="n">
         <v>10131</v>
@@ -46769,7 +46769,7 @@
         <v>8.19999980926514</v>
       </c>
       <c r="G1600" t="n">
-        <v>7.68890237808228</v>
+        <v>7.68890285491943</v>
       </c>
       <c r="H1600" t="n">
         <v>3694</v>
@@ -46798,7 +46798,7 @@
         <v>8.19999980926514</v>
       </c>
       <c r="G1601" t="n">
-        <v>7.68890237808228</v>
+        <v>7.68890285491943</v>
       </c>
       <c r="H1601" t="n">
         <v>7348</v>
@@ -46827,7 +46827,7 @@
         <v>8.19999980926514</v>
       </c>
       <c r="G1602" t="n">
-        <v>7.68890237808228</v>
+        <v>7.68890285491943</v>
       </c>
       <c r="H1602" t="n">
         <v>200</v>
@@ -46885,7 +46885,7 @@
         <v>8.19999980926514</v>
       </c>
       <c r="G1604" t="n">
-        <v>7.68890237808228</v>
+        <v>7.68890285491943</v>
       </c>
       <c r="H1604" t="n">
         <v>10056</v>
@@ -46972,7 +46972,7 @@
         <v>8.14000034332275</v>
       </c>
       <c r="G1607" t="n">
-        <v>7.63264226913452</v>
+        <v>7.63264274597168</v>
       </c>
       <c r="H1607" t="n">
         <v>3200</v>
@@ -47001,7 +47001,7 @@
         <v>8.10000038146973</v>
       </c>
       <c r="G1608" t="n">
-        <v>7.59513568878174</v>
+        <v>7.5951361656189</v>
       </c>
       <c r="H1608" t="n">
         <v>2829</v>
@@ -47030,7 +47030,7 @@
         <v>8.18000030517578</v>
       </c>
       <c r="G1609" t="n">
-        <v>7.67014932632446</v>
+        <v>7.67014980316162</v>
       </c>
       <c r="H1609" t="n">
         <v>6376</v>
@@ -47117,7 +47117,7 @@
         <v>7.96999979019165</v>
       </c>
       <c r="G1612" t="n">
-        <v>7.47323799133301</v>
+        <v>7.47323751449585</v>
       </c>
       <c r="H1612" t="n">
         <v>3428</v>
@@ -47146,7 +47146,7 @@
         <v>7.96999979019165</v>
       </c>
       <c r="G1613" t="n">
-        <v>7.47323799133301</v>
+        <v>7.47323751449585</v>
       </c>
       <c r="H1613" t="n">
         <v>6427</v>
@@ -47233,7 +47233,7 @@
         <v>8.14000034332275</v>
       </c>
       <c r="G1616" t="n">
-        <v>7.63264226913452</v>
+        <v>7.63264274597168</v>
       </c>
       <c r="H1616" t="n">
         <v>5441</v>
@@ -47262,7 +47262,7 @@
         <v>8.27000045776367</v>
       </c>
       <c r="G1617" t="n">
-        <v>7.75453996658325</v>
+        <v>7.75454092025757</v>
       </c>
       <c r="H1617" t="n">
         <v>27464</v>
@@ -47291,7 +47291,7 @@
         <v>8.10999965667725</v>
       </c>
       <c r="G1618" t="n">
-        <v>7.60451173782349</v>
+        <v>7.60451221466064</v>
       </c>
       <c r="H1618" t="n">
         <v>1085</v>
@@ -47320,7 +47320,7 @@
         <v>8.23999977111816</v>
       </c>
       <c r="G1619" t="n">
-        <v>7.7264084815979</v>
+        <v>7.72640943527222</v>
       </c>
       <c r="H1619" t="n">
         <v>22090</v>
@@ -47407,7 +47407,7 @@
         <v>8.31999969482422</v>
       </c>
       <c r="G1622" t="n">
-        <v>7.8014235496521</v>
+        <v>7.80142259597778</v>
       </c>
       <c r="H1622" t="n">
         <v>39241</v>
@@ -47697,7 +47697,7 @@
         <v>8.31999969482422</v>
       </c>
       <c r="G1632" t="n">
-        <v>7.8014235496521</v>
+        <v>7.80142259597778</v>
       </c>
       <c r="H1632" t="n">
         <v>3163</v>
@@ -47726,7 +47726,7 @@
         <v>8.31999969482422</v>
       </c>
       <c r="G1633" t="n">
-        <v>7.8014235496521</v>
+        <v>7.80142259597778</v>
       </c>
       <c r="H1633" t="n">
         <v>6253</v>
@@ -47813,7 +47813,7 @@
         <v>8.17000007629395</v>
       </c>
       <c r="G1636" t="n">
-        <v>7.66077280044556</v>
+        <v>7.66077327728271</v>
       </c>
       <c r="H1636" t="n">
         <v>1895</v>
@@ -48016,7 +48016,7 @@
         <v>8.35999965667725</v>
       </c>
       <c r="G1643" t="n">
-        <v>7.83893013000488</v>
+        <v>7.83892917633057</v>
       </c>
       <c r="H1643" t="n">
         <v>14035</v>
@@ -48045,7 +48045,7 @@
         <v>8.32999992370605</v>
       </c>
       <c r="G1644" t="n">
-        <v>7.81080007553101</v>
+        <v>7.81079912185669</v>
       </c>
       <c r="H1644" t="n">
         <v>10427</v>
@@ -48074,7 +48074,7 @@
         <v>8.31999969482422</v>
       </c>
       <c r="G1645" t="n">
-        <v>7.8014235496521</v>
+        <v>7.80142259597778</v>
       </c>
       <c r="H1645" t="n">
         <v>3390</v>
@@ -48103,7 +48103,7 @@
         <v>8.36999988555908</v>
       </c>
       <c r="G1646" t="n">
-        <v>7.84830617904663</v>
+        <v>7.84830713272095</v>
       </c>
       <c r="H1646" t="n">
         <v>16906</v>
@@ -48161,7 +48161,7 @@
         <v>8.22000026702881</v>
       </c>
       <c r="G1648" t="n">
-        <v>7.70765590667725</v>
+        <v>7.7076563835144</v>
       </c>
       <c r="H1648" t="n">
         <v>5676</v>
@@ -48190,7 +48190,7 @@
         <v>8.31999969482422</v>
       </c>
       <c r="G1649" t="n">
-        <v>7.8014235496521</v>
+        <v>7.80142259597778</v>
       </c>
       <c r="H1649" t="n">
         <v>1791</v>
@@ -48277,7 +48277,7 @@
         <v>8.22000026702881</v>
       </c>
       <c r="G1652" t="n">
-        <v>7.70765590667725</v>
+        <v>7.7076563835144</v>
       </c>
       <c r="H1652" t="n">
         <v>1737</v>
@@ -48306,7 +48306,7 @@
         <v>8.35999965667725</v>
       </c>
       <c r="G1653" t="n">
-        <v>7.83893013000488</v>
+        <v>7.83892917633057</v>
       </c>
       <c r="H1653" t="n">
         <v>19707</v>
@@ -48364,7 +48364,7 @@
         <v>8.10000038146973</v>
       </c>
       <c r="G1655" t="n">
-        <v>7.59513568878174</v>
+        <v>7.5951361656189</v>
       </c>
       <c r="H1655" t="n">
         <v>13506</v>
@@ -48422,7 +48422,7 @@
         <v>8.14000034332275</v>
       </c>
       <c r="G1657" t="n">
-        <v>7.63264226913452</v>
+        <v>7.63264274597168</v>
       </c>
       <c r="H1657" t="n">
         <v>1682</v>
@@ -48451,7 +48451,7 @@
         <v>8.14000034332275</v>
       </c>
       <c r="G1658" t="n">
-        <v>7.63264226913452</v>
+        <v>7.63264274597168</v>
       </c>
       <c r="H1658" t="n">
         <v>0</v>
@@ -48480,7 +48480,7 @@
         <v>8.13000011444092</v>
       </c>
       <c r="G1659" t="n">
-        <v>7.62326574325562</v>
+        <v>7.62326526641846</v>
       </c>
       <c r="H1659" t="n">
         <v>5403</v>
@@ -48509,7 +48509,7 @@
         <v>8.13000011444092</v>
       </c>
       <c r="G1660" t="n">
-        <v>7.62326574325562</v>
+        <v>7.62326526641846</v>
       </c>
       <c r="H1660" t="n">
         <v>277</v>
@@ -48567,7 +48567,7 @@
         <v>7.75</v>
       </c>
       <c r="G1662" t="n">
-        <v>7.26695013046265</v>
+        <v>7.2669506072998</v>
       </c>
       <c r="H1662" t="n">
         <v>5323</v>
@@ -48654,7 +48654,7 @@
         <v>7.82000017166138</v>
       </c>
       <c r="G1665" t="n">
-        <v>7.33258724212646</v>
+        <v>7.33258771896362</v>
       </c>
       <c r="H1665" t="n">
         <v>11862</v>
@@ -48915,7 +48915,7 @@
         <v>7.40000009536743</v>
       </c>
       <c r="G1674" t="n">
-        <v>6.93876600265503</v>
+        <v>6.93876552581787</v>
       </c>
       <c r="H1674" t="n">
         <v>15401</v>
@@ -48944,7 +48944,7 @@
         <v>7.40000009536743</v>
       </c>
       <c r="G1675" t="n">
-        <v>6.93876600265503</v>
+        <v>6.93876552581787</v>
       </c>
       <c r="H1675" t="n">
         <v>118167</v>
@@ -74110,7 +74110,7 @@
         <v>6.57999992370605</v>
       </c>
       <c r="E2543" t="n">
-        <v>6.46000003814697</v>
+        <v>6.44000005722046</v>
       </c>
       <c r="F2543" t="n">
         <v>6.44000005722046</v>
@@ -74119,9 +74119,38 @@
         <v>6.44000005722046</v>
       </c>
       <c r="H2543" t="n">
-        <v>15635</v>
+        <v>15866</v>
       </c>
       <c r="I2543" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2544">
+      <c r="A2544" t="s">
+        <v>9</v>
+      </c>
+      <c r="B2544" s="1" t="n">
+        <v>46317.2916666667</v>
+      </c>
+      <c r="C2544" t="n">
+        <v>6.44000005722046</v>
+      </c>
+      <c r="D2544" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="E2544" t="n">
+        <v>6.30000019073486</v>
+      </c>
+      <c r="F2544" t="n">
+        <v>6.23999977111816</v>
+      </c>
+      <c r="G2544" t="n">
+        <v>6.23999977111816</v>
+      </c>
+      <c r="H2544" t="n">
+        <v>18250</v>
+      </c>
+      <c r="I2544" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/FF.MI.xlsx
+++ b/data/FF.MI.xlsx
@@ -427,7 +427,7 @@
         <v>10</v>
       </c>
       <c r="G2" t="n">
-        <v>8.92192840576172</v>
+        <v>8.92193031311035</v>
       </c>
       <c r="H2" t="n">
         <v>2800</v>
@@ -485,7 +485,7 @@
         <v>10</v>
       </c>
       <c r="G4" t="n">
-        <v>8.92192840576172</v>
+        <v>8.92193031311035</v>
       </c>
       <c r="H4" t="n">
         <v>600</v>
@@ -514,7 +514,7 @@
         <v>10</v>
       </c>
       <c r="G5" t="n">
-        <v>8.92192840576172</v>
+        <v>8.92193031311035</v>
       </c>
       <c r="H5" t="n">
         <v>0</v>
@@ -543,7 +543,7 @@
         <v>10</v>
       </c>
       <c r="G6" t="n">
-        <v>8.92192840576172</v>
+        <v>8.92193031311035</v>
       </c>
       <c r="H6" t="n">
         <v>600</v>
@@ -572,7 +572,7 @@
         <v>10</v>
       </c>
       <c r="G7" t="n">
-        <v>8.92192840576172</v>
+        <v>8.92193031311035</v>
       </c>
       <c r="H7" t="n">
         <v>200</v>
@@ -601,7 +601,7 @@
         <v>10.0100002288818</v>
       </c>
       <c r="G8" t="n">
-        <v>8.93085098266602</v>
+        <v>8.93085193634033</v>
       </c>
       <c r="H8" t="n">
         <v>200</v>
@@ -630,7 +630,7 @@
         <v>10.0100002288818</v>
       </c>
       <c r="G9" t="n">
-        <v>8.93085098266602</v>
+        <v>8.93085193634033</v>
       </c>
       <c r="H9" t="n">
         <v>0</v>
@@ -659,7 +659,7 @@
         <v>10</v>
       </c>
       <c r="G10" t="n">
-        <v>8.92192840576172</v>
+        <v>8.92193031311035</v>
       </c>
       <c r="H10" t="n">
         <v>200</v>
@@ -688,7 +688,7 @@
         <v>10</v>
       </c>
       <c r="G11" t="n">
-        <v>8.92192840576172</v>
+        <v>8.92193031311035</v>
       </c>
       <c r="H11" t="n">
         <v>0</v>
@@ -717,7 +717,7 @@
         <v>10</v>
       </c>
       <c r="G12" t="n">
-        <v>8.92192840576172</v>
+        <v>8.92193031311035</v>
       </c>
       <c r="H12" t="n">
         <v>0</v>
@@ -746,7 +746,7 @@
         <v>10</v>
       </c>
       <c r="G13" t="n">
-        <v>8.92192840576172</v>
+        <v>8.92193031311035</v>
       </c>
       <c r="H13" t="n">
         <v>0</v>
@@ -775,7 +775,7 @@
         <v>10</v>
       </c>
       <c r="G14" t="n">
-        <v>8.92192840576172</v>
+        <v>8.92193031311035</v>
       </c>
       <c r="H14" t="n">
         <v>0</v>
@@ -804,7 +804,7 @@
         <v>10.1899995803833</v>
       </c>
       <c r="G15" t="n">
-        <v>9.09144401550293</v>
+        <v>9.0914478302002</v>
       </c>
       <c r="H15" t="n">
         <v>200</v>
@@ -833,7 +833,7 @@
         <v>10.1899995803833</v>
       </c>
       <c r="G16" t="n">
-        <v>9.09144401550293</v>
+        <v>9.0914478302002</v>
       </c>
       <c r="H16" t="n">
         <v>0</v>
@@ -891,7 +891,7 @@
         <v>10.0500001907349</v>
       </c>
       <c r="G18" t="n">
-        <v>8.96653938293457</v>
+        <v>8.96653842926025</v>
       </c>
       <c r="H18" t="n">
         <v>1200</v>
@@ -1036,7 +1036,7 @@
         <v>9.86499977111816</v>
       </c>
       <c r="G23" t="n">
-        <v>8.80148410797119</v>
+        <v>8.80148220062256</v>
       </c>
       <c r="H23" t="n">
         <v>1000</v>
@@ -1065,7 +1065,7 @@
         <v>9.86499977111816</v>
       </c>
       <c r="G24" t="n">
-        <v>8.80148410797119</v>
+        <v>8.80148220062256</v>
       </c>
       <c r="H24" t="n">
         <v>0</v>
@@ -1094,7 +1094,7 @@
         <v>9.86499977111816</v>
       </c>
       <c r="G25" t="n">
-        <v>8.80148410797119</v>
+        <v>8.80148220062256</v>
       </c>
       <c r="H25" t="n">
         <v>0</v>
@@ -1123,7 +1123,7 @@
         <v>10</v>
       </c>
       <c r="G26" t="n">
-        <v>8.92192840576172</v>
+        <v>8.92193031311035</v>
       </c>
       <c r="H26" t="n">
         <v>400</v>
@@ -1152,7 +1152,7 @@
         <v>9.80500030517578</v>
       </c>
       <c r="G27" t="n">
-        <v>8.74795246124268</v>
+        <v>8.74795055389404</v>
       </c>
       <c r="H27" t="n">
         <v>200</v>
@@ -1181,7 +1181,7 @@
         <v>9.80500030517578</v>
       </c>
       <c r="G28" t="n">
-        <v>8.74795246124268</v>
+        <v>8.74795055389404</v>
       </c>
       <c r="H28" t="n">
         <v>0</v>
@@ -1210,7 +1210,7 @@
         <v>9.80500030517578</v>
       </c>
       <c r="G29" t="n">
-        <v>8.74795246124268</v>
+        <v>8.74795055389404</v>
       </c>
       <c r="H29" t="n">
         <v>0</v>
@@ -1239,7 +1239,7 @@
         <v>9.80500030517578</v>
       </c>
       <c r="G30" t="n">
-        <v>8.74795246124268</v>
+        <v>8.74795055389404</v>
       </c>
       <c r="H30" t="n">
         <v>0</v>
@@ -1268,7 +1268,7 @@
         <v>9.80500030517578</v>
       </c>
       <c r="G31" t="n">
-        <v>8.74795246124268</v>
+        <v>8.74795055389404</v>
       </c>
       <c r="H31" t="n">
         <v>0</v>
@@ -1297,7 +1297,7 @@
         <v>9.80500030517578</v>
       </c>
       <c r="G32" t="n">
-        <v>8.74795246124268</v>
+        <v>8.74795055389404</v>
       </c>
       <c r="H32" t="n">
         <v>0</v>
@@ -1326,7 +1326,7 @@
         <v>9.80500030517578</v>
       </c>
       <c r="G33" t="n">
-        <v>8.74795246124268</v>
+        <v>8.74795055389404</v>
       </c>
       <c r="H33" t="n">
         <v>0</v>
@@ -1355,7 +1355,7 @@
         <v>9.80500030517578</v>
       </c>
       <c r="G34" t="n">
-        <v>8.74795246124268</v>
+        <v>8.74795055389404</v>
       </c>
       <c r="H34" t="n">
         <v>0</v>
@@ -1384,7 +1384,7 @@
         <v>9.80500030517578</v>
       </c>
       <c r="G35" t="n">
-        <v>8.74795246124268</v>
+        <v>8.74795055389404</v>
       </c>
       <c r="H35" t="n">
         <v>0</v>
@@ -1413,7 +1413,7 @@
         <v>9.80500030517578</v>
       </c>
       <c r="G36" t="n">
-        <v>8.74795246124268</v>
+        <v>8.74795055389404</v>
       </c>
       <c r="H36" t="n">
         <v>0</v>
@@ -1442,7 +1442,7 @@
         <v>9.80500030517578</v>
       </c>
       <c r="G37" t="n">
-        <v>8.74795246124268</v>
+        <v>8.74795055389404</v>
       </c>
       <c r="H37" t="n">
         <v>0</v>
@@ -1471,7 +1471,7 @@
         <v>9.80500030517578</v>
       </c>
       <c r="G38" t="n">
-        <v>8.74795246124268</v>
+        <v>8.74795055389404</v>
       </c>
       <c r="H38" t="n">
         <v>0</v>
@@ -1500,7 +1500,7 @@
         <v>9.80500030517578</v>
       </c>
       <c r="G39" t="n">
-        <v>8.74795246124268</v>
+        <v>8.74795055389404</v>
       </c>
       <c r="H39" t="n">
         <v>0</v>
@@ -1529,7 +1529,7 @@
         <v>9.80000019073486</v>
       </c>
       <c r="G40" t="n">
-        <v>8.74349021911621</v>
+        <v>8.74349117279053</v>
       </c>
       <c r="H40" t="n">
         <v>200</v>
@@ -1558,7 +1558,7 @@
         <v>9.80000019073486</v>
       </c>
       <c r="G41" t="n">
-        <v>8.74349021911621</v>
+        <v>8.74349117279053</v>
       </c>
       <c r="H41" t="n">
         <v>21400</v>
@@ -1587,7 +1587,7 @@
         <v>9.80000019073486</v>
       </c>
       <c r="G42" t="n">
-        <v>8.74349021911621</v>
+        <v>8.74349117279053</v>
       </c>
       <c r="H42" t="n">
         <v>0</v>
@@ -1616,7 +1616,7 @@
         <v>9.80000019073486</v>
       </c>
       <c r="G43" t="n">
-        <v>8.74349021911621</v>
+        <v>8.74349117279053</v>
       </c>
       <c r="H43" t="n">
         <v>0</v>
@@ -1645,7 +1645,7 @@
         <v>9.80000019073486</v>
       </c>
       <c r="G44" t="n">
-        <v>8.74349021911621</v>
+        <v>8.74349117279053</v>
       </c>
       <c r="H44" t="n">
         <v>0</v>
@@ -1674,7 +1674,7 @@
         <v>9.80000019073486</v>
       </c>
       <c r="G45" t="n">
-        <v>8.74349021911621</v>
+        <v>8.74349117279053</v>
       </c>
       <c r="H45" t="n">
         <v>0</v>
@@ -1703,7 +1703,7 @@
         <v>9.80000019073486</v>
       </c>
       <c r="G46" t="n">
-        <v>8.74349021911621</v>
+        <v>8.74349117279053</v>
       </c>
       <c r="H46" t="n">
         <v>400</v>
@@ -1732,7 +1732,7 @@
         <v>9.80000019073486</v>
       </c>
       <c r="G47" t="n">
-        <v>8.74349021911621</v>
+        <v>8.74349117279053</v>
       </c>
       <c r="H47" t="n">
         <v>0</v>
@@ -1761,7 +1761,7 @@
         <v>9.80000019073486</v>
       </c>
       <c r="G48" t="n">
-        <v>8.74349021911621</v>
+        <v>8.74349117279053</v>
       </c>
       <c r="H48" t="n">
         <v>0</v>
@@ -1790,7 +1790,7 @@
         <v>10</v>
       </c>
       <c r="G49" t="n">
-        <v>8.92192840576172</v>
+        <v>8.92193031311035</v>
       </c>
       <c r="H49" t="n">
         <v>200</v>
@@ -1819,7 +1819,7 @@
         <v>10</v>
       </c>
       <c r="G50" t="n">
-        <v>8.92192840576172</v>
+        <v>8.92193031311035</v>
       </c>
       <c r="H50" t="n">
         <v>0</v>
@@ -1848,7 +1848,7 @@
         <v>9.80000019073486</v>
       </c>
       <c r="G51" t="n">
-        <v>8.74349021911621</v>
+        <v>8.74349117279053</v>
       </c>
       <c r="H51" t="n">
         <v>400</v>
@@ -1877,7 +1877,7 @@
         <v>9.80000019073486</v>
       </c>
       <c r="G52" t="n">
-        <v>8.74349021911621</v>
+        <v>8.74349117279053</v>
       </c>
       <c r="H52" t="n">
         <v>0</v>
@@ -1906,7 +1906,7 @@
         <v>9.75</v>
       </c>
       <c r="G53" t="n">
-        <v>8.69888210296631</v>
+        <v>8.69888114929199</v>
       </c>
       <c r="H53" t="n">
         <v>400</v>
@@ -1935,7 +1935,7 @@
         <v>9.75</v>
       </c>
       <c r="G54" t="n">
-        <v>8.69888210296631</v>
+        <v>8.69888114929199</v>
       </c>
       <c r="H54" t="n">
         <v>0</v>
@@ -1964,7 +1964,7 @@
         <v>9.75</v>
       </c>
       <c r="G55" t="n">
-        <v>8.69888210296631</v>
+        <v>8.69888114929199</v>
       </c>
       <c r="H55" t="n">
         <v>0</v>
@@ -1993,7 +1993,7 @@
         <v>9.75</v>
       </c>
       <c r="G56" t="n">
-        <v>8.69888210296631</v>
+        <v>8.69888114929199</v>
       </c>
       <c r="H56" t="n">
         <v>0</v>
@@ -2022,7 +2022,7 @@
         <v>9.75</v>
       </c>
       <c r="G57" t="n">
-        <v>8.69888210296631</v>
+        <v>8.69888114929199</v>
       </c>
       <c r="H57" t="n">
         <v>0</v>
@@ -2051,7 +2051,7 @@
         <v>9.75</v>
       </c>
       <c r="G58" t="n">
-        <v>8.69888210296631</v>
+        <v>8.69888114929199</v>
       </c>
       <c r="H58" t="n">
         <v>0</v>
@@ -2080,7 +2080,7 @@
         <v>9.80000019073486</v>
       </c>
       <c r="G59" t="n">
-        <v>8.74349021911621</v>
+        <v>8.74349117279053</v>
       </c>
       <c r="H59" t="n">
         <v>200</v>
@@ -2109,7 +2109,7 @@
         <v>9.80000019073486</v>
       </c>
       <c r="G60" t="n">
-        <v>8.74349021911621</v>
+        <v>8.74349117279053</v>
       </c>
       <c r="H60" t="n">
         <v>0</v>
@@ -2138,7 +2138,7 @@
         <v>9.80000019073486</v>
       </c>
       <c r="G61" t="n">
-        <v>8.74349021911621</v>
+        <v>8.74349117279053</v>
       </c>
       <c r="H61" t="n">
         <v>0</v>
@@ -2167,7 +2167,7 @@
         <v>9.80500030517578</v>
       </c>
       <c r="G62" t="n">
-        <v>8.74795246124268</v>
+        <v>8.74795055389404</v>
       </c>
       <c r="H62" t="n">
         <v>200</v>
@@ -2196,7 +2196,7 @@
         <v>9.80500030517578</v>
       </c>
       <c r="G63" t="n">
-        <v>8.74795246124268</v>
+        <v>8.74795055389404</v>
       </c>
       <c r="H63" t="n">
         <v>0</v>
@@ -2225,7 +2225,7 @@
         <v>9.80500030517578</v>
       </c>
       <c r="G64" t="n">
-        <v>8.74795246124268</v>
+        <v>8.74795055389404</v>
       </c>
       <c r="H64" t="n">
         <v>0</v>
@@ -2254,7 +2254,7 @@
         <v>9.80500030517578</v>
       </c>
       <c r="G65" t="n">
-        <v>8.74795246124268</v>
+        <v>8.74795055389404</v>
       </c>
       <c r="H65" t="n">
         <v>0</v>
@@ -2283,7 +2283,7 @@
         <v>9.76000022888184</v>
       </c>
       <c r="G66" t="n">
-        <v>8.70780372619629</v>
+        <v>8.70780181884766</v>
       </c>
       <c r="H66" t="n">
         <v>200</v>
@@ -2312,7 +2312,7 @@
         <v>9.76000022888184</v>
       </c>
       <c r="G67" t="n">
-        <v>8.70780372619629</v>
+        <v>8.70780181884766</v>
       </c>
       <c r="H67" t="n">
         <v>0</v>
@@ -2428,7 +2428,7 @@
         <v>9.65999984741211</v>
       </c>
       <c r="G71" t="n">
-        <v>8.61858367919922</v>
+        <v>8.6185827255249</v>
       </c>
       <c r="H71" t="n">
         <v>20200</v>
@@ -2457,7 +2457,7 @@
         <v>9.65999984741211</v>
       </c>
       <c r="G72" t="n">
-        <v>8.61858367919922</v>
+        <v>8.6185827255249</v>
       </c>
       <c r="H72" t="n">
         <v>0</v>
@@ -2486,7 +2486,7 @@
         <v>9.65999984741211</v>
       </c>
       <c r="G73" t="n">
-        <v>8.61858367919922</v>
+        <v>8.6185827255249</v>
       </c>
       <c r="H73" t="n">
         <v>0</v>
@@ -2515,7 +2515,7 @@
         <v>9.77000045776367</v>
       </c>
       <c r="G74" t="n">
-        <v>8.71672439575195</v>
+        <v>8.71672534942627</v>
       </c>
       <c r="H74" t="n">
         <v>400</v>
@@ -2544,7 +2544,7 @@
         <v>9.77000045776367</v>
       </c>
       <c r="G75" t="n">
-        <v>8.71672439575195</v>
+        <v>8.71672534942627</v>
       </c>
       <c r="H75" t="n">
         <v>0</v>
@@ -2573,7 +2573,7 @@
         <v>9.77000045776367</v>
       </c>
       <c r="G76" t="n">
-        <v>8.71672439575195</v>
+        <v>8.71672534942627</v>
       </c>
       <c r="H76" t="n">
         <v>0</v>
@@ -2602,7 +2602,7 @@
         <v>9.77000045776367</v>
       </c>
       <c r="G77" t="n">
-        <v>8.71672439575195</v>
+        <v>8.71672534942627</v>
       </c>
       <c r="H77" t="n">
         <v>0</v>
@@ -2631,7 +2631,7 @@
         <v>9.77000045776367</v>
       </c>
       <c r="G78" t="n">
-        <v>8.71672439575195</v>
+        <v>8.71672534942627</v>
       </c>
       <c r="H78" t="n">
         <v>0</v>
@@ -2660,7 +2660,7 @@
         <v>9.77000045776367</v>
       </c>
       <c r="G79" t="n">
-        <v>8.71672439575195</v>
+        <v>8.71672534942627</v>
       </c>
       <c r="H79" t="n">
         <v>0</v>
@@ -2689,7 +2689,7 @@
         <v>9.77000045776367</v>
       </c>
       <c r="G80" t="n">
-        <v>8.71672439575195</v>
+        <v>8.71672534942627</v>
       </c>
       <c r="H80" t="n">
         <v>0</v>
@@ -2718,7 +2718,7 @@
         <v>9.77000045776367</v>
       </c>
       <c r="G81" t="n">
-        <v>8.71672439575195</v>
+        <v>8.71672534942627</v>
       </c>
       <c r="H81" t="n">
         <v>0</v>
@@ -2747,7 +2747,7 @@
         <v>9.77000045776367</v>
       </c>
       <c r="G82" t="n">
-        <v>8.71672439575195</v>
+        <v>8.71672534942627</v>
       </c>
       <c r="H82" t="n">
         <v>0</v>
@@ -2776,7 +2776,7 @@
         <v>9.77000045776367</v>
       </c>
       <c r="G83" t="n">
-        <v>8.71672439575195</v>
+        <v>8.71672534942627</v>
       </c>
       <c r="H83" t="n">
         <v>0</v>
@@ -2805,7 +2805,7 @@
         <v>9.77000045776367</v>
       </c>
       <c r="G84" t="n">
-        <v>8.71672439575195</v>
+        <v>8.71672534942627</v>
       </c>
       <c r="H84" t="n">
         <v>0</v>
@@ -2834,7 +2834,7 @@
         <v>9.77000045776367</v>
       </c>
       <c r="G85" t="n">
-        <v>8.71672439575195</v>
+        <v>8.71672534942627</v>
       </c>
       <c r="H85" t="n">
         <v>0</v>
@@ -3066,7 +3066,7 @@
         <v>10.1700000762939</v>
       </c>
       <c r="G93" t="n">
-        <v>9.07360172271729</v>
+        <v>9.0736026763916</v>
       </c>
       <c r="H93" t="n">
         <v>400</v>
@@ -3095,7 +3095,7 @@
         <v>10.1700000762939</v>
       </c>
       <c r="G94" t="n">
-        <v>9.07360172271729</v>
+        <v>9.0736026763916</v>
       </c>
       <c r="H94" t="n">
         <v>0</v>
@@ -3124,7 +3124,7 @@
         <v>10.1700000762939</v>
       </c>
       <c r="G95" t="n">
-        <v>9.07360172271729</v>
+        <v>9.0736026763916</v>
       </c>
       <c r="H95" t="n">
         <v>0</v>
@@ -3153,7 +3153,7 @@
         <v>10.1700000762939</v>
       </c>
       <c r="G96" t="n">
-        <v>9.07360172271729</v>
+        <v>9.0736026763916</v>
       </c>
       <c r="H96" t="n">
         <v>200</v>
@@ -3182,7 +3182,7 @@
         <v>10.1700000762939</v>
       </c>
       <c r="G97" t="n">
-        <v>9.07360172271729</v>
+        <v>9.0736026763916</v>
       </c>
       <c r="H97" t="n">
         <v>0</v>
@@ -3211,7 +3211,7 @@
         <v>10.1700000762939</v>
       </c>
       <c r="G98" t="n">
-        <v>9.07360172271729</v>
+        <v>9.0736026763916</v>
       </c>
       <c r="H98" t="n">
         <v>1000</v>
@@ -3240,7 +3240,7 @@
         <v>10.1700000762939</v>
       </c>
       <c r="G99" t="n">
-        <v>9.07360172271729</v>
+        <v>9.0736026763916</v>
       </c>
       <c r="H99" t="n">
         <v>400</v>
@@ -3269,7 +3269,7 @@
         <v>10.1700000762939</v>
       </c>
       <c r="G100" t="n">
-        <v>9.07360172271729</v>
+        <v>9.0736026763916</v>
       </c>
       <c r="H100" t="n">
         <v>0</v>
@@ -3298,7 +3298,7 @@
         <v>10.1700000762939</v>
       </c>
       <c r="G101" t="n">
-        <v>9.07360172271729</v>
+        <v>9.0736026763916</v>
       </c>
       <c r="H101" t="n">
         <v>0</v>
@@ -3327,7 +3327,7 @@
         <v>10.0500001907349</v>
       </c>
       <c r="G102" t="n">
-        <v>8.96653938293457</v>
+        <v>8.96653842926025</v>
       </c>
       <c r="H102" t="n">
         <v>200</v>
@@ -3356,7 +3356,7 @@
         <v>10.0500001907349</v>
       </c>
       <c r="G103" t="n">
-        <v>8.96653938293457</v>
+        <v>8.96653842926025</v>
       </c>
       <c r="H103" t="n">
         <v>0</v>
@@ -3385,7 +3385,7 @@
         <v>10</v>
       </c>
       <c r="G104" t="n">
-        <v>8.92192840576172</v>
+        <v>8.92193031311035</v>
       </c>
       <c r="H104" t="n">
         <v>400</v>
@@ -3414,7 +3414,7 @@
         <v>10</v>
       </c>
       <c r="G105" t="n">
-        <v>8.92192840576172</v>
+        <v>8.92193031311035</v>
       </c>
       <c r="H105" t="n">
         <v>200</v>
@@ -3443,7 +3443,7 @@
         <v>10.039999961853</v>
       </c>
       <c r="G106" t="n">
-        <v>8.95761680603027</v>
+        <v>8.95761775970459</v>
       </c>
       <c r="H106" t="n">
         <v>600</v>
@@ -3472,7 +3472,7 @@
         <v>10.039999961853</v>
       </c>
       <c r="G107" t="n">
-        <v>8.95761680603027</v>
+        <v>8.95761775970459</v>
       </c>
       <c r="H107" t="n">
         <v>0</v>
@@ -3501,7 +3501,7 @@
         <v>10.039999961853</v>
       </c>
       <c r="G108" t="n">
-        <v>8.95761680603027</v>
+        <v>8.95761775970459</v>
       </c>
       <c r="H108" t="n">
         <v>0</v>
@@ -3530,7 +3530,7 @@
         <v>10.0500001907349</v>
       </c>
       <c r="G109" t="n">
-        <v>8.96653938293457</v>
+        <v>8.96653842926025</v>
       </c>
       <c r="H109" t="n">
         <v>400</v>
@@ -3559,7 +3559,7 @@
         <v>10</v>
       </c>
       <c r="G110" t="n">
-        <v>8.92192840576172</v>
+        <v>8.92193031311035</v>
       </c>
       <c r="H110" t="n">
         <v>200</v>
@@ -3588,7 +3588,7 @@
         <v>10</v>
       </c>
       <c r="G111" t="n">
-        <v>8.92192840576172</v>
+        <v>8.92193031311035</v>
       </c>
       <c r="H111" t="n">
         <v>0</v>
@@ -3617,7 +3617,7 @@
         <v>10</v>
       </c>
       <c r="G112" t="n">
-        <v>8.92192840576172</v>
+        <v>8.92193031311035</v>
       </c>
       <c r="H112" t="n">
         <v>0</v>
@@ -3646,7 +3646,7 @@
         <v>10.0100002288818</v>
       </c>
       <c r="G113" t="n">
-        <v>8.93085098266602</v>
+        <v>8.93085193634033</v>
       </c>
       <c r="H113" t="n">
         <v>200</v>
@@ -3675,7 +3675,7 @@
         <v>10.0100002288818</v>
       </c>
       <c r="G114" t="n">
-        <v>8.93085098266602</v>
+        <v>8.93085193634033</v>
       </c>
       <c r="H114" t="n">
         <v>0</v>
@@ -3704,7 +3704,7 @@
         <v>9.88000011444092</v>
       </c>
       <c r="G115" t="n">
-        <v>8.814866065979</v>
+        <v>8.81486511230469</v>
       </c>
       <c r="H115" t="n">
         <v>400</v>
@@ -3733,7 +3733,7 @@
         <v>9.88000011444092</v>
       </c>
       <c r="G116" t="n">
-        <v>8.814866065979</v>
+        <v>8.81486511230469</v>
       </c>
       <c r="H116" t="n">
         <v>4400</v>
@@ -3762,7 +3762,7 @@
         <v>9.81999969482422</v>
       </c>
       <c r="G117" t="n">
-        <v>8.7613353729248</v>
+        <v>8.76133441925049</v>
       </c>
       <c r="H117" t="n">
         <v>6000</v>
@@ -3791,7 +3791,7 @@
         <v>10</v>
       </c>
       <c r="G118" t="n">
-        <v>8.92192840576172</v>
+        <v>8.92193031311035</v>
       </c>
       <c r="H118" t="n">
         <v>200</v>
@@ -3820,7 +3820,7 @@
         <v>9.88000011444092</v>
       </c>
       <c r="G119" t="n">
-        <v>8.814866065979</v>
+        <v>8.81486511230469</v>
       </c>
       <c r="H119" t="n">
         <v>1000</v>
@@ -3849,7 +3849,7 @@
         <v>9.88000011444092</v>
       </c>
       <c r="G120" t="n">
-        <v>8.814866065979</v>
+        <v>8.81486511230469</v>
       </c>
       <c r="H120" t="n">
         <v>0</v>
@@ -3878,7 +3878,7 @@
         <v>9.80000019073486</v>
       </c>
       <c r="G121" t="n">
-        <v>8.74349021911621</v>
+        <v>8.74349117279053</v>
       </c>
       <c r="H121" t="n">
         <v>400</v>
@@ -3907,7 +3907,7 @@
         <v>9.80000019073486</v>
       </c>
       <c r="G122" t="n">
-        <v>8.74349021911621</v>
+        <v>8.74349117279053</v>
       </c>
       <c r="H122" t="n">
         <v>0</v>
@@ -3965,7 +3965,7 @@
         <v>9.81999969482422</v>
       </c>
       <c r="G124" t="n">
-        <v>8.7613353729248</v>
+        <v>8.76133441925049</v>
       </c>
       <c r="H124" t="n">
         <v>2400</v>
@@ -3994,7 +3994,7 @@
         <v>10</v>
       </c>
       <c r="G125" t="n">
-        <v>8.92192840576172</v>
+        <v>8.92193031311035</v>
       </c>
       <c r="H125" t="n">
         <v>1000</v>
@@ -4023,7 +4023,7 @@
         <v>10.0500001907349</v>
       </c>
       <c r="G126" t="n">
-        <v>8.96653938293457</v>
+        <v>8.96653842926025</v>
       </c>
       <c r="H126" t="n">
         <v>1000</v>
@@ -4052,7 +4052,7 @@
         <v>10</v>
       </c>
       <c r="G127" t="n">
-        <v>8.92192840576172</v>
+        <v>8.92193031311035</v>
       </c>
       <c r="H127" t="n">
         <v>200</v>
@@ -4197,7 +4197,7 @@
         <v>10</v>
       </c>
       <c r="G132" t="n">
-        <v>8.92192840576172</v>
+        <v>8.92193031311035</v>
       </c>
       <c r="H132" t="n">
         <v>1400</v>
@@ -4313,7 +4313,7 @@
         <v>10.3999996185303</v>
       </c>
       <c r="G136" t="n">
-        <v>9.27880573272705</v>
+        <v>9.27880668640137</v>
       </c>
       <c r="H136" t="n">
         <v>82000</v>
@@ -4458,7 +4458,7 @@
         <v>10.8000001907349</v>
       </c>
       <c r="G141" t="n">
-        <v>9.6356840133667</v>
+        <v>9.63568305969238</v>
       </c>
       <c r="H141" t="n">
         <v>9600</v>
@@ -4574,7 +4574,7 @@
         <v>10.5600004196167</v>
       </c>
       <c r="G145" t="n">
-        <v>9.42155742645264</v>
+        <v>9.42155838012695</v>
       </c>
       <c r="H145" t="n">
         <v>9200</v>
@@ -4603,7 +4603,7 @@
         <v>10.5500001907349</v>
       </c>
       <c r="G146" t="n">
-        <v>9.41263675689697</v>
+        <v>9.41263484954834</v>
       </c>
       <c r="H146" t="n">
         <v>10800</v>
@@ -4661,7 +4661,7 @@
         <v>10.5</v>
       </c>
       <c r="G148" t="n">
-        <v>9.36802673339844</v>
+        <v>9.36802577972412</v>
       </c>
       <c r="H148" t="n">
         <v>19800</v>
@@ -4690,7 +4690,7 @@
         <v>10.4700002670288</v>
       </c>
       <c r="G149" t="n">
-        <v>9.34125995635986</v>
+        <v>9.34126091003418</v>
       </c>
       <c r="H149" t="n">
         <v>24800</v>
@@ -4719,7 +4719,7 @@
         <v>10.5</v>
       </c>
       <c r="G150" t="n">
-        <v>9.36802673339844</v>
+        <v>9.36802577972412</v>
       </c>
       <c r="H150" t="n">
         <v>4400</v>
@@ -4748,7 +4748,7 @@
         <v>10.5600004196167</v>
       </c>
       <c r="G151" t="n">
-        <v>9.42155742645264</v>
+        <v>9.42155838012695</v>
       </c>
       <c r="H151" t="n">
         <v>6000</v>
@@ -4777,7 +4777,7 @@
         <v>10.5799999237061</v>
       </c>
       <c r="G152" t="n">
-        <v>9.4394006729126</v>
+        <v>9.43940162658691</v>
       </c>
       <c r="H152" t="n">
         <v>1000</v>
@@ -4806,7 +4806,7 @@
         <v>10.5500001907349</v>
       </c>
       <c r="G153" t="n">
-        <v>9.41263675689697</v>
+        <v>9.41263484954834</v>
       </c>
       <c r="H153" t="n">
         <v>2000</v>
@@ -4835,7 +4835,7 @@
         <v>10.6199998855591</v>
       </c>
       <c r="G154" t="n">
-        <v>9.47508811950684</v>
+        <v>9.47508907318115</v>
       </c>
       <c r="H154" t="n">
         <v>6000</v>
@@ -4864,7 +4864,7 @@
         <v>10.5600004196167</v>
       </c>
       <c r="G155" t="n">
-        <v>9.42155742645264</v>
+        <v>9.42155838012695</v>
       </c>
       <c r="H155" t="n">
         <v>20400</v>
@@ -4951,7 +4951,7 @@
         <v>10.9700002670288</v>
       </c>
       <c r="G158" t="n">
-        <v>9.78735828399658</v>
+        <v>9.78735637664795</v>
       </c>
       <c r="H158" t="n">
         <v>5800</v>
@@ -4980,7 +4980,7 @@
         <v>10.8000001907349</v>
       </c>
       <c r="G159" t="n">
-        <v>9.6356840133667</v>
+        <v>9.63568305969238</v>
       </c>
       <c r="H159" t="n">
         <v>7200</v>
@@ -5009,7 +5009,7 @@
         <v>10.8000001907349</v>
       </c>
       <c r="G160" t="n">
-        <v>9.6356840133667</v>
+        <v>9.63568305969238</v>
       </c>
       <c r="H160" t="n">
         <v>0</v>
@@ -5096,7 +5096,7 @@
         <v>10.7299995422363</v>
       </c>
       <c r="G163" t="n">
-        <v>9.57322978973389</v>
+        <v>9.5732307434082</v>
       </c>
       <c r="H163" t="n">
         <v>11400</v>
@@ -5154,7 +5154,7 @@
         <v>10.7299995422363</v>
       </c>
       <c r="G165" t="n">
-        <v>9.57322978973389</v>
+        <v>9.5732307434082</v>
       </c>
       <c r="H165" t="n">
         <v>600</v>
@@ -5270,7 +5270,7 @@
         <v>10.6300001144409</v>
       </c>
       <c r="G169" t="n">
-        <v>9.48401069641113</v>
+        <v>9.48401165008545</v>
       </c>
       <c r="H169" t="n">
         <v>8600</v>
@@ -5357,7 +5357,7 @@
         <v>10.8199996948242</v>
       </c>
       <c r="G172" t="n">
-        <v>9.65352916717529</v>
+        <v>9.65352630615234</v>
       </c>
       <c r="H172" t="n">
         <v>6400</v>
@@ -5386,7 +5386,7 @@
         <v>10.6899995803833</v>
       </c>
       <c r="G173" t="n">
-        <v>9.53754234313965</v>
+        <v>9.53754329681396</v>
       </c>
       <c r="H173" t="n">
         <v>10800</v>
@@ -5415,7 +5415,7 @@
         <v>10.710000038147</v>
       </c>
       <c r="G174" t="n">
-        <v>9.55538654327393</v>
+        <v>9.55538558959961</v>
       </c>
       <c r="H174" t="n">
         <v>8800</v>
@@ -5502,7 +5502,7 @@
         <v>10.6599998474121</v>
       </c>
       <c r="G177" t="n">
-        <v>9.51077651977539</v>
+        <v>9.51077747344971</v>
       </c>
       <c r="H177" t="n">
         <v>11200</v>
@@ -5560,7 +5560,7 @@
         <v>10.5600004196167</v>
       </c>
       <c r="G179" t="n">
-        <v>9.42155742645264</v>
+        <v>9.42155838012695</v>
       </c>
       <c r="H179" t="n">
         <v>8000</v>
@@ -5589,7 +5589,7 @@
         <v>10.4700002670288</v>
       </c>
       <c r="G180" t="n">
-        <v>9.34125995635986</v>
+        <v>9.34126091003418</v>
       </c>
       <c r="H180" t="n">
         <v>10000</v>
@@ -5647,7 +5647,7 @@
         <v>10.6199998855591</v>
       </c>
       <c r="G182" t="n">
-        <v>9.47508811950684</v>
+        <v>9.47508907318115</v>
       </c>
       <c r="H182" t="n">
         <v>400</v>
@@ -5676,7 +5676,7 @@
         <v>10.6400003433228</v>
       </c>
       <c r="G183" t="n">
-        <v>9.49293422698975</v>
+        <v>9.49293327331543</v>
       </c>
       <c r="H183" t="n">
         <v>200</v>
@@ -5734,7 +5734,7 @@
         <v>10.5500001907349</v>
       </c>
       <c r="G185" t="n">
-        <v>9.41263675689697</v>
+        <v>9.41263484954834</v>
       </c>
       <c r="H185" t="n">
         <v>2400</v>
@@ -5763,7 +5763,7 @@
         <v>10.5</v>
       </c>
       <c r="G186" t="n">
-        <v>9.36802673339844</v>
+        <v>9.36802577972412</v>
       </c>
       <c r="H186" t="n">
         <v>2600</v>
@@ -5792,7 +5792,7 @@
         <v>10.5</v>
       </c>
       <c r="G187" t="n">
-        <v>9.36802673339844</v>
+        <v>9.36802577972412</v>
       </c>
       <c r="H187" t="n">
         <v>0</v>
@@ -5966,7 +5966,7 @@
         <v>10.6899995803833</v>
       </c>
       <c r="G193" t="n">
-        <v>9.53754234313965</v>
+        <v>9.53754329681396</v>
       </c>
       <c r="H193" t="n">
         <v>2600</v>
@@ -5995,7 +5995,7 @@
         <v>10.6899995803833</v>
       </c>
       <c r="G194" t="n">
-        <v>9.53754234313965</v>
+        <v>9.53754329681396</v>
       </c>
       <c r="H194" t="n">
         <v>3000</v>
@@ -6082,7 +6082,7 @@
         <v>10.7299995422363</v>
       </c>
       <c r="G197" t="n">
-        <v>9.57322978973389</v>
+        <v>9.5732307434082</v>
       </c>
       <c r="H197" t="n">
         <v>200</v>
@@ -6111,7 +6111,7 @@
         <v>10.5</v>
       </c>
       <c r="G198" t="n">
-        <v>9.36802673339844</v>
+        <v>9.36802577972412</v>
       </c>
       <c r="H198" t="n">
         <v>41200</v>
@@ -6140,7 +6140,7 @@
         <v>10.5500001907349</v>
       </c>
       <c r="G199" t="n">
-        <v>9.41263675689697</v>
+        <v>9.41263484954834</v>
       </c>
       <c r="H199" t="n">
         <v>4800</v>
@@ -6169,7 +6169,7 @@
         <v>10.5</v>
       </c>
       <c r="G200" t="n">
-        <v>9.36802673339844</v>
+        <v>9.36802577972412</v>
       </c>
       <c r="H200" t="n">
         <v>12000</v>
@@ -6227,7 +6227,7 @@
         <v>10.6400003433228</v>
       </c>
       <c r="G202" t="n">
-        <v>9.49293422698975</v>
+        <v>9.49293327331543</v>
       </c>
       <c r="H202" t="n">
         <v>17000</v>
@@ -6256,7 +6256,7 @@
         <v>10.6899995803833</v>
       </c>
       <c r="G203" t="n">
-        <v>9.53754234313965</v>
+        <v>9.53754329681396</v>
       </c>
       <c r="H203" t="n">
         <v>5400</v>
@@ -6285,7 +6285,7 @@
         <v>10.6599998474121</v>
       </c>
       <c r="G204" t="n">
-        <v>9.51077651977539</v>
+        <v>9.51077747344971</v>
       </c>
       <c r="H204" t="n">
         <v>20200</v>
@@ -6314,7 +6314,7 @@
         <v>10.6199998855591</v>
       </c>
       <c r="G205" t="n">
-        <v>9.47508811950684</v>
+        <v>9.47508907318115</v>
       </c>
       <c r="H205" t="n">
         <v>17200</v>
@@ -6343,7 +6343,7 @@
         <v>10.6700000762939</v>
       </c>
       <c r="G206" t="n">
-        <v>9.519700050354</v>
+        <v>9.51969909667969</v>
       </c>
       <c r="H206" t="n">
         <v>10800</v>
@@ -6372,7 +6372,7 @@
         <v>10.6199998855591</v>
       </c>
       <c r="G207" t="n">
-        <v>9.47508811950684</v>
+        <v>9.47508907318115</v>
       </c>
       <c r="H207" t="n">
         <v>3000</v>
@@ -6430,7 +6430,7 @@
         <v>10.6300001144409</v>
       </c>
       <c r="G209" t="n">
-        <v>9.48401069641113</v>
+        <v>9.48401165008545</v>
       </c>
       <c r="H209" t="n">
         <v>600</v>
@@ -6517,7 +6517,7 @@
         <v>10.8100004196167</v>
       </c>
       <c r="G212" t="n">
-        <v>9.64460563659668</v>
+        <v>9.644606590271</v>
       </c>
       <c r="H212" t="n">
         <v>7200</v>
@@ -6546,7 +6546,7 @@
         <v>10.8100004196167</v>
       </c>
       <c r="G213" t="n">
-        <v>9.64460563659668</v>
+        <v>9.644606590271</v>
       </c>
       <c r="H213" t="n">
         <v>0</v>
@@ -6575,7 +6575,7 @@
         <v>10.8299999237061</v>
       </c>
       <c r="G214" t="n">
-        <v>9.66244888305664</v>
+        <v>9.66245079040527</v>
       </c>
       <c r="H214" t="n">
         <v>600</v>
@@ -6604,7 +6604,7 @@
         <v>10.8500003814697</v>
       </c>
       <c r="G215" t="n">
-        <v>9.68029499053955</v>
+        <v>9.68029403686523</v>
       </c>
       <c r="H215" t="n">
         <v>1600</v>
@@ -6749,7 +6749,7 @@
         <v>10.7299995422363</v>
       </c>
       <c r="G220" t="n">
-        <v>9.57322978973389</v>
+        <v>9.5732307434082</v>
       </c>
       <c r="H220" t="n">
         <v>1600</v>
@@ -6778,7 +6778,7 @@
         <v>10.6199998855591</v>
       </c>
       <c r="G221" t="n">
-        <v>9.47508811950684</v>
+        <v>9.47508907318115</v>
       </c>
       <c r="H221" t="n">
         <v>5800</v>
@@ -6807,7 +6807,7 @@
         <v>10.8000001907349</v>
       </c>
       <c r="G222" t="n">
-        <v>9.6356840133667</v>
+        <v>9.63568305969238</v>
       </c>
       <c r="H222" t="n">
         <v>13000</v>
@@ -6836,7 +6836,7 @@
         <v>10.8199996948242</v>
       </c>
       <c r="G223" t="n">
-        <v>9.65352916717529</v>
+        <v>9.65352630615234</v>
       </c>
       <c r="H223" t="n">
         <v>3600</v>
@@ -6865,7 +6865,7 @@
         <v>10.8000001907349</v>
       </c>
       <c r="G224" t="n">
-        <v>9.6356840133667</v>
+        <v>9.63568305969238</v>
       </c>
       <c r="H224" t="n">
         <v>1000</v>
@@ -6894,7 +6894,7 @@
         <v>10.8000001907349</v>
       </c>
       <c r="G225" t="n">
-        <v>9.6356840133667</v>
+        <v>9.63568305969238</v>
       </c>
       <c r="H225" t="n">
         <v>0</v>
@@ -7010,7 +7010,7 @@
         <v>10.710000038147</v>
       </c>
       <c r="G229" t="n">
-        <v>9.55538654327393</v>
+        <v>9.55538558959961</v>
       </c>
       <c r="H229" t="n">
         <v>1000</v>
@@ -7068,7 +7068,7 @@
         <v>10.8000001907349</v>
       </c>
       <c r="G231" t="n">
-        <v>9.6356840133667</v>
+        <v>9.63568305969238</v>
       </c>
       <c r="H231" t="n">
         <v>9000</v>
@@ -7097,7 +7097,7 @@
         <v>10.710000038147</v>
       </c>
       <c r="G232" t="n">
-        <v>9.55538654327393</v>
+        <v>9.55538558959961</v>
       </c>
       <c r="H232" t="n">
         <v>2000</v>
@@ -7184,7 +7184,7 @@
         <v>10.6400003433228</v>
       </c>
       <c r="G235" t="n">
-        <v>9.49293422698975</v>
+        <v>9.49293327331543</v>
       </c>
       <c r="H235" t="n">
         <v>10600</v>
@@ -7242,7 +7242,7 @@
         <v>10.7299995422363</v>
       </c>
       <c r="G237" t="n">
-        <v>9.57322978973389</v>
+        <v>9.5732307434082</v>
       </c>
       <c r="H237" t="n">
         <v>4400</v>
@@ -7387,7 +7387,7 @@
         <v>10.3999996185303</v>
       </c>
       <c r="G242" t="n">
-        <v>9.27880573272705</v>
+        <v>9.27880668640137</v>
       </c>
       <c r="H242" t="n">
         <v>23800</v>
@@ -7445,7 +7445,7 @@
         <v>10.3000001907349</v>
       </c>
       <c r="G244" t="n">
-        <v>9.1895866394043</v>
+        <v>9.18958759307861</v>
       </c>
       <c r="H244" t="n">
         <v>9000</v>
@@ -7474,7 +7474,7 @@
         <v>10.3999996185303</v>
       </c>
       <c r="G245" t="n">
-        <v>9.27880573272705</v>
+        <v>9.27880668640137</v>
       </c>
       <c r="H245" t="n">
         <v>8800</v>
@@ -7561,7 +7561,7 @@
         <v>10.1999998092651</v>
       </c>
       <c r="G248" t="n">
-        <v>9.10036849975586</v>
+        <v>9.10036659240723</v>
       </c>
       <c r="H248" t="n">
         <v>2000</v>
@@ -7590,7 +7590,7 @@
         <v>10.1999998092651</v>
       </c>
       <c r="G249" t="n">
-        <v>9.10036849975586</v>
+        <v>9.10036659240723</v>
       </c>
       <c r="H249" t="n">
         <v>0</v>
@@ -7619,7 +7619,7 @@
         <v>10.1999998092651</v>
       </c>
       <c r="G250" t="n">
-        <v>9.10036849975586</v>
+        <v>9.10036659240723</v>
       </c>
       <c r="H250" t="n">
         <v>11000</v>
@@ -7677,7 +7677,7 @@
         <v>10.1199998855591</v>
       </c>
       <c r="G252" t="n">
-        <v>9.02899074554443</v>
+        <v>9.02899169921875</v>
       </c>
       <c r="H252" t="n">
         <v>42600</v>
@@ -7735,7 +7735,7 @@
         <v>10.3699998855591</v>
       </c>
       <c r="G254" t="n">
-        <v>9.25203990936279</v>
+        <v>9.25204086303711</v>
       </c>
       <c r="H254" t="n">
         <v>400</v>
@@ -7793,7 +7793,7 @@
         <v>10.2600002288818</v>
       </c>
       <c r="G256" t="n">
-        <v>9.15390110015869</v>
+        <v>9.15389919281006</v>
       </c>
       <c r="H256" t="n">
         <v>600</v>
@@ -7851,7 +7851,7 @@
         <v>10.2399997711182</v>
       </c>
       <c r="G258" t="n">
-        <v>9.13605499267578</v>
+        <v>9.1360559463501</v>
       </c>
       <c r="H258" t="n">
         <v>2200</v>
@@ -7880,7 +7880,7 @@
         <v>10.3000001907349</v>
       </c>
       <c r="G259" t="n">
-        <v>9.1895866394043</v>
+        <v>9.18958759307861</v>
       </c>
       <c r="H259" t="n">
         <v>3400</v>
@@ -7967,7 +7967,7 @@
         <v>10.3299999237061</v>
       </c>
       <c r="G262" t="n">
-        <v>9.21635341644287</v>
+        <v>9.21635246276855</v>
       </c>
       <c r="H262" t="n">
         <v>400</v>
@@ -8025,7 +8025,7 @@
         <v>10.3000001907349</v>
       </c>
       <c r="G264" t="n">
-        <v>9.1895866394043</v>
+        <v>9.18958759307861</v>
       </c>
       <c r="H264" t="n">
         <v>11400</v>
@@ -8054,7 +8054,7 @@
         <v>10.3400001525879</v>
       </c>
       <c r="G265" t="n">
-        <v>9.22527408599854</v>
+        <v>9.22527503967285</v>
       </c>
       <c r="H265" t="n">
         <v>1200</v>
@@ -8083,7 +8083,7 @@
         <v>10.3299999237061</v>
       </c>
       <c r="G266" t="n">
-        <v>9.21635341644287</v>
+        <v>9.21635246276855</v>
       </c>
       <c r="H266" t="n">
         <v>3000</v>
@@ -8112,7 +8112,7 @@
         <v>10.4200000762939</v>
       </c>
       <c r="G267" t="n">
-        <v>9.29664993286133</v>
+        <v>9.29665088653564</v>
       </c>
       <c r="H267" t="n">
         <v>4000</v>
@@ -8141,7 +8141,7 @@
         <v>10.3500003814697</v>
       </c>
       <c r="G268" t="n">
-        <v>9.23419952392578</v>
+        <v>9.23419761657715</v>
       </c>
       <c r="H268" t="n">
         <v>2000</v>
@@ -8170,7 +8170,7 @@
         <v>10.4200000762939</v>
       </c>
       <c r="G269" t="n">
-        <v>9.29664993286133</v>
+        <v>9.29665088653564</v>
       </c>
       <c r="H269" t="n">
         <v>15000</v>
@@ -8199,7 +8199,7 @@
         <v>10.4499998092651</v>
       </c>
       <c r="G270" t="n">
-        <v>9.32341575622559</v>
+        <v>9.3234167098999</v>
       </c>
       <c r="H270" t="n">
         <v>11200</v>
@@ -8228,7 +8228,7 @@
         <v>10.460000038147</v>
       </c>
       <c r="G271" t="n">
-        <v>9.3323392868042</v>
+        <v>9.33233833312988</v>
       </c>
       <c r="H271" t="n">
         <v>3000</v>
@@ -8344,7 +8344,7 @@
         <v>10.3000001907349</v>
       </c>
       <c r="G275" t="n">
-        <v>9.1895866394043</v>
+        <v>9.18958759307861</v>
       </c>
       <c r="H275" t="n">
         <v>1200</v>
@@ -8460,7 +8460,7 @@
         <v>10.1400003433228</v>
       </c>
       <c r="G279" t="n">
-        <v>9.04683780670166</v>
+        <v>9.04683685302734</v>
       </c>
       <c r="H279" t="n">
         <v>20400</v>
@@ -8489,7 +8489,7 @@
         <v>10.1199998855591</v>
       </c>
       <c r="G280" t="n">
-        <v>9.02899074554443</v>
+        <v>9.02899169921875</v>
       </c>
       <c r="H280" t="n">
         <v>12200</v>
@@ -8576,7 +8576,7 @@
         <v>10.1999998092651</v>
       </c>
       <c r="G283" t="n">
-        <v>9.10036849975586</v>
+        <v>9.10036659240723</v>
       </c>
       <c r="H283" t="n">
         <v>1400</v>
@@ -8721,7 +8721,7 @@
         <v>10.1400003433228</v>
       </c>
       <c r="G288" t="n">
-        <v>9.04683780670166</v>
+        <v>9.04683685302734</v>
       </c>
       <c r="H288" t="n">
         <v>5200</v>
@@ -8750,7 +8750,7 @@
         <v>10.1400003433228</v>
       </c>
       <c r="G289" t="n">
-        <v>9.04683780670166</v>
+        <v>9.04683685302734</v>
       </c>
       <c r="H289" t="n">
         <v>10000</v>
@@ -8837,7 +8837,7 @@
         <v>10.1199998855591</v>
       </c>
       <c r="G292" t="n">
-        <v>9.02899074554443</v>
+        <v>9.02899169921875</v>
       </c>
       <c r="H292" t="n">
         <v>200</v>
@@ -8953,7 +8953,7 @@
         <v>10.1199998855591</v>
       </c>
       <c r="G296" t="n">
-        <v>9.02899074554443</v>
+        <v>9.02899169921875</v>
       </c>
       <c r="H296" t="n">
         <v>5600</v>
@@ -8982,7 +8982,7 @@
         <v>10.1199998855591</v>
       </c>
       <c r="G297" t="n">
-        <v>9.02899074554443</v>
+        <v>9.02899169921875</v>
       </c>
       <c r="H297" t="n">
         <v>2600</v>
@@ -9301,7 +9301,7 @@
         <v>10.0100002288818</v>
       </c>
       <c r="G308" t="n">
-        <v>8.93085098266602</v>
+        <v>8.93085193634033</v>
       </c>
       <c r="H308" t="n">
         <v>25000</v>
@@ -9330,7 +9330,7 @@
         <v>10.0100002288818</v>
       </c>
       <c r="G309" t="n">
-        <v>8.93085098266602</v>
+        <v>8.93085193634033</v>
       </c>
       <c r="H309" t="n">
         <v>0</v>
@@ -9388,7 +9388,7 @@
         <v>10</v>
       </c>
       <c r="G311" t="n">
-        <v>8.92192840576172</v>
+        <v>8.92193031311035</v>
       </c>
       <c r="H311" t="n">
         <v>2800</v>
@@ -9417,7 +9417,7 @@
         <v>10</v>
       </c>
       <c r="G312" t="n">
-        <v>8.92192840576172</v>
+        <v>8.92193031311035</v>
       </c>
       <c r="H312" t="n">
         <v>0</v>
@@ -9446,7 +9446,7 @@
         <v>10</v>
       </c>
       <c r="G313" t="n">
-        <v>8.92192840576172</v>
+        <v>8.92193031311035</v>
       </c>
       <c r="H313" t="n">
         <v>2800</v>
@@ -9475,7 +9475,7 @@
         <v>10</v>
       </c>
       <c r="G314" t="n">
-        <v>8.92192840576172</v>
+        <v>8.92193031311035</v>
       </c>
       <c r="H314" t="n">
         <v>0</v>
@@ -9591,7 +9591,7 @@
         <v>10.1999998092651</v>
       </c>
       <c r="G318" t="n">
-        <v>9.10036849975586</v>
+        <v>9.10036659240723</v>
       </c>
       <c r="H318" t="n">
         <v>8600</v>
@@ -9620,7 +9620,7 @@
         <v>10.1999998092651</v>
       </c>
       <c r="G319" t="n">
-        <v>9.10036849975586</v>
+        <v>9.10036659240723</v>
       </c>
       <c r="H319" t="n">
         <v>0</v>
@@ -9649,7 +9649,7 @@
         <v>10</v>
       </c>
       <c r="G320" t="n">
-        <v>8.92192840576172</v>
+        <v>8.92193031311035</v>
       </c>
       <c r="H320" t="n">
         <v>30800</v>
@@ -9678,7 +9678,7 @@
         <v>10.1999998092651</v>
       </c>
       <c r="G321" t="n">
-        <v>9.10036849975586</v>
+        <v>9.10036659240723</v>
       </c>
       <c r="H321" t="n">
         <v>24600</v>
@@ -9707,7 +9707,7 @@
         <v>10.1999998092651</v>
       </c>
       <c r="G322" t="n">
-        <v>9.10036849975586</v>
+        <v>9.10036659240723</v>
       </c>
       <c r="H322" t="n">
         <v>12200</v>
@@ -9794,7 +9794,7 @@
         <v>10.1999998092651</v>
       </c>
       <c r="G325" t="n">
-        <v>9.10036849975586</v>
+        <v>9.10036659240723</v>
       </c>
       <c r="H325" t="n">
         <v>1800</v>
@@ -9823,7 +9823,7 @@
         <v>10.1999998092651</v>
       </c>
       <c r="G326" t="n">
-        <v>9.10036849975586</v>
+        <v>9.10036659240723</v>
       </c>
       <c r="H326" t="n">
         <v>2400</v>
@@ -9881,7 +9881,7 @@
         <v>10</v>
       </c>
       <c r="G328" t="n">
-        <v>8.92192840576172</v>
+        <v>8.92193031311035</v>
       </c>
       <c r="H328" t="n">
         <v>6400</v>
@@ -9997,7 +9997,7 @@
         <v>10</v>
       </c>
       <c r="G332" t="n">
-        <v>8.92192840576172</v>
+        <v>8.92193031311035</v>
       </c>
       <c r="H332" t="n">
         <v>600</v>
@@ -10026,7 +10026,7 @@
         <v>10</v>
       </c>
       <c r="G333" t="n">
-        <v>8.92192840576172</v>
+        <v>8.92193031311035</v>
       </c>
       <c r="H333" t="n">
         <v>1200</v>
@@ -10055,7 +10055,7 @@
         <v>10</v>
       </c>
       <c r="G334" t="n">
-        <v>8.92192840576172</v>
+        <v>8.92193031311035</v>
       </c>
       <c r="H334" t="n">
         <v>200</v>
@@ -10084,7 +10084,7 @@
         <v>10</v>
       </c>
       <c r="G335" t="n">
-        <v>8.92192840576172</v>
+        <v>8.92193031311035</v>
       </c>
       <c r="H335" t="n">
         <v>0</v>
@@ -10200,7 +10200,7 @@
         <v>10</v>
       </c>
       <c r="G339" t="n">
-        <v>8.92192840576172</v>
+        <v>8.92193031311035</v>
       </c>
       <c r="H339" t="n">
         <v>8000</v>
@@ -10287,7 +10287,7 @@
         <v>10</v>
       </c>
       <c r="G342" t="n">
-        <v>8.92192840576172</v>
+        <v>8.92193031311035</v>
       </c>
       <c r="H342" t="n">
         <v>4400</v>
@@ -10316,7 +10316,7 @@
         <v>10</v>
       </c>
       <c r="G343" t="n">
-        <v>8.92192840576172</v>
+        <v>8.92193031311035</v>
       </c>
       <c r="H343" t="n">
         <v>1400</v>
@@ -10345,7 +10345,7 @@
         <v>10</v>
       </c>
       <c r="G344" t="n">
-        <v>8.92192840576172</v>
+        <v>8.92193031311035</v>
       </c>
       <c r="H344" t="n">
         <v>0</v>
@@ -10374,7 +10374,7 @@
         <v>10</v>
       </c>
       <c r="G345" t="n">
-        <v>8.92192840576172</v>
+        <v>8.92193031311035</v>
       </c>
       <c r="H345" t="n">
         <v>2000</v>
@@ -10403,7 +10403,7 @@
         <v>10</v>
       </c>
       <c r="G346" t="n">
-        <v>8.92192840576172</v>
+        <v>8.92193031311035</v>
       </c>
       <c r="H346" t="n">
         <v>14400</v>
@@ -10432,7 +10432,7 @@
         <v>10</v>
       </c>
       <c r="G347" t="n">
-        <v>8.92192840576172</v>
+        <v>8.92193031311035</v>
       </c>
       <c r="H347" t="n">
         <v>0</v>
@@ -10461,7 +10461,7 @@
         <v>10</v>
       </c>
       <c r="G348" t="n">
-        <v>8.92192840576172</v>
+        <v>8.92193031311035</v>
       </c>
       <c r="H348" t="n">
         <v>2000</v>
@@ -10490,7 +10490,7 @@
         <v>10</v>
       </c>
       <c r="G349" t="n">
-        <v>8.92192840576172</v>
+        <v>8.92193031311035</v>
       </c>
       <c r="H349" t="n">
         <v>3600</v>
@@ -10548,7 +10548,7 @@
         <v>10</v>
       </c>
       <c r="G351" t="n">
-        <v>8.92192840576172</v>
+        <v>8.92193031311035</v>
       </c>
       <c r="H351" t="n">
         <v>4000</v>
@@ -10577,7 +10577,7 @@
         <v>10</v>
       </c>
       <c r="G352" t="n">
-        <v>8.92192840576172</v>
+        <v>8.92193031311035</v>
       </c>
       <c r="H352" t="n">
         <v>0</v>
@@ -10606,7 +10606,7 @@
         <v>10</v>
       </c>
       <c r="G353" t="n">
-        <v>8.92192840576172</v>
+        <v>8.92193031311035</v>
       </c>
       <c r="H353" t="n">
         <v>400</v>
@@ -10635,7 +10635,7 @@
         <v>10</v>
       </c>
       <c r="G354" t="n">
-        <v>8.92192840576172</v>
+        <v>8.92193031311035</v>
       </c>
       <c r="H354" t="n">
         <v>4200</v>
@@ -10896,7 +10896,7 @@
         <v>10</v>
       </c>
       <c r="G363" t="n">
-        <v>8.92192840576172</v>
+        <v>8.92193031311035</v>
       </c>
       <c r="H363" t="n">
         <v>1000</v>
@@ -11012,7 +11012,7 @@
         <v>9.80000019073486</v>
       </c>
       <c r="G367" t="n">
-        <v>8.74349021911621</v>
+        <v>8.74349117279053</v>
       </c>
       <c r="H367" t="n">
         <v>2000</v>
@@ -11244,7 +11244,7 @@
         <v>10</v>
       </c>
       <c r="G375" t="n">
-        <v>8.92192840576172</v>
+        <v>8.92193031311035</v>
       </c>
       <c r="H375" t="n">
         <v>2000</v>
@@ -11273,7 +11273,7 @@
         <v>10</v>
       </c>
       <c r="G376" t="n">
-        <v>8.92192840576172</v>
+        <v>8.92193031311035</v>
       </c>
       <c r="H376" t="n">
         <v>1400</v>
@@ -11331,7 +11331,7 @@
         <v>10</v>
       </c>
       <c r="G378" t="n">
-        <v>8.92192840576172</v>
+        <v>8.92193031311035</v>
       </c>
       <c r="H378" t="n">
         <v>200</v>
@@ -11360,7 +11360,7 @@
         <v>10</v>
       </c>
       <c r="G379" t="n">
-        <v>8.92192840576172</v>
+        <v>8.92193031311035</v>
       </c>
       <c r="H379" t="n">
         <v>800</v>
@@ -11389,7 +11389,7 @@
         <v>10</v>
       </c>
       <c r="G380" t="n">
-        <v>8.92192840576172</v>
+        <v>8.92193031311035</v>
       </c>
       <c r="H380" t="n">
         <v>6600</v>
@@ -11418,7 +11418,7 @@
         <v>10</v>
       </c>
       <c r="G381" t="n">
-        <v>8.92192840576172</v>
+        <v>8.92193031311035</v>
       </c>
       <c r="H381" t="n">
         <v>0</v>
@@ -11447,7 +11447,7 @@
         <v>10</v>
       </c>
       <c r="G382" t="n">
-        <v>8.92192840576172</v>
+        <v>8.92193031311035</v>
       </c>
       <c r="H382" t="n">
         <v>0</v>
@@ -11621,7 +11621,7 @@
         <v>9.80000019073486</v>
       </c>
       <c r="G388" t="n">
-        <v>8.74349021911621</v>
+        <v>8.74349117279053</v>
       </c>
       <c r="H388" t="n">
         <v>18400</v>
@@ -11650,7 +11650,7 @@
         <v>9.80000019073486</v>
       </c>
       <c r="G389" t="n">
-        <v>8.74349021911621</v>
+        <v>8.74349117279053</v>
       </c>
       <c r="H389" t="n">
         <v>0</v>
@@ -12230,7 +12230,7 @@
         <v>9.75</v>
       </c>
       <c r="G409" t="n">
-        <v>8.69888210296631</v>
+        <v>8.69888114929199</v>
       </c>
       <c r="H409" t="n">
         <v>13800</v>
@@ -12259,7 +12259,7 @@
         <v>9.75</v>
       </c>
       <c r="G410" t="n">
-        <v>8.69888210296631</v>
+        <v>8.69888114929199</v>
       </c>
       <c r="H410" t="n">
         <v>12600</v>
@@ -12288,7 +12288,7 @@
         <v>9.75</v>
       </c>
       <c r="G411" t="n">
-        <v>8.69888210296631</v>
+        <v>8.69888114929199</v>
       </c>
       <c r="H411" t="n">
         <v>0</v>
@@ -12317,7 +12317,7 @@
         <v>9.75</v>
       </c>
       <c r="G412" t="n">
-        <v>8.69888210296631</v>
+        <v>8.69888114929199</v>
       </c>
       <c r="H412" t="n">
         <v>10000</v>
@@ -12404,7 +12404,7 @@
         <v>9.80000019073486</v>
       </c>
       <c r="G415" t="n">
-        <v>8.74349021911621</v>
+        <v>8.74349117279053</v>
       </c>
       <c r="H415" t="n">
         <v>2400</v>
@@ -12491,7 +12491,7 @@
         <v>9.80000019073486</v>
       </c>
       <c r="G418" t="n">
-        <v>8.74349021911621</v>
+        <v>8.74349117279053</v>
       </c>
       <c r="H418" t="n">
         <v>35200</v>
@@ -12520,7 +12520,7 @@
         <v>9.75</v>
       </c>
       <c r="G419" t="n">
-        <v>8.69888210296631</v>
+        <v>8.69888114929199</v>
       </c>
       <c r="H419" t="n">
         <v>600</v>
@@ -12549,7 +12549,7 @@
         <v>9.75</v>
       </c>
       <c r="G420" t="n">
-        <v>8.69888210296631</v>
+        <v>8.69888114929199</v>
       </c>
       <c r="H420" t="n">
         <v>0</v>
@@ -12578,7 +12578,7 @@
         <v>9.75</v>
       </c>
       <c r="G421" t="n">
-        <v>8.69888210296631</v>
+        <v>8.69888114929199</v>
       </c>
       <c r="H421" t="n">
         <v>800</v>
@@ -12607,7 +12607,7 @@
         <v>9.80000019073486</v>
       </c>
       <c r="G422" t="n">
-        <v>8.74349021911621</v>
+        <v>8.74349117279053</v>
       </c>
       <c r="H422" t="n">
         <v>600</v>
@@ -12984,7 +12984,7 @@
         <v>10.1999998092651</v>
       </c>
       <c r="G435" t="n">
-        <v>9.10036849975586</v>
+        <v>9.10036659240723</v>
       </c>
       <c r="H435" t="n">
         <v>10800</v>
@@ -13013,7 +13013,7 @@
         <v>10.1999998092651</v>
       </c>
       <c r="G436" t="n">
-        <v>9.10036849975586</v>
+        <v>9.10036659240723</v>
       </c>
       <c r="H436" t="n">
         <v>800</v>
@@ -13042,7 +13042,7 @@
         <v>10.1999998092651</v>
       </c>
       <c r="G437" t="n">
-        <v>9.10036849975586</v>
+        <v>9.10036659240723</v>
       </c>
       <c r="H437" t="n">
         <v>205800</v>
@@ -13071,7 +13071,7 @@
         <v>10.1999998092651</v>
       </c>
       <c r="G438" t="n">
-        <v>9.10036849975586</v>
+        <v>9.10036659240723</v>
       </c>
       <c r="H438" t="n">
         <v>4400</v>
@@ -13100,7 +13100,7 @@
         <v>10.1999998092651</v>
       </c>
       <c r="G439" t="n">
-        <v>9.10036849975586</v>
+        <v>9.10036659240723</v>
       </c>
       <c r="H439" t="n">
         <v>328400</v>
@@ -13129,7 +13129,7 @@
         <v>10.3000001907349</v>
       </c>
       <c r="G440" t="n">
-        <v>9.1895866394043</v>
+        <v>9.18958759307861</v>
       </c>
       <c r="H440" t="n">
         <v>5000</v>
@@ -13158,7 +13158,7 @@
         <v>10.3000001907349</v>
       </c>
       <c r="G441" t="n">
-        <v>9.1895866394043</v>
+        <v>9.18958759307861</v>
       </c>
       <c r="H441" t="n">
         <v>27000</v>
@@ -13187,7 +13187,7 @@
         <v>10.3000001907349</v>
       </c>
       <c r="G442" t="n">
-        <v>9.1895866394043</v>
+        <v>9.18958759307861</v>
       </c>
       <c r="H442" t="n">
         <v>1400</v>
@@ -13216,7 +13216,7 @@
         <v>10.3000001907349</v>
       </c>
       <c r="G443" t="n">
-        <v>9.1895866394043</v>
+        <v>9.18958759307861</v>
       </c>
       <c r="H443" t="n">
         <v>2400</v>
@@ -13245,7 +13245,7 @@
         <v>10.3999996185303</v>
       </c>
       <c r="G444" t="n">
-        <v>9.27880573272705</v>
+        <v>9.27880668640137</v>
       </c>
       <c r="H444" t="n">
         <v>9000</v>
@@ -13274,7 +13274,7 @@
         <v>10.3999996185303</v>
       </c>
       <c r="G445" t="n">
-        <v>9.27880573272705</v>
+        <v>9.27880668640137</v>
       </c>
       <c r="H445" t="n">
         <v>1000</v>
@@ -13303,7 +13303,7 @@
         <v>10.3999996185303</v>
       </c>
       <c r="G446" t="n">
-        <v>9.27880573272705</v>
+        <v>9.27880668640137</v>
       </c>
       <c r="H446" t="n">
         <v>0</v>
@@ -13332,7 +13332,7 @@
         <v>10.3999996185303</v>
       </c>
       <c r="G447" t="n">
-        <v>9.27880573272705</v>
+        <v>9.27880668640137</v>
       </c>
       <c r="H447" t="n">
         <v>18200</v>
@@ -13361,7 +13361,7 @@
         <v>10.3999996185303</v>
       </c>
       <c r="G448" t="n">
-        <v>9.27880573272705</v>
+        <v>9.27880668640137</v>
       </c>
       <c r="H448" t="n">
         <v>3000</v>
@@ -13390,7 +13390,7 @@
         <v>10.1999998092651</v>
       </c>
       <c r="G449" t="n">
-        <v>9.10036849975586</v>
+        <v>9.10036659240723</v>
       </c>
       <c r="H449" t="n">
         <v>8000</v>
@@ -13419,7 +13419,7 @@
         <v>10.3000001907349</v>
       </c>
       <c r="G450" t="n">
-        <v>9.1895866394043</v>
+        <v>9.18958759307861</v>
       </c>
       <c r="H450" t="n">
         <v>21000</v>
@@ -13448,7 +13448,7 @@
         <v>10.3999996185303</v>
       </c>
       <c r="G451" t="n">
-        <v>9.27880573272705</v>
+        <v>9.27880668640137</v>
       </c>
       <c r="H451" t="n">
         <v>16400</v>
@@ -13477,7 +13477,7 @@
         <v>10.3999996185303</v>
       </c>
       <c r="G452" t="n">
-        <v>9.27880573272705</v>
+        <v>9.27880668640137</v>
       </c>
       <c r="H452" t="n">
         <v>10800</v>
@@ -13506,7 +13506,7 @@
         <v>10.3999996185303</v>
       </c>
       <c r="G453" t="n">
-        <v>9.27880573272705</v>
+        <v>9.27880668640137</v>
       </c>
       <c r="H453" t="n">
         <v>30600</v>
@@ -13535,7 +13535,7 @@
         <v>10.3000001907349</v>
       </c>
       <c r="G454" t="n">
-        <v>9.1895866394043</v>
+        <v>9.18958759307861</v>
       </c>
       <c r="H454" t="n">
         <v>7000</v>
@@ -13564,7 +13564,7 @@
         <v>10.3999996185303</v>
       </c>
       <c r="G455" t="n">
-        <v>9.27880573272705</v>
+        <v>9.27880668640137</v>
       </c>
       <c r="H455" t="n">
         <v>7600</v>
@@ -13593,7 +13593,7 @@
         <v>10.3000001907349</v>
       </c>
       <c r="G456" t="n">
-        <v>9.1895866394043</v>
+        <v>9.18958759307861</v>
       </c>
       <c r="H456" t="n">
         <v>5000</v>
@@ -13622,7 +13622,7 @@
         <v>10.3999996185303</v>
       </c>
       <c r="G457" t="n">
-        <v>9.27880573272705</v>
+        <v>9.27880668640137</v>
       </c>
       <c r="H457" t="n">
         <v>34200</v>
@@ -13651,7 +13651,7 @@
         <v>10.3000001907349</v>
       </c>
       <c r="G458" t="n">
-        <v>9.1895866394043</v>
+        <v>9.18958759307861</v>
       </c>
       <c r="H458" t="n">
         <v>600</v>
@@ -13680,7 +13680,7 @@
         <v>10.3000001907349</v>
       </c>
       <c r="G459" t="n">
-        <v>9.1895866394043</v>
+        <v>9.18958759307861</v>
       </c>
       <c r="H459" t="n">
         <v>600</v>
@@ -13709,7 +13709,7 @@
         <v>10.3999996185303</v>
       </c>
       <c r="G460" t="n">
-        <v>9.27880573272705</v>
+        <v>9.27880668640137</v>
       </c>
       <c r="H460" t="n">
         <v>10000</v>
@@ -13738,7 +13738,7 @@
         <v>10.3999996185303</v>
       </c>
       <c r="G461" t="n">
-        <v>9.27880573272705</v>
+        <v>9.27880668640137</v>
       </c>
       <c r="H461" t="n">
         <v>0</v>
@@ -13767,7 +13767,7 @@
         <v>10.3000001907349</v>
       </c>
       <c r="G462" t="n">
-        <v>9.1895866394043</v>
+        <v>9.18958759307861</v>
       </c>
       <c r="H462" t="n">
         <v>2400</v>
@@ -13796,7 +13796,7 @@
         <v>10.3000001907349</v>
       </c>
       <c r="G463" t="n">
-        <v>9.1895866394043</v>
+        <v>9.18958759307861</v>
       </c>
       <c r="H463" t="n">
         <v>9600</v>
@@ -13854,7 +13854,7 @@
         <v>10.3000001907349</v>
       </c>
       <c r="G465" t="n">
-        <v>9.1895866394043</v>
+        <v>9.18958759307861</v>
       </c>
       <c r="H465" t="n">
         <v>200</v>
@@ -13941,7 +13941,7 @@
         <v>10.1999998092651</v>
       </c>
       <c r="G468" t="n">
-        <v>9.10036849975586</v>
+        <v>9.10036659240723</v>
       </c>
       <c r="H468" t="n">
         <v>12000</v>
@@ -13970,7 +13970,7 @@
         <v>10.1999998092651</v>
       </c>
       <c r="G469" t="n">
-        <v>9.10036849975586</v>
+        <v>9.10036659240723</v>
       </c>
       <c r="H469" t="n">
         <v>3000</v>
@@ -13999,7 +13999,7 @@
         <v>10.1999998092651</v>
       </c>
       <c r="G470" t="n">
-        <v>9.10036849975586</v>
+        <v>9.10036659240723</v>
       </c>
       <c r="H470" t="n">
         <v>40000</v>
@@ -14028,7 +14028,7 @@
         <v>10.1999998092651</v>
       </c>
       <c r="G471" t="n">
-        <v>9.10036849975586</v>
+        <v>9.10036659240723</v>
       </c>
       <c r="H471" t="n">
         <v>0</v>
@@ -14086,7 +14086,7 @@
         <v>10.1999998092651</v>
       </c>
       <c r="G473" t="n">
-        <v>9.10036849975586</v>
+        <v>9.10036659240723</v>
       </c>
       <c r="H473" t="n">
         <v>5000</v>
@@ -14115,7 +14115,7 @@
         <v>10.1999998092651</v>
       </c>
       <c r="G474" t="n">
-        <v>9.10036849975586</v>
+        <v>9.10036659240723</v>
       </c>
       <c r="H474" t="n">
         <v>29200</v>
@@ -14144,7 +14144,7 @@
         <v>10.3000001907349</v>
       </c>
       <c r="G475" t="n">
-        <v>9.1895866394043</v>
+        <v>9.18958759307861</v>
       </c>
       <c r="H475" t="n">
         <v>2000</v>
@@ -14173,7 +14173,7 @@
         <v>10.1999998092651</v>
       </c>
       <c r="G476" t="n">
-        <v>9.10036849975586</v>
+        <v>9.10036659240723</v>
       </c>
       <c r="H476" t="n">
         <v>400</v>
@@ -14202,7 +14202,7 @@
         <v>10.1999998092651</v>
       </c>
       <c r="G477" t="n">
-        <v>9.10036849975586</v>
+        <v>9.10036659240723</v>
       </c>
       <c r="H477" t="n">
         <v>10600</v>
@@ -14231,7 +14231,7 @@
         <v>10.1999998092651</v>
       </c>
       <c r="G478" t="n">
-        <v>9.10036849975586</v>
+        <v>9.10036659240723</v>
       </c>
       <c r="H478" t="n">
         <v>0</v>
@@ -14260,7 +14260,7 @@
         <v>10.1999998092651</v>
       </c>
       <c r="G479" t="n">
-        <v>9.10036849975586</v>
+        <v>9.10036659240723</v>
       </c>
       <c r="H479" t="n">
         <v>1600</v>
@@ -14289,7 +14289,7 @@
         <v>10.1999998092651</v>
       </c>
       <c r="G480" t="n">
-        <v>9.10036849975586</v>
+        <v>9.10036659240723</v>
       </c>
       <c r="H480" t="n">
         <v>1000</v>
@@ -14318,7 +14318,7 @@
         <v>10.1999998092651</v>
       </c>
       <c r="G481" t="n">
-        <v>9.10036849975586</v>
+        <v>9.10036659240723</v>
       </c>
       <c r="H481" t="n">
         <v>4200</v>
@@ -14376,7 +14376,7 @@
         <v>10.1999998092651</v>
       </c>
       <c r="G483" t="n">
-        <v>9.10036849975586</v>
+        <v>9.10036659240723</v>
       </c>
       <c r="H483" t="n">
         <v>11800</v>
@@ -14405,7 +14405,7 @@
         <v>10.1999998092651</v>
       </c>
       <c r="G484" t="n">
-        <v>9.10036849975586</v>
+        <v>9.10036659240723</v>
       </c>
       <c r="H484" t="n">
         <v>0</v>
@@ -14463,7 +14463,7 @@
         <v>10</v>
       </c>
       <c r="G486" t="n">
-        <v>8.92192840576172</v>
+        <v>8.92193031311035</v>
       </c>
       <c r="H486" t="n">
         <v>7200</v>
@@ -14550,7 +14550,7 @@
         <v>10.1999998092651</v>
       </c>
       <c r="G489" t="n">
-        <v>9.10036849975586</v>
+        <v>9.10036659240723</v>
       </c>
       <c r="H489" t="n">
         <v>1000</v>
@@ -14579,7 +14579,7 @@
         <v>10.1999998092651</v>
       </c>
       <c r="G490" t="n">
-        <v>9.10036849975586</v>
+        <v>9.10036659240723</v>
       </c>
       <c r="H490" t="n">
         <v>400</v>
@@ -14637,7 +14637,7 @@
         <v>10.1999998092651</v>
       </c>
       <c r="G492" t="n">
-        <v>9.10036849975586</v>
+        <v>9.10036659240723</v>
       </c>
       <c r="H492" t="n">
         <v>3200</v>
@@ -14666,7 +14666,7 @@
         <v>10</v>
       </c>
       <c r="G493" t="n">
-        <v>8.92192840576172</v>
+        <v>8.92193031311035</v>
       </c>
       <c r="H493" t="n">
         <v>800</v>
@@ -14782,7 +14782,7 @@
         <v>10</v>
       </c>
       <c r="G497" t="n">
-        <v>8.92192840576172</v>
+        <v>8.92193031311035</v>
       </c>
       <c r="H497" t="n">
         <v>9000</v>
@@ -14811,7 +14811,7 @@
         <v>9.64999961853027</v>
       </c>
       <c r="G498" t="n">
-        <v>8.60966110229492</v>
+        <v>8.60966205596924</v>
       </c>
       <c r="H498" t="n">
         <v>65200</v>
@@ -14840,7 +14840,7 @@
         <v>9.80000019073486</v>
       </c>
       <c r="G499" t="n">
-        <v>8.74349021911621</v>
+        <v>8.74349117279053</v>
       </c>
       <c r="H499" t="n">
         <v>17600</v>
@@ -14869,7 +14869,7 @@
         <v>9.75</v>
       </c>
       <c r="G500" t="n">
-        <v>8.69888210296631</v>
+        <v>8.69888114929199</v>
       </c>
       <c r="H500" t="n">
         <v>10200</v>
@@ -14956,7 +14956,7 @@
         <v>9.80000019073486</v>
       </c>
       <c r="G503" t="n">
-        <v>8.74349021911621</v>
+        <v>8.74349117279053</v>
       </c>
       <c r="H503" t="n">
         <v>1800</v>
@@ -14985,7 +14985,7 @@
         <v>9.80000019073486</v>
       </c>
       <c r="G504" t="n">
-        <v>8.74349021911621</v>
+        <v>8.74349117279053</v>
       </c>
       <c r="H504" t="n">
         <v>23000</v>
@@ -15043,7 +15043,7 @@
         <v>9.80000019073486</v>
       </c>
       <c r="G506" t="n">
-        <v>8.74349021911621</v>
+        <v>8.74349117279053</v>
       </c>
       <c r="H506" t="n">
         <v>6800</v>
@@ -15101,7 +15101,7 @@
         <v>9.80000019073486</v>
       </c>
       <c r="G508" t="n">
-        <v>8.74349021911621</v>
+        <v>8.74349117279053</v>
       </c>
       <c r="H508" t="n">
         <v>1000</v>
@@ -15188,7 +15188,7 @@
         <v>9.80000019073486</v>
       </c>
       <c r="G511" t="n">
-        <v>8.74349021911621</v>
+        <v>8.74349117279053</v>
       </c>
       <c r="H511" t="n">
         <v>1200</v>
@@ -15217,7 +15217,7 @@
         <v>9.80000019073486</v>
       </c>
       <c r="G512" t="n">
-        <v>8.74349021911621</v>
+        <v>8.74349117279053</v>
       </c>
       <c r="H512" t="n">
         <v>21800</v>
@@ -15275,7 +15275,7 @@
         <v>9.64999961853027</v>
       </c>
       <c r="G514" t="n">
-        <v>8.60966110229492</v>
+        <v>8.60966205596924</v>
       </c>
       <c r="H514" t="n">
         <v>10200</v>
@@ -15304,7 +15304,7 @@
         <v>9.64999961853027</v>
       </c>
       <c r="G515" t="n">
-        <v>8.60966110229492</v>
+        <v>8.60966205596924</v>
       </c>
       <c r="H515" t="n">
         <v>3800</v>
@@ -15362,7 +15362,7 @@
         <v>9.64999961853027</v>
       </c>
       <c r="G517" t="n">
-        <v>8.60966110229492</v>
+        <v>8.60966205596924</v>
       </c>
       <c r="H517" t="n">
         <v>2200</v>
@@ -15449,7 +15449,7 @@
         <v>9.75</v>
       </c>
       <c r="G520" t="n">
-        <v>8.69888210296631</v>
+        <v>8.69888114929199</v>
       </c>
       <c r="H520" t="n">
         <v>200</v>
@@ -15478,7 +15478,7 @@
         <v>9.75</v>
       </c>
       <c r="G521" t="n">
-        <v>8.69888210296631</v>
+        <v>8.69888114929199</v>
       </c>
       <c r="H521" t="n">
         <v>0</v>
@@ -15507,7 +15507,7 @@
         <v>9.75</v>
       </c>
       <c r="G522" t="n">
-        <v>8.69888210296631</v>
+        <v>8.69888114929199</v>
       </c>
       <c r="H522" t="n">
         <v>200</v>
@@ -15536,7 +15536,7 @@
         <v>9.64999961853027</v>
       </c>
       <c r="G523" t="n">
-        <v>8.60966110229492</v>
+        <v>8.60966205596924</v>
       </c>
       <c r="H523" t="n">
         <v>200</v>
@@ -15565,7 +15565,7 @@
         <v>9.80000019073486</v>
       </c>
       <c r="G524" t="n">
-        <v>8.74349021911621</v>
+        <v>8.74349117279053</v>
       </c>
       <c r="H524" t="n">
         <v>200</v>
@@ -15594,7 +15594,7 @@
         <v>9.80000019073486</v>
       </c>
       <c r="G525" t="n">
-        <v>8.74349021911621</v>
+        <v>8.74349117279053</v>
       </c>
       <c r="H525" t="n">
         <v>6200</v>
@@ -15623,7 +15623,7 @@
         <v>9.64999961853027</v>
       </c>
       <c r="G526" t="n">
-        <v>8.60966110229492</v>
+        <v>8.60966205596924</v>
       </c>
       <c r="H526" t="n">
         <v>4200</v>
@@ -15681,7 +15681,7 @@
         <v>9.55000019073486</v>
       </c>
       <c r="G528" t="n">
-        <v>8.52044200897217</v>
+        <v>8.52044296264648</v>
       </c>
       <c r="H528" t="n">
         <v>3400</v>
@@ -15710,7 +15710,7 @@
         <v>9.5</v>
       </c>
       <c r="G529" t="n">
-        <v>8.47583198547363</v>
+        <v>8.47583389282227</v>
       </c>
       <c r="H529" t="n">
         <v>10600</v>
@@ -15768,7 +15768,7 @@
         <v>9.19999980926514</v>
       </c>
       <c r="G531" t="n">
-        <v>8.20817470550537</v>
+        <v>8.20817565917969</v>
       </c>
       <c r="H531" t="n">
         <v>12800</v>
@@ -15855,7 +15855,7 @@
         <v>8.80000019073486</v>
       </c>
       <c r="G534" t="n">
-        <v>7.85129737854004</v>
+        <v>7.85129880905151</v>
       </c>
       <c r="H534" t="n">
         <v>9600</v>
@@ -15884,7 +15884,7 @@
         <v>8.85000038146973</v>
       </c>
       <c r="G535" t="n">
-        <v>7.89590787887573</v>
+        <v>7.89590835571289</v>
       </c>
       <c r="H535" t="n">
         <v>400</v>
@@ -15913,7 +15913,7 @@
         <v>8.85000038146973</v>
       </c>
       <c r="G536" t="n">
-        <v>7.89590787887573</v>
+        <v>7.89590835571289</v>
       </c>
       <c r="H536" t="n">
         <v>0</v>
@@ -16000,7 +16000,7 @@
         <v>9.10000038146973</v>
       </c>
       <c r="G539" t="n">
-        <v>8.11895561218262</v>
+        <v>8.11895656585693</v>
       </c>
       <c r="H539" t="n">
         <v>2200</v>
@@ -16029,7 +16029,7 @@
         <v>9.19999980926514</v>
       </c>
       <c r="G540" t="n">
-        <v>8.20817470550537</v>
+        <v>8.20817565917969</v>
       </c>
       <c r="H540" t="n">
         <v>2400</v>
@@ -16058,7 +16058,7 @@
         <v>9.19999980926514</v>
       </c>
       <c r="G541" t="n">
-        <v>8.20817470550537</v>
+        <v>8.20817565917969</v>
       </c>
       <c r="H541" t="n">
         <v>0</v>
@@ -16087,7 +16087,7 @@
         <v>9.19999980926514</v>
       </c>
       <c r="G542" t="n">
-        <v>8.20817470550537</v>
+        <v>8.20817565917969</v>
       </c>
       <c r="H542" t="n">
         <v>0</v>
@@ -16116,7 +16116,7 @@
         <v>9.10000038146973</v>
       </c>
       <c r="G543" t="n">
-        <v>8.11895561218262</v>
+        <v>8.11895656585693</v>
       </c>
       <c r="H543" t="n">
         <v>2000</v>
@@ -16145,7 +16145,7 @@
         <v>9.10000038146973</v>
       </c>
       <c r="G544" t="n">
-        <v>8.11895561218262</v>
+        <v>8.11895656585693</v>
       </c>
       <c r="H544" t="n">
         <v>0</v>
@@ -16174,7 +16174,7 @@
         <v>9.10000038146973</v>
       </c>
       <c r="G545" t="n">
-        <v>8.11895561218262</v>
+        <v>8.11895656585693</v>
       </c>
       <c r="H545" t="n">
         <v>0</v>
@@ -16232,7 +16232,7 @@
         <v>8.85000038146973</v>
       </c>
       <c r="G547" t="n">
-        <v>7.89590787887573</v>
+        <v>7.89590835571289</v>
       </c>
       <c r="H547" t="n">
         <v>5200</v>
@@ -16261,7 +16261,7 @@
         <v>8.85000038146973</v>
       </c>
       <c r="G548" t="n">
-        <v>7.89590787887573</v>
+        <v>7.89590835571289</v>
       </c>
       <c r="H548" t="n">
         <v>10200</v>
@@ -16290,7 +16290,7 @@
         <v>8.85000038146973</v>
       </c>
       <c r="G549" t="n">
-        <v>7.89590787887573</v>
+        <v>7.89590835571289</v>
       </c>
       <c r="H549" t="n">
         <v>0</v>
@@ -16319,7 +16319,7 @@
         <v>8.85000038146973</v>
       </c>
       <c r="G550" t="n">
-        <v>7.89590787887573</v>
+        <v>7.89590835571289</v>
       </c>
       <c r="H550" t="n">
         <v>0</v>
@@ -16348,7 +16348,7 @@
         <v>8.80000019073486</v>
       </c>
       <c r="G551" t="n">
-        <v>7.85129737854004</v>
+        <v>7.85129880905151</v>
       </c>
       <c r="H551" t="n">
         <v>13400</v>
@@ -16377,7 +16377,7 @@
         <v>8.80000019073486</v>
       </c>
       <c r="G552" t="n">
-        <v>7.85129737854004</v>
+        <v>7.85129880905151</v>
       </c>
       <c r="H552" t="n">
         <v>0</v>
@@ -16406,7 +16406,7 @@
         <v>8.75</v>
       </c>
       <c r="G553" t="n">
-        <v>7.80668783187866</v>
+        <v>7.80668830871582</v>
       </c>
       <c r="H553" t="n">
         <v>1400</v>
@@ -16435,7 +16435,7 @@
         <v>8.75</v>
       </c>
       <c r="G554" t="n">
-        <v>7.80668783187866</v>
+        <v>7.80668830871582</v>
       </c>
       <c r="H554" t="n">
         <v>0</v>
@@ -16464,7 +16464,7 @@
         <v>8.75</v>
       </c>
       <c r="G555" t="n">
-        <v>7.80668783187866</v>
+        <v>7.80668830871582</v>
       </c>
       <c r="H555" t="n">
         <v>0</v>
@@ -16493,7 +16493,7 @@
         <v>9.14999961853027</v>
       </c>
       <c r="G556" t="n">
-        <v>8.16356468200684</v>
+        <v>8.16356563568115</v>
       </c>
       <c r="H556" t="n">
         <v>20400</v>
@@ -16522,7 +16522,7 @@
         <v>9.05000019073486</v>
       </c>
       <c r="G557" t="n">
-        <v>8.0743465423584</v>
+        <v>8.07434558868408</v>
       </c>
       <c r="H557" t="n">
         <v>11600</v>
@@ -16667,7 +16667,7 @@
         <v>9.44999980926514</v>
       </c>
       <c r="G562" t="n">
-        <v>8.4312219619751</v>
+        <v>8.43122291564941</v>
       </c>
       <c r="H562" t="n">
         <v>600</v>
@@ -16696,7 +16696,7 @@
         <v>9.64999961853027</v>
       </c>
       <c r="G563" t="n">
-        <v>8.60966110229492</v>
+        <v>8.60966205596924</v>
       </c>
       <c r="H563" t="n">
         <v>3200</v>
@@ -16725,7 +16725,7 @@
         <v>9.55000019073486</v>
       </c>
       <c r="G564" t="n">
-        <v>8.52044200897217</v>
+        <v>8.52044296264648</v>
       </c>
       <c r="H564" t="n">
         <v>4600</v>
@@ -16754,7 +16754,7 @@
         <v>9.60000038146973</v>
       </c>
       <c r="G565" t="n">
-        <v>8.5650520324707</v>
+        <v>8.56505298614502</v>
       </c>
       <c r="H565" t="n">
         <v>3200</v>
@@ -16783,7 +16783,7 @@
         <v>9.60000038146973</v>
       </c>
       <c r="G566" t="n">
-        <v>8.5650520324707</v>
+        <v>8.56505298614502</v>
       </c>
       <c r="H566" t="n">
         <v>9400</v>
@@ -16812,7 +16812,7 @@
         <v>9.60000038146973</v>
       </c>
       <c r="G567" t="n">
-        <v>8.5650520324707</v>
+        <v>8.56505298614502</v>
       </c>
       <c r="H567" t="n">
         <v>11000</v>
@@ -16841,7 +16841,7 @@
         <v>9.64999961853027</v>
       </c>
       <c r="G568" t="n">
-        <v>8.60966110229492</v>
+        <v>8.60966205596924</v>
       </c>
       <c r="H568" t="n">
         <v>10000</v>
@@ -16870,7 +16870,7 @@
         <v>9.55000019073486</v>
       </c>
       <c r="G569" t="n">
-        <v>8.52044200897217</v>
+        <v>8.52044296264648</v>
       </c>
       <c r="H569" t="n">
         <v>6800</v>
@@ -16899,7 +16899,7 @@
         <v>9.60000038146973</v>
       </c>
       <c r="G570" t="n">
-        <v>8.5650520324707</v>
+        <v>8.56505298614502</v>
       </c>
       <c r="H570" t="n">
         <v>1600</v>
@@ -16928,7 +16928,7 @@
         <v>9.60000038146973</v>
       </c>
       <c r="G571" t="n">
-        <v>8.5650520324707</v>
+        <v>8.56505298614502</v>
       </c>
       <c r="H571" t="n">
         <v>4200</v>
@@ -16957,7 +16957,7 @@
         <v>9.60000038146973</v>
       </c>
       <c r="G572" t="n">
-        <v>8.5650520324707</v>
+        <v>8.56505298614502</v>
       </c>
       <c r="H572" t="n">
         <v>13200</v>
@@ -16986,7 +16986,7 @@
         <v>9.64999961853027</v>
       </c>
       <c r="G573" t="n">
-        <v>8.60966110229492</v>
+        <v>8.60966205596924</v>
       </c>
       <c r="H573" t="n">
         <v>5600</v>
@@ -17015,7 +17015,7 @@
         <v>9.64999961853027</v>
       </c>
       <c r="G574" t="n">
-        <v>8.60966110229492</v>
+        <v>8.60966205596924</v>
       </c>
       <c r="H574" t="n">
         <v>8200</v>
@@ -17044,7 +17044,7 @@
         <v>9.64999961853027</v>
       </c>
       <c r="G575" t="n">
-        <v>8.60966110229492</v>
+        <v>8.60966205596924</v>
       </c>
       <c r="H575" t="n">
         <v>17800</v>
@@ -17073,7 +17073,7 @@
         <v>9.64999961853027</v>
       </c>
       <c r="G576" t="n">
-        <v>8.60966110229492</v>
+        <v>8.60966205596924</v>
       </c>
       <c r="H576" t="n">
         <v>13800</v>
@@ -17131,7 +17131,7 @@
         <v>9.80000019073486</v>
       </c>
       <c r="G578" t="n">
-        <v>8.74349021911621</v>
+        <v>8.74349117279053</v>
       </c>
       <c r="H578" t="n">
         <v>5200</v>
@@ -17189,7 +17189,7 @@
         <v>9.80000019073486</v>
       </c>
       <c r="G580" t="n">
-        <v>8.74349021911621</v>
+        <v>8.74349117279053</v>
       </c>
       <c r="H580" t="n">
         <v>9800</v>
@@ -17218,7 +17218,7 @@
         <v>9.80000019073486</v>
       </c>
       <c r="G581" t="n">
-        <v>8.74349021911621</v>
+        <v>8.74349117279053</v>
       </c>
       <c r="H581" t="n">
         <v>21200</v>
@@ -17566,7 +17566,7 @@
         <v>10</v>
       </c>
       <c r="G593" t="n">
-        <v>8.92192840576172</v>
+        <v>8.92193031311035</v>
       </c>
       <c r="H593" t="n">
         <v>49400</v>
@@ -17595,7 +17595,7 @@
         <v>10</v>
       </c>
       <c r="G594" t="n">
-        <v>8.92192840576172</v>
+        <v>8.92193031311035</v>
       </c>
       <c r="H594" t="n">
         <v>45800</v>
@@ -17624,7 +17624,7 @@
         <v>10</v>
       </c>
       <c r="G595" t="n">
-        <v>8.92192840576172</v>
+        <v>8.92193031311035</v>
       </c>
       <c r="H595" t="n">
         <v>25000</v>
@@ -17682,7 +17682,7 @@
         <v>10.1999998092651</v>
       </c>
       <c r="G597" t="n">
-        <v>9.10036849975586</v>
+        <v>9.10036659240723</v>
       </c>
       <c r="H597" t="n">
         <v>20600</v>
@@ -17711,7 +17711,7 @@
         <v>10.1999998092651</v>
       </c>
       <c r="G598" t="n">
-        <v>9.10036849975586</v>
+        <v>9.10036659240723</v>
       </c>
       <c r="H598" t="n">
         <v>14200</v>
@@ -17769,7 +17769,7 @@
         <v>10.1999998092651</v>
       </c>
       <c r="G600" t="n">
-        <v>9.10036849975586</v>
+        <v>9.10036659240723</v>
       </c>
       <c r="H600" t="n">
         <v>4800</v>
@@ -17856,7 +17856,7 @@
         <v>10.1999998092651</v>
       </c>
       <c r="G603" t="n">
-        <v>9.10036849975586</v>
+        <v>9.10036659240723</v>
       </c>
       <c r="H603" t="n">
         <v>21800</v>
@@ -17914,7 +17914,7 @@
         <v>10.1999998092651</v>
       </c>
       <c r="G605" t="n">
-        <v>9.10036849975586</v>
+        <v>9.10036659240723</v>
       </c>
       <c r="H605" t="n">
         <v>63000</v>
@@ -18001,7 +18001,7 @@
         <v>10.1999998092651</v>
       </c>
       <c r="G608" t="n">
-        <v>9.10036849975586</v>
+        <v>9.10036659240723</v>
       </c>
       <c r="H608" t="n">
         <v>400</v>
@@ -18030,7 +18030,7 @@
         <v>10.1999998092651</v>
       </c>
       <c r="G609" t="n">
-        <v>9.10036849975586</v>
+        <v>9.10036659240723</v>
       </c>
       <c r="H609" t="n">
         <v>5200</v>
@@ -18088,7 +18088,7 @@
         <v>10.1999998092651</v>
       </c>
       <c r="G611" t="n">
-        <v>9.10036849975586</v>
+        <v>9.10036659240723</v>
       </c>
       <c r="H611" t="n">
         <v>22400</v>
@@ -18117,7 +18117,7 @@
         <v>10.3000001907349</v>
       </c>
       <c r="G612" t="n">
-        <v>9.1895866394043</v>
+        <v>9.18958759307861</v>
       </c>
       <c r="H612" t="n">
         <v>24600</v>
@@ -18146,7 +18146,7 @@
         <v>10.1999998092651</v>
       </c>
       <c r="G613" t="n">
-        <v>9.10036849975586</v>
+        <v>9.10036659240723</v>
       </c>
       <c r="H613" t="n">
         <v>50200</v>
@@ -18175,7 +18175,7 @@
         <v>10.3000001907349</v>
       </c>
       <c r="G614" t="n">
-        <v>9.1895866394043</v>
+        <v>9.18958759307861</v>
       </c>
       <c r="H614" t="n">
         <v>6800</v>
@@ -18204,7 +18204,7 @@
         <v>10.3999996185303</v>
       </c>
       <c r="G615" t="n">
-        <v>9.27880573272705</v>
+        <v>9.27880668640137</v>
       </c>
       <c r="H615" t="n">
         <v>14600</v>
@@ -18233,7 +18233,7 @@
         <v>10.3999996185303</v>
       </c>
       <c r="G616" t="n">
-        <v>9.27880573272705</v>
+        <v>9.27880668640137</v>
       </c>
       <c r="H616" t="n">
         <v>13600</v>
@@ -18291,7 +18291,7 @@
         <v>10.5</v>
       </c>
       <c r="G618" t="n">
-        <v>9.36802673339844</v>
+        <v>9.36802577972412</v>
       </c>
       <c r="H618" t="n">
         <v>26400</v>
@@ -18320,7 +18320,7 @@
         <v>10.5</v>
       </c>
       <c r="G619" t="n">
-        <v>9.36802673339844</v>
+        <v>9.36802577972412</v>
       </c>
       <c r="H619" t="n">
         <v>76800</v>
@@ -18436,7 +18436,7 @@
         <v>10.5</v>
       </c>
       <c r="G623" t="n">
-        <v>9.36802673339844</v>
+        <v>9.36802577972412</v>
       </c>
       <c r="H623" t="n">
         <v>39400</v>
@@ -18465,7 +18465,7 @@
         <v>10.3999996185303</v>
       </c>
       <c r="G624" t="n">
-        <v>9.27880573272705</v>
+        <v>9.27880668640137</v>
       </c>
       <c r="H624" t="n">
         <v>6000</v>
@@ -18494,7 +18494,7 @@
         <v>10.3999996185303</v>
       </c>
       <c r="G625" t="n">
-        <v>9.27880573272705</v>
+        <v>9.27880668640137</v>
       </c>
       <c r="H625" t="n">
         <v>3600</v>
@@ -18523,7 +18523,7 @@
         <v>10.5</v>
       </c>
       <c r="G626" t="n">
-        <v>9.36802673339844</v>
+        <v>9.36802577972412</v>
       </c>
       <c r="H626" t="n">
         <v>18800</v>
@@ -18552,7 +18552,7 @@
         <v>10.5</v>
       </c>
       <c r="G627" t="n">
-        <v>9.36802673339844</v>
+        <v>9.36802577972412</v>
       </c>
       <c r="H627" t="n">
         <v>17400</v>
@@ -18581,7 +18581,7 @@
         <v>10.5</v>
       </c>
       <c r="G628" t="n">
-        <v>9.36802673339844</v>
+        <v>9.36802577972412</v>
       </c>
       <c r="H628" t="n">
         <v>5800</v>
@@ -18610,7 +18610,7 @@
         <v>10.5</v>
       </c>
       <c r="G629" t="n">
-        <v>9.36802673339844</v>
+        <v>9.36802577972412</v>
       </c>
       <c r="H629" t="n">
         <v>11400</v>
@@ -18639,7 +18639,7 @@
         <v>10.5</v>
       </c>
       <c r="G630" t="n">
-        <v>9.36802673339844</v>
+        <v>9.36802577972412</v>
       </c>
       <c r="H630" t="n">
         <v>5800</v>
@@ -18668,7 +18668,7 @@
         <v>10.5</v>
       </c>
       <c r="G631" t="n">
-        <v>9.36802673339844</v>
+        <v>9.36802577972412</v>
       </c>
       <c r="H631" t="n">
         <v>2600</v>
@@ -18697,7 +18697,7 @@
         <v>10.3999996185303</v>
       </c>
       <c r="G632" t="n">
-        <v>9.27880573272705</v>
+        <v>9.27880668640137</v>
       </c>
       <c r="H632" t="n">
         <v>4600</v>
@@ -18726,7 +18726,7 @@
         <v>10.5</v>
       </c>
       <c r="G633" t="n">
-        <v>9.36802673339844</v>
+        <v>9.36802577972412</v>
       </c>
       <c r="H633" t="n">
         <v>32552</v>
@@ -18755,7 +18755,7 @@
         <v>10.5</v>
       </c>
       <c r="G634" t="n">
-        <v>9.36802673339844</v>
+        <v>9.36802577972412</v>
       </c>
       <c r="H634" t="n">
         <v>38554</v>
@@ -18784,7 +18784,7 @@
         <v>10.3999996185303</v>
       </c>
       <c r="G635" t="n">
-        <v>9.27880573272705</v>
+        <v>9.27880668640137</v>
       </c>
       <c r="H635" t="n">
         <v>26940</v>
@@ -18813,7 +18813,7 @@
         <v>10.5</v>
       </c>
       <c r="G636" t="n">
-        <v>9.36802673339844</v>
+        <v>9.36802577972412</v>
       </c>
       <c r="H636" t="n">
         <v>4300</v>
@@ -18842,7 +18842,7 @@
         <v>10.5</v>
       </c>
       <c r="G637" t="n">
-        <v>9.36802673339844</v>
+        <v>9.36802577972412</v>
       </c>
       <c r="H637" t="n">
         <v>18422</v>
@@ -18871,7 +18871,7 @@
         <v>10.3999996185303</v>
       </c>
       <c r="G638" t="n">
-        <v>9.27880573272705</v>
+        <v>9.27880668640137</v>
       </c>
       <c r="H638" t="n">
         <v>20479</v>
@@ -18900,7 +18900,7 @@
         <v>10.5</v>
       </c>
       <c r="G639" t="n">
-        <v>9.36802673339844</v>
+        <v>9.36802577972412</v>
       </c>
       <c r="H639" t="n">
         <v>14946</v>
@@ -18929,7 +18929,7 @@
         <v>10.3999996185303</v>
       </c>
       <c r="G640" t="n">
-        <v>9.27880573272705</v>
+        <v>9.27880668640137</v>
       </c>
       <c r="H640" t="n">
         <v>20526</v>
@@ -18958,7 +18958,7 @@
         <v>10.3999996185303</v>
       </c>
       <c r="G641" t="n">
-        <v>9.27880573272705</v>
+        <v>9.27880668640137</v>
       </c>
       <c r="H641" t="n">
         <v>16273</v>
@@ -18987,7 +18987,7 @@
         <v>10.3999996185303</v>
       </c>
       <c r="G642" t="n">
-        <v>9.27880573272705</v>
+        <v>9.27880668640137</v>
       </c>
       <c r="H642" t="n">
         <v>24392</v>
@@ -19016,7 +19016,7 @@
         <v>10.3000001907349</v>
       </c>
       <c r="G643" t="n">
-        <v>9.1895866394043</v>
+        <v>9.18958759307861</v>
       </c>
       <c r="H643" t="n">
         <v>13916</v>
@@ -19132,7 +19132,7 @@
         <v>10.3000001907349</v>
       </c>
       <c r="G647" t="n">
-        <v>9.2796802520752</v>
+        <v>9.27968120574951</v>
       </c>
       <c r="H647" t="n">
         <v>5125</v>
@@ -19190,7 +19190,7 @@
         <v>10</v>
       </c>
       <c r="G649" t="n">
-        <v>9.0093994140625</v>
+        <v>9.00940036773682</v>
       </c>
       <c r="H649" t="n">
         <v>8239</v>
@@ -19219,7 +19219,7 @@
         <v>10</v>
       </c>
       <c r="G650" t="n">
-        <v>9.0093994140625</v>
+        <v>9.00940036773682</v>
       </c>
       <c r="H650" t="n">
         <v>1359</v>
@@ -19248,7 +19248,7 @@
         <v>10</v>
       </c>
       <c r="G651" t="n">
-        <v>9.0093994140625</v>
+        <v>9.00940036773682</v>
       </c>
       <c r="H651" t="n">
         <v>1881</v>
@@ -19277,7 +19277,7 @@
         <v>10</v>
       </c>
       <c r="G652" t="n">
-        <v>9.0093994140625</v>
+        <v>9.00940036773682</v>
       </c>
       <c r="H652" t="n">
         <v>5346</v>
@@ -19306,7 +19306,7 @@
         <v>10</v>
       </c>
       <c r="G653" t="n">
-        <v>9.0093994140625</v>
+        <v>9.00940036773682</v>
       </c>
       <c r="H653" t="n">
         <v>5847</v>
@@ -19364,7 +19364,7 @@
         <v>10</v>
       </c>
       <c r="G655" t="n">
-        <v>9.0093994140625</v>
+        <v>9.00940036773682</v>
       </c>
       <c r="H655" t="n">
         <v>6200</v>
@@ -19393,7 +19393,7 @@
         <v>10</v>
       </c>
       <c r="G656" t="n">
-        <v>9.0093994140625</v>
+        <v>9.00940036773682</v>
       </c>
       <c r="H656" t="n">
         <v>4396</v>
@@ -19422,7 +19422,7 @@
         <v>10</v>
       </c>
       <c r="G657" t="n">
-        <v>9.0093994140625</v>
+        <v>9.00940036773682</v>
       </c>
       <c r="H657" t="n">
         <v>252</v>
@@ -19451,7 +19451,7 @@
         <v>10</v>
       </c>
       <c r="G658" t="n">
-        <v>9.0093994140625</v>
+        <v>9.00940036773682</v>
       </c>
       <c r="H658" t="n">
         <v>97</v>
@@ -19567,7 +19567,7 @@
         <v>10</v>
       </c>
       <c r="G662" t="n">
-        <v>9.0093994140625</v>
+        <v>9.00940036773682</v>
       </c>
       <c r="H662" t="n">
         <v>3769</v>
@@ -19770,7 +19770,7 @@
         <v>10</v>
       </c>
       <c r="G669" t="n">
-        <v>9.0093994140625</v>
+        <v>9.00940036773682</v>
       </c>
       <c r="H669" t="n">
         <v>9000</v>
@@ -19857,7 +19857,7 @@
         <v>9.89999961853027</v>
       </c>
       <c r="G672" t="n">
-        <v>8.91930389404297</v>
+        <v>8.91930484771729</v>
       </c>
       <c r="H672" t="n">
         <v>2834</v>
@@ -19973,7 +19973,7 @@
         <v>10</v>
       </c>
       <c r="G676" t="n">
-        <v>9.0093994140625</v>
+        <v>9.00940036773682</v>
       </c>
       <c r="H676" t="n">
         <v>8425</v>
@@ -20002,7 +20002,7 @@
         <v>10</v>
       </c>
       <c r="G677" t="n">
-        <v>9.0093994140625</v>
+        <v>9.00940036773682</v>
       </c>
       <c r="H677" t="n">
         <v>0</v>
@@ -20031,7 +20031,7 @@
         <v>10</v>
       </c>
       <c r="G678" t="n">
-        <v>9.0093994140625</v>
+        <v>9.00940036773682</v>
       </c>
       <c r="H678" t="n">
         <v>1967</v>
@@ -20060,7 +20060,7 @@
         <v>10</v>
       </c>
       <c r="G679" t="n">
-        <v>9.0093994140625</v>
+        <v>9.00940036773682</v>
       </c>
       <c r="H679" t="n">
         <v>1008</v>
@@ -20089,7 +20089,7 @@
         <v>10</v>
       </c>
       <c r="G680" t="n">
-        <v>9.0093994140625</v>
+        <v>9.00940036773682</v>
       </c>
       <c r="H680" t="n">
         <v>9553</v>
@@ -20118,7 +20118,7 @@
         <v>9.89999961853027</v>
       </c>
       <c r="G681" t="n">
-        <v>8.91930389404297</v>
+        <v>8.91930484771729</v>
       </c>
       <c r="H681" t="n">
         <v>17800</v>
@@ -20234,7 +20234,7 @@
         <v>9.89999961853027</v>
       </c>
       <c r="G685" t="n">
-        <v>8.91930389404297</v>
+        <v>8.91930484771729</v>
       </c>
       <c r="H685" t="n">
         <v>1637</v>
@@ -20263,7 +20263,7 @@
         <v>10.3000001907349</v>
       </c>
       <c r="G686" t="n">
-        <v>9.2796802520752</v>
+        <v>9.27968120574951</v>
       </c>
       <c r="H686" t="n">
         <v>6745</v>
@@ -20321,7 +20321,7 @@
         <v>10.3000001907349</v>
       </c>
       <c r="G688" t="n">
-        <v>9.2796802520752</v>
+        <v>9.27968120574951</v>
       </c>
       <c r="H688" t="n">
         <v>19506</v>
@@ -20350,7 +20350,7 @@
         <v>10.3000001907349</v>
       </c>
       <c r="G689" t="n">
-        <v>9.2796802520752</v>
+        <v>9.27968120574951</v>
       </c>
       <c r="H689" t="n">
         <v>601</v>
@@ -20437,7 +20437,7 @@
         <v>10</v>
       </c>
       <c r="G692" t="n">
-        <v>9.0093994140625</v>
+        <v>9.00940036773682</v>
       </c>
       <c r="H692" t="n">
         <v>666</v>
@@ -20466,7 +20466,7 @@
         <v>10</v>
       </c>
       <c r="G693" t="n">
-        <v>9.0093994140625</v>
+        <v>9.00940036773682</v>
       </c>
       <c r="H693" t="n">
         <v>634</v>
@@ -20582,7 +20582,7 @@
         <v>10</v>
       </c>
       <c r="G697" t="n">
-        <v>9.0093994140625</v>
+        <v>9.00940036773682</v>
       </c>
       <c r="H697" t="n">
         <v>21791</v>
@@ -20640,7 +20640,7 @@
         <v>10</v>
       </c>
       <c r="G699" t="n">
-        <v>9.0093994140625</v>
+        <v>9.00940036773682</v>
       </c>
       <c r="H699" t="n">
         <v>10723</v>
@@ -20669,7 +20669,7 @@
         <v>10</v>
       </c>
       <c r="G700" t="n">
-        <v>9.0093994140625</v>
+        <v>9.00940036773682</v>
       </c>
       <c r="H700" t="n">
         <v>935</v>
@@ -20698,7 +20698,7 @@
         <v>10</v>
       </c>
       <c r="G701" t="n">
-        <v>9.0093994140625</v>
+        <v>9.00940036773682</v>
       </c>
       <c r="H701" t="n">
         <v>18421</v>
@@ -20727,7 +20727,7 @@
         <v>10</v>
       </c>
       <c r="G702" t="n">
-        <v>9.0093994140625</v>
+        <v>9.00940036773682</v>
       </c>
       <c r="H702" t="n">
         <v>13847</v>
@@ -20756,7 +20756,7 @@
         <v>9.89999961853027</v>
       </c>
       <c r="G703" t="n">
-        <v>8.91930389404297</v>
+        <v>8.91930484771729</v>
       </c>
       <c r="H703" t="n">
         <v>35</v>
@@ -20785,7 +20785,7 @@
         <v>10</v>
       </c>
       <c r="G704" t="n">
-        <v>9.0093994140625</v>
+        <v>9.00940036773682</v>
       </c>
       <c r="H704" t="n">
         <v>417</v>
@@ -20930,7 +20930,7 @@
         <v>10</v>
       </c>
       <c r="G709" t="n">
-        <v>9.0093994140625</v>
+        <v>9.00940036773682</v>
       </c>
       <c r="H709" t="n">
         <v>11574</v>
@@ -20959,7 +20959,7 @@
         <v>10</v>
       </c>
       <c r="G710" t="n">
-        <v>9.0093994140625</v>
+        <v>9.00940036773682</v>
       </c>
       <c r="H710" t="n">
         <v>11313</v>
@@ -20988,7 +20988,7 @@
         <v>10</v>
       </c>
       <c r="G711" t="n">
-        <v>9.0093994140625</v>
+        <v>9.00940036773682</v>
       </c>
       <c r="H711" t="n">
         <v>2011</v>
@@ -21046,7 +21046,7 @@
         <v>10</v>
       </c>
       <c r="G713" t="n">
-        <v>9.0093994140625</v>
+        <v>9.00940036773682</v>
       </c>
       <c r="H713" t="n">
         <v>3561</v>
@@ -21075,7 +21075,7 @@
         <v>10</v>
       </c>
       <c r="G714" t="n">
-        <v>9.0093994140625</v>
+        <v>9.00940036773682</v>
       </c>
       <c r="H714" t="n">
         <v>370</v>
@@ -21162,7 +21162,7 @@
         <v>10</v>
       </c>
       <c r="G717" t="n">
-        <v>9.0093994140625</v>
+        <v>9.00940036773682</v>
       </c>
       <c r="H717" t="n">
         <v>4760</v>
@@ -21191,7 +21191,7 @@
         <v>10</v>
       </c>
       <c r="G718" t="n">
-        <v>9.0093994140625</v>
+        <v>9.00940036773682</v>
       </c>
       <c r="H718" t="n">
         <v>100</v>
@@ -21220,7 +21220,7 @@
         <v>9.89999961853027</v>
       </c>
       <c r="G719" t="n">
-        <v>8.91930389404297</v>
+        <v>8.91930484771729</v>
       </c>
       <c r="H719" t="n">
         <v>200</v>
@@ -21249,7 +21249,7 @@
         <v>9.89999961853027</v>
       </c>
       <c r="G720" t="n">
-        <v>8.91930389404297</v>
+        <v>8.91930484771729</v>
       </c>
       <c r="H720" t="n">
         <v>0</v>
@@ -21365,7 +21365,7 @@
         <v>10</v>
       </c>
       <c r="G724" t="n">
-        <v>9.0093994140625</v>
+        <v>9.00940036773682</v>
       </c>
       <c r="H724" t="n">
         <v>997</v>
@@ -21394,7 +21394,7 @@
         <v>10</v>
       </c>
       <c r="G725" t="n">
-        <v>9.0093994140625</v>
+        <v>9.00940036773682</v>
       </c>
       <c r="H725" t="n">
         <v>1</v>
@@ -21423,7 +21423,7 @@
         <v>10</v>
       </c>
       <c r="G726" t="n">
-        <v>9.0093994140625</v>
+        <v>9.00940036773682</v>
       </c>
       <c r="H726" t="n">
         <v>0</v>
@@ -21452,7 +21452,7 @@
         <v>10</v>
       </c>
       <c r="G727" t="n">
-        <v>9.0093994140625</v>
+        <v>9.00940036773682</v>
       </c>
       <c r="H727" t="n">
         <v>1455</v>
@@ -21481,7 +21481,7 @@
         <v>10</v>
       </c>
       <c r="G728" t="n">
-        <v>9.0093994140625</v>
+        <v>9.00940036773682</v>
       </c>
       <c r="H728" t="n">
         <v>500</v>
@@ -21510,7 +21510,7 @@
         <v>10</v>
       </c>
       <c r="G729" t="n">
-        <v>9.0093994140625</v>
+        <v>9.00940036773682</v>
       </c>
       <c r="H729" t="n">
         <v>541</v>
@@ -21539,7 +21539,7 @@
         <v>10</v>
       </c>
       <c r="G730" t="n">
-        <v>9.0093994140625</v>
+        <v>9.00940036773682</v>
       </c>
       <c r="H730" t="n">
         <v>0</v>
@@ -21713,7 +21713,7 @@
         <v>10</v>
       </c>
       <c r="G736" t="n">
-        <v>9.0093994140625</v>
+        <v>9.00940036773682</v>
       </c>
       <c r="H736" t="n">
         <v>4145</v>
@@ -21771,7 +21771,7 @@
         <v>10</v>
       </c>
       <c r="G738" t="n">
-        <v>9.0093994140625</v>
+        <v>9.00940036773682</v>
       </c>
       <c r="H738" t="n">
         <v>8175</v>
@@ -21800,7 +21800,7 @@
         <v>10</v>
       </c>
       <c r="G739" t="n">
-        <v>9.0093994140625</v>
+        <v>9.00940036773682</v>
       </c>
       <c r="H739" t="n">
         <v>9256</v>
@@ -21887,7 +21887,7 @@
         <v>10.3000001907349</v>
       </c>
       <c r="G742" t="n">
-        <v>9.2796802520752</v>
+        <v>9.27968120574951</v>
       </c>
       <c r="H742" t="n">
         <v>17701</v>
@@ -22206,7 +22206,7 @@
         <v>10.3000001907349</v>
       </c>
       <c r="G753" t="n">
-        <v>9.2796802520752</v>
+        <v>9.27968120574951</v>
       </c>
       <c r="H753" t="n">
         <v>8871</v>
@@ -22264,7 +22264,7 @@
         <v>10.5</v>
       </c>
       <c r="G755" t="n">
-        <v>9.45987033843994</v>
+        <v>9.45986843109131</v>
       </c>
       <c r="H755" t="n">
         <v>109777</v>
@@ -22815,7 +22815,7 @@
         <v>10.8999996185303</v>
       </c>
       <c r="G774" t="n">
-        <v>9.82024478912354</v>
+        <v>9.82024383544922</v>
       </c>
       <c r="H774" t="n">
         <v>3936</v>
@@ -23134,7 +23134,7 @@
         <v>10.8999996185303</v>
       </c>
       <c r="G785" t="n">
-        <v>9.82024478912354</v>
+        <v>9.82024383544922</v>
       </c>
       <c r="H785" t="n">
         <v>5615</v>
@@ -23163,7 +23163,7 @@
         <v>10.8999996185303</v>
       </c>
       <c r="G786" t="n">
-        <v>9.82024478912354</v>
+        <v>9.82024383544922</v>
       </c>
       <c r="H786" t="n">
         <v>6113</v>
@@ -23192,7 +23192,7 @@
         <v>10.8999996185303</v>
       </c>
       <c r="G787" t="n">
-        <v>9.82024478912354</v>
+        <v>9.82024383544922</v>
       </c>
       <c r="H787" t="n">
         <v>12682</v>
@@ -23221,7 +23221,7 @@
         <v>11.1000003814697</v>
       </c>
       <c r="G788" t="n">
-        <v>10.0004320144653</v>
+        <v>10.0004348754883</v>
       </c>
       <c r="H788" t="n">
         <v>19242</v>
@@ -23482,7 +23482,7 @@
         <v>11.6000003814697</v>
       </c>
       <c r="G797" t="n">
-        <v>10.4509038925171</v>
+        <v>10.4509048461914</v>
       </c>
       <c r="H797" t="n">
         <v>23568</v>
@@ -23540,7 +23540,7 @@
         <v>11.6000003814697</v>
       </c>
       <c r="G799" t="n">
-        <v>10.4509038925171</v>
+        <v>10.4509048461914</v>
       </c>
       <c r="H799" t="n">
         <v>12081</v>
@@ -23598,7 +23598,7 @@
         <v>11.6999998092651</v>
       </c>
       <c r="G801" t="n">
-        <v>10.5409965515137</v>
+        <v>10.540997505188</v>
       </c>
       <c r="H801" t="n">
         <v>69604</v>
@@ -23714,7 +23714,7 @@
         <v>11.8999996185303</v>
       </c>
       <c r="G805" t="n">
-        <v>10.7211837768555</v>
+        <v>10.7211847305298</v>
       </c>
       <c r="H805" t="n">
         <v>30450</v>
@@ -23772,7 +23772,7 @@
         <v>11.8999996185303</v>
       </c>
       <c r="G807" t="n">
-        <v>10.7211837768555</v>
+        <v>10.7211847305298</v>
       </c>
       <c r="H807" t="n">
         <v>59524</v>
@@ -23801,7 +23801,7 @@
         <v>11.8999996185303</v>
       </c>
       <c r="G808" t="n">
-        <v>10.7211837768555</v>
+        <v>10.7211847305298</v>
       </c>
       <c r="H808" t="n">
         <v>896</v>
@@ -23830,7 +23830,7 @@
         <v>11.6999998092651</v>
       </c>
       <c r="G809" t="n">
-        <v>10.5409965515137</v>
+        <v>10.540997505188</v>
       </c>
       <c r="H809" t="n">
         <v>7445</v>
@@ -23859,7 +23859,7 @@
         <v>12</v>
       </c>
       <c r="G810" t="n">
-        <v>10.811279296875</v>
+        <v>10.8112802505493</v>
       </c>
       <c r="H810" t="n">
         <v>111993</v>
@@ -23888,7 +23888,7 @@
         <v>12</v>
       </c>
       <c r="G811" t="n">
-        <v>10.811279296875</v>
+        <v>10.8112802505493</v>
       </c>
       <c r="H811" t="n">
         <v>17424</v>
@@ -23917,7 +23917,7 @@
         <v>12.1000003814697</v>
       </c>
       <c r="G812" t="n">
-        <v>10.9013738632202</v>
+        <v>10.9013729095459</v>
       </c>
       <c r="H812" t="n">
         <v>19065</v>
@@ -23946,7 +23946,7 @@
         <v>12.1000003814697</v>
       </c>
       <c r="G813" t="n">
-        <v>10.9013738632202</v>
+        <v>10.9013729095459</v>
       </c>
       <c r="H813" t="n">
         <v>3622</v>
@@ -23975,7 +23975,7 @@
         <v>12.1000003814697</v>
       </c>
       <c r="G814" t="n">
-        <v>10.9013738632202</v>
+        <v>10.9013729095459</v>
       </c>
       <c r="H814" t="n">
         <v>5715</v>
@@ -24004,7 +24004,7 @@
         <v>12</v>
       </c>
       <c r="G815" t="n">
-        <v>10.811279296875</v>
+        <v>10.8112802505493</v>
       </c>
       <c r="H815" t="n">
         <v>147502</v>
@@ -24033,7 +24033,7 @@
         <v>12.1000003814697</v>
       </c>
       <c r="G816" t="n">
-        <v>10.9013738632202</v>
+        <v>10.9013729095459</v>
       </c>
       <c r="H816" t="n">
         <v>12451</v>
@@ -24062,7 +24062,7 @@
         <v>12.1000003814697</v>
       </c>
       <c r="G817" t="n">
-        <v>10.9013738632202</v>
+        <v>10.9013729095459</v>
       </c>
       <c r="H817" t="n">
         <v>8094</v>
@@ -24149,7 +24149,7 @@
         <v>12</v>
       </c>
       <c r="G820" t="n">
-        <v>10.811279296875</v>
+        <v>10.8112802505493</v>
       </c>
       <c r="H820" t="n">
         <v>37372</v>
@@ -24178,7 +24178,7 @@
         <v>12</v>
       </c>
       <c r="G821" t="n">
-        <v>10.811279296875</v>
+        <v>10.8112802505493</v>
       </c>
       <c r="H821" t="n">
         <v>20396</v>
@@ -24207,7 +24207,7 @@
         <v>12.1000003814697</v>
       </c>
       <c r="G822" t="n">
-        <v>10.9013738632202</v>
+        <v>10.9013729095459</v>
       </c>
       <c r="H822" t="n">
         <v>8221</v>
@@ -24236,7 +24236,7 @@
         <v>12.3000001907349</v>
       </c>
       <c r="G823" t="n">
-        <v>11.081561088562</v>
+        <v>11.0815620422363</v>
       </c>
       <c r="H823" t="n">
         <v>13559</v>
@@ -24294,7 +24294,7 @@
         <v>12.3000001907349</v>
       </c>
       <c r="G825" t="n">
-        <v>11.081561088562</v>
+        <v>11.0815620422363</v>
       </c>
       <c r="H825" t="n">
         <v>56143</v>
@@ -24352,7 +24352,7 @@
         <v>12.1000003814697</v>
       </c>
       <c r="G827" t="n">
-        <v>10.9013738632202</v>
+        <v>10.9013729095459</v>
       </c>
       <c r="H827" t="n">
         <v>13104</v>
@@ -24381,7 +24381,7 @@
         <v>12</v>
       </c>
       <c r="G828" t="n">
-        <v>10.811279296875</v>
+        <v>10.8112802505493</v>
       </c>
       <c r="H828" t="n">
         <v>31355</v>
@@ -24410,7 +24410,7 @@
         <v>12.3000001907349</v>
       </c>
       <c r="G829" t="n">
-        <v>11.081561088562</v>
+        <v>11.0815620422363</v>
       </c>
       <c r="H829" t="n">
         <v>13811</v>
@@ -24468,7 +24468,7 @@
         <v>12.3000001907349</v>
       </c>
       <c r="G831" t="n">
-        <v>11.081561088562</v>
+        <v>11.0815620422363</v>
       </c>
       <c r="H831" t="n">
         <v>4605</v>
@@ -24613,7 +24613,7 @@
         <v>12.3000001907349</v>
       </c>
       <c r="G836" t="n">
-        <v>11.081561088562</v>
+        <v>11.0815620422363</v>
       </c>
       <c r="H836" t="n">
         <v>4238</v>
@@ -24671,7 +24671,7 @@
         <v>12.3000001907349</v>
       </c>
       <c r="G838" t="n">
-        <v>11.081561088562</v>
+        <v>11.0815620422363</v>
       </c>
       <c r="H838" t="n">
         <v>9765</v>
@@ -24729,7 +24729,7 @@
         <v>12.3000001907349</v>
       </c>
       <c r="G840" t="n">
-        <v>11.081561088562</v>
+        <v>11.0815620422363</v>
       </c>
       <c r="H840" t="n">
         <v>23765</v>
@@ -24758,7 +24758,7 @@
         <v>12.3999996185303</v>
       </c>
       <c r="G841" t="n">
-        <v>11.1716547012329</v>
+        <v>11.1716556549072</v>
       </c>
       <c r="H841" t="n">
         <v>40850</v>
@@ -24787,7 +24787,7 @@
         <v>12.3000001907349</v>
       </c>
       <c r="G842" t="n">
-        <v>11.081561088562</v>
+        <v>11.0815620422363</v>
       </c>
       <c r="H842" t="n">
         <v>14735</v>
@@ -24816,7 +24816,7 @@
         <v>12.3000001907349</v>
       </c>
       <c r="G843" t="n">
-        <v>11.081561088562</v>
+        <v>11.0815620422363</v>
       </c>
       <c r="H843" t="n">
         <v>23374</v>
@@ -24845,7 +24845,7 @@
         <v>12.3000001907349</v>
       </c>
       <c r="G844" t="n">
-        <v>11.081561088562</v>
+        <v>11.0815620422363</v>
       </c>
       <c r="H844" t="n">
         <v>1714</v>
@@ -24903,7 +24903,7 @@
         <v>12.1000003814697</v>
       </c>
       <c r="G846" t="n">
-        <v>10.9013738632202</v>
+        <v>10.9013729095459</v>
       </c>
       <c r="H846" t="n">
         <v>24081</v>
@@ -24961,7 +24961,7 @@
         <v>12</v>
       </c>
       <c r="G848" t="n">
-        <v>10.811279296875</v>
+        <v>10.8112802505493</v>
       </c>
       <c r="H848" t="n">
         <v>19006</v>
@@ -24990,7 +24990,7 @@
         <v>11.8999996185303</v>
       </c>
       <c r="G849" t="n">
-        <v>10.7211837768555</v>
+        <v>10.7211847305298</v>
       </c>
       <c r="H849" t="n">
         <v>33307</v>
@@ -25077,7 +25077,7 @@
         <v>11.6000003814697</v>
       </c>
       <c r="G852" t="n">
-        <v>10.4509038925171</v>
+        <v>10.4509048461914</v>
       </c>
       <c r="H852" t="n">
         <v>24301</v>
@@ -25222,7 +25222,7 @@
         <v>11.1000003814697</v>
       </c>
       <c r="G857" t="n">
-        <v>10.0004320144653</v>
+        <v>10.0004348754883</v>
       </c>
       <c r="H857" t="n">
         <v>18055</v>
@@ -25309,7 +25309,7 @@
         <v>10</v>
       </c>
       <c r="G860" t="n">
-        <v>9.0093994140625</v>
+        <v>9.00940036773682</v>
       </c>
       <c r="H860" t="n">
         <v>7755</v>
@@ -25367,7 +25367,7 @@
         <v>9.60000038146973</v>
       </c>
       <c r="G862" t="n">
-        <v>8.64902305603027</v>
+        <v>8.64902400970459</v>
       </c>
       <c r="H862" t="n">
         <v>13499</v>
@@ -25396,7 +25396,7 @@
         <v>10</v>
       </c>
       <c r="G863" t="n">
-        <v>9.0093994140625</v>
+        <v>9.00940036773682</v>
       </c>
       <c r="H863" t="n">
         <v>9235</v>
@@ -25512,7 +25512,7 @@
         <v>10</v>
       </c>
       <c r="G867" t="n">
-        <v>9.0093994140625</v>
+        <v>9.00940036773682</v>
       </c>
       <c r="H867" t="n">
         <v>7510</v>
@@ -25541,7 +25541,7 @@
         <v>10</v>
       </c>
       <c r="G868" t="n">
-        <v>9.0093994140625</v>
+        <v>9.00940036773682</v>
       </c>
       <c r="H868" t="n">
         <v>5244</v>
@@ -25570,7 +25570,7 @@
         <v>9.89999961853027</v>
       </c>
       <c r="G869" t="n">
-        <v>8.91930389404297</v>
+        <v>8.91930484771729</v>
       </c>
       <c r="H869" t="n">
         <v>1924</v>
@@ -25628,7 +25628,7 @@
         <v>10.5</v>
       </c>
       <c r="G871" t="n">
-        <v>9.45987033843994</v>
+        <v>9.45986843109131</v>
       </c>
       <c r="H871" t="n">
         <v>4639</v>
@@ -25686,7 +25686,7 @@
         <v>10.3000001907349</v>
       </c>
       <c r="G873" t="n">
-        <v>9.2796802520752</v>
+        <v>9.27968120574951</v>
       </c>
       <c r="H873" t="n">
         <v>2220</v>
@@ -25802,7 +25802,7 @@
         <v>10.0500001907349</v>
       </c>
       <c r="G877" t="n">
-        <v>9.05444717407227</v>
+        <v>9.05444622039795</v>
       </c>
       <c r="H877" t="n">
         <v>11800</v>
@@ -25831,7 +25831,7 @@
         <v>10.1499996185303</v>
       </c>
       <c r="G878" t="n">
-        <v>9.14453983306885</v>
+        <v>9.14454078674316</v>
       </c>
       <c r="H878" t="n">
         <v>1300</v>
@@ -25860,7 +25860,7 @@
         <v>9.85999965667725</v>
       </c>
       <c r="G879" t="n">
-        <v>8.88326740264893</v>
+        <v>8.88326835632324</v>
       </c>
       <c r="H879" t="n">
         <v>2160</v>
@@ -25889,7 +25889,7 @@
         <v>10</v>
       </c>
       <c r="G880" t="n">
-        <v>9.0093994140625</v>
+        <v>9.00940036773682</v>
       </c>
       <c r="H880" t="n">
         <v>14131</v>
@@ -25918,7 +25918,7 @@
         <v>10.3000001907349</v>
       </c>
       <c r="G881" t="n">
-        <v>9.2796802520752</v>
+        <v>9.27968120574951</v>
       </c>
       <c r="H881" t="n">
         <v>18487</v>
@@ -25947,7 +25947,7 @@
         <v>10.25</v>
       </c>
       <c r="G882" t="n">
-        <v>9.23463439941406</v>
+        <v>9.23463535308838</v>
       </c>
       <c r="H882" t="n">
         <v>9917</v>
@@ -25976,7 +25976,7 @@
         <v>10.5</v>
       </c>
       <c r="G883" t="n">
-        <v>9.45987033843994</v>
+        <v>9.45986843109131</v>
       </c>
       <c r="H883" t="n">
         <v>18374</v>
@@ -26034,7 +26034,7 @@
         <v>10.6499996185303</v>
       </c>
       <c r="G885" t="n">
-        <v>9.59501075744629</v>
+        <v>9.59500980377197</v>
       </c>
       <c r="H885" t="n">
         <v>676</v>
@@ -26150,7 +26150,7 @@
         <v>10.5500001907349</v>
       </c>
       <c r="G889" t="n">
-        <v>9.50491714477539</v>
+        <v>9.50491619110107</v>
       </c>
       <c r="H889" t="n">
         <v>1500</v>
@@ -26295,7 +26295,7 @@
         <v>10.6499996185303</v>
       </c>
       <c r="G894" t="n">
-        <v>9.59501075744629</v>
+        <v>9.59500980377197</v>
       </c>
       <c r="H894" t="n">
         <v>19250</v>
@@ -26382,7 +26382,7 @@
         <v>10.9499998092651</v>
       </c>
       <c r="G897" t="n">
-        <v>9.86529159545898</v>
+        <v>9.8652925491333</v>
       </c>
       <c r="H897" t="n">
         <v>3575</v>
@@ -26411,7 +26411,7 @@
         <v>10.8500003814697</v>
       </c>
       <c r="G898" t="n">
-        <v>9.7751989364624</v>
+        <v>9.77519989013672</v>
       </c>
       <c r="H898" t="n">
         <v>18584</v>
@@ -26440,7 +26440,7 @@
         <v>10.5</v>
       </c>
       <c r="G899" t="n">
-        <v>9.45987033843994</v>
+        <v>9.45986843109131</v>
       </c>
       <c r="H899" t="n">
         <v>2580</v>
@@ -26498,7 +26498,7 @@
         <v>10.6000003814697</v>
       </c>
       <c r="G901" t="n">
-        <v>9.65828037261963</v>
+        <v>9.65828132629395</v>
       </c>
       <c r="H901" t="n">
         <v>2022</v>
@@ -26527,7 +26527,7 @@
         <v>10.5</v>
       </c>
       <c r="G902" t="n">
-        <v>9.56716537475586</v>
+        <v>9.56716442108154</v>
       </c>
       <c r="H902" t="n">
         <v>8060</v>
@@ -26556,7 +26556,7 @@
         <v>10.3500003814697</v>
       </c>
       <c r="G903" t="n">
-        <v>9.43049144744873</v>
+        <v>9.43049049377441</v>
       </c>
       <c r="H903" t="n">
         <v>36431</v>
@@ -26585,7 +26585,7 @@
         <v>10.75</v>
       </c>
       <c r="G904" t="n">
-        <v>9.79495429992676</v>
+        <v>9.79495525360107</v>
       </c>
       <c r="H904" t="n">
         <v>758</v>
@@ -26643,7 +26643,7 @@
         <v>10.6000003814697</v>
       </c>
       <c r="G906" t="n">
-        <v>9.65828037261963</v>
+        <v>9.65828132629395</v>
       </c>
       <c r="H906" t="n">
         <v>360</v>
@@ -26672,7 +26672,7 @@
         <v>10.3000001907349</v>
       </c>
       <c r="G907" t="n">
-        <v>9.38493347167969</v>
+        <v>9.38493251800537</v>
       </c>
       <c r="H907" t="n">
         <v>1834</v>
@@ -26701,7 +26701,7 @@
         <v>10.8000001907349</v>
       </c>
       <c r="G908" t="n">
-        <v>9.8405122756958</v>
+        <v>9.84051322937012</v>
       </c>
       <c r="H908" t="n">
         <v>4550</v>
@@ -26730,7 +26730,7 @@
         <v>10.8000001907349</v>
       </c>
       <c r="G909" t="n">
-        <v>9.8405122756958</v>
+        <v>9.84051322937012</v>
       </c>
       <c r="H909" t="n">
         <v>238</v>
@@ -26759,7 +26759,7 @@
         <v>10.8000001907349</v>
       </c>
       <c r="G910" t="n">
-        <v>9.8405122756958</v>
+        <v>9.84051322937012</v>
       </c>
       <c r="H910" t="n">
         <v>2050</v>
@@ -26875,7 +26875,7 @@
         <v>10.9499998092651</v>
       </c>
       <c r="G914" t="n">
-        <v>9.97718715667725</v>
+        <v>9.97718620300293</v>
       </c>
       <c r="H914" t="n">
         <v>11302</v>
@@ -26933,7 +26933,7 @@
         <v>10.9499998092651</v>
       </c>
       <c r="G916" t="n">
-        <v>9.97718715667725</v>
+        <v>9.97718620300293</v>
       </c>
       <c r="H916" t="n">
         <v>143</v>
@@ -27020,7 +27020,7 @@
         <v>10.8000001907349</v>
       </c>
       <c r="G919" t="n">
-        <v>9.8405122756958</v>
+        <v>9.84051322937012</v>
       </c>
       <c r="H919" t="n">
         <v>899</v>
@@ -27078,7 +27078,7 @@
         <v>10.5</v>
       </c>
       <c r="G921" t="n">
-        <v>9.56716537475586</v>
+        <v>9.56716442108154</v>
       </c>
       <c r="H921" t="n">
         <v>15128</v>
@@ -27107,7 +27107,7 @@
         <v>10.75</v>
       </c>
       <c r="G922" t="n">
-        <v>9.79495429992676</v>
+        <v>9.79495525360107</v>
       </c>
       <c r="H922" t="n">
         <v>33283</v>
@@ -27136,7 +27136,7 @@
         <v>10.75</v>
       </c>
       <c r="G923" t="n">
-        <v>9.79495429992676</v>
+        <v>9.79495525360107</v>
       </c>
       <c r="H923" t="n">
         <v>26805</v>
@@ -27223,7 +27223,7 @@
         <v>10.75</v>
       </c>
       <c r="G926" t="n">
-        <v>9.79495429992676</v>
+        <v>9.79495525360107</v>
       </c>
       <c r="H926" t="n">
         <v>2330</v>
@@ -27281,7 +27281,7 @@
         <v>10.9499998092651</v>
       </c>
       <c r="G928" t="n">
-        <v>9.97718715667725</v>
+        <v>9.97718620300293</v>
       </c>
       <c r="H928" t="n">
         <v>502</v>
@@ -27310,7 +27310,7 @@
         <v>10.9499998092651</v>
       </c>
       <c r="G929" t="n">
-        <v>9.97718715667725</v>
+        <v>9.97718620300293</v>
       </c>
       <c r="H929" t="n">
         <v>1290</v>
@@ -27571,7 +27571,7 @@
         <v>10.8000001907349</v>
       </c>
       <c r="G938" t="n">
-        <v>9.8405122756958</v>
+        <v>9.84051322937012</v>
       </c>
       <c r="H938" t="n">
         <v>1861</v>
@@ -27600,7 +27600,7 @@
         <v>10.8000001907349</v>
       </c>
       <c r="G939" t="n">
-        <v>9.8405122756958</v>
+        <v>9.84051322937012</v>
       </c>
       <c r="H939" t="n">
         <v>472</v>
@@ -27629,7 +27629,7 @@
         <v>10.8000001907349</v>
       </c>
       <c r="G940" t="n">
-        <v>9.8405122756958</v>
+        <v>9.84051322937012</v>
       </c>
       <c r="H940" t="n">
         <v>357</v>
@@ -27687,7 +27687,7 @@
         <v>10.6000003814697</v>
       </c>
       <c r="G942" t="n">
-        <v>9.65828037261963</v>
+        <v>9.65828132629395</v>
       </c>
       <c r="H942" t="n">
         <v>311</v>
@@ -27745,7 +27745,7 @@
         <v>10.6000003814697</v>
       </c>
       <c r="G944" t="n">
-        <v>9.65828037261963</v>
+        <v>9.65828132629395</v>
       </c>
       <c r="H944" t="n">
         <v>869</v>
@@ -27803,7 +27803,7 @@
         <v>10.8000001907349</v>
       </c>
       <c r="G946" t="n">
-        <v>9.8405122756958</v>
+        <v>9.84051322937012</v>
       </c>
       <c r="H946" t="n">
         <v>5337</v>
@@ -27832,7 +27832,7 @@
         <v>10.9499998092651</v>
       </c>
       <c r="G947" t="n">
-        <v>9.97718715667725</v>
+        <v>9.97718620300293</v>
       </c>
       <c r="H947" t="n">
         <v>59288</v>
@@ -27890,7 +27890,7 @@
         <v>10.8500003814697</v>
       </c>
       <c r="G949" t="n">
-        <v>9.88607025146484</v>
+        <v>9.88607120513916</v>
       </c>
       <c r="H949" t="n">
         <v>1399</v>
@@ -28006,7 +28006,7 @@
         <v>11.0500001907349</v>
       </c>
       <c r="G953" t="n">
-        <v>10.0683031082153</v>
+        <v>10.068302154541</v>
       </c>
       <c r="H953" t="n">
         <v>31606</v>
@@ -28035,7 +28035,7 @@
         <v>11.1999998092651</v>
       </c>
       <c r="G954" t="n">
-        <v>10.2049760818481</v>
+        <v>10.2049751281738</v>
       </c>
       <c r="H954" t="n">
         <v>18997</v>
@@ -28093,7 +28093,7 @@
         <v>11.0500001907349</v>
       </c>
       <c r="G956" t="n">
-        <v>10.0683031082153</v>
+        <v>10.068302154541</v>
       </c>
       <c r="H956" t="n">
         <v>282</v>
@@ -28238,7 +28238,7 @@
         <v>11.1999998092651</v>
       </c>
       <c r="G961" t="n">
-        <v>10.2049760818481</v>
+        <v>10.2049751281738</v>
       </c>
       <c r="H961" t="n">
         <v>5288</v>
@@ -28296,7 +28296,7 @@
         <v>11.1999998092651</v>
       </c>
       <c r="G963" t="n">
-        <v>10.2049760818481</v>
+        <v>10.2049751281738</v>
       </c>
       <c r="H963" t="n">
         <v>8124</v>
@@ -28325,7 +28325,7 @@
         <v>11.1999998092651</v>
       </c>
       <c r="G964" t="n">
-        <v>10.2049760818481</v>
+        <v>10.2049751281738</v>
       </c>
       <c r="H964" t="n">
         <v>236</v>
@@ -28354,7 +28354,7 @@
         <v>11.1999998092651</v>
       </c>
       <c r="G965" t="n">
-        <v>10.2049760818481</v>
+        <v>10.2049751281738</v>
       </c>
       <c r="H965" t="n">
         <v>10203</v>
@@ -28383,7 +28383,7 @@
         <v>11.1999998092651</v>
       </c>
       <c r="G966" t="n">
-        <v>10.2049760818481</v>
+        <v>10.2049751281738</v>
       </c>
       <c r="H966" t="n">
         <v>547</v>
@@ -28615,7 +28615,7 @@
         <v>10.9499998092651</v>
       </c>
       <c r="G974" t="n">
-        <v>9.97718715667725</v>
+        <v>9.97718620300293</v>
       </c>
       <c r="H974" t="n">
         <v>900</v>
@@ -28847,7 +28847,7 @@
         <v>10.9499998092651</v>
       </c>
       <c r="G982" t="n">
-        <v>9.97718715667725</v>
+        <v>9.97718620300293</v>
       </c>
       <c r="H982" t="n">
         <v>4050</v>
@@ -28876,7 +28876,7 @@
         <v>10.9499998092651</v>
       </c>
       <c r="G983" t="n">
-        <v>9.97718715667725</v>
+        <v>9.97718620300293</v>
       </c>
       <c r="H983" t="n">
         <v>2157</v>
@@ -28905,7 +28905,7 @@
         <v>10.9499998092651</v>
       </c>
       <c r="G984" t="n">
-        <v>9.97718715667725</v>
+        <v>9.97718620300293</v>
       </c>
       <c r="H984" t="n">
         <v>0</v>
@@ -28934,7 +28934,7 @@
         <v>10.9499998092651</v>
       </c>
       <c r="G985" t="n">
-        <v>9.97718715667725</v>
+        <v>9.97718620300293</v>
       </c>
       <c r="H985" t="n">
         <v>3713</v>
@@ -29050,7 +29050,7 @@
         <v>10.8000001907349</v>
       </c>
       <c r="G989" t="n">
-        <v>9.8405122756958</v>
+        <v>9.84051322937012</v>
       </c>
       <c r="H989" t="n">
         <v>2879</v>
@@ -29137,7 +29137,7 @@
         <v>10.8000001907349</v>
       </c>
       <c r="G992" t="n">
-        <v>9.8405122756958</v>
+        <v>9.84051322937012</v>
       </c>
       <c r="H992" t="n">
         <v>1802</v>
@@ -29253,7 +29253,7 @@
         <v>10.4499998092651</v>
       </c>
       <c r="G996" t="n">
-        <v>9.52160835266113</v>
+        <v>9.5216064453125</v>
       </c>
       <c r="H996" t="n">
         <v>1795</v>
@@ -29311,7 +29311,7 @@
         <v>10.6000003814697</v>
       </c>
       <c r="G998" t="n">
-        <v>9.65828037261963</v>
+        <v>9.65828132629395</v>
       </c>
       <c r="H998" t="n">
         <v>6553</v>
@@ -29340,7 +29340,7 @@
         <v>10.6000003814697</v>
       </c>
       <c r="G999" t="n">
-        <v>9.65828037261963</v>
+        <v>9.65828132629395</v>
       </c>
       <c r="H999" t="n">
         <v>134</v>
@@ -29427,7 +29427,7 @@
         <v>10.4499998092651</v>
       </c>
       <c r="G1002" t="n">
-        <v>9.52160835266113</v>
+        <v>9.5216064453125</v>
       </c>
       <c r="H1002" t="n">
         <v>5462</v>
@@ -29456,7 +29456,7 @@
         <v>10.6000003814697</v>
       </c>
       <c r="G1003" t="n">
-        <v>9.65828037261963</v>
+        <v>9.65828132629395</v>
       </c>
       <c r="H1003" t="n">
         <v>5015</v>
@@ -29485,7 +29485,7 @@
         <v>10.3999996185303</v>
       </c>
       <c r="G1004" t="n">
-        <v>9.47604942321777</v>
+        <v>9.47604846954346</v>
       </c>
       <c r="H1004" t="n">
         <v>1509</v>
@@ -29543,7 +29543,7 @@
         <v>10.3500003814697</v>
       </c>
       <c r="G1006" t="n">
-        <v>9.43049144744873</v>
+        <v>9.43049049377441</v>
       </c>
       <c r="H1006" t="n">
         <v>3628</v>
@@ -29630,7 +29630,7 @@
         <v>9.92000007629395</v>
       </c>
       <c r="G1009" t="n">
-        <v>9.03869247436523</v>
+        <v>9.03869342803955</v>
       </c>
       <c r="H1009" t="n">
         <v>28204</v>
@@ -29833,7 +29833,7 @@
         <v>9.76000022888184</v>
       </c>
       <c r="G1016" t="n">
-        <v>8.89290714263916</v>
+        <v>8.89290618896484</v>
       </c>
       <c r="H1016" t="n">
         <v>15819</v>
@@ -29862,7 +29862,7 @@
         <v>9.84000015258789</v>
       </c>
       <c r="G1017" t="n">
-        <v>8.96580123901367</v>
+        <v>8.96579933166504</v>
       </c>
       <c r="H1017" t="n">
         <v>2452</v>
@@ -29920,7 +29920,7 @@
         <v>9.68000030517578</v>
       </c>
       <c r="G1019" t="n">
-        <v>8.82001399993896</v>
+        <v>8.82001495361328</v>
       </c>
       <c r="H1019" t="n">
         <v>1580</v>
@@ -30007,7 +30007,7 @@
         <v>9.65999984741211</v>
       </c>
       <c r="G1022" t="n">
-        <v>8.80179214477539</v>
+        <v>8.80179119110107</v>
       </c>
       <c r="H1022" t="n">
         <v>12995</v>
@@ -30065,7 +30065,7 @@
         <v>9.68000030517578</v>
       </c>
       <c r="G1024" t="n">
-        <v>8.82001399993896</v>
+        <v>8.82001495361328</v>
       </c>
       <c r="H1024" t="n">
         <v>6017</v>
@@ -30094,7 +30094,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G1025" t="n">
-        <v>8.83823871612549</v>
+        <v>8.83823776245117</v>
       </c>
       <c r="H1025" t="n">
         <v>12478</v>
@@ -30123,7 +30123,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G1026" t="n">
-        <v>8.83823871612549</v>
+        <v>8.83823776245117</v>
       </c>
       <c r="H1026" t="n">
         <v>1517</v>
@@ -30152,7 +30152,7 @@
         <v>9.46000003814697</v>
       </c>
       <c r="G1027" t="n">
-        <v>8.61956119537354</v>
+        <v>8.61956024169922</v>
       </c>
       <c r="H1027" t="n">
         <v>4125</v>
@@ -30181,7 +30181,7 @@
         <v>9.60000038146973</v>
       </c>
       <c r="G1028" t="n">
-        <v>8.74712181091309</v>
+        <v>8.7471227645874</v>
       </c>
       <c r="H1028" t="n">
         <v>2275</v>
@@ -30239,7 +30239,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G1030" t="n">
-        <v>8.83823871612549</v>
+        <v>8.83823776245117</v>
       </c>
       <c r="H1030" t="n">
         <v>1104</v>
@@ -30268,7 +30268,7 @@
         <v>9.60000038146973</v>
       </c>
       <c r="G1031" t="n">
-        <v>8.74712181091309</v>
+        <v>8.7471227645874</v>
       </c>
       <c r="H1031" t="n">
         <v>22721</v>
@@ -30297,7 +30297,7 @@
         <v>9.60000038146973</v>
       </c>
       <c r="G1032" t="n">
-        <v>8.74712181091309</v>
+        <v>8.7471227645874</v>
       </c>
       <c r="H1032" t="n">
         <v>11947</v>
@@ -30326,7 +30326,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G1033" t="n">
-        <v>8.83823871612549</v>
+        <v>8.83823776245117</v>
       </c>
       <c r="H1033" t="n">
         <v>6924</v>
@@ -30500,7 +30500,7 @@
         <v>11.0500001907349</v>
       </c>
       <c r="G1039" t="n">
-        <v>10.0683031082153</v>
+        <v>10.068302154541</v>
       </c>
       <c r="H1039" t="n">
         <v>16443</v>
@@ -30732,7 +30732,7 @@
         <v>11.1499996185303</v>
       </c>
       <c r="G1047" t="n">
-        <v>10.1594171524048</v>
+        <v>10.1594161987305</v>
       </c>
       <c r="H1047" t="n">
         <v>11652</v>
@@ -30761,7 +30761,7 @@
         <v>10.9499998092651</v>
       </c>
       <c r="G1048" t="n">
-        <v>9.97718715667725</v>
+        <v>9.97718620300293</v>
       </c>
       <c r="H1048" t="n">
         <v>16113</v>
@@ -30790,7 +30790,7 @@
         <v>10.9499998092651</v>
       </c>
       <c r="G1049" t="n">
-        <v>9.97718715667725</v>
+        <v>9.97718620300293</v>
       </c>
       <c r="H1049" t="n">
         <v>7113</v>
@@ -30819,7 +30819,7 @@
         <v>10.9499998092651</v>
       </c>
       <c r="G1050" t="n">
-        <v>9.97718715667725</v>
+        <v>9.97718620300293</v>
       </c>
       <c r="H1050" t="n">
         <v>6511</v>
@@ -30906,7 +30906,7 @@
         <v>10.9499998092651</v>
       </c>
       <c r="G1053" t="n">
-        <v>9.97718715667725</v>
+        <v>9.97718620300293</v>
       </c>
       <c r="H1053" t="n">
         <v>4421</v>
@@ -30964,7 +30964,7 @@
         <v>10.9499998092651</v>
       </c>
       <c r="G1055" t="n">
-        <v>9.97718715667725</v>
+        <v>9.97718620300293</v>
       </c>
       <c r="H1055" t="n">
         <v>4602</v>
@@ -30993,7 +30993,7 @@
         <v>10.8000001907349</v>
       </c>
       <c r="G1056" t="n">
-        <v>9.8405122756958</v>
+        <v>9.84051322937012</v>
       </c>
       <c r="H1056" t="n">
         <v>19566</v>
@@ -31022,7 +31022,7 @@
         <v>10.9499998092651</v>
       </c>
       <c r="G1057" t="n">
-        <v>9.97718715667725</v>
+        <v>9.97718620300293</v>
       </c>
       <c r="H1057" t="n">
         <v>613</v>
@@ -31051,7 +31051,7 @@
         <v>10.8500003814697</v>
       </c>
       <c r="G1058" t="n">
-        <v>9.88607025146484</v>
+        <v>9.88607120513916</v>
       </c>
       <c r="H1058" t="n">
         <v>15783</v>
@@ -31080,7 +31080,7 @@
         <v>10.8000001907349</v>
       </c>
       <c r="G1059" t="n">
-        <v>9.8405122756958</v>
+        <v>9.84051322937012</v>
       </c>
       <c r="H1059" t="n">
         <v>400</v>
@@ -31109,7 +31109,7 @@
         <v>10.75</v>
       </c>
       <c r="G1060" t="n">
-        <v>9.79495429992676</v>
+        <v>9.79495525360107</v>
       </c>
       <c r="H1060" t="n">
         <v>3130</v>
@@ -31138,7 +31138,7 @@
         <v>10.6000003814697</v>
       </c>
       <c r="G1061" t="n">
-        <v>9.65828037261963</v>
+        <v>9.65828132629395</v>
       </c>
       <c r="H1061" t="n">
         <v>5560</v>
@@ -31196,7 +31196,7 @@
         <v>10.75</v>
       </c>
       <c r="G1063" t="n">
-        <v>9.79495429992676</v>
+        <v>9.79495525360107</v>
       </c>
       <c r="H1063" t="n">
         <v>8500</v>
@@ -31225,7 +31225,7 @@
         <v>10.5</v>
       </c>
       <c r="G1064" t="n">
-        <v>9.56716537475586</v>
+        <v>9.56716442108154</v>
       </c>
       <c r="H1064" t="n">
         <v>30990</v>
@@ -31254,7 +31254,7 @@
         <v>10.3999996185303</v>
       </c>
       <c r="G1065" t="n">
-        <v>9.47604942321777</v>
+        <v>9.47604846954346</v>
       </c>
       <c r="H1065" t="n">
         <v>9282</v>
@@ -31283,7 +31283,7 @@
         <v>10.5</v>
       </c>
       <c r="G1066" t="n">
-        <v>9.56716537475586</v>
+        <v>9.56716442108154</v>
       </c>
       <c r="H1066" t="n">
         <v>5535</v>
@@ -31312,7 +31312,7 @@
         <v>10.6000003814697</v>
       </c>
       <c r="G1067" t="n">
-        <v>9.65828037261963</v>
+        <v>9.65828132629395</v>
       </c>
       <c r="H1067" t="n">
         <v>2591</v>
@@ -31399,7 +31399,7 @@
         <v>10.8000001907349</v>
       </c>
       <c r="G1070" t="n">
-        <v>9.8405122756958</v>
+        <v>9.84051322937012</v>
       </c>
       <c r="H1070" t="n">
         <v>14898</v>
@@ -31457,7 +31457,7 @@
         <v>10.75</v>
       </c>
       <c r="G1072" t="n">
-        <v>9.79495429992676</v>
+        <v>9.79495525360107</v>
       </c>
       <c r="H1072" t="n">
         <v>18487</v>
@@ -31486,7 +31486,7 @@
         <v>10.8000001907349</v>
       </c>
       <c r="G1073" t="n">
-        <v>9.8405122756958</v>
+        <v>9.84051322937012</v>
       </c>
       <c r="H1073" t="n">
         <v>1135</v>
@@ -31515,7 +31515,7 @@
         <v>10.8500003814697</v>
       </c>
       <c r="G1074" t="n">
-        <v>9.88607025146484</v>
+        <v>9.88607120513916</v>
       </c>
       <c r="H1074" t="n">
         <v>6030</v>
@@ -31544,7 +31544,7 @@
         <v>10.8500003814697</v>
       </c>
       <c r="G1075" t="n">
-        <v>9.88607025146484</v>
+        <v>9.88607120513916</v>
       </c>
       <c r="H1075" t="n">
         <v>2661</v>
@@ -31573,7 +31573,7 @@
         <v>10.8500003814697</v>
       </c>
       <c r="G1076" t="n">
-        <v>9.88607025146484</v>
+        <v>9.88607120513916</v>
       </c>
       <c r="H1076" t="n">
         <v>3712</v>
@@ -31602,7 +31602,7 @@
         <v>10.75</v>
       </c>
       <c r="G1077" t="n">
-        <v>9.79495429992676</v>
+        <v>9.79495525360107</v>
       </c>
       <c r="H1077" t="n">
         <v>4356</v>
@@ -31631,7 +31631,7 @@
         <v>10.75</v>
       </c>
       <c r="G1078" t="n">
-        <v>9.79495429992676</v>
+        <v>9.79495525360107</v>
       </c>
       <c r="H1078" t="n">
         <v>45</v>
@@ -31660,7 +31660,7 @@
         <v>10.75</v>
       </c>
       <c r="G1079" t="n">
-        <v>9.79495429992676</v>
+        <v>9.79495525360107</v>
       </c>
       <c r="H1079" t="n">
         <v>9723</v>
@@ -31747,7 +31747,7 @@
         <v>10.6000003814697</v>
       </c>
       <c r="G1082" t="n">
-        <v>9.65828037261963</v>
+        <v>9.65828132629395</v>
       </c>
       <c r="H1082" t="n">
         <v>10531</v>
@@ -31776,7 +31776,7 @@
         <v>10.6000003814697</v>
       </c>
       <c r="G1083" t="n">
-        <v>9.65828037261963</v>
+        <v>9.65828132629395</v>
       </c>
       <c r="H1083" t="n">
         <v>3666</v>
@@ -31805,7 +31805,7 @@
         <v>10.3500003814697</v>
       </c>
       <c r="G1084" t="n">
-        <v>9.43049144744873</v>
+        <v>9.43049049377441</v>
       </c>
       <c r="H1084" t="n">
         <v>6448</v>
@@ -31834,7 +31834,7 @@
         <v>10.3000001907349</v>
       </c>
       <c r="G1085" t="n">
-        <v>9.38493347167969</v>
+        <v>9.38493251800537</v>
       </c>
       <c r="H1085" t="n">
         <v>34653</v>
@@ -31921,7 +31921,7 @@
         <v>10.6000003814697</v>
       </c>
       <c r="G1088" t="n">
-        <v>9.65828037261963</v>
+        <v>9.65828132629395</v>
       </c>
       <c r="H1088" t="n">
         <v>1963</v>
@@ -31950,7 +31950,7 @@
         <v>10.8000001907349</v>
       </c>
       <c r="G1089" t="n">
-        <v>9.8405122756958</v>
+        <v>9.84051322937012</v>
       </c>
       <c r="H1089" t="n">
         <v>14366</v>
@@ -31979,7 +31979,7 @@
         <v>10.8000001907349</v>
       </c>
       <c r="G1090" t="n">
-        <v>9.8405122756958</v>
+        <v>9.84051322937012</v>
       </c>
       <c r="H1090" t="n">
         <v>906</v>
@@ -32037,7 +32037,7 @@
         <v>10.8500003814697</v>
       </c>
       <c r="G1092" t="n">
-        <v>9.88607025146484</v>
+        <v>9.88607120513916</v>
       </c>
       <c r="H1092" t="n">
         <v>6196</v>
@@ -32066,7 +32066,7 @@
         <v>10.8500003814697</v>
       </c>
       <c r="G1093" t="n">
-        <v>9.88607025146484</v>
+        <v>9.88607120513916</v>
       </c>
       <c r="H1093" t="n">
         <v>9361</v>
@@ -32182,7 +32182,7 @@
         <v>10.6000003814697</v>
       </c>
       <c r="G1097" t="n">
-        <v>9.65828037261963</v>
+        <v>9.65828132629395</v>
       </c>
       <c r="H1097" t="n">
         <v>5284</v>
@@ -32211,7 +32211,7 @@
         <v>10.75</v>
       </c>
       <c r="G1098" t="n">
-        <v>9.79495429992676</v>
+        <v>9.79495525360107</v>
       </c>
       <c r="H1098" t="n">
         <v>5377</v>
@@ -32240,7 +32240,7 @@
         <v>10.8000001907349</v>
       </c>
       <c r="G1099" t="n">
-        <v>9.8405122756958</v>
+        <v>9.84051322937012</v>
       </c>
       <c r="H1099" t="n">
         <v>9104</v>
@@ -32269,7 +32269,7 @@
         <v>10.8000001907349</v>
       </c>
       <c r="G1100" t="n">
-        <v>9.8405122756958</v>
+        <v>9.84051322937012</v>
       </c>
       <c r="H1100" t="n">
         <v>24254</v>
@@ -32298,7 +32298,7 @@
         <v>10.75</v>
       </c>
       <c r="G1101" t="n">
-        <v>9.79495429992676</v>
+        <v>9.79495525360107</v>
       </c>
       <c r="H1101" t="n">
         <v>13932</v>
@@ -32356,7 +32356,7 @@
         <v>10.9499998092651</v>
       </c>
       <c r="G1103" t="n">
-        <v>9.97718715667725</v>
+        <v>9.97718620300293</v>
       </c>
       <c r="H1103" t="n">
         <v>10723</v>
@@ -32414,7 +32414,7 @@
         <v>10.8000001907349</v>
       </c>
       <c r="G1105" t="n">
-        <v>9.8405122756958</v>
+        <v>9.84051322937012</v>
       </c>
       <c r="H1105" t="n">
         <v>3539</v>
@@ -32472,7 +32472,7 @@
         <v>10.8000001907349</v>
       </c>
       <c r="G1107" t="n">
-        <v>9.8405122756958</v>
+        <v>9.84051322937012</v>
       </c>
       <c r="H1107" t="n">
         <v>4910</v>
@@ -32501,7 +32501,7 @@
         <v>10.8000001907349</v>
       </c>
       <c r="G1108" t="n">
-        <v>9.8405122756958</v>
+        <v>9.84051322937012</v>
       </c>
       <c r="H1108" t="n">
         <v>3654</v>
@@ -32559,7 +32559,7 @@
         <v>10.8000001907349</v>
       </c>
       <c r="G1110" t="n">
-        <v>9.8405122756958</v>
+        <v>9.84051322937012</v>
       </c>
       <c r="H1110" t="n">
         <v>2457</v>
@@ -32617,7 +32617,7 @@
         <v>10.8000001907349</v>
       </c>
       <c r="G1112" t="n">
-        <v>9.8405122756958</v>
+        <v>9.84051322937012</v>
       </c>
       <c r="H1112" t="n">
         <v>4426</v>
@@ -32675,7 +32675,7 @@
         <v>10.8000001907349</v>
       </c>
       <c r="G1114" t="n">
-        <v>9.8405122756958</v>
+        <v>9.84051322937012</v>
       </c>
       <c r="H1114" t="n">
         <v>1323</v>
@@ -32704,7 +32704,7 @@
         <v>10.75</v>
       </c>
       <c r="G1115" t="n">
-        <v>9.79495429992676</v>
+        <v>9.79495525360107</v>
       </c>
       <c r="H1115" t="n">
         <v>6893</v>
@@ -32733,7 +32733,7 @@
         <v>10.75</v>
       </c>
       <c r="G1116" t="n">
-        <v>9.79495429992676</v>
+        <v>9.79495525360107</v>
       </c>
       <c r="H1116" t="n">
         <v>6550</v>
@@ -32762,7 +32762,7 @@
         <v>10.9499998092651</v>
       </c>
       <c r="G1117" t="n">
-        <v>9.97718715667725</v>
+        <v>9.97718620300293</v>
       </c>
       <c r="H1117" t="n">
         <v>6390</v>
@@ -32878,7 +32878,7 @@
         <v>11.0500001907349</v>
       </c>
       <c r="G1121" t="n">
-        <v>10.0683031082153</v>
+        <v>10.068302154541</v>
       </c>
       <c r="H1121" t="n">
         <v>5584</v>
@@ -32907,7 +32907,7 @@
         <v>11.1499996185303</v>
       </c>
       <c r="G1122" t="n">
-        <v>10.1594171524048</v>
+        <v>10.1594161987305</v>
       </c>
       <c r="H1122" t="n">
         <v>15698</v>
@@ -33023,7 +33023,7 @@
         <v>10.9499998092651</v>
       </c>
       <c r="G1126" t="n">
-        <v>9.97718715667725</v>
+        <v>9.97718620300293</v>
       </c>
       <c r="H1126" t="n">
         <v>1792</v>
@@ -33052,7 +33052,7 @@
         <v>11.0500001907349</v>
       </c>
       <c r="G1127" t="n">
-        <v>10.0683031082153</v>
+        <v>10.068302154541</v>
       </c>
       <c r="H1127" t="n">
         <v>12329</v>
@@ -33139,7 +33139,7 @@
         <v>11.8999996185303</v>
       </c>
       <c r="G1130" t="n">
-        <v>10.8427858352661</v>
+        <v>10.8427867889404</v>
       </c>
       <c r="H1130" t="n">
         <v>13781</v>
@@ -33168,7 +33168,7 @@
         <v>12.1000003814697</v>
       </c>
       <c r="G1131" t="n">
-        <v>11.0250186920166</v>
+        <v>11.0250196456909</v>
       </c>
       <c r="H1131" t="n">
         <v>13540</v>
@@ -33197,7 +33197,7 @@
         <v>12.3999996185303</v>
       </c>
       <c r="G1132" t="n">
-        <v>11.2983646392822</v>
+        <v>11.2983655929565</v>
       </c>
       <c r="H1132" t="n">
         <v>74102</v>
@@ -33284,7 +33284,7 @@
         <v>12.5500001907349</v>
       </c>
       <c r="G1135" t="n">
-        <v>11.4350395202637</v>
+        <v>11.435040473938</v>
       </c>
       <c r="H1135" t="n">
         <v>17670</v>
@@ -33371,7 +33371,7 @@
         <v>12.5500001907349</v>
       </c>
       <c r="G1138" t="n">
-        <v>11.4350395202637</v>
+        <v>11.435040473938</v>
       </c>
       <c r="H1138" t="n">
         <v>9552</v>
@@ -33400,7 +33400,7 @@
         <v>12.8500003814697</v>
       </c>
       <c r="G1139" t="n">
-        <v>11.7083873748779</v>
+        <v>11.7083892822266</v>
       </c>
       <c r="H1139" t="n">
         <v>22061</v>
@@ -33429,7 +33429,7 @@
         <v>12.8999996185303</v>
       </c>
       <c r="G1140" t="n">
-        <v>11.7539443969727</v>
+        <v>11.753945350647</v>
       </c>
       <c r="H1140" t="n">
         <v>36171</v>
@@ -33458,7 +33458,7 @@
         <v>12.8999996185303</v>
       </c>
       <c r="G1141" t="n">
-        <v>11.7539443969727</v>
+        <v>11.753945350647</v>
       </c>
       <c r="H1141" t="n">
         <v>13867</v>
@@ -33487,7 +33487,7 @@
         <v>13.1499996185303</v>
       </c>
       <c r="G1142" t="n">
-        <v>11.9817352294922</v>
+        <v>11.9817342758179</v>
       </c>
       <c r="H1142" t="n">
         <v>17446</v>
@@ -33516,7 +33516,7 @@
         <v>13.25</v>
       </c>
       <c r="G1143" t="n">
-        <v>12.0728521347046</v>
+        <v>12.072850227356</v>
       </c>
       <c r="H1143" t="n">
         <v>34754</v>
@@ -33574,7 +33574,7 @@
         <v>13.5</v>
       </c>
       <c r="G1145" t="n">
-        <v>12.3006401062012</v>
+        <v>12.3006391525269</v>
       </c>
       <c r="H1145" t="n">
         <v>75731</v>
@@ -33632,7 +33632,7 @@
         <v>13.1000003814697</v>
       </c>
       <c r="G1147" t="n">
-        <v>11.9361782073975</v>
+        <v>11.9361772537231</v>
       </c>
       <c r="H1147" t="n">
         <v>3372</v>
@@ -33661,7 +33661,7 @@
         <v>13.0500001907349</v>
       </c>
       <c r="G1148" t="n">
-        <v>11.8906202316284</v>
+        <v>11.8906192779541</v>
       </c>
       <c r="H1148" t="n">
         <v>8972</v>
@@ -33690,7 +33690,7 @@
         <v>13.1000003814697</v>
       </c>
       <c r="G1149" t="n">
-        <v>11.9361782073975</v>
+        <v>11.9361772537231</v>
       </c>
       <c r="H1149" t="n">
         <v>7550</v>
@@ -33777,7 +33777,7 @@
         <v>13.5</v>
       </c>
       <c r="G1152" t="n">
-        <v>12.4335174560547</v>
+        <v>12.4335165023804</v>
       </c>
       <c r="H1152" t="n">
         <v>6951</v>
@@ -33835,7 +33835,7 @@
         <v>13.25</v>
       </c>
       <c r="G1154" t="n">
-        <v>12.2032680511475</v>
+        <v>12.2032661437988</v>
       </c>
       <c r="H1154" t="n">
         <v>6770</v>
@@ -33864,7 +33864,7 @@
         <v>13.5</v>
       </c>
       <c r="G1155" t="n">
-        <v>12.4335174560547</v>
+        <v>12.4335165023804</v>
       </c>
       <c r="H1155" t="n">
         <v>40169</v>
@@ -33893,7 +33893,7 @@
         <v>13.6000003814697</v>
       </c>
       <c r="G1156" t="n">
-        <v>12.5256185531616</v>
+        <v>12.525616645813</v>
       </c>
       <c r="H1156" t="n">
         <v>18328</v>
@@ -33922,7 +33922,7 @@
         <v>13.5</v>
       </c>
       <c r="G1157" t="n">
-        <v>12.4335174560547</v>
+        <v>12.4335165023804</v>
       </c>
       <c r="H1157" t="n">
         <v>24760</v>
@@ -33951,7 +33951,7 @@
         <v>13.6000003814697</v>
       </c>
       <c r="G1158" t="n">
-        <v>12.5256185531616</v>
+        <v>12.525616645813</v>
       </c>
       <c r="H1158" t="n">
         <v>13524</v>
@@ -34009,7 +34009,7 @@
         <v>13.5500001907349</v>
       </c>
       <c r="G1160" t="n">
-        <v>12.479567527771</v>
+        <v>12.4795665740967</v>
       </c>
       <c r="H1160" t="n">
         <v>28389</v>
@@ -34038,7 +34038,7 @@
         <v>13.6000003814697</v>
       </c>
       <c r="G1161" t="n">
-        <v>12.5256185531616</v>
+        <v>12.525616645813</v>
       </c>
       <c r="H1161" t="n">
         <v>12700</v>
@@ -34096,7 +34096,7 @@
         <v>13.25</v>
       </c>
       <c r="G1163" t="n">
-        <v>12.2032680511475</v>
+        <v>12.2032661437988</v>
       </c>
       <c r="H1163" t="n">
         <v>29089</v>
@@ -34125,7 +34125,7 @@
         <v>13.25</v>
       </c>
       <c r="G1164" t="n">
-        <v>12.2032680511475</v>
+        <v>12.2032661437988</v>
       </c>
       <c r="H1164" t="n">
         <v>25726</v>
@@ -34154,7 +34154,7 @@
         <v>13.0500001907349</v>
       </c>
       <c r="G1165" t="n">
-        <v>12.0190677642822</v>
+        <v>12.0190668106079</v>
       </c>
       <c r="H1165" t="n">
         <v>3456</v>
@@ -34212,7 +34212,7 @@
         <v>13.25</v>
       </c>
       <c r="G1167" t="n">
-        <v>12.2032680511475</v>
+        <v>12.2032661437988</v>
       </c>
       <c r="H1167" t="n">
         <v>15931</v>
@@ -34241,7 +34241,7 @@
         <v>13.1499996185303</v>
       </c>
       <c r="G1168" t="n">
-        <v>12.1111669540405</v>
+        <v>12.1111660003662</v>
       </c>
       <c r="H1168" t="n">
         <v>13997</v>
@@ -34270,7 +34270,7 @@
         <v>13.1000003814697</v>
       </c>
       <c r="G1169" t="n">
-        <v>12.0651178359985</v>
+        <v>12.0651168823242</v>
       </c>
       <c r="H1169" t="n">
         <v>14679</v>
@@ -34328,7 +34328,7 @@
         <v>13.25</v>
       </c>
       <c r="G1171" t="n">
-        <v>12.2032680511475</v>
+        <v>12.2032661437988</v>
       </c>
       <c r="H1171" t="n">
         <v>29663</v>
@@ -34386,7 +34386,7 @@
         <v>13.6000003814697</v>
       </c>
       <c r="G1173" t="n">
-        <v>12.5256185531616</v>
+        <v>12.525616645813</v>
       </c>
       <c r="H1173" t="n">
         <v>110733</v>
@@ -34415,7 +34415,7 @@
         <v>13.5500001907349</v>
       </c>
       <c r="G1174" t="n">
-        <v>12.479567527771</v>
+        <v>12.4795665740967</v>
       </c>
       <c r="H1174" t="n">
         <v>17802</v>
@@ -34502,7 +34502,7 @@
         <v>13.5</v>
       </c>
       <c r="G1177" t="n">
-        <v>12.4335174560547</v>
+        <v>12.4335165023804</v>
       </c>
       <c r="H1177" t="n">
         <v>6774</v>
@@ -34531,7 +34531,7 @@
         <v>13.4499998092651</v>
       </c>
       <c r="G1178" t="n">
-        <v>12.3874683380127</v>
+        <v>12.3874664306641</v>
       </c>
       <c r="H1178" t="n">
         <v>10766</v>
@@ -34560,7 +34560,7 @@
         <v>13.6000003814697</v>
       </c>
       <c r="G1179" t="n">
-        <v>12.5256185531616</v>
+        <v>12.525616645813</v>
       </c>
       <c r="H1179" t="n">
         <v>3641</v>
@@ -34589,7 +34589,7 @@
         <v>13.6000003814697</v>
       </c>
       <c r="G1180" t="n">
-        <v>12.5256185531616</v>
+        <v>12.525616645813</v>
       </c>
       <c r="H1180" t="n">
         <v>17307</v>
@@ -34618,7 +34618,7 @@
         <v>13.6000003814697</v>
       </c>
       <c r="G1181" t="n">
-        <v>12.5256185531616</v>
+        <v>12.525616645813</v>
       </c>
       <c r="H1181" t="n">
         <v>2093</v>
@@ -34647,7 +34647,7 @@
         <v>13.6000003814697</v>
       </c>
       <c r="G1182" t="n">
-        <v>12.5256185531616</v>
+        <v>12.525616645813</v>
       </c>
       <c r="H1182" t="n">
         <v>8035</v>
@@ -34676,7 +34676,7 @@
         <v>13.5500001907349</v>
       </c>
       <c r="G1183" t="n">
-        <v>12.479567527771</v>
+        <v>12.4795665740967</v>
       </c>
       <c r="H1183" t="n">
         <v>16220</v>
@@ -34705,7 +34705,7 @@
         <v>13.4499998092651</v>
       </c>
       <c r="G1184" t="n">
-        <v>12.3874683380127</v>
+        <v>12.3874664306641</v>
       </c>
       <c r="H1184" t="n">
         <v>7360</v>
@@ -34734,7 +34734,7 @@
         <v>13.6000003814697</v>
       </c>
       <c r="G1185" t="n">
-        <v>12.5256185531616</v>
+        <v>12.525616645813</v>
       </c>
       <c r="H1185" t="n">
         <v>6448</v>
@@ -34763,7 +34763,7 @@
         <v>13.6000003814697</v>
       </c>
       <c r="G1186" t="n">
-        <v>12.5256185531616</v>
+        <v>12.525616645813</v>
       </c>
       <c r="H1186" t="n">
         <v>7807</v>
@@ -34792,7 +34792,7 @@
         <v>13.5</v>
       </c>
       <c r="G1187" t="n">
-        <v>12.4335174560547</v>
+        <v>12.4335165023804</v>
       </c>
       <c r="H1187" t="n">
         <v>6462</v>
@@ -34821,7 +34821,7 @@
         <v>13.5500001907349</v>
       </c>
       <c r="G1188" t="n">
-        <v>12.479567527771</v>
+        <v>12.4795665740967</v>
       </c>
       <c r="H1188" t="n">
         <v>22832</v>
@@ -34879,7 +34879,7 @@
         <v>13.4499998092651</v>
       </c>
       <c r="G1190" t="n">
-        <v>12.3874683380127</v>
+        <v>12.3874664306641</v>
       </c>
       <c r="H1190" t="n">
         <v>5662</v>
@@ -35053,7 +35053,7 @@
         <v>13.1000003814697</v>
       </c>
       <c r="G1196" t="n">
-        <v>12.0651178359985</v>
+        <v>12.0651168823242</v>
       </c>
       <c r="H1196" t="n">
         <v>5195</v>
@@ -35111,7 +35111,7 @@
         <v>13.4499998092651</v>
       </c>
       <c r="G1198" t="n">
-        <v>12.3874683380127</v>
+        <v>12.3874664306641</v>
       </c>
       <c r="H1198" t="n">
         <v>19804</v>
@@ -35140,7 +35140,7 @@
         <v>13.6000003814697</v>
       </c>
       <c r="G1199" t="n">
-        <v>12.5256185531616</v>
+        <v>12.525616645813</v>
       </c>
       <c r="H1199" t="n">
         <v>24469</v>
@@ -35285,7 +35285,7 @@
         <v>13.6000003814697</v>
       </c>
       <c r="G1204" t="n">
-        <v>12.5256185531616</v>
+        <v>12.525616645813</v>
       </c>
       <c r="H1204" t="n">
         <v>10928</v>
@@ -35343,7 +35343,7 @@
         <v>13.5</v>
       </c>
       <c r="G1206" t="n">
-        <v>12.4335174560547</v>
+        <v>12.4335165023804</v>
       </c>
       <c r="H1206" t="n">
         <v>7665</v>
@@ -35372,7 +35372,7 @@
         <v>13.4499998092651</v>
       </c>
       <c r="G1207" t="n">
-        <v>12.3874683380127</v>
+        <v>12.3874664306641</v>
       </c>
       <c r="H1207" t="n">
         <v>6781</v>
@@ -35488,7 +35488,7 @@
         <v>13.5</v>
       </c>
       <c r="G1211" t="n">
-        <v>12.4335174560547</v>
+        <v>12.4335165023804</v>
       </c>
       <c r="H1211" t="n">
         <v>20277</v>
@@ -35749,7 +35749,7 @@
         <v>15.5500001907349</v>
       </c>
       <c r="G1220" t="n">
-        <v>14.321572303772</v>
+        <v>14.3215703964233</v>
       </c>
       <c r="H1220" t="n">
         <v>39798</v>
@@ -35807,7 +35807,7 @@
         <v>16.1499996185303</v>
       </c>
       <c r="G1222" t="n">
-        <v>14.8741703033447</v>
+        <v>14.874171257019</v>
       </c>
       <c r="H1222" t="n">
         <v>56456</v>
@@ -35836,7 +35836,7 @@
         <v>16.1499996185303</v>
       </c>
       <c r="G1223" t="n">
-        <v>14.8741703033447</v>
+        <v>14.874171257019</v>
       </c>
       <c r="H1223" t="n">
         <v>13742</v>
@@ -35865,7 +35865,7 @@
         <v>15.75</v>
       </c>
       <c r="G1224" t="n">
-        <v>14.5057706832886</v>
+        <v>14.5057697296143</v>
       </c>
       <c r="H1224" t="n">
         <v>20576</v>
@@ -35923,7 +35923,7 @@
         <v>16.2000007629395</v>
       </c>
       <c r="G1226" t="n">
-        <v>14.9202222824097</v>
+        <v>14.9202213287354</v>
       </c>
       <c r="H1226" t="n">
         <v>16853</v>
@@ -35952,7 +35952,7 @@
         <v>16.3500003814697</v>
       </c>
       <c r="G1227" t="n">
-        <v>15.0583715438843</v>
+        <v>15.0583734512329</v>
       </c>
       <c r="H1227" t="n">
         <v>31110</v>
@@ -35981,7 +35981,7 @@
         <v>15.8999996185303</v>
       </c>
       <c r="G1228" t="n">
-        <v>14.6439199447632</v>
+        <v>14.6439208984375</v>
       </c>
       <c r="H1228" t="n">
         <v>13706</v>
@@ -36010,7 +36010,7 @@
         <v>16.2000007629395</v>
       </c>
       <c r="G1229" t="n">
-        <v>14.9202222824097</v>
+        <v>14.9202213287354</v>
       </c>
       <c r="H1229" t="n">
         <v>15791</v>
@@ -36068,7 +36068,7 @@
         <v>16.4500007629395</v>
       </c>
       <c r="G1231" t="n">
-        <v>15.1504716873169</v>
+        <v>15.1504726409912</v>
       </c>
       <c r="H1231" t="n">
         <v>17502</v>
@@ -36097,7 +36097,7 @@
         <v>16.6000003814697</v>
       </c>
       <c r="G1232" t="n">
-        <v>15.2886219024658</v>
+        <v>15.2886228561401</v>
       </c>
       <c r="H1232" t="n">
         <v>26978</v>
@@ -36126,7 +36126,7 @@
         <v>17.1499996185303</v>
       </c>
       <c r="G1233" t="n">
-        <v>15.7951726913452</v>
+        <v>15.7951707839966</v>
       </c>
       <c r="H1233" t="n">
         <v>46558</v>
@@ -36155,7 +36155,7 @@
         <v>18</v>
       </c>
       <c r="G1234" t="n">
-        <v>16.5780258178711</v>
+        <v>16.5780239105225</v>
       </c>
       <c r="H1234" t="n">
         <v>55851</v>
@@ -36184,7 +36184,7 @@
         <v>18.1499996185303</v>
       </c>
       <c r="G1235" t="n">
-        <v>16.7161750793457</v>
+        <v>16.7161731719971</v>
       </c>
       <c r="H1235" t="n">
         <v>37688</v>
@@ -36213,7 +36213,7 @@
         <v>18</v>
       </c>
       <c r="G1236" t="n">
-        <v>16.5780258178711</v>
+        <v>16.5780239105225</v>
       </c>
       <c r="H1236" t="n">
         <v>29143</v>
@@ -36242,7 +36242,7 @@
         <v>17.8999996185303</v>
       </c>
       <c r="G1237" t="n">
-        <v>16.4859218597412</v>
+        <v>16.4859237670898</v>
       </c>
       <c r="H1237" t="n">
         <v>37360</v>
@@ -36300,7 +36300,7 @@
         <v>18.2000007629395</v>
       </c>
       <c r="G1239" t="n">
-        <v>16.7622222900391</v>
+        <v>16.7622241973877</v>
       </c>
       <c r="H1239" t="n">
         <v>31567</v>
@@ -36329,7 +36329,7 @@
         <v>18.1000003814697</v>
       </c>
       <c r="G1240" t="n">
-        <v>16.6701259613037</v>
+        <v>16.6701240539551</v>
       </c>
       <c r="H1240" t="n">
         <v>35362</v>
@@ -36358,7 +36358,7 @@
         <v>17.8500003814697</v>
       </c>
       <c r="G1241" t="n">
-        <v>16.4398746490479</v>
+        <v>16.4398727416992</v>
       </c>
       <c r="H1241" t="n">
         <v>30423</v>
@@ -36387,7 +36387,7 @@
         <v>17.8999996185303</v>
       </c>
       <c r="G1242" t="n">
-        <v>16.4859218597412</v>
+        <v>16.4859237670898</v>
       </c>
       <c r="H1242" t="n">
         <v>32070</v>
@@ -36416,7 +36416,7 @@
         <v>18</v>
       </c>
       <c r="G1243" t="n">
-        <v>16.5780258178711</v>
+        <v>16.5780239105225</v>
       </c>
       <c r="H1243" t="n">
         <v>23468</v>
@@ -36445,7 +36445,7 @@
         <v>17.75</v>
       </c>
       <c r="G1244" t="n">
-        <v>16.3477745056152</v>
+        <v>16.3477725982666</v>
       </c>
       <c r="H1244" t="n">
         <v>8695</v>
@@ -36474,7 +36474,7 @@
         <v>17.8500003814697</v>
       </c>
       <c r="G1245" t="n">
-        <v>16.4398746490479</v>
+        <v>16.4398727416992</v>
       </c>
       <c r="H1245" t="n">
         <v>32163</v>
@@ -36532,7 +36532,7 @@
         <v>17.7000007629395</v>
       </c>
       <c r="G1247" t="n">
-        <v>16.3017234802246</v>
+        <v>16.3017253875732</v>
       </c>
       <c r="H1247" t="n">
         <v>26545</v>
@@ -36561,7 +36561,7 @@
         <v>17.8500003814697</v>
       </c>
       <c r="G1248" t="n">
-        <v>16.4398746490479</v>
+        <v>16.4398727416992</v>
       </c>
       <c r="H1248" t="n">
         <v>21176</v>
@@ -36619,7 +36619,7 @@
         <v>17.2999992370605</v>
       </c>
       <c r="G1250" t="n">
-        <v>15.9333209991455</v>
+        <v>15.9333219528198</v>
       </c>
       <c r="H1250" t="n">
         <v>36251</v>
@@ -36706,7 +36706,7 @@
         <v>18.1499996185303</v>
       </c>
       <c r="G1253" t="n">
-        <v>16.7161750793457</v>
+        <v>16.7161731719971</v>
       </c>
       <c r="H1253" t="n">
         <v>51561</v>
@@ -36735,7 +36735,7 @@
         <v>18.1499996185303</v>
       </c>
       <c r="G1254" t="n">
-        <v>16.7161750793457</v>
+        <v>16.7161731719971</v>
       </c>
       <c r="H1254" t="n">
         <v>19292</v>
@@ -36764,7 +36764,7 @@
         <v>17.5</v>
       </c>
       <c r="G1255" t="n">
-        <v>16.1175212860107</v>
+        <v>16.1175231933594</v>
       </c>
       <c r="H1255" t="n">
         <v>42708</v>
@@ -36793,7 +36793,7 @@
         <v>17.1499996185303</v>
       </c>
       <c r="G1256" t="n">
-        <v>15.7951726913452</v>
+        <v>15.7951707839966</v>
       </c>
       <c r="H1256" t="n">
         <v>46906</v>
@@ -36851,7 +36851,7 @@
         <v>16.8999996185303</v>
       </c>
       <c r="G1258" t="n">
-        <v>15.564920425415</v>
+        <v>15.5649213790894</v>
       </c>
       <c r="H1258" t="n">
         <v>66123</v>
@@ -36880,7 +36880,7 @@
         <v>17.2000007629395</v>
       </c>
       <c r="G1259" t="n">
-        <v>15.8412218093872</v>
+        <v>15.8412237167358</v>
       </c>
       <c r="H1259" t="n">
         <v>34176</v>
@@ -36909,7 +36909,7 @@
         <v>17.1000003814697</v>
       </c>
       <c r="G1260" t="n">
-        <v>15.7491226196289</v>
+        <v>15.7491235733032</v>
       </c>
       <c r="H1260" t="n">
         <v>17883</v>
@@ -36938,7 +36938,7 @@
         <v>17.25</v>
       </c>
       <c r="G1261" t="n">
-        <v>15.8872718811035</v>
+        <v>15.8872728347778</v>
       </c>
       <c r="H1261" t="n">
         <v>15494</v>
@@ -36967,7 +36967,7 @@
         <v>16.8999996185303</v>
       </c>
       <c r="G1262" t="n">
-        <v>15.564920425415</v>
+        <v>15.5649213790894</v>
       </c>
       <c r="H1262" t="n">
         <v>11633</v>
@@ -37025,7 +37025,7 @@
         <v>17.2000007629395</v>
       </c>
       <c r="G1264" t="n">
-        <v>15.8412218093872</v>
+        <v>15.8412237167358</v>
       </c>
       <c r="H1264" t="n">
         <v>8184</v>
@@ -37054,7 +37054,7 @@
         <v>16.7999992370605</v>
       </c>
       <c r="G1265" t="n">
-        <v>15.4728212356567</v>
+        <v>15.4728221893311</v>
       </c>
       <c r="H1265" t="n">
         <v>8522</v>
@@ -37141,7 +37141,7 @@
         <v>17.75</v>
       </c>
       <c r="G1268" t="n">
-        <v>16.3477745056152</v>
+        <v>16.3477725982666</v>
       </c>
       <c r="H1268" t="n">
         <v>31701</v>
@@ -37170,7 +37170,7 @@
         <v>18.1000003814697</v>
       </c>
       <c r="G1269" t="n">
-        <v>16.6701259613037</v>
+        <v>16.6701240539551</v>
       </c>
       <c r="H1269" t="n">
         <v>26641</v>
@@ -37228,7 +37228,7 @@
         <v>18.1000003814697</v>
       </c>
       <c r="G1271" t="n">
-        <v>16.6701259613037</v>
+        <v>16.6701240539551</v>
       </c>
       <c r="H1271" t="n">
         <v>24651</v>
@@ -37257,7 +37257,7 @@
         <v>18.1499996185303</v>
       </c>
       <c r="G1272" t="n">
-        <v>16.7161750793457</v>
+        <v>16.7161731719971</v>
       </c>
       <c r="H1272" t="n">
         <v>17506</v>
@@ -37315,7 +37315,7 @@
         <v>18.25</v>
       </c>
       <c r="G1274" t="n">
-        <v>16.8082714080811</v>
+        <v>16.8082733154297</v>
       </c>
       <c r="H1274" t="n">
         <v>38466</v>
@@ -37431,7 +37431,7 @@
         <v>17.9500007629395</v>
       </c>
       <c r="G1278" t="n">
-        <v>16.5319747924805</v>
+        <v>16.5319728851318</v>
       </c>
       <c r="H1278" t="n">
         <v>21896</v>
@@ -37460,7 +37460,7 @@
         <v>17.8500003814697</v>
       </c>
       <c r="G1279" t="n">
-        <v>16.4398746490479</v>
+        <v>16.4398727416992</v>
       </c>
       <c r="H1279" t="n">
         <v>10328</v>
@@ -37489,7 +37489,7 @@
         <v>17.9500007629395</v>
       </c>
       <c r="G1280" t="n">
-        <v>16.5319747924805</v>
+        <v>16.5319728851318</v>
       </c>
       <c r="H1280" t="n">
         <v>4603</v>
@@ -37518,7 +37518,7 @@
         <v>17.9500007629395</v>
       </c>
       <c r="G1281" t="n">
-        <v>16.5319747924805</v>
+        <v>16.5319728851318</v>
       </c>
       <c r="H1281" t="n">
         <v>17215</v>
@@ -37547,7 +37547,7 @@
         <v>17.7000007629395</v>
       </c>
       <c r="G1282" t="n">
-        <v>16.3017234802246</v>
+        <v>16.3017253875732</v>
       </c>
       <c r="H1282" t="n">
         <v>9795</v>
@@ -37576,7 +37576,7 @@
         <v>17.8999996185303</v>
       </c>
       <c r="G1283" t="n">
-        <v>16.4859218597412</v>
+        <v>16.4859237670898</v>
       </c>
       <c r="H1283" t="n">
         <v>10193</v>
@@ -37634,7 +37634,7 @@
         <v>17.8999996185303</v>
       </c>
       <c r="G1285" t="n">
-        <v>16.4859218597412</v>
+        <v>16.4859237670898</v>
       </c>
       <c r="H1285" t="n">
         <v>11787</v>
@@ -37663,7 +37663,7 @@
         <v>17.7000007629395</v>
       </c>
       <c r="G1286" t="n">
-        <v>16.3017234802246</v>
+        <v>16.3017253875732</v>
       </c>
       <c r="H1286" t="n">
         <v>8700</v>
@@ -37750,7 +37750,7 @@
         <v>17.7000007629395</v>
       </c>
       <c r="G1289" t="n">
-        <v>16.3017234802246</v>
+        <v>16.3017253875732</v>
       </c>
       <c r="H1289" t="n">
         <v>5832</v>
@@ -37808,7 +37808,7 @@
         <v>16.2999992370605</v>
       </c>
       <c r="G1291" t="n">
-        <v>15.0123205184937</v>
+        <v>15.012321472168</v>
       </c>
       <c r="H1291" t="n">
         <v>35185</v>
@@ -37837,7 +37837,7 @@
         <v>16.1000003814697</v>
       </c>
       <c r="G1292" t="n">
-        <v>14.8281221389771</v>
+        <v>14.8281211853027</v>
       </c>
       <c r="H1292" t="n">
         <v>32547</v>
@@ -37866,7 +37866,7 @@
         <v>16</v>
       </c>
       <c r="G1293" t="n">
-        <v>14.7360200881958</v>
+        <v>14.7360210418701</v>
       </c>
       <c r="H1293" t="n">
         <v>19002</v>
@@ -37895,7 +37895,7 @@
         <v>16</v>
       </c>
       <c r="G1294" t="n">
-        <v>14.7360200881958</v>
+        <v>14.7360210418701</v>
       </c>
       <c r="H1294" t="n">
         <v>17942</v>
@@ -37924,7 +37924,7 @@
         <v>15.8000001907349</v>
       </c>
       <c r="G1295" t="n">
-        <v>14.5518198013306</v>
+        <v>14.5518217086792</v>
       </c>
       <c r="H1295" t="n">
         <v>22331</v>
@@ -37953,7 +37953,7 @@
         <v>15.75</v>
       </c>
       <c r="G1296" t="n">
-        <v>14.5057706832886</v>
+        <v>14.5057697296143</v>
       </c>
       <c r="H1296" t="n">
         <v>44985</v>
@@ -37982,7 +37982,7 @@
         <v>15.75</v>
       </c>
       <c r="G1297" t="n">
-        <v>14.5057706832886</v>
+        <v>14.5057697296143</v>
       </c>
       <c r="H1297" t="n">
         <v>31133</v>
@@ -38011,7 +38011,7 @@
         <v>15.4499998092651</v>
       </c>
       <c r="G1298" t="n">
-        <v>14.2294702529907</v>
+        <v>14.2294692993164</v>
       </c>
       <c r="H1298" t="n">
         <v>31832</v>
@@ -38040,7 +38040,7 @@
         <v>15.3500003814697</v>
       </c>
       <c r="G1299" t="n">
-        <v>14.1373691558838</v>
+        <v>14.1373701095581</v>
       </c>
       <c r="H1299" t="n">
         <v>11239</v>
@@ -38069,7 +38069,7 @@
         <v>15.0500001907349</v>
       </c>
       <c r="G1300" t="n">
-        <v>13.8610687255859</v>
+        <v>13.8610696792603</v>
       </c>
       <c r="H1300" t="n">
         <v>16158</v>
@@ -38127,7 +38127,7 @@
         <v>15.5</v>
       </c>
       <c r="G1302" t="n">
-        <v>14.275520324707</v>
+        <v>14.2755193710327</v>
       </c>
       <c r="H1302" t="n">
         <v>9288</v>
@@ -38156,7 +38156,7 @@
         <v>15.3500003814697</v>
       </c>
       <c r="G1303" t="n">
-        <v>14.1373691558838</v>
+        <v>14.1373701095581</v>
       </c>
       <c r="H1303" t="n">
         <v>6390</v>
@@ -38243,7 +38243,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G1306" t="n">
-        <v>13.9992189407349</v>
+        <v>13.9992198944092</v>
       </c>
       <c r="H1306" t="n">
         <v>33686</v>
@@ -38417,7 +38417,7 @@
         <v>15.0500001907349</v>
       </c>
       <c r="G1312" t="n">
-        <v>13.8610687255859</v>
+        <v>13.8610696792603</v>
       </c>
       <c r="H1312" t="n">
         <v>19109</v>
@@ -38446,7 +38446,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G1313" t="n">
-        <v>13.9992189407349</v>
+        <v>13.9992198944092</v>
       </c>
       <c r="H1313" t="n">
         <v>22212</v>
@@ -38562,7 +38562,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G1317" t="n">
-        <v>13.9071207046509</v>
+        <v>13.9071197509766</v>
       </c>
       <c r="H1317" t="n">
         <v>15322</v>
@@ -38591,7 +38591,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G1318" t="n">
-        <v>13.9071207046509</v>
+        <v>13.9071197509766</v>
       </c>
       <c r="H1318" t="n">
         <v>8220</v>
@@ -38620,7 +38620,7 @@
         <v>15.5</v>
       </c>
       <c r="G1319" t="n">
-        <v>14.275520324707</v>
+        <v>14.2755193710327</v>
       </c>
       <c r="H1319" t="n">
         <v>13138</v>
@@ -38649,7 +38649,7 @@
         <v>15.5</v>
       </c>
       <c r="G1320" t="n">
-        <v>14.275520324707</v>
+        <v>14.2755193710327</v>
       </c>
       <c r="H1320" t="n">
         <v>8836</v>
@@ -38678,7 +38678,7 @@
         <v>15.5500001907349</v>
       </c>
       <c r="G1321" t="n">
-        <v>14.321572303772</v>
+        <v>14.3215703964233</v>
       </c>
       <c r="H1321" t="n">
         <v>12139</v>
@@ -38707,7 +38707,7 @@
         <v>15.3999996185303</v>
       </c>
       <c r="G1322" t="n">
-        <v>14.1834201812744</v>
+        <v>14.1834192276001</v>
       </c>
       <c r="H1322" t="n">
         <v>2323</v>
@@ -38736,7 +38736,7 @@
         <v>15.6000003814697</v>
       </c>
       <c r="G1323" t="n">
-        <v>14.367621421814</v>
+        <v>14.3676204681396</v>
       </c>
       <c r="H1323" t="n">
         <v>7547</v>
@@ -38765,7 +38765,7 @@
         <v>15.5</v>
       </c>
       <c r="G1324" t="n">
-        <v>14.275520324707</v>
+        <v>14.2755193710327</v>
       </c>
       <c r="H1324" t="n">
         <v>17577</v>
@@ -38794,7 +38794,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G1325" t="n">
-        <v>13.9992189407349</v>
+        <v>13.9992198944092</v>
       </c>
       <c r="H1325" t="n">
         <v>19479</v>
@@ -38823,7 +38823,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G1326" t="n">
-        <v>13.5387182235718</v>
+        <v>13.5387191772461</v>
       </c>
       <c r="H1326" t="n">
         <v>9817</v>
@@ -38881,7 +38881,7 @@
         <v>14.25</v>
       </c>
       <c r="G1328" t="n">
-        <v>13.1242685317993</v>
+        <v>13.124267578125</v>
       </c>
       <c r="H1328" t="n">
         <v>29727</v>
@@ -38910,7 +38910,7 @@
         <v>14.1999998092651</v>
       </c>
       <c r="G1329" t="n">
-        <v>13.0782175064087</v>
+        <v>13.078218460083</v>
       </c>
       <c r="H1329" t="n">
         <v>22122</v>
@@ -38968,7 +38968,7 @@
         <v>13.8999996185303</v>
       </c>
       <c r="G1331" t="n">
-        <v>12.8019180297852</v>
+        <v>12.8019170761108</v>
       </c>
       <c r="H1331" t="n">
         <v>4498</v>
@@ -38997,7 +38997,7 @@
         <v>14.1999998092651</v>
       </c>
       <c r="G1332" t="n">
-        <v>13.0782175064087</v>
+        <v>13.078218460083</v>
       </c>
       <c r="H1332" t="n">
         <v>14523</v>
@@ -39026,7 +39026,7 @@
         <v>14.1999998092651</v>
       </c>
       <c r="G1333" t="n">
-        <v>13.0782175064087</v>
+        <v>13.078218460083</v>
       </c>
       <c r="H1333" t="n">
         <v>11624</v>
@@ -39084,7 +39084,7 @@
         <v>14</v>
       </c>
       <c r="G1335" t="n">
-        <v>12.8940191268921</v>
+        <v>12.8940181732178</v>
       </c>
       <c r="H1335" t="n">
         <v>29719</v>
@@ -39113,7 +39113,7 @@
         <v>14</v>
       </c>
       <c r="G1336" t="n">
-        <v>12.8940191268921</v>
+        <v>12.8940181732178</v>
       </c>
       <c r="H1336" t="n">
         <v>9780</v>
@@ -39171,7 +39171,7 @@
         <v>13.5500001907349</v>
       </c>
       <c r="G1338" t="n">
-        <v>12.479567527771</v>
+        <v>12.4795665740967</v>
       </c>
       <c r="H1338" t="n">
         <v>30533</v>
@@ -39229,7 +39229,7 @@
         <v>13.6000003814697</v>
       </c>
       <c r="G1340" t="n">
-        <v>12.5256185531616</v>
+        <v>12.525616645813</v>
       </c>
       <c r="H1340" t="n">
         <v>6667</v>
@@ -39287,7 +39287,7 @@
         <v>13.5</v>
       </c>
       <c r="G1342" t="n">
-        <v>12.4335174560547</v>
+        <v>12.4335165023804</v>
       </c>
       <c r="H1342" t="n">
         <v>3861</v>
@@ -39374,7 +39374,7 @@
         <v>13.5500001907349</v>
       </c>
       <c r="G1345" t="n">
-        <v>12.479567527771</v>
+        <v>12.4795665740967</v>
       </c>
       <c r="H1345" t="n">
         <v>19625</v>
@@ -39432,7 +39432,7 @@
         <v>13.0500001907349</v>
       </c>
       <c r="G1347" t="n">
-        <v>12.0190677642822</v>
+        <v>12.0190668106079</v>
       </c>
       <c r="H1347" t="n">
         <v>10398</v>
@@ -39461,7 +39461,7 @@
         <v>12.8999996185303</v>
       </c>
       <c r="G1348" t="n">
-        <v>11.8809156417847</v>
+        <v>11.880916595459</v>
       </c>
       <c r="H1348" t="n">
         <v>10513</v>
@@ -39490,7 +39490,7 @@
         <v>12.8000001907349</v>
       </c>
       <c r="G1349" t="n">
-        <v>11.7888164520264</v>
+        <v>11.7888174057007</v>
       </c>
       <c r="H1349" t="n">
         <v>24319</v>
@@ -39519,7 +39519,7 @@
         <v>13.1000003814697</v>
       </c>
       <c r="G1350" t="n">
-        <v>12.0651178359985</v>
+        <v>12.0651168823242</v>
       </c>
       <c r="H1350" t="n">
         <v>17127</v>
@@ -39577,7 +39577,7 @@
         <v>13.0500001907349</v>
       </c>
       <c r="G1352" t="n">
-        <v>12.0190677642822</v>
+        <v>12.0190668106079</v>
       </c>
       <c r="H1352" t="n">
         <v>25648</v>
@@ -39606,7 +39606,7 @@
         <v>12.6999998092651</v>
       </c>
       <c r="G1353" t="n">
-        <v>11.6967163085938</v>
+        <v>11.6967172622681</v>
       </c>
       <c r="H1353" t="n">
         <v>18107</v>
@@ -39635,7 +39635,7 @@
         <v>12.8500003814697</v>
       </c>
       <c r="G1354" t="n">
-        <v>11.8348665237427</v>
+        <v>11.8348684310913</v>
       </c>
       <c r="H1354" t="n">
         <v>8453</v>
@@ -39664,7 +39664,7 @@
         <v>13.1000003814697</v>
       </c>
       <c r="G1355" t="n">
-        <v>12.0651178359985</v>
+        <v>12.0651168823242</v>
       </c>
       <c r="H1355" t="n">
         <v>16860</v>
@@ -39751,7 +39751,7 @@
         <v>12.6999998092651</v>
       </c>
       <c r="G1358" t="n">
-        <v>11.6967163085938</v>
+        <v>11.6967172622681</v>
       </c>
       <c r="H1358" t="n">
         <v>15150</v>
@@ -39780,7 +39780,7 @@
         <v>12.25</v>
       </c>
       <c r="G1359" t="n">
-        <v>11.2822647094727</v>
+        <v>11.282265663147</v>
       </c>
       <c r="H1359" t="n">
         <v>42261</v>
@@ -39809,7 +39809,7 @@
         <v>12</v>
       </c>
       <c r="G1360" t="n">
-        <v>11.0520162582397</v>
+        <v>11.0520153045654</v>
       </c>
       <c r="H1360" t="n">
         <v>9891</v>
@@ -39983,7 +39983,7 @@
         <v>11.6999998092651</v>
       </c>
       <c r="G1366" t="n">
-        <v>10.7757148742676</v>
+        <v>10.7757158279419</v>
       </c>
       <c r="H1366" t="n">
         <v>4839</v>
@@ -40041,7 +40041,7 @@
         <v>11.6999998092651</v>
       </c>
       <c r="G1368" t="n">
-        <v>10.7757148742676</v>
+        <v>10.7757158279419</v>
       </c>
       <c r="H1368" t="n">
         <v>10060</v>
@@ -40070,7 +40070,7 @@
         <v>11.6999998092651</v>
       </c>
       <c r="G1369" t="n">
-        <v>10.7757148742676</v>
+        <v>10.7757158279419</v>
       </c>
       <c r="H1369" t="n">
         <v>8696</v>
@@ -40099,7 +40099,7 @@
         <v>11.9499998092651</v>
       </c>
       <c r="G1370" t="n">
-        <v>11.0059671401978</v>
+        <v>11.0059652328491</v>
       </c>
       <c r="H1370" t="n">
         <v>8903</v>
@@ -40128,7 +40128,7 @@
         <v>12</v>
       </c>
       <c r="G1371" t="n">
-        <v>11.0520162582397</v>
+        <v>11.0520153045654</v>
       </c>
       <c r="H1371" t="n">
         <v>4332</v>
@@ -40157,7 +40157,7 @@
         <v>12.3500003814697</v>
       </c>
       <c r="G1372" t="n">
-        <v>11.3743658065796</v>
+        <v>11.3743667602539</v>
       </c>
       <c r="H1372" t="n">
         <v>2891</v>
@@ -40186,7 +40186,7 @@
         <v>12.1000003814697</v>
       </c>
       <c r="G1373" t="n">
-        <v>11.144115447998</v>
+        <v>11.1441164016724</v>
       </c>
       <c r="H1373" t="n">
         <v>3062</v>
@@ -40215,7 +40215,7 @@
         <v>12.0500001907349</v>
       </c>
       <c r="G1374" t="n">
-        <v>11.0980653762817</v>
+        <v>11.0980663299561</v>
       </c>
       <c r="H1374" t="n">
         <v>6759</v>
@@ -40302,7 +40302,7 @@
         <v>12.5500001907349</v>
       </c>
       <c r="G1377" t="n">
-        <v>11.5585660934448</v>
+        <v>11.5585670471191</v>
       </c>
       <c r="H1377" t="n">
         <v>8078</v>
@@ -40331,7 +40331,7 @@
         <v>12.8500003814697</v>
       </c>
       <c r="G1378" t="n">
-        <v>11.8348665237427</v>
+        <v>11.8348684310913</v>
       </c>
       <c r="H1378" t="n">
         <v>2949</v>
@@ -40360,7 +40360,7 @@
         <v>13.0500001907349</v>
       </c>
       <c r="G1379" t="n">
-        <v>12.0190677642822</v>
+        <v>12.0190668106079</v>
       </c>
       <c r="H1379" t="n">
         <v>8883</v>
@@ -40389,7 +40389,7 @@
         <v>12.8999996185303</v>
       </c>
       <c r="G1380" t="n">
-        <v>11.8809156417847</v>
+        <v>11.880916595459</v>
       </c>
       <c r="H1380" t="n">
         <v>3352</v>
@@ -40534,7 +40534,7 @@
         <v>13.5500001907349</v>
       </c>
       <c r="G1385" t="n">
-        <v>12.479567527771</v>
+        <v>12.4795665740967</v>
       </c>
       <c r="H1385" t="n">
         <v>10551</v>
@@ -40563,7 +40563,7 @@
         <v>11.75</v>
       </c>
       <c r="G1386" t="n">
-        <v>10.8217649459839</v>
+        <v>10.8217658996582</v>
       </c>
       <c r="H1386" t="n">
         <v>92513</v>
@@ -40708,7 +40708,7 @@
         <v>9.02000045776367</v>
       </c>
       <c r="G1391" t="n">
-        <v>8.30743217468262</v>
+        <v>8.30743312835693</v>
       </c>
       <c r="H1391" t="n">
         <v>49666</v>
@@ -40737,7 +40737,7 @@
         <v>9.19999980926514</v>
       </c>
       <c r="G1392" t="n">
-        <v>8.47321128845215</v>
+        <v>8.47321224212646</v>
       </c>
       <c r="H1392" t="n">
         <v>43171</v>
@@ -40766,7 +40766,7 @@
         <v>9.01000022888184</v>
       </c>
       <c r="G1393" t="n">
-        <v>8.29822254180908</v>
+        <v>8.29822158813477</v>
       </c>
       <c r="H1393" t="n">
         <v>15513</v>
@@ -40795,7 +40795,7 @@
         <v>8.89000034332275</v>
       </c>
       <c r="G1394" t="n">
-        <v>8.18770217895508</v>
+        <v>8.18770122528076</v>
       </c>
       <c r="H1394" t="n">
         <v>15541</v>
@@ -40853,7 +40853,7 @@
         <v>9</v>
       </c>
       <c r="G1396" t="n">
-        <v>8.28901290893555</v>
+        <v>8.28901195526123</v>
       </c>
       <c r="H1396" t="n">
         <v>6827</v>
@@ -40882,7 +40882,7 @@
         <v>9.03999996185303</v>
       </c>
       <c r="G1397" t="n">
-        <v>8.32585144042969</v>
+        <v>8.325852394104</v>
       </c>
       <c r="H1397" t="n">
         <v>49566</v>
@@ -40969,7 +40969,7 @@
         <v>8.63000011444092</v>
       </c>
       <c r="G1400" t="n">
-        <v>7.94824028015137</v>
+        <v>7.9482421875</v>
       </c>
       <c r="H1400" t="n">
         <v>11269</v>
@@ -40998,7 +40998,7 @@
         <v>8.3100004196167</v>
       </c>
       <c r="G1401" t="n">
-        <v>7.65352058410645</v>
+        <v>7.6535210609436</v>
       </c>
       <c r="H1401" t="n">
         <v>21362</v>
@@ -41027,7 +41027,7 @@
         <v>8</v>
       </c>
       <c r="G1402" t="n">
-        <v>7.3680100440979</v>
+        <v>7.36801052093506</v>
       </c>
       <c r="H1402" t="n">
         <v>23498</v>
@@ -41114,7 +41114,7 @@
         <v>8.35999965667725</v>
       </c>
       <c r="G1405" t="n">
-        <v>7.6995701789856</v>
+        <v>7.69957113265991</v>
       </c>
       <c r="H1405" t="n">
         <v>38004</v>
@@ -41172,7 +41172,7 @@
         <v>8.01000022888184</v>
       </c>
       <c r="G1407" t="n">
-        <v>7.37722015380859</v>
+        <v>7.37722063064575</v>
       </c>
       <c r="H1407" t="n">
         <v>9665</v>
@@ -41201,7 +41201,7 @@
         <v>7.86999988555908</v>
       </c>
       <c r="G1408" t="n">
-        <v>7.24828004837036</v>
+        <v>7.24828052520752</v>
       </c>
       <c r="H1408" t="n">
         <v>10131</v>
@@ -41230,7 +41230,7 @@
         <v>7.59999990463257</v>
       </c>
       <c r="G1409" t="n">
-        <v>6.99960947036743</v>
+        <v>6.99960994720459</v>
       </c>
       <c r="H1409" t="n">
         <v>28306</v>
@@ -41433,7 +41433,7 @@
         <v>8.05000019073486</v>
       </c>
       <c r="G1416" t="n">
-        <v>7.41406106948853</v>
+        <v>7.41406059265137</v>
       </c>
       <c r="H1416" t="n">
         <v>14741</v>
@@ -41462,7 +41462,7 @@
         <v>8.63000011444092</v>
       </c>
       <c r="G1417" t="n">
-        <v>7.94824028015137</v>
+        <v>7.9482421875</v>
       </c>
       <c r="H1417" t="n">
         <v>40461</v>
@@ -41491,7 +41491,7 @@
         <v>8.75</v>
       </c>
       <c r="G1418" t="n">
-        <v>8.05876064300537</v>
+        <v>8.05876159667969</v>
       </c>
       <c r="H1418" t="n">
         <v>24664</v>
@@ -41520,7 +41520,7 @@
         <v>8.77000045776367</v>
       </c>
       <c r="G1419" t="n">
-        <v>8.07718181610107</v>
+        <v>8.07718276977539</v>
       </c>
       <c r="H1419" t="n">
         <v>21481</v>
@@ -41549,7 +41549,7 @@
         <v>9</v>
       </c>
       <c r="G1420" t="n">
-        <v>8.28901290893555</v>
+        <v>8.28901195526123</v>
       </c>
       <c r="H1420" t="n">
         <v>62353</v>
@@ -41665,7 +41665,7 @@
         <v>9.10000038146973</v>
       </c>
       <c r="G1424" t="n">
-        <v>8.53280735015869</v>
+        <v>8.53280639648438</v>
       </c>
       <c r="H1424" t="n">
         <v>15786</v>
@@ -41752,7 +41752,7 @@
         <v>9.10000038146973</v>
       </c>
       <c r="G1427" t="n">
-        <v>8.53280735015869</v>
+        <v>8.53280639648438</v>
       </c>
       <c r="H1427" t="n">
         <v>17846</v>
@@ -41897,7 +41897,7 @@
         <v>8.80000019073486</v>
       </c>
       <c r="G1432" t="n">
-        <v>8.25150585174561</v>
+        <v>8.25150489807129</v>
       </c>
       <c r="H1432" t="n">
         <v>9669</v>
@@ -41926,7 +41926,7 @@
         <v>9.02000045776367</v>
       </c>
       <c r="G1433" t="n">
-        <v>8.45779323577881</v>
+        <v>8.45779418945312</v>
       </c>
       <c r="H1433" t="n">
         <v>12940</v>
@@ -41984,7 +41984,7 @@
         <v>8.69999980926514</v>
       </c>
       <c r="G1435" t="n">
-        <v>8.15773868560791</v>
+        <v>8.15773773193359</v>
       </c>
       <c r="H1435" t="n">
         <v>13463</v>
@@ -42100,7 +42100,7 @@
         <v>8.22000026702881</v>
       </c>
       <c r="G1439" t="n">
-        <v>7.7076563835144</v>
+        <v>7.70765590667725</v>
       </c>
       <c r="H1439" t="n">
         <v>3073</v>
@@ -42361,7 +42361,7 @@
         <v>8.46000003814697</v>
       </c>
       <c r="G1448" t="n">
-        <v>7.93269634246826</v>
+        <v>7.93269729614258</v>
       </c>
       <c r="H1448" t="n">
         <v>7163</v>
@@ -42419,7 +42419,7 @@
         <v>8.36999988555908</v>
       </c>
       <c r="G1450" t="n">
-        <v>7.84830713272095</v>
+        <v>7.84830617904663</v>
       </c>
       <c r="H1450" t="n">
         <v>1746</v>
@@ -42535,7 +42535,7 @@
         <v>8.57999992370605</v>
       </c>
       <c r="G1454" t="n">
-        <v>8.0452184677124</v>
+        <v>8.04521751403809</v>
       </c>
       <c r="H1454" t="n">
         <v>2825</v>
@@ -42651,7 +42651,7 @@
         <v>8.36999988555908</v>
       </c>
       <c r="G1458" t="n">
-        <v>7.84830713272095</v>
+        <v>7.84830617904663</v>
       </c>
       <c r="H1458" t="n">
         <v>5445</v>
@@ -42738,7 +42738,7 @@
         <v>8.23999977111816</v>
       </c>
       <c r="G1461" t="n">
-        <v>7.72640943527222</v>
+        <v>7.7264084815979</v>
       </c>
       <c r="H1461" t="n">
         <v>7810</v>
@@ -42912,7 +42912,7 @@
         <v>8.14000034332275</v>
       </c>
       <c r="G1467" t="n">
-        <v>7.63264274597168</v>
+        <v>7.63264226913452</v>
       </c>
       <c r="H1467" t="n">
         <v>7352</v>
@@ -42941,7 +42941,7 @@
         <v>8.10000038146973</v>
       </c>
       <c r="G1468" t="n">
-        <v>7.5951361656189</v>
+        <v>7.59513568878174</v>
       </c>
       <c r="H1468" t="n">
         <v>10532</v>
@@ -43028,7 +43028,7 @@
         <v>8.02999973297119</v>
       </c>
       <c r="G1471" t="n">
-        <v>7.52949857711792</v>
+        <v>7.52949810028076</v>
       </c>
       <c r="H1471" t="n">
         <v>8187</v>
@@ -43086,7 +43086,7 @@
         <v>8.72999954223633</v>
       </c>
       <c r="G1473" t="n">
-        <v>8.18586730957031</v>
+        <v>8.18586826324463</v>
       </c>
       <c r="H1473" t="n">
         <v>27107</v>
@@ -43115,7 +43115,7 @@
         <v>8.51000022888184</v>
       </c>
       <c r="G1474" t="n">
-        <v>7.97958087921143</v>
+        <v>7.97958040237427</v>
       </c>
       <c r="H1474" t="n">
         <v>17996</v>
@@ -43144,7 +43144,7 @@
         <v>8.31999969482422</v>
       </c>
       <c r="G1475" t="n">
-        <v>7.80142259597778</v>
+        <v>7.8014235496521</v>
       </c>
       <c r="H1475" t="n">
         <v>6885</v>
@@ -43173,7 +43173,7 @@
         <v>8.59000015258789</v>
       </c>
       <c r="G1476" t="n">
-        <v>8.05459403991699</v>
+        <v>8.05459499359131</v>
       </c>
       <c r="H1476" t="n">
         <v>5022</v>
@@ -43231,7 +43231,7 @@
         <v>8.63000011444092</v>
       </c>
       <c r="G1478" t="n">
-        <v>8.09210109710693</v>
+        <v>8.09210205078125</v>
       </c>
       <c r="H1478" t="n">
         <v>2527</v>
@@ -43260,7 +43260,7 @@
         <v>8.72000026702881</v>
       </c>
       <c r="G1479" t="n">
-        <v>8.17649269104004</v>
+        <v>8.17649173736572</v>
       </c>
       <c r="H1479" t="n">
         <v>2805</v>
@@ -43463,7 +43463,7 @@
         <v>8.69999980926514</v>
       </c>
       <c r="G1486" t="n">
-        <v>8.15773868560791</v>
+        <v>8.15773773193359</v>
       </c>
       <c r="H1486" t="n">
         <v>2443</v>
@@ -43637,7 +43637,7 @@
         <v>8.23999977111816</v>
       </c>
       <c r="G1492" t="n">
-        <v>7.72640943527222</v>
+        <v>7.7264084815979</v>
       </c>
       <c r="H1492" t="n">
         <v>7241</v>
@@ -43695,7 +43695,7 @@
         <v>8.19999980926514</v>
       </c>
       <c r="G1494" t="n">
-        <v>7.68890285491943</v>
+        <v>7.68890237808228</v>
       </c>
       <c r="H1494" t="n">
         <v>4819</v>
@@ -43724,7 +43724,7 @@
         <v>8.19999980926514</v>
       </c>
       <c r="G1495" t="n">
-        <v>7.68890285491943</v>
+        <v>7.68890237808228</v>
       </c>
       <c r="H1495" t="n">
         <v>1979</v>
@@ -43753,7 +43753,7 @@
         <v>8.35999965667725</v>
       </c>
       <c r="G1496" t="n">
-        <v>7.83892917633057</v>
+        <v>7.83893013000488</v>
       </c>
       <c r="H1496" t="n">
         <v>3456</v>
@@ -43811,7 +43811,7 @@
         <v>8.36999988555908</v>
       </c>
       <c r="G1498" t="n">
-        <v>7.84830713272095</v>
+        <v>7.84830617904663</v>
       </c>
       <c r="H1498" t="n">
         <v>7184</v>
@@ -44072,7 +44072,7 @@
         <v>8.10000038146973</v>
       </c>
       <c r="G1507" t="n">
-        <v>7.5951361656189</v>
+        <v>7.59513568878174</v>
       </c>
       <c r="H1507" t="n">
         <v>1395</v>
@@ -44101,7 +44101,7 @@
         <v>8.19999980926514</v>
       </c>
       <c r="G1508" t="n">
-        <v>7.68890285491943</v>
+        <v>7.68890237808228</v>
       </c>
       <c r="H1508" t="n">
         <v>831</v>
@@ -44130,7 +44130,7 @@
         <v>8.10999965667725</v>
       </c>
       <c r="G1509" t="n">
-        <v>7.60451221466064</v>
+        <v>7.60451173782349</v>
       </c>
       <c r="H1509" t="n">
         <v>3386</v>
@@ -44217,7 +44217,7 @@
         <v>7.96000003814697</v>
       </c>
       <c r="G1512" t="n">
-        <v>7.46386194229126</v>
+        <v>7.4638614654541</v>
       </c>
       <c r="H1512" t="n">
         <v>1387</v>
@@ -44275,7 +44275,7 @@
         <v>7.90000009536743</v>
       </c>
       <c r="G1514" t="n">
-        <v>7.40760135650635</v>
+        <v>7.40760183334351</v>
       </c>
       <c r="H1514" t="n">
         <v>2950</v>
@@ -44333,7 +44333,7 @@
         <v>7.98999977111816</v>
       </c>
       <c r="G1516" t="n">
-        <v>7.49199104309082</v>
+        <v>7.49199151992798</v>
       </c>
       <c r="H1516" t="n">
         <v>1046</v>
@@ -44507,7 +44507,7 @@
         <v>7.53000020980835</v>
       </c>
       <c r="G1522" t="n">
-        <v>7.0606632232666</v>
+        <v>7.06066274642944</v>
       </c>
       <c r="H1522" t="n">
         <v>4031</v>
@@ -44565,7 +44565,7 @@
         <v>7.46999979019165</v>
       </c>
       <c r="G1524" t="n">
-        <v>7.00440216064453</v>
+        <v>7.00440263748169</v>
       </c>
       <c r="H1524" t="n">
         <v>1166</v>
@@ -44594,7 +44594,7 @@
         <v>7.57999992370605</v>
       </c>
       <c r="G1525" t="n">
-        <v>7.10754632949829</v>
+        <v>7.10754585266113</v>
       </c>
       <c r="H1525" t="n">
         <v>15647</v>
@@ -44826,7 +44826,7 @@
         <v>7.80999994277954</v>
       </c>
       <c r="G1533" t="n">
-        <v>7.32321119308472</v>
+        <v>7.32321071624756</v>
       </c>
       <c r="H1533" t="n">
         <v>459</v>
@@ -44855,7 +44855,7 @@
         <v>7.6399998664856</v>
       </c>
       <c r="G1534" t="n">
-        <v>7.16380643844604</v>
+        <v>7.1638069152832</v>
       </c>
       <c r="H1534" t="n">
         <v>7564</v>
@@ -44884,7 +44884,7 @@
         <v>7.75</v>
       </c>
       <c r="G1535" t="n">
-        <v>7.2669506072998</v>
+        <v>7.26695013046265</v>
       </c>
       <c r="H1535" t="n">
         <v>4595</v>
@@ -44942,7 +44942,7 @@
         <v>7.69000005722046</v>
       </c>
       <c r="G1537" t="n">
-        <v>7.21069002151489</v>
+        <v>7.21069049835205</v>
       </c>
       <c r="H1537" t="n">
         <v>210</v>
@@ -45000,7 +45000,7 @@
         <v>7.69000005722046</v>
       </c>
       <c r="G1539" t="n">
-        <v>7.21069002151489</v>
+        <v>7.21069049835205</v>
       </c>
       <c r="H1539" t="n">
         <v>60</v>
@@ -45087,7 +45087,7 @@
         <v>7.96000003814697</v>
       </c>
       <c r="G1542" t="n">
-        <v>7.46386194229126</v>
+        <v>7.4638614654541</v>
       </c>
       <c r="H1542" t="n">
         <v>2633</v>
@@ -45145,7 +45145,7 @@
         <v>8.32999992370605</v>
       </c>
       <c r="G1544" t="n">
-        <v>7.81079912185669</v>
+        <v>7.81080007553101</v>
       </c>
       <c r="H1544" t="n">
         <v>6825</v>
@@ -45174,7 +45174,7 @@
         <v>8.10000038146973</v>
       </c>
       <c r="G1545" t="n">
-        <v>7.5951361656189</v>
+        <v>7.59513568878174</v>
       </c>
       <c r="H1545" t="n">
         <v>3886</v>
@@ -45232,7 +45232,7 @@
         <v>7.82000017166138</v>
       </c>
       <c r="G1547" t="n">
-        <v>7.33258771896362</v>
+        <v>7.33258724212646</v>
       </c>
       <c r="H1547" t="n">
         <v>4523</v>
@@ -45261,7 +45261,7 @@
         <v>8.07999992370605</v>
       </c>
       <c r="G1548" t="n">
-        <v>7.57638216018677</v>
+        <v>7.57638168334961</v>
       </c>
       <c r="H1548" t="n">
         <v>7143</v>
@@ -45290,7 +45290,7 @@
         <v>8.07999992370605</v>
       </c>
       <c r="G1549" t="n">
-        <v>7.57638216018677</v>
+        <v>7.57638168334961</v>
       </c>
       <c r="H1549" t="n">
         <v>4415</v>
@@ -45435,7 +45435,7 @@
         <v>8.19999980926514</v>
       </c>
       <c r="G1554" t="n">
-        <v>7.68890285491943</v>
+        <v>7.68890237808228</v>
       </c>
       <c r="H1554" t="n">
         <v>798</v>
@@ -45725,7 +45725,7 @@
         <v>8.31999969482422</v>
       </c>
       <c r="G1564" t="n">
-        <v>7.80142259597778</v>
+        <v>7.8014235496521</v>
       </c>
       <c r="H1564" t="n">
         <v>42119</v>
@@ -45812,7 +45812,7 @@
         <v>8.35999965667725</v>
       </c>
       <c r="G1567" t="n">
-        <v>7.83892917633057</v>
+        <v>7.83893013000488</v>
       </c>
       <c r="H1567" t="n">
         <v>10959</v>
@@ -45928,7 +45928,7 @@
         <v>8.13000011444092</v>
       </c>
       <c r="G1571" t="n">
-        <v>7.62326526641846</v>
+        <v>7.62326574325562</v>
       </c>
       <c r="H1571" t="n">
         <v>364</v>
@@ -45957,7 +45957,7 @@
         <v>8.1899995803833</v>
       </c>
       <c r="G1572" t="n">
-        <v>7.67952489852905</v>
+        <v>7.67952537536621</v>
       </c>
       <c r="H1572" t="n">
         <v>1114</v>
@@ -45986,7 +45986,7 @@
         <v>8.17000007629395</v>
       </c>
       <c r="G1573" t="n">
-        <v>7.66077327728271</v>
+        <v>7.66077280044556</v>
       </c>
       <c r="H1573" t="n">
         <v>16</v>
@@ -46189,7 +46189,7 @@
         <v>8.32999992370605</v>
       </c>
       <c r="G1580" t="n">
-        <v>7.81079912185669</v>
+        <v>7.81080007553101</v>
       </c>
       <c r="H1580" t="n">
         <v>12</v>
@@ -46218,7 +46218,7 @@
         <v>8.31999969482422</v>
       </c>
       <c r="G1581" t="n">
-        <v>7.80142259597778</v>
+        <v>7.8014235496521</v>
       </c>
       <c r="H1581" t="n">
         <v>4632</v>
@@ -46247,7 +46247,7 @@
         <v>8.32999992370605</v>
       </c>
       <c r="G1582" t="n">
-        <v>7.81079912185669</v>
+        <v>7.81080007553101</v>
       </c>
       <c r="H1582" t="n">
         <v>1433</v>
@@ -46276,7 +46276,7 @@
         <v>8.31999969482422</v>
       </c>
       <c r="G1583" t="n">
-        <v>7.80142259597778</v>
+        <v>7.8014235496521</v>
       </c>
       <c r="H1583" t="n">
         <v>218</v>
@@ -46363,7 +46363,7 @@
         <v>8.23999977111816</v>
       </c>
       <c r="G1586" t="n">
-        <v>7.72640943527222</v>
+        <v>7.7264084815979</v>
       </c>
       <c r="H1586" t="n">
         <v>370</v>
@@ -46392,7 +46392,7 @@
         <v>8.23999977111816</v>
       </c>
       <c r="G1587" t="n">
-        <v>7.72640943527222</v>
+        <v>7.7264084815979</v>
       </c>
       <c r="H1587" t="n">
         <v>1309</v>
@@ -46421,7 +46421,7 @@
         <v>8.10000038146973</v>
       </c>
       <c r="G1588" t="n">
-        <v>7.5951361656189</v>
+        <v>7.59513568878174</v>
       </c>
       <c r="H1588" t="n">
         <v>2104</v>
@@ -46450,7 +46450,7 @@
         <v>8.18000030517578</v>
       </c>
       <c r="G1589" t="n">
-        <v>7.67014980316162</v>
+        <v>7.67014932632446</v>
       </c>
       <c r="H1589" t="n">
         <v>2104</v>
@@ -46479,7 +46479,7 @@
         <v>8.10999965667725</v>
       </c>
       <c r="G1590" t="n">
-        <v>7.60451221466064</v>
+        <v>7.60451173782349</v>
       </c>
       <c r="H1590" t="n">
         <v>1937</v>
@@ -46508,7 +46508,7 @@
         <v>8.10000038146973</v>
       </c>
       <c r="G1591" t="n">
-        <v>7.5951361656189</v>
+        <v>7.59513568878174</v>
       </c>
       <c r="H1591" t="n">
         <v>5358</v>
@@ -46537,7 +46537,7 @@
         <v>8.18000030517578</v>
       </c>
       <c r="G1592" t="n">
-        <v>7.67014980316162</v>
+        <v>7.67014932632446</v>
       </c>
       <c r="H1592" t="n">
         <v>5541</v>
@@ -46566,7 +46566,7 @@
         <v>8.18000030517578</v>
       </c>
       <c r="G1593" t="n">
-        <v>7.67014980316162</v>
+        <v>7.67014932632446</v>
       </c>
       <c r="H1593" t="n">
         <v>8319</v>
@@ -46595,7 +46595,7 @@
         <v>8.19999980926514</v>
       </c>
       <c r="G1594" t="n">
-        <v>7.68890285491943</v>
+        <v>7.68890237808228</v>
       </c>
       <c r="H1594" t="n">
         <v>200</v>
@@ -46624,7 +46624,7 @@
         <v>8.22000026702881</v>
       </c>
       <c r="G1595" t="n">
-        <v>7.7076563835144</v>
+        <v>7.70765590667725</v>
       </c>
       <c r="H1595" t="n">
         <v>1653</v>
@@ -46653,7 +46653,7 @@
         <v>8.22999954223633</v>
       </c>
       <c r="G1596" t="n">
-        <v>7.71703195571899</v>
+        <v>7.71703243255615</v>
       </c>
       <c r="H1596" t="n">
         <v>1071</v>
@@ -46682,7 +46682,7 @@
         <v>8.19999980926514</v>
       </c>
       <c r="G1597" t="n">
-        <v>7.68890285491943</v>
+        <v>7.68890237808228</v>
       </c>
       <c r="H1597" t="n">
         <v>3243</v>
@@ -46711,7 +46711,7 @@
         <v>8.19999980926514</v>
       </c>
       <c r="G1598" t="n">
-        <v>7.68890285491943</v>
+        <v>7.68890237808228</v>
       </c>
       <c r="H1598" t="n">
         <v>10131</v>
@@ -46769,7 +46769,7 @@
         <v>8.19999980926514</v>
       </c>
       <c r="G1600" t="n">
-        <v>7.68890285491943</v>
+        <v>7.68890237808228</v>
       </c>
       <c r="H1600" t="n">
         <v>3694</v>
@@ -46798,7 +46798,7 @@
         <v>8.19999980926514</v>
       </c>
       <c r="G1601" t="n">
-        <v>7.68890285491943</v>
+        <v>7.68890237808228</v>
       </c>
       <c r="H1601" t="n">
         <v>7348</v>
@@ -46827,7 +46827,7 @@
         <v>8.19999980926514</v>
       </c>
       <c r="G1602" t="n">
-        <v>7.68890285491943</v>
+        <v>7.68890237808228</v>
       </c>
       <c r="H1602" t="n">
         <v>200</v>
@@ -46885,7 +46885,7 @@
         <v>8.19999980926514</v>
       </c>
       <c r="G1604" t="n">
-        <v>7.68890285491943</v>
+        <v>7.68890237808228</v>
       </c>
       <c r="H1604" t="n">
         <v>10056</v>
@@ -46972,7 +46972,7 @@
         <v>8.14000034332275</v>
       </c>
       <c r="G1607" t="n">
-        <v>7.63264274597168</v>
+        <v>7.63264226913452</v>
       </c>
       <c r="H1607" t="n">
         <v>3200</v>
@@ -47001,7 +47001,7 @@
         <v>8.10000038146973</v>
       </c>
       <c r="G1608" t="n">
-        <v>7.5951361656189</v>
+        <v>7.59513568878174</v>
       </c>
       <c r="H1608" t="n">
         <v>2829</v>
@@ -47030,7 +47030,7 @@
         <v>8.18000030517578</v>
       </c>
       <c r="G1609" t="n">
-        <v>7.67014980316162</v>
+        <v>7.67014932632446</v>
       </c>
       <c r="H1609" t="n">
         <v>6376</v>
@@ -47117,7 +47117,7 @@
         <v>7.96999979019165</v>
       </c>
       <c r="G1612" t="n">
-        <v>7.47323751449585</v>
+        <v>7.47323799133301</v>
       </c>
       <c r="H1612" t="n">
         <v>3428</v>
@@ -47146,7 +47146,7 @@
         <v>7.96999979019165</v>
       </c>
       <c r="G1613" t="n">
-        <v>7.47323751449585</v>
+        <v>7.47323799133301</v>
       </c>
       <c r="H1613" t="n">
         <v>6427</v>
@@ -47233,7 +47233,7 @@
         <v>8.14000034332275</v>
       </c>
       <c r="G1616" t="n">
-        <v>7.63264274597168</v>
+        <v>7.63264226913452</v>
       </c>
       <c r="H1616" t="n">
         <v>5441</v>
@@ -47262,7 +47262,7 @@
         <v>8.27000045776367</v>
       </c>
       <c r="G1617" t="n">
-        <v>7.75454092025757</v>
+        <v>7.75453996658325</v>
       </c>
       <c r="H1617" t="n">
         <v>27464</v>
@@ -47291,7 +47291,7 @@
         <v>8.10999965667725</v>
       </c>
       <c r="G1618" t="n">
-        <v>7.60451221466064</v>
+        <v>7.60451173782349</v>
       </c>
       <c r="H1618" t="n">
         <v>1085</v>
@@ -47320,7 +47320,7 @@
         <v>8.23999977111816</v>
       </c>
       <c r="G1619" t="n">
-        <v>7.72640943527222</v>
+        <v>7.7264084815979</v>
       </c>
       <c r="H1619" t="n">
         <v>22090</v>
@@ -47407,7 +47407,7 @@
         <v>8.31999969482422</v>
       </c>
       <c r="G1622" t="n">
-        <v>7.80142259597778</v>
+        <v>7.8014235496521</v>
       </c>
       <c r="H1622" t="n">
         <v>39241</v>
@@ -47697,7 +47697,7 @@
         <v>8.31999969482422</v>
       </c>
       <c r="G1632" t="n">
-        <v>7.80142259597778</v>
+        <v>7.8014235496521</v>
       </c>
       <c r="H1632" t="n">
         <v>3163</v>
@@ -47726,7 +47726,7 @@
         <v>8.31999969482422</v>
       </c>
       <c r="G1633" t="n">
-        <v>7.80142259597778</v>
+        <v>7.8014235496521</v>
       </c>
       <c r="H1633" t="n">
         <v>6253</v>
@@ -47813,7 +47813,7 @@
         <v>8.17000007629395</v>
       </c>
       <c r="G1636" t="n">
-        <v>7.66077327728271</v>
+        <v>7.66077280044556</v>
       </c>
       <c r="H1636" t="n">
         <v>1895</v>
@@ -48016,7 +48016,7 @@
         <v>8.35999965667725</v>
       </c>
       <c r="G1643" t="n">
-        <v>7.83892917633057</v>
+        <v>7.83893013000488</v>
       </c>
       <c r="H1643" t="n">
         <v>14035</v>
@@ -48045,7 +48045,7 @@
         <v>8.32999992370605</v>
       </c>
       <c r="G1644" t="n">
-        <v>7.81079912185669</v>
+        <v>7.81080007553101</v>
       </c>
       <c r="H1644" t="n">
         <v>10427</v>
@@ -48074,7 +48074,7 @@
         <v>8.31999969482422</v>
       </c>
       <c r="G1645" t="n">
-        <v>7.80142259597778</v>
+        <v>7.8014235496521</v>
       </c>
       <c r="H1645" t="n">
         <v>3390</v>
@@ -48103,7 +48103,7 @@
         <v>8.36999988555908</v>
       </c>
       <c r="G1646" t="n">
-        <v>7.84830713272095</v>
+        <v>7.84830617904663</v>
       </c>
       <c r="H1646" t="n">
         <v>16906</v>
@@ -48161,7 +48161,7 @@
         <v>8.22000026702881</v>
       </c>
       <c r="G1648" t="n">
-        <v>7.7076563835144</v>
+        <v>7.70765590667725</v>
       </c>
       <c r="H1648" t="n">
         <v>5676</v>
@@ -48190,7 +48190,7 @@
         <v>8.31999969482422</v>
       </c>
       <c r="G1649" t="n">
-        <v>7.80142259597778</v>
+        <v>7.8014235496521</v>
       </c>
       <c r="H1649" t="n">
         <v>1791</v>
@@ -48277,7 +48277,7 @@
         <v>8.22000026702881</v>
       </c>
       <c r="G1652" t="n">
-        <v>7.7076563835144</v>
+        <v>7.70765590667725</v>
       </c>
       <c r="H1652" t="n">
         <v>1737</v>
@@ -48306,7 +48306,7 @@
         <v>8.35999965667725</v>
       </c>
       <c r="G1653" t="n">
-        <v>7.83892917633057</v>
+        <v>7.83893013000488</v>
       </c>
       <c r="H1653" t="n">
         <v>19707</v>
@@ -48364,7 +48364,7 @@
         <v>8.10000038146973</v>
       </c>
       <c r="G1655" t="n">
-        <v>7.5951361656189</v>
+        <v>7.59513568878174</v>
       </c>
       <c r="H1655" t="n">
         <v>13506</v>
@@ -48422,7 +48422,7 @@
         <v>8.14000034332275</v>
       </c>
       <c r="G1657" t="n">
-        <v>7.63264274597168</v>
+        <v>7.63264226913452</v>
       </c>
       <c r="H1657" t="n">
         <v>1682</v>
@@ -48451,7 +48451,7 @@
         <v>8.14000034332275</v>
       </c>
       <c r="G1658" t="n">
-        <v>7.63264274597168</v>
+        <v>7.63264226913452</v>
       </c>
       <c r="H1658" t="n">
         <v>0</v>
@@ -48480,7 +48480,7 @@
         <v>8.13000011444092</v>
       </c>
       <c r="G1659" t="n">
-        <v>7.62326526641846</v>
+        <v>7.62326574325562</v>
       </c>
       <c r="H1659" t="n">
         <v>5403</v>
@@ -48509,7 +48509,7 @@
         <v>8.13000011444092</v>
       </c>
       <c r="G1660" t="n">
-        <v>7.62326526641846</v>
+        <v>7.62326574325562</v>
       </c>
       <c r="H1660" t="n">
         <v>277</v>
@@ -48567,7 +48567,7 @@
         <v>7.75</v>
       </c>
       <c r="G1662" t="n">
-        <v>7.2669506072998</v>
+        <v>7.26695013046265</v>
       </c>
       <c r="H1662" t="n">
         <v>5323</v>
@@ -48654,7 +48654,7 @@
         <v>7.82000017166138</v>
       </c>
       <c r="G1665" t="n">
-        <v>7.33258771896362</v>
+        <v>7.33258724212646</v>
       </c>
       <c r="H1665" t="n">
         <v>11862</v>
@@ -48915,7 +48915,7 @@
         <v>7.40000009536743</v>
       </c>
       <c r="G1674" t="n">
-        <v>6.93876552581787</v>
+        <v>6.93876600265503</v>
       </c>
       <c r="H1674" t="n">
         <v>15401</v>
@@ -48944,7 +48944,7 @@
         <v>7.40000009536743</v>
       </c>
       <c r="G1675" t="n">
-        <v>6.93876552581787</v>
+        <v>6.93876600265503</v>
       </c>
       <c r="H1675" t="n">
         <v>118167</v>
@@ -74139,7 +74139,7 @@
         <v>6.5</v>
       </c>
       <c r="E2544" t="n">
-        <v>6.30000019073486</v>
+        <v>6.23999977111816</v>
       </c>
       <c r="F2544" t="n">
         <v>6.23999977111816</v>
@@ -74151,6 +74151,35 @@
         <v>18250</v>
       </c>
       <c r="I2544" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2545">
+      <c r="A2545" t="s">
+        <v>9</v>
+      </c>
+      <c r="B2545" s="1" t="n">
+        <v>46318.2916666667</v>
+      </c>
+      <c r="C2545" t="n">
+        <v>6.32000017166138</v>
+      </c>
+      <c r="D2545" t="n">
+        <v>6.48000001907349</v>
+      </c>
+      <c r="E2545" t="n">
+        <v>6.30000019073486</v>
+      </c>
+      <c r="F2545" t="n">
+        <v>6.34000015258789</v>
+      </c>
+      <c r="G2545" t="n">
+        <v>6.34000015258789</v>
+      </c>
+      <c r="H2545" t="n">
+        <v>22672</v>
+      </c>
+      <c r="I2545" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/FF.MI.xlsx
+++ b/data/FF.MI.xlsx
@@ -601,7 +601,7 @@
         <v>10.0100002288818</v>
       </c>
       <c r="G8" t="n">
-        <v>8.93085098266602</v>
+        <v>8.93085193634033</v>
       </c>
       <c r="H8" t="n">
         <v>200</v>
@@ -630,7 +630,7 @@
         <v>10.0100002288818</v>
       </c>
       <c r="G9" t="n">
-        <v>8.93085098266602</v>
+        <v>8.93085193634033</v>
       </c>
       <c r="H9" t="n">
         <v>0</v>
@@ -804,7 +804,7 @@
         <v>10.1899995803833</v>
       </c>
       <c r="G15" t="n">
-        <v>9.09144496917725</v>
+        <v>9.09144592285156</v>
       </c>
       <c r="H15" t="n">
         <v>200</v>
@@ -833,7 +833,7 @@
         <v>10.1899995803833</v>
       </c>
       <c r="G16" t="n">
-        <v>9.09144496917725</v>
+        <v>9.09144592285156</v>
       </c>
       <c r="H16" t="n">
         <v>0</v>
@@ -862,7 +862,7 @@
         <v>10.0200004577637</v>
       </c>
       <c r="G17" t="n">
-        <v>8.93977355957031</v>
+        <v>8.93977451324463</v>
       </c>
       <c r="H17" t="n">
         <v>800</v>
@@ -891,7 +891,7 @@
         <v>10.0500001907349</v>
       </c>
       <c r="G18" t="n">
-        <v>8.96653938293457</v>
+        <v>8.96653842926025</v>
       </c>
       <c r="H18" t="n">
         <v>1200</v>
@@ -1036,7 +1036,7 @@
         <v>9.86499977111816</v>
       </c>
       <c r="G23" t="n">
-        <v>8.80148220062256</v>
+        <v>8.80148315429688</v>
       </c>
       <c r="H23" t="n">
         <v>1000</v>
@@ -1065,7 +1065,7 @@
         <v>9.86499977111816</v>
       </c>
       <c r="G24" t="n">
-        <v>8.80148220062256</v>
+        <v>8.80148315429688</v>
       </c>
       <c r="H24" t="n">
         <v>0</v>
@@ -1094,7 +1094,7 @@
         <v>9.86499977111816</v>
       </c>
       <c r="G25" t="n">
-        <v>8.80148220062256</v>
+        <v>8.80148315429688</v>
       </c>
       <c r="H25" t="n">
         <v>0</v>
@@ -1152,7 +1152,7 @@
         <v>9.80500030517578</v>
       </c>
       <c r="G27" t="n">
-        <v>8.74795246124268</v>
+        <v>8.74795341491699</v>
       </c>
       <c r="H27" t="n">
         <v>200</v>
@@ -1181,7 +1181,7 @@
         <v>9.80500030517578</v>
       </c>
       <c r="G28" t="n">
-        <v>8.74795246124268</v>
+        <v>8.74795341491699</v>
       </c>
       <c r="H28" t="n">
         <v>0</v>
@@ -1210,7 +1210,7 @@
         <v>9.80500030517578</v>
       </c>
       <c r="G29" t="n">
-        <v>8.74795246124268</v>
+        <v>8.74795341491699</v>
       </c>
       <c r="H29" t="n">
         <v>0</v>
@@ -1239,7 +1239,7 @@
         <v>9.80500030517578</v>
       </c>
       <c r="G30" t="n">
-        <v>8.74795246124268</v>
+        <v>8.74795341491699</v>
       </c>
       <c r="H30" t="n">
         <v>0</v>
@@ -1268,7 +1268,7 @@
         <v>9.80500030517578</v>
       </c>
       <c r="G31" t="n">
-        <v>8.74795246124268</v>
+        <v>8.74795341491699</v>
       </c>
       <c r="H31" t="n">
         <v>0</v>
@@ -1297,7 +1297,7 @@
         <v>9.80500030517578</v>
       </c>
       <c r="G32" t="n">
-        <v>8.74795246124268</v>
+        <v>8.74795341491699</v>
       </c>
       <c r="H32" t="n">
         <v>0</v>
@@ -1326,7 +1326,7 @@
         <v>9.80500030517578</v>
       </c>
       <c r="G33" t="n">
-        <v>8.74795246124268</v>
+        <v>8.74795341491699</v>
       </c>
       <c r="H33" t="n">
         <v>0</v>
@@ -1355,7 +1355,7 @@
         <v>9.80500030517578</v>
       </c>
       <c r="G34" t="n">
-        <v>8.74795246124268</v>
+        <v>8.74795341491699</v>
       </c>
       <c r="H34" t="n">
         <v>0</v>
@@ -1384,7 +1384,7 @@
         <v>9.80500030517578</v>
       </c>
       <c r="G35" t="n">
-        <v>8.74795246124268</v>
+        <v>8.74795341491699</v>
       </c>
       <c r="H35" t="n">
         <v>0</v>
@@ -1413,7 +1413,7 @@
         <v>9.80500030517578</v>
       </c>
       <c r="G36" t="n">
-        <v>8.74795246124268</v>
+        <v>8.74795341491699</v>
       </c>
       <c r="H36" t="n">
         <v>0</v>
@@ -1442,7 +1442,7 @@
         <v>9.80500030517578</v>
       </c>
       <c r="G37" t="n">
-        <v>8.74795246124268</v>
+        <v>8.74795341491699</v>
       </c>
       <c r="H37" t="n">
         <v>0</v>
@@ -1471,7 +1471,7 @@
         <v>9.80500030517578</v>
       </c>
       <c r="G38" t="n">
-        <v>8.74795246124268</v>
+        <v>8.74795341491699</v>
       </c>
       <c r="H38" t="n">
         <v>0</v>
@@ -1500,7 +1500,7 @@
         <v>9.80500030517578</v>
       </c>
       <c r="G39" t="n">
-        <v>8.74795246124268</v>
+        <v>8.74795341491699</v>
       </c>
       <c r="H39" t="n">
         <v>0</v>
@@ -1529,7 +1529,7 @@
         <v>9.80000019073486</v>
       </c>
       <c r="G40" t="n">
-        <v>8.74349212646484</v>
+        <v>8.74349021911621</v>
       </c>
       <c r="H40" t="n">
         <v>200</v>
@@ -1558,7 +1558,7 @@
         <v>9.80000019073486</v>
       </c>
       <c r="G41" t="n">
-        <v>8.74349212646484</v>
+        <v>8.74349021911621</v>
       </c>
       <c r="H41" t="n">
         <v>21400</v>
@@ -1587,7 +1587,7 @@
         <v>9.80000019073486</v>
       </c>
       <c r="G42" t="n">
-        <v>8.74349212646484</v>
+        <v>8.74349021911621</v>
       </c>
       <c r="H42" t="n">
         <v>0</v>
@@ -1616,7 +1616,7 @@
         <v>9.80000019073486</v>
       </c>
       <c r="G43" t="n">
-        <v>8.74349212646484</v>
+        <v>8.74349021911621</v>
       </c>
       <c r="H43" t="n">
         <v>0</v>
@@ -1645,7 +1645,7 @@
         <v>9.80000019073486</v>
       </c>
       <c r="G44" t="n">
-        <v>8.74349212646484</v>
+        <v>8.74349021911621</v>
       </c>
       <c r="H44" t="n">
         <v>0</v>
@@ -1674,7 +1674,7 @@
         <v>9.80000019073486</v>
       </c>
       <c r="G45" t="n">
-        <v>8.74349212646484</v>
+        <v>8.74349021911621</v>
       </c>
       <c r="H45" t="n">
         <v>0</v>
@@ -1703,7 +1703,7 @@
         <v>9.80000019073486</v>
       </c>
       <c r="G46" t="n">
-        <v>8.74349212646484</v>
+        <v>8.74349021911621</v>
       </c>
       <c r="H46" t="n">
         <v>400</v>
@@ -1732,7 +1732,7 @@
         <v>9.80000019073486</v>
       </c>
       <c r="G47" t="n">
-        <v>8.74349212646484</v>
+        <v>8.74349021911621</v>
       </c>
       <c r="H47" t="n">
         <v>0</v>
@@ -1761,7 +1761,7 @@
         <v>9.80000019073486</v>
       </c>
       <c r="G48" t="n">
-        <v>8.74349212646484</v>
+        <v>8.74349021911621</v>
       </c>
       <c r="H48" t="n">
         <v>0</v>
@@ -1848,7 +1848,7 @@
         <v>9.80000019073486</v>
       </c>
       <c r="G51" t="n">
-        <v>8.74349212646484</v>
+        <v>8.74349021911621</v>
       </c>
       <c r="H51" t="n">
         <v>400</v>
@@ -1877,7 +1877,7 @@
         <v>9.80000019073486</v>
       </c>
       <c r="G52" t="n">
-        <v>8.74349212646484</v>
+        <v>8.74349021911621</v>
       </c>
       <c r="H52" t="n">
         <v>0</v>
@@ -2080,7 +2080,7 @@
         <v>9.80000019073486</v>
       </c>
       <c r="G59" t="n">
-        <v>8.74349212646484</v>
+        <v>8.74349021911621</v>
       </c>
       <c r="H59" t="n">
         <v>200</v>
@@ -2109,7 +2109,7 @@
         <v>9.80000019073486</v>
       </c>
       <c r="G60" t="n">
-        <v>8.74349212646484</v>
+        <v>8.74349021911621</v>
       </c>
       <c r="H60" t="n">
         <v>0</v>
@@ -2138,7 +2138,7 @@
         <v>9.80000019073486</v>
       </c>
       <c r="G61" t="n">
-        <v>8.74349212646484</v>
+        <v>8.74349021911621</v>
       </c>
       <c r="H61" t="n">
         <v>0</v>
@@ -2167,7 +2167,7 @@
         <v>9.80500030517578</v>
       </c>
       <c r="G62" t="n">
-        <v>8.74795246124268</v>
+        <v>8.74795341491699</v>
       </c>
       <c r="H62" t="n">
         <v>200</v>
@@ -2196,7 +2196,7 @@
         <v>9.80500030517578</v>
       </c>
       <c r="G63" t="n">
-        <v>8.74795246124268</v>
+        <v>8.74795341491699</v>
       </c>
       <c r="H63" t="n">
         <v>0</v>
@@ -2225,7 +2225,7 @@
         <v>9.80500030517578</v>
       </c>
       <c r="G64" t="n">
-        <v>8.74795246124268</v>
+        <v>8.74795341491699</v>
       </c>
       <c r="H64" t="n">
         <v>0</v>
@@ -2254,7 +2254,7 @@
         <v>9.80500030517578</v>
       </c>
       <c r="G65" t="n">
-        <v>8.74795246124268</v>
+        <v>8.74795341491699</v>
       </c>
       <c r="H65" t="n">
         <v>0</v>
@@ -2283,7 +2283,7 @@
         <v>9.76000022888184</v>
       </c>
       <c r="G66" t="n">
-        <v>8.70780181884766</v>
+        <v>8.70780277252197</v>
       </c>
       <c r="H66" t="n">
         <v>200</v>
@@ -2312,7 +2312,7 @@
         <v>9.76000022888184</v>
       </c>
       <c r="G67" t="n">
-        <v>8.70780181884766</v>
+        <v>8.70780277252197</v>
       </c>
       <c r="H67" t="n">
         <v>0</v>
@@ -2341,7 +2341,7 @@
         <v>9.77999973297119</v>
       </c>
       <c r="G68" t="n">
-        <v>8.72564697265625</v>
+        <v>8.72564601898193</v>
       </c>
       <c r="H68" t="n">
         <v>200</v>
@@ -2370,7 +2370,7 @@
         <v>9.77999973297119</v>
       </c>
       <c r="G69" t="n">
-        <v>8.72564697265625</v>
+        <v>8.72564601898193</v>
       </c>
       <c r="H69" t="n">
         <v>200</v>
@@ -2399,7 +2399,7 @@
         <v>9.77999973297119</v>
       </c>
       <c r="G70" t="n">
-        <v>8.72564697265625</v>
+        <v>8.72564601898193</v>
       </c>
       <c r="H70" t="n">
         <v>0</v>
@@ -2428,7 +2428,7 @@
         <v>9.65999984741211</v>
       </c>
       <c r="G71" t="n">
-        <v>8.6185827255249</v>
+        <v>8.61858463287354</v>
       </c>
       <c r="H71" t="n">
         <v>20200</v>
@@ -2457,7 +2457,7 @@
         <v>9.65999984741211</v>
       </c>
       <c r="G72" t="n">
-        <v>8.6185827255249</v>
+        <v>8.61858463287354</v>
       </c>
       <c r="H72" t="n">
         <v>0</v>
@@ -2486,7 +2486,7 @@
         <v>9.65999984741211</v>
       </c>
       <c r="G73" t="n">
-        <v>8.6185827255249</v>
+        <v>8.61858463287354</v>
       </c>
       <c r="H73" t="n">
         <v>0</v>
@@ -2515,7 +2515,7 @@
         <v>9.77000045776367</v>
       </c>
       <c r="G74" t="n">
-        <v>8.71672630310059</v>
+        <v>8.71672534942627</v>
       </c>
       <c r="H74" t="n">
         <v>400</v>
@@ -2544,7 +2544,7 @@
         <v>9.77000045776367</v>
       </c>
       <c r="G75" t="n">
-        <v>8.71672630310059</v>
+        <v>8.71672534942627</v>
       </c>
       <c r="H75" t="n">
         <v>0</v>
@@ -2573,7 +2573,7 @@
         <v>9.77000045776367</v>
       </c>
       <c r="G76" t="n">
-        <v>8.71672630310059</v>
+        <v>8.71672534942627</v>
       </c>
       <c r="H76" t="n">
         <v>0</v>
@@ -2602,7 +2602,7 @@
         <v>9.77000045776367</v>
       </c>
       <c r="G77" t="n">
-        <v>8.71672630310059</v>
+        <v>8.71672534942627</v>
       </c>
       <c r="H77" t="n">
         <v>0</v>
@@ -2631,7 +2631,7 @@
         <v>9.77000045776367</v>
       </c>
       <c r="G78" t="n">
-        <v>8.71672630310059</v>
+        <v>8.71672534942627</v>
       </c>
       <c r="H78" t="n">
         <v>0</v>
@@ -2660,7 +2660,7 @@
         <v>9.77000045776367</v>
       </c>
       <c r="G79" t="n">
-        <v>8.71672630310059</v>
+        <v>8.71672534942627</v>
       </c>
       <c r="H79" t="n">
         <v>0</v>
@@ -2689,7 +2689,7 @@
         <v>9.77000045776367</v>
       </c>
       <c r="G80" t="n">
-        <v>8.71672630310059</v>
+        <v>8.71672534942627</v>
       </c>
       <c r="H80" t="n">
         <v>0</v>
@@ -2718,7 +2718,7 @@
         <v>9.77000045776367</v>
       </c>
       <c r="G81" t="n">
-        <v>8.71672630310059</v>
+        <v>8.71672534942627</v>
       </c>
       <c r="H81" t="n">
         <v>0</v>
@@ -2747,7 +2747,7 @@
         <v>9.77000045776367</v>
       </c>
       <c r="G82" t="n">
-        <v>8.71672630310059</v>
+        <v>8.71672534942627</v>
       </c>
       <c r="H82" t="n">
         <v>0</v>
@@ -2776,7 +2776,7 @@
         <v>9.77000045776367</v>
       </c>
       <c r="G83" t="n">
-        <v>8.71672630310059</v>
+        <v>8.71672534942627</v>
       </c>
       <c r="H83" t="n">
         <v>0</v>
@@ -2805,7 +2805,7 @@
         <v>9.77000045776367</v>
       </c>
       <c r="G84" t="n">
-        <v>8.71672630310059</v>
+        <v>8.71672534942627</v>
       </c>
       <c r="H84" t="n">
         <v>0</v>
@@ -2834,7 +2834,7 @@
         <v>9.77000045776367</v>
       </c>
       <c r="G85" t="n">
-        <v>8.71672630310059</v>
+        <v>8.71672534942627</v>
       </c>
       <c r="H85" t="n">
         <v>0</v>
@@ -3066,7 +3066,7 @@
         <v>10.1700000762939</v>
       </c>
       <c r="G93" t="n">
-        <v>9.07360363006592</v>
+        <v>9.0736026763916</v>
       </c>
       <c r="H93" t="n">
         <v>400</v>
@@ -3095,7 +3095,7 @@
         <v>10.1700000762939</v>
       </c>
       <c r="G94" t="n">
-        <v>9.07360363006592</v>
+        <v>9.0736026763916</v>
       </c>
       <c r="H94" t="n">
         <v>0</v>
@@ -3124,7 +3124,7 @@
         <v>10.1700000762939</v>
       </c>
       <c r="G95" t="n">
-        <v>9.07360363006592</v>
+        <v>9.0736026763916</v>
       </c>
       <c r="H95" t="n">
         <v>0</v>
@@ -3153,7 +3153,7 @@
         <v>10.1700000762939</v>
       </c>
       <c r="G96" t="n">
-        <v>9.07360363006592</v>
+        <v>9.0736026763916</v>
       </c>
       <c r="H96" t="n">
         <v>200</v>
@@ -3182,7 +3182,7 @@
         <v>10.1700000762939</v>
       </c>
       <c r="G97" t="n">
-        <v>9.07360363006592</v>
+        <v>9.0736026763916</v>
       </c>
       <c r="H97" t="n">
         <v>0</v>
@@ -3211,7 +3211,7 @@
         <v>10.1700000762939</v>
       </c>
       <c r="G98" t="n">
-        <v>9.07360363006592</v>
+        <v>9.0736026763916</v>
       </c>
       <c r="H98" t="n">
         <v>1000</v>
@@ -3240,7 +3240,7 @@
         <v>10.1700000762939</v>
       </c>
       <c r="G99" t="n">
-        <v>9.07360363006592</v>
+        <v>9.0736026763916</v>
       </c>
       <c r="H99" t="n">
         <v>400</v>
@@ -3269,7 +3269,7 @@
         <v>10.1700000762939</v>
       </c>
       <c r="G100" t="n">
-        <v>9.07360363006592</v>
+        <v>9.0736026763916</v>
       </c>
       <c r="H100" t="n">
         <v>0</v>
@@ -3298,7 +3298,7 @@
         <v>10.1700000762939</v>
       </c>
       <c r="G101" t="n">
-        <v>9.07360363006592</v>
+        <v>9.0736026763916</v>
       </c>
       <c r="H101" t="n">
         <v>0</v>
@@ -3327,7 +3327,7 @@
         <v>10.0500001907349</v>
       </c>
       <c r="G102" t="n">
-        <v>8.96653938293457</v>
+        <v>8.96653842926025</v>
       </c>
       <c r="H102" t="n">
         <v>200</v>
@@ -3356,7 +3356,7 @@
         <v>10.0500001907349</v>
       </c>
       <c r="G103" t="n">
-        <v>8.96653938293457</v>
+        <v>8.96653842926025</v>
       </c>
       <c r="H103" t="n">
         <v>0</v>
@@ -3530,7 +3530,7 @@
         <v>10.0500001907349</v>
       </c>
       <c r="G109" t="n">
-        <v>8.96653938293457</v>
+        <v>8.96653842926025</v>
       </c>
       <c r="H109" t="n">
         <v>400</v>
@@ -3646,7 +3646,7 @@
         <v>10.0100002288818</v>
       </c>
       <c r="G113" t="n">
-        <v>8.93085098266602</v>
+        <v>8.93085193634033</v>
       </c>
       <c r="H113" t="n">
         <v>200</v>
@@ -3675,7 +3675,7 @@
         <v>10.0100002288818</v>
       </c>
       <c r="G114" t="n">
-        <v>8.93085098266602</v>
+        <v>8.93085193634033</v>
       </c>
       <c r="H114" t="n">
         <v>0</v>
@@ -3878,7 +3878,7 @@
         <v>9.80000019073486</v>
       </c>
       <c r="G121" t="n">
-        <v>8.74349212646484</v>
+        <v>8.74349021911621</v>
       </c>
       <c r="H121" t="n">
         <v>400</v>
@@ -3907,7 +3907,7 @@
         <v>9.80000019073486</v>
       </c>
       <c r="G122" t="n">
-        <v>8.74349212646484</v>
+        <v>8.74349021911621</v>
       </c>
       <c r="H122" t="n">
         <v>0</v>
@@ -3936,7 +3936,7 @@
         <v>9.82999992370605</v>
       </c>
       <c r="G123" t="n">
-        <v>8.7702579498291</v>
+        <v>8.77025604248047</v>
       </c>
       <c r="H123" t="n">
         <v>2600</v>
@@ -4023,7 +4023,7 @@
         <v>10.0500001907349</v>
       </c>
       <c r="G126" t="n">
-        <v>8.96653938293457</v>
+        <v>8.96653842926025</v>
       </c>
       <c r="H126" t="n">
         <v>1000</v>
@@ -4255,7 +4255,7 @@
         <v>10.0900001525879</v>
       </c>
       <c r="G134" t="n">
-        <v>9.00222682952881</v>
+        <v>9.00222492218018</v>
       </c>
       <c r="H134" t="n">
         <v>80000</v>
@@ -4284,7 +4284,7 @@
         <v>10.1000003814697</v>
       </c>
       <c r="G135" t="n">
-        <v>9.01114940643311</v>
+        <v>9.01114749908447</v>
       </c>
       <c r="H135" t="n">
         <v>124800</v>
@@ -4342,7 +4342,7 @@
         <v>10.5200004577637</v>
       </c>
       <c r="G137" t="n">
-        <v>9.3858699798584</v>
+        <v>9.38587093353271</v>
       </c>
       <c r="H137" t="n">
         <v>44600</v>
@@ -4371,7 +4371,7 @@
         <v>10.6000003814697</v>
       </c>
       <c r="G138" t="n">
-        <v>9.45724582672119</v>
+        <v>9.45724487304688</v>
       </c>
       <c r="H138" t="n">
         <v>28000</v>
@@ -4400,7 +4400,7 @@
         <v>10.6000003814697</v>
       </c>
       <c r="G139" t="n">
-        <v>9.45724582672119</v>
+        <v>9.45724487304688</v>
       </c>
       <c r="H139" t="n">
         <v>28400</v>
@@ -4429,7 +4429,7 @@
         <v>10.6000003814697</v>
       </c>
       <c r="G140" t="n">
-        <v>9.45724582672119</v>
+        <v>9.45724487304688</v>
       </c>
       <c r="H140" t="n">
         <v>10000</v>
@@ -4458,7 +4458,7 @@
         <v>10.8000001907349</v>
       </c>
       <c r="G141" t="n">
-        <v>9.6356840133667</v>
+        <v>9.63568496704102</v>
       </c>
       <c r="H141" t="n">
         <v>9600</v>
@@ -4487,7 +4487,7 @@
         <v>10.6999998092651</v>
       </c>
       <c r="G142" t="n">
-        <v>9.54646492004395</v>
+        <v>9.54646396636963</v>
       </c>
       <c r="H142" t="n">
         <v>9200</v>
@@ -4516,7 +4516,7 @@
         <v>10.6999998092651</v>
       </c>
       <c r="G143" t="n">
-        <v>9.54646492004395</v>
+        <v>9.54646396636963</v>
       </c>
       <c r="H143" t="n">
         <v>3400</v>
@@ -4545,7 +4545,7 @@
         <v>10.539999961853</v>
       </c>
       <c r="G144" t="n">
-        <v>9.40371227264404</v>
+        <v>9.40371322631836</v>
       </c>
       <c r="H144" t="n">
         <v>3400</v>
@@ -4632,7 +4632,7 @@
         <v>10.6000003814697</v>
       </c>
       <c r="G147" t="n">
-        <v>9.45724582672119</v>
+        <v>9.45724487304688</v>
       </c>
       <c r="H147" t="n">
         <v>4400</v>
@@ -4893,7 +4893,7 @@
         <v>10.6000003814697</v>
       </c>
       <c r="G156" t="n">
-        <v>9.45724582672119</v>
+        <v>9.45724487304688</v>
       </c>
       <c r="H156" t="n">
         <v>3600</v>
@@ -4922,7 +4922,7 @@
         <v>10.789999961853</v>
       </c>
       <c r="G157" t="n">
-        <v>9.62676048278809</v>
+        <v>9.6267614364624</v>
       </c>
       <c r="H157" t="n">
         <v>32400</v>
@@ -4951,7 +4951,7 @@
         <v>10.9700002670288</v>
       </c>
       <c r="G158" t="n">
-        <v>9.78735637664795</v>
+        <v>9.78735733032227</v>
       </c>
       <c r="H158" t="n">
         <v>5800</v>
@@ -4980,7 +4980,7 @@
         <v>10.8000001907349</v>
       </c>
       <c r="G159" t="n">
-        <v>9.6356840133667</v>
+        <v>9.63568496704102</v>
       </c>
       <c r="H159" t="n">
         <v>7200</v>
@@ -5009,7 +5009,7 @@
         <v>10.8000001907349</v>
       </c>
       <c r="G160" t="n">
-        <v>9.6356840133667</v>
+        <v>9.63568496704102</v>
       </c>
       <c r="H160" t="n">
         <v>0</v>
@@ -5038,7 +5038,7 @@
         <v>10.9499998092651</v>
       </c>
       <c r="G161" t="n">
-        <v>9.76951217651367</v>
+        <v>9.76951313018799</v>
       </c>
       <c r="H161" t="n">
         <v>5800</v>
@@ -5096,7 +5096,7 @@
         <v>10.7299995422363</v>
       </c>
       <c r="G163" t="n">
-        <v>9.5732307434082</v>
+        <v>9.57322883605957</v>
       </c>
       <c r="H163" t="n">
         <v>11400</v>
@@ -5125,7 +5125,7 @@
         <v>10.7600002288818</v>
       </c>
       <c r="G164" t="n">
-        <v>9.59999656677246</v>
+        <v>9.59999561309814</v>
       </c>
       <c r="H164" t="n">
         <v>4200</v>
@@ -5154,7 +5154,7 @@
         <v>10.7299995422363</v>
       </c>
       <c r="G165" t="n">
-        <v>9.5732307434082</v>
+        <v>9.57322883605957</v>
       </c>
       <c r="H165" t="n">
         <v>600</v>
@@ -5212,7 +5212,7 @@
         <v>10.75</v>
       </c>
       <c r="G167" t="n">
-        <v>9.59107494354248</v>
+        <v>9.59107303619385</v>
       </c>
       <c r="H167" t="n">
         <v>2400</v>
@@ -5241,7 +5241,7 @@
         <v>10.789999961853</v>
       </c>
       <c r="G168" t="n">
-        <v>9.62676048278809</v>
+        <v>9.6267614364624</v>
       </c>
       <c r="H168" t="n">
         <v>8000</v>
@@ -5270,7 +5270,7 @@
         <v>10.6300001144409</v>
       </c>
       <c r="G169" t="n">
-        <v>9.48401165008545</v>
+        <v>9.48401069641113</v>
       </c>
       <c r="H169" t="n">
         <v>8600</v>
@@ -5299,7 +5299,7 @@
         <v>10.75</v>
       </c>
       <c r="G170" t="n">
-        <v>9.59107494354248</v>
+        <v>9.59107303619385</v>
       </c>
       <c r="H170" t="n">
         <v>4800</v>
@@ -5328,7 +5328,7 @@
         <v>10.75</v>
       </c>
       <c r="G171" t="n">
-        <v>9.59107494354248</v>
+        <v>9.59107303619385</v>
       </c>
       <c r="H171" t="n">
         <v>2400</v>
@@ -5357,7 +5357,7 @@
         <v>10.8199996948242</v>
       </c>
       <c r="G172" t="n">
-        <v>9.65352630615234</v>
+        <v>9.65352916717529</v>
       </c>
       <c r="H172" t="n">
         <v>6400</v>
@@ -5444,7 +5444,7 @@
         <v>10.75</v>
       </c>
       <c r="G175" t="n">
-        <v>9.59107494354248</v>
+        <v>9.59107303619385</v>
       </c>
       <c r="H175" t="n">
         <v>9000</v>
@@ -5502,7 +5502,7 @@
         <v>10.6599998474121</v>
       </c>
       <c r="G177" t="n">
-        <v>9.51077651977539</v>
+        <v>9.51077747344971</v>
       </c>
       <c r="H177" t="n">
         <v>11200</v>
@@ -5618,7 +5618,7 @@
         <v>10.6099996566772</v>
       </c>
       <c r="G181" t="n">
-        <v>9.46616649627686</v>
+        <v>9.46616744995117</v>
       </c>
       <c r="H181" t="n">
         <v>2600</v>
@@ -5676,7 +5676,7 @@
         <v>10.6400003433228</v>
       </c>
       <c r="G183" t="n">
-        <v>9.49293422698975</v>
+        <v>9.49293327331543</v>
       </c>
       <c r="H183" t="n">
         <v>200</v>
@@ -5705,7 +5705,7 @@
         <v>10.6000003814697</v>
       </c>
       <c r="G184" t="n">
-        <v>9.45724582672119</v>
+        <v>9.45724487304688</v>
       </c>
       <c r="H184" t="n">
         <v>200</v>
@@ -5821,7 +5821,7 @@
         <v>10.789999961853</v>
       </c>
       <c r="G188" t="n">
-        <v>9.62676048278809</v>
+        <v>9.6267614364624</v>
       </c>
       <c r="H188" t="n">
         <v>5200</v>
@@ -5850,7 +5850,7 @@
         <v>10.789999961853</v>
       </c>
       <c r="G189" t="n">
-        <v>9.62676048278809</v>
+        <v>9.6267614364624</v>
       </c>
       <c r="H189" t="n">
         <v>7200</v>
@@ -5879,7 +5879,7 @@
         <v>10.6000003814697</v>
       </c>
       <c r="G190" t="n">
-        <v>9.45724582672119</v>
+        <v>9.45724487304688</v>
       </c>
       <c r="H190" t="n">
         <v>9000</v>
@@ -5908,7 +5908,7 @@
         <v>10.6000003814697</v>
       </c>
       <c r="G191" t="n">
-        <v>9.45724582672119</v>
+        <v>9.45724487304688</v>
       </c>
       <c r="H191" t="n">
         <v>6600</v>
@@ -5937,7 +5937,7 @@
         <v>10.6000003814697</v>
       </c>
       <c r="G192" t="n">
-        <v>9.45724582672119</v>
+        <v>9.45724487304688</v>
       </c>
       <c r="H192" t="n">
         <v>10400</v>
@@ -6024,7 +6024,7 @@
         <v>10.6099996566772</v>
       </c>
       <c r="G195" t="n">
-        <v>9.46616649627686</v>
+        <v>9.46616744995117</v>
       </c>
       <c r="H195" t="n">
         <v>600</v>
@@ -6053,7 +6053,7 @@
         <v>10.6999998092651</v>
       </c>
       <c r="G196" t="n">
-        <v>9.54646492004395</v>
+        <v>9.54646396636963</v>
       </c>
       <c r="H196" t="n">
         <v>3000</v>
@@ -6082,7 +6082,7 @@
         <v>10.7299995422363</v>
       </c>
       <c r="G197" t="n">
-        <v>9.5732307434082</v>
+        <v>9.57322883605957</v>
       </c>
       <c r="H197" t="n">
         <v>200</v>
@@ -6198,7 +6198,7 @@
         <v>10.539999961853</v>
       </c>
       <c r="G201" t="n">
-        <v>9.40371227264404</v>
+        <v>9.40371322631836</v>
       </c>
       <c r="H201" t="n">
         <v>1600</v>
@@ -6227,7 +6227,7 @@
         <v>10.6400003433228</v>
       </c>
       <c r="G202" t="n">
-        <v>9.49293422698975</v>
+        <v>9.49293327331543</v>
       </c>
       <c r="H202" t="n">
         <v>17000</v>
@@ -6285,7 +6285,7 @@
         <v>10.6599998474121</v>
       </c>
       <c r="G204" t="n">
-        <v>9.51077651977539</v>
+        <v>9.51077747344971</v>
       </c>
       <c r="H204" t="n">
         <v>20200</v>
@@ -6430,7 +6430,7 @@
         <v>10.6300001144409</v>
       </c>
       <c r="G209" t="n">
-        <v>9.48401165008545</v>
+        <v>9.48401069641113</v>
       </c>
       <c r="H209" t="n">
         <v>600</v>
@@ -6459,7 +6459,7 @@
         <v>10.6999998092651</v>
       </c>
       <c r="G210" t="n">
-        <v>9.54646492004395</v>
+        <v>9.54646396636963</v>
       </c>
       <c r="H210" t="n">
         <v>163600</v>
@@ -6488,7 +6488,7 @@
         <v>10.789999961853</v>
       </c>
       <c r="G211" t="n">
-        <v>9.62676048278809</v>
+        <v>9.6267614364624</v>
       </c>
       <c r="H211" t="n">
         <v>1600</v>
@@ -6517,7 +6517,7 @@
         <v>10.8100004196167</v>
       </c>
       <c r="G212" t="n">
-        <v>9.644606590271</v>
+        <v>9.64460563659668</v>
       </c>
       <c r="H212" t="n">
         <v>7200</v>
@@ -6546,7 +6546,7 @@
         <v>10.8100004196167</v>
       </c>
       <c r="G213" t="n">
-        <v>9.644606590271</v>
+        <v>9.64460563659668</v>
       </c>
       <c r="H213" t="n">
         <v>0</v>
@@ -6575,7 +6575,7 @@
         <v>10.8299999237061</v>
       </c>
       <c r="G214" t="n">
-        <v>9.66245079040527</v>
+        <v>9.66244983673096</v>
       </c>
       <c r="H214" t="n">
         <v>600</v>
@@ -6604,7 +6604,7 @@
         <v>10.8500003814697</v>
       </c>
       <c r="G215" t="n">
-        <v>9.68029308319092</v>
+        <v>9.68029499053955</v>
       </c>
       <c r="H215" t="n">
         <v>1600</v>
@@ -6662,7 +6662,7 @@
         <v>10.7600002288818</v>
       </c>
       <c r="G217" t="n">
-        <v>9.59999656677246</v>
+        <v>9.59999561309814</v>
       </c>
       <c r="H217" t="n">
         <v>2400</v>
@@ -6749,7 +6749,7 @@
         <v>10.7299995422363</v>
       </c>
       <c r="G220" t="n">
-        <v>9.5732307434082</v>
+        <v>9.57322883605957</v>
       </c>
       <c r="H220" t="n">
         <v>1600</v>
@@ -6807,7 +6807,7 @@
         <v>10.8000001907349</v>
       </c>
       <c r="G222" t="n">
-        <v>9.6356840133667</v>
+        <v>9.63568496704102</v>
       </c>
       <c r="H222" t="n">
         <v>13000</v>
@@ -6836,7 +6836,7 @@
         <v>10.8199996948242</v>
       </c>
       <c r="G223" t="n">
-        <v>9.65352630615234</v>
+        <v>9.65352916717529</v>
       </c>
       <c r="H223" t="n">
         <v>3600</v>
@@ -6865,7 +6865,7 @@
         <v>10.8000001907349</v>
       </c>
       <c r="G224" t="n">
-        <v>9.6356840133667</v>
+        <v>9.63568496704102</v>
       </c>
       <c r="H224" t="n">
         <v>1000</v>
@@ -6894,7 +6894,7 @@
         <v>10.8000001907349</v>
       </c>
       <c r="G225" t="n">
-        <v>9.6356840133667</v>
+        <v>9.63568496704102</v>
       </c>
       <c r="H225" t="n">
         <v>0</v>
@@ -6923,7 +6923,7 @@
         <v>10.6999998092651</v>
       </c>
       <c r="G226" t="n">
-        <v>9.54646492004395</v>
+        <v>9.54646396636963</v>
       </c>
       <c r="H226" t="n">
         <v>5800</v>
@@ -6952,7 +6952,7 @@
         <v>10.7600002288818</v>
       </c>
       <c r="G227" t="n">
-        <v>9.59999656677246</v>
+        <v>9.59999561309814</v>
       </c>
       <c r="H227" t="n">
         <v>3400</v>
@@ -6981,7 +6981,7 @@
         <v>10.7200002670288</v>
       </c>
       <c r="G228" t="n">
-        <v>9.56430816650391</v>
+        <v>9.56430912017822</v>
       </c>
       <c r="H228" t="n">
         <v>3000</v>
@@ -7068,7 +7068,7 @@
         <v>10.8000001907349</v>
       </c>
       <c r="G231" t="n">
-        <v>9.6356840133667</v>
+        <v>9.63568496704102</v>
       </c>
       <c r="H231" t="n">
         <v>9000</v>
@@ -7126,7 +7126,7 @@
         <v>10.75</v>
       </c>
       <c r="G233" t="n">
-        <v>9.59107494354248</v>
+        <v>9.59107303619385</v>
       </c>
       <c r="H233" t="n">
         <v>1600</v>
@@ -7155,7 +7155,7 @@
         <v>10.75</v>
       </c>
       <c r="G234" t="n">
-        <v>9.59107494354248</v>
+        <v>9.59107303619385</v>
       </c>
       <c r="H234" t="n">
         <v>8200</v>
@@ -7184,7 +7184,7 @@
         <v>10.6400003433228</v>
       </c>
       <c r="G235" t="n">
-        <v>9.49293422698975</v>
+        <v>9.49293327331543</v>
       </c>
       <c r="H235" t="n">
         <v>10600</v>
@@ -7213,7 +7213,7 @@
         <v>10.6000003814697</v>
       </c>
       <c r="G236" t="n">
-        <v>9.45724582672119</v>
+        <v>9.45724487304688</v>
       </c>
       <c r="H236" t="n">
         <v>1200</v>
@@ -7242,7 +7242,7 @@
         <v>10.7299995422363</v>
       </c>
       <c r="G237" t="n">
-        <v>9.5732307434082</v>
+        <v>9.57322883605957</v>
       </c>
       <c r="H237" t="n">
         <v>4400</v>
@@ -7271,7 +7271,7 @@
         <v>10.6999998092651</v>
       </c>
       <c r="G238" t="n">
-        <v>9.54646492004395</v>
+        <v>9.54646396636963</v>
       </c>
       <c r="H238" t="n">
         <v>22200</v>
@@ -7300,7 +7300,7 @@
         <v>10.6000003814697</v>
       </c>
       <c r="G239" t="n">
-        <v>9.45724582672119</v>
+        <v>9.45724487304688</v>
       </c>
       <c r="H239" t="n">
         <v>3800</v>
@@ -7329,7 +7329,7 @@
         <v>10.6000003814697</v>
       </c>
       <c r="G240" t="n">
-        <v>9.45724582672119</v>
+        <v>9.45724487304688</v>
       </c>
       <c r="H240" t="n">
         <v>0</v>
@@ -7358,7 +7358,7 @@
         <v>10.6000003814697</v>
       </c>
       <c r="G241" t="n">
-        <v>9.45724582672119</v>
+        <v>9.45724487304688</v>
       </c>
       <c r="H241" t="n">
         <v>27800</v>
@@ -7416,7 +7416,7 @@
         <v>10.5299997329712</v>
       </c>
       <c r="G243" t="n">
-        <v>9.39479160308838</v>
+        <v>9.3947925567627</v>
       </c>
       <c r="H243" t="n">
         <v>8000</v>
@@ -7445,7 +7445,7 @@
         <v>10.3000001907349</v>
       </c>
       <c r="G244" t="n">
-        <v>9.18958759307861</v>
+        <v>9.1895866394043</v>
       </c>
       <c r="H244" t="n">
         <v>9000</v>
@@ -7503,7 +7503,7 @@
         <v>10.289999961853</v>
       </c>
       <c r="G246" t="n">
-        <v>9.18066596984863</v>
+        <v>9.18066501617432</v>
       </c>
       <c r="H246" t="n">
         <v>11000</v>
@@ -7532,7 +7532,7 @@
         <v>10.2200002670288</v>
       </c>
       <c r="G247" t="n">
-        <v>9.1182107925415</v>
+        <v>9.11821174621582</v>
       </c>
       <c r="H247" t="n">
         <v>15200</v>
@@ -7706,7 +7706,7 @@
         <v>10.289999961853</v>
       </c>
       <c r="G253" t="n">
-        <v>9.18066596984863</v>
+        <v>9.18066501617432</v>
       </c>
       <c r="H253" t="n">
         <v>8400</v>
@@ -7822,7 +7822,7 @@
         <v>10.210000038147</v>
       </c>
       <c r="G257" t="n">
-        <v>9.10928916931152</v>
+        <v>9.10929107666016</v>
       </c>
       <c r="H257" t="n">
         <v>14400</v>
@@ -7880,7 +7880,7 @@
         <v>10.3000001907349</v>
       </c>
       <c r="G259" t="n">
-        <v>9.18958759307861</v>
+        <v>9.1895866394043</v>
       </c>
       <c r="H259" t="n">
         <v>3400</v>
@@ -7909,7 +7909,7 @@
         <v>10.2299995422363</v>
       </c>
       <c r="G260" t="n">
-        <v>9.1271333694458</v>
+        <v>9.12713241577148</v>
       </c>
       <c r="H260" t="n">
         <v>11000</v>
@@ -7938,7 +7938,7 @@
         <v>10.2299995422363</v>
       </c>
       <c r="G261" t="n">
-        <v>9.1271333694458</v>
+        <v>9.12713241577148</v>
       </c>
       <c r="H261" t="n">
         <v>0</v>
@@ -7967,7 +7967,7 @@
         <v>10.3299999237061</v>
       </c>
       <c r="G262" t="n">
-        <v>9.21635246276855</v>
+        <v>9.21635341644287</v>
       </c>
       <c r="H262" t="n">
         <v>400</v>
@@ -8025,7 +8025,7 @@
         <v>10.3000001907349</v>
       </c>
       <c r="G264" t="n">
-        <v>9.18958759307861</v>
+        <v>9.1895866394043</v>
       </c>
       <c r="H264" t="n">
         <v>11400</v>
@@ -8054,7 +8054,7 @@
         <v>10.3400001525879</v>
       </c>
       <c r="G265" t="n">
-        <v>9.22527599334717</v>
+        <v>9.22527694702148</v>
       </c>
       <c r="H265" t="n">
         <v>1200</v>
@@ -8083,7 +8083,7 @@
         <v>10.3299999237061</v>
       </c>
       <c r="G266" t="n">
-        <v>9.21635246276855</v>
+        <v>9.21635341644287</v>
       </c>
       <c r="H266" t="n">
         <v>3000</v>
@@ -8112,7 +8112,7 @@
         <v>10.4200000762939</v>
       </c>
       <c r="G267" t="n">
-        <v>9.29665088653564</v>
+        <v>9.29664993286133</v>
       </c>
       <c r="H267" t="n">
         <v>4000</v>
@@ -8170,7 +8170,7 @@
         <v>10.4200000762939</v>
       </c>
       <c r="G269" t="n">
-        <v>9.29665088653564</v>
+        <v>9.29664993286133</v>
       </c>
       <c r="H269" t="n">
         <v>15000</v>
@@ -8199,7 +8199,7 @@
         <v>10.4499998092651</v>
       </c>
       <c r="G270" t="n">
-        <v>9.3234167098999</v>
+        <v>9.32341575622559</v>
       </c>
       <c r="H270" t="n">
         <v>11200</v>
@@ -8257,7 +8257,7 @@
         <v>10.4099998474121</v>
       </c>
       <c r="G272" t="n">
-        <v>9.28772830963135</v>
+        <v>9.28772640228271</v>
       </c>
       <c r="H272" t="n">
         <v>3000</v>
@@ -8286,7 +8286,7 @@
         <v>10.539999961853</v>
       </c>
       <c r="G273" t="n">
-        <v>9.40371227264404</v>
+        <v>9.40371322631836</v>
       </c>
       <c r="H273" t="n">
         <v>3400</v>
@@ -8315,7 +8315,7 @@
         <v>10.4399995803833</v>
       </c>
       <c r="G274" t="n">
-        <v>9.31449508666992</v>
+        <v>9.31449317932129</v>
       </c>
       <c r="H274" t="n">
         <v>12800</v>
@@ -8344,7 +8344,7 @@
         <v>10.3000001907349</v>
       </c>
       <c r="G275" t="n">
-        <v>9.18958759307861</v>
+        <v>9.1895866394043</v>
       </c>
       <c r="H275" t="n">
         <v>1200</v>
@@ -8431,7 +8431,7 @@
         <v>10.1499996185303</v>
       </c>
       <c r="G278" t="n">
-        <v>9.05575847625732</v>
+        <v>9.05575752258301</v>
       </c>
       <c r="H278" t="n">
         <v>10200</v>
@@ -8518,7 +8518,7 @@
         <v>10.1000003814697</v>
       </c>
       <c r="G281" t="n">
-        <v>9.01114940643311</v>
+        <v>9.01114749908447</v>
       </c>
       <c r="H281" t="n">
         <v>19600</v>
@@ -8547,7 +8547,7 @@
         <v>10.2299995422363</v>
       </c>
       <c r="G282" t="n">
-        <v>9.1271333694458</v>
+        <v>9.12713241577148</v>
       </c>
       <c r="H282" t="n">
         <v>6000</v>
@@ -8663,7 +8663,7 @@
         <v>10.0600004196167</v>
       </c>
       <c r="G286" t="n">
-        <v>8.97546100616455</v>
+        <v>8.97546291351318</v>
       </c>
       <c r="H286" t="n">
         <v>15200</v>
@@ -8692,7 +8692,7 @@
         <v>10.0900001525879</v>
       </c>
       <c r="G287" t="n">
-        <v>9.00222682952881</v>
+        <v>9.00222492218018</v>
       </c>
       <c r="H287" t="n">
         <v>200</v>
@@ -8866,7 +8866,7 @@
         <v>10.0900001525879</v>
       </c>
       <c r="G293" t="n">
-        <v>9.00222682952881</v>
+        <v>9.00222492218018</v>
       </c>
       <c r="H293" t="n">
         <v>6600</v>
@@ -8895,7 +8895,7 @@
         <v>10.0900001525879</v>
       </c>
       <c r="G294" t="n">
-        <v>9.00222682952881</v>
+        <v>9.00222492218018</v>
       </c>
       <c r="H294" t="n">
         <v>0</v>
@@ -9040,7 +9040,7 @@
         <v>10.0600004196167</v>
       </c>
       <c r="G299" t="n">
-        <v>8.97546100616455</v>
+        <v>8.97546291351318</v>
       </c>
       <c r="H299" t="n">
         <v>17200</v>
@@ -9069,7 +9069,7 @@
         <v>10.0600004196167</v>
       </c>
       <c r="G300" t="n">
-        <v>8.97546100616455</v>
+        <v>8.97546291351318</v>
       </c>
       <c r="H300" t="n">
         <v>1000</v>
@@ -9098,7 +9098,7 @@
         <v>10.0600004196167</v>
       </c>
       <c r="G301" t="n">
-        <v>8.97546100616455</v>
+        <v>8.97546291351318</v>
       </c>
       <c r="H301" t="n">
         <v>12600</v>
@@ -9127,7 +9127,7 @@
         <v>10.0600004196167</v>
       </c>
       <c r="G302" t="n">
-        <v>8.97546100616455</v>
+        <v>8.97546291351318</v>
       </c>
       <c r="H302" t="n">
         <v>2000</v>
@@ -9156,7 +9156,7 @@
         <v>10.0600004196167</v>
       </c>
       <c r="G303" t="n">
-        <v>8.97546100616455</v>
+        <v>8.97546291351318</v>
       </c>
       <c r="H303" t="n">
         <v>0</v>
@@ -9185,7 +9185,7 @@
         <v>10.0900001525879</v>
       </c>
       <c r="G304" t="n">
-        <v>9.00222682952881</v>
+        <v>9.00222492218018</v>
       </c>
       <c r="H304" t="n">
         <v>18400</v>
@@ -9214,7 +9214,7 @@
         <v>10.0600004196167</v>
       </c>
       <c r="G305" t="n">
-        <v>8.97546100616455</v>
+        <v>8.97546291351318</v>
       </c>
       <c r="H305" t="n">
         <v>200</v>
@@ -9272,7 +9272,7 @@
         <v>10.0600004196167</v>
       </c>
       <c r="G307" t="n">
-        <v>8.97546100616455</v>
+        <v>8.97546291351318</v>
       </c>
       <c r="H307" t="n">
         <v>4200</v>
@@ -9301,7 +9301,7 @@
         <v>10.0100002288818</v>
       </c>
       <c r="G308" t="n">
-        <v>8.93085098266602</v>
+        <v>8.93085193634033</v>
       </c>
       <c r="H308" t="n">
         <v>25000</v>
@@ -9330,7 +9330,7 @@
         <v>10.0100002288818</v>
       </c>
       <c r="G309" t="n">
-        <v>8.93085098266602</v>
+        <v>8.93085193634033</v>
       </c>
       <c r="H309" t="n">
         <v>0</v>
@@ -9359,7 +9359,7 @@
         <v>10.1000003814697</v>
       </c>
       <c r="G310" t="n">
-        <v>9.01114940643311</v>
+        <v>9.01114749908447</v>
       </c>
       <c r="H310" t="n">
         <v>1200</v>
@@ -9504,7 +9504,7 @@
         <v>10.1000003814697</v>
       </c>
       <c r="G315" t="n">
-        <v>9.01114940643311</v>
+        <v>9.01114749908447</v>
       </c>
       <c r="H315" t="n">
         <v>19800</v>
@@ -9533,7 +9533,7 @@
         <v>10.1000003814697</v>
       </c>
       <c r="G316" t="n">
-        <v>9.01114940643311</v>
+        <v>9.01114749908447</v>
       </c>
       <c r="H316" t="n">
         <v>25600</v>
@@ -9562,7 +9562,7 @@
         <v>10.1000003814697</v>
       </c>
       <c r="G317" t="n">
-        <v>9.01114940643311</v>
+        <v>9.01114749908447</v>
       </c>
       <c r="H317" t="n">
         <v>0</v>
@@ -9736,7 +9736,7 @@
         <v>10.1000003814697</v>
       </c>
       <c r="G323" t="n">
-        <v>9.01114940643311</v>
+        <v>9.01114749908447</v>
       </c>
       <c r="H323" t="n">
         <v>1200</v>
@@ -9765,7 +9765,7 @@
         <v>10.1000003814697</v>
       </c>
       <c r="G324" t="n">
-        <v>9.01114940643311</v>
+        <v>9.01114749908447</v>
       </c>
       <c r="H324" t="n">
         <v>4400</v>
@@ -9852,7 +9852,7 @@
         <v>10.1000003814697</v>
       </c>
       <c r="G327" t="n">
-        <v>9.01114940643311</v>
+        <v>9.01114749908447</v>
       </c>
       <c r="H327" t="n">
         <v>2400</v>
@@ -9910,7 +9910,7 @@
         <v>10.1000003814697</v>
       </c>
       <c r="G329" t="n">
-        <v>9.01114940643311</v>
+        <v>9.01114749908447</v>
       </c>
       <c r="H329" t="n">
         <v>800</v>
@@ -9939,7 +9939,7 @@
         <v>10.1000003814697</v>
       </c>
       <c r="G330" t="n">
-        <v>9.01114940643311</v>
+        <v>9.01114749908447</v>
       </c>
       <c r="H330" t="n">
         <v>0</v>
@@ -10519,7 +10519,7 @@
         <v>10.1000003814697</v>
       </c>
       <c r="G350" t="n">
-        <v>9.01114940643311</v>
+        <v>9.01114749908447</v>
       </c>
       <c r="H350" t="n">
         <v>400</v>
@@ -10983,7 +10983,7 @@
         <v>9.85000038146973</v>
       </c>
       <c r="G366" t="n">
-        <v>8.78810119628906</v>
+        <v>8.78810214996338</v>
       </c>
       <c r="H366" t="n">
         <v>1200</v>
@@ -11012,7 +11012,7 @@
         <v>9.80000019073486</v>
       </c>
       <c r="G367" t="n">
-        <v>8.74349212646484</v>
+        <v>8.74349021911621</v>
       </c>
       <c r="H367" t="n">
         <v>2000</v>
@@ -11157,7 +11157,7 @@
         <v>9.85000038146973</v>
       </c>
       <c r="G372" t="n">
-        <v>8.78810119628906</v>
+        <v>8.78810214996338</v>
       </c>
       <c r="H372" t="n">
         <v>6800</v>
@@ -11215,7 +11215,7 @@
         <v>10.1000003814697</v>
       </c>
       <c r="G374" t="n">
-        <v>9.01114940643311</v>
+        <v>9.01114749908447</v>
       </c>
       <c r="H374" t="n">
         <v>35200</v>
@@ -11621,7 +11621,7 @@
         <v>9.80000019073486</v>
       </c>
       <c r="G388" t="n">
-        <v>8.74349212646484</v>
+        <v>8.74349021911621</v>
       </c>
       <c r="H388" t="n">
         <v>18400</v>
@@ -11650,7 +11650,7 @@
         <v>9.80000019073486</v>
       </c>
       <c r="G389" t="n">
-        <v>8.74349212646484</v>
+        <v>8.74349021911621</v>
       </c>
       <c r="H389" t="n">
         <v>0</v>
@@ -11679,7 +11679,7 @@
         <v>9.85000038146973</v>
       </c>
       <c r="G390" t="n">
-        <v>8.78810119628906</v>
+        <v>8.78810214996338</v>
       </c>
       <c r="H390" t="n">
         <v>400</v>
@@ -11708,7 +11708,7 @@
         <v>9.85000038146973</v>
       </c>
       <c r="G391" t="n">
-        <v>8.78810119628906</v>
+        <v>8.78810214996338</v>
       </c>
       <c r="H391" t="n">
         <v>10000</v>
@@ -11737,7 +11737,7 @@
         <v>9.85000038146973</v>
       </c>
       <c r="G392" t="n">
-        <v>8.78810119628906</v>
+        <v>8.78810214996338</v>
       </c>
       <c r="H392" t="n">
         <v>0</v>
@@ -11766,7 +11766,7 @@
         <v>9.85000038146973</v>
       </c>
       <c r="G393" t="n">
-        <v>8.78810119628906</v>
+        <v>8.78810214996338</v>
       </c>
       <c r="H393" t="n">
         <v>0</v>
@@ -11795,7 +11795,7 @@
         <v>9.85000038146973</v>
       </c>
       <c r="G394" t="n">
-        <v>8.78810119628906</v>
+        <v>8.78810214996338</v>
       </c>
       <c r="H394" t="n">
         <v>24000</v>
@@ -12114,7 +12114,7 @@
         <v>9.85000038146973</v>
       </c>
       <c r="G405" t="n">
-        <v>8.78810119628906</v>
+        <v>8.78810214996338</v>
       </c>
       <c r="H405" t="n">
         <v>200</v>
@@ -12143,7 +12143,7 @@
         <v>9.85000038146973</v>
       </c>
       <c r="G406" t="n">
-        <v>8.78810119628906</v>
+        <v>8.78810214996338</v>
       </c>
       <c r="H406" t="n">
         <v>13800</v>
@@ -12404,7 +12404,7 @@
         <v>9.80000019073486</v>
       </c>
       <c r="G415" t="n">
-        <v>8.74349212646484</v>
+        <v>8.74349021911621</v>
       </c>
       <c r="H415" t="n">
         <v>2400</v>
@@ -12491,7 +12491,7 @@
         <v>9.80000019073486</v>
       </c>
       <c r="G418" t="n">
-        <v>8.74349212646484</v>
+        <v>8.74349021911621</v>
       </c>
       <c r="H418" t="n">
         <v>35200</v>
@@ -12607,7 +12607,7 @@
         <v>9.80000019073486</v>
       </c>
       <c r="G422" t="n">
-        <v>8.74349212646484</v>
+        <v>8.74349021911621</v>
       </c>
       <c r="H422" t="n">
         <v>600</v>
@@ -12636,7 +12636,7 @@
         <v>9.85000038146973</v>
       </c>
       <c r="G423" t="n">
-        <v>8.78810119628906</v>
+        <v>8.78810214996338</v>
       </c>
       <c r="H423" t="n">
         <v>28400</v>
@@ -12752,7 +12752,7 @@
         <v>10.1000003814697</v>
       </c>
       <c r="G427" t="n">
-        <v>9.01114940643311</v>
+        <v>9.01114749908447</v>
       </c>
       <c r="H427" t="n">
         <v>180800</v>
@@ -12781,7 +12781,7 @@
         <v>10.1000003814697</v>
       </c>
       <c r="G428" t="n">
-        <v>9.01114940643311</v>
+        <v>9.01114749908447</v>
       </c>
       <c r="H428" t="n">
         <v>29200</v>
@@ -12810,7 +12810,7 @@
         <v>10.1000003814697</v>
       </c>
       <c r="G429" t="n">
-        <v>9.01114940643311</v>
+        <v>9.01114749908447</v>
       </c>
       <c r="H429" t="n">
         <v>29600</v>
@@ -12839,7 +12839,7 @@
         <v>10.1000003814697</v>
       </c>
       <c r="G430" t="n">
-        <v>9.01114940643311</v>
+        <v>9.01114749908447</v>
       </c>
       <c r="H430" t="n">
         <v>70000</v>
@@ -12868,7 +12868,7 @@
         <v>10.1000003814697</v>
       </c>
       <c r="G431" t="n">
-        <v>9.01114940643311</v>
+        <v>9.01114749908447</v>
       </c>
       <c r="H431" t="n">
         <v>8400</v>
@@ -12897,7 +12897,7 @@
         <v>10.1000003814697</v>
       </c>
       <c r="G432" t="n">
-        <v>9.01114940643311</v>
+        <v>9.01114749908447</v>
       </c>
       <c r="H432" t="n">
         <v>3200</v>
@@ -12926,7 +12926,7 @@
         <v>10.1000003814697</v>
       </c>
       <c r="G433" t="n">
-        <v>9.01114940643311</v>
+        <v>9.01114749908447</v>
       </c>
       <c r="H433" t="n">
         <v>3600</v>
@@ -12955,7 +12955,7 @@
         <v>10.1000003814697</v>
       </c>
       <c r="G434" t="n">
-        <v>9.01114940643311</v>
+        <v>9.01114749908447</v>
       </c>
       <c r="H434" t="n">
         <v>2400</v>
@@ -13129,7 +13129,7 @@
         <v>10.3000001907349</v>
       </c>
       <c r="G440" t="n">
-        <v>9.18958759307861</v>
+        <v>9.1895866394043</v>
       </c>
       <c r="H440" t="n">
         <v>5000</v>
@@ -13158,7 +13158,7 @@
         <v>10.3000001907349</v>
       </c>
       <c r="G441" t="n">
-        <v>9.18958759307861</v>
+        <v>9.1895866394043</v>
       </c>
       <c r="H441" t="n">
         <v>27000</v>
@@ -13187,7 +13187,7 @@
         <v>10.3000001907349</v>
       </c>
       <c r="G442" t="n">
-        <v>9.18958759307861</v>
+        <v>9.1895866394043</v>
       </c>
       <c r="H442" t="n">
         <v>1400</v>
@@ -13216,7 +13216,7 @@
         <v>10.3000001907349</v>
       </c>
       <c r="G443" t="n">
-        <v>9.18958759307861</v>
+        <v>9.1895866394043</v>
       </c>
       <c r="H443" t="n">
         <v>2400</v>
@@ -13419,7 +13419,7 @@
         <v>10.3000001907349</v>
       </c>
       <c r="G450" t="n">
-        <v>9.18958759307861</v>
+        <v>9.1895866394043</v>
       </c>
       <c r="H450" t="n">
         <v>21000</v>
@@ -13535,7 +13535,7 @@
         <v>10.3000001907349</v>
       </c>
       <c r="G454" t="n">
-        <v>9.18958759307861</v>
+        <v>9.1895866394043</v>
       </c>
       <c r="H454" t="n">
         <v>7000</v>
@@ -13593,7 +13593,7 @@
         <v>10.3000001907349</v>
       </c>
       <c r="G456" t="n">
-        <v>9.18958759307861</v>
+        <v>9.1895866394043</v>
       </c>
       <c r="H456" t="n">
         <v>5000</v>
@@ -13651,7 +13651,7 @@
         <v>10.3000001907349</v>
       </c>
       <c r="G458" t="n">
-        <v>9.18958759307861</v>
+        <v>9.1895866394043</v>
       </c>
       <c r="H458" t="n">
         <v>600</v>
@@ -13680,7 +13680,7 @@
         <v>10.3000001907349</v>
       </c>
       <c r="G459" t="n">
-        <v>9.18958759307861</v>
+        <v>9.1895866394043</v>
       </c>
       <c r="H459" t="n">
         <v>600</v>
@@ -13767,7 +13767,7 @@
         <v>10.3000001907349</v>
       </c>
       <c r="G462" t="n">
-        <v>9.18958759307861</v>
+        <v>9.1895866394043</v>
       </c>
       <c r="H462" t="n">
         <v>2400</v>
@@ -13796,7 +13796,7 @@
         <v>10.3000001907349</v>
       </c>
       <c r="G463" t="n">
-        <v>9.18958759307861</v>
+        <v>9.1895866394043</v>
       </c>
       <c r="H463" t="n">
         <v>9600</v>
@@ -13825,7 +13825,7 @@
         <v>10.1000003814697</v>
       </c>
       <c r="G464" t="n">
-        <v>9.01114940643311</v>
+        <v>9.01114749908447</v>
       </c>
       <c r="H464" t="n">
         <v>2000</v>
@@ -13854,7 +13854,7 @@
         <v>10.3000001907349</v>
       </c>
       <c r="G465" t="n">
-        <v>9.18958759307861</v>
+        <v>9.1895866394043</v>
       </c>
       <c r="H465" t="n">
         <v>200</v>
@@ -13883,7 +13883,7 @@
         <v>10.1000003814697</v>
       </c>
       <c r="G466" t="n">
-        <v>9.01114940643311</v>
+        <v>9.01114749908447</v>
       </c>
       <c r="H466" t="n">
         <v>200</v>
@@ -13912,7 +13912,7 @@
         <v>10.1000003814697</v>
       </c>
       <c r="G467" t="n">
-        <v>9.01114940643311</v>
+        <v>9.01114749908447</v>
       </c>
       <c r="H467" t="n">
         <v>600</v>
@@ -14057,7 +14057,7 @@
         <v>10.1000003814697</v>
       </c>
       <c r="G472" t="n">
-        <v>9.01114940643311</v>
+        <v>9.01114749908447</v>
       </c>
       <c r="H472" t="n">
         <v>1000</v>
@@ -14144,7 +14144,7 @@
         <v>10.3000001907349</v>
       </c>
       <c r="G475" t="n">
-        <v>9.18958759307861</v>
+        <v>9.1895866394043</v>
       </c>
       <c r="H475" t="n">
         <v>2000</v>
@@ -14347,7 +14347,7 @@
         <v>10.1000003814697</v>
       </c>
       <c r="G482" t="n">
-        <v>9.01114940643311</v>
+        <v>9.01114749908447</v>
       </c>
       <c r="H482" t="n">
         <v>8400</v>
@@ -14434,7 +14434,7 @@
         <v>10.1000003814697</v>
       </c>
       <c r="G485" t="n">
-        <v>9.01114940643311</v>
+        <v>9.01114749908447</v>
       </c>
       <c r="H485" t="n">
         <v>10000</v>
@@ -14492,7 +14492,7 @@
         <v>10.1000003814697</v>
       </c>
       <c r="G487" t="n">
-        <v>9.01114940643311</v>
+        <v>9.01114749908447</v>
       </c>
       <c r="H487" t="n">
         <v>7000</v>
@@ -14521,7 +14521,7 @@
         <v>10.1000003814697</v>
       </c>
       <c r="G488" t="n">
-        <v>9.01114940643311</v>
+        <v>9.01114749908447</v>
       </c>
       <c r="H488" t="n">
         <v>800</v>
@@ -14608,7 +14608,7 @@
         <v>10.1000003814697</v>
       </c>
       <c r="G491" t="n">
-        <v>9.01114940643311</v>
+        <v>9.01114749908447</v>
       </c>
       <c r="H491" t="n">
         <v>1600</v>
@@ -14695,7 +14695,7 @@
         <v>10.1000003814697</v>
       </c>
       <c r="G494" t="n">
-        <v>9.01114940643311</v>
+        <v>9.01114749908447</v>
       </c>
       <c r="H494" t="n">
         <v>1000</v>
@@ -14724,7 +14724,7 @@
         <v>10.1000003814697</v>
       </c>
       <c r="G495" t="n">
-        <v>9.01114940643311</v>
+        <v>9.01114749908447</v>
       </c>
       <c r="H495" t="n">
         <v>7600</v>
@@ -14753,7 +14753,7 @@
         <v>10.1000003814697</v>
       </c>
       <c r="G496" t="n">
-        <v>9.01114940643311</v>
+        <v>9.01114749908447</v>
       </c>
       <c r="H496" t="n">
         <v>10800</v>
@@ -14811,7 +14811,7 @@
         <v>9.64999961853027</v>
       </c>
       <c r="G498" t="n">
-        <v>8.60966110229492</v>
+        <v>8.60966014862061</v>
       </c>
       <c r="H498" t="n">
         <v>65200</v>
@@ -14840,7 +14840,7 @@
         <v>9.80000019073486</v>
       </c>
       <c r="G499" t="n">
-        <v>8.74349212646484</v>
+        <v>8.74349021911621</v>
       </c>
       <c r="H499" t="n">
         <v>17600</v>
@@ -14898,7 +14898,7 @@
         <v>9.85000038146973</v>
       </c>
       <c r="G501" t="n">
-        <v>8.78810119628906</v>
+        <v>8.78810214996338</v>
       </c>
       <c r="H501" t="n">
         <v>18200</v>
@@ -14927,7 +14927,7 @@
         <v>9.85000038146973</v>
       </c>
       <c r="G502" t="n">
-        <v>8.78810119628906</v>
+        <v>8.78810214996338</v>
       </c>
       <c r="H502" t="n">
         <v>0</v>
@@ -14956,7 +14956,7 @@
         <v>9.80000019073486</v>
       </c>
       <c r="G503" t="n">
-        <v>8.74349212646484</v>
+        <v>8.74349021911621</v>
       </c>
       <c r="H503" t="n">
         <v>1800</v>
@@ -14985,7 +14985,7 @@
         <v>9.80000019073486</v>
       </c>
       <c r="G504" t="n">
-        <v>8.74349212646484</v>
+        <v>8.74349021911621</v>
       </c>
       <c r="H504" t="n">
         <v>23000</v>
@@ -15043,7 +15043,7 @@
         <v>9.80000019073486</v>
       </c>
       <c r="G506" t="n">
-        <v>8.74349212646484</v>
+        <v>8.74349021911621</v>
       </c>
       <c r="H506" t="n">
         <v>6800</v>
@@ -15101,7 +15101,7 @@
         <v>9.80000019073486</v>
       </c>
       <c r="G508" t="n">
-        <v>8.74349212646484</v>
+        <v>8.74349021911621</v>
       </c>
       <c r="H508" t="n">
         <v>1000</v>
@@ -15159,7 +15159,7 @@
         <v>9.85000038146973</v>
       </c>
       <c r="G510" t="n">
-        <v>8.78810119628906</v>
+        <v>8.78810214996338</v>
       </c>
       <c r="H510" t="n">
         <v>5000</v>
@@ -15188,7 +15188,7 @@
         <v>9.80000019073486</v>
       </c>
       <c r="G511" t="n">
-        <v>8.74349212646484</v>
+        <v>8.74349021911621</v>
       </c>
       <c r="H511" t="n">
         <v>1200</v>
@@ -15217,7 +15217,7 @@
         <v>9.80000019073486</v>
       </c>
       <c r="G512" t="n">
-        <v>8.74349212646484</v>
+        <v>8.74349021911621</v>
       </c>
       <c r="H512" t="n">
         <v>21800</v>
@@ -15275,7 +15275,7 @@
         <v>9.64999961853027</v>
       </c>
       <c r="G514" t="n">
-        <v>8.60966110229492</v>
+        <v>8.60966014862061</v>
       </c>
       <c r="H514" t="n">
         <v>10200</v>
@@ -15304,7 +15304,7 @@
         <v>9.64999961853027</v>
       </c>
       <c r="G515" t="n">
-        <v>8.60966110229492</v>
+        <v>8.60966014862061</v>
       </c>
       <c r="H515" t="n">
         <v>3800</v>
@@ -15362,7 +15362,7 @@
         <v>9.64999961853027</v>
       </c>
       <c r="G517" t="n">
-        <v>8.60966110229492</v>
+        <v>8.60966014862061</v>
       </c>
       <c r="H517" t="n">
         <v>2200</v>
@@ -15536,7 +15536,7 @@
         <v>9.64999961853027</v>
       </c>
       <c r="G523" t="n">
-        <v>8.60966110229492</v>
+        <v>8.60966014862061</v>
       </c>
       <c r="H523" t="n">
         <v>200</v>
@@ -15565,7 +15565,7 @@
         <v>9.80000019073486</v>
       </c>
       <c r="G524" t="n">
-        <v>8.74349212646484</v>
+        <v>8.74349021911621</v>
       </c>
       <c r="H524" t="n">
         <v>200</v>
@@ -15594,7 +15594,7 @@
         <v>9.80000019073486</v>
       </c>
       <c r="G525" t="n">
-        <v>8.74349212646484</v>
+        <v>8.74349021911621</v>
       </c>
       <c r="H525" t="n">
         <v>6200</v>
@@ -15623,7 +15623,7 @@
         <v>9.64999961853027</v>
       </c>
       <c r="G526" t="n">
-        <v>8.60966110229492</v>
+        <v>8.60966014862061</v>
       </c>
       <c r="H526" t="n">
         <v>4200</v>
@@ -15681,7 +15681,7 @@
         <v>9.55000019073486</v>
       </c>
       <c r="G528" t="n">
-        <v>8.52044296264648</v>
+        <v>8.52044200897217</v>
       </c>
       <c r="H528" t="n">
         <v>3400</v>
@@ -15710,7 +15710,7 @@
         <v>9.5</v>
       </c>
       <c r="G529" t="n">
-        <v>8.47583389282227</v>
+        <v>8.47583293914795</v>
       </c>
       <c r="H529" t="n">
         <v>10600</v>
@@ -15739,7 +15739,7 @@
         <v>9.39999961853027</v>
       </c>
       <c r="G530" t="n">
-        <v>8.38661289215088</v>
+        <v>8.3866138458252</v>
       </c>
       <c r="H530" t="n">
         <v>20000</v>
@@ -15768,7 +15768,7 @@
         <v>9.19999980926514</v>
       </c>
       <c r="G531" t="n">
-        <v>8.20817565917969</v>
+        <v>8.208176612854</v>
       </c>
       <c r="H531" t="n">
         <v>12800</v>
@@ -15797,7 +15797,7 @@
         <v>9</v>
       </c>
       <c r="G532" t="n">
-        <v>8.02973556518555</v>
+        <v>8.02973651885986</v>
       </c>
       <c r="H532" t="n">
         <v>6800</v>
@@ -15826,7 +15826,7 @@
         <v>9</v>
       </c>
       <c r="G533" t="n">
-        <v>8.02973556518555</v>
+        <v>8.02973651885986</v>
       </c>
       <c r="H533" t="n">
         <v>12200</v>
@@ -15855,7 +15855,7 @@
         <v>8.80000019073486</v>
       </c>
       <c r="G534" t="n">
-        <v>7.85129880905151</v>
+        <v>7.8512978553772</v>
       </c>
       <c r="H534" t="n">
         <v>9600</v>
@@ -15884,7 +15884,7 @@
         <v>8.85000038146973</v>
       </c>
       <c r="G535" t="n">
-        <v>7.89590740203857</v>
+        <v>7.89590787887573</v>
       </c>
       <c r="H535" t="n">
         <v>400</v>
@@ -15913,7 +15913,7 @@
         <v>8.85000038146973</v>
       </c>
       <c r="G536" t="n">
-        <v>7.89590740203857</v>
+        <v>7.89590787887573</v>
       </c>
       <c r="H536" t="n">
         <v>0</v>
@@ -15942,7 +15942,7 @@
         <v>8.94999980926514</v>
       </c>
       <c r="G537" t="n">
-        <v>7.98512649536133</v>
+        <v>7.98512554168701</v>
       </c>
       <c r="H537" t="n">
         <v>5800</v>
@@ -15971,7 +15971,7 @@
         <v>9</v>
       </c>
       <c r="G538" t="n">
-        <v>8.02973556518555</v>
+        <v>8.02973651885986</v>
       </c>
       <c r="H538" t="n">
         <v>2200</v>
@@ -16000,7 +16000,7 @@
         <v>9.10000038146973</v>
       </c>
       <c r="G539" t="n">
-        <v>8.11895656585693</v>
+        <v>8.11895561218262</v>
       </c>
       <c r="H539" t="n">
         <v>2200</v>
@@ -16029,7 +16029,7 @@
         <v>9.19999980926514</v>
       </c>
       <c r="G540" t="n">
-        <v>8.20817565917969</v>
+        <v>8.208176612854</v>
       </c>
       <c r="H540" t="n">
         <v>2400</v>
@@ -16058,7 +16058,7 @@
         <v>9.19999980926514</v>
       </c>
       <c r="G541" t="n">
-        <v>8.20817565917969</v>
+        <v>8.208176612854</v>
       </c>
       <c r="H541" t="n">
         <v>0</v>
@@ -16087,7 +16087,7 @@
         <v>9.19999980926514</v>
       </c>
       <c r="G542" t="n">
-        <v>8.20817565917969</v>
+        <v>8.208176612854</v>
       </c>
       <c r="H542" t="n">
         <v>0</v>
@@ -16116,7 +16116,7 @@
         <v>9.10000038146973</v>
       </c>
       <c r="G543" t="n">
-        <v>8.11895656585693</v>
+        <v>8.11895561218262</v>
       </c>
       <c r="H543" t="n">
         <v>2000</v>
@@ -16145,7 +16145,7 @@
         <v>9.10000038146973</v>
       </c>
       <c r="G544" t="n">
-        <v>8.11895656585693</v>
+        <v>8.11895561218262</v>
       </c>
       <c r="H544" t="n">
         <v>0</v>
@@ -16174,7 +16174,7 @@
         <v>9.10000038146973</v>
       </c>
       <c r="G545" t="n">
-        <v>8.11895656585693</v>
+        <v>8.11895561218262</v>
       </c>
       <c r="H545" t="n">
         <v>0</v>
@@ -16203,7 +16203,7 @@
         <v>9</v>
       </c>
       <c r="G546" t="n">
-        <v>8.02973556518555</v>
+        <v>8.02973651885986</v>
       </c>
       <c r="H546" t="n">
         <v>1200</v>
@@ -16232,7 +16232,7 @@
         <v>8.85000038146973</v>
       </c>
       <c r="G547" t="n">
-        <v>7.89590740203857</v>
+        <v>7.89590787887573</v>
       </c>
       <c r="H547" t="n">
         <v>5200</v>
@@ -16261,7 +16261,7 @@
         <v>8.85000038146973</v>
       </c>
       <c r="G548" t="n">
-        <v>7.89590740203857</v>
+        <v>7.89590787887573</v>
       </c>
       <c r="H548" t="n">
         <v>10200</v>
@@ -16290,7 +16290,7 @@
         <v>8.85000038146973</v>
       </c>
       <c r="G549" t="n">
-        <v>7.89590740203857</v>
+        <v>7.89590787887573</v>
       </c>
       <c r="H549" t="n">
         <v>0</v>
@@ -16319,7 +16319,7 @@
         <v>8.85000038146973</v>
       </c>
       <c r="G550" t="n">
-        <v>7.89590740203857</v>
+        <v>7.89590787887573</v>
       </c>
       <c r="H550" t="n">
         <v>0</v>
@@ -16348,7 +16348,7 @@
         <v>8.80000019073486</v>
       </c>
       <c r="G551" t="n">
-        <v>7.85129880905151</v>
+        <v>7.8512978553772</v>
       </c>
       <c r="H551" t="n">
         <v>13400</v>
@@ -16377,7 +16377,7 @@
         <v>8.80000019073486</v>
       </c>
       <c r="G552" t="n">
-        <v>7.85129880905151</v>
+        <v>7.8512978553772</v>
       </c>
       <c r="H552" t="n">
         <v>0</v>
@@ -16493,7 +16493,7 @@
         <v>9.14999961853027</v>
       </c>
       <c r="G556" t="n">
-        <v>8.16356468200684</v>
+        <v>8.16356563568115</v>
       </c>
       <c r="H556" t="n">
         <v>20400</v>
@@ -16522,7 +16522,7 @@
         <v>9.05000019073486</v>
       </c>
       <c r="G557" t="n">
-        <v>8.07434558868408</v>
+        <v>8.07434844970703</v>
       </c>
       <c r="H557" t="n">
         <v>11600</v>
@@ -16667,7 +16667,7 @@
         <v>9.44999980926514</v>
       </c>
       <c r="G562" t="n">
-        <v>8.43122291564941</v>
+        <v>8.43122386932373</v>
       </c>
       <c r="H562" t="n">
         <v>600</v>
@@ -16696,7 +16696,7 @@
         <v>9.64999961853027</v>
       </c>
       <c r="G563" t="n">
-        <v>8.60966110229492</v>
+        <v>8.60966014862061</v>
       </c>
       <c r="H563" t="n">
         <v>3200</v>
@@ -16725,7 +16725,7 @@
         <v>9.55000019073486</v>
       </c>
       <c r="G564" t="n">
-        <v>8.52044296264648</v>
+        <v>8.52044200897217</v>
       </c>
       <c r="H564" t="n">
         <v>4600</v>
@@ -16754,7 +16754,7 @@
         <v>9.60000038146973</v>
       </c>
       <c r="G565" t="n">
-        <v>8.56505298614502</v>
+        <v>8.5650520324707</v>
       </c>
       <c r="H565" t="n">
         <v>3200</v>
@@ -16783,7 +16783,7 @@
         <v>9.60000038146973</v>
       </c>
       <c r="G566" t="n">
-        <v>8.56505298614502</v>
+        <v>8.5650520324707</v>
       </c>
       <c r="H566" t="n">
         <v>9400</v>
@@ -16812,7 +16812,7 @@
         <v>9.60000038146973</v>
       </c>
       <c r="G567" t="n">
-        <v>8.56505298614502</v>
+        <v>8.5650520324707</v>
       </c>
       <c r="H567" t="n">
         <v>11000</v>
@@ -16841,7 +16841,7 @@
         <v>9.64999961853027</v>
       </c>
       <c r="G568" t="n">
-        <v>8.60966110229492</v>
+        <v>8.60966014862061</v>
       </c>
       <c r="H568" t="n">
         <v>10000</v>
@@ -16870,7 +16870,7 @@
         <v>9.55000019073486</v>
       </c>
       <c r="G569" t="n">
-        <v>8.52044296264648</v>
+        <v>8.52044200897217</v>
       </c>
       <c r="H569" t="n">
         <v>6800</v>
@@ -16899,7 +16899,7 @@
         <v>9.60000038146973</v>
       </c>
       <c r="G570" t="n">
-        <v>8.56505298614502</v>
+        <v>8.5650520324707</v>
       </c>
       <c r="H570" t="n">
         <v>1600</v>
@@ -16928,7 +16928,7 @@
         <v>9.60000038146973</v>
       </c>
       <c r="G571" t="n">
-        <v>8.56505298614502</v>
+        <v>8.5650520324707</v>
       </c>
       <c r="H571" t="n">
         <v>4200</v>
@@ -16957,7 +16957,7 @@
         <v>9.60000038146973</v>
       </c>
       <c r="G572" t="n">
-        <v>8.56505298614502</v>
+        <v>8.5650520324707</v>
       </c>
       <c r="H572" t="n">
         <v>13200</v>
@@ -16986,7 +16986,7 @@
         <v>9.64999961853027</v>
       </c>
       <c r="G573" t="n">
-        <v>8.60966110229492</v>
+        <v>8.60966014862061</v>
       </c>
       <c r="H573" t="n">
         <v>5600</v>
@@ -17015,7 +17015,7 @@
         <v>9.64999961853027</v>
       </c>
       <c r="G574" t="n">
-        <v>8.60966110229492</v>
+        <v>8.60966014862061</v>
       </c>
       <c r="H574" t="n">
         <v>8200</v>
@@ -17044,7 +17044,7 @@
         <v>9.64999961853027</v>
       </c>
       <c r="G575" t="n">
-        <v>8.60966110229492</v>
+        <v>8.60966014862061</v>
       </c>
       <c r="H575" t="n">
         <v>17800</v>
@@ -17073,7 +17073,7 @@
         <v>9.64999961853027</v>
       </c>
       <c r="G576" t="n">
-        <v>8.60966110229492</v>
+        <v>8.60966014862061</v>
       </c>
       <c r="H576" t="n">
         <v>13800</v>
@@ -17131,7 +17131,7 @@
         <v>9.80000019073486</v>
       </c>
       <c r="G578" t="n">
-        <v>8.74349212646484</v>
+        <v>8.74349021911621</v>
       </c>
       <c r="H578" t="n">
         <v>5200</v>
@@ -17189,7 +17189,7 @@
         <v>9.80000019073486</v>
       </c>
       <c r="G580" t="n">
-        <v>8.74349212646484</v>
+        <v>8.74349021911621</v>
       </c>
       <c r="H580" t="n">
         <v>9800</v>
@@ -17218,7 +17218,7 @@
         <v>9.80000019073486</v>
       </c>
       <c r="G581" t="n">
-        <v>8.74349212646484</v>
+        <v>8.74349021911621</v>
       </c>
       <c r="H581" t="n">
         <v>21200</v>
@@ -17247,7 +17247,7 @@
         <v>9.85000038146973</v>
       </c>
       <c r="G582" t="n">
-        <v>8.78810119628906</v>
+        <v>8.78810214996338</v>
       </c>
       <c r="H582" t="n">
         <v>35600</v>
@@ -17276,7 +17276,7 @@
         <v>9.85000038146973</v>
       </c>
       <c r="G583" t="n">
-        <v>8.78810119628906</v>
+        <v>8.78810214996338</v>
       </c>
       <c r="H583" t="n">
         <v>3600</v>
@@ -17334,7 +17334,7 @@
         <v>9.85000038146973</v>
       </c>
       <c r="G585" t="n">
-        <v>8.78810119628906</v>
+        <v>8.78810214996338</v>
       </c>
       <c r="H585" t="n">
         <v>121400</v>
@@ -17363,7 +17363,7 @@
         <v>9.85000038146973</v>
       </c>
       <c r="G586" t="n">
-        <v>8.78810119628906</v>
+        <v>8.78810214996338</v>
       </c>
       <c r="H586" t="n">
         <v>6200</v>
@@ -17392,7 +17392,7 @@
         <v>9.85000038146973</v>
       </c>
       <c r="G587" t="n">
-        <v>8.78810119628906</v>
+        <v>8.78810214996338</v>
       </c>
       <c r="H587" t="n">
         <v>19200</v>
@@ -17421,7 +17421,7 @@
         <v>9.85000038146973</v>
       </c>
       <c r="G588" t="n">
-        <v>8.78810119628906</v>
+        <v>8.78810214996338</v>
       </c>
       <c r="H588" t="n">
         <v>2600</v>
@@ -17653,7 +17653,7 @@
         <v>10.1000003814697</v>
       </c>
       <c r="G596" t="n">
-        <v>9.01114940643311</v>
+        <v>9.01114749908447</v>
       </c>
       <c r="H596" t="n">
         <v>18400</v>
@@ -17740,7 +17740,7 @@
         <v>10.1000003814697</v>
       </c>
       <c r="G599" t="n">
-        <v>9.01114940643311</v>
+        <v>9.01114749908447</v>
       </c>
       <c r="H599" t="n">
         <v>3200</v>
@@ -17798,7 +17798,7 @@
         <v>10.1000003814697</v>
       </c>
       <c r="G601" t="n">
-        <v>9.01114940643311</v>
+        <v>9.01114749908447</v>
       </c>
       <c r="H601" t="n">
         <v>6200</v>
@@ -17827,7 +17827,7 @@
         <v>10.1000003814697</v>
       </c>
       <c r="G602" t="n">
-        <v>9.01114940643311</v>
+        <v>9.01114749908447</v>
       </c>
       <c r="H602" t="n">
         <v>5400</v>
@@ -17885,7 +17885,7 @@
         <v>10.1000003814697</v>
       </c>
       <c r="G604" t="n">
-        <v>9.01114940643311</v>
+        <v>9.01114749908447</v>
       </c>
       <c r="H604" t="n">
         <v>69000</v>
@@ -17943,7 +17943,7 @@
         <v>10.1000003814697</v>
       </c>
       <c r="G606" t="n">
-        <v>9.01114940643311</v>
+        <v>9.01114749908447</v>
       </c>
       <c r="H606" t="n">
         <v>14000</v>
@@ -17972,7 +17972,7 @@
         <v>10.1000003814697</v>
       </c>
       <c r="G607" t="n">
-        <v>9.01114940643311</v>
+        <v>9.01114749908447</v>
       </c>
       <c r="H607" t="n">
         <v>21400</v>
@@ -18059,7 +18059,7 @@
         <v>10.1000003814697</v>
       </c>
       <c r="G610" t="n">
-        <v>9.01114940643311</v>
+        <v>9.01114749908447</v>
       </c>
       <c r="H610" t="n">
         <v>12600</v>
@@ -18117,7 +18117,7 @@
         <v>10.3000001907349</v>
       </c>
       <c r="G612" t="n">
-        <v>9.18958759307861</v>
+        <v>9.1895866394043</v>
       </c>
       <c r="H612" t="n">
         <v>24600</v>
@@ -18175,7 +18175,7 @@
         <v>10.3000001907349</v>
       </c>
       <c r="G614" t="n">
-        <v>9.18958759307861</v>
+        <v>9.1895866394043</v>
       </c>
       <c r="H614" t="n">
         <v>6800</v>
@@ -18262,7 +18262,7 @@
         <v>10.6999998092651</v>
       </c>
       <c r="G617" t="n">
-        <v>9.54646492004395</v>
+        <v>9.54646396636963</v>
       </c>
       <c r="H617" t="n">
         <v>33400</v>
@@ -18349,7 +18349,7 @@
         <v>10.6999998092651</v>
       </c>
       <c r="G620" t="n">
-        <v>9.54646492004395</v>
+        <v>9.54646396636963</v>
       </c>
       <c r="H620" t="n">
         <v>42400</v>
@@ -18378,7 +18378,7 @@
         <v>10.6999998092651</v>
       </c>
       <c r="G621" t="n">
-        <v>9.54646492004395</v>
+        <v>9.54646396636963</v>
       </c>
       <c r="H621" t="n">
         <v>23200</v>
@@ -18407,7 +18407,7 @@
         <v>10.6000003814697</v>
       </c>
       <c r="G622" t="n">
-        <v>9.45724582672119</v>
+        <v>9.45724487304688</v>
       </c>
       <c r="H622" t="n">
         <v>19200</v>
@@ -19016,7 +19016,7 @@
         <v>10.3000001907349</v>
       </c>
       <c r="G643" t="n">
-        <v>9.18958759307861</v>
+        <v>9.1895866394043</v>
       </c>
       <c r="H643" t="n">
         <v>13916</v>
@@ -19045,7 +19045,7 @@
         <v>10.3999996185303</v>
       </c>
       <c r="G644" t="n">
-        <v>9.36977577209473</v>
+        <v>9.36977481842041</v>
       </c>
       <c r="H644" t="n">
         <v>9716</v>
@@ -19103,7 +19103,7 @@
         <v>10.1000003814697</v>
       </c>
       <c r="G646" t="n">
-        <v>9.09949398040771</v>
+        <v>9.0994930267334</v>
       </c>
       <c r="H646" t="n">
         <v>3279</v>
@@ -19161,7 +19161,7 @@
         <v>10.1000003814697</v>
       </c>
       <c r="G648" t="n">
-        <v>9.09949398040771</v>
+        <v>9.0994930267334</v>
       </c>
       <c r="H648" t="n">
         <v>8142</v>
@@ -19335,7 +19335,7 @@
         <v>10.1000003814697</v>
       </c>
       <c r="G654" t="n">
-        <v>9.09949398040771</v>
+        <v>9.0994930267334</v>
       </c>
       <c r="H654" t="n">
         <v>20832</v>
@@ -19480,7 +19480,7 @@
         <v>10.1000003814697</v>
       </c>
       <c r="G659" t="n">
-        <v>9.09949398040771</v>
+        <v>9.0994930267334</v>
       </c>
       <c r="H659" t="n">
         <v>600</v>
@@ -19509,7 +19509,7 @@
         <v>10.1000003814697</v>
       </c>
       <c r="G660" t="n">
-        <v>9.09949398040771</v>
+        <v>9.0994930267334</v>
       </c>
       <c r="H660" t="n">
         <v>933</v>
@@ -19538,7 +19538,7 @@
         <v>10.1000003814697</v>
       </c>
       <c r="G661" t="n">
-        <v>9.09949398040771</v>
+        <v>9.0994930267334</v>
       </c>
       <c r="H661" t="n">
         <v>4319</v>
@@ -19596,7 +19596,7 @@
         <v>10.1000003814697</v>
       </c>
       <c r="G663" t="n">
-        <v>9.09949398040771</v>
+        <v>9.0994930267334</v>
       </c>
       <c r="H663" t="n">
         <v>12669</v>
@@ -19625,7 +19625,7 @@
         <v>10.1000003814697</v>
       </c>
       <c r="G664" t="n">
-        <v>9.09949398040771</v>
+        <v>9.0994930267334</v>
       </c>
       <c r="H664" t="n">
         <v>11554</v>
@@ -19654,7 +19654,7 @@
         <v>10.1000003814697</v>
       </c>
       <c r="G665" t="n">
-        <v>9.09949398040771</v>
+        <v>9.0994930267334</v>
       </c>
       <c r="H665" t="n">
         <v>9780</v>
@@ -19683,7 +19683,7 @@
         <v>10.1000003814697</v>
       </c>
       <c r="G666" t="n">
-        <v>9.09949398040771</v>
+        <v>9.0994930267334</v>
       </c>
       <c r="H666" t="n">
         <v>1066</v>
@@ -19712,7 +19712,7 @@
         <v>10.1000003814697</v>
       </c>
       <c r="G667" t="n">
-        <v>9.09949398040771</v>
+        <v>9.0994930267334</v>
       </c>
       <c r="H667" t="n">
         <v>3333</v>
@@ -19741,7 +19741,7 @@
         <v>10.1000003814697</v>
       </c>
       <c r="G668" t="n">
-        <v>9.09949398040771</v>
+        <v>9.0994930267334</v>
       </c>
       <c r="H668" t="n">
         <v>1001</v>
@@ -19799,7 +19799,7 @@
         <v>10.1000003814697</v>
       </c>
       <c r="G670" t="n">
-        <v>9.09949398040771</v>
+        <v>9.0994930267334</v>
       </c>
       <c r="H670" t="n">
         <v>1307</v>
@@ -19828,7 +19828,7 @@
         <v>10.1000003814697</v>
       </c>
       <c r="G671" t="n">
-        <v>9.09949398040771</v>
+        <v>9.0994930267334</v>
       </c>
       <c r="H671" t="n">
         <v>1333</v>
@@ -19915,7 +19915,7 @@
         <v>9.80000019073486</v>
       </c>
       <c r="G674" t="n">
-        <v>8.8292121887207</v>
+        <v>8.82921123504639</v>
       </c>
       <c r="H674" t="n">
         <v>41176</v>
@@ -20379,7 +20379,7 @@
         <v>10.1000003814697</v>
       </c>
       <c r="G690" t="n">
-        <v>9.09949398040771</v>
+        <v>9.0994930267334</v>
       </c>
       <c r="H690" t="n">
         <v>16801</v>
@@ -20408,7 +20408,7 @@
         <v>10.1000003814697</v>
       </c>
       <c r="G691" t="n">
-        <v>9.09949398040771</v>
+        <v>9.0994930267334</v>
       </c>
       <c r="H691" t="n">
         <v>350</v>
@@ -20495,7 +20495,7 @@
         <v>10.1000003814697</v>
       </c>
       <c r="G694" t="n">
-        <v>9.09949398040771</v>
+        <v>9.0994930267334</v>
       </c>
       <c r="H694" t="n">
         <v>610</v>
@@ -20524,7 +20524,7 @@
         <v>10.1000003814697</v>
       </c>
       <c r="G695" t="n">
-        <v>9.09949398040771</v>
+        <v>9.0994930267334</v>
       </c>
       <c r="H695" t="n">
         <v>1890</v>
@@ -21278,7 +21278,7 @@
         <v>10.1000003814697</v>
       </c>
       <c r="G721" t="n">
-        <v>9.09949398040771</v>
+        <v>9.0994930267334</v>
       </c>
       <c r="H721" t="n">
         <v>6432</v>
@@ -21336,7 +21336,7 @@
         <v>10.1000003814697</v>
       </c>
       <c r="G723" t="n">
-        <v>9.09949398040771</v>
+        <v>9.0994930267334</v>
       </c>
       <c r="H723" t="n">
         <v>1050</v>
@@ -21568,7 +21568,7 @@
         <v>10.1000003814697</v>
       </c>
       <c r="G731" t="n">
-        <v>9.09949398040771</v>
+        <v>9.0994930267334</v>
       </c>
       <c r="H731" t="n">
         <v>200</v>
@@ -21626,7 +21626,7 @@
         <v>10.1000003814697</v>
       </c>
       <c r="G733" t="n">
-        <v>9.09949398040771</v>
+        <v>9.0994930267334</v>
       </c>
       <c r="H733" t="n">
         <v>12534</v>
@@ -21655,7 +21655,7 @@
         <v>10.1000003814697</v>
       </c>
       <c r="G734" t="n">
-        <v>9.09949398040771</v>
+        <v>9.0994930267334</v>
       </c>
       <c r="H734" t="n">
         <v>850</v>
@@ -21916,7 +21916,7 @@
         <v>10.3999996185303</v>
       </c>
       <c r="G743" t="n">
-        <v>9.36977577209473</v>
+        <v>9.36977481842041</v>
       </c>
       <c r="H743" t="n">
         <v>5001</v>
@@ -22003,7 +22003,7 @@
         <v>10.1000003814697</v>
       </c>
       <c r="G746" t="n">
-        <v>9.09949398040771</v>
+        <v>9.0994930267334</v>
       </c>
       <c r="H746" t="n">
         <v>17350</v>
@@ -22148,7 +22148,7 @@
         <v>10.1000003814697</v>
       </c>
       <c r="G751" t="n">
-        <v>9.09949398040771</v>
+        <v>9.0994930267334</v>
       </c>
       <c r="H751" t="n">
         <v>2450</v>
@@ -22235,7 +22235,7 @@
         <v>10.3999996185303</v>
       </c>
       <c r="G754" t="n">
-        <v>9.36977577209473</v>
+        <v>9.36977481842041</v>
       </c>
       <c r="H754" t="n">
         <v>3043</v>
@@ -22264,7 +22264,7 @@
         <v>10.5</v>
       </c>
       <c r="G755" t="n">
-        <v>9.45986843109131</v>
+        <v>9.45986938476562</v>
       </c>
       <c r="H755" t="n">
         <v>109777</v>
@@ -22815,7 +22815,7 @@
         <v>10.8999996185303</v>
       </c>
       <c r="G774" t="n">
-        <v>9.82024478912354</v>
+        <v>9.82024383544922</v>
       </c>
       <c r="H774" t="n">
         <v>3936</v>
@@ -23134,7 +23134,7 @@
         <v>10.8999996185303</v>
       </c>
       <c r="G785" t="n">
-        <v>9.82024478912354</v>
+        <v>9.82024383544922</v>
       </c>
       <c r="H785" t="n">
         <v>5615</v>
@@ -23163,7 +23163,7 @@
         <v>10.8999996185303</v>
       </c>
       <c r="G786" t="n">
-        <v>9.82024478912354</v>
+        <v>9.82024383544922</v>
       </c>
       <c r="H786" t="n">
         <v>6113</v>
@@ -23192,7 +23192,7 @@
         <v>10.8999996185303</v>
       </c>
       <c r="G787" t="n">
-        <v>9.82024478912354</v>
+        <v>9.82024383544922</v>
       </c>
       <c r="H787" t="n">
         <v>12682</v>
@@ -23337,7 +23337,7 @@
         <v>11.3000001907349</v>
       </c>
       <c r="G792" t="n">
-        <v>10.1806221008301</v>
+        <v>10.1806211471558</v>
       </c>
       <c r="H792" t="n">
         <v>45707</v>
@@ -23424,7 +23424,7 @@
         <v>11.3000001907349</v>
       </c>
       <c r="G795" t="n">
-        <v>10.1806221008301</v>
+        <v>10.1806211471558</v>
       </c>
       <c r="H795" t="n">
         <v>71299</v>
@@ -23453,7 +23453,7 @@
         <v>11.5</v>
       </c>
       <c r="G796" t="n">
-        <v>10.3608093261719</v>
+        <v>10.3608102798462</v>
       </c>
       <c r="H796" t="n">
         <v>50499</v>
@@ -23511,7 +23511,7 @@
         <v>11.5</v>
       </c>
       <c r="G798" t="n">
-        <v>10.3608093261719</v>
+        <v>10.3608102798462</v>
       </c>
       <c r="H798" t="n">
         <v>57131</v>
@@ -23569,7 +23569,7 @@
         <v>11.8000001907349</v>
       </c>
       <c r="G800" t="n">
-        <v>10.6310920715332</v>
+        <v>10.6310930252075</v>
       </c>
       <c r="H800" t="n">
         <v>49722</v>
@@ -23627,7 +23627,7 @@
         <v>11.8000001907349</v>
       </c>
       <c r="G802" t="n">
-        <v>10.6310920715332</v>
+        <v>10.6310930252075</v>
       </c>
       <c r="H802" t="n">
         <v>46365</v>
@@ -23656,7 +23656,7 @@
         <v>11.8000001907349</v>
       </c>
       <c r="G803" t="n">
-        <v>10.6310920715332</v>
+        <v>10.6310930252075</v>
       </c>
       <c r="H803" t="n">
         <v>22026</v>
@@ -23685,7 +23685,7 @@
         <v>11.8000001907349</v>
       </c>
       <c r="G804" t="n">
-        <v>10.6310920715332</v>
+        <v>10.6310930252075</v>
       </c>
       <c r="H804" t="n">
         <v>22008</v>
@@ -23743,7 +23743,7 @@
         <v>11.8000001907349</v>
       </c>
       <c r="G806" t="n">
-        <v>10.6310920715332</v>
+        <v>10.6310930252075</v>
       </c>
       <c r="H806" t="n">
         <v>10733</v>
@@ -23859,7 +23859,7 @@
         <v>12</v>
       </c>
       <c r="G810" t="n">
-        <v>10.8112802505493</v>
+        <v>10.8112783432007</v>
       </c>
       <c r="H810" t="n">
         <v>111993</v>
@@ -23888,7 +23888,7 @@
         <v>12</v>
       </c>
       <c r="G811" t="n">
-        <v>10.8112802505493</v>
+        <v>10.8112783432007</v>
       </c>
       <c r="H811" t="n">
         <v>17424</v>
@@ -24004,7 +24004,7 @@
         <v>12</v>
       </c>
       <c r="G815" t="n">
-        <v>10.8112802505493</v>
+        <v>10.8112783432007</v>
       </c>
       <c r="H815" t="n">
         <v>147502</v>
@@ -24091,7 +24091,7 @@
         <v>12.1999998092651</v>
       </c>
       <c r="G818" t="n">
-        <v>10.9914684295654</v>
+        <v>10.9914665222168</v>
       </c>
       <c r="H818" t="n">
         <v>28509</v>
@@ -24120,7 +24120,7 @@
         <v>12.1999998092651</v>
       </c>
       <c r="G819" t="n">
-        <v>10.9914684295654</v>
+        <v>10.9914665222168</v>
       </c>
       <c r="H819" t="n">
         <v>3696</v>
@@ -24149,7 +24149,7 @@
         <v>12</v>
       </c>
       <c r="G820" t="n">
-        <v>10.8112802505493</v>
+        <v>10.8112783432007</v>
       </c>
       <c r="H820" t="n">
         <v>37372</v>
@@ -24178,7 +24178,7 @@
         <v>12</v>
       </c>
       <c r="G821" t="n">
-        <v>10.8112802505493</v>
+        <v>10.8112783432007</v>
       </c>
       <c r="H821" t="n">
         <v>20396</v>
@@ -24236,7 +24236,7 @@
         <v>12.3000001907349</v>
       </c>
       <c r="G823" t="n">
-        <v>11.081561088562</v>
+        <v>11.0815629959106</v>
       </c>
       <c r="H823" t="n">
         <v>13559</v>
@@ -24265,7 +24265,7 @@
         <v>12.1999998092651</v>
       </c>
       <c r="G824" t="n">
-        <v>10.9914684295654</v>
+        <v>10.9914665222168</v>
       </c>
       <c r="H824" t="n">
         <v>30353</v>
@@ -24294,7 +24294,7 @@
         <v>12.3000001907349</v>
       </c>
       <c r="G825" t="n">
-        <v>11.081561088562</v>
+        <v>11.0815629959106</v>
       </c>
       <c r="H825" t="n">
         <v>56143</v>
@@ -24323,7 +24323,7 @@
         <v>12.1999998092651</v>
       </c>
       <c r="G826" t="n">
-        <v>10.9914684295654</v>
+        <v>10.9914665222168</v>
       </c>
       <c r="H826" t="n">
         <v>14080</v>
@@ -24381,7 +24381,7 @@
         <v>12</v>
       </c>
       <c r="G828" t="n">
-        <v>10.8112802505493</v>
+        <v>10.8112783432007</v>
       </c>
       <c r="H828" t="n">
         <v>31355</v>
@@ -24410,7 +24410,7 @@
         <v>12.3000001907349</v>
       </c>
       <c r="G829" t="n">
-        <v>11.081561088562</v>
+        <v>11.0815629959106</v>
       </c>
       <c r="H829" t="n">
         <v>13811</v>
@@ -24439,7 +24439,7 @@
         <v>12.1999998092651</v>
       </c>
       <c r="G830" t="n">
-        <v>10.9914684295654</v>
+        <v>10.9914665222168</v>
       </c>
       <c r="H830" t="n">
         <v>14447</v>
@@ -24468,7 +24468,7 @@
         <v>12.3000001907349</v>
       </c>
       <c r="G831" t="n">
-        <v>11.081561088562</v>
+        <v>11.0815629959106</v>
       </c>
       <c r="H831" t="n">
         <v>4605</v>
@@ -24497,7 +24497,7 @@
         <v>12.1999998092651</v>
       </c>
       <c r="G832" t="n">
-        <v>10.9914684295654</v>
+        <v>10.9914665222168</v>
       </c>
       <c r="H832" t="n">
         <v>1958</v>
@@ -24526,7 +24526,7 @@
         <v>12.1999998092651</v>
       </c>
       <c r="G833" t="n">
-        <v>10.9914684295654</v>
+        <v>10.9914665222168</v>
       </c>
       <c r="H833" t="n">
         <v>19330</v>
@@ -24555,7 +24555,7 @@
         <v>12.1999998092651</v>
       </c>
       <c r="G834" t="n">
-        <v>10.9914684295654</v>
+        <v>10.9914665222168</v>
       </c>
       <c r="H834" t="n">
         <v>11083</v>
@@ -24584,7 +24584,7 @@
         <v>12.1999998092651</v>
       </c>
       <c r="G835" t="n">
-        <v>10.9914684295654</v>
+        <v>10.9914665222168</v>
       </c>
       <c r="H835" t="n">
         <v>10809</v>
@@ -24613,7 +24613,7 @@
         <v>12.3000001907349</v>
       </c>
       <c r="G836" t="n">
-        <v>11.081561088562</v>
+        <v>11.0815629959106</v>
       </c>
       <c r="H836" t="n">
         <v>4238</v>
@@ -24671,7 +24671,7 @@
         <v>12.3000001907349</v>
       </c>
       <c r="G838" t="n">
-        <v>11.081561088562</v>
+        <v>11.0815629959106</v>
       </c>
       <c r="H838" t="n">
         <v>9765</v>
@@ -24700,7 +24700,7 @@
         <v>12.1999998092651</v>
       </c>
       <c r="G839" t="n">
-        <v>10.9914684295654</v>
+        <v>10.9914665222168</v>
       </c>
       <c r="H839" t="n">
         <v>7897</v>
@@ -24729,7 +24729,7 @@
         <v>12.3000001907349</v>
       </c>
       <c r="G840" t="n">
-        <v>11.081561088562</v>
+        <v>11.0815629959106</v>
       </c>
       <c r="H840" t="n">
         <v>23765</v>
@@ -24758,7 +24758,7 @@
         <v>12.3999996185303</v>
       </c>
       <c r="G841" t="n">
-        <v>11.1716547012329</v>
+        <v>11.1716556549072</v>
       </c>
       <c r="H841" t="n">
         <v>40850</v>
@@ -24787,7 +24787,7 @@
         <v>12.3000001907349</v>
       </c>
       <c r="G842" t="n">
-        <v>11.081561088562</v>
+        <v>11.0815629959106</v>
       </c>
       <c r="H842" t="n">
         <v>14735</v>
@@ -24816,7 +24816,7 @@
         <v>12.3000001907349</v>
       </c>
       <c r="G843" t="n">
-        <v>11.081561088562</v>
+        <v>11.0815629959106</v>
       </c>
       <c r="H843" t="n">
         <v>23374</v>
@@ -24845,7 +24845,7 @@
         <v>12.3000001907349</v>
       </c>
       <c r="G844" t="n">
-        <v>11.081561088562</v>
+        <v>11.0815629959106</v>
       </c>
       <c r="H844" t="n">
         <v>1714</v>
@@ -24874,7 +24874,7 @@
         <v>12.1999998092651</v>
       </c>
       <c r="G845" t="n">
-        <v>10.9914684295654</v>
+        <v>10.9914665222168</v>
       </c>
       <c r="H845" t="n">
         <v>6045</v>
@@ -24932,7 +24932,7 @@
         <v>12.1999998092651</v>
       </c>
       <c r="G847" t="n">
-        <v>10.9914684295654</v>
+        <v>10.9914665222168</v>
       </c>
       <c r="H847" t="n">
         <v>16080</v>
@@ -24961,7 +24961,7 @@
         <v>12</v>
       </c>
       <c r="G848" t="n">
-        <v>10.8112802505493</v>
+        <v>10.8112783432007</v>
       </c>
       <c r="H848" t="n">
         <v>19006</v>
@@ -25019,7 +25019,7 @@
         <v>11.8000001907349</v>
       </c>
       <c r="G850" t="n">
-        <v>10.6310920715332</v>
+        <v>10.6310930252075</v>
       </c>
       <c r="H850" t="n">
         <v>111180</v>
@@ -25048,7 +25048,7 @@
         <v>11.8000001907349</v>
       </c>
       <c r="G851" t="n">
-        <v>10.6310920715332</v>
+        <v>10.6310930252075</v>
       </c>
       <c r="H851" t="n">
         <v>21012</v>
@@ -25106,7 +25106,7 @@
         <v>11.5</v>
       </c>
       <c r="G853" t="n">
-        <v>10.3608093261719</v>
+        <v>10.3608102798462</v>
       </c>
       <c r="H853" t="n">
         <v>19258</v>
@@ -25135,7 +25135,7 @@
         <v>11.3000001907349</v>
       </c>
       <c r="G854" t="n">
-        <v>10.1806221008301</v>
+        <v>10.1806211471558</v>
       </c>
       <c r="H854" t="n">
         <v>13640</v>
@@ -25164,7 +25164,7 @@
         <v>11.3999996185303</v>
       </c>
       <c r="G855" t="n">
-        <v>10.270715713501</v>
+        <v>10.2707147598267</v>
       </c>
       <c r="H855" t="n">
         <v>6144</v>
@@ -25251,7 +25251,7 @@
         <v>10.6000003814697</v>
       </c>
       <c r="G858" t="n">
-        <v>9.54996395111084</v>
+        <v>9.54996299743652</v>
       </c>
       <c r="H858" t="n">
         <v>32468</v>
@@ -25280,7 +25280,7 @@
         <v>10.1000003814697</v>
       </c>
       <c r="G859" t="n">
-        <v>9.09949398040771</v>
+        <v>9.0994930267334</v>
       </c>
       <c r="H859" t="n">
         <v>21455</v>
@@ -25367,7 +25367,7 @@
         <v>9.60000038146973</v>
       </c>
       <c r="G862" t="n">
-        <v>8.64902400970459</v>
+        <v>8.64902305603027</v>
       </c>
       <c r="H862" t="n">
         <v>13499</v>
@@ -25425,7 +25425,7 @@
         <v>9</v>
       </c>
       <c r="G864" t="n">
-        <v>8.10845851898193</v>
+        <v>8.10845947265625</v>
       </c>
       <c r="H864" t="n">
         <v>14181</v>
@@ -25454,7 +25454,7 @@
         <v>9</v>
       </c>
       <c r="G865" t="n">
-        <v>8.10845851898193</v>
+        <v>8.10845947265625</v>
       </c>
       <c r="H865" t="n">
         <v>19428</v>
@@ -25599,7 +25599,7 @@
         <v>10.1000003814697</v>
       </c>
       <c r="G870" t="n">
-        <v>9.09949398040771</v>
+        <v>9.0994930267334</v>
       </c>
       <c r="H870" t="n">
         <v>6877</v>
@@ -25628,7 +25628,7 @@
         <v>10.5</v>
       </c>
       <c r="G871" t="n">
-        <v>9.45986843109131</v>
+        <v>9.45986938476562</v>
       </c>
       <c r="H871" t="n">
         <v>4639</v>
@@ -25773,7 +25773,7 @@
         <v>10.1000003814697</v>
       </c>
       <c r="G876" t="n">
-        <v>9.09949398040771</v>
+        <v>9.0994930267334</v>
       </c>
       <c r="H876" t="n">
         <v>16782</v>
@@ -25802,7 +25802,7 @@
         <v>10.0500001907349</v>
       </c>
       <c r="G877" t="n">
-        <v>9.05444717407227</v>
+        <v>9.05444622039795</v>
       </c>
       <c r="H877" t="n">
         <v>11800</v>
@@ -25831,7 +25831,7 @@
         <v>10.1499996185303</v>
       </c>
       <c r="G878" t="n">
-        <v>9.14454078674316</v>
+        <v>9.14453983306885</v>
       </c>
       <c r="H878" t="n">
         <v>1300</v>
@@ -25947,7 +25947,7 @@
         <v>10.25</v>
       </c>
       <c r="G882" t="n">
-        <v>9.23463439941406</v>
+        <v>9.23463344573975</v>
       </c>
       <c r="H882" t="n">
         <v>9917</v>
@@ -25976,7 +25976,7 @@
         <v>10.5</v>
       </c>
       <c r="G883" t="n">
-        <v>9.45986843109131</v>
+        <v>9.45986938476562</v>
       </c>
       <c r="H883" t="n">
         <v>18374</v>
@@ -26005,7 +26005,7 @@
         <v>10.6000003814697</v>
       </c>
       <c r="G884" t="n">
-        <v>9.54996395111084</v>
+        <v>9.54996299743652</v>
       </c>
       <c r="H884" t="n">
         <v>8101</v>
@@ -26150,7 +26150,7 @@
         <v>10.5500001907349</v>
       </c>
       <c r="G889" t="n">
-        <v>9.50491714477539</v>
+        <v>9.50491619110107</v>
       </c>
       <c r="H889" t="n">
         <v>1500</v>
@@ -26179,7 +26179,7 @@
         <v>10.6000003814697</v>
       </c>
       <c r="G890" t="n">
-        <v>9.54996395111084</v>
+        <v>9.54996299743652</v>
       </c>
       <c r="H890" t="n">
         <v>450</v>
@@ -26208,7 +26208,7 @@
         <v>10.4499998092651</v>
       </c>
       <c r="G891" t="n">
-        <v>9.41482257843018</v>
+        <v>9.41482162475586</v>
       </c>
       <c r="H891" t="n">
         <v>658</v>
@@ -26237,7 +26237,7 @@
         <v>10.4499998092651</v>
       </c>
       <c r="G892" t="n">
-        <v>9.41482257843018</v>
+        <v>9.41482162475586</v>
       </c>
       <c r="H892" t="n">
         <v>9150</v>
@@ -26266,7 +26266,7 @@
         <v>10.6000003814697</v>
       </c>
       <c r="G893" t="n">
-        <v>9.54996395111084</v>
+        <v>9.54996299743652</v>
       </c>
       <c r="H893" t="n">
         <v>1843</v>
@@ -26353,7 +26353,7 @@
         <v>10.6000003814697</v>
       </c>
       <c r="G896" t="n">
-        <v>9.54996395111084</v>
+        <v>9.54996299743652</v>
       </c>
       <c r="H896" t="n">
         <v>1484</v>
@@ -26382,7 +26382,7 @@
         <v>10.9499998092651</v>
       </c>
       <c r="G897" t="n">
-        <v>9.86529159545898</v>
+        <v>9.8652925491333</v>
       </c>
       <c r="H897" t="n">
         <v>3575</v>
@@ -26411,7 +26411,7 @@
         <v>10.8500003814697</v>
       </c>
       <c r="G898" t="n">
-        <v>9.7751989364624</v>
+        <v>9.77519989013672</v>
       </c>
       <c r="H898" t="n">
         <v>18584</v>
@@ -26440,7 +26440,7 @@
         <v>10.5</v>
       </c>
       <c r="G899" t="n">
-        <v>9.45986843109131</v>
+        <v>9.45986938476562</v>
       </c>
       <c r="H899" t="n">
         <v>2580</v>
@@ -26498,7 +26498,7 @@
         <v>10.6000003814697</v>
       </c>
       <c r="G901" t="n">
-        <v>9.65828227996826</v>
+        <v>9.65828132629395</v>
       </c>
       <c r="H901" t="n">
         <v>2022</v>
@@ -26527,7 +26527,7 @@
         <v>10.5</v>
       </c>
       <c r="G902" t="n">
-        <v>9.56716442108154</v>
+        <v>9.56716537475586</v>
       </c>
       <c r="H902" t="n">
         <v>8060</v>
@@ -26556,7 +26556,7 @@
         <v>10.3500003814697</v>
       </c>
       <c r="G903" t="n">
-        <v>9.43049049377441</v>
+        <v>9.43049144744873</v>
       </c>
       <c r="H903" t="n">
         <v>36431</v>
@@ -26585,7 +26585,7 @@
         <v>10.75</v>
       </c>
       <c r="G904" t="n">
-        <v>9.79495525360107</v>
+        <v>9.79495429992676</v>
       </c>
       <c r="H904" t="n">
         <v>758</v>
@@ -26614,7 +26614,7 @@
         <v>10.6999998092651</v>
       </c>
       <c r="G905" t="n">
-        <v>9.74939823150635</v>
+        <v>9.7493953704834</v>
       </c>
       <c r="H905" t="n">
         <v>1830</v>
@@ -26643,7 +26643,7 @@
         <v>10.6000003814697</v>
       </c>
       <c r="G906" t="n">
-        <v>9.65828227996826</v>
+        <v>9.65828132629395</v>
       </c>
       <c r="H906" t="n">
         <v>360</v>
@@ -26701,7 +26701,7 @@
         <v>10.8000001907349</v>
       </c>
       <c r="G908" t="n">
-        <v>9.84051322937012</v>
+        <v>9.8405122756958</v>
       </c>
       <c r="H908" t="n">
         <v>4550</v>
@@ -26730,7 +26730,7 @@
         <v>10.8000001907349</v>
       </c>
       <c r="G909" t="n">
-        <v>9.84051322937012</v>
+        <v>9.8405122756958</v>
       </c>
       <c r="H909" t="n">
         <v>238</v>
@@ -26759,7 +26759,7 @@
         <v>10.8000001907349</v>
       </c>
       <c r="G910" t="n">
-        <v>9.84051322937012</v>
+        <v>9.8405122756958</v>
       </c>
       <c r="H910" t="n">
         <v>2050</v>
@@ -26788,7 +26788,7 @@
         <v>10.8999996185303</v>
       </c>
       <c r="G911" t="n">
-        <v>9.93162822723389</v>
+        <v>9.93162727355957</v>
       </c>
       <c r="H911" t="n">
         <v>2924</v>
@@ -26817,7 +26817,7 @@
         <v>10.8999996185303</v>
       </c>
       <c r="G912" t="n">
-        <v>9.93162822723389</v>
+        <v>9.93162727355957</v>
       </c>
       <c r="H912" t="n">
         <v>1808</v>
@@ -26846,7 +26846,7 @@
         <v>10.8999996185303</v>
       </c>
       <c r="G913" t="n">
-        <v>9.93162822723389</v>
+        <v>9.93162727355957</v>
       </c>
       <c r="H913" t="n">
         <v>4730</v>
@@ -26875,7 +26875,7 @@
         <v>10.9499998092651</v>
       </c>
       <c r="G914" t="n">
-        <v>9.97718620300293</v>
+        <v>9.97718524932861</v>
       </c>
       <c r="H914" t="n">
         <v>11302</v>
@@ -26904,7 +26904,7 @@
         <v>10.8999996185303</v>
       </c>
       <c r="G915" t="n">
-        <v>9.93162822723389</v>
+        <v>9.93162727355957</v>
       </c>
       <c r="H915" t="n">
         <v>706</v>
@@ -26933,7 +26933,7 @@
         <v>10.9499998092651</v>
       </c>
       <c r="G916" t="n">
-        <v>9.97718620300293</v>
+        <v>9.97718524932861</v>
       </c>
       <c r="H916" t="n">
         <v>143</v>
@@ -26962,7 +26962,7 @@
         <v>11</v>
       </c>
       <c r="G917" t="n">
-        <v>10.0227451324463</v>
+        <v>10.022744178772</v>
       </c>
       <c r="H917" t="n">
         <v>3783</v>
@@ -26991,7 +26991,7 @@
         <v>10.8999996185303</v>
       </c>
       <c r="G918" t="n">
-        <v>9.93162822723389</v>
+        <v>9.93162727355957</v>
       </c>
       <c r="H918" t="n">
         <v>7283</v>
@@ -27020,7 +27020,7 @@
         <v>10.8000001907349</v>
       </c>
       <c r="G919" t="n">
-        <v>9.84051322937012</v>
+        <v>9.8405122756958</v>
       </c>
       <c r="H919" t="n">
         <v>899</v>
@@ -27078,7 +27078,7 @@
         <v>10.5</v>
       </c>
       <c r="G921" t="n">
-        <v>9.56716442108154</v>
+        <v>9.56716537475586</v>
       </c>
       <c r="H921" t="n">
         <v>15128</v>
@@ -27107,7 +27107,7 @@
         <v>10.75</v>
       </c>
       <c r="G922" t="n">
-        <v>9.79495525360107</v>
+        <v>9.79495429992676</v>
       </c>
       <c r="H922" t="n">
         <v>33283</v>
@@ -27136,7 +27136,7 @@
         <v>10.75</v>
       </c>
       <c r="G923" t="n">
-        <v>9.79495525360107</v>
+        <v>9.79495429992676</v>
       </c>
       <c r="H923" t="n">
         <v>26805</v>
@@ -27165,7 +27165,7 @@
         <v>10.6999998092651</v>
       </c>
       <c r="G924" t="n">
-        <v>9.74939823150635</v>
+        <v>9.7493953704834</v>
       </c>
       <c r="H924" t="n">
         <v>925</v>
@@ -27194,7 +27194,7 @@
         <v>10.6999998092651</v>
       </c>
       <c r="G925" t="n">
-        <v>9.74939823150635</v>
+        <v>9.7493953704834</v>
       </c>
       <c r="H925" t="n">
         <v>7560</v>
@@ -27223,7 +27223,7 @@
         <v>10.75</v>
       </c>
       <c r="G926" t="n">
-        <v>9.79495525360107</v>
+        <v>9.79495429992676</v>
       </c>
       <c r="H926" t="n">
         <v>2330</v>
@@ -27252,7 +27252,7 @@
         <v>11</v>
       </c>
       <c r="G927" t="n">
-        <v>10.0227451324463</v>
+        <v>10.022744178772</v>
       </c>
       <c r="H927" t="n">
         <v>6753</v>
@@ -27281,7 +27281,7 @@
         <v>10.9499998092651</v>
       </c>
       <c r="G928" t="n">
-        <v>9.97718620300293</v>
+        <v>9.97718524932861</v>
       </c>
       <c r="H928" t="n">
         <v>502</v>
@@ -27310,7 +27310,7 @@
         <v>10.9499998092651</v>
       </c>
       <c r="G929" t="n">
-        <v>9.97718620300293</v>
+        <v>9.97718524932861</v>
       </c>
       <c r="H929" t="n">
         <v>1290</v>
@@ -27339,7 +27339,7 @@
         <v>11</v>
       </c>
       <c r="G930" t="n">
-        <v>10.0227451324463</v>
+        <v>10.022744178772</v>
       </c>
       <c r="H930" t="n">
         <v>8307</v>
@@ -27368,7 +27368,7 @@
         <v>10.8999996185303</v>
       </c>
       <c r="G931" t="n">
-        <v>9.93162822723389</v>
+        <v>9.93162727355957</v>
       </c>
       <c r="H931" t="n">
         <v>8316</v>
@@ -27397,7 +27397,7 @@
         <v>10.8999996185303</v>
       </c>
       <c r="G932" t="n">
-        <v>9.93162822723389</v>
+        <v>9.93162727355957</v>
       </c>
       <c r="H932" t="n">
         <v>4203</v>
@@ -27426,7 +27426,7 @@
         <v>10.8999996185303</v>
       </c>
       <c r="G933" t="n">
-        <v>9.93162822723389</v>
+        <v>9.93162727355957</v>
       </c>
       <c r="H933" t="n">
         <v>1219</v>
@@ -27455,7 +27455,7 @@
         <v>10.8999996185303</v>
       </c>
       <c r="G934" t="n">
-        <v>9.93162822723389</v>
+        <v>9.93162727355957</v>
       </c>
       <c r="H934" t="n">
         <v>5600</v>
@@ -27484,7 +27484,7 @@
         <v>10.8999996185303</v>
       </c>
       <c r="G935" t="n">
-        <v>9.93162822723389</v>
+        <v>9.93162727355957</v>
       </c>
       <c r="H935" t="n">
         <v>3105</v>
@@ -27513,7 +27513,7 @@
         <v>10.8999996185303</v>
       </c>
       <c r="G936" t="n">
-        <v>9.93162822723389</v>
+        <v>9.93162727355957</v>
       </c>
       <c r="H936" t="n">
         <v>0</v>
@@ -27542,7 +27542,7 @@
         <v>10.8999996185303</v>
       </c>
       <c r="G937" t="n">
-        <v>9.93162822723389</v>
+        <v>9.93162727355957</v>
       </c>
       <c r="H937" t="n">
         <v>47</v>
@@ -27571,7 +27571,7 @@
         <v>10.8000001907349</v>
       </c>
       <c r="G938" t="n">
-        <v>9.84051322937012</v>
+        <v>9.8405122756958</v>
       </c>
       <c r="H938" t="n">
         <v>1861</v>
@@ -27600,7 +27600,7 @@
         <v>10.8000001907349</v>
       </c>
       <c r="G939" t="n">
-        <v>9.84051322937012</v>
+        <v>9.8405122756958</v>
       </c>
       <c r="H939" t="n">
         <v>472</v>
@@ -27629,7 +27629,7 @@
         <v>10.8000001907349</v>
       </c>
       <c r="G940" t="n">
-        <v>9.84051322937012</v>
+        <v>9.8405122756958</v>
       </c>
       <c r="H940" t="n">
         <v>357</v>
@@ -27658,7 +27658,7 @@
         <v>10.6999998092651</v>
       </c>
       <c r="G941" t="n">
-        <v>9.74939823150635</v>
+        <v>9.7493953704834</v>
       </c>
       <c r="H941" t="n">
         <v>286</v>
@@ -27687,7 +27687,7 @@
         <v>10.6000003814697</v>
       </c>
       <c r="G942" t="n">
-        <v>9.65828227996826</v>
+        <v>9.65828132629395</v>
       </c>
       <c r="H942" t="n">
         <v>311</v>
@@ -27716,7 +27716,7 @@
         <v>10.6499996185303</v>
       </c>
       <c r="G943" t="n">
-        <v>9.70383930206299</v>
+        <v>9.70383834838867</v>
       </c>
       <c r="H943" t="n">
         <v>2750</v>
@@ -27745,7 +27745,7 @@
         <v>10.6000003814697</v>
       </c>
       <c r="G944" t="n">
-        <v>9.65828227996826</v>
+        <v>9.65828132629395</v>
       </c>
       <c r="H944" t="n">
         <v>869</v>
@@ -27774,7 +27774,7 @@
         <v>10.6499996185303</v>
       </c>
       <c r="G945" t="n">
-        <v>9.70383930206299</v>
+        <v>9.70383834838867</v>
       </c>
       <c r="H945" t="n">
         <v>1750</v>
@@ -27803,7 +27803,7 @@
         <v>10.8000001907349</v>
       </c>
       <c r="G946" t="n">
-        <v>9.84051322937012</v>
+        <v>9.8405122756958</v>
       </c>
       <c r="H946" t="n">
         <v>5337</v>
@@ -27832,7 +27832,7 @@
         <v>10.9499998092651</v>
       </c>
       <c r="G947" t="n">
-        <v>9.97718620300293</v>
+        <v>9.97718524932861</v>
       </c>
       <c r="H947" t="n">
         <v>59288</v>
@@ -27861,7 +27861,7 @@
         <v>10.8999996185303</v>
       </c>
       <c r="G948" t="n">
-        <v>9.93162822723389</v>
+        <v>9.93162727355957</v>
       </c>
       <c r="H948" t="n">
         <v>28960</v>
@@ -27890,7 +27890,7 @@
         <v>10.8500003814697</v>
       </c>
       <c r="G949" t="n">
-        <v>9.88607120513916</v>
+        <v>9.88607025146484</v>
       </c>
       <c r="H949" t="n">
         <v>1399</v>
@@ -28006,7 +28006,7 @@
         <v>11.0500001907349</v>
       </c>
       <c r="G953" t="n">
-        <v>10.0683040618896</v>
+        <v>10.068302154541</v>
       </c>
       <c r="H953" t="n">
         <v>31606</v>
@@ -28035,7 +28035,7 @@
         <v>11.1999998092651</v>
       </c>
       <c r="G954" t="n">
-        <v>10.2049760818481</v>
+        <v>10.2049751281738</v>
       </c>
       <c r="H954" t="n">
         <v>18997</v>
@@ -28093,7 +28093,7 @@
         <v>11.0500001907349</v>
       </c>
       <c r="G956" t="n">
-        <v>10.0683040618896</v>
+        <v>10.068302154541</v>
       </c>
       <c r="H956" t="n">
         <v>282</v>
@@ -28180,7 +28180,7 @@
         <v>11</v>
       </c>
       <c r="G959" t="n">
-        <v>10.0227451324463</v>
+        <v>10.022744178772</v>
       </c>
       <c r="H959" t="n">
         <v>365</v>
@@ -28238,7 +28238,7 @@
         <v>11.1999998092651</v>
       </c>
       <c r="G961" t="n">
-        <v>10.2049760818481</v>
+        <v>10.2049751281738</v>
       </c>
       <c r="H961" t="n">
         <v>5288</v>
@@ -28296,7 +28296,7 @@
         <v>11.1999998092651</v>
       </c>
       <c r="G963" t="n">
-        <v>10.2049760818481</v>
+        <v>10.2049751281738</v>
       </c>
       <c r="H963" t="n">
         <v>8124</v>
@@ -28325,7 +28325,7 @@
         <v>11.1999998092651</v>
       </c>
       <c r="G964" t="n">
-        <v>10.2049760818481</v>
+        <v>10.2049751281738</v>
       </c>
       <c r="H964" t="n">
         <v>236</v>
@@ -28354,7 +28354,7 @@
         <v>11.1999998092651</v>
       </c>
       <c r="G965" t="n">
-        <v>10.2049760818481</v>
+        <v>10.2049751281738</v>
       </c>
       <c r="H965" t="n">
         <v>10203</v>
@@ -28383,7 +28383,7 @@
         <v>11.1999998092651</v>
       </c>
       <c r="G966" t="n">
-        <v>10.2049760818481</v>
+        <v>10.2049751281738</v>
       </c>
       <c r="H966" t="n">
         <v>547</v>
@@ -28470,7 +28470,7 @@
         <v>11</v>
       </c>
       <c r="G969" t="n">
-        <v>10.0227451324463</v>
+        <v>10.022744178772</v>
       </c>
       <c r="H969" t="n">
         <v>378</v>
@@ -28499,7 +28499,7 @@
         <v>11</v>
       </c>
       <c r="G970" t="n">
-        <v>10.0227451324463</v>
+        <v>10.022744178772</v>
       </c>
       <c r="H970" t="n">
         <v>1280</v>
@@ -28528,7 +28528,7 @@
         <v>11</v>
       </c>
       <c r="G971" t="n">
-        <v>10.0227451324463</v>
+        <v>10.022744178772</v>
       </c>
       <c r="H971" t="n">
         <v>210</v>
@@ -28557,7 +28557,7 @@
         <v>11</v>
       </c>
       <c r="G972" t="n">
-        <v>10.0227451324463</v>
+        <v>10.022744178772</v>
       </c>
       <c r="H972" t="n">
         <v>0</v>
@@ -28586,7 +28586,7 @@
         <v>11</v>
       </c>
       <c r="G973" t="n">
-        <v>10.0227451324463</v>
+        <v>10.022744178772</v>
       </c>
       <c r="H973" t="n">
         <v>850</v>
@@ -28615,7 +28615,7 @@
         <v>10.9499998092651</v>
       </c>
       <c r="G974" t="n">
-        <v>9.97718620300293</v>
+        <v>9.97718524932861</v>
       </c>
       <c r="H974" t="n">
         <v>900</v>
@@ -28644,7 +28644,7 @@
         <v>11</v>
       </c>
       <c r="G975" t="n">
-        <v>10.0227451324463</v>
+        <v>10.022744178772</v>
       </c>
       <c r="H975" t="n">
         <v>2587</v>
@@ -28760,7 +28760,7 @@
         <v>11</v>
       </c>
       <c r="G979" t="n">
-        <v>10.0227451324463</v>
+        <v>10.022744178772</v>
       </c>
       <c r="H979" t="n">
         <v>4140</v>
@@ -28789,7 +28789,7 @@
         <v>11</v>
       </c>
       <c r="G980" t="n">
-        <v>10.0227451324463</v>
+        <v>10.022744178772</v>
       </c>
       <c r="H980" t="n">
         <v>254</v>
@@ -28818,7 +28818,7 @@
         <v>11</v>
       </c>
       <c r="G981" t="n">
-        <v>10.0227451324463</v>
+        <v>10.022744178772</v>
       </c>
       <c r="H981" t="n">
         <v>1383</v>
@@ -28847,7 +28847,7 @@
         <v>10.9499998092651</v>
       </c>
       <c r="G982" t="n">
-        <v>9.97718620300293</v>
+        <v>9.97718524932861</v>
       </c>
       <c r="H982" t="n">
         <v>4050</v>
@@ -28876,7 +28876,7 @@
         <v>10.9499998092651</v>
       </c>
       <c r="G983" t="n">
-        <v>9.97718620300293</v>
+        <v>9.97718524932861</v>
       </c>
       <c r="H983" t="n">
         <v>2157</v>
@@ -28905,7 +28905,7 @@
         <v>10.9499998092651</v>
       </c>
       <c r="G984" t="n">
-        <v>9.97718620300293</v>
+        <v>9.97718524932861</v>
       </c>
       <c r="H984" t="n">
         <v>0</v>
@@ -28934,7 +28934,7 @@
         <v>10.9499998092651</v>
       </c>
       <c r="G985" t="n">
-        <v>9.97718620300293</v>
+        <v>9.97718524932861</v>
       </c>
       <c r="H985" t="n">
         <v>3713</v>
@@ -28963,7 +28963,7 @@
         <v>10.8999996185303</v>
       </c>
       <c r="G986" t="n">
-        <v>9.93162822723389</v>
+        <v>9.93162727355957</v>
       </c>
       <c r="H986" t="n">
         <v>350</v>
@@ -28992,7 +28992,7 @@
         <v>10.8999996185303</v>
       </c>
       <c r="G987" t="n">
-        <v>9.93162822723389</v>
+        <v>9.93162727355957</v>
       </c>
       <c r="H987" t="n">
         <v>293</v>
@@ -29021,7 +29021,7 @@
         <v>10.8999996185303</v>
       </c>
       <c r="G988" t="n">
-        <v>9.93162822723389</v>
+        <v>9.93162727355957</v>
       </c>
       <c r="H988" t="n">
         <v>2158</v>
@@ -29050,7 +29050,7 @@
         <v>10.8000001907349</v>
       </c>
       <c r="G989" t="n">
-        <v>9.84051322937012</v>
+        <v>9.8405122756958</v>
       </c>
       <c r="H989" t="n">
         <v>2879</v>
@@ -29079,7 +29079,7 @@
         <v>10.6999998092651</v>
       </c>
       <c r="G990" t="n">
-        <v>9.74939823150635</v>
+        <v>9.7493953704834</v>
       </c>
       <c r="H990" t="n">
         <v>1336</v>
@@ -29108,7 +29108,7 @@
         <v>10.6999998092651</v>
       </c>
       <c r="G991" t="n">
-        <v>9.74939823150635</v>
+        <v>9.7493953704834</v>
       </c>
       <c r="H991" t="n">
         <v>1250</v>
@@ -29137,7 +29137,7 @@
         <v>10.8000001907349</v>
       </c>
       <c r="G992" t="n">
-        <v>9.84051322937012</v>
+        <v>9.8405122756958</v>
       </c>
       <c r="H992" t="n">
         <v>1802</v>
@@ -29166,7 +29166,7 @@
         <v>10.6999998092651</v>
       </c>
       <c r="G993" t="n">
-        <v>9.74939823150635</v>
+        <v>9.7493953704834</v>
       </c>
       <c r="H993" t="n">
         <v>292</v>
@@ -29195,7 +29195,7 @@
         <v>10.6999998092651</v>
       </c>
       <c r="G994" t="n">
-        <v>9.74939823150635</v>
+        <v>9.7493953704834</v>
       </c>
       <c r="H994" t="n">
         <v>400</v>
@@ -29224,7 +29224,7 @@
         <v>10.6999998092651</v>
       </c>
       <c r="G995" t="n">
-        <v>9.74939823150635</v>
+        <v>9.7493953704834</v>
       </c>
       <c r="H995" t="n">
         <v>2308</v>
@@ -29253,7 +29253,7 @@
         <v>10.4499998092651</v>
       </c>
       <c r="G996" t="n">
-        <v>9.5216064453125</v>
+        <v>9.52160739898682</v>
       </c>
       <c r="H996" t="n">
         <v>1795</v>
@@ -29282,7 +29282,7 @@
         <v>10.6499996185303</v>
       </c>
       <c r="G997" t="n">
-        <v>9.70383930206299</v>
+        <v>9.70383834838867</v>
       </c>
       <c r="H997" t="n">
         <v>12</v>
@@ -29311,7 +29311,7 @@
         <v>10.6000003814697</v>
       </c>
       <c r="G998" t="n">
-        <v>9.65828227996826</v>
+        <v>9.65828132629395</v>
       </c>
       <c r="H998" t="n">
         <v>6553</v>
@@ -29340,7 +29340,7 @@
         <v>10.6000003814697</v>
       </c>
       <c r="G999" t="n">
-        <v>9.65828227996826</v>
+        <v>9.65828132629395</v>
       </c>
       <c r="H999" t="n">
         <v>134</v>
@@ -29369,7 +29369,7 @@
         <v>10.6499996185303</v>
       </c>
       <c r="G1000" t="n">
-        <v>9.70383930206299</v>
+        <v>9.70383834838867</v>
       </c>
       <c r="H1000" t="n">
         <v>5660</v>
@@ -29427,7 +29427,7 @@
         <v>10.4499998092651</v>
       </c>
       <c r="G1002" t="n">
-        <v>9.5216064453125</v>
+        <v>9.52160739898682</v>
       </c>
       <c r="H1002" t="n">
         <v>5462</v>
@@ -29456,7 +29456,7 @@
         <v>10.6000003814697</v>
       </c>
       <c r="G1003" t="n">
-        <v>9.65828227996826</v>
+        <v>9.65828132629395</v>
       </c>
       <c r="H1003" t="n">
         <v>5015</v>
@@ -29543,7 +29543,7 @@
         <v>10.3500003814697</v>
       </c>
       <c r="G1006" t="n">
-        <v>9.43049049377441</v>
+        <v>9.43049144744873</v>
       </c>
       <c r="H1006" t="n">
         <v>3628</v>
@@ -29572,7 +29572,7 @@
         <v>10.0500001907349</v>
       </c>
       <c r="G1007" t="n">
-        <v>9.15714263916016</v>
+        <v>9.15714359283447</v>
       </c>
       <c r="H1007" t="n">
         <v>29748</v>
@@ -29601,7 +29601,7 @@
         <v>9.96000003814697</v>
       </c>
       <c r="G1008" t="n">
-        <v>9.07513809204102</v>
+        <v>9.07513999938965</v>
       </c>
       <c r="H1008" t="n">
         <v>250</v>
@@ -29688,7 +29688,7 @@
         <v>10</v>
       </c>
       <c r="G1011" t="n">
-        <v>9.11158466339111</v>
+        <v>9.11158561706543</v>
       </c>
       <c r="H1011" t="n">
         <v>42205</v>
@@ -29746,7 +29746,7 @@
         <v>10</v>
       </c>
       <c r="G1013" t="n">
-        <v>9.11158466339111</v>
+        <v>9.11158561706543</v>
       </c>
       <c r="H1013" t="n">
         <v>40699</v>
@@ -29833,7 +29833,7 @@
         <v>9.76000022888184</v>
       </c>
       <c r="G1016" t="n">
-        <v>8.89290618896484</v>
+        <v>8.89290714263916</v>
       </c>
       <c r="H1016" t="n">
         <v>15819</v>
@@ -29862,7 +29862,7 @@
         <v>9.84000015258789</v>
       </c>
       <c r="G1017" t="n">
-        <v>8.96580123901367</v>
+        <v>8.96580028533936</v>
       </c>
       <c r="H1017" t="n">
         <v>2452</v>
@@ -29891,7 +29891,7 @@
         <v>9.77999973297119</v>
       </c>
       <c r="G1018" t="n">
-        <v>8.91113090515137</v>
+        <v>8.91112995147705</v>
       </c>
       <c r="H1018" t="n">
         <v>2309</v>
@@ -29920,7 +29920,7 @@
         <v>9.68000030517578</v>
       </c>
       <c r="G1019" t="n">
-        <v>8.82001495361328</v>
+        <v>8.8200159072876</v>
       </c>
       <c r="H1019" t="n">
         <v>1580</v>
@@ -29978,7 +29978,7 @@
         <v>9.73999977111816</v>
       </c>
       <c r="G1021" t="n">
-        <v>8.87468433380127</v>
+        <v>8.87468338012695</v>
       </c>
       <c r="H1021" t="n">
         <v>21365</v>
@@ -30007,7 +30007,7 @@
         <v>9.65999984741211</v>
       </c>
       <c r="G1022" t="n">
-        <v>8.80179119110107</v>
+        <v>8.80179214477539</v>
       </c>
       <c r="H1022" t="n">
         <v>12995</v>
@@ -30036,7 +30036,7 @@
         <v>9.39999961853027</v>
       </c>
       <c r="G1023" t="n">
-        <v>8.56489086151123</v>
+        <v>8.56488990783691</v>
       </c>
       <c r="H1023" t="n">
         <v>5113</v>
@@ -30065,7 +30065,7 @@
         <v>9.68000030517578</v>
       </c>
       <c r="G1024" t="n">
-        <v>8.82001495361328</v>
+        <v>8.8200159072876</v>
       </c>
       <c r="H1024" t="n">
         <v>6017</v>
@@ -30152,7 +30152,7 @@
         <v>9.46000003814697</v>
       </c>
       <c r="G1027" t="n">
-        <v>8.61956024169922</v>
+        <v>8.6195592880249</v>
       </c>
       <c r="H1027" t="n">
         <v>4125</v>
@@ -30210,7 +30210,7 @@
         <v>9.64000034332275</v>
       </c>
       <c r="G1029" t="n">
-        <v>8.7835693359375</v>
+        <v>8.78357028961182</v>
       </c>
       <c r="H1029" t="n">
         <v>2510</v>
@@ -30442,7 +30442,7 @@
         <v>10.6499996185303</v>
       </c>
       <c r="G1037" t="n">
-        <v>9.70383930206299</v>
+        <v>9.70383834838867</v>
       </c>
       <c r="H1037" t="n">
         <v>50821</v>
@@ -30500,7 +30500,7 @@
         <v>11.0500001907349</v>
       </c>
       <c r="G1039" t="n">
-        <v>10.0683040618896</v>
+        <v>10.068302154541</v>
       </c>
       <c r="H1039" t="n">
         <v>16443</v>
@@ -30529,7 +30529,7 @@
         <v>11</v>
       </c>
       <c r="G1040" t="n">
-        <v>10.0227451324463</v>
+        <v>10.022744178772</v>
       </c>
       <c r="H1040" t="n">
         <v>23628</v>
@@ -30732,7 +30732,7 @@
         <v>11.1499996185303</v>
       </c>
       <c r="G1047" t="n">
-        <v>10.1594171524048</v>
+        <v>10.1594181060791</v>
       </c>
       <c r="H1047" t="n">
         <v>11652</v>
@@ -30761,7 +30761,7 @@
         <v>10.9499998092651</v>
       </c>
       <c r="G1048" t="n">
-        <v>9.97718620300293</v>
+        <v>9.97718524932861</v>
       </c>
       <c r="H1048" t="n">
         <v>16113</v>
@@ -30790,7 +30790,7 @@
         <v>10.9499998092651</v>
       </c>
       <c r="G1049" t="n">
-        <v>9.97718620300293</v>
+        <v>9.97718524932861</v>
       </c>
       <c r="H1049" t="n">
         <v>7113</v>
@@ -30819,7 +30819,7 @@
         <v>10.9499998092651</v>
       </c>
       <c r="G1050" t="n">
-        <v>9.97718620300293</v>
+        <v>9.97718524932861</v>
       </c>
       <c r="H1050" t="n">
         <v>6511</v>
@@ -30848,7 +30848,7 @@
         <v>10.8999996185303</v>
       </c>
       <c r="G1051" t="n">
-        <v>9.93162822723389</v>
+        <v>9.93162727355957</v>
       </c>
       <c r="H1051" t="n">
         <v>3234</v>
@@ -30877,7 +30877,7 @@
         <v>11</v>
       </c>
       <c r="G1052" t="n">
-        <v>10.0227451324463</v>
+        <v>10.022744178772</v>
       </c>
       <c r="H1052" t="n">
         <v>2315</v>
@@ -30906,7 +30906,7 @@
         <v>10.9499998092651</v>
       </c>
       <c r="G1053" t="n">
-        <v>9.97718620300293</v>
+        <v>9.97718524932861</v>
       </c>
       <c r="H1053" t="n">
         <v>4421</v>
@@ -30935,7 +30935,7 @@
         <v>10.6999998092651</v>
       </c>
       <c r="G1054" t="n">
-        <v>9.74939823150635</v>
+        <v>9.7493953704834</v>
       </c>
       <c r="H1054" t="n">
         <v>10846</v>
@@ -30964,7 +30964,7 @@
         <v>10.9499998092651</v>
       </c>
       <c r="G1055" t="n">
-        <v>9.97718620300293</v>
+        <v>9.97718524932861</v>
       </c>
       <c r="H1055" t="n">
         <v>4602</v>
@@ -30993,7 +30993,7 @@
         <v>10.8000001907349</v>
       </c>
       <c r="G1056" t="n">
-        <v>9.84051322937012</v>
+        <v>9.8405122756958</v>
       </c>
       <c r="H1056" t="n">
         <v>19566</v>
@@ -31022,7 +31022,7 @@
         <v>10.9499998092651</v>
       </c>
       <c r="G1057" t="n">
-        <v>9.97718620300293</v>
+        <v>9.97718524932861</v>
       </c>
       <c r="H1057" t="n">
         <v>613</v>
@@ -31051,7 +31051,7 @@
         <v>10.8500003814697</v>
       </c>
       <c r="G1058" t="n">
-        <v>9.88607120513916</v>
+        <v>9.88607025146484</v>
       </c>
       <c r="H1058" t="n">
         <v>15783</v>
@@ -31080,7 +31080,7 @@
         <v>10.8000001907349</v>
       </c>
       <c r="G1059" t="n">
-        <v>9.84051322937012</v>
+        <v>9.8405122756958</v>
       </c>
       <c r="H1059" t="n">
         <v>400</v>
@@ -31109,7 +31109,7 @@
         <v>10.75</v>
       </c>
       <c r="G1060" t="n">
-        <v>9.79495525360107</v>
+        <v>9.79495429992676</v>
       </c>
       <c r="H1060" t="n">
         <v>3130</v>
@@ -31138,7 +31138,7 @@
         <v>10.6000003814697</v>
       </c>
       <c r="G1061" t="n">
-        <v>9.65828227996826</v>
+        <v>9.65828132629395</v>
       </c>
       <c r="H1061" t="n">
         <v>5560</v>
@@ -31167,7 +31167,7 @@
         <v>10.6999998092651</v>
       </c>
       <c r="G1062" t="n">
-        <v>9.74939823150635</v>
+        <v>9.7493953704834</v>
       </c>
       <c r="H1062" t="n">
         <v>11833</v>
@@ -31196,7 +31196,7 @@
         <v>10.75</v>
       </c>
       <c r="G1063" t="n">
-        <v>9.79495525360107</v>
+        <v>9.79495429992676</v>
       </c>
       <c r="H1063" t="n">
         <v>8500</v>
@@ -31225,7 +31225,7 @@
         <v>10.5</v>
       </c>
       <c r="G1064" t="n">
-        <v>9.56716442108154</v>
+        <v>9.56716537475586</v>
       </c>
       <c r="H1064" t="n">
         <v>30990</v>
@@ -31283,7 +31283,7 @@
         <v>10.5</v>
       </c>
       <c r="G1066" t="n">
-        <v>9.56716442108154</v>
+        <v>9.56716537475586</v>
       </c>
       <c r="H1066" t="n">
         <v>5535</v>
@@ -31312,7 +31312,7 @@
         <v>10.6000003814697</v>
       </c>
       <c r="G1067" t="n">
-        <v>9.65828227996826</v>
+        <v>9.65828132629395</v>
       </c>
       <c r="H1067" t="n">
         <v>2591</v>
@@ -31399,7 +31399,7 @@
         <v>10.8000001907349</v>
       </c>
       <c r="G1070" t="n">
-        <v>9.84051322937012</v>
+        <v>9.8405122756958</v>
       </c>
       <c r="H1070" t="n">
         <v>14898</v>
@@ -31428,7 +31428,7 @@
         <v>10.8999996185303</v>
       </c>
       <c r="G1071" t="n">
-        <v>9.93162822723389</v>
+        <v>9.93162727355957</v>
       </c>
       <c r="H1071" t="n">
         <v>8809</v>
@@ -31457,7 +31457,7 @@
         <v>10.75</v>
       </c>
       <c r="G1072" t="n">
-        <v>9.79495525360107</v>
+        <v>9.79495429992676</v>
       </c>
       <c r="H1072" t="n">
         <v>18487</v>
@@ -31486,7 +31486,7 @@
         <v>10.8000001907349</v>
       </c>
       <c r="G1073" t="n">
-        <v>9.84051322937012</v>
+        <v>9.8405122756958</v>
       </c>
       <c r="H1073" t="n">
         <v>1135</v>
@@ -31515,7 +31515,7 @@
         <v>10.8500003814697</v>
       </c>
       <c r="G1074" t="n">
-        <v>9.88607120513916</v>
+        <v>9.88607025146484</v>
       </c>
       <c r="H1074" t="n">
         <v>6030</v>
@@ -31544,7 +31544,7 @@
         <v>10.8500003814697</v>
       </c>
       <c r="G1075" t="n">
-        <v>9.88607120513916</v>
+        <v>9.88607025146484</v>
       </c>
       <c r="H1075" t="n">
         <v>2661</v>
@@ -31573,7 +31573,7 @@
         <v>10.8500003814697</v>
       </c>
       <c r="G1076" t="n">
-        <v>9.88607120513916</v>
+        <v>9.88607025146484</v>
       </c>
       <c r="H1076" t="n">
         <v>3712</v>
@@ -31602,7 +31602,7 @@
         <v>10.75</v>
       </c>
       <c r="G1077" t="n">
-        <v>9.79495525360107</v>
+        <v>9.79495429992676</v>
       </c>
       <c r="H1077" t="n">
         <v>4356</v>
@@ -31631,7 +31631,7 @@
         <v>10.75</v>
       </c>
       <c r="G1078" t="n">
-        <v>9.79495525360107</v>
+        <v>9.79495429992676</v>
       </c>
       <c r="H1078" t="n">
         <v>45</v>
@@ -31660,7 +31660,7 @@
         <v>10.75</v>
       </c>
       <c r="G1079" t="n">
-        <v>9.79495525360107</v>
+        <v>9.79495429992676</v>
       </c>
       <c r="H1079" t="n">
         <v>9723</v>
@@ -31689,7 +31689,7 @@
         <v>10.6499996185303</v>
       </c>
       <c r="G1080" t="n">
-        <v>9.70383930206299</v>
+        <v>9.70383834838867</v>
       </c>
       <c r="H1080" t="n">
         <v>11884</v>
@@ -31747,7 +31747,7 @@
         <v>10.6000003814697</v>
       </c>
       <c r="G1082" t="n">
-        <v>9.65828227996826</v>
+        <v>9.65828132629395</v>
       </c>
       <c r="H1082" t="n">
         <v>10531</v>
@@ -31776,7 +31776,7 @@
         <v>10.6000003814697</v>
       </c>
       <c r="G1083" t="n">
-        <v>9.65828227996826</v>
+        <v>9.65828132629395</v>
       </c>
       <c r="H1083" t="n">
         <v>3666</v>
@@ -31805,7 +31805,7 @@
         <v>10.3500003814697</v>
       </c>
       <c r="G1084" t="n">
-        <v>9.43049049377441</v>
+        <v>9.43049144744873</v>
       </c>
       <c r="H1084" t="n">
         <v>6448</v>
@@ -31892,7 +31892,7 @@
         <v>10.6499996185303</v>
       </c>
       <c r="G1087" t="n">
-        <v>9.70383930206299</v>
+        <v>9.70383834838867</v>
       </c>
       <c r="H1087" t="n">
         <v>8442</v>
@@ -31921,7 +31921,7 @@
         <v>10.6000003814697</v>
       </c>
       <c r="G1088" t="n">
-        <v>9.65828227996826</v>
+        <v>9.65828132629395</v>
       </c>
       <c r="H1088" t="n">
         <v>1963</v>
@@ -31950,7 +31950,7 @@
         <v>10.8000001907349</v>
       </c>
       <c r="G1089" t="n">
-        <v>9.84051322937012</v>
+        <v>9.8405122756958</v>
       </c>
       <c r="H1089" t="n">
         <v>14366</v>
@@ -31979,7 +31979,7 @@
         <v>10.8000001907349</v>
       </c>
       <c r="G1090" t="n">
-        <v>9.84051322937012</v>
+        <v>9.8405122756958</v>
       </c>
       <c r="H1090" t="n">
         <v>906</v>
@@ -32008,7 +32008,7 @@
         <v>10.8999996185303</v>
       </c>
       <c r="G1091" t="n">
-        <v>9.93162822723389</v>
+        <v>9.93162727355957</v>
       </c>
       <c r="H1091" t="n">
         <v>2852</v>
@@ -32037,7 +32037,7 @@
         <v>10.8500003814697</v>
       </c>
       <c r="G1092" t="n">
-        <v>9.88607120513916</v>
+        <v>9.88607025146484</v>
       </c>
       <c r="H1092" t="n">
         <v>6196</v>
@@ -32066,7 +32066,7 @@
         <v>10.8500003814697</v>
       </c>
       <c r="G1093" t="n">
-        <v>9.88607120513916</v>
+        <v>9.88607025146484</v>
       </c>
       <c r="H1093" t="n">
         <v>9361</v>
@@ -32095,7 +32095,7 @@
         <v>10.8999996185303</v>
       </c>
       <c r="G1094" t="n">
-        <v>9.93162822723389</v>
+        <v>9.93162727355957</v>
       </c>
       <c r="H1094" t="n">
         <v>1016</v>
@@ -32124,7 +32124,7 @@
         <v>10.6999998092651</v>
       </c>
       <c r="G1095" t="n">
-        <v>9.74939823150635</v>
+        <v>9.7493953704834</v>
       </c>
       <c r="H1095" t="n">
         <v>6967</v>
@@ -32153,7 +32153,7 @@
         <v>10.6999998092651</v>
       </c>
       <c r="G1096" t="n">
-        <v>9.74939823150635</v>
+        <v>9.7493953704834</v>
       </c>
       <c r="H1096" t="n">
         <v>6539</v>
@@ -32182,7 +32182,7 @@
         <v>10.6000003814697</v>
       </c>
       <c r="G1097" t="n">
-        <v>9.65828227996826</v>
+        <v>9.65828132629395</v>
       </c>
       <c r="H1097" t="n">
         <v>5284</v>
@@ -32211,7 +32211,7 @@
         <v>10.75</v>
       </c>
       <c r="G1098" t="n">
-        <v>9.79495525360107</v>
+        <v>9.79495429992676</v>
       </c>
       <c r="H1098" t="n">
         <v>5377</v>
@@ -32240,7 +32240,7 @@
         <v>10.8000001907349</v>
       </c>
       <c r="G1099" t="n">
-        <v>9.84051322937012</v>
+        <v>9.8405122756958</v>
       </c>
       <c r="H1099" t="n">
         <v>9104</v>
@@ -32269,7 +32269,7 @@
         <v>10.8000001907349</v>
       </c>
       <c r="G1100" t="n">
-        <v>9.84051322937012</v>
+        <v>9.8405122756958</v>
       </c>
       <c r="H1100" t="n">
         <v>24254</v>
@@ -32298,7 +32298,7 @@
         <v>10.75</v>
       </c>
       <c r="G1101" t="n">
-        <v>9.79495525360107</v>
+        <v>9.79495429992676</v>
       </c>
       <c r="H1101" t="n">
         <v>13932</v>
@@ -32327,7 +32327,7 @@
         <v>10.8999996185303</v>
       </c>
       <c r="G1102" t="n">
-        <v>9.93162822723389</v>
+        <v>9.93162727355957</v>
       </c>
       <c r="H1102" t="n">
         <v>16059</v>
@@ -32356,7 +32356,7 @@
         <v>10.9499998092651</v>
       </c>
       <c r="G1103" t="n">
-        <v>9.97718620300293</v>
+        <v>9.97718524932861</v>
       </c>
       <c r="H1103" t="n">
         <v>10723</v>
@@ -32385,7 +32385,7 @@
         <v>10.8999996185303</v>
       </c>
       <c r="G1104" t="n">
-        <v>9.93162822723389</v>
+        <v>9.93162727355957</v>
       </c>
       <c r="H1104" t="n">
         <v>1346</v>
@@ -32414,7 +32414,7 @@
         <v>10.8000001907349</v>
       </c>
       <c r="G1105" t="n">
-        <v>9.84051322937012</v>
+        <v>9.8405122756958</v>
       </c>
       <c r="H1105" t="n">
         <v>3539</v>
@@ -32443,7 +32443,7 @@
         <v>10.6999998092651</v>
       </c>
       <c r="G1106" t="n">
-        <v>9.74939823150635</v>
+        <v>9.7493953704834</v>
       </c>
       <c r="H1106" t="n">
         <v>4936</v>
@@ -32472,7 +32472,7 @@
         <v>10.8000001907349</v>
       </c>
       <c r="G1107" t="n">
-        <v>9.84051322937012</v>
+        <v>9.8405122756958</v>
       </c>
       <c r="H1107" t="n">
         <v>4910</v>
@@ -32501,7 +32501,7 @@
         <v>10.8000001907349</v>
       </c>
       <c r="G1108" t="n">
-        <v>9.84051322937012</v>
+        <v>9.8405122756958</v>
       </c>
       <c r="H1108" t="n">
         <v>3654</v>
@@ -32530,7 +32530,7 @@
         <v>10.8999996185303</v>
       </c>
       <c r="G1109" t="n">
-        <v>9.93162822723389</v>
+        <v>9.93162727355957</v>
       </c>
       <c r="H1109" t="n">
         <v>534</v>
@@ -32559,7 +32559,7 @@
         <v>10.8000001907349</v>
       </c>
       <c r="G1110" t="n">
-        <v>9.84051322937012</v>
+        <v>9.8405122756958</v>
       </c>
       <c r="H1110" t="n">
         <v>2457</v>
@@ -32588,7 +32588,7 @@
         <v>10.6999998092651</v>
       </c>
       <c r="G1111" t="n">
-        <v>9.74939823150635</v>
+        <v>9.7493953704834</v>
       </c>
       <c r="H1111" t="n">
         <v>550</v>
@@ -32617,7 +32617,7 @@
         <v>10.8000001907349</v>
       </c>
       <c r="G1112" t="n">
-        <v>9.84051322937012</v>
+        <v>9.8405122756958</v>
       </c>
       <c r="H1112" t="n">
         <v>4426</v>
@@ -32646,7 +32646,7 @@
         <v>10.8999996185303</v>
       </c>
       <c r="G1113" t="n">
-        <v>9.93162822723389</v>
+        <v>9.93162727355957</v>
       </c>
       <c r="H1113" t="n">
         <v>1001</v>
@@ -32675,7 +32675,7 @@
         <v>10.8000001907349</v>
       </c>
       <c r="G1114" t="n">
-        <v>9.84051322937012</v>
+        <v>9.8405122756958</v>
       </c>
       <c r="H1114" t="n">
         <v>1323</v>
@@ -32704,7 +32704,7 @@
         <v>10.75</v>
       </c>
       <c r="G1115" t="n">
-        <v>9.79495525360107</v>
+        <v>9.79495429992676</v>
       </c>
       <c r="H1115" t="n">
         <v>6893</v>
@@ -32733,7 +32733,7 @@
         <v>10.75</v>
       </c>
       <c r="G1116" t="n">
-        <v>9.79495525360107</v>
+        <v>9.79495429992676</v>
       </c>
       <c r="H1116" t="n">
         <v>6550</v>
@@ -32762,7 +32762,7 @@
         <v>10.9499998092651</v>
       </c>
       <c r="G1117" t="n">
-        <v>9.97718620300293</v>
+        <v>9.97718524932861</v>
       </c>
       <c r="H1117" t="n">
         <v>6390</v>
@@ -32791,7 +32791,7 @@
         <v>10.8999996185303</v>
       </c>
       <c r="G1118" t="n">
-        <v>9.93162822723389</v>
+        <v>9.93162727355957</v>
       </c>
       <c r="H1118" t="n">
         <v>7385</v>
@@ -32820,7 +32820,7 @@
         <v>11</v>
       </c>
       <c r="G1119" t="n">
-        <v>10.0227451324463</v>
+        <v>10.022744178772</v>
       </c>
       <c r="H1119" t="n">
         <v>2415</v>
@@ -32849,7 +32849,7 @@
         <v>11</v>
       </c>
       <c r="G1120" t="n">
-        <v>10.0227451324463</v>
+        <v>10.022744178772</v>
       </c>
       <c r="H1120" t="n">
         <v>9711</v>
@@ -32878,7 +32878,7 @@
         <v>11.0500001907349</v>
       </c>
       <c r="G1121" t="n">
-        <v>10.0683040618896</v>
+        <v>10.068302154541</v>
       </c>
       <c r="H1121" t="n">
         <v>5584</v>
@@ -32907,7 +32907,7 @@
         <v>11.1499996185303</v>
       </c>
       <c r="G1122" t="n">
-        <v>10.1594171524048</v>
+        <v>10.1594181060791</v>
       </c>
       <c r="H1122" t="n">
         <v>15698</v>
@@ -33023,7 +33023,7 @@
         <v>10.9499998092651</v>
       </c>
       <c r="G1126" t="n">
-        <v>9.97718620300293</v>
+        <v>9.97718524932861</v>
       </c>
       <c r="H1126" t="n">
         <v>1792</v>
@@ -33052,7 +33052,7 @@
         <v>11.0500001907349</v>
       </c>
       <c r="G1127" t="n">
-        <v>10.0683040618896</v>
+        <v>10.068302154541</v>
       </c>
       <c r="H1127" t="n">
         <v>12329</v>
@@ -33081,7 +33081,7 @@
         <v>11.8500003814697</v>
       </c>
       <c r="G1128" t="n">
-        <v>10.7972288131714</v>
+        <v>10.7972297668457</v>
       </c>
       <c r="H1128" t="n">
         <v>64836</v>
@@ -33110,7 +33110,7 @@
         <v>11.8500003814697</v>
       </c>
       <c r="G1129" t="n">
-        <v>10.7972288131714</v>
+        <v>10.7972297668457</v>
       </c>
       <c r="H1129" t="n">
         <v>20580</v>
@@ -33168,7 +33168,7 @@
         <v>12.1000003814697</v>
       </c>
       <c r="G1131" t="n">
-        <v>11.0250196456909</v>
+        <v>11.0250186920166</v>
       </c>
       <c r="H1131" t="n">
         <v>13540</v>
@@ -33197,7 +33197,7 @@
         <v>12.3999996185303</v>
       </c>
       <c r="G1132" t="n">
-        <v>11.2983646392822</v>
+        <v>11.2983665466309</v>
       </c>
       <c r="H1132" t="n">
         <v>74102</v>
@@ -33255,7 +33255,7 @@
         <v>12.5</v>
       </c>
       <c r="G1134" t="n">
-        <v>11.3894834518433</v>
+        <v>11.3894815444946</v>
       </c>
       <c r="H1134" t="n">
         <v>13196</v>
@@ -33284,7 +33284,7 @@
         <v>12.5500001907349</v>
       </c>
       <c r="G1135" t="n">
-        <v>11.4350395202637</v>
+        <v>11.435040473938</v>
       </c>
       <c r="H1135" t="n">
         <v>17670</v>
@@ -33371,7 +33371,7 @@
         <v>12.5500001907349</v>
       </c>
       <c r="G1138" t="n">
-        <v>11.4350395202637</v>
+        <v>11.435040473938</v>
       </c>
       <c r="H1138" t="n">
         <v>9552</v>
@@ -33661,7 +33661,7 @@
         <v>13.0500001907349</v>
       </c>
       <c r="G1148" t="n">
-        <v>11.8906202316284</v>
+        <v>11.8906192779541</v>
       </c>
       <c r="H1148" t="n">
         <v>8972</v>
@@ -33719,7 +33719,7 @@
         <v>13.3999996185303</v>
       </c>
       <c r="G1150" t="n">
-        <v>12.3414182662964</v>
+        <v>12.3414173126221</v>
       </c>
       <c r="H1150" t="n">
         <v>7563</v>
@@ -33748,7 +33748,7 @@
         <v>13.3500003814697</v>
       </c>
       <c r="G1151" t="n">
-        <v>12.2953672409058</v>
+        <v>12.2953681945801</v>
       </c>
       <c r="H1151" t="n">
         <v>12253</v>
@@ -33806,7 +33806,7 @@
         <v>13.3000001907349</v>
       </c>
       <c r="G1153" t="n">
-        <v>12.2493171691895</v>
+        <v>12.2493181228638</v>
       </c>
       <c r="H1153" t="n">
         <v>16947</v>
@@ -33893,7 +33893,7 @@
         <v>13.6000003814697</v>
       </c>
       <c r="G1156" t="n">
-        <v>12.5256185531616</v>
+        <v>12.5256175994873</v>
       </c>
       <c r="H1156" t="n">
         <v>18328</v>
@@ -33951,7 +33951,7 @@
         <v>13.6000003814697</v>
       </c>
       <c r="G1158" t="n">
-        <v>12.5256185531616</v>
+        <v>12.5256175994873</v>
       </c>
       <c r="H1158" t="n">
         <v>13524</v>
@@ -33980,7 +33980,7 @@
         <v>13.3999996185303</v>
       </c>
       <c r="G1159" t="n">
-        <v>12.3414182662964</v>
+        <v>12.3414173126221</v>
       </c>
       <c r="H1159" t="n">
         <v>4891</v>
@@ -34038,7 +34038,7 @@
         <v>13.6000003814697</v>
       </c>
       <c r="G1161" t="n">
-        <v>12.5256185531616</v>
+        <v>12.5256175994873</v>
       </c>
       <c r="H1161" t="n">
         <v>12700</v>
@@ -34067,7 +34067,7 @@
         <v>13.3000001907349</v>
       </c>
       <c r="G1162" t="n">
-        <v>12.2493171691895</v>
+        <v>12.2493181228638</v>
       </c>
       <c r="H1162" t="n">
         <v>38669</v>
@@ -34154,7 +34154,7 @@
         <v>13.0500001907349</v>
       </c>
       <c r="G1165" t="n">
-        <v>12.0190677642822</v>
+        <v>12.0190668106079</v>
       </c>
       <c r="H1165" t="n">
         <v>3456</v>
@@ -34183,7 +34183,7 @@
         <v>13</v>
       </c>
       <c r="G1166" t="n">
-        <v>11.9730176925659</v>
+        <v>11.9730167388916</v>
       </c>
       <c r="H1166" t="n">
         <v>5721</v>
@@ -34241,7 +34241,7 @@
         <v>13.1499996185303</v>
       </c>
       <c r="G1168" t="n">
-        <v>12.1111660003662</v>
+        <v>12.1111669540405</v>
       </c>
       <c r="H1168" t="n">
         <v>13997</v>
@@ -34299,7 +34299,7 @@
         <v>13.3500003814697</v>
       </c>
       <c r="G1170" t="n">
-        <v>12.2953672409058</v>
+        <v>12.2953681945801</v>
       </c>
       <c r="H1170" t="n">
         <v>10823</v>
@@ -34357,7 +34357,7 @@
         <v>13.3999996185303</v>
       </c>
       <c r="G1172" t="n">
-        <v>12.3414182662964</v>
+        <v>12.3414173126221</v>
       </c>
       <c r="H1172" t="n">
         <v>1524</v>
@@ -34386,7 +34386,7 @@
         <v>13.6000003814697</v>
       </c>
       <c r="G1173" t="n">
-        <v>12.5256185531616</v>
+        <v>12.5256175994873</v>
       </c>
       <c r="H1173" t="n">
         <v>110733</v>
@@ -34531,7 +34531,7 @@
         <v>13.4499998092651</v>
       </c>
       <c r="G1178" t="n">
-        <v>12.3874673843384</v>
+        <v>12.3874664306641</v>
       </c>
       <c r="H1178" t="n">
         <v>10766</v>
@@ -34560,7 +34560,7 @@
         <v>13.6000003814697</v>
       </c>
       <c r="G1179" t="n">
-        <v>12.5256185531616</v>
+        <v>12.5256175994873</v>
       </c>
       <c r="H1179" t="n">
         <v>3641</v>
@@ -34589,7 +34589,7 @@
         <v>13.6000003814697</v>
       </c>
       <c r="G1180" t="n">
-        <v>12.5256185531616</v>
+        <v>12.5256175994873</v>
       </c>
       <c r="H1180" t="n">
         <v>17307</v>
@@ -34618,7 +34618,7 @@
         <v>13.6000003814697</v>
       </c>
       <c r="G1181" t="n">
-        <v>12.5256185531616</v>
+        <v>12.5256175994873</v>
       </c>
       <c r="H1181" t="n">
         <v>2093</v>
@@ -34647,7 +34647,7 @@
         <v>13.6000003814697</v>
       </c>
       <c r="G1182" t="n">
-        <v>12.5256185531616</v>
+        <v>12.5256175994873</v>
       </c>
       <c r="H1182" t="n">
         <v>8035</v>
@@ -34705,7 +34705,7 @@
         <v>13.4499998092651</v>
       </c>
       <c r="G1184" t="n">
-        <v>12.3874673843384</v>
+        <v>12.3874664306641</v>
       </c>
       <c r="H1184" t="n">
         <v>7360</v>
@@ -34734,7 +34734,7 @@
         <v>13.6000003814697</v>
       </c>
       <c r="G1185" t="n">
-        <v>12.5256185531616</v>
+        <v>12.5256175994873</v>
       </c>
       <c r="H1185" t="n">
         <v>6448</v>
@@ -34763,7 +34763,7 @@
         <v>13.6000003814697</v>
       </c>
       <c r="G1186" t="n">
-        <v>12.5256185531616</v>
+        <v>12.5256175994873</v>
       </c>
       <c r="H1186" t="n">
         <v>7807</v>
@@ -34850,7 +34850,7 @@
         <v>13.3500003814697</v>
       </c>
       <c r="G1189" t="n">
-        <v>12.2953672409058</v>
+        <v>12.2953681945801</v>
       </c>
       <c r="H1189" t="n">
         <v>92732</v>
@@ -34879,7 +34879,7 @@
         <v>13.4499998092651</v>
       </c>
       <c r="G1190" t="n">
-        <v>12.3874673843384</v>
+        <v>12.3874664306641</v>
       </c>
       <c r="H1190" t="n">
         <v>5662</v>
@@ -34908,7 +34908,7 @@
         <v>13.3500003814697</v>
       </c>
       <c r="G1191" t="n">
-        <v>12.2953672409058</v>
+        <v>12.2953681945801</v>
       </c>
       <c r="H1191" t="n">
         <v>13113</v>
@@ -34937,7 +34937,7 @@
         <v>13.3999996185303</v>
       </c>
       <c r="G1192" t="n">
-        <v>12.3414182662964</v>
+        <v>12.3414173126221</v>
       </c>
       <c r="H1192" t="n">
         <v>1625</v>
@@ -34966,7 +34966,7 @@
         <v>13.3500003814697</v>
       </c>
       <c r="G1193" t="n">
-        <v>12.2953672409058</v>
+        <v>12.2953681945801</v>
       </c>
       <c r="H1193" t="n">
         <v>9634</v>
@@ -34995,7 +34995,7 @@
         <v>13.3500003814697</v>
       </c>
       <c r="G1194" t="n">
-        <v>12.2953672409058</v>
+        <v>12.2953681945801</v>
       </c>
       <c r="H1194" t="n">
         <v>8343</v>
@@ -35024,7 +35024,7 @@
         <v>13.3000001907349</v>
       </c>
       <c r="G1195" t="n">
-        <v>12.2493171691895</v>
+        <v>12.2493181228638</v>
       </c>
       <c r="H1195" t="n">
         <v>9948</v>
@@ -35082,7 +35082,7 @@
         <v>13.3000001907349</v>
       </c>
       <c r="G1197" t="n">
-        <v>12.2493171691895</v>
+        <v>12.2493181228638</v>
       </c>
       <c r="H1197" t="n">
         <v>7826</v>
@@ -35111,7 +35111,7 @@
         <v>13.4499998092651</v>
       </c>
       <c r="G1198" t="n">
-        <v>12.3874673843384</v>
+        <v>12.3874664306641</v>
       </c>
       <c r="H1198" t="n">
         <v>19804</v>
@@ -35140,7 +35140,7 @@
         <v>13.6000003814697</v>
       </c>
       <c r="G1199" t="n">
-        <v>12.5256185531616</v>
+        <v>12.5256175994873</v>
       </c>
       <c r="H1199" t="n">
         <v>24469</v>
@@ -35285,7 +35285,7 @@
         <v>13.6000003814697</v>
       </c>
       <c r="G1204" t="n">
-        <v>12.5256185531616</v>
+        <v>12.5256175994873</v>
       </c>
       <c r="H1204" t="n">
         <v>10928</v>
@@ -35314,7 +35314,7 @@
         <v>13.3500003814697</v>
       </c>
       <c r="G1205" t="n">
-        <v>12.2953672409058</v>
+        <v>12.2953681945801</v>
       </c>
       <c r="H1205" t="n">
         <v>22149</v>
@@ -35372,7 +35372,7 @@
         <v>13.4499998092651</v>
       </c>
       <c r="G1207" t="n">
-        <v>12.3874673843384</v>
+        <v>12.3874664306641</v>
       </c>
       <c r="H1207" t="n">
         <v>6781</v>
@@ -35401,7 +35401,7 @@
         <v>13.3999996185303</v>
       </c>
       <c r="G1208" t="n">
-        <v>12.3414182662964</v>
+        <v>12.3414173126221</v>
       </c>
       <c r="H1208" t="n">
         <v>5908</v>
@@ -35459,7 +35459,7 @@
         <v>13.3500003814697</v>
       </c>
       <c r="G1210" t="n">
-        <v>12.2953672409058</v>
+        <v>12.2953681945801</v>
       </c>
       <c r="H1210" t="n">
         <v>14763</v>
@@ -35633,7 +35633,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G1216" t="n">
-        <v>13.630820274353</v>
+        <v>13.6308193206787</v>
       </c>
       <c r="H1216" t="n">
         <v>30840</v>
@@ -36242,7 +36242,7 @@
         <v>17.8999996185303</v>
       </c>
       <c r="G1237" t="n">
-        <v>16.4859237670898</v>
+        <v>16.4859256744385</v>
       </c>
       <c r="H1237" t="n">
         <v>37360</v>
@@ -36300,7 +36300,7 @@
         <v>18.2000007629395</v>
       </c>
       <c r="G1239" t="n">
-        <v>16.7622241973877</v>
+        <v>16.7622261047363</v>
       </c>
       <c r="H1239" t="n">
         <v>31567</v>
@@ -36387,7 +36387,7 @@
         <v>17.8999996185303</v>
       </c>
       <c r="G1242" t="n">
-        <v>16.4859237670898</v>
+        <v>16.4859256744385</v>
       </c>
       <c r="H1242" t="n">
         <v>32070</v>
@@ -36532,7 +36532,7 @@
         <v>17.7000007629395</v>
       </c>
       <c r="G1247" t="n">
-        <v>16.3017253875732</v>
+        <v>16.3017234802246</v>
       </c>
       <c r="H1247" t="n">
         <v>26545</v>
@@ -36677,7 +36677,7 @@
         <v>18.2999992370605</v>
       </c>
       <c r="G1252" t="n">
-        <v>16.8543224334717</v>
+        <v>16.8543243408203</v>
       </c>
       <c r="H1252" t="n">
         <v>179017</v>
@@ -36909,7 +36909,7 @@
         <v>17.1000003814697</v>
       </c>
       <c r="G1260" t="n">
-        <v>15.7491216659546</v>
+        <v>15.7491235733032</v>
       </c>
       <c r="H1260" t="n">
         <v>17883</v>
@@ -36938,7 +36938,7 @@
         <v>17.25</v>
       </c>
       <c r="G1261" t="n">
-        <v>15.8872709274292</v>
+        <v>15.8872728347778</v>
       </c>
       <c r="H1261" t="n">
         <v>15494</v>
@@ -37112,7 +37112,7 @@
         <v>17.5499992370605</v>
       </c>
       <c r="G1267" t="n">
-        <v>16.16357421875</v>
+        <v>16.1635723114014</v>
       </c>
       <c r="H1267" t="n">
         <v>18170</v>
@@ -37199,7 +37199,7 @@
         <v>18.0499992370605</v>
       </c>
       <c r="G1270" t="n">
-        <v>16.6240711212158</v>
+        <v>16.6240730285645</v>
       </c>
       <c r="H1270" t="n">
         <v>15616</v>
@@ -37286,7 +37286,7 @@
         <v>18.0499992370605</v>
       </c>
       <c r="G1273" t="n">
-        <v>16.6240711212158</v>
+        <v>16.6240730285645</v>
       </c>
       <c r="H1273" t="n">
         <v>16916</v>
@@ -37373,7 +37373,7 @@
         <v>18.0499992370605</v>
       </c>
       <c r="G1276" t="n">
-        <v>16.6240711212158</v>
+        <v>16.6240730285645</v>
       </c>
       <c r="H1276" t="n">
         <v>19014</v>
@@ -37402,7 +37402,7 @@
         <v>17.7999992370605</v>
       </c>
       <c r="G1277" t="n">
-        <v>16.3938236236572</v>
+        <v>16.3938255310059</v>
       </c>
       <c r="H1277" t="n">
         <v>16313</v>
@@ -37431,7 +37431,7 @@
         <v>17.9500007629395</v>
       </c>
       <c r="G1278" t="n">
-        <v>16.5319747924805</v>
+        <v>16.5319766998291</v>
       </c>
       <c r="H1278" t="n">
         <v>21896</v>
@@ -37489,7 +37489,7 @@
         <v>17.9500007629395</v>
       </c>
       <c r="G1280" t="n">
-        <v>16.5319747924805</v>
+        <v>16.5319766998291</v>
       </c>
       <c r="H1280" t="n">
         <v>4603</v>
@@ -37518,7 +37518,7 @@
         <v>17.9500007629395</v>
       </c>
       <c r="G1281" t="n">
-        <v>16.5319747924805</v>
+        <v>16.5319766998291</v>
       </c>
       <c r="H1281" t="n">
         <v>17215</v>
@@ -37547,7 +37547,7 @@
         <v>17.7000007629395</v>
       </c>
       <c r="G1282" t="n">
-        <v>16.3017253875732</v>
+        <v>16.3017234802246</v>
       </c>
       <c r="H1282" t="n">
         <v>9795</v>
@@ -37576,7 +37576,7 @@
         <v>17.8999996185303</v>
       </c>
       <c r="G1283" t="n">
-        <v>16.4859237670898</v>
+        <v>16.4859256744385</v>
       </c>
       <c r="H1283" t="n">
         <v>10193</v>
@@ -37605,7 +37605,7 @@
         <v>17.7999992370605</v>
       </c>
       <c r="G1284" t="n">
-        <v>16.3938236236572</v>
+        <v>16.3938255310059</v>
       </c>
       <c r="H1284" t="n">
         <v>14118</v>
@@ -37634,7 +37634,7 @@
         <v>17.8999996185303</v>
       </c>
       <c r="G1285" t="n">
-        <v>16.4859237670898</v>
+        <v>16.4859256744385</v>
       </c>
       <c r="H1285" t="n">
         <v>11787</v>
@@ -37663,7 +37663,7 @@
         <v>17.7000007629395</v>
       </c>
       <c r="G1286" t="n">
-        <v>16.3017253875732</v>
+        <v>16.3017234802246</v>
       </c>
       <c r="H1286" t="n">
         <v>8700</v>
@@ -37750,7 +37750,7 @@
         <v>17.7000007629395</v>
       </c>
       <c r="G1289" t="n">
-        <v>16.3017253875732</v>
+        <v>16.3017234802246</v>
       </c>
       <c r="H1289" t="n">
         <v>5832</v>
@@ -37866,7 +37866,7 @@
         <v>16</v>
       </c>
       <c r="G1293" t="n">
-        <v>14.7360210418701</v>
+        <v>14.7360200881958</v>
       </c>
       <c r="H1293" t="n">
         <v>19002</v>
@@ -37895,7 +37895,7 @@
         <v>16</v>
       </c>
       <c r="G1294" t="n">
-        <v>14.7360210418701</v>
+        <v>14.7360200881958</v>
       </c>
       <c r="H1294" t="n">
         <v>17942</v>
@@ -37924,7 +37924,7 @@
         <v>15.8000001907349</v>
       </c>
       <c r="G1295" t="n">
-        <v>14.5518207550049</v>
+        <v>14.5518198013306</v>
       </c>
       <c r="H1295" t="n">
         <v>22331</v>
@@ -38011,7 +38011,7 @@
         <v>15.4499998092651</v>
       </c>
       <c r="G1298" t="n">
-        <v>14.2294702529907</v>
+        <v>14.2294692993164</v>
       </c>
       <c r="H1298" t="n">
         <v>31832</v>
@@ -38185,7 +38185,7 @@
         <v>14.8999996185303</v>
       </c>
       <c r="G1304" t="n">
-        <v>13.7229194641113</v>
+        <v>13.722918510437</v>
       </c>
       <c r="H1304" t="n">
         <v>44097</v>
@@ -38214,7 +38214,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G1305" t="n">
-        <v>13.630820274353</v>
+        <v>13.6308193206787</v>
       </c>
       <c r="H1305" t="n">
         <v>6433</v>
@@ -38301,7 +38301,7 @@
         <v>15.1499996185303</v>
       </c>
       <c r="G1308" t="n">
-        <v>13.9531688690186</v>
+        <v>13.9531698226929</v>
       </c>
       <c r="H1308" t="n">
         <v>6440</v>
@@ -38359,7 +38359,7 @@
         <v>14.8999996185303</v>
       </c>
       <c r="G1310" t="n">
-        <v>13.7229194641113</v>
+        <v>13.722918510437</v>
       </c>
       <c r="H1310" t="n">
         <v>57497</v>
@@ -38562,7 +38562,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G1317" t="n">
-        <v>13.9071197509766</v>
+        <v>13.9071207046509</v>
       </c>
       <c r="H1317" t="n">
         <v>15322</v>
@@ -38591,7 +38591,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G1318" t="n">
-        <v>13.9071197509766</v>
+        <v>13.9071207046509</v>
       </c>
       <c r="H1318" t="n">
         <v>8220</v>
@@ -38707,7 +38707,7 @@
         <v>15.3999996185303</v>
       </c>
       <c r="G1322" t="n">
-        <v>14.1834201812744</v>
+        <v>14.1834192276001</v>
       </c>
       <c r="H1322" t="n">
         <v>2323</v>
@@ -38736,7 +38736,7 @@
         <v>15.6000003814697</v>
       </c>
       <c r="G1323" t="n">
-        <v>14.3676204681396</v>
+        <v>14.3676195144653</v>
       </c>
       <c r="H1323" t="n">
         <v>7547</v>
@@ -38852,7 +38852,7 @@
         <v>15.1499996185303</v>
       </c>
       <c r="G1327" t="n">
-        <v>13.9531688690186</v>
+        <v>13.9531698226929</v>
       </c>
       <c r="H1327" t="n">
         <v>18122</v>
@@ -39200,7 +39200,7 @@
         <v>13.3999996185303</v>
       </c>
       <c r="G1339" t="n">
-        <v>12.3414182662964</v>
+        <v>12.3414173126221</v>
       </c>
       <c r="H1339" t="n">
         <v>27692</v>
@@ -39229,7 +39229,7 @@
         <v>13.6000003814697</v>
       </c>
       <c r="G1340" t="n">
-        <v>12.5256185531616</v>
+        <v>12.5256175994873</v>
       </c>
       <c r="H1340" t="n">
         <v>6667</v>
@@ -39432,7 +39432,7 @@
         <v>13.0500001907349</v>
       </c>
       <c r="G1347" t="n">
-        <v>12.0190677642822</v>
+        <v>12.0190668106079</v>
       </c>
       <c r="H1347" t="n">
         <v>10398</v>
@@ -39548,7 +39548,7 @@
         <v>13</v>
       </c>
       <c r="G1351" t="n">
-        <v>11.9730176925659</v>
+        <v>11.9730167388916</v>
       </c>
       <c r="H1351" t="n">
         <v>35030</v>
@@ -39577,7 +39577,7 @@
         <v>13.0500001907349</v>
       </c>
       <c r="G1352" t="n">
-        <v>12.0190677642822</v>
+        <v>12.0190668106079</v>
       </c>
       <c r="H1352" t="n">
         <v>25648</v>
@@ -39867,7 +39867,7 @@
         <v>12.4499998092651</v>
       </c>
       <c r="G1362" t="n">
-        <v>11.4664669036865</v>
+        <v>11.4664659500122</v>
       </c>
       <c r="H1362" t="n">
         <v>9865</v>
@@ -40012,7 +40012,7 @@
         <v>11.4499998092651</v>
       </c>
       <c r="G1367" t="n">
-        <v>10.5454635620117</v>
+        <v>10.545464515686</v>
       </c>
       <c r="H1367" t="n">
         <v>15067</v>
@@ -40099,7 +40099,7 @@
         <v>11.9499998092651</v>
       </c>
       <c r="G1370" t="n">
-        <v>11.0059642791748</v>
+        <v>11.0059652328491</v>
       </c>
       <c r="H1370" t="n">
         <v>8903</v>
@@ -40244,7 +40244,7 @@
         <v>12.5</v>
       </c>
       <c r="G1375" t="n">
-        <v>11.5125179290771</v>
+        <v>11.5125169754028</v>
       </c>
       <c r="H1375" t="n">
         <v>3725</v>
@@ -40273,7 +40273,7 @@
         <v>12.4499998092651</v>
       </c>
       <c r="G1376" t="n">
-        <v>11.4664669036865</v>
+        <v>11.4664659500122</v>
       </c>
       <c r="H1376" t="n">
         <v>6250</v>
@@ -40302,7 +40302,7 @@
         <v>12.5500001907349</v>
       </c>
       <c r="G1377" t="n">
-        <v>11.5585660934448</v>
+        <v>11.5585670471191</v>
       </c>
       <c r="H1377" t="n">
         <v>8078</v>
@@ -40360,7 +40360,7 @@
         <v>13.0500001907349</v>
       </c>
       <c r="G1379" t="n">
-        <v>12.0190677642822</v>
+        <v>12.0190668106079</v>
       </c>
       <c r="H1379" t="n">
         <v>8883</v>
@@ -40447,7 +40447,7 @@
         <v>13</v>
       </c>
       <c r="G1382" t="n">
-        <v>11.9730176925659</v>
+        <v>11.9730167388916</v>
       </c>
       <c r="H1382" t="n">
         <v>2751</v>
@@ -40476,7 +40476,7 @@
         <v>13</v>
       </c>
       <c r="G1383" t="n">
-        <v>11.9730176925659</v>
+        <v>11.9730167388916</v>
       </c>
       <c r="H1383" t="n">
         <v>8236</v>
@@ -40505,7 +40505,7 @@
         <v>13.3999996185303</v>
       </c>
       <c r="G1384" t="n">
-        <v>12.3414182662964</v>
+        <v>12.3414173126221</v>
       </c>
       <c r="H1384" t="n">
         <v>22273</v>
@@ -40621,7 +40621,7 @@
         <v>8.89999961853027</v>
       </c>
       <c r="G1388" t="n">
-        <v>8.19691181182861</v>
+        <v>8.19691276550293</v>
       </c>
       <c r="H1388" t="n">
         <v>323786</v>
@@ -40650,7 +40650,7 @@
         <v>9.14999961853027</v>
       </c>
       <c r="G1389" t="n">
-        <v>8.42716121673584</v>
+        <v>8.42716217041016</v>
       </c>
       <c r="H1389" t="n">
         <v>114134</v>
@@ -40708,7 +40708,7 @@
         <v>9.02000045776367</v>
       </c>
       <c r="G1391" t="n">
-        <v>8.3074312210083</v>
+        <v>8.30743217468262</v>
       </c>
       <c r="H1391" t="n">
         <v>49666</v>
@@ -40737,7 +40737,7 @@
         <v>9.19999980926514</v>
       </c>
       <c r="G1392" t="n">
-        <v>8.47321319580078</v>
+        <v>8.47321224212646</v>
       </c>
       <c r="H1392" t="n">
         <v>43171</v>
@@ -40766,7 +40766,7 @@
         <v>9.01000022888184</v>
       </c>
       <c r="G1393" t="n">
-        <v>8.29822254180908</v>
+        <v>8.29822158813477</v>
       </c>
       <c r="H1393" t="n">
         <v>15513</v>
@@ -40795,7 +40795,7 @@
         <v>8.89000034332275</v>
       </c>
       <c r="G1394" t="n">
-        <v>8.18770217895508</v>
+        <v>8.18770122528076</v>
       </c>
       <c r="H1394" t="n">
         <v>15541</v>
@@ -40882,7 +40882,7 @@
         <v>9.03999996185303</v>
       </c>
       <c r="G1397" t="n">
-        <v>8.325852394104</v>
+        <v>8.32585144042969</v>
       </c>
       <c r="H1397" t="n">
         <v>49566</v>
@@ -41027,7 +41027,7 @@
         <v>8</v>
       </c>
       <c r="G1402" t="n">
-        <v>7.36801052093506</v>
+        <v>7.3680100440979</v>
       </c>
       <c r="H1402" t="n">
         <v>23498</v>
@@ -41114,7 +41114,7 @@
         <v>8.35999965667725</v>
       </c>
       <c r="G1405" t="n">
-        <v>7.6995701789856</v>
+        <v>7.69957065582275</v>
       </c>
       <c r="H1405" t="n">
         <v>38004</v>
@@ -41143,7 +41143,7 @@
         <v>8.4399995803833</v>
       </c>
       <c r="G1406" t="n">
-        <v>7.77325057983398</v>
+        <v>7.77325010299683</v>
       </c>
       <c r="H1406" t="n">
         <v>17144</v>
@@ -41288,7 +41288,7 @@
         <v>7.44999980926514</v>
       </c>
       <c r="G1411" t="n">
-        <v>6.86145973205566</v>
+        <v>6.86145925521851</v>
       </c>
       <c r="H1411" t="n">
         <v>29817</v>
@@ -41317,7 +41317,7 @@
         <v>7.40000009536743</v>
       </c>
       <c r="G1412" t="n">
-        <v>6.81541013717651</v>
+        <v>6.81540966033936</v>
       </c>
       <c r="H1412" t="n">
         <v>13765</v>
@@ -41404,7 +41404,7 @@
         <v>7.84000015258789</v>
       </c>
       <c r="G1415" t="n">
-        <v>7.2206506729126</v>
+        <v>7.22065019607544</v>
       </c>
       <c r="H1415" t="n">
         <v>4689</v>
@@ -41578,7 +41578,7 @@
         <v>9.06999969482422</v>
       </c>
       <c r="G1421" t="n">
-        <v>8.50467586517334</v>
+        <v>8.50467681884766</v>
       </c>
       <c r="H1421" t="n">
         <v>35417</v>
@@ -41636,7 +41636,7 @@
         <v>8.94999980926514</v>
       </c>
       <c r="G1423" t="n">
-        <v>8.39215564727783</v>
+        <v>8.39215660095215</v>
       </c>
       <c r="H1423" t="n">
         <v>14908</v>
@@ -41665,7 +41665,7 @@
         <v>9.10000038146973</v>
       </c>
       <c r="G1424" t="n">
-        <v>8.53280639648438</v>
+        <v>8.53280735015869</v>
       </c>
       <c r="H1424" t="n">
         <v>15786</v>
@@ -41694,7 +41694,7 @@
         <v>9.19999980926514</v>
       </c>
       <c r="G1425" t="n">
-        <v>8.62657451629639</v>
+        <v>8.62657356262207</v>
       </c>
       <c r="H1425" t="n">
         <v>17323</v>
@@ -41752,7 +41752,7 @@
         <v>9.10000038146973</v>
       </c>
       <c r="G1427" t="n">
-        <v>8.53280639648438</v>
+        <v>8.53280735015869</v>
       </c>
       <c r="H1427" t="n">
         <v>17846</v>
@@ -41781,7 +41781,7 @@
         <v>9.14999961853027</v>
       </c>
       <c r="G1428" t="n">
-        <v>8.57968902587891</v>
+        <v>8.57968997955322</v>
       </c>
       <c r="H1428" t="n">
         <v>6158</v>
@@ -41810,7 +41810,7 @@
         <v>9.07999992370605</v>
       </c>
       <c r="G1429" t="n">
-        <v>8.51405334472656</v>
+        <v>8.51405239105225</v>
       </c>
       <c r="H1429" t="n">
         <v>7399</v>
@@ -41839,7 +41839,7 @@
         <v>8.90999984741211</v>
       </c>
       <c r="G1430" t="n">
-        <v>8.35464859008789</v>
+        <v>8.35464954376221</v>
       </c>
       <c r="H1430" t="n">
         <v>25920</v>
@@ -41868,7 +41868,7 @@
         <v>8.82999992370605</v>
       </c>
       <c r="G1431" t="n">
-        <v>8.27963447570801</v>
+        <v>8.27963542938232</v>
       </c>
       <c r="H1431" t="n">
         <v>3860</v>
@@ -41897,7 +41897,7 @@
         <v>8.80000019073486</v>
       </c>
       <c r="G1432" t="n">
-        <v>8.25150585174561</v>
+        <v>8.25150489807129</v>
       </c>
       <c r="H1432" t="n">
         <v>9669</v>
@@ -41926,7 +41926,7 @@
         <v>9.02000045776367</v>
       </c>
       <c r="G1433" t="n">
-        <v>8.45779228210449</v>
+        <v>8.45779323577881</v>
       </c>
       <c r="H1433" t="n">
         <v>12940</v>
@@ -41955,7 +41955,7 @@
         <v>8.89999961853027</v>
       </c>
       <c r="G1434" t="n">
-        <v>8.34527206420898</v>
+        <v>8.3452730178833</v>
       </c>
       <c r="H1434" t="n">
         <v>10215</v>
@@ -42071,7 +42071,7 @@
         <v>8.5</v>
       </c>
       <c r="G1438" t="n">
-        <v>7.97020387649536</v>
+        <v>7.97020435333252</v>
       </c>
       <c r="H1438" t="n">
         <v>1049</v>
@@ -42129,7 +42129,7 @@
         <v>8.73999977111816</v>
       </c>
       <c r="G1440" t="n">
-        <v>8.19524383544922</v>
+        <v>8.19524478912354</v>
       </c>
       <c r="H1440" t="n">
         <v>20556</v>
@@ -42187,7 +42187,7 @@
         <v>8.5</v>
       </c>
       <c r="G1442" t="n">
-        <v>7.97020387649536</v>
+        <v>7.97020435333252</v>
       </c>
       <c r="H1442" t="n">
         <v>578</v>
@@ -42274,7 +42274,7 @@
         <v>8.5</v>
       </c>
       <c r="G1445" t="n">
-        <v>7.97020387649536</v>
+        <v>7.97020435333252</v>
       </c>
       <c r="H1445" t="n">
         <v>8134</v>
@@ -42361,7 +42361,7 @@
         <v>8.46000003814697</v>
       </c>
       <c r="G1448" t="n">
-        <v>7.9326958656311</v>
+        <v>7.93269634246826</v>
       </c>
       <c r="H1448" t="n">
         <v>7163</v>
@@ -42419,7 +42419,7 @@
         <v>8.36999988555908</v>
       </c>
       <c r="G1450" t="n">
-        <v>7.84830713272095</v>
+        <v>7.84830665588379</v>
       </c>
       <c r="H1450" t="n">
         <v>1746</v>
@@ -42448,7 +42448,7 @@
         <v>8.71000003814697</v>
       </c>
       <c r="G1451" t="n">
-        <v>8.1671142578125</v>
+        <v>8.16711521148682</v>
       </c>
       <c r="H1451" t="n">
         <v>5997</v>
@@ -42477,7 +42477,7 @@
         <v>8.65999984741211</v>
       </c>
       <c r="G1452" t="n">
-        <v>8.12023067474365</v>
+        <v>8.12023162841797</v>
       </c>
       <c r="H1452" t="n">
         <v>4014</v>
@@ -42564,7 +42564,7 @@
         <v>8.5</v>
       </c>
       <c r="G1455" t="n">
-        <v>7.97020387649536</v>
+        <v>7.97020435333252</v>
       </c>
       <c r="H1455" t="n">
         <v>11262</v>
@@ -42622,7 +42622,7 @@
         <v>8.42000007629395</v>
       </c>
       <c r="G1457" t="n">
-        <v>7.89518976211548</v>
+        <v>7.89519023895264</v>
       </c>
       <c r="H1457" t="n">
         <v>3526</v>
@@ -42651,7 +42651,7 @@
         <v>8.36999988555908</v>
       </c>
       <c r="G1458" t="n">
-        <v>7.84830713272095</v>
+        <v>7.84830665588379</v>
       </c>
       <c r="H1458" t="n">
         <v>5445</v>
@@ -42680,7 +42680,7 @@
         <v>8.35000038146973</v>
       </c>
       <c r="G1459" t="n">
-        <v>7.82955408096313</v>
+        <v>7.82955360412598</v>
       </c>
       <c r="H1459" t="n">
         <v>609</v>
@@ -42738,7 +42738,7 @@
         <v>8.23999977111816</v>
       </c>
       <c r="G1461" t="n">
-        <v>7.72640895843506</v>
+        <v>7.72640943527222</v>
       </c>
       <c r="H1461" t="n">
         <v>7810</v>
@@ -42970,7 +42970,7 @@
         <v>8.02000045776367</v>
       </c>
       <c r="G1469" t="n">
-        <v>7.52012252807617</v>
+        <v>7.52012205123901</v>
       </c>
       <c r="H1469" t="n">
         <v>13845</v>
@@ -42999,7 +42999,7 @@
         <v>8</v>
       </c>
       <c r="G1470" t="n">
-        <v>7.50136852264404</v>
+        <v>7.50136804580688</v>
       </c>
       <c r="H1470" t="n">
         <v>17929</v>
@@ -43057,7 +43057,7 @@
         <v>8.5600004196167</v>
       </c>
       <c r="G1472" t="n">
-        <v>8.02646446228027</v>
+        <v>8.02646350860596</v>
       </c>
       <c r="H1472" t="n">
         <v>11278</v>
@@ -43086,7 +43086,7 @@
         <v>8.72999954223633</v>
       </c>
       <c r="G1473" t="n">
-        <v>8.18586730957031</v>
+        <v>8.185866355896</v>
       </c>
       <c r="H1473" t="n">
         <v>27107</v>
@@ -43115,7 +43115,7 @@
         <v>8.51000022888184</v>
       </c>
       <c r="G1474" t="n">
-        <v>7.97958135604858</v>
+        <v>7.97958040237427</v>
       </c>
       <c r="H1474" t="n">
         <v>17996</v>
@@ -43144,7 +43144,7 @@
         <v>8.31999969482422</v>
       </c>
       <c r="G1475" t="n">
-        <v>7.80142259597778</v>
+        <v>7.80142307281494</v>
       </c>
       <c r="H1475" t="n">
         <v>6885</v>
@@ -43173,7 +43173,7 @@
         <v>8.59000015258789</v>
       </c>
       <c r="G1476" t="n">
-        <v>8.05459403991699</v>
+        <v>8.05459499359131</v>
       </c>
       <c r="H1476" t="n">
         <v>5022</v>
@@ -43202,7 +43202,7 @@
         <v>8.5</v>
       </c>
       <c r="G1477" t="n">
-        <v>7.97020387649536</v>
+        <v>7.97020435333252</v>
       </c>
       <c r="H1477" t="n">
         <v>3960</v>
@@ -43289,7 +43289,7 @@
         <v>8.55000019073486</v>
       </c>
       <c r="G1480" t="n">
-        <v>8.01708698272705</v>
+        <v>8.01708793640137</v>
       </c>
       <c r="H1480" t="n">
         <v>5594</v>
@@ -43318,7 +43318,7 @@
         <v>8.61999988555908</v>
       </c>
       <c r="G1481" t="n">
-        <v>8.08272361755371</v>
+        <v>8.08272457122803</v>
       </c>
       <c r="H1481" t="n">
         <v>4281</v>
@@ -43376,7 +43376,7 @@
         <v>8.71000003814697</v>
       </c>
       <c r="G1483" t="n">
-        <v>8.1671142578125</v>
+        <v>8.16711521148682</v>
       </c>
       <c r="H1483" t="n">
         <v>2852</v>
@@ -43405,7 +43405,7 @@
         <v>8.5</v>
       </c>
       <c r="G1484" t="n">
-        <v>7.97020387649536</v>
+        <v>7.97020435333252</v>
       </c>
       <c r="H1484" t="n">
         <v>2454</v>
@@ -43579,7 +43579,7 @@
         <v>8.34000015258789</v>
       </c>
       <c r="G1490" t="n">
-        <v>7.82017707824707</v>
+        <v>7.82017660140991</v>
       </c>
       <c r="H1490" t="n">
         <v>9472</v>
@@ -43637,7 +43637,7 @@
         <v>8.23999977111816</v>
       </c>
       <c r="G1492" t="n">
-        <v>7.72640895843506</v>
+        <v>7.72640943527222</v>
       </c>
       <c r="H1492" t="n">
         <v>7241</v>
@@ -43753,7 +43753,7 @@
         <v>8.35999965667725</v>
       </c>
       <c r="G1496" t="n">
-        <v>7.83892917633057</v>
+        <v>7.83892965316772</v>
       </c>
       <c r="H1496" t="n">
         <v>3456</v>
@@ -43811,7 +43811,7 @@
         <v>8.36999988555908</v>
       </c>
       <c r="G1498" t="n">
-        <v>7.84830713272095</v>
+        <v>7.84830665588379</v>
       </c>
       <c r="H1498" t="n">
         <v>7184</v>
@@ -43869,7 +43869,7 @@
         <v>8.4399995803833</v>
       </c>
       <c r="G1500" t="n">
-        <v>7.91394329071045</v>
+        <v>7.91394281387329</v>
       </c>
       <c r="H1500" t="n">
         <v>5123</v>
@@ -44014,7 +44014,7 @@
         <v>8.35000038146973</v>
       </c>
       <c r="G1505" t="n">
-        <v>7.82955408096313</v>
+        <v>7.82955360412598</v>
       </c>
       <c r="H1505" t="n">
         <v>4398</v>
@@ -44188,7 +44188,7 @@
         <v>7.88000011444092</v>
       </c>
       <c r="G1511" t="n">
-        <v>7.38884830474854</v>
+        <v>7.38884782791138</v>
       </c>
       <c r="H1511" t="n">
         <v>4797</v>
@@ -44217,7 +44217,7 @@
         <v>7.96000003814697</v>
       </c>
       <c r="G1512" t="n">
-        <v>7.46386194229126</v>
+        <v>7.4638614654541</v>
       </c>
       <c r="H1512" t="n">
         <v>1387</v>
@@ -44246,7 +44246,7 @@
         <v>7.80000019073486</v>
       </c>
       <c r="G1513" t="n">
-        <v>7.31383419036865</v>
+        <v>7.31383371353149</v>
       </c>
       <c r="H1513" t="n">
         <v>662</v>
@@ -44275,7 +44275,7 @@
         <v>7.90000009536743</v>
       </c>
       <c r="G1514" t="n">
-        <v>7.40760135650635</v>
+        <v>7.40760087966919</v>
       </c>
       <c r="H1514" t="n">
         <v>2950</v>
@@ -44304,7 +44304,7 @@
         <v>7.80000019073486</v>
       </c>
       <c r="G1515" t="n">
-        <v>7.31383419036865</v>
+        <v>7.31383371353149</v>
       </c>
       <c r="H1515" t="n">
         <v>4982</v>
@@ -44362,7 +44362,7 @@
         <v>8</v>
       </c>
       <c r="G1517" t="n">
-        <v>7.50136852264404</v>
+        <v>7.50136804580688</v>
       </c>
       <c r="H1517" t="n">
         <v>2609</v>
@@ -44391,7 +44391,7 @@
         <v>8</v>
       </c>
       <c r="G1518" t="n">
-        <v>7.50136852264404</v>
+        <v>7.50136804580688</v>
       </c>
       <c r="H1518" t="n">
         <v>438</v>
@@ -44449,7 +44449,7 @@
         <v>7.69999980926514</v>
       </c>
       <c r="G1520" t="n">
-        <v>7.22006702423096</v>
+        <v>7.2200665473938</v>
       </c>
       <c r="H1520" t="n">
         <v>7075</v>
@@ -44478,7 +44478,7 @@
         <v>7.55000019073486</v>
       </c>
       <c r="G1521" t="n">
-        <v>7.07941627502441</v>
+        <v>7.07941675186157</v>
       </c>
       <c r="H1521" t="n">
         <v>1148</v>
@@ -44507,7 +44507,7 @@
         <v>7.53000020980835</v>
       </c>
       <c r="G1522" t="n">
-        <v>7.06066274642944</v>
+        <v>7.0606632232666</v>
       </c>
       <c r="H1522" t="n">
         <v>4031</v>
@@ -44594,7 +44594,7 @@
         <v>7.57999992370605</v>
       </c>
       <c r="G1525" t="n">
-        <v>7.10754680633545</v>
+        <v>7.10754632949829</v>
       </c>
       <c r="H1525" t="n">
         <v>15647</v>
@@ -44855,7 +44855,7 @@
         <v>7.6399998664856</v>
       </c>
       <c r="G1534" t="n">
-        <v>7.16380643844604</v>
+        <v>7.16380596160889</v>
       </c>
       <c r="H1534" t="n">
         <v>7564</v>
@@ -44913,7 +44913,7 @@
         <v>7.69999980926514</v>
       </c>
       <c r="G1536" t="n">
-        <v>7.22006702423096</v>
+        <v>7.2200665473938</v>
       </c>
       <c r="H1536" t="n">
         <v>5350</v>
@@ -45029,7 +45029,7 @@
         <v>7.69999980926514</v>
       </c>
       <c r="G1540" t="n">
-        <v>7.22006702423096</v>
+        <v>7.2200665473938</v>
       </c>
       <c r="H1540" t="n">
         <v>2307</v>
@@ -45058,7 +45058,7 @@
         <v>7.98000001907349</v>
       </c>
       <c r="G1541" t="n">
-        <v>7.48261499404907</v>
+        <v>7.48261451721191</v>
       </c>
       <c r="H1541" t="n">
         <v>47536</v>
@@ -45087,7 +45087,7 @@
         <v>7.96000003814697</v>
       </c>
       <c r="G1542" t="n">
-        <v>7.46386194229126</v>
+        <v>7.4638614654541</v>
       </c>
       <c r="H1542" t="n">
         <v>2633</v>
@@ -45116,7 +45116,7 @@
         <v>8.28999996185303</v>
       </c>
       <c r="G1543" t="n">
-        <v>7.77329301834106</v>
+        <v>7.77329254150391</v>
       </c>
       <c r="H1543" t="n">
         <v>12100</v>
@@ -45203,7 +45203,7 @@
         <v>7.80000019073486</v>
       </c>
       <c r="G1546" t="n">
-        <v>7.31383419036865</v>
+        <v>7.31383371353149</v>
       </c>
       <c r="H1546" t="n">
         <v>5724</v>
@@ -45232,7 +45232,7 @@
         <v>7.82000017166138</v>
       </c>
       <c r="G1547" t="n">
-        <v>7.33258771896362</v>
+        <v>7.33258724212646</v>
       </c>
       <c r="H1547" t="n">
         <v>4523</v>
@@ -45406,7 +45406,7 @@
         <v>8.26000022888184</v>
       </c>
       <c r="G1553" t="n">
-        <v>7.74516248703003</v>
+        <v>7.74516296386719</v>
       </c>
       <c r="H1553" t="n">
         <v>3488</v>
@@ -45464,7 +45464,7 @@
         <v>8.35000038146973</v>
       </c>
       <c r="G1555" t="n">
-        <v>7.82955408096313</v>
+        <v>7.82955360412598</v>
       </c>
       <c r="H1555" t="n">
         <v>6040</v>
@@ -45522,7 +45522,7 @@
         <v>8.28999996185303</v>
       </c>
       <c r="G1557" t="n">
-        <v>7.77329301834106</v>
+        <v>7.77329254150391</v>
       </c>
       <c r="H1557" t="n">
         <v>1372</v>
@@ -45551,7 +45551,7 @@
         <v>8.35000038146973</v>
       </c>
       <c r="G1558" t="n">
-        <v>7.82955408096313</v>
+        <v>7.82955360412598</v>
       </c>
       <c r="H1558" t="n">
         <v>1827</v>
@@ -45580,7 +45580,7 @@
         <v>8.35000038146973</v>
       </c>
       <c r="G1559" t="n">
-        <v>7.82955408096313</v>
+        <v>7.82955360412598</v>
       </c>
       <c r="H1559" t="n">
         <v>240</v>
@@ -45638,7 +45638,7 @@
         <v>8.28999996185303</v>
       </c>
       <c r="G1561" t="n">
-        <v>7.77329301834106</v>
+        <v>7.77329254150391</v>
       </c>
       <c r="H1561" t="n">
         <v>1367</v>
@@ -45667,7 +45667,7 @@
         <v>8.28999996185303</v>
       </c>
       <c r="G1562" t="n">
-        <v>7.77329301834106</v>
+        <v>7.77329254150391</v>
       </c>
       <c r="H1562" t="n">
         <v>58</v>
@@ -45725,7 +45725,7 @@
         <v>8.31999969482422</v>
       </c>
       <c r="G1564" t="n">
-        <v>7.80142259597778</v>
+        <v>7.80142307281494</v>
       </c>
       <c r="H1564" t="n">
         <v>42119</v>
@@ -45812,7 +45812,7 @@
         <v>8.35999965667725</v>
       </c>
       <c r="G1567" t="n">
-        <v>7.83892917633057</v>
+        <v>7.83892965316772</v>
       </c>
       <c r="H1567" t="n">
         <v>10959</v>
@@ -46015,7 +46015,7 @@
         <v>8.28999996185303</v>
       </c>
       <c r="G1574" t="n">
-        <v>7.77329301834106</v>
+        <v>7.77329254150391</v>
       </c>
       <c r="H1574" t="n">
         <v>64</v>
@@ -46073,7 +46073,7 @@
         <v>8.5</v>
       </c>
       <c r="G1576" t="n">
-        <v>7.97020387649536</v>
+        <v>7.97020435333252</v>
       </c>
       <c r="H1576" t="n">
         <v>6863</v>
@@ -46131,7 +46131,7 @@
         <v>8.34000015258789</v>
       </c>
       <c r="G1578" t="n">
-        <v>7.82017707824707</v>
+        <v>7.82017660140991</v>
       </c>
       <c r="H1578" t="n">
         <v>250</v>
@@ -46160,7 +46160,7 @@
         <v>8.35000038146973</v>
       </c>
       <c r="G1579" t="n">
-        <v>7.82955408096313</v>
+        <v>7.82955360412598</v>
       </c>
       <c r="H1579" t="n">
         <v>2100</v>
@@ -46218,7 +46218,7 @@
         <v>8.31999969482422</v>
       </c>
       <c r="G1581" t="n">
-        <v>7.80142259597778</v>
+        <v>7.80142307281494</v>
       </c>
       <c r="H1581" t="n">
         <v>4632</v>
@@ -46276,7 +46276,7 @@
         <v>8.31999969482422</v>
       </c>
       <c r="G1583" t="n">
-        <v>7.80142259597778</v>
+        <v>7.80142307281494</v>
       </c>
       <c r="H1583" t="n">
         <v>218</v>
@@ -46305,7 +46305,7 @@
         <v>8.26000022888184</v>
       </c>
       <c r="G1584" t="n">
-        <v>7.74516248703003</v>
+        <v>7.74516296386719</v>
       </c>
       <c r="H1584" t="n">
         <v>4844</v>
@@ -46363,7 +46363,7 @@
         <v>8.23999977111816</v>
       </c>
       <c r="G1586" t="n">
-        <v>7.72640895843506</v>
+        <v>7.72640943527222</v>
       </c>
       <c r="H1586" t="n">
         <v>370</v>
@@ -46392,7 +46392,7 @@
         <v>8.23999977111816</v>
       </c>
       <c r="G1587" t="n">
-        <v>7.72640895843506</v>
+        <v>7.72640943527222</v>
       </c>
       <c r="H1587" t="n">
         <v>1309</v>
@@ -46856,7 +46856,7 @@
         <v>8.11999988555908</v>
       </c>
       <c r="G1603" t="n">
-        <v>7.61388826370239</v>
+        <v>7.61388874053955</v>
       </c>
       <c r="H1603" t="n">
         <v>369</v>
@@ -47088,7 +47088,7 @@
         <v>8.02000045776367</v>
       </c>
       <c r="G1611" t="n">
-        <v>7.52012252807617</v>
+        <v>7.52012205123901</v>
       </c>
       <c r="H1611" t="n">
         <v>3266</v>
@@ -47320,7 +47320,7 @@
         <v>8.23999977111816</v>
       </c>
       <c r="G1619" t="n">
-        <v>7.72640895843506</v>
+        <v>7.72640943527222</v>
       </c>
       <c r="H1619" t="n">
         <v>22090</v>
@@ -47349,7 +47349,7 @@
         <v>8.26000022888184</v>
       </c>
       <c r="G1620" t="n">
-        <v>7.74516248703003</v>
+        <v>7.74516296386719</v>
       </c>
       <c r="H1620" t="n">
         <v>9204</v>
@@ -47407,7 +47407,7 @@
         <v>8.31999969482422</v>
       </c>
       <c r="G1622" t="n">
-        <v>7.80142259597778</v>
+        <v>7.80142307281494</v>
       </c>
       <c r="H1622" t="n">
         <v>39241</v>
@@ -47697,7 +47697,7 @@
         <v>8.31999969482422</v>
       </c>
       <c r="G1632" t="n">
-        <v>7.80142259597778</v>
+        <v>7.80142307281494</v>
       </c>
       <c r="H1632" t="n">
         <v>3163</v>
@@ -47726,7 +47726,7 @@
         <v>8.31999969482422</v>
       </c>
       <c r="G1633" t="n">
-        <v>7.80142259597778</v>
+        <v>7.80142307281494</v>
       </c>
       <c r="H1633" t="n">
         <v>6253</v>
@@ -47871,7 +47871,7 @@
         <v>8.34000015258789</v>
       </c>
       <c r="G1638" t="n">
-        <v>7.82017707824707</v>
+        <v>7.82017660140991</v>
       </c>
       <c r="H1638" t="n">
         <v>16528</v>
@@ -48016,7 +48016,7 @@
         <v>8.35999965667725</v>
       </c>
       <c r="G1643" t="n">
-        <v>7.83892917633057</v>
+        <v>7.83892965316772</v>
       </c>
       <c r="H1643" t="n">
         <v>14035</v>
@@ -48074,7 +48074,7 @@
         <v>8.31999969482422</v>
       </c>
       <c r="G1645" t="n">
-        <v>7.80142259597778</v>
+        <v>7.80142307281494</v>
       </c>
       <c r="H1645" t="n">
         <v>3390</v>
@@ -48103,7 +48103,7 @@
         <v>8.36999988555908</v>
       </c>
       <c r="G1646" t="n">
-        <v>7.84830713272095</v>
+        <v>7.84830665588379</v>
       </c>
       <c r="H1646" t="n">
         <v>16906</v>
@@ -48132,7 +48132,7 @@
         <v>8.35000038146973</v>
       </c>
       <c r="G1647" t="n">
-        <v>7.82955408096313</v>
+        <v>7.82955360412598</v>
       </c>
       <c r="H1647" t="n">
         <v>4322</v>
@@ -48190,7 +48190,7 @@
         <v>8.31999969482422</v>
       </c>
       <c r="G1649" t="n">
-        <v>7.80142259597778</v>
+        <v>7.80142307281494</v>
       </c>
       <c r="H1649" t="n">
         <v>1791</v>
@@ -48219,7 +48219,7 @@
         <v>8.35000038146973</v>
       </c>
       <c r="G1650" t="n">
-        <v>7.82955408096313</v>
+        <v>7.82955360412598</v>
       </c>
       <c r="H1650" t="n">
         <v>4718</v>
@@ -48248,7 +48248,7 @@
         <v>8.34000015258789</v>
       </c>
       <c r="G1651" t="n">
-        <v>7.82017707824707</v>
+        <v>7.82017660140991</v>
       </c>
       <c r="H1651" t="n">
         <v>5002</v>
@@ -48306,7 +48306,7 @@
         <v>8.35999965667725</v>
       </c>
       <c r="G1653" t="n">
-        <v>7.83892917633057</v>
+        <v>7.83892965316772</v>
       </c>
       <c r="H1653" t="n">
         <v>19707</v>
@@ -48335,7 +48335,7 @@
         <v>8.35000038146973</v>
       </c>
       <c r="G1654" t="n">
-        <v>7.82955408096313</v>
+        <v>7.82955360412598</v>
       </c>
       <c r="H1654" t="n">
         <v>2310</v>
@@ -48538,7 +48538,7 @@
         <v>7.98000001907349</v>
       </c>
       <c r="G1661" t="n">
-        <v>7.48261499404907</v>
+        <v>7.48261451721191</v>
       </c>
       <c r="H1661" t="n">
         <v>3071</v>
@@ -48596,7 +48596,7 @@
         <v>7.55000019073486</v>
       </c>
       <c r="G1663" t="n">
-        <v>7.07941627502441</v>
+        <v>7.07941675186157</v>
       </c>
       <c r="H1663" t="n">
         <v>8336</v>
@@ -48625,7 +48625,7 @@
         <v>7.55000019073486</v>
       </c>
       <c r="G1664" t="n">
-        <v>7.07941627502441</v>
+        <v>7.07941675186157</v>
       </c>
       <c r="H1664" t="n">
         <v>4363</v>
@@ -48654,7 +48654,7 @@
         <v>7.82000017166138</v>
       </c>
       <c r="G1665" t="n">
-        <v>7.33258771896362</v>
+        <v>7.33258724212646</v>
       </c>
       <c r="H1665" t="n">
         <v>11862</v>
@@ -48741,7 +48741,7 @@
         <v>7.44999980926514</v>
       </c>
       <c r="G1668" t="n">
-        <v>6.98564910888672</v>
+        <v>6.98564863204956</v>
       </c>
       <c r="H1668" t="n">
         <v>3310</v>
@@ -48770,7 +48770,7 @@
         <v>7.44999980926514</v>
       </c>
       <c r="G1669" t="n">
-        <v>6.98564910888672</v>
+        <v>6.98564863204956</v>
       </c>
       <c r="H1669" t="n">
         <v>7993</v>
@@ -48828,7 +48828,7 @@
         <v>7.44999980926514</v>
       </c>
       <c r="G1671" t="n">
-        <v>6.98564910888672</v>
+        <v>6.98564863204956</v>
       </c>
       <c r="H1671" t="n">
         <v>24714</v>
@@ -48915,7 +48915,7 @@
         <v>7.40000009536743</v>
       </c>
       <c r="G1674" t="n">
-        <v>6.93876600265503</v>
+        <v>6.93876552581787</v>
       </c>
       <c r="H1674" t="n">
         <v>15401</v>
@@ -48944,7 +48944,7 @@
         <v>7.40000009536743</v>
       </c>
       <c r="G1675" t="n">
-        <v>6.93876600265503</v>
+        <v>6.93876552581787</v>
       </c>
       <c r="H1675" t="n">
         <v>118167</v>
@@ -49002,7 +49002,7 @@
         <v>8.26000022888184</v>
       </c>
       <c r="G1677" t="n">
-        <v>7.85126113891602</v>
+        <v>7.85126161575317</v>
       </c>
       <c r="H1677" t="n">
         <v>20296</v>
@@ -49060,7 +49060,7 @@
         <v>8.31999969482422</v>
       </c>
       <c r="G1679" t="n">
-        <v>7.90829038619995</v>
+        <v>7.90829086303711</v>
       </c>
       <c r="H1679" t="n">
         <v>2625</v>
@@ -49089,7 +49089,7 @@
         <v>8.27000045776367</v>
       </c>
       <c r="G1680" t="n">
-        <v>7.86076641082764</v>
+        <v>7.86076688766479</v>
       </c>
       <c r="H1680" t="n">
         <v>6258</v>
@@ -49147,7 +49147,7 @@
         <v>8.35000038146973</v>
       </c>
       <c r="G1682" t="n">
-        <v>7.93680763244629</v>
+        <v>7.93680715560913</v>
       </c>
       <c r="H1682" t="n">
         <v>4613</v>
@@ -49205,7 +49205,7 @@
         <v>8.35000038146973</v>
       </c>
       <c r="G1684" t="n">
-        <v>7.93680763244629</v>
+        <v>7.93680715560913</v>
       </c>
       <c r="H1684" t="n">
         <v>3977</v>
@@ -49263,7 +49263,7 @@
         <v>8.31999969482422</v>
       </c>
       <c r="G1686" t="n">
-        <v>7.90829038619995</v>
+        <v>7.90829086303711</v>
       </c>
       <c r="H1686" t="n">
         <v>890</v>
@@ -49292,7 +49292,7 @@
         <v>8.32999992370605</v>
       </c>
       <c r="G1687" t="n">
-        <v>7.91779613494873</v>
+        <v>7.91779661178589</v>
       </c>
       <c r="H1687" t="n">
         <v>1780</v>
@@ -49321,7 +49321,7 @@
         <v>8.35000038146973</v>
       </c>
       <c r="G1688" t="n">
-        <v>7.93680763244629</v>
+        <v>7.93680715560913</v>
       </c>
       <c r="H1688" t="n">
         <v>4087</v>
@@ -49379,7 +49379,7 @@
         <v>8.32999992370605</v>
       </c>
       <c r="G1690" t="n">
-        <v>7.91779613494873</v>
+        <v>7.91779661178589</v>
       </c>
       <c r="H1690" t="n">
         <v>1983</v>
@@ -49408,7 +49408,7 @@
         <v>8.35000038146973</v>
       </c>
       <c r="G1691" t="n">
-        <v>7.93680763244629</v>
+        <v>7.93680715560913</v>
       </c>
       <c r="H1691" t="n">
         <v>509</v>
@@ -49495,7 +49495,7 @@
         <v>8.25</v>
       </c>
       <c r="G1694" t="n">
-        <v>7.84175634384155</v>
+        <v>7.84175586700439</v>
       </c>
       <c r="H1694" t="n">
         <v>1286</v>
@@ -49524,7 +49524,7 @@
         <v>8.31999969482422</v>
       </c>
       <c r="G1695" t="n">
-        <v>7.90829038619995</v>
+        <v>7.90829086303711</v>
       </c>
       <c r="H1695" t="n">
         <v>2041</v>
@@ -49582,7 +49582,7 @@
         <v>8.26000022888184</v>
       </c>
       <c r="G1697" t="n">
-        <v>7.85126113891602</v>
+        <v>7.85126161575317</v>
       </c>
       <c r="H1697" t="n">
         <v>2593</v>
@@ -49785,7 +49785,7 @@
         <v>7.90000009536743</v>
       </c>
       <c r="G1704" t="n">
-        <v>7.50907564163208</v>
+        <v>7.50907516479492</v>
       </c>
       <c r="H1704" t="n">
         <v>418</v>
@@ -49814,7 +49814,7 @@
         <v>8</v>
       </c>
       <c r="G1705" t="n">
-        <v>7.60412645339966</v>
+        <v>7.60412693023682</v>
       </c>
       <c r="H1705" t="n">
         <v>276</v>
@@ -49843,7 +49843,7 @@
         <v>8.27999973297119</v>
       </c>
       <c r="G1706" t="n">
-        <v>7.87027072906494</v>
+        <v>7.8702712059021</v>
       </c>
       <c r="H1706" t="n">
         <v>2197</v>
@@ -49930,7 +49930,7 @@
         <v>8.10999965667725</v>
       </c>
       <c r="G1709" t="n">
-        <v>7.70868301391602</v>
+        <v>7.70868253707886</v>
       </c>
       <c r="H1709" t="n">
         <v>3380</v>
@@ -49959,7 +49959,7 @@
         <v>8.03999996185303</v>
       </c>
       <c r="G1710" t="n">
-        <v>7.64214706420898</v>
+        <v>7.64214754104614</v>
       </c>
       <c r="H1710" t="n">
         <v>14944</v>
@@ -50017,7 +50017,7 @@
         <v>8.11999988555908</v>
       </c>
       <c r="G1712" t="n">
-        <v>7.71818828582764</v>
+        <v>7.71818876266479</v>
       </c>
       <c r="H1712" t="n">
         <v>2868</v>
@@ -50104,7 +50104,7 @@
         <v>8.06999969482422</v>
       </c>
       <c r="G1715" t="n">
-        <v>7.67066287994385</v>
+        <v>7.67066240310669</v>
       </c>
       <c r="H1715" t="n">
         <v>3573</v>
@@ -50278,7 +50278,7 @@
         <v>7.98999977111816</v>
       </c>
       <c r="G1721" t="n">
-        <v>7.59462118148804</v>
+        <v>7.5946216583252</v>
       </c>
       <c r="H1721" t="n">
         <v>3549</v>
@@ -50365,7 +50365,7 @@
         <v>8</v>
       </c>
       <c r="G1724" t="n">
-        <v>7.60412645339966</v>
+        <v>7.60412693023682</v>
       </c>
       <c r="H1724" t="n">
         <v>13949</v>
@@ -50423,7 +50423,7 @@
         <v>8.03999996185303</v>
       </c>
       <c r="G1726" t="n">
-        <v>7.64214706420898</v>
+        <v>7.64214754104614</v>
       </c>
       <c r="H1726" t="n">
         <v>2161</v>
@@ -50510,7 +50510,7 @@
         <v>8.06999969482422</v>
       </c>
       <c r="G1729" t="n">
-        <v>7.67066287994385</v>
+        <v>7.67066240310669</v>
       </c>
       <c r="H1729" t="n">
         <v>32727</v>
@@ -50539,7 +50539,7 @@
         <v>7.98999977111816</v>
       </c>
       <c r="G1730" t="n">
-        <v>7.59462118148804</v>
+        <v>7.5946216583252</v>
       </c>
       <c r="H1730" t="n">
         <v>5160</v>
@@ -50771,7 +50771,7 @@
         <v>8.15999984741211</v>
       </c>
       <c r="G1738" t="n">
-        <v>7.75620889663696</v>
+        <v>7.75620937347412</v>
       </c>
       <c r="H1738" t="n">
         <v>2476</v>
@@ -50800,7 +50800,7 @@
         <v>8.11999988555908</v>
       </c>
       <c r="G1739" t="n">
-        <v>7.71818828582764</v>
+        <v>7.71818876266479</v>
       </c>
       <c r="H1739" t="n">
         <v>1132</v>
@@ -50829,7 +50829,7 @@
         <v>8.11999988555908</v>
       </c>
       <c r="G1740" t="n">
-        <v>7.71818828582764</v>
+        <v>7.71818876266479</v>
       </c>
       <c r="H1740" t="n">
         <v>824</v>
@@ -50858,7 +50858,7 @@
         <v>8</v>
       </c>
       <c r="G1741" t="n">
-        <v>7.60412645339966</v>
+        <v>7.60412693023682</v>
       </c>
       <c r="H1741" t="n">
         <v>2628</v>
@@ -51003,7 +51003,7 @@
         <v>7.98999977111816</v>
       </c>
       <c r="G1746" t="n">
-        <v>7.59462118148804</v>
+        <v>7.5946216583252</v>
       </c>
       <c r="H1746" t="n">
         <v>5006</v>
@@ -51061,7 +51061,7 @@
         <v>8.27999973297119</v>
       </c>
       <c r="G1748" t="n">
-        <v>7.87027072906494</v>
+        <v>7.8702712059021</v>
       </c>
       <c r="H1748" t="n">
         <v>17226</v>
@@ -51090,7 +51090,7 @@
         <v>8.27999973297119</v>
       </c>
       <c r="G1749" t="n">
-        <v>7.87027072906494</v>
+        <v>7.8702712059021</v>
       </c>
       <c r="H1749" t="n">
         <v>1982</v>
@@ -51119,7 +51119,7 @@
         <v>8.27999973297119</v>
       </c>
       <c r="G1750" t="n">
-        <v>7.87027072906494</v>
+        <v>7.8702712059021</v>
       </c>
       <c r="H1750" t="n">
         <v>3817</v>
@@ -51206,7 +51206,7 @@
         <v>8.36999988555908</v>
       </c>
       <c r="G1753" t="n">
-        <v>7.95581722259521</v>
+        <v>7.95581674575806</v>
       </c>
       <c r="H1753" t="n">
         <v>4823</v>
@@ -51351,7 +51351,7 @@
         <v>8.40999984741211</v>
       </c>
       <c r="G1758" t="n">
-        <v>7.99383783340454</v>
+        <v>7.99383735656738</v>
       </c>
       <c r="H1758" t="n">
         <v>6538</v>
@@ -51380,7 +51380,7 @@
         <v>8.43000030517578</v>
       </c>
       <c r="G1759" t="n">
-        <v>8.01284885406494</v>
+        <v>8.01284790039062</v>
       </c>
       <c r="H1759" t="n">
         <v>12759</v>
@@ -51438,7 +51438,7 @@
         <v>8.39000034332275</v>
       </c>
       <c r="G1761" t="n">
-        <v>7.97482824325562</v>
+        <v>7.97482776641846</v>
       </c>
       <c r="H1761" t="n">
         <v>6571</v>
@@ -51496,7 +51496,7 @@
         <v>8.3100004196167</v>
       </c>
       <c r="G1763" t="n">
-        <v>7.89878702163696</v>
+        <v>7.8987865447998</v>
       </c>
       <c r="H1763" t="n">
         <v>7835</v>
@@ -51554,7 +51554,7 @@
         <v>8.26000022888184</v>
       </c>
       <c r="G1765" t="n">
-        <v>7.85126113891602</v>
+        <v>7.85126161575317</v>
       </c>
       <c r="H1765" t="n">
         <v>4626</v>
@@ -51583,7 +51583,7 @@
         <v>8.32999992370605</v>
       </c>
       <c r="G1766" t="n">
-        <v>7.91779613494873</v>
+        <v>7.91779661178589</v>
       </c>
       <c r="H1766" t="n">
         <v>5614</v>
@@ -51641,7 +51641,7 @@
         <v>8.11999988555908</v>
       </c>
       <c r="G1768" t="n">
-        <v>7.71818828582764</v>
+        <v>7.71818876266479</v>
       </c>
       <c r="H1768" t="n">
         <v>7002</v>
@@ -51670,7 +51670,7 @@
         <v>8.39000034332275</v>
       </c>
       <c r="G1769" t="n">
-        <v>7.97482824325562</v>
+        <v>7.97482776641846</v>
       </c>
       <c r="H1769" t="n">
         <v>7986</v>
@@ -51699,7 +51699,7 @@
         <v>8.27999973297119</v>
       </c>
       <c r="G1770" t="n">
-        <v>7.87027072906494</v>
+        <v>7.8702712059021</v>
       </c>
       <c r="H1770" t="n">
         <v>30419</v>
@@ -51728,7 +51728,7 @@
         <v>8.3100004196167</v>
       </c>
       <c r="G1771" t="n">
-        <v>7.89878702163696</v>
+        <v>7.8987865447998</v>
       </c>
       <c r="H1771" t="n">
         <v>3351</v>
@@ -51989,7 +51989,7 @@
         <v>8</v>
       </c>
       <c r="G1780" t="n">
-        <v>7.60412645339966</v>
+        <v>7.60412693023682</v>
       </c>
       <c r="H1780" t="n">
         <v>2842</v>
@@ -52018,7 +52018,7 @@
         <v>8</v>
       </c>
       <c r="G1781" t="n">
-        <v>7.60412645339966</v>
+        <v>7.60412693023682</v>
       </c>
       <c r="H1781" t="n">
         <v>8165</v>
@@ -52279,7 +52279,7 @@
         <v>7.59999990463257</v>
       </c>
       <c r="G1790" t="n">
-        <v>7.2239203453064</v>
+        <v>7.22391986846924</v>
       </c>
       <c r="H1790" t="n">
         <v>12785</v>
@@ -52308,7 +52308,7 @@
         <v>7.63000011444092</v>
       </c>
       <c r="G1791" t="n">
-        <v>7.2524356842041</v>
+        <v>7.25243616104126</v>
       </c>
       <c r="H1791" t="n">
         <v>1834</v>
@@ -52337,7 +52337,7 @@
         <v>7.63000011444092</v>
       </c>
       <c r="G1792" t="n">
-        <v>7.2524356842041</v>
+        <v>7.25243616104126</v>
       </c>
       <c r="H1792" t="n">
         <v>0</v>
@@ -52366,7 +52366,7 @@
         <v>7.69000005722046</v>
       </c>
       <c r="G1793" t="n">
-        <v>7.30946636199951</v>
+        <v>7.30946683883667</v>
       </c>
       <c r="H1793" t="n">
         <v>995</v>
@@ -52395,7 +52395,7 @@
         <v>7.59999990463257</v>
       </c>
       <c r="G1794" t="n">
-        <v>7.2239203453064</v>
+        <v>7.22391986846924</v>
       </c>
       <c r="H1794" t="n">
         <v>4546</v>
@@ -52540,7 +52540,7 @@
         <v>7.73999977111816</v>
       </c>
       <c r="G1799" t="n">
-        <v>7.35699224472046</v>
+        <v>7.35699272155762</v>
       </c>
       <c r="H1799" t="n">
         <v>3436</v>
@@ -52598,7 +52598,7 @@
         <v>7.90000009536743</v>
       </c>
       <c r="G1801" t="n">
-        <v>7.50907564163208</v>
+        <v>7.50907516479492</v>
       </c>
       <c r="H1801" t="n">
         <v>5821</v>
@@ -52685,7 +52685,7 @@
         <v>7.90000009536743</v>
       </c>
       <c r="G1804" t="n">
-        <v>7.50907564163208</v>
+        <v>7.50907516479492</v>
       </c>
       <c r="H1804" t="n">
         <v>1663</v>
@@ -52714,7 +52714,7 @@
         <v>8</v>
       </c>
       <c r="G1805" t="n">
-        <v>7.60412645339966</v>
+        <v>7.60412693023682</v>
       </c>
       <c r="H1805" t="n">
         <v>6833</v>
@@ -52859,7 +52859,7 @@
         <v>7.94000005722046</v>
       </c>
       <c r="G1810" t="n">
-        <v>7.54709577560425</v>
+        <v>7.54709529876709</v>
       </c>
       <c r="H1810" t="n">
         <v>712</v>
@@ -52917,7 +52917,7 @@
         <v>7.84999990463257</v>
       </c>
       <c r="G1812" t="n">
-        <v>7.46154928207397</v>
+        <v>7.46154880523682</v>
       </c>
       <c r="H1812" t="n">
         <v>3418</v>
@@ -52975,7 +52975,7 @@
         <v>7.94000005722046</v>
       </c>
       <c r="G1814" t="n">
-        <v>7.54709577560425</v>
+        <v>7.54709529876709</v>
       </c>
       <c r="H1814" t="n">
         <v>966</v>
@@ -53062,7 +53062,7 @@
         <v>8.22999954223633</v>
       </c>
       <c r="G1817" t="n">
-        <v>7.82274532318115</v>
+        <v>7.82274484634399</v>
       </c>
       <c r="H1817" t="n">
         <v>5327</v>
@@ -53120,7 +53120,7 @@
         <v>8.36999988555908</v>
       </c>
       <c r="G1819" t="n">
-        <v>7.95581722259521</v>
+        <v>7.95581674575806</v>
       </c>
       <c r="H1819" t="n">
         <v>7425</v>
@@ -53149,7 +53149,7 @@
         <v>8.23999977111816</v>
       </c>
       <c r="G1820" t="n">
-        <v>7.83225059509277</v>
+        <v>7.83225011825562</v>
       </c>
       <c r="H1820" t="n">
         <v>5964</v>
@@ -53236,7 +53236,7 @@
         <v>8.28999996185303</v>
       </c>
       <c r="G1823" t="n">
-        <v>7.87977647781372</v>
+        <v>7.87977695465088</v>
       </c>
       <c r="H1823" t="n">
         <v>8348</v>
@@ -53265,7 +53265,7 @@
         <v>8.36999988555908</v>
       </c>
       <c r="G1824" t="n">
-        <v>7.95581722259521</v>
+        <v>7.95581674575806</v>
       </c>
       <c r="H1824" t="n">
         <v>7224</v>
@@ -53323,7 +53323,7 @@
         <v>8.65999984741211</v>
       </c>
       <c r="G1826" t="n">
-        <v>8.23146724700928</v>
+        <v>8.23146629333496</v>
       </c>
       <c r="H1826" t="n">
         <v>17770</v>
@@ -53352,7 +53352,7 @@
         <v>8.65999984741211</v>
       </c>
       <c r="G1827" t="n">
-        <v>8.23146724700928</v>
+        <v>8.23146629333496</v>
       </c>
       <c r="H1827" t="n">
         <v>35806</v>
@@ -53555,7 +53555,7 @@
         <v>8.75</v>
       </c>
       <c r="G1834" t="n">
-        <v>8.31701278686523</v>
+        <v>8.31701374053955</v>
       </c>
       <c r="H1834" t="n">
         <v>14462</v>
@@ -53584,7 +53584,7 @@
         <v>8.75</v>
       </c>
       <c r="G1835" t="n">
-        <v>8.31701278686523</v>
+        <v>8.31701374053955</v>
       </c>
       <c r="H1835" t="n">
         <v>941</v>
@@ -53700,7 +53700,7 @@
         <v>8.65999984741211</v>
       </c>
       <c r="G1839" t="n">
-        <v>8.23146724700928</v>
+        <v>8.23146629333496</v>
       </c>
       <c r="H1839" t="n">
         <v>3164</v>
@@ -53787,7 +53787,7 @@
         <v>8.89999961853027</v>
       </c>
       <c r="G1842" t="n">
-        <v>8.45959091186523</v>
+        <v>8.45958995819092</v>
       </c>
       <c r="H1842" t="n">
         <v>5908</v>
@@ -53845,7 +53845,7 @@
         <v>8.75</v>
       </c>
       <c r="G1844" t="n">
-        <v>8.31701278686523</v>
+        <v>8.31701374053955</v>
       </c>
       <c r="H1844" t="n">
         <v>1841</v>
@@ -53874,7 +53874,7 @@
         <v>8.71000003814697</v>
       </c>
       <c r="G1845" t="n">
-        <v>8.27899265289307</v>
+        <v>8.27899360656738</v>
       </c>
       <c r="H1845" t="n">
         <v>3095</v>
@@ -53961,7 +53961,7 @@
         <v>8.85000038146973</v>
       </c>
       <c r="G1848" t="n">
-        <v>8.41206645965576</v>
+        <v>8.41206550598145</v>
       </c>
       <c r="H1848" t="n">
         <v>10956</v>
@@ -54048,7 +54048,7 @@
         <v>8.97999954223633</v>
       </c>
       <c r="G1851" t="n">
-        <v>8.53563117980957</v>
+        <v>8.53563213348389</v>
       </c>
       <c r="H1851" t="n">
         <v>4186</v>
@@ -54077,7 +54077,7 @@
         <v>9.0600004196167</v>
       </c>
       <c r="G1852" t="n">
-        <v>8.61167335510254</v>
+        <v>8.61167430877686</v>
       </c>
       <c r="H1852" t="n">
         <v>8723</v>
@@ -54222,7 +54222,7 @@
         <v>8.86999988555908</v>
       </c>
       <c r="G1857" t="n">
-        <v>8.43107509613037</v>
+        <v>8.43107604980469</v>
       </c>
       <c r="H1857" t="n">
         <v>9479</v>
@@ -54309,7 +54309,7 @@
         <v>8.89999961853027</v>
       </c>
       <c r="G1860" t="n">
-        <v>8.45959091186523</v>
+        <v>8.45958995819092</v>
       </c>
       <c r="H1860" t="n">
         <v>476</v>
@@ -54338,7 +54338,7 @@
         <v>8.89999961853027</v>
       </c>
       <c r="G1861" t="n">
-        <v>8.45959091186523</v>
+        <v>8.45958995819092</v>
       </c>
       <c r="H1861" t="n">
         <v>9439</v>
@@ -54396,7 +54396,7 @@
         <v>8.85000038146973</v>
       </c>
       <c r="G1863" t="n">
-        <v>8.41206645965576</v>
+        <v>8.41206550598145</v>
       </c>
       <c r="H1863" t="n">
         <v>12301</v>
@@ -54425,7 +54425,7 @@
         <v>8.85000038146973</v>
       </c>
       <c r="G1864" t="n">
-        <v>8.41206645965576</v>
+        <v>8.41206550598145</v>
       </c>
       <c r="H1864" t="n">
         <v>5902</v>
@@ -54599,7 +54599,7 @@
         <v>8.85000038146973</v>
       </c>
       <c r="G1870" t="n">
-        <v>8.41206645965576</v>
+        <v>8.41206550598145</v>
       </c>
       <c r="H1870" t="n">
         <v>1247</v>
@@ -54628,7 +54628,7 @@
         <v>8.93000030517578</v>
       </c>
       <c r="G1871" t="n">
-        <v>8.4881067276001</v>
+        <v>8.48810577392578</v>
       </c>
       <c r="H1871" t="n">
         <v>10048</v>
@@ -54657,7 +54657,7 @@
         <v>8.89999961853027</v>
       </c>
       <c r="G1872" t="n">
-        <v>8.45959091186523</v>
+        <v>8.45958995819092</v>
       </c>
       <c r="H1872" t="n">
         <v>3615</v>
@@ -54773,7 +54773,7 @@
         <v>8.59000015258789</v>
       </c>
       <c r="G1876" t="n">
-        <v>8.16493129730225</v>
+        <v>8.16493034362793</v>
       </c>
       <c r="H1876" t="n">
         <v>2645</v>
@@ -54802,7 +54802,7 @@
         <v>8.44999980926514</v>
       </c>
       <c r="G1877" t="n">
-        <v>8.03185844421387</v>
+        <v>8.03185939788818</v>
       </c>
       <c r="H1877" t="n">
         <v>1800</v>
@@ -54860,7 +54860,7 @@
         <v>8.39000034332275</v>
       </c>
       <c r="G1879" t="n">
-        <v>7.97482824325562</v>
+        <v>7.97482776641846</v>
       </c>
       <c r="H1879" t="n">
         <v>7706</v>
@@ -54889,7 +54889,7 @@
         <v>8.39000034332275</v>
       </c>
       <c r="G1880" t="n">
-        <v>7.97482824325562</v>
+        <v>7.97482776641846</v>
       </c>
       <c r="H1880" t="n">
         <v>4308</v>
@@ -54918,7 +54918,7 @@
         <v>8.27999973297119</v>
       </c>
       <c r="G1881" t="n">
-        <v>7.87027072906494</v>
+        <v>7.8702712059021</v>
       </c>
       <c r="H1881" t="n">
         <v>823</v>
@@ -54976,7 +54976,7 @@
         <v>8.22999954223633</v>
       </c>
       <c r="G1883" t="n">
-        <v>7.82274532318115</v>
+        <v>7.82274484634399</v>
       </c>
       <c r="H1883" t="n">
         <v>463</v>
@@ -55005,7 +55005,7 @@
         <v>8.25</v>
       </c>
       <c r="G1884" t="n">
-        <v>7.84175634384155</v>
+        <v>7.84175586700439</v>
       </c>
       <c r="H1884" t="n">
         <v>6791</v>
@@ -55034,7 +55034,7 @@
         <v>8.26000022888184</v>
       </c>
       <c r="G1885" t="n">
-        <v>7.85126113891602</v>
+        <v>7.85126161575317</v>
       </c>
       <c r="H1885" t="n">
         <v>1714</v>
@@ -55121,7 +55121,7 @@
         <v>8.22999954223633</v>
       </c>
       <c r="G1888" t="n">
-        <v>7.82274532318115</v>
+        <v>7.82274484634399</v>
       </c>
       <c r="H1888" t="n">
         <v>1973</v>
@@ -55150,7 +55150,7 @@
         <v>8.32999992370605</v>
       </c>
       <c r="G1889" t="n">
-        <v>7.91779613494873</v>
+        <v>7.91779661178589</v>
       </c>
       <c r="H1889" t="n">
         <v>577</v>
@@ -55266,7 +55266,7 @@
         <v>8.35000038146973</v>
       </c>
       <c r="G1893" t="n">
-        <v>7.93680763244629</v>
+        <v>7.93680715560913</v>
       </c>
       <c r="H1893" t="n">
         <v>9152</v>
@@ -55411,7 +55411,7 @@
         <v>8.31999969482422</v>
       </c>
       <c r="G1898" t="n">
-        <v>7.90829038619995</v>
+        <v>7.90829086303711</v>
       </c>
       <c r="H1898" t="n">
         <v>33951</v>
@@ -55469,7 +55469,7 @@
         <v>8.31999969482422</v>
       </c>
       <c r="G1900" t="n">
-        <v>7.90829038619995</v>
+        <v>7.90829086303711</v>
       </c>
       <c r="H1900" t="n">
         <v>10485</v>
@@ -55527,7 +55527,7 @@
         <v>8.15999984741211</v>
       </c>
       <c r="G1902" t="n">
-        <v>7.75620889663696</v>
+        <v>7.75620937347412</v>
       </c>
       <c r="H1902" t="n">
         <v>4188</v>
@@ -55556,7 +55556,7 @@
         <v>8.11999988555908</v>
       </c>
       <c r="G1903" t="n">
-        <v>7.71818828582764</v>
+        <v>7.71818876266479</v>
       </c>
       <c r="H1903" t="n">
         <v>4305</v>
@@ -55585,7 +55585,7 @@
         <v>8.27999973297119</v>
       </c>
       <c r="G1904" t="n">
-        <v>7.87027072906494</v>
+        <v>7.8702712059021</v>
       </c>
       <c r="H1904" t="n">
         <v>1338</v>
@@ -55730,7 +55730,7 @@
         <v>8.31999969482422</v>
       </c>
       <c r="G1909" t="n">
-        <v>7.90829038619995</v>
+        <v>7.90829086303711</v>
       </c>
       <c r="H1909" t="n">
         <v>12586</v>
@@ -55904,7 +55904,7 @@
         <v>8.46000003814697</v>
       </c>
       <c r="G1915" t="n">
-        <v>8.04136371612549</v>
+        <v>8.0413646697998</v>
       </c>
       <c r="H1915" t="n">
         <v>11855</v>
@@ -56078,7 +56078,7 @@
         <v>8.47999954223633</v>
       </c>
       <c r="G1921" t="n">
-        <v>8.06037330627441</v>
+        <v>8.06037425994873</v>
       </c>
       <c r="H1921" t="n">
         <v>1956</v>
@@ -56136,7 +56136,7 @@
         <v>8.46000003814697</v>
       </c>
       <c r="G1923" t="n">
-        <v>8.04136371612549</v>
+        <v>8.0413646697998</v>
       </c>
       <c r="H1923" t="n">
         <v>1672</v>
@@ -56165,7 +56165,7 @@
         <v>8.46000003814697</v>
       </c>
       <c r="G1924" t="n">
-        <v>8.04136371612549</v>
+        <v>8.0413646697998</v>
       </c>
       <c r="H1924" t="n">
         <v>1191</v>
@@ -56194,7 +56194,7 @@
         <v>8.47999954223633</v>
       </c>
       <c r="G1925" t="n">
-        <v>8.06037330627441</v>
+        <v>8.06037425994873</v>
       </c>
       <c r="H1925" t="n">
         <v>808</v>
@@ -56600,7 +56600,7 @@
         <v>8.60000038146973</v>
       </c>
       <c r="G1939" t="n">
-        <v>8.29149341583252</v>
+        <v>8.2914924621582</v>
       </c>
       <c r="H1939" t="n">
         <v>17382</v>
@@ -56658,7 +56658,7 @@
         <v>8.80000019073486</v>
       </c>
       <c r="G1941" t="n">
-        <v>8.48431873321533</v>
+        <v>8.48431777954102</v>
       </c>
       <c r="H1941" t="n">
         <v>55725</v>
@@ -56745,7 +56745,7 @@
         <v>8.80000019073486</v>
       </c>
       <c r="G1944" t="n">
-        <v>8.48431873321533</v>
+        <v>8.48431777954102</v>
       </c>
       <c r="H1944" t="n">
         <v>8835</v>
@@ -56803,7 +56803,7 @@
         <v>9</v>
       </c>
       <c r="G1946" t="n">
-        <v>8.67714405059814</v>
+        <v>8.67714309692383</v>
       </c>
       <c r="H1946" t="n">
         <v>17406</v>
@@ -56919,7 +56919,7 @@
         <v>9.03999996185303</v>
       </c>
       <c r="G1950" t="n">
-        <v>8.71570777893066</v>
+        <v>8.71570873260498</v>
       </c>
       <c r="H1950" t="n">
         <v>4890</v>
@@ -57006,7 +57006,7 @@
         <v>9.11999988555908</v>
       </c>
       <c r="G1953" t="n">
-        <v>8.79283905029297</v>
+        <v>8.79283809661865</v>
       </c>
       <c r="H1953" t="n">
         <v>4327</v>
@@ -57093,7 +57093,7 @@
         <v>9.38000011444092</v>
       </c>
       <c r="G1956" t="n">
-        <v>9.04351139068604</v>
+        <v>9.04351234436035</v>
       </c>
       <c r="H1956" t="n">
         <v>7577</v>
@@ -57122,7 +57122,7 @@
         <v>9.30000019073486</v>
       </c>
       <c r="G1957" t="n">
-        <v>8.96638202667236</v>
+        <v>8.96638107299805</v>
       </c>
       <c r="H1957" t="n">
         <v>2349</v>
@@ -57180,7 +57180,7 @@
         <v>9.30000019073486</v>
       </c>
       <c r="G1959" t="n">
-        <v>8.96638202667236</v>
+        <v>8.96638107299805</v>
       </c>
       <c r="H1959" t="n">
         <v>13033</v>
@@ -57209,7 +57209,7 @@
         <v>9.11999988555908</v>
       </c>
       <c r="G1960" t="n">
-        <v>8.79283905029297</v>
+        <v>8.79283809661865</v>
       </c>
       <c r="H1960" t="n">
         <v>3417</v>
@@ -57238,7 +57238,7 @@
         <v>9.30000019073486</v>
       </c>
       <c r="G1961" t="n">
-        <v>8.96638202667236</v>
+        <v>8.96638107299805</v>
       </c>
       <c r="H1961" t="n">
         <v>2683</v>
@@ -57325,7 +57325,7 @@
         <v>9.31999969482422</v>
       </c>
       <c r="G1964" t="n">
-        <v>8.98566436767578</v>
+        <v>8.98566341400146</v>
       </c>
       <c r="H1964" t="n">
         <v>4321</v>
@@ -57383,7 +57383,7 @@
         <v>9.03999996185303</v>
       </c>
       <c r="G1966" t="n">
-        <v>8.71570777893066</v>
+        <v>8.71570873260498</v>
       </c>
       <c r="H1966" t="n">
         <v>13221</v>
@@ -57441,7 +57441,7 @@
         <v>8.84000015258789</v>
       </c>
       <c r="G1968" t="n">
-        <v>8.52288246154785</v>
+        <v>8.52288341522217</v>
       </c>
       <c r="H1968" t="n">
         <v>936</v>
@@ -57528,7 +57528,7 @@
         <v>9</v>
       </c>
       <c r="G1971" t="n">
-        <v>8.67714405059814</v>
+        <v>8.67714309692383</v>
       </c>
       <c r="H1971" t="n">
         <v>2333</v>
@@ -57557,7 +57557,7 @@
         <v>9</v>
       </c>
       <c r="G1972" t="n">
-        <v>8.67714405059814</v>
+        <v>8.67714309692383</v>
       </c>
       <c r="H1972" t="n">
         <v>3757</v>
@@ -57702,7 +57702,7 @@
         <v>8.72000026702881</v>
       </c>
       <c r="G1977" t="n">
-        <v>8.40718841552734</v>
+        <v>8.40718746185303</v>
       </c>
       <c r="H1977" t="n">
         <v>2845</v>
@@ -57760,7 +57760,7 @@
         <v>8.84000015258789</v>
       </c>
       <c r="G1979" t="n">
-        <v>8.52288246154785</v>
+        <v>8.52288341522217</v>
       </c>
       <c r="H1979" t="n">
         <v>1522</v>
@@ -57818,7 +57818,7 @@
         <v>8.80000019073486</v>
       </c>
       <c r="G1981" t="n">
-        <v>8.48431873321533</v>
+        <v>8.48431777954102</v>
       </c>
       <c r="H1981" t="n">
         <v>1001</v>
@@ -57876,7 +57876,7 @@
         <v>8.34000015258789</v>
       </c>
       <c r="G1983" t="n">
-        <v>8.04081916809082</v>
+        <v>8.04082012176514</v>
       </c>
       <c r="H1983" t="n">
         <v>7311</v>
@@ -57905,7 +57905,7 @@
         <v>8.18000030517578</v>
       </c>
       <c r="G1984" t="n">
-        <v>7.88655996322632</v>
+        <v>7.886559009552</v>
       </c>
       <c r="H1984" t="n">
         <v>7410</v>
@@ -57963,7 +57963,7 @@
         <v>8.26000022888184</v>
       </c>
       <c r="G1986" t="n">
-        <v>7.96368980407715</v>
+        <v>7.96368932723999</v>
       </c>
       <c r="H1986" t="n">
         <v>416</v>
@@ -58021,7 +58021,7 @@
         <v>8.15999984741211</v>
       </c>
       <c r="G1988" t="n">
-        <v>7.86727666854858</v>
+        <v>7.86727619171143</v>
       </c>
       <c r="H1988" t="n">
         <v>401</v>
@@ -58050,7 +58050,7 @@
         <v>8.18000030517578</v>
       </c>
       <c r="G1989" t="n">
-        <v>7.88655996322632</v>
+        <v>7.886559009552</v>
       </c>
       <c r="H1989" t="n">
         <v>2524</v>
@@ -58108,7 +58108,7 @@
         <v>8.18000030517578</v>
       </c>
       <c r="G1991" t="n">
-        <v>7.88655996322632</v>
+        <v>7.886559009552</v>
       </c>
       <c r="H1991" t="n">
         <v>380</v>
@@ -58195,7 +58195,7 @@
         <v>8.26000022888184</v>
       </c>
       <c r="G1994" t="n">
-        <v>7.96368980407715</v>
+        <v>7.96368932723999</v>
       </c>
       <c r="H1994" t="n">
         <v>1109</v>
@@ -58282,7 +58282,7 @@
         <v>8.18000030517578</v>
       </c>
       <c r="G1997" t="n">
-        <v>7.88655996322632</v>
+        <v>7.886559009552</v>
       </c>
       <c r="H1997" t="n">
         <v>3978</v>
@@ -58340,7 +58340,7 @@
         <v>8.35999965667725</v>
       </c>
       <c r="G1999" t="n">
-        <v>8.06010150909424</v>
+        <v>8.06010246276855</v>
       </c>
       <c r="H1999" t="n">
         <v>746</v>
@@ -58398,7 +58398,7 @@
         <v>8.19999980926514</v>
       </c>
       <c r="G2001" t="n">
-        <v>7.90584182739258</v>
+        <v>7.90584135055542</v>
       </c>
       <c r="H2001" t="n">
         <v>12373</v>
@@ -58427,7 +58427,7 @@
         <v>8.35999965667725</v>
       </c>
       <c r="G2002" t="n">
-        <v>8.06010150909424</v>
+        <v>8.06010246276855</v>
       </c>
       <c r="H2002" t="n">
         <v>1852</v>
@@ -58456,7 +58456,7 @@
         <v>8.26000022888184</v>
       </c>
       <c r="G2003" t="n">
-        <v>7.96368980407715</v>
+        <v>7.96368932723999</v>
       </c>
       <c r="H2003" t="n">
         <v>1076</v>
@@ -58485,7 +58485,7 @@
         <v>8.23999977111816</v>
       </c>
       <c r="G2004" t="n">
-        <v>7.94440650939941</v>
+        <v>7.94440603256226</v>
       </c>
       <c r="H2004" t="n">
         <v>1587</v>
@@ -58572,7 +58572,7 @@
         <v>8.34000015258789</v>
       </c>
       <c r="G2007" t="n">
-        <v>8.04081916809082</v>
+        <v>8.04082012176514</v>
       </c>
       <c r="H2007" t="n">
         <v>2756</v>
@@ -58601,7 +58601,7 @@
         <v>8.15999984741211</v>
       </c>
       <c r="G2008" t="n">
-        <v>7.86727666854858</v>
+        <v>7.86727619171143</v>
       </c>
       <c r="H2008" t="n">
         <v>2869</v>
@@ -58688,7 +58688,7 @@
         <v>8.23999977111816</v>
       </c>
       <c r="G2011" t="n">
-        <v>7.94440650939941</v>
+        <v>7.94440603256226</v>
       </c>
       <c r="H2011" t="n">
         <v>246</v>
@@ -58746,7 +58746,7 @@
         <v>8.27999973297119</v>
       </c>
       <c r="G2013" t="n">
-        <v>7.98297166824341</v>
+        <v>7.98297214508057</v>
       </c>
       <c r="H2013" t="n">
         <v>3829</v>
@@ -58775,7 +58775,7 @@
         <v>8.27999973297119</v>
       </c>
       <c r="G2014" t="n">
-        <v>7.98297166824341</v>
+        <v>7.98297214508057</v>
       </c>
       <c r="H2014" t="n">
         <v>8836</v>
@@ -58833,7 +58833,7 @@
         <v>8.18000030517578</v>
       </c>
       <c r="G2016" t="n">
-        <v>7.88655996322632</v>
+        <v>7.886559009552</v>
       </c>
       <c r="H2016" t="n">
         <v>7369</v>
@@ -59268,7 +59268,7 @@
         <v>8.77999973297119</v>
       </c>
       <c r="G2031" t="n">
-        <v>8.4650354385376</v>
+        <v>8.46503448486328</v>
       </c>
       <c r="H2031" t="n">
         <v>871</v>
@@ -59674,7 +59674,7 @@
         <v>8.35999965667725</v>
       </c>
       <c r="G2045" t="n">
-        <v>8.06010150909424</v>
+        <v>8.06010246276855</v>
       </c>
       <c r="H2045" t="n">
         <v>3413</v>
@@ -59732,7 +59732,7 @@
         <v>8.34000015258789</v>
       </c>
       <c r="G2047" t="n">
-        <v>8.04081916809082</v>
+        <v>8.04082012176514</v>
       </c>
       <c r="H2047" t="n">
         <v>4596</v>
@@ -59761,7 +59761,7 @@
         <v>8.23999977111816</v>
       </c>
       <c r="G2048" t="n">
-        <v>7.94440650939941</v>
+        <v>7.94440603256226</v>
       </c>
       <c r="H2048" t="n">
         <v>2879</v>
@@ -59790,7 +59790,7 @@
         <v>8.35999965667725</v>
       </c>
       <c r="G2049" t="n">
-        <v>8.06010150909424</v>
+        <v>8.06010246276855</v>
       </c>
       <c r="H2049" t="n">
         <v>5056</v>
@@ -59848,7 +59848,7 @@
         <v>8.23999977111816</v>
       </c>
       <c r="G2051" t="n">
-        <v>7.94440650939941</v>
+        <v>7.94440603256226</v>
       </c>
       <c r="H2051" t="n">
         <v>3823</v>
@@ -59906,7 +59906,7 @@
         <v>8.19999980926514</v>
       </c>
       <c r="G2053" t="n">
-        <v>7.90584182739258</v>
+        <v>7.90584135055542</v>
       </c>
       <c r="H2053" t="n">
         <v>468</v>
@@ -59935,7 +59935,7 @@
         <v>8.23999977111816</v>
       </c>
       <c r="G2054" t="n">
-        <v>7.94440650939941</v>
+        <v>7.94440603256226</v>
       </c>
       <c r="H2054" t="n">
         <v>1563</v>
@@ -59964,7 +59964,7 @@
         <v>8.10000038146973</v>
       </c>
       <c r="G2055" t="n">
-        <v>7.80942964553833</v>
+        <v>7.80942916870117</v>
       </c>
       <c r="H2055" t="n">
         <v>6727</v>
@@ -60022,7 +60022,7 @@
         <v>8.15999984741211</v>
       </c>
       <c r="G2057" t="n">
-        <v>7.86727666854858</v>
+        <v>7.86727619171143</v>
       </c>
       <c r="H2057" t="n">
         <v>3459</v>
@@ -60051,7 +60051,7 @@
         <v>8.10000038146973</v>
       </c>
       <c r="G2058" t="n">
-        <v>7.80942964553833</v>
+        <v>7.80942916870117</v>
       </c>
       <c r="H2058" t="n">
         <v>1644</v>
@@ -60167,7 +60167,7 @@
         <v>7.94000005722046</v>
       </c>
       <c r="G2062" t="n">
-        <v>7.6551685333252</v>
+        <v>7.65516901016235</v>
       </c>
       <c r="H2062" t="n">
         <v>5078</v>
@@ -60196,7 +60196,7 @@
         <v>7.88000011444092</v>
       </c>
       <c r="G2063" t="n">
-        <v>7.59732103347778</v>
+        <v>7.59732151031494</v>
       </c>
       <c r="H2063" t="n">
         <v>693</v>
@@ -60225,7 +60225,7 @@
         <v>7.94000005722046</v>
       </c>
       <c r="G2064" t="n">
-        <v>7.6551685333252</v>
+        <v>7.65516901016235</v>
       </c>
       <c r="H2064" t="n">
         <v>1017</v>
@@ -60254,7 +60254,7 @@
         <v>7.92000007629395</v>
       </c>
       <c r="G2065" t="n">
-        <v>7.63588666915894</v>
+        <v>7.63588619232178</v>
       </c>
       <c r="H2065" t="n">
         <v>1086</v>
@@ -60341,7 +60341,7 @@
         <v>7.84000015258789</v>
       </c>
       <c r="G2068" t="n">
-        <v>7.55875635147095</v>
+        <v>7.55875587463379</v>
       </c>
       <c r="H2068" t="n">
         <v>6229</v>
@@ -60544,7 +60544,7 @@
         <v>7.88000011444092</v>
       </c>
       <c r="G2075" t="n">
-        <v>7.59732103347778</v>
+        <v>7.59732151031494</v>
       </c>
       <c r="H2075" t="n">
         <v>35486</v>
@@ -60573,7 +60573,7 @@
         <v>7.88000011444092</v>
       </c>
       <c r="G2076" t="n">
-        <v>7.59732103347778</v>
+        <v>7.59732151031494</v>
       </c>
       <c r="H2076" t="n">
         <v>5618</v>
@@ -60631,7 +60631,7 @@
         <v>7.67999982833862</v>
       </c>
       <c r="G2078" t="n">
-        <v>7.40449523925781</v>
+        <v>7.40449571609497</v>
       </c>
       <c r="H2078" t="n">
         <v>4972</v>
@@ -60689,7 +60689,7 @@
         <v>7.57999992370605</v>
       </c>
       <c r="G2080" t="n">
-        <v>7.30808305740356</v>
+        <v>7.30808258056641</v>
       </c>
       <c r="H2080" t="n">
         <v>1250</v>
@@ -60834,7 +60834,7 @@
         <v>7.5</v>
       </c>
       <c r="G2085" t="n">
-        <v>7.23095321655273</v>
+        <v>7.23095273971558</v>
       </c>
       <c r="H2085" t="n">
         <v>1381</v>
@@ -60863,7 +60863,7 @@
         <v>7.5</v>
       </c>
       <c r="G2086" t="n">
-        <v>7.23095321655273</v>
+        <v>7.23095273971558</v>
       </c>
       <c r="H2086" t="n">
         <v>1336</v>
@@ -60921,7 +60921,7 @@
         <v>7.94000005722046</v>
       </c>
       <c r="G2088" t="n">
-        <v>7.6551685333252</v>
+        <v>7.65516901016235</v>
       </c>
       <c r="H2088" t="n">
         <v>4981</v>
@@ -61037,7 +61037,7 @@
         <v>7.55999994277954</v>
       </c>
       <c r="G2092" t="n">
-        <v>7.28880071640015</v>
+        <v>7.28880023956299</v>
       </c>
       <c r="H2092" t="n">
         <v>15687</v>
@@ -61269,7 +61269,7 @@
         <v>7.03999996185303</v>
       </c>
       <c r="G2100" t="n">
-        <v>6.78745460510254</v>
+        <v>6.78745412826538</v>
       </c>
       <c r="H2100" t="n">
         <v>6085</v>
@@ -61414,7 +61414,7 @@
         <v>6.82000017166138</v>
       </c>
       <c r="G2105" t="n">
-        <v>6.57534646987915</v>
+        <v>6.57534694671631</v>
       </c>
       <c r="H2105" t="n">
         <v>2244</v>
@@ -61472,7 +61472,7 @@
         <v>6.80000019073486</v>
       </c>
       <c r="G2107" t="n">
-        <v>6.55606412887573</v>
+        <v>6.55606365203857</v>
       </c>
       <c r="H2107" t="n">
         <v>36838</v>
@@ -61617,7 +61617,7 @@
         <v>6.84000015258789</v>
       </c>
       <c r="G2112" t="n">
-        <v>6.59462881088257</v>
+        <v>6.59462928771973</v>
       </c>
       <c r="H2112" t="n">
         <v>7586</v>
@@ -61820,7 +61820,7 @@
         <v>6.84000015258789</v>
       </c>
       <c r="G2119" t="n">
-        <v>6.59462881088257</v>
+        <v>6.59462928771973</v>
       </c>
       <c r="H2119" t="n">
         <v>5894</v>
@@ -61849,7 +61849,7 @@
         <v>6.98000001907349</v>
       </c>
       <c r="G2120" t="n">
-        <v>6.72960710525513</v>
+        <v>6.72960662841797</v>
       </c>
       <c r="H2120" t="n">
         <v>30669</v>
@@ -61878,7 +61878,7 @@
         <v>6.82000017166138</v>
       </c>
       <c r="G2121" t="n">
-        <v>6.57534646987915</v>
+        <v>6.57534694671631</v>
       </c>
       <c r="H2121" t="n">
         <v>25569</v>
@@ -61907,7 +61907,7 @@
         <v>6.80000019073486</v>
       </c>
       <c r="G2122" t="n">
-        <v>6.55606412887573</v>
+        <v>6.55606365203857</v>
       </c>
       <c r="H2122" t="n">
         <v>5373</v>
@@ -61994,7 +61994,7 @@
         <v>6.80000019073486</v>
       </c>
       <c r="G2125" t="n">
-        <v>6.55606412887573</v>
+        <v>6.55606365203857</v>
       </c>
       <c r="H2125" t="n">
         <v>126519</v>
@@ -62139,7 +62139,7 @@
         <v>6.80000019073486</v>
       </c>
       <c r="G2130" t="n">
-        <v>6.55606412887573</v>
+        <v>6.55606365203857</v>
       </c>
       <c r="H2130" t="n">
         <v>952</v>
@@ -62168,7 +62168,7 @@
         <v>6.84000015258789</v>
       </c>
       <c r="G2131" t="n">
-        <v>6.59462881088257</v>
+        <v>6.59462928771973</v>
       </c>
       <c r="H2131" t="n">
         <v>8908</v>
@@ -62313,7 +62313,7 @@
         <v>6.78000020980835</v>
       </c>
       <c r="G2136" t="n">
-        <v>6.53678178787231</v>
+        <v>6.53678131103516</v>
       </c>
       <c r="H2136" t="n">
         <v>35024</v>
@@ -62342,7 +62342,7 @@
         <v>6.51999998092651</v>
       </c>
       <c r="G2137" t="n">
-        <v>6.28610849380493</v>
+        <v>6.28610801696777</v>
       </c>
       <c r="H2137" t="n">
         <v>22723</v>
@@ -62429,7 +62429,7 @@
         <v>7.15999984741211</v>
       </c>
       <c r="G2140" t="n">
-        <v>6.90314912796021</v>
+        <v>6.90314960479736</v>
       </c>
       <c r="H2140" t="n">
         <v>65679</v>
@@ -62690,7 +62690,7 @@
         <v>6.98000001907349</v>
       </c>
       <c r="G2149" t="n">
-        <v>6.72960710525513</v>
+        <v>6.72960662841797</v>
       </c>
       <c r="H2149" t="n">
         <v>8144</v>
@@ -62748,7 +62748,7 @@
         <v>6.82000017166138</v>
       </c>
       <c r="G2151" t="n">
-        <v>6.57534646987915</v>
+        <v>6.57534694671631</v>
       </c>
       <c r="H2151" t="n">
         <v>6736</v>
@@ -62777,7 +62777,7 @@
         <v>6.84000015258789</v>
       </c>
       <c r="G2152" t="n">
-        <v>6.59462881088257</v>
+        <v>6.59462928771973</v>
       </c>
       <c r="H2152" t="n">
         <v>12210</v>
@@ -62806,7 +62806,7 @@
         <v>6.73999977111816</v>
       </c>
       <c r="G2153" t="n">
-        <v>6.498215675354</v>
+        <v>6.49821615219116</v>
       </c>
       <c r="H2153" t="n">
         <v>4977</v>
@@ -63154,7 +63154,7 @@
         <v>7.30000019073486</v>
       </c>
       <c r="G2165" t="n">
-        <v>7.03812789916992</v>
+        <v>7.03812742233276</v>
       </c>
       <c r="H2165" t="n">
         <v>6271</v>
@@ -74238,6 +74238,35 @@
         <v>36871</v>
       </c>
       <c r="I2547" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2548">
+      <c r="A2548" t="s">
+        <v>9</v>
+      </c>
+      <c r="B2548" s="1" t="n">
+        <v>46323.3333333333</v>
+      </c>
+      <c r="C2548" t="n">
+        <v>6.48000001907349</v>
+      </c>
+      <c r="D2548" t="n">
+        <v>6.65999984741211</v>
+      </c>
+      <c r="E2548" t="n">
+        <v>6.44000005722046</v>
+      </c>
+      <c r="F2548" t="n">
+        <v>6.57999992370605</v>
+      </c>
+      <c r="G2548" t="n">
+        <v>6.57999992370605</v>
+      </c>
+      <c r="H2548" t="n">
+        <v>14507</v>
+      </c>
+      <c r="I2548" t="s">
         <v>9</v>
       </c>
     </row>
